--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -28,12 +28,17 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,9 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,11 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B543"/>
+  <dimension ref="A1:D543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,6 +443,16 @@
           <t>price_00:00</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price_00:15</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>change_00:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,6 +463,12 @@
       <c r="B2" s="1" t="n">
         <v>70175.89999999999</v>
       </c>
+      <c r="C2" s="1" t="n">
+        <v>70406.3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.003283178413102059</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -454,6 +479,12 @@
       <c r="B3" s="1" t="n">
         <v>2048.3</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <v>2053.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.002489869648000736</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -464,6 +495,12 @@
       <c r="B4" s="1" t="n">
         <v>85.34</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.005390203890320995</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -474,6 +511,12 @@
       <c r="B5" s="1" t="n">
         <v>0.014311</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <v>0.014787</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.03326112780378723</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -484,6 +527,12 @@
       <c r="B6" s="1" t="n">
         <v>0.09227</v>
       </c>
+      <c r="C6" s="1" t="n">
+        <v>0.09263</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.00390159315053646</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -494,6 +543,12 @@
       <c r="B7" s="1" t="n">
         <v>1.3815</v>
       </c>
+      <c r="C7" s="1" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.001085776330076046</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -504,6 +559,12 @@
       <c r="B8" s="1" t="n">
         <v>36.309</v>
       </c>
+      <c r="C8" s="1" t="n">
+        <v>36.073</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-0.00649976589826206</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -514,6 +575,12 @@
       <c r="B9" s="1" t="n">
         <v>645.9</v>
       </c>
+      <c r="C9" s="1" t="n">
+        <v>648.38</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.003839603653816409</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -524,6 +591,12 @@
       <c r="B10" s="1" t="n">
         <v>15.159</v>
       </c>
+      <c r="C10" s="1" t="n">
+        <v>14.985</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-0.01147832970512575</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -534,6 +607,12 @@
       <c r="B11" s="1" t="n">
         <v>210.96</v>
       </c>
+      <c r="C11" s="1" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.00170648464163829</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -544,6 +623,12 @@
       <c r="B12" s="1" t="n">
         <v>0.0033349</v>
       </c>
+      <c r="C12" s="1" t="n">
+        <v>0.0033367</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.0005397463192300076</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -554,6 +639,12 @@
       <c r="B13" s="1" t="n">
         <v>0.03824</v>
       </c>
+      <c r="C13" s="1" t="n">
+        <v>0.03802</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0.005753138075313935</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -564,6 +655,12 @@
       <c r="B14" s="1" t="n">
         <v>2.725</v>
       </c>
+      <c r="C14" s="1" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-0.01357798165137612</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -574,6 +671,12 @@
       <c r="B15" s="1" t="n">
         <v>0.9724</v>
       </c>
+      <c r="C15" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.001645413410119225</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -584,6 +687,12 @@
       <c r="B16" s="1" t="n">
         <v>0.05776</v>
       </c>
+      <c r="C16" s="1" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.003635734072022193</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -594,6 +703,12 @@
       <c r="B17" s="1" t="n">
         <v>0.88</v>
       </c>
+      <c r="C17" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.001136363636363637</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,6 +719,12 @@
       <c r="B18" s="1" t="n">
         <v>0.2623</v>
       </c>
+      <c r="C18" s="1" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.001524971406786167</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -614,6 +735,12 @@
       <c r="B19" s="1" t="n">
         <v>0.34256</v>
       </c>
+      <c r="C19" s="1" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-0.01932508173750572</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -624,6 +751,12 @@
       <c r="B20" s="1" t="n">
         <v>9.592000000000001</v>
       </c>
+      <c r="C20" s="1" t="n">
+        <v>9.598000000000001</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.0006255212677231263</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -634,6 +767,12 @@
       <c r="B21" s="1" t="n">
         <v>198.1</v>
       </c>
+      <c r="C21" s="1" t="n">
+        <v>198.37</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.001362948006057598</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -644,6 +783,12 @@
       <c r="B22" s="1" t="n">
         <v>0.020987</v>
       </c>
+      <c r="C22" s="1" t="n">
+        <v>0.020456</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-0.02530137704293135</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -654,6 +799,12 @@
       <c r="B23" s="1" t="n">
         <v>455.21</v>
       </c>
+      <c r="C23" s="1" t="n">
+        <v>455.99</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.001713494870499395</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -664,6 +815,12 @@
       <c r="B24" s="1" t="n">
         <v>5166.08</v>
       </c>
+      <c r="C24" s="1" t="n">
+        <v>5170.76</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.0009059093161546648</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -674,6 +831,12 @@
       <c r="B25" s="1" t="n">
         <v>8.991</v>
       </c>
+      <c r="C25" s="1" t="n">
+        <v>8.997999999999999</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.0007785563341118533</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -684,6 +847,12 @@
       <c r="B26" s="1" t="n">
         <v>0.12597</v>
       </c>
+      <c r="C26" s="1" t="n">
+        <v>0.12475</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-0.009684845598158283</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -694,6 +863,12 @@
       <c r="B27" s="1" t="n">
         <v>0.0122</v>
       </c>
+      <c r="C27" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.01885245901639339</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -704,6 +879,12 @@
       <c r="B28" s="1" t="n">
         <v>1.294</v>
       </c>
+      <c r="C28" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-0.003091190108191656</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -714,6 +895,12 @@
       <c r="B29" s="1" t="n">
         <v>0.05892</v>
       </c>
+      <c r="C29" s="1" t="n">
+        <v>0.05975</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.01408689748811944</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -724,6 +911,12 @@
       <c r="B30" s="1" t="n">
         <v>1.517</v>
       </c>
+      <c r="C30" s="1" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.001318391562294003</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -734,6 +927,12 @@
       <c r="B31" s="1" t="n">
         <v>0.002052</v>
       </c>
+      <c r="C31" s="1" t="n">
+        <v>0.002035</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0.008284600389863591</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -744,6 +943,12 @@
       <c r="B32" s="1" t="n">
         <v>0.04035</v>
       </c>
+      <c r="C32" s="1" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.00247831474597281</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -754,6 +959,12 @@
       <c r="B33" s="1" t="n">
         <v>0.0983</v>
       </c>
+      <c r="C33" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-0.001017293997965441</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -764,6 +975,12 @@
       <c r="B34" s="1" t="n">
         <v>0.1045</v>
       </c>
+      <c r="C34" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.0009569377990430897</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -774,6 +991,12 @@
       <c r="B35" s="1" t="n">
         <v>0.00899</v>
       </c>
+      <c r="C35" s="1" t="n">
+        <v>0.008959999999999999</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-0.003337041156840991</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -784,6 +1007,12 @@
       <c r="B36" s="1" t="n">
         <v>0.3567</v>
       </c>
+      <c r="C36" s="1" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.002523128679562536</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -794,6 +1023,12 @@
       <c r="B37" s="1" t="n">
         <v>0.005834</v>
       </c>
+      <c r="C37" s="1" t="n">
+        <v>0.005835</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.0001714089818306707</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -804,6 +1039,12 @@
       <c r="B38" s="1" t="n">
         <v>0.26322</v>
       </c>
+      <c r="C38" s="1" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.005356735810348632</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -814,6 +1055,12 @@
       <c r="B39" s="1" t="n">
         <v>0.05089</v>
       </c>
+      <c r="C39" s="1" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>-0.007663588131263402</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -824,6 +1071,12 @@
       <c r="B40" s="1" t="n">
         <v>0.14707</v>
       </c>
+      <c r="C40" s="1" t="n">
+        <v>0.14753</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.003127762290065875</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -834,6 +1087,12 @@
       <c r="B41" s="1" t="n">
         <v>0.1665</v>
       </c>
+      <c r="C41" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.00180180180180177</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -844,6 +1103,12 @@
       <c r="B42" s="1" t="n">
         <v>111.24</v>
       </c>
+      <c r="C42" s="1" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-0.0006292700467457137</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -854,6 +1119,12 @@
       <c r="B43" s="1" t="n">
         <v>0.6269</v>
       </c>
+      <c r="C43" s="1" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>-0.004785452225235289</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -864,6 +1135,12 @@
       <c r="B44" s="1" t="n">
         <v>54.51</v>
       </c>
+      <c r="C44" s="1" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.002568336085122006</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -874,6 +1151,12 @@
       <c r="B45" s="1" t="n">
         <v>0.5114300000000001</v>
       </c>
+      <c r="C45" s="1" t="n">
+        <v>0.51711</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.01110611422873102</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -884,6 +1167,12 @@
       <c r="B46" s="1" t="n">
         <v>0.6995</v>
       </c>
+      <c r="C46" s="1" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.003573981415296564</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -894,6 +1183,12 @@
       <c r="B47" s="1" t="n">
         <v>3.898</v>
       </c>
+      <c r="C47" s="1" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-0.0007696254489482077</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -904,6 +1199,12 @@
       <c r="B48" s="1" t="n">
         <v>0.15931</v>
       </c>
+      <c r="C48" s="1" t="n">
+        <v>0.15902</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-0.001820350260498477</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -914,6 +1215,12 @@
       <c r="B49" s="1" t="n">
         <v>0.06051</v>
       </c>
+      <c r="C49" s="1" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-0.003470500743678761</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -924,6 +1231,12 @@
       <c r="B50" s="1" t="n">
         <v>0.0385</v>
       </c>
+      <c r="C50" s="1" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -934,6 +1247,12 @@
       <c r="B51" s="1" t="n">
         <v>0.35293</v>
       </c>
+      <c r="C51" s="1" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-0.07066557107641747</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -944,6 +1263,12 @@
       <c r="B52" s="1" t="n">
         <v>0.2964</v>
       </c>
+      <c r="C52" s="1" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-0.01282051282051272</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -954,6 +1279,12 @@
       <c r="B53" s="1" t="n">
         <v>0.159</v>
       </c>
+      <c r="C53" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-0.005031446540880473</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -964,6 +1295,12 @@
       <c r="B54" s="1" t="n">
         <v>0.29037</v>
       </c>
+      <c r="C54" s="1" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.0004132658332472672</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -974,6 +1311,12 @@
       <c r="B55" s="1" t="n">
         <v>0.00712</v>
       </c>
+      <c r="C55" s="1" t="n">
+        <v>0.007144</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.003370786516854015</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -984,6 +1327,12 @@
       <c r="B56" s="1" t="n">
         <v>0.02785</v>
       </c>
+      <c r="C56" s="1" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>-0.005385996409335757</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -994,6 +1343,12 @@
       <c r="B57" s="1" t="n">
         <v>0.04193</v>
       </c>
+      <c r="C57" s="1" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.001192463629859323</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1004,6 +1359,12 @@
       <c r="B58" s="1" t="n">
         <v>0.04773</v>
       </c>
+      <c r="C58" s="1" t="n">
+        <v>0.04739</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>-0.007123402472239681</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1014,6 +1375,12 @@
       <c r="B59" s="1" t="n">
         <v>1.516</v>
       </c>
+      <c r="C59" s="1" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.001978891820580404</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1024,6 +1391,12 @@
       <c r="B60" s="1" t="n">
         <v>0.00342</v>
       </c>
+      <c r="C60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.002923976608187142</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1034,6 +1407,12 @@
       <c r="B61" s="1" t="n">
         <v>0.1534</v>
       </c>
+      <c r="C61" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.002607561929595722</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1044,6 +1423,12 @@
       <c r="B62" s="1" t="n">
         <v>1.152</v>
       </c>
+      <c r="C62" s="1" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.001736111111111113</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1054,6 +1439,12 @@
       <c r="B63" s="1" t="n">
         <v>0.6972</v>
       </c>
+      <c r="C63" s="1" t="n">
+        <v>0.6984</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.001721170395869161</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1064,6 +1455,12 @@
       <c r="B64" s="1" t="n">
         <v>2.932</v>
       </c>
+      <c r="C64" s="1" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1074,6 +1471,12 @@
       <c r="B65" s="1" t="n">
         <v>0.02372</v>
       </c>
+      <c r="C65" s="1" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.004637436762225926</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1084,6 +1487,12 @@
       <c r="B66" s="1" t="n">
         <v>0.1006</v>
       </c>
+      <c r="C66" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.003976143141153196</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1094,6 +1503,12 @@
       <c r="B67" s="1" t="n">
         <v>0.00743</v>
       </c>
+      <c r="C67" s="1" t="n">
+        <v>0.007393</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>-0.004979811574697134</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1104,6 +1519,12 @@
       <c r="B68" s="1" t="n">
         <v>18.77</v>
       </c>
+      <c r="C68" s="1" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>-0.008524240809802885</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1114,6 +1535,12 @@
       <c r="B69" s="1" t="n">
         <v>0.05439</v>
       </c>
+      <c r="C69" s="1" t="n">
+        <v>0.05388</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>-0.009376723662438012</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1124,6 +1551,12 @@
       <c r="B70" s="1" t="n">
         <v>0.24</v>
       </c>
+      <c r="C70" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1134,6 +1567,12 @@
       <c r="B71" s="1" t="n">
         <v>5.753</v>
       </c>
+      <c r="C71" s="1" t="n">
+        <v>5.787</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.005909960020858649</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1144,6 +1583,12 @@
       <c r="B72" s="1" t="n">
         <v>0.002078</v>
       </c>
+      <c r="C72" s="1" t="n">
+        <v>0.002088</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.004812319538017337</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1154,6 +1599,12 @@
       <c r="B73" s="1" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="C73" s="1" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>-0.0002127659574467851</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1164,6 +1615,12 @@
       <c r="B74" s="1" t="n">
         <v>0.1203</v>
       </c>
+      <c r="C74" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.001662510390689874</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1174,6 +1631,12 @@
       <c r="B75" s="1" t="n">
         <v>353.05</v>
       </c>
+      <c r="C75" s="1" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>-0.00852570457442286</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1184,6 +1647,12 @@
       <c r="B76" s="1" t="n">
         <v>0.11958</v>
       </c>
+      <c r="C76" s="1" t="n">
+        <v>0.11726</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>-0.01940123766516142</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1194,6 +1663,12 @@
       <c r="B77" s="1" t="n">
         <v>0.06209</v>
       </c>
+      <c r="C77" s="1" t="n">
+        <v>0.06219</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0.001610565308423303</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1204,6 +1679,12 @@
       <c r="B78" s="1" t="n">
         <v>0.09397</v>
       </c>
+      <c r="C78" s="1" t="n">
+        <v>0.09376</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>-0.0022347557731191</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1214,6 +1695,12 @@
       <c r="B79" s="1" t="n">
         <v>0.4045</v>
       </c>
+      <c r="C79" s="1" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.01755253399258342</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1224,6 +1711,12 @@
       <c r="B80" s="1" t="n">
         <v>0.005976</v>
       </c>
+      <c r="C80" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.0001673360107093817</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1234,6 +1727,12 @@
       <c r="B81" s="1" t="n">
         <v>0.1026</v>
       </c>
+      <c r="C81" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.00779727095516578</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1244,6 +1743,12 @@
       <c r="B82" s="1" t="n">
         <v>0.1016</v>
       </c>
+      <c r="C82" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>-0.0009842519685038286</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1254,6 +1759,12 @@
       <c r="B83" s="1" t="n">
         <v>0.05845</v>
       </c>
+      <c r="C83" s="1" t="n">
+        <v>0.05922</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.01317365269461078</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1264,6 +1775,12 @@
       <c r="B84" s="1" t="n">
         <v>1.1024</v>
       </c>
+      <c r="C84" s="1" t="n">
+        <v>1.1029</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.00045355587808413</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1274,6 +1791,12 @@
       <c r="B85" s="1" t="n">
         <v>0.01361</v>
       </c>
+      <c r="C85" s="1" t="n">
+        <v>0.01363</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0.001469507714915443</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1284,6 +1807,12 @@
       <c r="B86" s="1" t="n">
         <v>0.0167</v>
       </c>
+      <c r="C86" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>-0.0005988023952095564</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1294,6 +1823,12 @@
       <c r="B87" s="1" t="n">
         <v>8.287000000000001</v>
       </c>
+      <c r="C87" s="1" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>-0.000844696512610287</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1304,6 +1839,12 @@
       <c r="B88" s="1" t="n">
         <v>2.1045</v>
       </c>
+      <c r="C88" s="1" t="n">
+        <v>2.1201</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0.007412687099073442</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1314,6 +1855,12 @@
       <c r="B89" s="1" t="n">
         <v>0.006929</v>
       </c>
+      <c r="C89" s="1" t="n">
+        <v>0.006906</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>-0.003319382306249163</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1324,6 +1871,12 @@
       <c r="B90" s="1" t="n">
         <v>15.23</v>
       </c>
+      <c r="C90" s="1" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.0006565988181221133</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1334,6 +1887,12 @@
       <c r="B91" s="1" t="n">
         <v>0.000225</v>
       </c>
+      <c r="C91" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>-0.008888888888888865</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1344,6 +1903,12 @@
       <c r="B92" s="1" t="n">
         <v>0.05339</v>
       </c>
+      <c r="C92" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>-0.02603483798464136</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1354,6 +1919,12 @@
       <c r="B93" s="1" t="n">
         <v>1.3134</v>
       </c>
+      <c r="C93" s="1" t="n">
+        <v>1.3156</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.001675041876047055</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1364,6 +1935,12 @@
       <c r="B94" s="1" t="n">
         <v>0.053871</v>
       </c>
+      <c r="C94" s="1" t="n">
+        <v>0.054239</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0.00683113363405172</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1374,6 +1951,12 @@
       <c r="B95" s="1" t="n">
         <v>0.2415</v>
       </c>
+      <c r="C95" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.001242236024844699</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1384,6 +1967,12 @@
       <c r="B96" s="1" t="n">
         <v>1.086</v>
       </c>
+      <c r="C96" s="1" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.0009208103130756095</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1394,6 +1983,12 @@
       <c r="B97" s="1" t="n">
         <v>0.2565</v>
       </c>
+      <c r="C97" s="1" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-0.0003898635477582417</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1404,6 +1999,12 @@
       <c r="B98" s="1" t="n">
         <v>0.5722</v>
       </c>
+      <c r="C98" s="1" t="n">
+        <v>0.5757</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0.006116742397762928</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1414,6 +2015,12 @@
       <c r="B99" s="1" t="n">
         <v>0.13972</v>
       </c>
+      <c r="C99" s="1" t="n">
+        <v>0.14044</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0.005153163469796725</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1424,6 +2031,12 @@
       <c r="B100" s="1" t="n">
         <v>0.03046</v>
       </c>
+      <c r="C100" s="1" t="n">
+        <v>0.03037</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>-0.002954694681549567</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1434,6 +2047,12 @@
       <c r="B101" s="1" t="n">
         <v>1.024</v>
       </c>
+      <c r="C101" s="1" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.001953125000000002</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1444,6 +2063,12 @@
       <c r="B102" s="1" t="n">
         <v>0.02231</v>
       </c>
+      <c r="C102" s="1" t="n">
+        <v>0.02215</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>-0.007171671896010776</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1454,6 +2079,12 @@
       <c r="B103" s="1" t="n">
         <v>0.0194</v>
       </c>
+      <c r="C103" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.001546391752577435</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1464,6 +2095,12 @@
       <c r="B104" s="1" t="n">
         <v>2.975</v>
       </c>
+      <c r="C104" s="1" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.0006722689075629512</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1474,6 +2111,12 @@
       <c r="B105" s="1" t="n">
         <v>32.2</v>
       </c>
+      <c r="C105" s="1" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>-0.001863354037267151</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1484,6 +2127,12 @@
       <c r="B106" s="1" t="n">
         <v>0.1649</v>
       </c>
+      <c r="C106" s="1" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.0006064281382655488</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1494,6 +2143,12 @@
       <c r="B107" s="1" t="n">
         <v>0.4408</v>
       </c>
+      <c r="C107" s="1" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.001588021778584343</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1504,6 +2159,12 @@
       <c r="B108" s="1" t="n">
         <v>0.3342</v>
       </c>
+      <c r="C108" s="1" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>-0.00149611011370437</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1514,6 +2175,12 @@
       <c r="B109" s="1" t="n">
         <v>0.2318</v>
       </c>
+      <c r="C109" s="1" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>-0.002588438308887045</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1524,6 +2191,12 @@
       <c r="B110" s="1" t="n">
         <v>0.01516</v>
       </c>
+      <c r="C110" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>-0.003298153034300772</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1534,6 +2207,12 @@
       <c r="B111" s="1" t="n">
         <v>1.823</v>
       </c>
+      <c r="C111" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.003291278113000552</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1544,6 +2223,12 @@
       <c r="B112" s="1" t="n">
         <v>0.03834</v>
       </c>
+      <c r="C112" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>-0.001043296817944663</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1554,6 +2239,12 @@
       <c r="B113" s="1" t="n">
         <v>4.33</v>
       </c>
+      <c r="C113" s="1" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>-0.008083140877598186</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1564,6 +2255,12 @@
       <c r="B114" s="1" t="n">
         <v>0.007718</v>
       </c>
+      <c r="C114" s="1" t="n">
+        <v>0.007489</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>-0.02967089919668308</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1574,6 +2271,12 @@
       <c r="B115" s="1" t="n">
         <v>0.09744</v>
       </c>
+      <c r="C115" s="1" t="n">
+        <v>0.09747</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.0003078817733990378</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1584,6 +2287,12 @@
       <c r="B116" s="1" t="n">
         <v>0.08259</v>
       </c>
+      <c r="C116" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>-0.0004843201356096183</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1594,6 +2303,12 @@
       <c r="B117" s="1" t="n">
         <v>0.2971</v>
       </c>
+      <c r="C117" s="1" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.004712218108381058</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1604,6 +2319,12 @@
       <c r="B118" s="1" t="n">
         <v>0.02278</v>
       </c>
+      <c r="C118" s="1" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>-0.0008779631255488434</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1614,6 +2335,12 @@
       <c r="B119" s="1" t="n">
         <v>0.1552</v>
       </c>
+      <c r="C119" s="1" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.004510309278350555</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1624,6 +2351,12 @@
       <c r="B120" s="1" t="n">
         <v>0.004394</v>
       </c>
+      <c r="C120" s="1" t="n">
+        <v>0.004181</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>-0.04847519344560776</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1634,6 +2367,12 @@
       <c r="B121" s="1" t="n">
         <v>0.4363</v>
       </c>
+      <c r="C121" s="1" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>-0.001375200550080323</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1644,6 +2383,12 @@
       <c r="B122" s="1" t="n">
         <v>0.774</v>
       </c>
+      <c r="C122" s="1" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>0.001291989664082688</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1654,6 +2399,12 @@
       <c r="B123" s="1" t="n">
         <v>0.0863</v>
       </c>
+      <c r="C123" s="1" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>-0.002317497103128687</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1664,6 +2415,12 @@
       <c r="B124" s="1" t="n">
         <v>0.01217</v>
       </c>
+      <c r="C124" s="1" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1674,6 +2431,12 @@
       <c r="B125" s="1" t="n">
         <v>0.09692000000000001</v>
       </c>
+      <c r="C125" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0.00185720181593066</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1684,6 +2447,12 @@
       <c r="B126" s="1" t="n">
         <v>0.04709</v>
       </c>
+      <c r="C126" s="1" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0.00976852834996819</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1694,6 +2463,12 @@
       <c r="B127" s="1" t="n">
         <v>3.13e-05</v>
       </c>
+      <c r="C127" s="1" t="n">
+        <v>3.13e-05</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1704,6 +2479,12 @@
       <c r="B128" s="1" t="n">
         <v>0.5789</v>
       </c>
+      <c r="C128" s="1" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>-0.003800310934530972</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1714,6 +2495,12 @@
       <c r="B129" s="1" t="n">
         <v>0.06560000000000001</v>
       </c>
+      <c r="C129" s="1" t="n">
+        <v>0.06616</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.008536585365853522</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1724,6 +2511,12 @@
       <c r="B130" s="1" t="n">
         <v>0.0005963</v>
       </c>
+      <c r="C130" s="1" t="n">
+        <v>0.000601</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0.007881938621499164</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1734,6 +2527,12 @@
       <c r="B131" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
+      <c r="C131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1744,6 +2543,12 @@
       <c r="B132" s="1" t="n">
         <v>0.3043</v>
       </c>
+      <c r="C132" s="1" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.007886953664147267</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1754,6 +2559,12 @@
       <c r="B133" s="1" t="n">
         <v>0.03394</v>
       </c>
+      <c r="C133" s="1" t="n">
+        <v>0.03366</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>-0.008249852681201991</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1764,6 +2575,12 @@
       <c r="B134" s="1" t="n">
         <v>0.14448</v>
       </c>
+      <c r="C134" s="1" t="n">
+        <v>0.14623</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>0.0121124031007752</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1774,6 +2591,12 @@
       <c r="B135" s="1" t="n">
         <v>0.0294</v>
       </c>
+      <c r="C135" s="1" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>0.0003401360544217549</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1784,6 +2607,12 @@
       <c r="B136" s="1" t="n">
         <v>27.91</v>
       </c>
+      <c r="C136" s="1" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>0.0003582945180939292</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1794,6 +2623,12 @@
       <c r="B137" s="1" t="n">
         <v>0.0004252</v>
       </c>
+      <c r="C137" s="1" t="n">
+        <v>0.0004259</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>0.001646284101599288</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1804,6 +2639,12 @@
       <c r="B138" s="1" t="n">
         <v>0.028983</v>
       </c>
+      <c r="C138" s="1" t="n">
+        <v>0.029493</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0.01759652209916158</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1814,6 +2655,12 @@
       <c r="B139" s="1" t="n">
         <v>0.09525</v>
       </c>
+      <c r="C139" s="1" t="n">
+        <v>0.09495000000000001</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>-0.003149606299212543</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1824,6 +2671,12 @@
       <c r="B140" s="1" t="n">
         <v>0.352</v>
       </c>
+      <c r="C140" s="1" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>-0.0008522727272726334</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1834,6 +2687,12 @@
       <c r="B141" s="1" t="n">
         <v>0.0272</v>
       </c>
+      <c r="C141" s="1" t="n">
+        <v>0.02723</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0.001102941176470671</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1844,6 +2703,12 @@
       <c r="B142" s="1" t="n">
         <v>0.07648000000000001</v>
       </c>
+      <c r="C142" s="1" t="n">
+        <v>0.07599</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>-0.006406903765690432</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1854,6 +2719,12 @@
       <c r="B143" s="1" t="n">
         <v>0.08812</v>
       </c>
+      <c r="C143" s="1" t="n">
+        <v>0.08846999999999999</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0.003971856559237281</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1864,6 +2735,12 @@
       <c r="B144" s="1" t="n">
         <v>0.02035</v>
       </c>
+      <c r="C144" s="1" t="n">
+        <v>0.02031</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>-0.001965601965601885</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1874,6 +2751,12 @@
       <c r="B145" s="1" t="n">
         <v>0.1139</v>
       </c>
+      <c r="C145" s="1" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0.002809482001755934</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1884,6 +2767,12 @@
       <c r="B146" s="1" t="n">
         <v>0.2997</v>
       </c>
+      <c r="C146" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0.004671338004671194</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1894,6 +2783,12 @@
       <c r="B147" s="1" t="n">
         <v>0.123</v>
       </c>
+      <c r="C147" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>-0.008130081300813016</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1904,6 +2799,12 @@
       <c r="B148" s="1" t="n">
         <v>1.959</v>
       </c>
+      <c r="C148" s="1" t="n">
+        <v>1.9457</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>-0.006789178152118473</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1914,6 +2815,12 @@
       <c r="B149" s="1" t="n">
         <v>0.06184</v>
       </c>
+      <c r="C149" s="1" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>0.004366106080206976</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1924,6 +2831,12 @@
       <c r="B150" s="1" t="n">
         <v>0.1517</v>
       </c>
+      <c r="C150" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0.01186552406064599</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1934,6 +2847,12 @@
       <c r="B151" s="1" t="n">
         <v>6.642e-05</v>
       </c>
+      <c r="C151" s="1" t="n">
+        <v>6.648e-05</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0.0009033423667569412</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1944,6 +2863,12 @@
       <c r="B152" s="1" t="n">
         <v>0.01497</v>
       </c>
+      <c r="C152" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>-0.001336005344021438</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1954,6 +2879,12 @@
       <c r="B153" s="1" t="n">
         <v>0.02082</v>
       </c>
+      <c r="C153" s="1" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>-0.001440922190201837</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1964,6 +2895,12 @@
       <c r="B154" s="1" t="n">
         <v>0.0005944</v>
       </c>
+      <c r="C154" s="1" t="n">
+        <v>0.0005955</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0.001850605652759038</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1974,6 +2911,12 @@
       <c r="B155" s="1" t="n">
         <v>0.04019</v>
       </c>
+      <c r="C155" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>-0.0007464543418759719</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1984,6 +2927,12 @@
       <c r="B156" s="1" t="n">
         <v>0.01894</v>
       </c>
+      <c r="C156" s="1" t="n">
+        <v>0.01887</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>-0.003695881731784433</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1994,6 +2943,12 @@
       <c r="B157" s="1" t="n">
         <v>0.08825</v>
       </c>
+      <c r="C157" s="1" t="n">
+        <v>0.08767999999999999</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>-0.006458923512747888</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2004,6 +2959,12 @@
       <c r="B158" s="1" t="n">
         <v>0.008286999999999999</v>
       </c>
+      <c r="C158" s="1" t="n">
+        <v>0.008246</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>-0.004947508145287724</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2014,6 +2975,12 @@
       <c r="B159" s="1" t="n">
         <v>2.494</v>
       </c>
+      <c r="C159" s="1" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>-0.001603849238171613</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2024,6 +2991,12 @@
       <c r="B160" s="1" t="n">
         <v>1.2723</v>
       </c>
+      <c r="C160" s="1" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0.000943173779768993</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2034,6 +3007,12 @@
       <c r="B161" s="1" t="n">
         <v>0.007547</v>
       </c>
+      <c r="C161" s="1" t="n">
+        <v>0.007639</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0.01219027428117134</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2044,6 +3023,12 @@
       <c r="B162" s="1" t="n">
         <v>0.004299</v>
       </c>
+      <c r="C162" s="1" t="n">
+        <v>0.004047</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>-0.05861828332170264</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2054,6 +3039,12 @@
       <c r="B163" s="1" t="n">
         <v>0.0961</v>
       </c>
+      <c r="C163" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>-0.002081165452653546</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2064,6 +3055,12 @@
       <c r="B164" s="1" t="n">
         <v>1.3741</v>
       </c>
+      <c r="C164" s="1" t="n">
+        <v>1.3772</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>0.002256022123571705</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2074,6 +3071,12 @@
       <c r="B165" s="1" t="n">
         <v>0.023017</v>
       </c>
+      <c r="C165" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>-0.003779814919407406</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2084,6 +3087,12 @@
       <c r="B166" s="1" t="n">
         <v>0.005501</v>
       </c>
+      <c r="C166" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>-0.001999636429739997</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2094,6 +3103,12 @@
       <c r="B167" s="1" t="n">
         <v>0.06657</v>
       </c>
+      <c r="C167" s="1" t="n">
+        <v>0.06587</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>-0.01051524710830714</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2104,6 +3119,12 @@
       <c r="B168" s="1" t="n">
         <v>0.0944</v>
       </c>
+      <c r="C168" s="1" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0.004237288135593195</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2114,6 +3135,12 @@
       <c r="B169" s="1" t="n">
         <v>0.03838</v>
       </c>
+      <c r="C169" s="1" t="n">
+        <v>0.03846</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0.002084418968212707</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2124,6 +3151,12 @@
       <c r="B170" s="1" t="n">
         <v>0.007094</v>
       </c>
+      <c r="C170" s="1" t="n">
+        <v>0.007098</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0.000563856780377859</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2134,6 +3167,12 @@
       <c r="B171" s="1" t="n">
         <v>0.3375</v>
       </c>
+      <c r="C171" s="1" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>0.00207407407407401</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2144,6 +3183,12 @@
       <c r="B172" s="1" t="n">
         <v>5.416</v>
       </c>
+      <c r="C172" s="1" t="n">
+        <v>5.423</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>0.001292466765140264</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2154,6 +3199,12 @@
       <c r="B173" s="1" t="n">
         <v>0.04534</v>
       </c>
+      <c r="C173" s="1" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>-0.0002205558006174707</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2164,6 +3215,12 @@
       <c r="B174" s="1" t="n">
         <v>0.03929</v>
       </c>
+      <c r="C174" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>-0.002290659200814451</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2174,6 +3231,12 @@
       <c r="B175" s="1" t="n">
         <v>0.005617</v>
       </c>
+      <c r="C175" s="1" t="n">
+        <v>0.005613</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>-0.0007121239095602037</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2184,6 +3247,12 @@
       <c r="B176" s="1" t="n">
         <v>0.00759</v>
       </c>
+      <c r="C176" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>-0.001317523056653552</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2194,6 +3263,12 @@
       <c r="B177" s="1" t="n">
         <v>1.696</v>
       </c>
+      <c r="C177" s="1" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0.01415094339622643</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2204,6 +3279,12 @@
       <c r="B178" s="1" t="n">
         <v>15.676</v>
       </c>
+      <c r="C178" s="1" t="n">
+        <v>15.627</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>-0.003125797397295196</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2214,6 +3295,12 @@
       <c r="B179" s="1" t="n">
         <v>0.312</v>
       </c>
+      <c r="C179" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>-0.003205128205128208</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2224,6 +3311,12 @@
       <c r="B180" s="1" t="n">
         <v>0.095</v>
       </c>
+      <c r="C180" s="1" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>-0.01105263157894732</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2234,6 +3327,12 @@
       <c r="B181" s="1" t="n">
         <v>0.1875</v>
       </c>
+      <c r="C181" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0.0005333333333332746</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2244,6 +3343,12 @@
       <c r="B182" s="1" t="n">
         <v>0.05979</v>
       </c>
+      <c r="C182" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>-0.005853821709315991</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2254,6 +3359,12 @@
       <c r="B183" s="1" t="n">
         <v>0.012</v>
       </c>
+      <c r="C183" s="1" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0.003333333333333342</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2264,6 +3375,12 @@
       <c r="B184" s="1" t="n">
         <v>0.02135</v>
       </c>
+      <c r="C184" s="1" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>0.0004683840749414329</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2274,6 +3391,12 @@
       <c r="B185" s="1" t="n">
         <v>0.365</v>
       </c>
+      <c r="C185" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>-0.005479452054794526</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2284,6 +3407,12 @@
       <c r="B186" s="1" t="n">
         <v>0.007671</v>
       </c>
+      <c r="C186" s="1" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>-0.0001303611002477034</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2294,6 +3423,12 @@
       <c r="B187" s="1" t="n">
         <v>0.2702</v>
       </c>
+      <c r="C187" s="1" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>-0.001850481125092526</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2304,6 +3439,12 @@
       <c r="B188" s="1" t="n">
         <v>0.04888</v>
       </c>
+      <c r="C188" s="1" t="n">
+        <v>0.04885</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>-0.0006137479541735321</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2314,6 +3455,12 @@
       <c r="B189" s="1" t="n">
         <v>0.255</v>
       </c>
+      <c r="C189" s="1" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>-0.0003921568627450548</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2324,6 +3471,12 @@
       <c r="B190" s="1" t="n">
         <v>0.5609</v>
       </c>
+      <c r="C190" s="1" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>0.002139418791228543</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2334,6 +3487,12 @@
       <c r="B191" s="1" t="n">
         <v>6.013</v>
       </c>
+      <c r="C191" s="1" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>0.0006652253450857222</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2344,6 +3503,12 @@
       <c r="B192" s="1" t="n">
         <v>0.3514</v>
       </c>
+      <c r="C192" s="1" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>-0.005976095617529854</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2354,6 +3519,12 @@
       <c r="B193" s="1" t="n">
         <v>0.0643</v>
       </c>
+      <c r="C193" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>-0.003110419906687276</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2364,6 +3535,12 @@
       <c r="B194" s="1" t="n">
         <v>0.01726</v>
       </c>
+      <c r="C194" s="1" t="n">
+        <v>0.01735</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>0.005214368482039385</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2374,6 +3551,12 @@
       <c r="B195" s="1" t="n">
         <v>0.0008718</v>
       </c>
+      <c r="C195" s="1" t="n">
+        <v>0.0008731</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>0.001491167699013509</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2384,6 +3567,12 @@
       <c r="B196" s="1" t="n">
         <v>0.001027</v>
       </c>
+      <c r="C196" s="1" t="n">
+        <v>0.001016</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>-0.01071080817916255</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2394,6 +3583,12 @@
       <c r="B197" s="1" t="n">
         <v>0.0001616</v>
       </c>
+      <c r="C197" s="1" t="n">
+        <v>0.0001615</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>-0.0006188118811881339</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2404,6 +3599,12 @@
       <c r="B198" s="1" t="n">
         <v>4.329</v>
       </c>
+      <c r="C198" s="1" t="n">
+        <v>4.339</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>0.002310002310002466</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2414,6 +3615,12 @@
       <c r="B199" s="1" t="n">
         <v>0.1619</v>
       </c>
+      <c r="C199" s="1" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>0.00432365657813469</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2424,6 +3631,12 @@
       <c r="B200" s="1" t="n">
         <v>0.023836</v>
       </c>
+      <c r="C200" s="1" t="n">
+        <v>0.023755</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>-0.003398221178050059</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2434,6 +3647,12 @@
       <c r="B201" s="1" t="n">
         <v>0.12065</v>
       </c>
+      <c r="C201" s="1" t="n">
+        <v>0.12257</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>0.01591380024865317</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2444,6 +3663,12 @@
       <c r="B202" s="1" t="n">
         <v>0.01376</v>
       </c>
+      <c r="C202" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>0.004360465116279144</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2454,6 +3679,12 @@
       <c r="B203" s="1" t="n">
         <v>0.04161</v>
       </c>
+      <c r="C203" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>-0.002643595289593823</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2464,6 +3695,12 @@
       <c r="B204" s="1" t="n">
         <v>0.02565</v>
       </c>
+      <c r="C204" s="1" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>0.0007797270955165374</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2474,6 +3711,12 @@
       <c r="B205" s="1" t="n">
         <v>0.4278</v>
       </c>
+      <c r="C205" s="1" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>0.003272557269752249</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2484,6 +3727,12 @@
       <c r="B206" s="1" t="n">
         <v>0.02292</v>
       </c>
+      <c r="C206" s="1" t="n">
+        <v>0.02291</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>-0.000436300174520052</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2494,6 +3743,12 @@
       <c r="B207" s="1" t="n">
         <v>4.155</v>
       </c>
+      <c r="C207" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>-0.00120336943441634</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2504,6 +3759,12 @@
       <c r="B208" s="1" t="n">
         <v>0.07407999999999999</v>
       </c>
+      <c r="C208" s="1" t="n">
+        <v>0.07393</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>-0.002024838012958928</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2514,6 +3775,12 @@
       <c r="B209" s="1" t="n">
         <v>0.04204</v>
       </c>
+      <c r="C209" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>0.0002378686964794511</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2524,6 +3791,12 @@
       <c r="B210" s="1" t="n">
         <v>0.1833</v>
       </c>
+      <c r="C210" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>0.001091107474086229</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2534,6 +3807,12 @@
       <c r="B211" s="1" t="n">
         <v>0.2372</v>
       </c>
+      <c r="C211" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>0.00126475548060706</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2544,6 +3823,12 @@
       <c r="B212" s="1" t="n">
         <v>0.002069</v>
       </c>
+      <c r="C212" s="1" t="n">
+        <v>0.002075</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>0.002899951667472174</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2554,6 +3839,12 @@
       <c r="B213" s="1" t="n">
         <v>0.927</v>
       </c>
+      <c r="C213" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>0.004314994606256746</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2564,6 +3855,12 @@
       <c r="B214" s="1" t="n">
         <v>0.005653</v>
       </c>
+      <c r="C214" s="1" t="n">
+        <v>0.005702</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>0.00866796391296649</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2574,6 +3871,12 @@
       <c r="B215" s="1" t="n">
         <v>0.05481</v>
       </c>
+      <c r="C215" s="1" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>-0.0003648969166210397</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2584,6 +3887,12 @@
       <c r="B216" s="1" t="n">
         <v>0.0634</v>
       </c>
+      <c r="C216" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2594,6 +3903,12 @@
       <c r="B217" s="1" t="n">
         <v>0.0921</v>
       </c>
+      <c r="C217" s="1" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>0.001085776330076035</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2604,6 +3919,12 @@
       <c r="B218" s="1" t="n">
         <v>0.27785</v>
       </c>
+      <c r="C218" s="1" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>-0.001403635054885735</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2614,6 +3935,12 @@
       <c r="B219" s="1" t="n">
         <v>0.003233</v>
       </c>
+      <c r="C219" s="1" t="n">
+        <v>0.003231</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>-0.0006186204763378489</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2624,6 +3951,12 @@
       <c r="B220" s="1" t="n">
         <v>0.999374</v>
       </c>
+      <c r="C220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2634,6 +3967,12 @@
       <c r="B221" s="1" t="n">
         <v>0.03827</v>
       </c>
+      <c r="C221" s="1" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>0.00313561536451534</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2644,6 +3983,12 @@
       <c r="B222" s="1" t="n">
         <v>0.04628</v>
       </c>
+      <c r="C222" s="1" t="n">
+        <v>0.04629</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>0.0002160760587726042</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2654,6 +3999,12 @@
       <c r="B223" s="1" t="n">
         <v>0.1049</v>
       </c>
+      <c r="C223" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2664,6 +4015,12 @@
       <c r="B224" s="1" t="n">
         <v>3.928</v>
       </c>
+      <c r="C224" s="1" t="n">
+        <v>3.938</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>0.002545824847250568</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2674,6 +4031,12 @@
       <c r="B225" s="1" t="n">
         <v>0.0009162</v>
       </c>
+      <c r="C225" s="1" t="n">
+        <v>0.0009173</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>0.001200611220257556</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2684,6 +4047,12 @@
       <c r="B226" s="1" t="n">
         <v>0.008531</v>
       </c>
+      <c r="C226" s="1" t="n">
+        <v>0.008456999999999999</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>-0.008674246864377112</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2694,6 +4063,12 @@
       <c r="B227" s="1" t="n">
         <v>0.04144</v>
       </c>
+      <c r="C227" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>-0.000965250965250926</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2704,6 +4079,12 @@
       <c r="B228" s="1" t="n">
         <v>0.0353</v>
       </c>
+      <c r="C228" s="1" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>0.003682719546742355</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2714,6 +4095,12 @@
       <c r="B229" s="1" t="n">
         <v>0.05151</v>
       </c>
+      <c r="C229" s="1" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>-0.0003882741215297842</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2724,6 +4111,12 @@
       <c r="B230" s="1" t="n">
         <v>0.001719</v>
       </c>
+      <c r="C230" s="1" t="n">
+        <v>0.001725</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>0.003490401396160517</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2734,6 +4127,12 @@
       <c r="B231" s="1" t="n">
         <v>0.0486</v>
       </c>
+      <c r="C231" s="1" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>0.003909465020576187</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2744,6 +4143,12 @@
       <c r="B232" s="1" t="n">
         <v>0.02147</v>
       </c>
+      <c r="C232" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>0.001863064741499853</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2754,6 +4159,12 @@
       <c r="B233" s="1" t="n">
         <v>0.0005832</v>
       </c>
+      <c r="C233" s="1" t="n">
+        <v>0.0005836</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>0.0006858710562414434</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2764,6 +4175,12 @@
       <c r="B234" s="1" t="n">
         <v>0.22158</v>
       </c>
+      <c r="C234" s="1" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>-0.01056051990251832</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2774,6 +4191,12 @@
       <c r="B235" s="1" t="n">
         <v>0.01396</v>
       </c>
+      <c r="C235" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>-0.01432664756446995</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2784,6 +4207,12 @@
       <c r="B236" s="1" t="n">
         <v>0.0413</v>
       </c>
+      <c r="C236" s="1" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2794,6 +4223,12 @@
       <c r="B237" s="1" t="n">
         <v>0.00416</v>
       </c>
+      <c r="C237" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>0.004807692307692321</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2804,6 +4239,12 @@
       <c r="B238" s="1" t="n">
         <v>0.0251</v>
       </c>
+      <c r="C238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>-0.007968127490039931</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2814,6 +4255,12 @@
       <c r="B239" s="1" t="n">
         <v>0.01495</v>
       </c>
+      <c r="C239" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>-0.001337792642140414</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2824,6 +4271,12 @@
       <c r="B240" s="1" t="n">
         <v>0.0003909</v>
       </c>
+      <c r="C240" s="1" t="n">
+        <v>0.0003913</v>
+      </c>
+      <c r="D240" s="2" t="n">
+        <v>0.001023279611153773</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2834,6 +4287,12 @@
       <c r="B241" s="1" t="n">
         <v>0.2655</v>
       </c>
+      <c r="C241" s="1" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>0.003389830508474621</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2844,6 +4303,12 @@
       <c r="B242" s="1" t="n">
         <v>0.07455000000000001</v>
       </c>
+      <c r="C242" s="1" t="n">
+        <v>0.07527</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>0.009657947686116679</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2854,6 +4319,12 @@
       <c r="B243" s="1" t="n">
         <v>0.01963</v>
       </c>
+      <c r="C243" s="1" t="n">
+        <v>0.01958</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>-0.002547121752419839</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2864,6 +4335,12 @@
       <c r="B244" s="1" t="n">
         <v>0.08842</v>
       </c>
+      <c r="C244" s="1" t="n">
+        <v>0.08803</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>-0.004410766794842812</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2874,6 +4351,12 @@
       <c r="B245" s="1" t="n">
         <v>1.4596</v>
       </c>
+      <c r="C245" s="1" t="n">
+        <v>1.4688</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>0.006303096738832623</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2884,6 +4367,12 @@
       <c r="B246" s="1" t="n">
         <v>0.01805</v>
       </c>
+      <c r="C246" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>-0.007202216066482085</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2894,6 +4383,12 @@
       <c r="B247" s="1" t="n">
         <v>0.006614</v>
       </c>
+      <c r="C247" s="1" t="n">
+        <v>0.006581</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>-0.004989416389476873</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2904,6 +4399,12 @@
       <c r="B248" s="1" t="n">
         <v>0.004119</v>
       </c>
+      <c r="C248" s="1" t="n">
+        <v>0.004108</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>-0.002670551104637191</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2914,6 +4415,12 @@
       <c r="B249" s="1" t="n">
         <v>0.1097</v>
       </c>
+      <c r="C249" s="1" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>0.0009115770282587875</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2924,6 +4431,12 @@
       <c r="B250" s="1" t="n">
         <v>0.03426</v>
       </c>
+      <c r="C250" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>0.0008756567425569833</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2934,6 +4447,12 @@
       <c r="B251" s="1" t="n">
         <v>0.04304</v>
       </c>
+      <c r="C251" s="1" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>0.007434944237918235</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2944,6 +4463,12 @@
       <c r="B252" s="1" t="n">
         <v>0.005744</v>
       </c>
+      <c r="C252" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>0.008704735376044515</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2954,6 +4479,12 @@
       <c r="B253" s="1" t="n">
         <v>0.01666</v>
       </c>
+      <c r="C253" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>0.001800720288115173</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -2964,6 +4495,12 @@
       <c r="B254" s="1" t="n">
         <v>0.1298</v>
       </c>
+      <c r="C254" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>0.004622496147919796</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -2974,6 +4511,12 @@
       <c r="B255" s="1" t="n">
         <v>0.02098</v>
       </c>
+      <c r="C255" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>-0.01191611058150621</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -2984,6 +4527,12 @@
       <c r="B256" s="1" t="n">
         <v>0.02095</v>
       </c>
+      <c r="C256" s="1" t="n">
+        <v>0.02097</v>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>0.0009546539379474551</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -2994,6 +4543,12 @@
       <c r="B257" s="1" t="n">
         <v>0.02566</v>
       </c>
+      <c r="C257" s="1" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>-0.007014809041309416</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3004,6 +4559,12 @@
       <c r="B258" s="1" t="n">
         <v>0.14764</v>
       </c>
+      <c r="C258" s="1" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>0.002167434299647892</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3014,6 +4575,12 @@
       <c r="B259" s="1" t="n">
         <v>0.05073</v>
       </c>
+      <c r="C259" s="1" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>0.001971220185294754</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3024,6 +4591,12 @@
       <c r="B260" s="1" t="n">
         <v>0.08272</v>
       </c>
+      <c r="C260" s="1" t="n">
+        <v>0.08268</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>-0.0004835589941972723</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3034,6 +4607,12 @@
       <c r="B261" s="1" t="n">
         <v>0.2352</v>
       </c>
+      <c r="C261" s="1" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>-0.003401360544217667</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3044,6 +4623,12 @@
       <c r="B262" s="1" t="n">
         <v>0.1428</v>
       </c>
+      <c r="C262" s="1" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>-0.002100840336134611</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3054,6 +4639,12 @@
       <c r="B263" s="1" t="n">
         <v>0.07759000000000001</v>
       </c>
+      <c r="C263" s="1" t="n">
+        <v>0.07754999999999999</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>-0.0005155303518496229</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3064,6 +4655,12 @@
       <c r="B264" s="1" t="n">
         <v>0.03875</v>
       </c>
+      <c r="C264" s="1" t="n">
+        <v>0.03846</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>-0.007483870967741899</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3074,6 +4671,12 @@
       <c r="B265" s="1" t="n">
         <v>0.0154</v>
       </c>
+      <c r="C265" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>-0.001298701298701358</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3084,6 +4687,12 @@
       <c r="B266" s="1" t="n">
         <v>0.005972</v>
       </c>
+      <c r="C266" s="1" t="n">
+        <v>0.005973</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>0.0001674480910917838</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3094,6 +4703,12 @@
       <c r="B267" s="1" t="n">
         <v>0.03708</v>
       </c>
+      <c r="C267" s="1" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>-0.001078748651564329</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3104,6 +4719,12 @@
       <c r="B268" s="1" t="n">
         <v>0.03047</v>
       </c>
+      <c r="C268" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3114,6 +4735,12 @@
       <c r="B269" s="1" t="n">
         <v>0.22842</v>
       </c>
+      <c r="C269" s="1" t="n">
+        <v>0.22748</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>-0.004115226337448665</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3124,6 +4751,12 @@
       <c r="B270" s="1" t="n">
         <v>0.923</v>
       </c>
+      <c r="C270" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>-0.004333694474539548</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3134,6 +4767,12 @@
       <c r="B271" s="1" t="n">
         <v>2.587</v>
       </c>
+      <c r="C271" s="1" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>-0.001932740626208093</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3144,6 +4783,12 @@
       <c r="B272" s="1" t="n">
         <v>0.1836</v>
       </c>
+      <c r="C272" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>0.001633986928104546</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3154,6 +4799,12 @@
       <c r="B273" s="1" t="n">
         <v>0.03068</v>
       </c>
+      <c r="C273" s="1" t="n">
+        <v>0.03076</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>0.002607561929595835</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3164,6 +4815,12 @@
       <c r="B274" s="1" t="n">
         <v>0.1886</v>
       </c>
+      <c r="C274" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>0.00742311770943803</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3174,6 +4831,12 @@
       <c r="B275" s="1" t="n">
         <v>0.06908</v>
       </c>
+      <c r="C275" s="1" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>0.001881876085697615</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3184,6 +4847,12 @@
       <c r="B276" s="1" t="n">
         <v>0.08073</v>
       </c>
+      <c r="C276" s="1" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>-0.001610305958131937</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3194,6 +4863,12 @@
       <c r="B277" s="1" t="n">
         <v>0.004259</v>
       </c>
+      <c r="C277" s="1" t="n">
+        <v>0.004238</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>-0.004930734914299175</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3204,6 +4879,12 @@
       <c r="B278" s="1" t="n">
         <v>1.552</v>
       </c>
+      <c r="C278" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>-0.001288659793814434</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3214,6 +4895,12 @@
       <c r="B279" s="1" t="n">
         <v>0.01099</v>
       </c>
+      <c r="C279" s="1" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>0.001819836214740757</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3224,6 +4911,12 @@
       <c r="B280" s="1" t="n">
         <v>0.03902</v>
       </c>
+      <c r="C280" s="1" t="n">
+        <v>0.03914</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <v>0.0030753459764224</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3234,6 +4927,12 @@
       <c r="B281" s="1" t="n">
         <v>0.08427</v>
       </c>
+      <c r="C281" s="1" t="n">
+        <v>0.08452999999999999</v>
+      </c>
+      <c r="D281" s="2" t="n">
+        <v>0.003085320992049322</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3244,6 +4943,12 @@
       <c r="B282" s="1" t="n">
         <v>0.0267</v>
       </c>
+      <c r="C282" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>-0.003745318352060032</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3254,6 +4959,12 @@
       <c r="B283" s="1" t="n">
         <v>0.07595</v>
       </c>
+      <c r="C283" s="1" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>-0.001974983541803783</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3264,6 +4975,12 @@
       <c r="B284" s="1" t="n">
         <v>0.001624</v>
       </c>
+      <c r="C284" s="1" t="n">
+        <v>0.001622</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>-0.001231527093596089</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3274,6 +4991,12 @@
       <c r="B285" s="1" t="n">
         <v>0.2016</v>
       </c>
+      <c r="C285" s="1" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>-0.0009920634920635204</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3284,6 +5007,12 @@
       <c r="B286" s="1" t="n">
         <v>0.10628</v>
       </c>
+      <c r="C286" s="1" t="n">
+        <v>0.10628</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3294,6 +5023,12 @@
       <c r="B287" s="1" t="n">
         <v>0.0171</v>
       </c>
+      <c r="C287" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>0.003508771929824621</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3304,6 +5039,12 @@
       <c r="B288" s="1" t="n">
         <v>0.01533</v>
       </c>
+      <c r="C288" s="1" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="D288" s="2" t="n">
+        <v>0.0006523157208088449</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3314,6 +5055,12 @@
       <c r="B289" s="1" t="n">
         <v>0.01602</v>
       </c>
+      <c r="C289" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="D289" s="2" t="n">
+        <v>0.006242197253433171</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3324,6 +5071,12 @@
       <c r="B290" s="1" t="n">
         <v>2.272</v>
       </c>
+      <c r="C290" s="1" t="n">
+        <v>2.269</v>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>-0.001320422535211122</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3334,6 +5087,12 @@
       <c r="B291" s="1" t="n">
         <v>0.4403</v>
       </c>
+      <c r="C291" s="1" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="D291" s="2" t="n">
+        <v>0.0004542357483533454</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3344,6 +5103,12 @@
       <c r="B292" s="1" t="n">
         <v>1.749</v>
       </c>
+      <c r="C292" s="1" t="n">
+        <v>1.741</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>-0.00457404230989137</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3354,6 +5119,12 @@
       <c r="B293" s="1" t="n">
         <v>0.05033</v>
       </c>
+      <c r="C293" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="D293" s="2" t="n">
+        <v>0.01331213987681297</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3364,6 +5135,12 @@
       <c r="B294" s="1" t="n">
         <v>0.06351</v>
       </c>
+      <c r="C294" s="1" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>-0.001102188631711551</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3374,6 +5151,12 @@
       <c r="B295" s="1" t="n">
         <v>0.0004089</v>
       </c>
+      <c r="C295" s="1" t="n">
+        <v>0.0004101</v>
+      </c>
+      <c r="D295" s="2" t="n">
+        <v>0.002934702861335228</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3384,6 +5167,12 @@
       <c r="B296" s="1" t="n">
         <v>62.31</v>
       </c>
+      <c r="C296" s="1" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="D296" s="2" t="n">
+        <v>0.002407318247472293</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3394,6 +5183,12 @@
       <c r="B297" s="1" t="n">
         <v>0.0979</v>
       </c>
+      <c r="C297" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3404,6 +5199,12 @@
       <c r="B298" s="1" t="n">
         <v>0.0955</v>
       </c>
+      <c r="C298" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>0.003141361256544447</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3414,6 +5215,12 @@
       <c r="B299" s="1" t="n">
         <v>0.09733</v>
       </c>
+      <c r="C299" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>-0.003390527072844929</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3424,6 +5231,12 @@
       <c r="B300" s="1" t="n">
         <v>0.01847</v>
       </c>
+      <c r="C300" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>0.001624255549539728</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3434,6 +5247,12 @@
       <c r="B301" s="1" t="n">
         <v>0.01333</v>
       </c>
+      <c r="C301" s="1" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>-0.0007501875468866911</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3444,6 +5263,12 @@
       <c r="B302" s="1" t="n">
         <v>0.004367</v>
       </c>
+      <c r="C302" s="1" t="n">
+        <v>0.004355</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>-0.002747881841080801</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3454,6 +5279,12 @@
       <c r="B303" s="1" t="n">
         <v>0.009299999999999999</v>
       </c>
+      <c r="C303" s="1" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>-0.001075268817204257</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -3464,6 +5295,12 @@
       <c r="B304" s="1" t="n">
         <v>4.719</v>
       </c>
+      <c r="C304" s="1" t="n">
+        <v>4.718</v>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>-0.0002119093028184645</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -3474,6 +5311,12 @@
       <c r="B305" s="1" t="n">
         <v>0.05308</v>
       </c>
+      <c r="C305" s="1" t="n">
+        <v>0.05313</v>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>0.0009419743782968066</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -3484,6 +5327,12 @@
       <c r="B306" s="1" t="n">
         <v>0.05824</v>
       </c>
+      <c r="C306" s="1" t="n">
+        <v>0.05835</v>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>0.001888736263736246</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -3494,6 +5343,12 @@
       <c r="B307" s="1" t="n">
         <v>0.1754</v>
       </c>
+      <c r="C307" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>0.001140250855188174</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -3504,6 +5359,12 @@
       <c r="B308" s="1" t="n">
         <v>0.04882</v>
       </c>
+      <c r="C308" s="1" t="n">
+        <v>0.04931</v>
+      </c>
+      <c r="D308" s="2" t="n">
+        <v>0.01003687013519044</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -3514,6 +5375,12 @@
       <c r="B309" s="1" t="n">
         <v>0.5434</v>
       </c>
+      <c r="C309" s="1" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>-0.00257637099742355</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -3524,6 +5391,12 @@
       <c r="B310" s="1" t="n">
         <v>0.00245</v>
       </c>
+      <c r="C310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>-0.004081632653061235</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -3534,6 +5407,12 @@
       <c r="B311" s="1" t="n">
         <v>0.07191</v>
       </c>
+      <c r="C311" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="D311" s="2" t="n">
+        <v>0.0002781254345708837</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -3544,6 +5423,12 @@
       <c r="B312" s="1" t="n">
         <v>0.009058999999999999</v>
       </c>
+      <c r="C312" s="1" t="n">
+        <v>0.009068</v>
+      </c>
+      <c r="D312" s="2" t="n">
+        <v>0.0009934871398609481</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -3554,6 +5439,12 @@
       <c r="B313" s="1" t="n">
         <v>0.011989</v>
       </c>
+      <c r="C313" s="1" t="n">
+        <v>0.011892</v>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>-0.008090749854032853</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -3564,6 +5455,12 @@
       <c r="B314" s="1" t="n">
         <v>0.02335</v>
       </c>
+      <c r="C314" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>-0.003854389721627401</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -3574,6 +5471,12 @@
       <c r="B315" s="1" t="n">
         <v>0.00708</v>
       </c>
+      <c r="C315" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -3584,6 +5487,12 @@
       <c r="B316" s="1" t="n">
         <v>0.2607</v>
       </c>
+      <c r="C316" s="1" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="D316" s="2" t="n">
+        <v>0.0003835826620636325</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -3594,6 +5503,12 @@
       <c r="B317" s="1" t="n">
         <v>1.12e-05</v>
       </c>
+      <c r="C317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -3604,6 +5519,12 @@
       <c r="B318" s="1" t="n">
         <v>0.052505</v>
       </c>
+      <c r="C318" s="1" t="n">
+        <v>0.052599</v>
+      </c>
+      <c r="D318" s="2" t="n">
+        <v>0.001790305685172781</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -3614,6 +5535,12 @@
       <c r="B319" s="1" t="n">
         <v>0.038</v>
       </c>
+      <c r="C319" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>-0.003421052631578899</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -3624,6 +5551,12 @@
       <c r="B320" s="1" t="n">
         <v>0.006817</v>
       </c>
+      <c r="C320" s="1" t="n">
+        <v>0.006788</v>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>-0.004254070705589024</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -3634,6 +5567,12 @@
       <c r="B321" s="1" t="n">
         <v>4.531</v>
       </c>
+      <c r="C321" s="1" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>-0.0002207018318250818</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -3644,6 +5583,12 @@
       <c r="B322" s="1" t="n">
         <v>1.918</v>
       </c>
+      <c r="C322" s="1" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>-0.00312825860271116</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -3654,6 +5599,12 @@
       <c r="B323" s="1" t="n">
         <v>0.007085</v>
       </c>
+      <c r="C323" s="1" t="n">
+        <v>0.007093</v>
+      </c>
+      <c r="D323" s="2" t="n">
+        <v>0.001129146083274551</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -3664,6 +5615,12 @@
       <c r="B324" s="1" t="n">
         <v>0.01817</v>
       </c>
+      <c r="C324" s="1" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="D324" s="2" t="n">
+        <v>0.0005503577325263106</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -3674,6 +5631,12 @@
       <c r="B325" s="1" t="n">
         <v>0.41</v>
       </c>
+      <c r="C325" s="1" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>-0.0009756097560974536</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -3684,6 +5647,12 @@
       <c r="B326" s="1" t="n">
         <v>0.007209</v>
       </c>
+      <c r="C326" s="1" t="n">
+        <v>0.007222</v>
+      </c>
+      <c r="D326" s="2" t="n">
+        <v>0.001803301428769592</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -3694,6 +5663,12 @@
       <c r="B327" s="1" t="n">
         <v>0.1914</v>
       </c>
+      <c r="C327" s="1" t="n">
+        <v>0.1916</v>
+      </c>
+      <c r="D327" s="2" t="n">
+        <v>0.001044932079414868</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -3704,6 +5679,12 @@
       <c r="B328" s="1" t="n">
         <v>0.4747</v>
       </c>
+      <c r="C328" s="1" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>-0.002949231093322124</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -3714,6 +5695,12 @@
       <c r="B329" s="1" t="n">
         <v>0.01348</v>
       </c>
+      <c r="C329" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>0.0007418397626112457</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -3724,6 +5711,12 @@
       <c r="B330" s="1" t="n">
         <v>0.1136</v>
       </c>
+      <c r="C330" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>-0.00176056338028174</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -3734,6 +5727,12 @@
       <c r="B331" s="1" t="n">
         <v>0.5941</v>
       </c>
+      <c r="C331" s="1" t="n">
+        <v>0.5961</v>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>0.003366436626830503</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -3744,6 +5743,12 @@
       <c r="B332" s="1" t="n">
         <v>0.29991</v>
       </c>
+      <c r="C332" s="1" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>-0.002300690207062198</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -3754,6 +5759,12 @@
       <c r="B333" s="1" t="n">
         <v>0.07012</v>
       </c>
+      <c r="C333" s="1" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>0.003993154592127816</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -3764,6 +5775,12 @@
       <c r="B334" s="1" t="n">
         <v>0.14773</v>
       </c>
+      <c r="C334" s="1" t="n">
+        <v>0.15099</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>0.02206728491166325</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -3774,6 +5791,12 @@
       <c r="B335" s="1" t="n">
         <v>0.1574</v>
       </c>
+      <c r="C335" s="1" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>-0.005082592121982356</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -3784,6 +5807,12 @@
       <c r="B336" s="1" t="n">
         <v>0.1739</v>
       </c>
+      <c r="C336" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>-0.001150086256469268</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -3794,6 +5823,12 @@
       <c r="B337" s="1" t="n">
         <v>0.04014</v>
       </c>
+      <c r="C337" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>-0.0007473841554559603</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -3804,6 +5839,12 @@
       <c r="B338" s="1" t="n">
         <v>0.005276</v>
       </c>
+      <c r="C338" s="1" t="n">
+        <v>0.005282</v>
+      </c>
+      <c r="D338" s="2" t="n">
+        <v>0.001137225170583762</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -3814,6 +5855,12 @@
       <c r="B339" s="1" t="n">
         <v>0.05117</v>
       </c>
+      <c r="C339" s="1" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>0.0009771350400625647</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -3824,6 +5871,12 @@
       <c r="B340" s="1" t="n">
         <v>0.15039</v>
       </c>
+      <c r="C340" s="1" t="n">
+        <v>0.15083</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>0.002925726444577405</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -3834,6 +5887,12 @@
       <c r="B341" s="1" t="n">
         <v>7.614</v>
       </c>
+      <c r="C341" s="1" t="n">
+        <v>7.588</v>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>-0.003414762280010481</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -3844,6 +5903,12 @@
       <c r="B342" s="1" t="n">
         <v>0.336</v>
       </c>
+      <c r="C342" s="1" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="D342" s="2" t="n">
+        <v>0.002380952380952284</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -3854,6 +5919,12 @@
       <c r="B343" s="1" t="n">
         <v>0.02026</v>
       </c>
+      <c r="C343" s="1" t="n">
+        <v>0.01977</v>
+      </c>
+      <c r="D343" s="3" t="n">
+        <v>-0.0241855873642646</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -3864,6 +5935,12 @@
       <c r="B344" s="1" t="n">
         <v>2.195</v>
       </c>
+      <c r="C344" s="1" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>0.0004555808656037968</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -3874,6 +5951,12 @@
       <c r="B345" s="1" t="n">
         <v>1.274</v>
       </c>
+      <c r="C345" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>-0.007064364207221443</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -3884,6 +5967,12 @@
       <c r="B346" s="1" t="n">
         <v>0.005191</v>
       </c>
+      <c r="C346" s="1" t="n">
+        <v>0.005198</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>0.001348487767289551</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -3894,6 +5983,12 @@
       <c r="B347" s="1" t="n">
         <v>0.05689</v>
       </c>
+      <c r="C347" s="1" t="n">
+        <v>0.05682</v>
+      </c>
+      <c r="D347" s="3" t="n">
+        <v>-0.001230444717876615</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -3904,6 +5999,12 @@
       <c r="B348" s="1" t="n">
         <v>0.1289</v>
       </c>
+      <c r="C348" s="1" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>-0.001551590380139472</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -3914,6 +6015,12 @@
       <c r="B349" s="1" t="n">
         <v>5217.6</v>
       </c>
+      <c r="C349" s="1" t="n">
+        <v>5223.1</v>
+      </c>
+      <c r="D349" s="2" t="n">
+        <v>0.001054124501686599</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -3924,6 +6031,12 @@
       <c r="B350" s="1" t="n">
         <v>0.02835</v>
       </c>
+      <c r="C350" s="1" t="n">
+        <v>0.02832</v>
+      </c>
+      <c r="D350" s="3" t="n">
+        <v>-0.001058201058201015</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -3934,6 +6047,12 @@
       <c r="B351" s="1" t="n">
         <v>0.001356</v>
       </c>
+      <c r="C351" s="1" t="n">
+        <v>0.001342</v>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>-0.01032448377581114</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -3944,6 +6063,12 @@
       <c r="B352" s="1" t="n">
         <v>0.01567</v>
       </c>
+      <c r="C352" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="D352" s="2" t="n">
+        <v>0.002552648372686559</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -3954,6 +6079,12 @@
       <c r="B353" s="1" t="n">
         <v>6.246</v>
       </c>
+      <c r="C353" s="1" t="n">
+        <v>6.258</v>
+      </c>
+      <c r="D353" s="2" t="n">
+        <v>0.001921229586935569</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -3964,6 +6095,12 @@
       <c r="B354" s="1" t="n">
         <v>0.2857</v>
       </c>
+      <c r="C354" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="D354" s="2" t="n">
+        <v>0.003150157507875436</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -3974,6 +6111,12 @@
       <c r="B355" s="1" t="n">
         <v>0.04158</v>
       </c>
+      <c r="C355" s="1" t="n">
+        <v>0.04152</v>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>-0.001443001443001384</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -3984,6 +6127,12 @@
       <c r="B356" s="1" t="n">
         <v>0.1147</v>
       </c>
+      <c r="C356" s="1" t="n">
+        <v>0.11377</v>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>-0.00810810810810811</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -3994,6 +6143,12 @@
       <c r="B357" s="1" t="n">
         <v>0.005209</v>
       </c>
+      <c r="C357" s="1" t="n">
+        <v>0.005211</v>
+      </c>
+      <c r="D357" s="2" t="n">
+        <v>0.0003839508542907017</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4004,6 +6159,12 @@
       <c r="B358" s="1" t="n">
         <v>0.1845</v>
       </c>
+      <c r="C358" s="1" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>0.001626016260162573</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4014,6 +6175,12 @@
       <c r="B359" s="1" t="n">
         <v>0.163</v>
       </c>
+      <c r="C359" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>-0.004907975460122669</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4024,6 +6191,12 @@
       <c r="B360" s="1" t="n">
         <v>0.08524</v>
       </c>
+      <c r="C360" s="1" t="n">
+        <v>0.08509</v>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>-0.001759737212576224</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4034,6 +6207,12 @@
       <c r="B361" s="1" t="n">
         <v>0.00776</v>
       </c>
+      <c r="C361" s="1" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="D361" s="2" t="n">
+        <v>0.02319587628865963</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4044,6 +6223,12 @@
       <c r="B362" s="1" t="n">
         <v>0.4246</v>
       </c>
+      <c r="C362" s="1" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="D362" s="2" t="n">
+        <v>0.0004710315591145396</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4054,6 +6239,12 @@
       <c r="B363" s="1" t="n">
         <v>3.662</v>
       </c>
+      <c r="C363" s="1" t="n">
+        <v>3.659</v>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>-0.0008192244675041272</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4064,6 +6255,12 @@
       <c r="B364" s="1" t="n">
         <v>0.01095</v>
       </c>
+      <c r="C364" s="1" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>-0.0009132420091323829</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4074,6 +6271,12 @@
       <c r="B365" s="1" t="n">
         <v>0.05509</v>
       </c>
+      <c r="C365" s="1" t="n">
+        <v>0.05502</v>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>-0.001270648030495564</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -4084,6 +6287,12 @@
       <c r="B366" s="1" t="n">
         <v>0.02189</v>
       </c>
+      <c r="C366" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>-0.002284148012791294</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -4094,6 +6303,12 @@
       <c r="B367" s="1" t="n">
         <v>0.001349</v>
       </c>
+      <c r="C367" s="1" t="n">
+        <v>0.001341</v>
+      </c>
+      <c r="D367" s="3" t="n">
+        <v>-0.005930318754633045</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -4104,6 +6319,12 @@
       <c r="B368" s="1" t="n">
         <v>0.2881</v>
       </c>
+      <c r="C368" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="D368" s="3" t="n">
+        <v>-0.003471017007983342</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -4114,6 +6335,12 @@
       <c r="B369" s="1" t="n">
         <v>0.01877</v>
       </c>
+      <c r="C369" s="1" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>-0.009057005860415558</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -4124,6 +6351,12 @@
       <c r="B370" s="1" t="n">
         <v>0.2014</v>
       </c>
+      <c r="C370" s="1" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="D370" s="2" t="n">
+        <v>0.003128103277060535</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -4134,6 +6367,12 @@
       <c r="B371" s="1" t="n">
         <v>0.075</v>
       </c>
+      <c r="C371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="D371" s="2" t="n">
+        <v>0.01333333333333335</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -4144,6 +6383,12 @@
       <c r="B372" s="1" t="n">
         <v>0.1048</v>
       </c>
+      <c r="C372" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="D372" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -4154,6 +6399,12 @@
       <c r="B373" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
+      <c r="C373" s="1" t="n">
+        <v>0.06629</v>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>-0.0003016136329360918</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -4164,6 +6415,12 @@
       <c r="B374" s="1" t="n">
         <v>0.00756</v>
       </c>
+      <c r="C374" s="1" t="n">
+        <v>0.007545</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>-0.001984126984127018</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -4174,6 +6431,12 @@
       <c r="B375" s="1" t="n">
         <v>0.1584</v>
       </c>
+      <c r="C375" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="D375" s="2" t="n">
+        <v>0.001262626262626124</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -4184,6 +6447,12 @@
       <c r="B376" s="1" t="n">
         <v>0.003385</v>
       </c>
+      <c r="C376" s="1" t="n">
+        <v>0.003392</v>
+      </c>
+      <c r="D376" s="2" t="n">
+        <v>0.002067946824224538</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -4194,6 +6463,12 @@
       <c r="B377" s="1" t="n">
         <v>0.0159</v>
       </c>
+      <c r="C377" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="D377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -4204,6 +6479,12 @@
       <c r="B378" s="1" t="n">
         <v>0.01119</v>
       </c>
+      <c r="C378" s="1" t="n">
+        <v>0.01126</v>
+      </c>
+      <c r="D378" s="2" t="n">
+        <v>0.006255585344057094</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -4214,6 +6495,12 @@
       <c r="B379" s="1" t="n">
         <v>0.02194</v>
       </c>
+      <c r="C379" s="1" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>-0.01458523245214224</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -4224,6 +6511,12 @@
       <c r="B380" s="1" t="n">
         <v>0.01876</v>
       </c>
+      <c r="C380" s="1" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -4234,6 +6527,12 @@
       <c r="B381" s="1" t="n">
         <v>0.1191</v>
       </c>
+      <c r="C381" s="1" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>0.001679261125105002</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -4244,6 +6543,12 @@
       <c r="B382" s="1" t="n">
         <v>0.02903</v>
       </c>
+      <c r="C382" s="1" t="n">
+        <v>0.02906</v>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>0.001033413709955177</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -4254,6 +6559,12 @@
       <c r="B383" s="1" t="n">
         <v>0.006533</v>
       </c>
+      <c r="C383" s="1" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>-0.000459207102403112</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -4264,6 +6575,12 @@
       <c r="B384" s="1" t="n">
         <v>0.02068</v>
       </c>
+      <c r="C384" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>0.02079303675048355</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -4274,6 +6591,12 @@
       <c r="B385" s="1" t="n">
         <v>2514</v>
       </c>
+      <c r="C385" s="1" t="n">
+        <v>2519</v>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>0.001988862370723946</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -4284,6 +6607,12 @@
       <c r="B386" s="1" t="n">
         <v>0.1988</v>
       </c>
+      <c r="C386" s="1" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="D386" s="3" t="n">
+        <v>-0.002012072434607703</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -4294,6 +6623,12 @@
       <c r="B387" s="1" t="n">
         <v>0.08473</v>
       </c>
+      <c r="C387" s="1" t="n">
+        <v>0.08515</v>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>0.004956921987489717</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -4304,6 +6639,12 @@
       <c r="B388" s="1" t="n">
         <v>0.005025</v>
       </c>
+      <c r="C388" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>0.0009950248756218499</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -4314,6 +6655,12 @@
       <c r="B389" s="1" t="n">
         <v>0.02191</v>
       </c>
+      <c r="C389" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>0.005020538566864558</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -4324,6 +6671,12 @@
       <c r="B390" s="1" t="n">
         <v>0.4951</v>
       </c>
+      <c r="C390" s="1" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>0.003837608563926505</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -4334,6 +6687,12 @@
       <c r="B391" s="1" t="n">
         <v>0.0005925</v>
       </c>
+      <c r="C391" s="1" t="n">
+        <v>0.0005936</v>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>0.001856540084388139</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -4344,6 +6703,12 @@
       <c r="B392" s="1" t="n">
         <v>0.05827</v>
       </c>
+      <c r="C392" s="1" t="n">
+        <v>0.05841</v>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>0.002402608546421731</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -4354,6 +6719,12 @@
       <c r="B393" s="1" t="n">
         <v>0.2677</v>
       </c>
+      <c r="C393" s="1" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>-0.004109077325364176</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -4364,6 +6735,12 @@
       <c r="B394" s="1" t="n">
         <v>0.006528</v>
       </c>
+      <c r="C394" s="1" t="n">
+        <v>0.006532</v>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>0.0006127450980391642</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -4374,6 +6751,12 @@
       <c r="B395" s="1" t="n">
         <v>0.1145</v>
       </c>
+      <c r="C395" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>0.0008733624454147509</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -4384,6 +6767,12 @@
       <c r="B396" s="1" t="n">
         <v>0.03078</v>
       </c>
+      <c r="C396" s="1" t="n">
+        <v>0.03089</v>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>0.003573749187784356</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -4394,6 +6783,12 @@
       <c r="B397" s="1" t="n">
         <v>0.1516</v>
       </c>
+      <c r="C397" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="D397" s="3" t="n">
+        <v>-0.003957783641161063</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -4404,6 +6799,12 @@
       <c r="B398" s="1" t="n">
         <v>0.003254</v>
       </c>
+      <c r="C398" s="1" t="n">
+        <v>0.003271</v>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>0.00522433927473881</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -4414,6 +6815,12 @@
       <c r="B399" s="1" t="n">
         <v>0.01881</v>
       </c>
+      <c r="C399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="D399" s="3" t="n">
+        <v>-0.004253056884635843</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -4424,6 +6831,12 @@
       <c r="B400" s="1" t="n">
         <v>0.007033</v>
       </c>
+      <c r="C400" s="1" t="n">
+        <v>0.007073</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>0.005687473339968734</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -4434,6 +6847,12 @@
       <c r="B401" s="1" t="n">
         <v>0.006862</v>
       </c>
+      <c r="C401" s="1" t="n">
+        <v>0.006905</v>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>0.006266394637131978</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -4444,6 +6863,12 @@
       <c r="B402" s="1" t="n">
         <v>0.008018000000000001</v>
       </c>
+      <c r="C402" s="1" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="D402" s="3" t="n">
+        <v>-0.0009977550511350787</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -4454,6 +6879,12 @@
       <c r="B403" s="1" t="n">
         <v>0.04785</v>
       </c>
+      <c r="C403" s="1" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>0.01274817136886116</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -4464,6 +6895,12 @@
       <c r="B404" s="1" t="n">
         <v>0.14425</v>
       </c>
+      <c r="C404" s="1" t="n">
+        <v>0.14429</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>0.0002772963604853535</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -4474,6 +6911,12 @@
       <c r="B405" s="1" t="n">
         <v>0.04274</v>
       </c>
+      <c r="C405" s="1" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>0.002105755732335045</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -4484,6 +6927,12 @@
       <c r="B406" s="1" t="n">
         <v>0.4777</v>
       </c>
+      <c r="C406" s="1" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>0.0004186728072011262</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -4494,6 +6943,12 @@
       <c r="B407" s="1" t="n">
         <v>0.0004896</v>
       </c>
+      <c r="C407" s="1" t="n">
+        <v>0.000489</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>-0.001225490196078461</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -4504,6 +6959,12 @@
       <c r="B408" s="1" t="n">
         <v>0.01224</v>
       </c>
+      <c r="C408" s="1" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>-0.007352941176470573</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -4514,6 +6975,12 @@
       <c r="B409" s="1" t="n">
         <v>0.3155</v>
       </c>
+      <c r="C409" s="1" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>0.006022187004754398</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -4524,6 +6991,12 @@
       <c r="B410" s="1" t="n">
         <v>0.04162</v>
       </c>
+      <c r="C410" s="1" t="n">
+        <v>0.04159</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>-0.0007208073041805697</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -4534,6 +7007,12 @@
       <c r="B411" s="1" t="n">
         <v>0.02971</v>
       </c>
+      <c r="C411" s="1" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>-0.0006731740154829749</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -4544,6 +7023,12 @@
       <c r="B412" s="1" t="n">
         <v>0.004557</v>
       </c>
+      <c r="C412" s="1" t="n">
+        <v>0.004558</v>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>0.0002194426157560089</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -4554,6 +7039,12 @@
       <c r="B413" s="1" t="n">
         <v>0.2529</v>
       </c>
+      <c r="C413" s="1" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>-0.00118623962040341</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -4564,6 +7055,12 @@
       <c r="B414" s="1" t="n">
         <v>1.273</v>
       </c>
+      <c r="C414" s="1" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>0.003142183817753341</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -4574,6 +7071,12 @@
       <c r="B415" s="1" t="n">
         <v>2.683</v>
       </c>
+      <c r="C415" s="1" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>0.002981736861721956</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -4584,6 +7087,12 @@
       <c r="B416" s="1" t="n">
         <v>0.03236</v>
       </c>
+      <c r="C416" s="1" t="n">
+        <v>0.03239</v>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>0.0009270704573548284</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -4594,6 +7103,12 @@
       <c r="B417" s="1" t="n">
         <v>0.03943</v>
       </c>
+      <c r="C417" s="1" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>0.005833121988333782</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -4604,6 +7119,12 @@
       <c r="B418" s="1" t="n">
         <v>0.07606</v>
       </c>
+      <c r="C418" s="1" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>0.0005259006047856741</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -4614,6 +7135,12 @@
       <c r="B419" s="1" t="n">
         <v>0.00665</v>
       </c>
+      <c r="C419" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="D419" s="3" t="n">
+        <v>-0.003007518796992489</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -4624,6 +7151,12 @@
       <c r="B420" s="1" t="n">
         <v>0.0885</v>
       </c>
+      <c r="C420" s="1" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>0.002259887005649782</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -4634,6 +7167,12 @@
       <c r="B421" s="1" t="n">
         <v>0.2391</v>
       </c>
+      <c r="C421" s="1" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>0.005855290673358363</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -4644,6 +7183,12 @@
       <c r="B422" s="1" t="n">
         <v>0.0193</v>
       </c>
+      <c r="C422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>0.005181347150259035</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -4654,6 +7199,12 @@
       <c r="B423" s="1" t="n">
         <v>0.1503</v>
       </c>
+      <c r="C423" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>-0.0006653359946772388</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -4664,6 +7215,12 @@
       <c r="B424" s="1" t="n">
         <v>0.0002108</v>
       </c>
+      <c r="C424" s="1" t="n">
+        <v>0.0002103</v>
+      </c>
+      <c r="D424" s="3" t="n">
+        <v>-0.002371916508538957</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -4674,6 +7231,12 @@
       <c r="B425" s="1" t="n">
         <v>1.236</v>
       </c>
+      <c r="C425" s="1" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="D425" s="3" t="n">
+        <v>-0.00242718446601933</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -4684,6 +7247,12 @@
       <c r="B426" s="1" t="n">
         <v>1.406</v>
       </c>
+      <c r="C426" s="1" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="D426" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -4694,6 +7263,12 @@
       <c r="B427" s="1" t="n">
         <v>0.01943</v>
       </c>
+      <c r="C427" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="D427" s="3" t="n">
+        <v>-0.00154400411734425</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -4704,6 +7279,12 @@
       <c r="B428" s="1" t="n">
         <v>0.06586</v>
       </c>
+      <c r="C428" s="1" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="D428" s="3" t="n">
+        <v>-0.0009110233829335635</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -4714,6 +7295,12 @@
       <c r="B429" s="1" t="n">
         <v>0.1327</v>
       </c>
+      <c r="C429" s="1" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>-0.001507159005275099</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -4724,6 +7311,12 @@
       <c r="B430" s="1" t="n">
         <v>0.011097</v>
       </c>
+      <c r="C430" s="1" t="n">
+        <v>0.011071</v>
+      </c>
+      <c r="D430" s="3" t="n">
+        <v>-0.00234297557898531</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -4734,6 +7327,12 @@
       <c r="B431" s="1" t="n">
         <v>0.006583</v>
       </c>
+      <c r="C431" s="1" t="n">
+        <v>0.006584</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>0.0001519064256416931</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -4744,6 +7343,12 @@
       <c r="B432" s="1" t="n">
         <v>0.001751</v>
       </c>
+      <c r="C432" s="1" t="n">
+        <v>0.001751</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -4754,6 +7359,12 @@
       <c r="B433" s="1" t="n">
         <v>0.001399</v>
       </c>
+      <c r="C433" s="1" t="n">
+        <v>0.001417</v>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>0.01286633309506791</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -4764,6 +7375,12 @@
       <c r="B434" s="1" t="n">
         <v>0.000408</v>
       </c>
+      <c r="C434" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -4774,6 +7391,12 @@
       <c r="B435" s="1" t="n">
         <v>0.12665</v>
       </c>
+      <c r="C435" s="1" t="n">
+        <v>0.12654</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>-0.0008685353335965177</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -4784,6 +7407,12 @@
       <c r="B436" s="1" t="n">
         <v>0.07736999999999999</v>
       </c>
+      <c r="C436" s="1" t="n">
+        <v>0.07747</v>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>0.001292490629442974</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -4794,6 +7423,12 @@
       <c r="B437" s="1" t="n">
         <v>0.6281</v>
       </c>
+      <c r="C437" s="1" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>0.01162235312848268</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -4804,6 +7439,12 @@
       <c r="B438" s="1" t="n">
         <v>0.04409</v>
       </c>
+      <c r="C438" s="1" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>0.000453617600363033</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -4814,6 +7455,12 @@
       <c r="B439" s="1" t="n">
         <v>0.07013</v>
       </c>
+      <c r="C439" s="1" t="n">
+        <v>0.07018000000000001</v>
+      </c>
+      <c r="D439" s="2" t="n">
+        <v>0.0007129616426637441</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -4824,6 +7471,12 @@
       <c r="B440" s="1" t="n">
         <v>0.001518</v>
       </c>
+      <c r="C440" s="1" t="n">
+        <v>0.001515</v>
+      </c>
+      <c r="D440" s="3" t="n">
+        <v>-0.001976284584980214</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -4834,6 +7487,12 @@
       <c r="B441" s="1" t="n">
         <v>0.009401</v>
       </c>
+      <c r="C441" s="1" t="n">
+        <v>0.009488</v>
+      </c>
+      <c r="D441" s="2" t="n">
+        <v>0.009254334645250535</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -4844,6 +7503,12 @@
       <c r="B442" s="1" t="n">
         <v>1.051</v>
       </c>
+      <c r="C442" s="1" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="D442" s="2" t="n">
+        <v>0.007611798287345393</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -4854,6 +7519,12 @@
       <c r="B443" s="1" t="n">
         <v>0.02214</v>
       </c>
+      <c r="C443" s="1" t="n">
+        <v>0.02223</v>
+      </c>
+      <c r="D443" s="2" t="n">
+        <v>0.004065040650406495</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -4864,6 +7535,12 @@
       <c r="B444" s="1" t="n">
         <v>0.0003811</v>
       </c>
+      <c r="C444" s="1" t="n">
+        <v>0.0003802</v>
+      </c>
+      <c r="D444" s="3" t="n">
+        <v>-0.002361584885856646</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -4874,6 +7551,12 @@
       <c r="B445" s="1" t="n">
         <v>0.03515</v>
       </c>
+      <c r="C445" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="D445" s="3" t="n">
+        <v>-0.004836415362731251</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -4884,6 +7567,12 @@
       <c r="B446" s="1" t="n">
         <v>0.08594</v>
       </c>
+      <c r="C446" s="1" t="n">
+        <v>0.08585</v>
+      </c>
+      <c r="D446" s="3" t="n">
+        <v>-0.001047242262043365</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -4894,6 +7583,12 @@
       <c r="B447" s="1" t="n">
         <v>3.246</v>
       </c>
+      <c r="C447" s="1" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="D447" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -4904,6 +7599,12 @@
       <c r="B448" s="1" t="n">
         <v>0.06387</v>
       </c>
+      <c r="C448" s="1" t="n">
+        <v>0.06387</v>
+      </c>
+      <c r="D448" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -4914,6 +7615,12 @@
       <c r="B449" s="1" t="n">
         <v>0.4883</v>
       </c>
+      <c r="C449" s="1" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="D449" s="3" t="n">
+        <v>-0.002662297767765766</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -4924,6 +7631,12 @@
       <c r="B450" s="1" t="n">
         <v>0.0376</v>
       </c>
+      <c r="C450" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="D450" s="3" t="n">
+        <v>-0.005319148936170181</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -4934,6 +7647,12 @@
       <c r="B451" s="1" t="n">
         <v>0.00544</v>
       </c>
+      <c r="C451" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="D451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -4944,6 +7663,12 @@
       <c r="B452" s="1" t="n">
         <v>0.10629</v>
       </c>
+      <c r="C452" s="1" t="n">
+        <v>0.10573</v>
+      </c>
+      <c r="D452" s="3" t="n">
+        <v>-0.005268604760560646</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -4954,6 +7679,12 @@
       <c r="B453" s="1" t="n">
         <v>0.01613</v>
       </c>
+      <c r="C453" s="1" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="D453" s="3" t="n">
+        <v>-0.004959702417854942</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -4964,6 +7695,12 @@
       <c r="B454" s="1" t="n">
         <v>2.841</v>
       </c>
+      <c r="C454" s="1" t="n">
+        <v>2.847</v>
+      </c>
+      <c r="D454" s="2" t="n">
+        <v>0.002111932418162542</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -4974,6 +7711,12 @@
       <c r="B455" s="1" t="n">
         <v>0.893</v>
       </c>
+      <c r="C455" s="1" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="D455" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -4984,6 +7727,12 @@
       <c r="B456" s="1" t="n">
         <v>2.945</v>
       </c>
+      <c r="C456" s="1" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="D456" s="3" t="n">
+        <v>-0.0006791171477079049</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -4994,6 +7743,12 @@
       <c r="B457" s="1" t="n">
         <v>0.00987</v>
       </c>
+      <c r="C457" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="D457" s="3" t="n">
+        <v>-0.00202634245187446</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -5004,6 +7759,12 @@
       <c r="B458" s="1" t="n">
         <v>0.06236</v>
       </c>
+      <c r="C458" s="1" t="n">
+        <v>0.06217</v>
+      </c>
+      <c r="D458" s="3" t="n">
+        <v>-0.003046824887748488</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -5014,6 +7775,12 @@
       <c r="B459" s="1" t="n">
         <v>0.01439</v>
       </c>
+      <c r="C459" s="1" t="n">
+        <v>0.01439</v>
+      </c>
+      <c r="D459" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -5024,6 +7791,12 @@
       <c r="B460" s="1" t="n">
         <v>0.015986</v>
       </c>
+      <c r="C460" s="1" t="n">
+        <v>0.016011</v>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>0.001563868384836777</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -5034,6 +7807,12 @@
       <c r="B461" s="1" t="n">
         <v>0.01637</v>
       </c>
+      <c r="C461" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="D461" s="2" t="n">
+        <v>0.001832620647526099</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -5044,6 +7823,12 @@
       <c r="B462" s="1" t="n">
         <v>0.0002084</v>
       </c>
+      <c r="C462" s="1" t="n">
+        <v>0.0002086</v>
+      </c>
+      <c r="D462" s="2" t="n">
+        <v>0.0009596928982725762</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -5054,6 +7839,12 @@
       <c r="B463" s="1" t="n">
         <v>0.098</v>
       </c>
+      <c r="C463" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="D463" s="2" t="n">
+        <v>0.001020408163265335</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -5064,6 +7855,12 @@
       <c r="B464" s="1" t="n">
         <v>0.02616</v>
       </c>
+      <c r="C464" s="1" t="n">
+        <v>0.02605</v>
+      </c>
+      <c r="D464" s="3" t="n">
+        <v>-0.004204892966360818</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -5074,6 +7871,12 @@
       <c r="B465" s="1" t="n">
         <v>0.01496</v>
       </c>
+      <c r="C465" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="D465" s="3" t="n">
+        <v>-0.004010695187165728</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -5084,6 +7887,12 @@
       <c r="B466" s="1" t="n">
         <v>0.05485</v>
       </c>
+      <c r="C466" s="1" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="D466" s="3" t="n">
+        <v>-0.003828623518687363</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -5094,6 +7903,12 @@
       <c r="B467" s="1" t="n">
         <v>0.03416</v>
       </c>
+      <c r="C467" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="D467" s="2" t="n">
+        <v>0.009074941451990566</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -5104,6 +7919,12 @@
       <c r="B468" s="1" t="n">
         <v>26.91</v>
       </c>
+      <c r="C468" s="1" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="D468" s="2" t="n">
+        <v>0.0003716090672612992</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -5114,6 +7935,12 @@
       <c r="B469" s="1" t="n">
         <v>0.0007455</v>
       </c>
+      <c r="C469" s="1" t="n">
+        <v>0.0007459</v>
+      </c>
+      <c r="D469" s="2" t="n">
+        <v>0.0005365526492287187</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -5124,6 +7951,12 @@
       <c r="B470" s="1" t="n">
         <v>0.873</v>
       </c>
+      <c r="C470" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D470" s="2" t="n">
+        <v>0.002290950744558994</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -5134,6 +7967,12 @@
       <c r="B471" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
+      <c r="C471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="D471" s="3" t="n">
+        <v>-0.001011122345803801</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -5144,6 +7983,12 @@
       <c r="B472" s="1" t="n">
         <v>0.04686</v>
       </c>
+      <c r="C472" s="1" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="D472" s="2" t="n">
+        <v>0.002347417840375565</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -5154,6 +7999,12 @@
       <c r="B473" s="1" t="n">
         <v>0.273</v>
       </c>
+      <c r="C473" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="D473" s="3" t="n">
+        <v>-0.0003663003663005293</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -5164,6 +8015,12 @@
       <c r="B474" s="1" t="n">
         <v>0.04334</v>
       </c>
+      <c r="C474" s="1" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="D474" s="2" t="n">
+        <v>0.006460544531610579</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -5174,6 +8031,12 @@
       <c r="B475" s="1" t="n">
         <v>0.008409</v>
       </c>
+      <c r="C475" s="1" t="n">
+        <v>0.008397999999999999</v>
+      </c>
+      <c r="D475" s="3" t="n">
+        <v>-0.001308122249970341</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -5184,6 +8047,12 @@
       <c r="B476" s="1" t="n">
         <v>0.08175</v>
       </c>
+      <c r="C476" s="1" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="D476" s="3" t="n">
+        <v>-0.0001223241590215291</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -5194,6 +8063,12 @@
       <c r="B477" s="1" t="n">
         <v>0.1354</v>
       </c>
+      <c r="C477" s="1" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="D477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -5204,6 +8079,12 @@
       <c r="B478" s="1" t="n">
         <v>0.3963</v>
       </c>
+      <c r="C478" s="1" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="D478" s="2" t="n">
+        <v>0.002775674993691622</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -5214,6 +8095,12 @@
       <c r="B479" s="1" t="n">
         <v>0.008358000000000001</v>
       </c>
+      <c r="C479" s="1" t="n">
+        <v>0.008382000000000001</v>
+      </c>
+      <c r="D479" s="2" t="n">
+        <v>0.002871500358937511</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -5224,6 +8111,12 @@
       <c r="B480" s="1" t="n">
         <v>0.01592</v>
       </c>
+      <c r="C480" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="D480" s="2" t="n">
+        <v>0.0006281407035175624</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -5234,6 +8127,12 @@
       <c r="B481" s="1" t="n">
         <v>0.07703</v>
       </c>
+      <c r="C481" s="1" t="n">
+        <v>0.07709000000000001</v>
+      </c>
+      <c r="D481" s="2" t="n">
+        <v>0.0007789173049461832</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -5244,6 +8143,12 @@
       <c r="B482" s="1" t="n">
         <v>0.05045</v>
       </c>
+      <c r="C482" s="1" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="D482" s="3" t="n">
+        <v>-0.0007928642220019498</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -5254,6 +8159,12 @@
       <c r="B483" s="1" t="n">
         <v>0.00971</v>
       </c>
+      <c r="C483" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="D483" s="3" t="n">
+        <v>-0.004119464469618961</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -5264,6 +8175,12 @@
       <c r="B484" s="1" t="n">
         <v>0.06788</v>
       </c>
+      <c r="C484" s="1" t="n">
+        <v>0.06797</v>
+      </c>
+      <c r="D484" s="2" t="n">
+        <v>0.001325869180907583</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -5274,6 +8191,12 @@
       <c r="B485" s="1" t="n">
         <v>0.0004475</v>
       </c>
+      <c r="C485" s="1" t="n">
+        <v>0.0004492</v>
+      </c>
+      <c r="D485" s="2" t="n">
+        <v>0.003798882681564338</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -5284,6 +8207,12 @@
       <c r="B486" s="1" t="n">
         <v>0.07971</v>
       </c>
+      <c r="C486" s="1" t="n">
+        <v>0.08019</v>
+      </c>
+      <c r="D486" s="2" t="n">
+        <v>0.006021829130598347</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -5294,6 +8223,12 @@
       <c r="B487" s="1" t="n">
         <v>0.000173</v>
       </c>
+      <c r="C487" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="D487" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -5304,6 +8239,12 @@
       <c r="B488" s="1" t="n">
         <v>0.08746</v>
       </c>
+      <c r="C488" s="1" t="n">
+        <v>0.08731999999999999</v>
+      </c>
+      <c r="D488" s="3" t="n">
+        <v>-0.001600731763091713</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -5314,6 +8255,12 @@
       <c r="B489" s="1" t="n">
         <v>0.0478</v>
       </c>
+      <c r="C489" s="1" t="n">
+        <v>0.04738</v>
+      </c>
+      <c r="D489" s="3" t="n">
+        <v>-0.008786610878661165</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -5324,6 +8271,12 @@
       <c r="B490" s="1" t="n">
         <v>0.03819</v>
       </c>
+      <c r="C490" s="1" t="n">
+        <v>0.03758</v>
+      </c>
+      <c r="D490" s="3" t="n">
+        <v>-0.01597276774024612</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -5334,6 +8287,12 @@
       <c r="B491" s="1" t="n">
         <v>0.07781</v>
       </c>
+      <c r="C491" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="D491" s="2" t="n">
+        <v>0.002441845521141186</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -5344,6 +8303,12 @@
       <c r="B492" s="1" t="n">
         <v>0.06328</v>
       </c>
+      <c r="C492" s="1" t="n">
+        <v>0.06327000000000001</v>
+      </c>
+      <c r="D492" s="3" t="n">
+        <v>-0.0001580278128950083</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -5354,6 +8319,12 @@
       <c r="B493" s="1" t="n">
         <v>0.00519</v>
       </c>
+      <c r="C493" s="1" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="D493" s="3" t="n">
+        <v>-0.001926782273603171</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -5364,6 +8335,12 @@
       <c r="B494" s="1" t="n">
         <v>0.2763</v>
       </c>
+      <c r="C494" s="1" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="D494" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -5374,6 +8351,12 @@
       <c r="B495" s="1" t="n">
         <v>0.06361</v>
       </c>
+      <c r="C495" s="1" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="D495" s="2" t="n">
+        <v>0.001257663889325526</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -5384,6 +8367,12 @@
       <c r="B496" s="1" t="n">
         <v>0.293</v>
       </c>
+      <c r="C496" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D496" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -5394,6 +8383,12 @@
       <c r="B497" s="1" t="n">
         <v>0.0833</v>
       </c>
+      <c r="C497" s="1" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="D497" s="3" t="n">
+        <v>-0.02304921968787521</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -5404,6 +8399,12 @@
       <c r="B498" s="1" t="n">
         <v>0.1034</v>
       </c>
+      <c r="C498" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="D498" s="3" t="n">
+        <v>-0.003868471953578447</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -5414,6 +8415,12 @@
       <c r="B499" s="1" t="n">
         <v>0.04148</v>
       </c>
+      <c r="C499" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="D499" s="3" t="n">
+        <v>-0.0007232401157184727</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -5424,6 +8431,12 @@
       <c r="B500" s="1" t="n">
         <v>0.0412</v>
       </c>
+      <c r="C500" s="1" t="n">
+        <v>0.04109</v>
+      </c>
+      <c r="D500" s="3" t="n">
+        <v>-0.002669902912621334</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -5434,6 +8447,12 @@
       <c r="B501" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
+      <c r="C501" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="D501" s="2" t="n">
+        <v>0.001004016064257057</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -5444,6 +8463,12 @@
       <c r="B502" s="1" t="n">
         <v>0.003305</v>
       </c>
+      <c r="C502" s="1" t="n">
+        <v>0.003304</v>
+      </c>
+      <c r="D502" s="3" t="n">
+        <v>-0.0003025718608169842</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -5454,6 +8479,12 @@
       <c r="B503" s="1" t="n">
         <v>0.00912</v>
       </c>
+      <c r="C503" s="1" t="n">
+        <v>0.009220000000000001</v>
+      </c>
+      <c r="D503" s="2" t="n">
+        <v>0.01096491228070188</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -5464,6 +8495,12 @@
       <c r="B504" s="1" t="n">
         <v>0.157</v>
       </c>
+      <c r="C504" s="1" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="D504" s="2" t="n">
+        <v>0.004458598726114689</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -5474,6 +8511,12 @@
       <c r="B505" s="1" t="n">
         <v>0.131</v>
       </c>
+      <c r="C505" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="D505" s="2" t="n">
+        <v>0.0007633587786258701</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -5484,6 +8527,12 @@
       <c r="B506" s="1" t="n">
         <v>0.01691</v>
       </c>
+      <c r="C506" s="1" t="n">
+        <v>0.01688</v>
+      </c>
+      <c r="D506" s="3" t="n">
+        <v>-0.00177409816676536</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -5494,6 +8543,12 @@
       <c r="B507" s="1" t="n">
         <v>0.00289</v>
       </c>
+      <c r="C507" s="1" t="n">
+        <v>0.002894</v>
+      </c>
+      <c r="D507" s="2" t="n">
+        <v>0.001384083044982582</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -5504,6 +8559,12 @@
       <c r="B508" s="1" t="n">
         <v>2.192</v>
       </c>
+      <c r="C508" s="1" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="D508" s="2" t="n">
+        <v>0.002737226277372164</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -5514,6 +8575,12 @@
       <c r="B509" s="1" t="n">
         <v>0.05524</v>
       </c>
+      <c r="C509" s="1" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="D509" s="3" t="n">
+        <v>-0.0003620564808109918</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -5524,6 +8591,12 @@
       <c r="B510" s="1" t="n">
         <v>0.02934</v>
       </c>
+      <c r="C510" s="1" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="D510" s="3" t="n">
+        <v>-0.001363326516700813</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -5534,6 +8607,12 @@
       <c r="B511" s="1" t="n">
         <v>0.04047</v>
       </c>
+      <c r="C511" s="1" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="D511" s="3" t="n">
+        <v>-0.002718062762540128</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -5544,6 +8623,12 @@
       <c r="B512" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
+      <c r="C512" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -5554,6 +8639,12 @@
       <c r="B513" s="1" t="n">
         <v>0.014814</v>
       </c>
+      <c r="C513" s="1" t="n">
+        <v>0.014809</v>
+      </c>
+      <c r="D513" s="3" t="n">
+        <v>-0.000337518563521097</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -5564,6 +8655,12 @@
       <c r="B514" s="1" t="n">
         <v>0.1742</v>
       </c>
+      <c r="C514" s="1" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="D514" s="2" t="n">
+        <v>0.0005740528128588792</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -5574,6 +8671,12 @@
       <c r="B515" s="1" t="n">
         <v>0.1072</v>
       </c>
+      <c r="C515" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="D515" s="2" t="n">
+        <v>0.002798507462686518</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -5584,6 +8687,12 @@
       <c r="B516" s="1" t="n">
         <v>0.00265</v>
       </c>
+      <c r="C516" s="1" t="n">
+        <v>0.00264</v>
+      </c>
+      <c r="D516" s="3" t="n">
+        <v>-0.003773584905660387</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -5594,6 +8703,12 @@
       <c r="B517" s="1" t="n">
         <v>0.007703</v>
       </c>
+      <c r="C517" s="1" t="n">
+        <v>0.007681</v>
+      </c>
+      <c r="D517" s="3" t="n">
+        <v>-0.00285603011813572</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -5604,6 +8719,12 @@
       <c r="B518" s="1" t="n">
         <v>0.01531</v>
       </c>
+      <c r="C518" s="1" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="D518" s="2" t="n">
+        <v>0.003919007184846459</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -5614,6 +8735,12 @@
       <c r="B519" s="1" t="n">
         <v>0.004116</v>
       </c>
+      <c r="C519" s="1" t="n">
+        <v>0.004106</v>
+      </c>
+      <c r="D519" s="3" t="n">
+        <v>-0.002429543245869678</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -5624,6 +8751,12 @@
       <c r="B520" s="1" t="n">
         <v>0.001162</v>
       </c>
+      <c r="C520" s="1" t="n">
+        <v>0.00116</v>
+      </c>
+      <c r="D520" s="3" t="n">
+        <v>-0.001721170395869233</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -5634,6 +8767,12 @@
       <c r="B521" s="1" t="n">
         <v>0.01346</v>
       </c>
+      <c r="C521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="D521" s="3" t="n">
+        <v>-0.009658246656760766</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -5644,6 +8783,12 @@
       <c r="B522" s="1" t="n">
         <v>0.6846</v>
       </c>
+      <c r="C522" s="1" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="D522" s="2" t="n">
+        <v>0.002044989775051224</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -5654,6 +8799,12 @@
       <c r="B523" s="1" t="n">
         <v>0.07013999999999999</v>
       </c>
+      <c r="C523" s="1" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="D523" s="3" t="n">
+        <v>-0.004847447961220318</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -5664,6 +8815,12 @@
       <c r="B524" s="1" t="n">
         <v>0.01153</v>
       </c>
+      <c r="C524" s="1" t="n">
+        <v>0.01155</v>
+      </c>
+      <c r="D524" s="2" t="n">
+        <v>0.001734605377276599</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -5674,6 +8831,12 @@
       <c r="B525" s="1" t="n">
         <v>0.01634</v>
       </c>
+      <c r="C525" s="1" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="D525" s="2" t="n">
+        <v>0.002447980416156571</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -5684,6 +8847,12 @@
       <c r="B526" s="1" t="n">
         <v>0.1362</v>
       </c>
+      <c r="C526" s="1" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="D526" s="3" t="n">
+        <v>-0.001027900146842887</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -5694,6 +8863,12 @@
       <c r="B527" s="1" t="n">
         <v>0.04288</v>
       </c>
+      <c r="C527" s="1" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="D527" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -5704,6 +8879,12 @@
       <c r="B528" s="1" t="n">
         <v>0.2717</v>
       </c>
+      <c r="C528" s="1" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="D528" s="3" t="n">
+        <v>-0.00147221199852783</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -5714,6 +8895,12 @@
       <c r="B529" s="1" t="n">
         <v>0.0007208</v>
       </c>
+      <c r="C529" s="1" t="n">
+        <v>0.0007206</v>
+      </c>
+      <c r="D529" s="3" t="n">
+        <v>-0.0002774694783573875</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -5724,6 +8911,12 @@
       <c r="B530" s="1" t="n">
         <v>0.004174</v>
       </c>
+      <c r="C530" s="1" t="n">
+        <v>0.004171</v>
+      </c>
+      <c r="D530" s="3" t="n">
+        <v>-0.0007187350263535053</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -5734,6 +8927,12 @@
       <c r="B531" s="1" t="n">
         <v>1.306</v>
       </c>
+      <c r="C531" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="D531" s="3" t="n">
+        <v>-0.0007656967840735926</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -5744,6 +8943,12 @@
       <c r="B532" s="1" t="n">
         <v>0.1182</v>
       </c>
+      <c r="C532" s="1" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="D532" s="2" t="n">
+        <v>0.0008460236886633068</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -5754,6 +8959,12 @@
       <c r="B533" s="1" t="n">
         <v>0.05329</v>
       </c>
+      <c r="C533" s="1" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="D533" s="3" t="n">
+        <v>-0.002814787014449191</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -5764,6 +8975,12 @@
       <c r="B534" s="1" t="n">
         <v>0.1503</v>
       </c>
+      <c r="C534" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="D534" s="2" t="n">
+        <v>0.001996007984032086</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -5774,6 +8991,12 @@
       <c r="B535" s="1" t="n">
         <v>0.01704</v>
       </c>
+      <c r="C535" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="D535" s="3" t="n">
+        <v>-0.001173708920187746</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -5784,6 +9007,12 @@
       <c r="B536" s="1" t="n">
         <v>0.004951</v>
       </c>
+      <c r="C536" s="1" t="n">
+        <v>0.004968</v>
+      </c>
+      <c r="D536" s="2" t="n">
+        <v>0.003433649767723798</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -5794,6 +9023,12 @@
       <c r="B537" s="1" t="n">
         <v>0.2901</v>
       </c>
+      <c r="C537" s="1" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="D537" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -5804,6 +9039,12 @@
       <c r="B538" s="1" t="n">
         <v>0.01316</v>
       </c>
+      <c r="C538" s="1" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="D538" s="3" t="n">
+        <v>-0.0007598784194528566</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -5814,6 +9055,12 @@
       <c r="B539" s="1" t="n">
         <v>0.02448</v>
       </c>
+      <c r="C539" s="1" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="D539" s="3" t="n">
+        <v>-0.001225490196078381</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -5824,6 +9071,12 @@
       <c r="B540" s="1" t="n">
         <v>0.05666</v>
       </c>
+      <c r="C540" s="1" t="n">
+        <v>0.05671</v>
+      </c>
+      <c r="D540" s="2" t="n">
+        <v>0.0008824567596188039</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -5834,6 +9087,12 @@
       <c r="B541" s="1" t="n">
         <v>0.0116</v>
       </c>
+      <c r="C541" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="D541" s="3" t="n">
+        <v>-0.008620689655172362</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -5844,6 +9103,12 @@
       <c r="B542" s="1" t="n">
         <v>1.1e-05</v>
       </c>
+      <c r="C542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="D542" s="2" t="n">
+        <v>0.009090909090909158</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -5853,6 +9118,12 @@
       </c>
       <c r="B543" s="1" t="n">
         <v>0.003671</v>
+      </c>
+      <c r="C543" s="1" t="n">
+        <v>0.003669</v>
+      </c>
+      <c r="D543" s="3" t="n">
+        <v>-0.0005448106782892487</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,13 +423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +455,16 @@
           <t>change_00:15</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price_00:30</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>change_00:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +481,12 @@
       <c r="D2" s="2" t="n">
         <v>0.003283178413102059</v>
       </c>
+      <c r="E2" s="1" t="n">
+        <v>70410.60000000001</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6.107408001844878e-05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +503,12 @@
       <c r="D3" s="2" t="n">
         <v>0.002489869648000736</v>
       </c>
+      <c r="E3" s="1" t="n">
+        <v>2054.9</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.0007304957631245738</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -501,6 +525,12 @@
       <c r="D4" s="2" t="n">
         <v>0.005390203890320995</v>
       </c>
+      <c r="E4" s="1" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.0004662004662005391</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +547,12 @@
       <c r="D5" s="2" t="n">
         <v>0.03326112780378723</v>
       </c>
+      <c r="E5" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.01778589301413399</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -533,6 +569,12 @@
       <c r="D6" s="2" t="n">
         <v>0.00390159315053646</v>
       </c>
+      <c r="E6" s="1" t="n">
+        <v>0.09252000000000001</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-0.001187520241822293</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,6 +591,12 @@
       <c r="D7" s="2" t="n">
         <v>0.001085776330076046</v>
       </c>
+      <c r="E7" s="1" t="n">
+        <v>1.3832</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.0001446131597975256</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -565,6 +613,12 @@
       <c r="D8" s="3" t="n">
         <v>-0.00649976589826206</v>
       </c>
+      <c r="E8" s="1" t="n">
+        <v>36.319</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.006819504892856214</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,6 +635,12 @@
       <c r="D9" s="2" t="n">
         <v>0.003839603653816409</v>
       </c>
+      <c r="E9" s="1" t="n">
+        <v>647.45</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-0.00143434405749707</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -597,6 +657,12 @@
       <c r="D10" s="3" t="n">
         <v>-0.01147832970512575</v>
       </c>
+      <c r="E10" s="1" t="n">
+        <v>14.857</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-0.008541875208541883</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -613,6 +679,12 @@
       <c r="D11" s="3" t="n">
         <v>-0.00170648464163829</v>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>209.45</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.005460588793922154</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -629,6 +701,12 @@
       <c r="D12" s="2" t="n">
         <v>0.0005397463192300076</v>
       </c>
+      <c r="E12" s="1" t="n">
+        <v>0.0033352</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-0.000449545958581892</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -645,6 +723,12 @@
       <c r="D13" s="3" t="n">
         <v>-0.005753138075313935</v>
       </c>
+      <c r="E13" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0.0247238295633876</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -661,6 +745,12 @@
       <c r="D14" s="3" t="n">
         <v>-0.01357798165137612</v>
       </c>
+      <c r="E14" s="1" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-0.01636904761904763</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -677,6 +767,12 @@
       <c r="D15" s="2" t="n">
         <v>0.001645413410119225</v>
       </c>
+      <c r="E15" s="1" t="n">
+        <v>0.9719</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-0.00215605749486652</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -693,6 +789,12 @@
       <c r="D16" s="2" t="n">
         <v>0.003635734072022193</v>
       </c>
+      <c r="E16" s="1" t="n">
+        <v>0.05665</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.02277039848197347</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -709,6 +811,12 @@
       <c r="D17" s="2" t="n">
         <v>0.001136363636363637</v>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0.001135073779795688</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -725,6 +833,12 @@
       <c r="D18" s="2" t="n">
         <v>0.001524971406786167</v>
       </c>
+      <c r="E18" s="1" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-0.001903311762466694</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -741,6 +855,12 @@
       <c r="D19" s="3" t="n">
         <v>-0.01932508173750572</v>
       </c>
+      <c r="E19" s="1" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.003542299220098734</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -757,6 +877,12 @@
       <c r="D20" s="2" t="n">
         <v>0.0006255212677231263</v>
       </c>
+      <c r="E20" s="1" t="n">
+        <v>9.599</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.0001041883725775626</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -773,6 +899,12 @@
       <c r="D21" s="2" t="n">
         <v>0.001362948006057598</v>
       </c>
+      <c r="E21" s="1" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.008116146594747116</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -789,6 +921,12 @@
       <c r="D22" s="3" t="n">
         <v>-0.02530137704293135</v>
       </c>
+      <c r="E22" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.01730543605788034</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -805,6 +943,12 @@
       <c r="D23" s="2" t="n">
         <v>0.001713494870499395</v>
       </c>
+      <c r="E23" s="1" t="n">
+        <v>455.77</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-0.00048246672076148</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -821,6 +965,12 @@
       <c r="D24" s="2" t="n">
         <v>0.0009059093161546648</v>
       </c>
+      <c r="E24" s="1" t="n">
+        <v>5165.64</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.0009901832612613794</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -837,6 +987,12 @@
       <c r="D25" s="2" t="n">
         <v>0.0007785563341118533</v>
       </c>
+      <c r="E25" s="1" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.000889086463658493</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -853,6 +1009,12 @@
       <c r="D26" s="3" t="n">
         <v>-0.009684845598158283</v>
       </c>
+      <c r="E26" s="1" t="n">
+        <v>0.12488</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.001042084168336714</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -869,6 +1031,12 @@
       <c r="D27" s="2" t="n">
         <v>0.01885245901639339</v>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.005631536604987982</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -885,6 +1053,12 @@
       <c r="D28" s="3" t="n">
         <v>-0.003091190108191656</v>
       </c>
+      <c r="E28" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.001550387596899226</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -901,6 +1075,12 @@
       <c r="D29" s="2" t="n">
         <v>0.01408689748811944</v>
       </c>
+      <c r="E29" s="1" t="n">
+        <v>0.05851</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.02075313807531378</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -917,6 +1097,12 @@
       <c r="D30" s="2" t="n">
         <v>0.001318391562294003</v>
       </c>
+      <c r="E30" s="1" t="n">
+        <v>1.518</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-0.000658327847267867</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -933,6 +1119,12 @@
       <c r="D31" s="3" t="n">
         <v>-0.008284600389863591</v>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0.00687960687960694</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -949,6 +1141,12 @@
       <c r="D32" s="2" t="n">
         <v>0.00247831474597281</v>
       </c>
+      <c r="E32" s="1" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-0.004449938195302833</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -965,6 +1163,12 @@
       <c r="D33" s="3" t="n">
         <v>-0.001017293997965441</v>
       </c>
+      <c r="E33" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>-0.003054989816700557</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -981,6 +1185,12 @@
       <c r="D34" s="2" t="n">
         <v>0.0009569377990430897</v>
       </c>
+      <c r="E34" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-0.001912045889101261</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -997,6 +1207,12 @@
       <c r="D35" s="3" t="n">
         <v>-0.003337041156840991</v>
       </c>
+      <c r="E35" s="1" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.0122767857142858</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1013,6 +1229,12 @@
       <c r="D36" s="2" t="n">
         <v>0.002523128679562536</v>
       </c>
+      <c r="E36" s="1" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>-0.002796420581655484</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1029,6 +1251,12 @@
       <c r="D37" s="2" t="n">
         <v>0.0001714089818306707</v>
       </c>
+      <c r="E37" s="1" t="n">
+        <v>0.005805</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>-0.005141388174807137</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1045,6 +1273,12 @@
       <c r="D38" s="2" t="n">
         <v>0.005356735810348632</v>
       </c>
+      <c r="E38" s="1" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>-0.004572421872047723</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1061,6 +1295,12 @@
       <c r="D39" s="3" t="n">
         <v>-0.007663588131263402</v>
       </c>
+      <c r="E39" s="1" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0.003564356435643556</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1077,6 +1317,12 @@
       <c r="D40" s="2" t="n">
         <v>0.003127762290065875</v>
       </c>
+      <c r="E40" s="1" t="n">
+        <v>0.14682</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>-0.004812580492103223</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1093,6 +1339,12 @@
       <c r="D41" s="2" t="n">
         <v>0.00180180180180177</v>
       </c>
+      <c r="E41" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.002398081534772085</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1109,6 +1361,12 @@
       <c r="D42" s="3" t="n">
         <v>-0.0006292700467457137</v>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>111.23</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.0005397139516056694</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1125,6 +1383,12 @@
       <c r="D43" s="3" t="n">
         <v>-0.004785452225235289</v>
       </c>
+      <c r="E43" s="1" t="n">
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0.04135278089437417</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1141,6 +1405,12 @@
       <c r="D44" s="2" t="n">
         <v>0.002568336085122006</v>
       </c>
+      <c r="E44" s="1" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.0001829826166513817</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1157,6 +1427,12 @@
       <c r="D45" s="2" t="n">
         <v>0.01110611422873102</v>
       </c>
+      <c r="E45" s="1" t="n">
+        <v>0.5204299999999999</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.006420297422211889</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1173,6 +1449,12 @@
       <c r="D46" s="2" t="n">
         <v>0.003573981415296564</v>
       </c>
+      <c r="E46" s="1" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-0.0002849002849002535</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1189,6 +1471,12 @@
       <c r="D47" s="3" t="n">
         <v>-0.0007696254489482077</v>
       </c>
+      <c r="E47" s="1" t="n">
+        <v>3.893</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>-0.0005134788189987738</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1205,6 +1493,12 @@
       <c r="D48" s="3" t="n">
         <v>-0.001820350260498477</v>
       </c>
+      <c r="E48" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>-0.002012325493648516</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1221,6 +1515,12 @@
       <c r="D49" s="3" t="n">
         <v>-0.003470500743678761</v>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1237,6 +1537,12 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E50" s="1" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-0.002597402597402672</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1253,6 +1559,12 @@
       <c r="D51" s="3" t="n">
         <v>-0.07066557107641747</v>
       </c>
+      <c r="E51" s="1" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0.0279581694563859</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1269,6 +1581,12 @@
       <c r="D52" s="3" t="n">
         <v>-0.01282051282051272</v>
       </c>
+      <c r="E52" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-0.01127819548872189</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1285,6 +1603,12 @@
       <c r="D53" s="3" t="n">
         <v>-0.005031446540880473</v>
       </c>
+      <c r="E53" s="1" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>-0.004424778761061986</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1301,6 +1625,12 @@
       <c r="D54" s="2" t="n">
         <v>0.0004132658332472672</v>
       </c>
+      <c r="E54" s="1" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>-0.0001032737787876691</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1317,6 +1647,12 @@
       <c r="D55" s="2" t="n">
         <v>0.003370786516854015</v>
       </c>
+      <c r="E55" s="1" t="n">
+        <v>0.007123</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>-0.002939529675251986</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1333,6 +1669,12 @@
       <c r="D56" s="3" t="n">
         <v>-0.005385996409335757</v>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>0.02775</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.0018050541516246</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1349,6 +1691,12 @@
       <c r="D57" s="2" t="n">
         <v>0.001192463629859323</v>
       </c>
+      <c r="E57" s="1" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>-0.001429252024773809</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1365,6 +1713,12 @@
       <c r="D58" s="3" t="n">
         <v>-0.007123402472239681</v>
       </c>
+      <c r="E58" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>-0.02553281282971097</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1381,6 +1735,12 @@
       <c r="D59" s="2" t="n">
         <v>0.001978891820580404</v>
       </c>
+      <c r="E59" s="1" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-0.001974983541803747</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1397,6 +1757,12 @@
       <c r="D60" s="2" t="n">
         <v>0.002923976608187142</v>
       </c>
+      <c r="E60" s="1" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-0.005830903790087479</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1413,6 +1779,12 @@
       <c r="D61" s="2" t="n">
         <v>0.002607561929595722</v>
       </c>
+      <c r="E61" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1429,6 +1801,12 @@
       <c r="D62" s="2" t="n">
         <v>0.001736111111111113</v>
       </c>
+      <c r="E62" s="1" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1445,6 +1823,12 @@
       <c r="D63" s="2" t="n">
         <v>0.001721170395869161</v>
       </c>
+      <c r="E63" s="1" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-0.004725085910652877</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1461,6 +1845,12 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E64" s="1" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1477,6 +1867,12 @@
       <c r="D65" s="2" t="n">
         <v>0.004637436762225926</v>
       </c>
+      <c r="E65" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0.003357112882920697</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1493,6 +1889,12 @@
       <c r="D66" s="2" t="n">
         <v>0.003976143141153196</v>
       </c>
+      <c r="E66" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>-0.001980198019802037</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1509,6 +1911,12 @@
       <c r="D67" s="3" t="n">
         <v>-0.004979811574697134</v>
       </c>
+      <c r="E67" s="1" t="n">
+        <v>0.007383</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>-0.001352630867036448</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1525,6 +1933,12 @@
       <c r="D68" s="3" t="n">
         <v>-0.008524240809802885</v>
       </c>
+      <c r="E68" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>-0.01182160128962917</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1541,6 +1955,12 @@
       <c r="D69" s="3" t="n">
         <v>-0.009376723662438012</v>
       </c>
+      <c r="E69" s="1" t="n">
+        <v>0.05399</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.002041573867854602</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1557,6 +1977,12 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>-0.008333333333333342</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1573,6 +1999,12 @@
       <c r="D71" s="2" t="n">
         <v>0.005909960020858649</v>
       </c>
+      <c r="E71" s="1" t="n">
+        <v>5.744</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>-0.007430447554864377</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1589,6 +2021,12 @@
       <c r="D72" s="2" t="n">
         <v>0.004812319538017337</v>
       </c>
+      <c r="E72" s="1" t="n">
+        <v>0.002079</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>-0.004310344827586156</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1605,6 +2043,12 @@
       <c r="D73" s="3" t="n">
         <v>-0.0002127659574467851</v>
       </c>
+      <c r="E73" s="1" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>-0.00180889550968283</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1621,6 +2065,12 @@
       <c r="D74" s="2" t="n">
         <v>0.001662510390689874</v>
       </c>
+      <c r="E74" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>-0.001659751037344331</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1637,6 +2087,12 @@
       <c r="D75" s="3" t="n">
         <v>-0.00852570457442286</v>
       </c>
+      <c r="E75" s="1" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0.00399954290938172</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1653,6 +2109,12 @@
       <c r="D76" s="3" t="n">
         <v>-0.01940123766516142</v>
       </c>
+      <c r="E76" s="1" t="n">
+        <v>0.11818</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.007845812723861421</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1669,6 +2131,12 @@
       <c r="D77" s="2" t="n">
         <v>0.001610565308423303</v>
       </c>
+      <c r="E77" s="1" t="n">
+        <v>0.06246</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.004341534008683058</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1685,6 +2153,12 @@
       <c r="D78" s="3" t="n">
         <v>-0.0022347557731191</v>
       </c>
+      <c r="E78" s="1" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>-0.002453071672354886</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1701,6 +2175,12 @@
       <c r="D79" s="2" t="n">
         <v>0.01755253399258342</v>
       </c>
+      <c r="E79" s="1" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0.01579203109815356</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1717,6 +2197,12 @@
       <c r="D80" s="2" t="n">
         <v>0.0001673360107093817</v>
       </c>
+      <c r="E80" s="1" t="n">
+        <v>0.005969</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>-0.001338464112430873</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1733,6 +2219,12 @@
       <c r="D81" s="2" t="n">
         <v>0.00779727095516578</v>
       </c>
+      <c r="E81" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0.003868471953578313</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1749,6 +2241,12 @@
       <c r="D82" s="3" t="n">
         <v>-0.0009842519685038286</v>
       </c>
+      <c r="E82" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>-0.0009852216748768754</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1765,6 +2263,12 @@
       <c r="D83" s="2" t="n">
         <v>0.01317365269461078</v>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>0.05925</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0.0005065856129685125</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1781,6 +2285,12 @@
       <c r="D84" s="2" t="n">
         <v>0.00045355587808413</v>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>1.1075</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.004170822377368698</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1797,6 +2307,12 @@
       <c r="D85" s="2" t="n">
         <v>0.001469507714915443</v>
       </c>
+      <c r="E85" s="1" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>-0.002201027146001505</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1813,6 +2329,12 @@
       <c r="D86" s="3" t="n">
         <v>-0.0005988023952095564</v>
       </c>
+      <c r="E86" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0.002995805871779595</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1829,6 +2351,12 @@
       <c r="D87" s="3" t="n">
         <v>-0.000844696512610287</v>
       </c>
+      <c r="E87" s="1" t="n">
+        <v>8.266</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>-0.001690821256038569</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1845,6 +2373,12 @@
       <c r="D88" s="2" t="n">
         <v>0.007412687099073442</v>
       </c>
+      <c r="E88" s="1" t="n">
+        <v>2.1268</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.00316022829111831</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1861,6 +2395,12 @@
       <c r="D89" s="3" t="n">
         <v>-0.003319382306249163</v>
       </c>
+      <c r="E89" s="1" t="n">
+        <v>0.006886</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>-0.002896032435563286</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1877,6 +2417,12 @@
       <c r="D90" s="2" t="n">
         <v>0.0006565988181221133</v>
       </c>
+      <c r="E90" s="1" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>-0.001312335958005221</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1893,6 +2439,12 @@
       <c r="D91" s="3" t="n">
         <v>-0.008888888888888865</v>
       </c>
+      <c r="E91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>-0.004484304932735414</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1909,6 +2461,12 @@
       <c r="D92" s="3" t="n">
         <v>-0.02603483798464136</v>
       </c>
+      <c r="E92" s="1" t="n">
+        <v>0.05301</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0.019423076923077</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1925,6 +2483,12 @@
       <c r="D93" s="2" t="n">
         <v>0.001675041876047055</v>
       </c>
+      <c r="E93" s="1" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>-7.601094557632336e-05</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1941,6 +2505,12 @@
       <c r="D94" s="2" t="n">
         <v>0.00683113363405172</v>
       </c>
+      <c r="E94" s="1" t="n">
+        <v>0.054309</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0.001290584265934118</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1957,6 +2527,12 @@
       <c r="D95" s="2" t="n">
         <v>0.001242236024844699</v>
       </c>
+      <c r="E95" s="1" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0.002067824648469811</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1973,6 +2549,12 @@
       <c r="D96" s="3" t="n">
         <v>-0.0009208103130756095</v>
       </c>
+      <c r="E96" s="1" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>-0.0006451612903225096</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1989,6 +2571,12 @@
       <c r="D97" s="3" t="n">
         <v>-0.0003898635477582417</v>
       </c>
+      <c r="E97" s="1" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>-0.002730109204368307</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2005,6 +2593,12 @@
       <c r="D98" s="2" t="n">
         <v>0.006116742397762928</v>
       </c>
+      <c r="E98" s="1" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>-0.003995136355740783</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2021,6 +2615,12 @@
       <c r="D99" s="2" t="n">
         <v>0.005153163469796725</v>
       </c>
+      <c r="E99" s="1" t="n">
+        <v>0.13753</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.02072059242381085</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2037,6 +2637,12 @@
       <c r="D100" s="3" t="n">
         <v>-0.002954694681549567</v>
       </c>
+      <c r="E100" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0.0003292723081988671</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2053,6 +2659,12 @@
       <c r="D101" s="2" t="n">
         <v>0.001953125000000002</v>
       </c>
+      <c r="E101" s="1" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>-0.002923976608187245</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2069,6 +2681,12 @@
       <c r="D102" s="3" t="n">
         <v>-0.007171671896010776</v>
       </c>
+      <c r="E102" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>-0.00586907449209924</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2085,6 +2703,12 @@
       <c r="D103" s="3" t="n">
         <v>-0.001546391752577435</v>
       </c>
+      <c r="E103" s="1" t="n">
+        <v>0.01962</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0.01290655653071762</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2101,6 +2725,12 @@
       <c r="D104" s="2" t="n">
         <v>0.0006722689075629512</v>
       </c>
+      <c r="E104" s="1" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>-0.0006718172657036546</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2117,6 +2747,12 @@
       <c r="D105" s="3" t="n">
         <v>-0.001863354037267151</v>
       </c>
+      <c r="E105" s="1" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>-0.003422526446795253</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2133,6 +2769,12 @@
       <c r="D106" s="3" t="n">
         <v>-0.0006064281382655488</v>
       </c>
+      <c r="E106" s="1" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.004247572815534018</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2149,6 +2791,12 @@
       <c r="D107" s="2" t="n">
         <v>0.001588021778584343</v>
       </c>
+      <c r="E107" s="1" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0.005662514156285396</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2165,6 +2813,12 @@
       <c r="D108" s="3" t="n">
         <v>-0.00149611011370437</v>
       </c>
+      <c r="E108" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>-0.001198681450404589</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2181,6 +2835,12 @@
       <c r="D109" s="3" t="n">
         <v>-0.002588438308887045</v>
       </c>
+      <c r="E109" s="1" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>0.01513840830449828</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2197,6 +2857,12 @@
       <c r="D110" s="3" t="n">
         <v>-0.003298153034300772</v>
       </c>
+      <c r="E110" s="1" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>-0.003309066843150211</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2213,6 +2879,12 @@
       <c r="D111" s="2" t="n">
         <v>0.003291278113000552</v>
       </c>
+      <c r="E111" s="1" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0.001093493712411155</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2229,6 +2901,12 @@
       <c r="D112" s="3" t="n">
         <v>-0.001043296817944663</v>
       </c>
+      <c r="E112" s="1" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0.0002610966057440241</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2245,6 +2923,12 @@
       <c r="D113" s="3" t="n">
         <v>-0.008083140877598186</v>
       </c>
+      <c r="E113" s="1" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>-0.001396973224679913</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2261,6 +2945,12 @@
       <c r="D114" s="3" t="n">
         <v>-0.02967089919668308</v>
       </c>
+      <c r="E114" s="1" t="n">
+        <v>0.007439</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>-0.006676458806249125</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2277,6 +2967,12 @@
       <c r="D115" s="2" t="n">
         <v>0.0003078817733990378</v>
       </c>
+      <c r="E115" s="1" t="n">
+        <v>0.09808</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.006258335898225089</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2293,6 +2989,12 @@
       <c r="D116" s="3" t="n">
         <v>-0.0004843201356096183</v>
       </c>
+      <c r="E116" s="1" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>-0.001332525741974549</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2309,6 +3011,12 @@
       <c r="D117" s="2" t="n">
         <v>0.004712218108381058</v>
       </c>
+      <c r="E117" s="1" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>-0.001675041876046903</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2325,6 +3033,12 @@
       <c r="D118" s="3" t="n">
         <v>-0.0008779631255488434</v>
       </c>
+      <c r="E118" s="1" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>-0.0004393673110720384</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2341,6 +3055,12 @@
       <c r="D119" s="2" t="n">
         <v>0.004510309278350555</v>
       </c>
+      <c r="E119" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>-0.008980115458627404</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2357,6 +3077,12 @@
       <c r="D120" s="3" t="n">
         <v>-0.04847519344560776</v>
       </c>
+      <c r="E120" s="1" t="n">
+        <v>0.004392</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.05046639559913903</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2373,6 +3099,12 @@
       <c r="D121" s="3" t="n">
         <v>-0.001375200550080323</v>
       </c>
+      <c r="E121" s="1" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>-0.008033050263943088</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2389,6 +3121,12 @@
       <c r="D122" s="2" t="n">
         <v>0.001291989664082688</v>
       </c>
+      <c r="E122" s="1" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>-0.001290322580645162</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2405,6 +3143,12 @@
       <c r="D123" s="3" t="n">
         <v>-0.002317497103128687</v>
       </c>
+      <c r="E123" s="1" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>-0.002322880371660765</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2421,6 +3165,12 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E124" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0.009038619556285866</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2437,6 +3187,12 @@
       <c r="D125" s="2" t="n">
         <v>0.00185720181593066</v>
       </c>
+      <c r="E125" s="1" t="n">
+        <v>0.09727</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0.001750772399587946</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2453,6 +3209,12 @@
       <c r="D126" s="2" t="n">
         <v>0.00976852834996819</v>
       </c>
+      <c r="E126" s="1" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>-0.004416403785488998</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2469,6 +3231,12 @@
       <c r="D127" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E127" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>0.003194888178913599</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2485,6 +3253,12 @@
       <c r="D128" s="3" t="n">
         <v>-0.003800310934530972</v>
       </c>
+      <c r="E128" s="1" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>-0.00814981792959951</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2501,6 +3275,12 @@
       <c r="D129" s="2" t="n">
         <v>0.008536585365853522</v>
       </c>
+      <c r="E129" s="1" t="n">
+        <v>0.06565</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>-0.007708585247883867</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2517,6 +3297,12 @@
       <c r="D130" s="2" t="n">
         <v>0.007881938621499164</v>
       </c>
+      <c r="E130" s="1" t="n">
+        <v>0.0005953</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>-0.009484193011647215</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2533,6 +3319,12 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2549,6 +3341,12 @@
       <c r="D132" s="3" t="n">
         <v>-0.007886953664147267</v>
       </c>
+      <c r="E132" s="1" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.006955945677376584</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2565,6 +3363,12 @@
       <c r="D133" s="3" t="n">
         <v>-0.008249852681201991</v>
       </c>
+      <c r="E133" s="1" t="n">
+        <v>0.03334</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>-0.009506833036244826</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2581,6 +3385,12 @@
       <c r="D134" s="2" t="n">
         <v>0.0121124031007752</v>
       </c>
+      <c r="E134" s="1" t="n">
+        <v>0.14595</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>-0.001914791766395421</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2597,6 +3407,12 @@
       <c r="D135" s="2" t="n">
         <v>0.0003401360544217549</v>
       </c>
+      <c r="E135" s="1" t="n">
+        <v>0.02937</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-0.001360081604896239</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2613,6 +3429,12 @@
       <c r="D136" s="2" t="n">
         <v>0.0003582945180939292</v>
       </c>
+      <c r="E136" s="1" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0.001790830945558637</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2629,6 +3451,12 @@
       <c r="D137" s="2" t="n">
         <v>0.001646284101599288</v>
       </c>
+      <c r="E137" s="1" t="n">
+        <v>0.0004254</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>-0.001173984503404584</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2645,6 +3473,12 @@
       <c r="D138" s="2" t="n">
         <v>0.01759652209916158</v>
       </c>
+      <c r="E138" s="1" t="n">
+        <v>0.02944</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>-0.001797036584952277</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2661,6 +3495,12 @@
       <c r="D139" s="3" t="n">
         <v>-0.003149606299212543</v>
       </c>
+      <c r="E139" s="1" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.01337546076882563</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2677,6 +3517,12 @@
       <c r="D140" s="3" t="n">
         <v>-0.0008522727272726334</v>
       </c>
+      <c r="E140" s="1" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.004264998578333811</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2693,6 +3539,12 @@
       <c r="D141" s="2" t="n">
         <v>0.001102941176470671</v>
       </c>
+      <c r="E141" s="1" t="n">
+        <v>0.02689</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>-0.01248622842453177</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2709,6 +3561,12 @@
       <c r="D142" s="3" t="n">
         <v>-0.006406903765690432</v>
       </c>
+      <c r="E142" s="1" t="n">
+        <v>0.07643999999999999</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0.005921831819976208</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2725,6 +3583,12 @@
       <c r="D143" s="2" t="n">
         <v>0.003971856559237281</v>
       </c>
+      <c r="E143" s="1" t="n">
+        <v>0.08802</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>-0.005086469989826971</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2741,6 +3605,12 @@
       <c r="D144" s="3" t="n">
         <v>-0.001965601965601885</v>
       </c>
+      <c r="E144" s="1" t="n">
+        <v>0.02023</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>-0.003938946331856238</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2757,6 +3627,12 @@
       <c r="D145" s="2" t="n">
         <v>0.002809482001755934</v>
       </c>
+      <c r="E145" s="1" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2773,6 +3649,12 @@
       <c r="D146" s="2" t="n">
         <v>0.004671338004671194</v>
       </c>
+      <c r="E146" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>-0.0003321155762204882</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2789,6 +3671,12 @@
       <c r="D147" s="3" t="n">
         <v>-0.008130081300813016</v>
       </c>
+      <c r="E147" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2805,6 +3693,12 @@
       <c r="D148" s="3" t="n">
         <v>-0.006789178152118473</v>
       </c>
+      <c r="E148" s="1" t="n">
+        <v>1.9562</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0.005396515392917692</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2821,6 +3715,12 @@
       <c r="D149" s="2" t="n">
         <v>0.004366106080206976</v>
       </c>
+      <c r="E149" s="1" t="n">
+        <v>0.06202</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>-0.001449042022218641</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2837,6 +3737,12 @@
       <c r="D150" s="2" t="n">
         <v>0.01186552406064599</v>
       </c>
+      <c r="E150" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0.0814332247557004</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2853,6 +3759,12 @@
       <c r="D151" s="2" t="n">
         <v>0.0009033423667569412</v>
       </c>
+      <c r="E151" s="1" t="n">
+        <v>6.633e-05</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>-0.002256317689530741</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2869,6 +3781,12 @@
       <c r="D152" s="3" t="n">
         <v>-0.001336005344021438</v>
       </c>
+      <c r="E152" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>-0.02073578595317722</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2885,6 +3803,12 @@
       <c r="D153" s="3" t="n">
         <v>-0.001440922190201837</v>
       </c>
+      <c r="E153" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>-0.002405002405002307</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2901,6 +3825,12 @@
       <c r="D154" s="2" t="n">
         <v>0.001850605652759038</v>
       </c>
+      <c r="E154" s="1" t="n">
+        <v>0.0005958</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0.0005037783375314073</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2917,6 +3847,12 @@
       <c r="D155" s="3" t="n">
         <v>-0.0007464543418759719</v>
       </c>
+      <c r="E155" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>-0.00273904382470117</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2933,6 +3869,12 @@
       <c r="D156" s="3" t="n">
         <v>-0.003695881731784433</v>
       </c>
+      <c r="E156" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>-0.002649708532061549</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2949,6 +3891,12 @@
       <c r="D157" s="3" t="n">
         <v>-0.006458923512747888</v>
       </c>
+      <c r="E157" s="1" t="n">
+        <v>0.08712</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>-0.006386861313868512</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2965,6 +3913,12 @@
       <c r="D158" s="3" t="n">
         <v>-0.004947508145287724</v>
       </c>
+      <c r="E158" s="1" t="n">
+        <v>0.008187</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>-0.007154984234780503</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2981,6 +3935,12 @@
       <c r="D159" s="3" t="n">
         <v>-0.001603849238171613</v>
       </c>
+      <c r="E159" s="1" t="n">
+        <v>2.486</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>-0.001606425702811246</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2997,6 +3957,12 @@
       <c r="D160" s="2" t="n">
         <v>0.000943173779768993</v>
       </c>
+      <c r="E160" s="1" t="n">
+        <v>1.2723</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>-0.0009422850412250411</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3013,6 +3979,12 @@
       <c r="D161" s="2" t="n">
         <v>0.01219027428117134</v>
       </c>
+      <c r="E161" s="1" t="n">
+        <v>0.007644</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>0.0006545359340227512</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3029,6 +4001,12 @@
       <c r="D162" s="3" t="n">
         <v>-0.05861828332170264</v>
       </c>
+      <c r="E162" s="1" t="n">
+        <v>0.004016</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>-0.007659995058067863</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3045,6 +4023,12 @@
       <c r="D163" s="3" t="n">
         <v>-0.002081165452653546</v>
       </c>
+      <c r="E163" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3061,6 +4045,12 @@
       <c r="D164" s="2" t="n">
         <v>0.002256022123571705</v>
       </c>
+      <c r="E164" s="1" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>-0.001597444089456854</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3077,6 +4067,12 @@
       <c r="D165" s="3" t="n">
         <v>-0.003779814919407406</v>
       </c>
+      <c r="E165" s="1" t="n">
+        <v>0.022964</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0.001482773658962028</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3093,6 +4089,12 @@
       <c r="D166" s="3" t="n">
         <v>-0.001999636429739997</v>
       </c>
+      <c r="E166" s="1" t="n">
+        <v>0.005412</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>-0.01420765027322403</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3109,6 +4111,12 @@
       <c r="D167" s="3" t="n">
         <v>-0.01051524710830714</v>
       </c>
+      <c r="E167" s="1" t="n">
+        <v>0.06553</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>-0.005161682101108139</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3125,6 +4133,12 @@
       <c r="D168" s="2" t="n">
         <v>0.004237288135593195</v>
       </c>
+      <c r="E168" s="1" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>-0.001054852320674989</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3141,6 +4155,12 @@
       <c r="D169" s="2" t="n">
         <v>0.002084418968212707</v>
       </c>
+      <c r="E169" s="1" t="n">
+        <v>0.03842</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>-0.001040041601664024</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3157,6 +4177,12 @@
       <c r="D170" s="2" t="n">
         <v>0.000563856780377859</v>
       </c>
+      <c r="E170" s="1" t="n">
+        <v>0.007087</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>-0.001549732318963049</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3173,6 +4199,12 @@
       <c r="D171" s="2" t="n">
         <v>0.00207407407407401</v>
       </c>
+      <c r="E171" s="1" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>-0.0002956830277941721</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3189,6 +4221,12 @@
       <c r="D172" s="2" t="n">
         <v>0.001292466765140264</v>
       </c>
+      <c r="E172" s="1" t="n">
+        <v>5.407</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>-0.002950396459524251</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3205,6 +4243,12 @@
       <c r="D173" s="3" t="n">
         <v>-0.0002205558006174707</v>
       </c>
+      <c r="E173" s="1" t="n">
+        <v>0.04522</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>-0.002426649018310148</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3221,6 +4265,12 @@
       <c r="D174" s="3" t="n">
         <v>-0.002290659200814451</v>
       </c>
+      <c r="E174" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>-0.001275510204081669</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3237,6 +4287,12 @@
       <c r="D175" s="3" t="n">
         <v>-0.0007121239095602037</v>
       </c>
+      <c r="E175" s="1" t="n">
+        <v>0.005541</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>-0.01282736504543025</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3253,6 +4309,12 @@
       <c r="D176" s="3" t="n">
         <v>-0.001317523056653552</v>
       </c>
+      <c r="E176" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>-0.00263852242744064</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3269,6 +4331,12 @@
       <c r="D177" s="2" t="n">
         <v>0.01415094339622643</v>
       </c>
+      <c r="E177" s="1" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>0.009302325581395357</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3285,6 +4353,12 @@
       <c r="D178" s="3" t="n">
         <v>-0.003125797397295196</v>
       </c>
+      <c r="E178" s="1" t="n">
+        <v>15.572</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>-0.003519549497664394</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3301,6 +4375,12 @@
       <c r="D179" s="3" t="n">
         <v>-0.003205128205128208</v>
       </c>
+      <c r="E179" s="1" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>-0.006430868167202578</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3317,6 +4397,12 @@
       <c r="D180" s="3" t="n">
         <v>-0.01105263157894732</v>
       </c>
+      <c r="E180" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0.001596593932943027</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3333,6 +4419,12 @@
       <c r="D181" s="2" t="n">
         <v>0.0005333333333332746</v>
       </c>
+      <c r="E181" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>-0.002665245202558638</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3349,6 +4441,12 @@
       <c r="D182" s="3" t="n">
         <v>-0.005853821709315991</v>
       </c>
+      <c r="E182" s="1" t="n">
+        <v>0.05963</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>0.003196500672947555</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3365,6 +4463,12 @@
       <c r="D183" s="2" t="n">
         <v>0.003333333333333342</v>
       </c>
+      <c r="E183" s="1" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0.004983388704318878</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3381,6 +4485,12 @@
       <c r="D184" s="2" t="n">
         <v>0.0004683840749414329</v>
       </c>
+      <c r="E184" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>0.001872659176029886</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3397,6 +4507,12 @@
       <c r="D185" s="3" t="n">
         <v>-0.005479452054794526</v>
       </c>
+      <c r="E185" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>-0.005509641873278242</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3413,6 +4529,12 @@
       <c r="D186" s="3" t="n">
         <v>-0.0001303611002477034</v>
       </c>
+      <c r="E186" s="1" t="n">
+        <v>0.007641</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>-0.003780964797913887</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3429,6 +4551,12 @@
       <c r="D187" s="3" t="n">
         <v>-0.001850481125092526</v>
       </c>
+      <c r="E187" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0.001112347052280395</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3445,6 +4573,12 @@
       <c r="D188" s="3" t="n">
         <v>-0.0006137479541735321</v>
       </c>
+      <c r="E188" s="1" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>-0.001228249744114587</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3461,6 +4595,12 @@
       <c r="D189" s="3" t="n">
         <v>-0.0003921568627450548</v>
       </c>
+      <c r="E189" s="1" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>-0.00235386426049427</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3477,6 +4617,12 @@
       <c r="D190" s="2" t="n">
         <v>0.002139418791228543</v>
       </c>
+      <c r="E190" s="1" t="n">
+        <v>0.5627</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>0.001067425724959854</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3493,6 +4639,12 @@
       <c r="D191" s="2" t="n">
         <v>0.0006652253450857222</v>
       </c>
+      <c r="E191" s="1" t="n">
+        <v>6.004</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>-0.002160545122154028</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3509,6 +4661,12 @@
       <c r="D192" s="3" t="n">
         <v>-0.005976095617529854</v>
       </c>
+      <c r="E192" s="1" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3525,6 +4683,12 @@
       <c r="D193" s="3" t="n">
         <v>-0.003110419906687276</v>
       </c>
+      <c r="E193" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3541,6 +4705,12 @@
       <c r="D194" s="2" t="n">
         <v>0.005214368482039385</v>
       </c>
+      <c r="E194" s="1" t="n">
+        <v>0.01723</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>-0.006916426512968418</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3557,6 +4727,12 @@
       <c r="D195" s="2" t="n">
         <v>0.001491167699013509</v>
       </c>
+      <c r="E195" s="1" t="n">
+        <v>0.0008654999999999999</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>-0.008704615737029065</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3573,6 +4749,12 @@
       <c r="D196" s="3" t="n">
         <v>-0.01071080817916255</v>
       </c>
+      <c r="E196" s="1" t="n">
+        <v>0.001018</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.001968503937007922</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3589,6 +4771,12 @@
       <c r="D197" s="3" t="n">
         <v>-0.0006188118811881339</v>
       </c>
+      <c r="E197" s="1" t="n">
+        <v>0.0001609</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>-0.003715170278637693</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3605,6 +4793,12 @@
       <c r="D198" s="2" t="n">
         <v>0.002310002310002466</v>
       </c>
+      <c r="E198" s="1" t="n">
+        <v>4.326</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>-0.002996082046554687</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3621,6 +4815,12 @@
       <c r="D199" s="2" t="n">
         <v>0.00432365657813469</v>
       </c>
+      <c r="E199" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>-0.002460024600245902</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3637,6 +4837,12 @@
       <c r="D200" s="3" t="n">
         <v>-0.003398221178050059</v>
       </c>
+      <c r="E200" s="1" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>-0.003999158071984756</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3653,6 +4859,12 @@
       <c r="D201" s="2" t="n">
         <v>0.01591380024865317</v>
       </c>
+      <c r="E201" s="1" t="n">
+        <v>0.12333</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>0.006200538467814284</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3669,6 +4881,12 @@
       <c r="D202" s="2" t="n">
         <v>0.004360465116279144</v>
       </c>
+      <c r="E202" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3685,6 +4903,12 @@
       <c r="D203" s="3" t="n">
         <v>-0.002643595289593823</v>
       </c>
+      <c r="E203" s="1" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>-0.01036144578313253</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3701,6 +4925,12 @@
       <c r="D204" s="2" t="n">
         <v>0.0007797270955165374</v>
       </c>
+      <c r="E204" s="1" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>-0.001947798987144447</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3717,6 +4947,12 @@
       <c r="D205" s="2" t="n">
         <v>0.003272557269752249</v>
       </c>
+      <c r="E205" s="1" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>-0.00186393289841571</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3733,6 +4969,12 @@
       <c r="D206" s="3" t="n">
         <v>-0.000436300174520052</v>
       </c>
+      <c r="E206" s="1" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>-0.001745962461807</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3749,6 +4991,12 @@
       <c r="D207" s="3" t="n">
         <v>-0.00120336943441634</v>
       </c>
+      <c r="E207" s="1" t="n">
+        <v>4.152</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>0.0004819277108433204</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3765,6 +5013,12 @@
       <c r="D208" s="3" t="n">
         <v>-0.002024838012958928</v>
       </c>
+      <c r="E208" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>0.0009468416069254784</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3781,6 +5035,12 @@
       <c r="D209" s="2" t="n">
         <v>0.0002378686964794511</v>
       </c>
+      <c r="E209" s="1" t="n">
+        <v>0.04214</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>0.00214030915576694</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3797,6 +5057,12 @@
       <c r="D210" s="2" t="n">
         <v>0.001091107474086229</v>
       </c>
+      <c r="E210" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3813,6 +5079,12 @@
       <c r="D211" s="2" t="n">
         <v>0.00126475548060706</v>
       </c>
+      <c r="E211" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>0.006315789473684216</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3829,6 +5101,12 @@
       <c r="D212" s="2" t="n">
         <v>0.002899951667472174</v>
       </c>
+      <c r="E212" s="1" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>0.002409638554216769</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3845,6 +5123,12 @@
       <c r="D213" s="2" t="n">
         <v>0.004314994606256746</v>
       </c>
+      <c r="E213" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>-0.00751879699248121</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3861,6 +5145,12 @@
       <c r="D214" s="2" t="n">
         <v>0.00866796391296649</v>
       </c>
+      <c r="E214" s="1" t="n">
+        <v>0.005686</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>-0.002806032970887324</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3877,6 +5167,12 @@
       <c r="D215" s="3" t="n">
         <v>-0.0003648969166210397</v>
       </c>
+      <c r="E215" s="1" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>-0.003467786092352541</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3893,6 +5189,12 @@
       <c r="D216" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>-0.004731861198738087</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3909,6 +5211,12 @@
       <c r="D217" s="2" t="n">
         <v>0.001085776330076035</v>
       </c>
+      <c r="E217" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>-0.001084598698481593</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3925,6 +5233,12 @@
       <c r="D218" s="3" t="n">
         <v>-0.001403635054885735</v>
       </c>
+      <c r="E218" s="1" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>-0.008613854249261166</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3941,6 +5255,12 @@
       <c r="D219" s="3" t="n">
         <v>-0.0006186204763378489</v>
       </c>
+      <c r="E219" s="1" t="n">
+        <v>0.003234</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>0.0009285051067780763</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3957,6 +5277,12 @@
       <c r="D220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3973,6 +5299,12 @@
       <c r="D221" s="2" t="n">
         <v>0.00313561536451534</v>
       </c>
+      <c r="E221" s="1" t="n">
+        <v>0.03829</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>-0.002604845011721877</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3989,6 +5321,12 @@
       <c r="D222" s="2" t="n">
         <v>0.0002160760587726042</v>
       </c>
+      <c r="E222" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>-0.002376323179952452</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4005,6 +5343,12 @@
       <c r="D223" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E223" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>-0.001906577693040914</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4021,6 +5365,12 @@
       <c r="D224" s="2" t="n">
         <v>0.002545824847250568</v>
       </c>
+      <c r="E224" s="1" t="n">
+        <v>3.893</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>-0.01142712036566795</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4037,6 +5387,12 @@
       <c r="D225" s="2" t="n">
         <v>0.001200611220257556</v>
       </c>
+      <c r="E225" s="1" t="n">
+        <v>0.0009162</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>-0.001199171481521828</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4053,6 +5409,12 @@
       <c r="D226" s="3" t="n">
         <v>-0.008674246864377112</v>
       </c>
+      <c r="E226" s="1" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>0.006266997753340543</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4069,6 +5431,12 @@
       <c r="D227" s="3" t="n">
         <v>-0.000965250965250926</v>
       </c>
+      <c r="E227" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>-0.001932367149758375</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4085,6 +5453,12 @@
       <c r="D228" s="2" t="n">
         <v>0.003682719546742355</v>
       </c>
+      <c r="E228" s="1" t="n">
+        <v>0.03546</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.0008467400508042705</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4101,6 +5475,12 @@
       <c r="D229" s="3" t="n">
         <v>-0.0003882741215297842</v>
       </c>
+      <c r="E229" s="1" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>-0.004855311711011851</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4117,6 +5497,12 @@
       <c r="D230" s="2" t="n">
         <v>0.003490401396160517</v>
       </c>
+      <c r="E230" s="1" t="n">
+        <v>0.001724</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>-0.0005797101449274874</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4133,6 +5519,12 @@
       <c r="D231" s="2" t="n">
         <v>0.003909465020576187</v>
       </c>
+      <c r="E231" s="1" t="n">
+        <v>0.04908</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>0.005943840951014523</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4149,6 +5541,12 @@
       <c r="D232" s="2" t="n">
         <v>0.001863064741499853</v>
       </c>
+      <c r="E232" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.002324500232449928</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4165,6 +5563,12 @@
       <c r="D233" s="2" t="n">
         <v>0.0006858710562414434</v>
       </c>
+      <c r="E233" s="1" t="n">
+        <v>0.0005829</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>-0.001199451679232287</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4181,6 +5585,12 @@
       <c r="D234" s="3" t="n">
         <v>-0.01056051990251832</v>
       </c>
+      <c r="E234" s="1" t="n">
+        <v>0.22327</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.01838168217478565</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4197,6 +5607,12 @@
       <c r="D235" s="3" t="n">
         <v>-0.01432664756446995</v>
       </c>
+      <c r="E235" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4213,6 +5629,12 @@
       <c r="D236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>-0.002421307506053338</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4229,6 +5651,12 @@
       <c r="D237" s="2" t="n">
         <v>0.004807692307692321</v>
       </c>
+      <c r="E237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>-0.002392344497607558</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4245,6 +5673,12 @@
       <c r="D238" s="3" t="n">
         <v>-0.007968127490039931</v>
       </c>
+      <c r="E238" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0.004016064257028227</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4261,6 +5695,12 @@
       <c r="D239" s="3" t="n">
         <v>-0.001337792642140414</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>-0.006028131279303402</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4277,6 +5717,12 @@
       <c r="D240" s="2" t="n">
         <v>0.001023279611153773</v>
       </c>
+      <c r="E240" s="1" t="n">
+        <v>0.0003904</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>-0.002300025555839565</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4293,6 +5739,12 @@
       <c r="D241" s="2" t="n">
         <v>0.003389830508474621</v>
       </c>
+      <c r="E241" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>-0.009009009009009058</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4309,6 +5761,12 @@
       <c r="D242" s="2" t="n">
         <v>0.009657947686116679</v>
       </c>
+      <c r="E242" s="1" t="n">
+        <v>0.07548000000000001</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.00278995615783183</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4325,6 +5783,12 @@
       <c r="D243" s="3" t="n">
         <v>-0.002547121752419839</v>
       </c>
+      <c r="E243" s="1" t="n">
+        <v>0.01955</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>-0.001532175689478998</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4341,6 +5805,12 @@
       <c r="D244" s="3" t="n">
         <v>-0.004410766794842812</v>
       </c>
+      <c r="E244" s="1" t="n">
+        <v>0.08824</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.002385550380552106</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4357,6 +5827,12 @@
       <c r="D245" s="2" t="n">
         <v>0.006303096738832623</v>
       </c>
+      <c r="E245" s="1" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>-0.01892701525054469</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4373,6 +5849,12 @@
       <c r="D246" s="3" t="n">
         <v>-0.007202216066482085</v>
       </c>
+      <c r="E246" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>-0.001116071428571383</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4389,6 +5871,12 @@
       <c r="D247" s="3" t="n">
         <v>-0.004989416389476873</v>
       </c>
+      <c r="E247" s="1" t="n">
+        <v>0.006579</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>-0.0003039051815833863</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4405,6 +5893,12 @@
       <c r="D248" s="3" t="n">
         <v>-0.002670551104637191</v>
       </c>
+      <c r="E248" s="1" t="n">
+        <v>0.004074</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>-0.008276533592989122</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4421,6 +5915,12 @@
       <c r="D249" s="2" t="n">
         <v>0.0009115770282587875</v>
       </c>
+      <c r="E249" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>-0.001821493624772239</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4437,6 +5937,12 @@
       <c r="D250" s="2" t="n">
         <v>0.0008756567425569833</v>
       </c>
+      <c r="E250" s="1" t="n">
+        <v>0.03413</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>-0.004666083406240898</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4453,6 +5959,12 @@
       <c r="D251" s="2" t="n">
         <v>0.007434944237918235</v>
       </c>
+      <c r="E251" s="1" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>-0.003228782287822906</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4469,6 +5981,12 @@
       <c r="D252" s="2" t="n">
         <v>0.008704735376044515</v>
       </c>
+      <c r="E252" s="1" t="n">
+        <v>0.00612</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.05626510182947875</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4485,6 +6003,12 @@
       <c r="D253" s="2" t="n">
         <v>0.001800720288115173</v>
       </c>
+      <c r="E253" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>0.0005991611743558774</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4501,6 +6025,12 @@
       <c r="D254" s="2" t="n">
         <v>0.004622496147919796</v>
       </c>
+      <c r="E254" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>-0.0007668711656440873</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4517,6 +6047,12 @@
       <c r="D255" s="3" t="n">
         <v>-0.01191611058150621</v>
       </c>
+      <c r="E255" s="1" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>-0.0004823926676314324</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4533,6 +6069,12 @@
       <c r="D256" s="2" t="n">
         <v>0.0009546539379474551</v>
       </c>
+      <c r="E256" s="1" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>-0.001430615164520686</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4549,6 +6091,12 @@
       <c r="D257" s="3" t="n">
         <v>-0.007014809041309416</v>
       </c>
+      <c r="E257" s="1" t="n">
+        <v>0.02536</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>-0.004709576138147511</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4565,6 +6113,12 @@
       <c r="D258" s="2" t="n">
         <v>0.002167434299647892</v>
       </c>
+      <c r="E258" s="1" t="n">
+        <v>0.14802</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.0004055150040551804</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4581,6 +6135,12 @@
       <c r="D259" s="2" t="n">
         <v>0.001971220185294754</v>
       </c>
+      <c r="E259" s="1" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.001770607908715322</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4597,6 +6157,12 @@
       <c r="D260" s="3" t="n">
         <v>-0.0004835589941972723</v>
       </c>
+      <c r="E260" s="1" t="n">
+        <v>0.08272</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0.0004837929366231056</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4613,6 +6179,12 @@
       <c r="D261" s="3" t="n">
         <v>-0.003401360544217667</v>
       </c>
+      <c r="E261" s="1" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0.01109215017064843</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4629,6 +6201,12 @@
       <c r="D262" s="3" t="n">
         <v>-0.002100840336134611</v>
       </c>
+      <c r="E262" s="1" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>-0.00140350877192967</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4645,6 +6223,12 @@
       <c r="D263" s="3" t="n">
         <v>-0.0005155303518496229</v>
       </c>
+      <c r="E263" s="1" t="n">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>-0.0003868471953576837</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4661,6 +6245,12 @@
       <c r="D264" s="3" t="n">
         <v>-0.007483870967741899</v>
       </c>
+      <c r="E264" s="1" t="n">
+        <v>0.03868</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>0.005720228809152314</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4677,6 +6267,12 @@
       <c r="D265" s="3" t="n">
         <v>-0.001298701298701358</v>
       </c>
+      <c r="E265" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>-0.001950585175552586</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4693,6 +6289,12 @@
       <c r="D266" s="2" t="n">
         <v>0.0001674480910917838</v>
       </c>
+      <c r="E266" s="1" t="n">
+        <v>0.005961</v>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>-0.002009040683073809</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4709,6 +6311,12 @@
       <c r="D267" s="3" t="n">
         <v>-0.001078748651564329</v>
       </c>
+      <c r="E267" s="1" t="n">
+        <v>0.03717</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>0.003509719222462341</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4725,6 +6333,12 @@
       <c r="D268" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E268" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>-0.001312766655727005</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4741,6 +6355,12 @@
       <c r="D269" s="3" t="n">
         <v>-0.004115226337448665</v>
       </c>
+      <c r="E269" s="1" t="n">
+        <v>0.22635</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>-0.004967469667663057</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4757,6 +6377,12 @@
       <c r="D270" s="3" t="n">
         <v>-0.004333694474539548</v>
       </c>
+      <c r="E270" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4773,6 +6399,12 @@
       <c r="D271" s="3" t="n">
         <v>-0.001932740626208093</v>
       </c>
+      <c r="E271" s="1" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>0.001936483346243353</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -4789,6 +6421,12 @@
       <c r="D272" s="2" t="n">
         <v>0.001633986928104546</v>
       </c>
+      <c r="E272" s="1" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>0.003262642740619845</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -4805,6 +6443,12 @@
       <c r="D273" s="2" t="n">
         <v>0.002607561929595835</v>
       </c>
+      <c r="E273" s="1" t="n">
+        <v>0.03071</v>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>-0.001625487646293822</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -4821,6 +6465,12 @@
       <c r="D274" s="2" t="n">
         <v>0.00742311770943803</v>
       </c>
+      <c r="E274" s="1" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>0.002631578947368423</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4837,6 +6487,12 @@
       <c r="D275" s="2" t="n">
         <v>0.001881876085697615</v>
       </c>
+      <c r="E275" s="1" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>-0.004479121514231916</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4853,6 +6509,12 @@
       <c r="D276" s="3" t="n">
         <v>-0.001610305958131937</v>
       </c>
+      <c r="E276" s="1" t="n">
+        <v>0.08067000000000001</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>0.0008684863523573277</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4869,6 +6531,12 @@
       <c r="D277" s="3" t="n">
         <v>-0.004930734914299175</v>
       </c>
+      <c r="E277" s="1" t="n">
+        <v>0.004202</v>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>-0.008494572911750726</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -4885,6 +6553,12 @@
       <c r="D278" s="3" t="n">
         <v>-0.001288659793814434</v>
       </c>
+      <c r="E278" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4901,6 +6575,12 @@
       <c r="D279" s="2" t="n">
         <v>0.001819836214740757</v>
       </c>
+      <c r="E279" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>-0.0009082652134424457</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4917,6 +6597,12 @@
       <c r="D280" s="2" t="n">
         <v>0.0030753459764224</v>
       </c>
+      <c r="E280" s="1" t="n">
+        <v>0.03917</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0.0007664793050588208</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4933,6 +6619,12 @@
       <c r="D281" s="2" t="n">
         <v>0.003085320992049322</v>
       </c>
+      <c r="E281" s="1" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>0.001183011948420713</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4949,6 +6641,12 @@
       <c r="D282" s="3" t="n">
         <v>-0.003745318352060032</v>
       </c>
+      <c r="E282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>-0.003759398496240579</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4965,6 +6663,12 @@
       <c r="D283" s="3" t="n">
         <v>-0.001974983541803783</v>
       </c>
+      <c r="E283" s="1" t="n">
+        <v>0.07591000000000001</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>0.001451187335092335</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4981,6 +6685,12 @@
       <c r="D284" s="3" t="n">
         <v>-0.001231527093596089</v>
       </c>
+      <c r="E284" s="1" t="n">
+        <v>0.001617</v>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>-0.003082614056720107</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -4997,6 +6707,12 @@
       <c r="D285" s="3" t="n">
         <v>-0.0009920634920635204</v>
       </c>
+      <c r="E285" s="1" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>-0.0004965243296921003</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5013,6 +6729,12 @@
       <c r="D286" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E286" s="1" t="n">
+        <v>0.10673</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.00423409860745207</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5029,6 +6751,12 @@
       <c r="D287" s="2" t="n">
         <v>0.003508771929824621</v>
       </c>
+      <c r="E287" s="1" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>-0.001748251748251879</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5045,6 +6773,12 @@
       <c r="D288" s="2" t="n">
         <v>0.0006523157208088449</v>
       </c>
+      <c r="E288" s="1" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F288" s="3" t="n">
+        <v>-0.002607561929595835</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5061,6 +6795,12 @@
       <c r="D289" s="2" t="n">
         <v>0.006242197253433171</v>
       </c>
+      <c r="E289" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>-0.003722084367245506</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5077,6 +6817,12 @@
       <c r="D290" s="3" t="n">
         <v>-0.001320422535211122</v>
       </c>
+      <c r="E290" s="1" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>-0.005288673424416046</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5093,6 +6839,12 @@
       <c r="D291" s="2" t="n">
         <v>0.0004542357483533454</v>
       </c>
+      <c r="E291" s="1" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="F291" s="3" t="n">
+        <v>-0.0004540295119182247</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5109,6 +6861,12 @@
       <c r="D292" s="3" t="n">
         <v>-0.00457404230989137</v>
       </c>
+      <c r="E292" s="1" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="F292" s="3" t="n">
+        <v>-0.002871912693854173</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5125,6 +6883,12 @@
       <c r="D293" s="2" t="n">
         <v>0.01331213987681297</v>
       </c>
+      <c r="E293" s="1" t="n">
+        <v>0.05055</v>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>-0.008823529411764687</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5141,6 +6905,12 @@
       <c r="D294" s="3" t="n">
         <v>-0.001102188631711551</v>
       </c>
+      <c r="E294" s="1" t="n">
+        <v>0.06337</v>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>-0.001103404791929392</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5157,6 +6927,12 @@
       <c r="D295" s="2" t="n">
         <v>0.002934702861335228</v>
       </c>
+      <c r="E295" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>-0.0002438429651304619</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5173,6 +6949,12 @@
       <c r="D296" s="2" t="n">
         <v>0.002407318247472293</v>
       </c>
+      <c r="E296" s="1" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>0.002881844380403454</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5189,6 +6971,12 @@
       <c r="D297" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E297" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>-0.001021450459652736</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5205,6 +6993,12 @@
       <c r="D298" s="2" t="n">
         <v>0.003141361256544447</v>
       </c>
+      <c r="E298" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>-0.003131524008350676</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5221,6 +7015,12 @@
       <c r="D299" s="3" t="n">
         <v>-0.003390527072844929</v>
       </c>
+      <c r="E299" s="1" t="n">
+        <v>0.09672</v>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>-0.002886597938144355</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5237,6 +7037,12 @@
       <c r="D300" s="2" t="n">
         <v>0.001624255549539728</v>
       </c>
+      <c r="E300" s="1" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>-0.001621621621621556</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5253,6 +7059,12 @@
       <c r="D301" s="3" t="n">
         <v>-0.0007501875468866911</v>
       </c>
+      <c r="E301" s="1" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F301" s="3" t="n">
+        <v>-0.00150150150150157</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5269,6 +7081,12 @@
       <c r="D302" s="3" t="n">
         <v>-0.002747881841080801</v>
       </c>
+      <c r="E302" s="1" t="n">
+        <v>0.004351</v>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>-0.0009184845005741747</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5285,6 +7103,12 @@
       <c r="D303" s="3" t="n">
         <v>-0.001075268817204257</v>
       </c>
+      <c r="E303" s="1" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>0.006458557588805277</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5301,6 +7125,12 @@
       <c r="D304" s="3" t="n">
         <v>-0.0002119093028184645</v>
       </c>
+      <c r="E304" s="1" t="n">
+        <v>4.712</v>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>-0.001271725307333664</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5317,6 +7147,12 @@
       <c r="D305" s="2" t="n">
         <v>0.0009419743782968066</v>
       </c>
+      <c r="E305" s="1" t="n">
+        <v>0.05305</v>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>-0.001505740636175358</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5333,6 +7169,12 @@
       <c r="D306" s="2" t="n">
         <v>0.001888736263736246</v>
       </c>
+      <c r="E306" s="1" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>0.001199657240788357</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5349,6 +7191,12 @@
       <c r="D307" s="2" t="n">
         <v>0.001140250855188174</v>
       </c>
+      <c r="E307" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5365,6 +7213,12 @@
       <c r="D308" s="2" t="n">
         <v>0.01003687013519044</v>
       </c>
+      <c r="E308" s="1" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>0.001013993104846916</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5381,6 +7235,12 @@
       <c r="D309" s="3" t="n">
         <v>-0.00257637099742355</v>
       </c>
+      <c r="E309" s="1" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="F309" s="3" t="n">
+        <v>-0.002767527675276858</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5397,6 +7257,12 @@
       <c r="D310" s="3" t="n">
         <v>-0.004081632653061235</v>
       </c>
+      <c r="E310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5413,6 +7279,12 @@
       <c r="D311" s="2" t="n">
         <v>0.0002781254345708837</v>
       </c>
+      <c r="E311" s="1" t="n">
+        <v>0.07191</v>
+      </c>
+      <c r="F311" s="3" t="n">
+        <v>-0.0002780481023215939</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5429,6 +7301,12 @@
       <c r="D312" s="2" t="n">
         <v>0.0009934871398609481</v>
       </c>
+      <c r="E312" s="1" t="n">
+        <v>0.008987</v>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>-0.008932509925010971</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5445,6 +7323,12 @@
       <c r="D313" s="3" t="n">
         <v>-0.008090749854032853</v>
       </c>
+      <c r="E313" s="1" t="n">
+        <v>0.011917</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>0.00210225361587628</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5461,6 +7345,12 @@
       <c r="D314" s="3" t="n">
         <v>-0.003854389721627401</v>
       </c>
+      <c r="E314" s="1" t="n">
+        <v>0.02316</v>
+      </c>
+      <c r="F314" s="3" t="n">
+        <v>-0.004299226139294901</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5477,6 +7367,12 @@
       <c r="D315" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E315" s="1" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>0.001412429378531016</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5493,6 +7389,12 @@
       <c r="D316" s="2" t="n">
         <v>0.0003835826620636325</v>
       </c>
+      <c r="E316" s="1" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="F316" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5509,6 +7411,12 @@
       <c r="D317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="F317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5525,6 +7433,12 @@
       <c r="D318" s="2" t="n">
         <v>0.001790305685172781</v>
       </c>
+      <c r="E318" s="1" t="n">
+        <v>0.052636</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0.0007034354265290654</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5541,6 +7455,12 @@
       <c r="D319" s="3" t="n">
         <v>-0.003421052631578899</v>
       </c>
+      <c r="E319" s="1" t="n">
+        <v>0.03804</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>0.004489041457618076</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5557,6 +7477,12 @@
       <c r="D320" s="3" t="n">
         <v>-0.004254070705589024</v>
       </c>
+      <c r="E320" s="1" t="n">
+        <v>0.006778</v>
+      </c>
+      <c r="F320" s="3" t="n">
+        <v>-0.001473187978786033</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5573,6 +7499,12 @@
       <c r="D321" s="3" t="n">
         <v>-0.0002207018318250818</v>
       </c>
+      <c r="E321" s="1" t="n">
+        <v>4.522</v>
+      </c>
+      <c r="F321" s="3" t="n">
+        <v>-0.001766004415011039</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5589,6 +7521,12 @@
       <c r="D322" s="3" t="n">
         <v>-0.00312825860271116</v>
       </c>
+      <c r="E322" s="1" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="F322" s="3" t="n">
+        <v>-0.002092050209205023</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5605,6 +7543,12 @@
       <c r="D323" s="2" t="n">
         <v>0.001129146083274551</v>
       </c>
+      <c r="E323" s="1" t="n">
+        <v>0.007079</v>
+      </c>
+      <c r="F323" s="3" t="n">
+        <v>-0.001973776963203175</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5621,6 +7565,12 @@
       <c r="D324" s="2" t="n">
         <v>0.0005503577325263106</v>
       </c>
+      <c r="E324" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="F324" s="3" t="n">
+        <v>-0.001100110011001246</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5637,6 +7587,12 @@
       <c r="D325" s="3" t="n">
         <v>-0.0009756097560974536</v>
       </c>
+      <c r="E325" s="1" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="F325" s="3" t="n">
+        <v>-0.001708984375000083</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5653,6 +7609,12 @@
       <c r="D326" s="2" t="n">
         <v>0.001803301428769592</v>
       </c>
+      <c r="E326" s="1" t="n">
+        <v>0.00721</v>
+      </c>
+      <c r="F326" s="3" t="n">
+        <v>-0.001661589587371899</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5669,6 +7631,12 @@
       <c r="D327" s="2" t="n">
         <v>0.001044932079414868</v>
       </c>
+      <c r="E327" s="1" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>0.001565762004175338</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -5685,6 +7653,12 @@
       <c r="D328" s="3" t="n">
         <v>-0.002949231093322124</v>
       </c>
+      <c r="E328" s="1" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="F328" s="3" t="n">
+        <v>-0.01436720895837729</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -5701,6 +7675,12 @@
       <c r="D329" s="2" t="n">
         <v>0.0007418397626112457</v>
       </c>
+      <c r="E329" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="F329" s="3" t="n">
+        <v>-0.001482579688658334</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -5717,6 +7697,12 @@
       <c r="D330" s="3" t="n">
         <v>-0.00176056338028174</v>
       </c>
+      <c r="E330" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="F330" s="3" t="n">
+        <v>-0.002645502645502599</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -5733,6 +7719,12 @@
       <c r="D331" s="2" t="n">
         <v>0.003366436626830503</v>
       </c>
+      <c r="E331" s="1" t="n">
+        <v>0.5955</v>
+      </c>
+      <c r="F331" s="3" t="n">
+        <v>-0.00100654252642163</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -5749,6 +7741,12 @@
       <c r="D332" s="3" t="n">
         <v>-0.002300690207062198</v>
       </c>
+      <c r="E332" s="1" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0.0002005213555243784</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -5765,6 +7763,12 @@
       <c r="D333" s="2" t="n">
         <v>0.003993154592127816</v>
       </c>
+      <c r="E333" s="1" t="n">
+        <v>0.07025000000000001</v>
+      </c>
+      <c r="F333" s="3" t="n">
+        <v>-0.002130681818181781</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5781,6 +7785,12 @@
       <c r="D334" s="2" t="n">
         <v>0.02206728491166325</v>
       </c>
+      <c r="E334" s="1" t="n">
+        <v>0.15166</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>0.00443737995893752</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -5797,6 +7807,12 @@
       <c r="D335" s="3" t="n">
         <v>-0.005082592121982356</v>
       </c>
+      <c r="E335" s="1" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="F335" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -5813,6 +7829,12 @@
       <c r="D336" s="3" t="n">
         <v>-0.001150086256469268</v>
       </c>
+      <c r="E336" s="1" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0.001151410477835381</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -5829,6 +7851,12 @@
       <c r="D337" s="3" t="n">
         <v>-0.0007473841554559603</v>
       </c>
+      <c r="E337" s="1" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="F337" s="3" t="n">
+        <v>-0.0007479431563201757</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -5845,6 +7873,12 @@
       <c r="D338" s="2" t="n">
         <v>0.001137225170583762</v>
       </c>
+      <c r="E338" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="F338" s="3" t="n">
+        <v>-0.0003786444528588159</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -5861,6 +7895,12 @@
       <c r="D339" s="2" t="n">
         <v>0.0009771350400625647</v>
       </c>
+      <c r="E339" s="1" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="F339" s="3" t="n">
+        <v>-0.001952362358453785</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -5877,6 +7917,12 @@
       <c r="D340" s="2" t="n">
         <v>0.002925726444577405</v>
       </c>
+      <c r="E340" s="1" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>0.002983491347875131</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -5893,6 +7939,12 @@
       <c r="D341" s="3" t="n">
         <v>-0.003414762280010481</v>
       </c>
+      <c r="E341" s="1" t="n">
+        <v>7.577</v>
+      </c>
+      <c r="F341" s="3" t="n">
+        <v>-0.00144965735371641</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -5909,6 +7961,12 @@
       <c r="D342" s="2" t="n">
         <v>0.002380952380952284</v>
       </c>
+      <c r="E342" s="1" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="F342" s="3" t="n">
+        <v>-0.00326603325415674</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -5925,6 +7983,12 @@
       <c r="D343" s="3" t="n">
         <v>-0.0241855873642646</v>
       </c>
+      <c r="E343" s="1" t="n">
+        <v>0.01965</v>
+      </c>
+      <c r="F343" s="3" t="n">
+        <v>-0.006069802731411157</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -5941,6 +8005,12 @@
       <c r="D344" s="2" t="n">
         <v>0.0004555808656037968</v>
       </c>
+      <c r="E344" s="1" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>0.0009107468123860563</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -5957,6 +8027,12 @@
       <c r="D345" s="3" t="n">
         <v>-0.007064364207221443</v>
       </c>
+      <c r="E345" s="1" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>0.003162055335968382</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -5973,6 +8049,12 @@
       <c r="D346" s="2" t="n">
         <v>0.001348487767289551</v>
       </c>
+      <c r="E346" s="1" t="n">
+        <v>0.005199</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>0.0001923816852634216</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -5989,6 +8071,12 @@
       <c r="D347" s="3" t="n">
         <v>-0.001230444717876615</v>
       </c>
+      <c r="E347" s="1" t="n">
+        <v>0.05689</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>0.001231960577261539</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6005,6 +8093,12 @@
       <c r="D348" s="3" t="n">
         <v>-0.001551590380139472</v>
       </c>
+      <c r="E348" s="1" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="F348" s="3" t="n">
+        <v>-0.004662004662004796</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6021,6 +8115,12 @@
       <c r="D349" s="2" t="n">
         <v>0.001054124501686599</v>
       </c>
+      <c r="E349" s="1" t="n">
+        <v>5221.7</v>
+      </c>
+      <c r="F349" s="3" t="n">
+        <v>-0.0002680400528422863</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6037,6 +8137,12 @@
       <c r="D350" s="3" t="n">
         <v>-0.001058201058201015</v>
       </c>
+      <c r="E350" s="1" t="n">
+        <v>0.02804</v>
+      </c>
+      <c r="F350" s="3" t="n">
+        <v>-0.0098870056497176</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6053,6 +8159,12 @@
       <c r="D351" s="3" t="n">
         <v>-0.01032448377581114</v>
       </c>
+      <c r="E351" s="1" t="n">
+        <v>0.001348</v>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>0.004470938897168352</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6069,6 +8181,12 @@
       <c r="D352" s="2" t="n">
         <v>0.002552648372686559</v>
       </c>
+      <c r="E352" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>0.001273074474856948</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6085,6 +8203,12 @@
       <c r="D353" s="2" t="n">
         <v>0.001921229586935569</v>
       </c>
+      <c r="E353" s="1" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F353" s="3" t="n">
+        <v>-0.00287631831255989</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6101,6 +8225,12 @@
       <c r="D354" s="2" t="n">
         <v>0.003150157507875436</v>
       </c>
+      <c r="E354" s="1" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="F354" s="3" t="n">
+        <v>-0.002791346824843066</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6117,6 +8247,12 @@
       <c r="D355" s="3" t="n">
         <v>-0.001443001443001384</v>
       </c>
+      <c r="E355" s="1" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="F355" s="3" t="n">
+        <v>-0.003853564547206176</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6133,6 +8269,12 @@
       <c r="D356" s="3" t="n">
         <v>-0.00810810810810811</v>
       </c>
+      <c r="E356" s="1" t="n">
+        <v>0.11344</v>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>-0.002900588907444818</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6149,6 +8291,12 @@
       <c r="D357" s="2" t="n">
         <v>0.0003839508542907017</v>
       </c>
+      <c r="E357" s="1" t="n">
+        <v>0.005215</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>0.0007676069852235009</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6165,6 +8313,12 @@
       <c r="D358" s="2" t="n">
         <v>0.001626016260162573</v>
       </c>
+      <c r="E358" s="1" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0.001082251082251113</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6181,6 +8335,12 @@
       <c r="D359" s="3" t="n">
         <v>-0.004907975460122669</v>
       </c>
+      <c r="E359" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="F359" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6197,6 +8357,12 @@
       <c r="D360" s="3" t="n">
         <v>-0.001759737212576224</v>
       </c>
+      <c r="E360" s="1" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="F360" s="3" t="n">
+        <v>-0.0001175226231049021</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6213,6 +8379,12 @@
       <c r="D361" s="2" t="n">
         <v>0.02319587628865963</v>
       </c>
+      <c r="E361" s="1" t="n">
+        <v>0.00797</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>0.003778337531486211</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6229,6 +8401,12 @@
       <c r="D362" s="2" t="n">
         <v>0.0004710315591145396</v>
       </c>
+      <c r="E362" s="1" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="F362" s="3" t="n">
+        <v>-0.0002354048964218197</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6245,6 +8423,12 @@
       <c r="D363" s="3" t="n">
         <v>-0.0008192244675041272</v>
       </c>
+      <c r="E363" s="1" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>0.007925662749385177</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6261,6 +8445,12 @@
       <c r="D364" s="3" t="n">
         <v>-0.0009132420091323829</v>
       </c>
+      <c r="E364" s="1" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="F364" s="3" t="n">
+        <v>-0.001828153564899536</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6277,6 +8467,12 @@
       <c r="D365" s="3" t="n">
         <v>-0.001270648030495564</v>
       </c>
+      <c r="E365" s="1" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="F365" s="3" t="n">
+        <v>-0.001090512540894176</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6293,6 +8489,12 @@
       <c r="D366" s="3" t="n">
         <v>-0.002284148012791294</v>
       </c>
+      <c r="E366" s="1" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="F366" s="2" t="n">
+        <v>0.02106227106227116</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6309,6 +8511,12 @@
       <c r="D367" s="3" t="n">
         <v>-0.005930318754633045</v>
       </c>
+      <c r="E367" s="1" t="n">
+        <v>0.001348</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>0.005219985085756944</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6325,6 +8533,12 @@
       <c r="D368" s="3" t="n">
         <v>-0.003471017007983342</v>
       </c>
+      <c r="E368" s="1" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0.000696621386276482</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -6341,6 +8555,12 @@
       <c r="D369" s="3" t="n">
         <v>-0.009057005860415558</v>
       </c>
+      <c r="E369" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="F369" s="3" t="n">
+        <v>-0.008064516129032117</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -6357,6 +8577,12 @@
       <c r="D370" s="2" t="n">
         <v>0.003128103277060535</v>
       </c>
+      <c r="E370" s="1" t="n">
+        <v>0.20187</v>
+      </c>
+      <c r="F370" s="3" t="n">
+        <v>-0.0007919615898628594</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6373,6 +8599,12 @@
       <c r="D371" s="2" t="n">
         <v>0.01333333333333335</v>
       </c>
+      <c r="E371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F371" s="3" t="n">
+        <v>-0.01315789473684212</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -6389,6 +8621,12 @@
       <c r="D372" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E372" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="F372" s="3" t="n">
+        <v>-0.00095419847328247</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -6405,6 +8643,12 @@
       <c r="D373" s="3" t="n">
         <v>-0.0003016136329360918</v>
       </c>
+      <c r="E373" s="1" t="n">
+        <v>0.06597</v>
+      </c>
+      <c r="F373" s="3" t="n">
+        <v>-0.004827274098657427</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -6421,6 +8665,12 @@
       <c r="D374" s="3" t="n">
         <v>-0.001984126984127018</v>
       </c>
+      <c r="E374" s="1" t="n">
+        <v>0.007551</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0.0007952286282307219</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -6437,6 +8687,12 @@
       <c r="D375" s="2" t="n">
         <v>0.001262626262626124</v>
       </c>
+      <c r="E375" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="F375" s="3" t="n">
+        <v>-0.001261034047919155</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6453,6 +8709,12 @@
       <c r="D376" s="2" t="n">
         <v>0.002067946824224538</v>
       </c>
+      <c r="E376" s="1" t="n">
+        <v>0.003381</v>
+      </c>
+      <c r="F376" s="3" t="n">
+        <v>-0.003242924528301934</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6469,6 +8731,12 @@
       <c r="D377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E377" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0.00628930817610059</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6485,6 +8753,12 @@
       <c r="D378" s="2" t="n">
         <v>0.006255585344057094</v>
       </c>
+      <c r="E378" s="1" t="n">
+        <v>0.01134</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>0.007104795737122577</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6501,6 +8775,12 @@
       <c r="D379" s="3" t="n">
         <v>-0.01458523245214224</v>
       </c>
+      <c r="E379" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>0.01110083256244221</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6517,6 +8797,12 @@
       <c r="D380" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E380" s="1" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F380" s="3" t="n">
+        <v>-0.003198294243070232</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6533,6 +8819,12 @@
       <c r="D381" s="2" t="n">
         <v>0.001679261125105002</v>
       </c>
+      <c r="E381" s="1" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>0.00167644593461854</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -6549,6 +8841,12 @@
       <c r="D382" s="2" t="n">
         <v>0.001033413709955177</v>
       </c>
+      <c r="E382" s="1" t="n">
+        <v>0.02892</v>
+      </c>
+      <c r="F382" s="3" t="n">
+        <v>-0.004817618719889806</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -6565,6 +8863,12 @@
       <c r="D383" s="3" t="n">
         <v>-0.000459207102403112</v>
       </c>
+      <c r="E383" s="1" t="n">
+        <v>0.006518</v>
+      </c>
+      <c r="F383" s="3" t="n">
+        <v>-0.001837672281776395</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6581,6 +8885,12 @@
       <c r="D384" s="2" t="n">
         <v>0.02079303675048355</v>
       </c>
+      <c r="E384" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="F384" s="3" t="n">
+        <v>-0.01042160113690201</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6597,6 +8907,12 @@
       <c r="D385" s="2" t="n">
         <v>0.001988862370723946</v>
       </c>
+      <c r="E385" s="1" t="n">
+        <v>2523</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>0.001587931718936086</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -6613,6 +8929,12 @@
       <c r="D386" s="3" t="n">
         <v>-0.002012072434607703</v>
       </c>
+      <c r="E386" s="1" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="F386" s="3" t="n">
+        <v>-0.001512096774193522</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -6629,6 +8951,12 @@
       <c r="D387" s="2" t="n">
         <v>0.004956921987489717</v>
       </c>
+      <c r="E387" s="1" t="n">
+        <v>0.08536000000000001</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>0.002466236054022335</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -6645,6 +8973,12 @@
       <c r="D388" s="2" t="n">
         <v>0.0009950248756218499</v>
       </c>
+      <c r="E388" s="1" t="n">
+        <v>0.005013</v>
+      </c>
+      <c r="F388" s="3" t="n">
+        <v>-0.003379721669980051</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -6661,6 +8995,12 @@
       <c r="D389" s="2" t="n">
         <v>0.005020538566864558</v>
       </c>
+      <c r="E389" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>0.00227066303360572</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -6677,6 +9017,12 @@
       <c r="D390" s="2" t="n">
         <v>0.003837608563926505</v>
       </c>
+      <c r="E390" s="1" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="F390" s="3" t="n">
+        <v>-0.004225352112676038</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -6693,6 +9039,12 @@
       <c r="D391" s="2" t="n">
         <v>0.001856540084388139</v>
       </c>
+      <c r="E391" s="1" t="n">
+        <v>0.0005932999999999999</v>
+      </c>
+      <c r="F391" s="3" t="n">
+        <v>-0.0005053908355796184</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -6709,6 +9061,12 @@
       <c r="D392" s="2" t="n">
         <v>0.002402608546421731</v>
       </c>
+      <c r="E392" s="1" t="n">
+        <v>0.05836</v>
+      </c>
+      <c r="F392" s="3" t="n">
+        <v>-0.0008560178051702533</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -6725,6 +9083,12 @@
       <c r="D393" s="3" t="n">
         <v>-0.004109077325364176</v>
       </c>
+      <c r="E393" s="1" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>0.001500375093773486</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -6741,6 +9105,12 @@
       <c r="D394" s="2" t="n">
         <v>0.0006127450980391642</v>
       </c>
+      <c r="E394" s="1" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="F394" s="3" t="n">
+        <v>-0.0003061849357010713</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -6757,6 +9127,12 @@
       <c r="D395" s="2" t="n">
         <v>0.0008733624454147509</v>
       </c>
+      <c r="E395" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="F395" s="3" t="n">
+        <v>-0.0008726003490400436</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -6773,6 +9149,12 @@
       <c r="D396" s="2" t="n">
         <v>0.003573749187784356</v>
       </c>
+      <c r="E396" s="1" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>0.0003237293622531431</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -6789,6 +9171,12 @@
       <c r="D397" s="3" t="n">
         <v>-0.003957783641161063</v>
       </c>
+      <c r="E397" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>0.001986754966887382</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -6805,6 +9193,12 @@
       <c r="D398" s="2" t="n">
         <v>0.00522433927473881</v>
       </c>
+      <c r="E398" s="1" t="n">
+        <v>0.003275</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.001222867624579669</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -6821,6 +9215,12 @@
       <c r="D399" s="3" t="n">
         <v>-0.004253056884635843</v>
       </c>
+      <c r="E399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="F399" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -6837,6 +9237,12 @@
       <c r="D400" s="2" t="n">
         <v>0.005687473339968734</v>
       </c>
+      <c r="E400" s="1" t="n">
+        <v>0.007091</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0.00254488901456239</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -6853,6 +9259,12 @@
       <c r="D401" s="2" t="n">
         <v>0.006266394637131978</v>
       </c>
+      <c r="E401" s="1" t="n">
+        <v>0.006935</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>0.004344677769732153</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -6869,6 +9281,12 @@
       <c r="D402" s="3" t="n">
         <v>-0.0009977550511350787</v>
       </c>
+      <c r="E402" s="1" t="n">
+        <v>0.008023000000000001</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.001622971285892741</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -6885,6 +9303,12 @@
       <c r="D403" s="2" t="n">
         <v>0.01274817136886116</v>
       </c>
+      <c r="E403" s="1" t="n">
+        <v>0.04868</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>0.004539826661163805</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -6901,6 +9325,12 @@
       <c r="D404" s="2" t="n">
         <v>0.0002772963604853535</v>
       </c>
+      <c r="E404" s="1" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>0.006583962852588581</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -6917,6 +9347,12 @@
       <c r="D405" s="2" t="n">
         <v>0.002105755732335045</v>
       </c>
+      <c r="E405" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="F405" s="3" t="n">
+        <v>-0.005370067709549405</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -6933,6 +9369,12 @@
       <c r="D406" s="2" t="n">
         <v>0.0004186728072011262</v>
       </c>
+      <c r="E406" s="1" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="F406" s="3" t="n">
+        <v>-0.0008369951872776971</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -6949,6 +9391,12 @@
       <c r="D407" s="3" t="n">
         <v>-0.001225490196078461</v>
       </c>
+      <c r="E407" s="1" t="n">
+        <v>0.0004881</v>
+      </c>
+      <c r="F407" s="3" t="n">
+        <v>-0.001840490797545946</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -6965,6 +9413,12 @@
       <c r="D408" s="3" t="n">
         <v>-0.007352941176470573</v>
       </c>
+      <c r="E408" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>0.0008230452674898212</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -6981,6 +9435,12 @@
       <c r="D409" s="2" t="n">
         <v>0.006022187004754398</v>
       </c>
+      <c r="E409" s="1" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="F409" s="3" t="n">
+        <v>-0.002835538752362986</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -6997,6 +9457,12 @@
       <c r="D410" s="3" t="n">
         <v>-0.0007208073041805697</v>
       </c>
+      <c r="E410" s="1" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="F410" s="3" t="n">
+        <v>-0.0007213272421255649</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7013,6 +9479,12 @@
       <c r="D411" s="3" t="n">
         <v>-0.0006731740154829749</v>
       </c>
+      <c r="E411" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>0.0003368137420006599</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7029,6 +9501,12 @@
       <c r="D412" s="2" t="n">
         <v>0.0002194426157560089</v>
       </c>
+      <c r="E412" s="1" t="n">
+        <v>0.004556</v>
+      </c>
+      <c r="F412" s="3" t="n">
+        <v>-0.0004387889425187067</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7045,6 +9523,12 @@
       <c r="D413" s="3" t="n">
         <v>-0.00118623962040341</v>
       </c>
+      <c r="E413" s="1" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>0.0003958828186856254</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7061,6 +9545,12 @@
       <c r="D414" s="2" t="n">
         <v>0.003142183817753341</v>
       </c>
+      <c r="E414" s="1" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="F414" s="3" t="n">
+        <v>-0.003132341425215352</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7077,6 +9567,12 @@
       <c r="D415" s="2" t="n">
         <v>0.002981736861721956</v>
       </c>
+      <c r="E415" s="1" t="n">
+        <v>2.689</v>
+      </c>
+      <c r="F415" s="3" t="n">
+        <v>-0.0007432181345224005</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7093,6 +9589,12 @@
       <c r="D416" s="2" t="n">
         <v>0.0009270704573548284</v>
       </c>
+      <c r="E416" s="1" t="n">
+        <v>0.03245</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>0.001852423587526939</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7109,6 +9611,12 @@
       <c r="D417" s="2" t="n">
         <v>0.005833121988333782</v>
       </c>
+      <c r="E417" s="1" t="n">
+        <v>0.03973</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>0.001765002521432189</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7125,6 +9633,12 @@
       <c r="D418" s="2" t="n">
         <v>0.0005259006047856741</v>
       </c>
+      <c r="E418" s="1" t="n">
+        <v>0.07623000000000001</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>0.001708278580814785</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7141,6 +9655,12 @@
       <c r="D419" s="3" t="n">
         <v>-0.003007518796992489</v>
       </c>
+      <c r="E419" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="F419" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7157,6 +9677,12 @@
       <c r="D420" s="2" t="n">
         <v>0.002259887005649782</v>
       </c>
+      <c r="E420" s="1" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="F420" s="3" t="n">
+        <v>-0.003382187147688779</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -7173,6 +9699,12 @@
       <c r="D421" s="2" t="n">
         <v>0.005855290673358363</v>
       </c>
+      <c r="E421" s="1" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>0.002494802494802566</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -7189,6 +9721,12 @@
       <c r="D422" s="2" t="n">
         <v>0.005181347150259035</v>
       </c>
+      <c r="E422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="F422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7205,6 +9743,12 @@
       <c r="D423" s="3" t="n">
         <v>-0.0006653359946772388</v>
       </c>
+      <c r="E423" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>0.0006657789613847469</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -7221,6 +9765,12 @@
       <c r="D424" s="3" t="n">
         <v>-0.002371916508538957</v>
       </c>
+      <c r="E424" s="1" t="n">
+        <v>0.0002102</v>
+      </c>
+      <c r="F424" s="3" t="n">
+        <v>-0.0004755111745126126</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -7237,6 +9787,12 @@
       <c r="D425" s="3" t="n">
         <v>-0.00242718446601933</v>
       </c>
+      <c r="E425" s="1" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>0.0008110300081102107</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -7253,6 +9809,12 @@
       <c r="D426" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E426" s="1" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="F426" s="3" t="n">
+        <v>-0.002133712660028373</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -7269,6 +9831,12 @@
       <c r="D427" s="3" t="n">
         <v>-0.00154400411734425</v>
       </c>
+      <c r="E427" s="1" t="n">
+        <v>0.01939</v>
+      </c>
+      <c r="F427" s="3" t="n">
+        <v>-0.0005154639175257522</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -7285,6 +9853,12 @@
       <c r="D428" s="3" t="n">
         <v>-0.0009110233829335635</v>
       </c>
+      <c r="E428" s="1" t="n">
+        <v>0.06569</v>
+      </c>
+      <c r="F428" s="3" t="n">
+        <v>-0.001671732522796337</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -7301,6 +9875,12 @@
       <c r="D429" s="3" t="n">
         <v>-0.001507159005275099</v>
       </c>
+      <c r="E429" s="1" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="F429" s="3" t="n">
+        <v>-0.0007547169811322017</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -7317,6 +9897,12 @@
       <c r="D430" s="3" t="n">
         <v>-0.00234297557898531</v>
       </c>
+      <c r="E430" s="1" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>0.002619456237015739</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -7333,6 +9919,12 @@
       <c r="D431" s="2" t="n">
         <v>0.0001519064256416931</v>
       </c>
+      <c r="E431" s="1" t="n">
+        <v>0.006642</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>0.008809234507898051</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -7349,6 +9941,12 @@
       <c r="D432" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E432" s="1" t="n">
+        <v>0.001749</v>
+      </c>
+      <c r="F432" s="3" t="n">
+        <v>-0.001142204454597401</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -7365,6 +9963,12 @@
       <c r="D433" s="2" t="n">
         <v>0.01286633309506791</v>
       </c>
+      <c r="E433" s="1" t="n">
+        <v>0.001392</v>
+      </c>
+      <c r="F433" s="3" t="n">
+        <v>-0.01764290755116448</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7381,6 +9985,12 @@
       <c r="D434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E434" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="F434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -7397,6 +10007,12 @@
       <c r="D435" s="3" t="n">
         <v>-0.0008685353335965177</v>
       </c>
+      <c r="E435" s="1" t="n">
+        <v>0.12641</v>
+      </c>
+      <c r="F435" s="3" t="n">
+        <v>-0.00102734313260644</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -7413,6 +10029,12 @@
       <c r="D436" s="2" t="n">
         <v>0.001292490629442974</v>
       </c>
+      <c r="E436" s="1" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+      <c r="F436" s="3" t="n">
+        <v>-0.002194397831418659</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -7429,6 +10051,12 @@
       <c r="D437" s="2" t="n">
         <v>0.01162235312848268</v>
       </c>
+      <c r="E437" s="1" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="F437" s="3" t="n">
+        <v>-0.004249291784702431</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -7445,6 +10073,12 @@
       <c r="D438" s="2" t="n">
         <v>0.000453617600363033</v>
       </c>
+      <c r="E438" s="1" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>0.0002267059623667223</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -7461,6 +10095,12 @@
       <c r="D439" s="2" t="n">
         <v>0.0007129616426637441</v>
       </c>
+      <c r="E439" s="1" t="n">
+        <v>0.07002</v>
+      </c>
+      <c r="F439" s="3" t="n">
+        <v>-0.002279851809632479</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7477,6 +10117,12 @@
       <c r="D440" s="3" t="n">
         <v>-0.001976284584980214</v>
       </c>
+      <c r="E440" s="1" t="n">
+        <v>0.001515</v>
+      </c>
+      <c r="F440" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -7493,6 +10139,12 @@
       <c r="D441" s="2" t="n">
         <v>0.009254334645250535</v>
       </c>
+      <c r="E441" s="1" t="n">
+        <v>0.009507</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>0.002002529510961206</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -7509,6 +10161,12 @@
       <c r="D442" s="2" t="n">
         <v>0.007611798287345393</v>
       </c>
+      <c r="E442" s="1" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>0.002832861189801807</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7525,6 +10183,12 @@
       <c r="D443" s="2" t="n">
         <v>0.004065040650406495</v>
       </c>
+      <c r="E443" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="F443" s="3" t="n">
+        <v>-0.004048582995951408</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -7541,6 +10205,12 @@
       <c r="D444" s="3" t="n">
         <v>-0.002361584885856646</v>
       </c>
+      <c r="E444" s="1" t="n">
+        <v>0.0003781</v>
+      </c>
+      <c r="F444" s="3" t="n">
+        <v>-0.00552340873224632</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -7557,6 +10227,12 @@
       <c r="D445" s="3" t="n">
         <v>-0.004836415362731251</v>
       </c>
+      <c r="E445" s="1" t="n">
+        <v>0.03507</v>
+      </c>
+      <c r="F445" s="2" t="n">
+        <v>0.002572898799313888</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -7573,6 +10249,12 @@
       <c r="D446" s="3" t="n">
         <v>-0.001047242262043365</v>
       </c>
+      <c r="E446" s="1" t="n">
+        <v>0.08519</v>
+      </c>
+      <c r="F446" s="3" t="n">
+        <v>-0.00768782760628997</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -7589,6 +10271,12 @@
       <c r="D447" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E447" s="1" t="n">
+        <v>3.237</v>
+      </c>
+      <c r="F447" s="3" t="n">
+        <v>-0.002772643253234719</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -7605,6 +10293,12 @@
       <c r="D448" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E448" s="1" t="n">
+        <v>0.06394</v>
+      </c>
+      <c r="F448" s="2" t="n">
+        <v>0.001095976201659631</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -7621,6 +10315,12 @@
       <c r="D449" s="3" t="n">
         <v>-0.002662297767765766</v>
       </c>
+      <c r="E449" s="1" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="F449" s="3" t="n">
+        <v>-0.003490759753593387</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -7637,6 +10337,12 @@
       <c r="D450" s="3" t="n">
         <v>-0.005319148936170181</v>
       </c>
+      <c r="E450" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="F450" s="2" t="n">
+        <v>0.004010695187165705</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -7653,6 +10359,12 @@
       <c r="D451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E451" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="F451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -7669,6 +10381,12 @@
       <c r="D452" s="3" t="n">
         <v>-0.005268604760560646</v>
       </c>
+      <c r="E452" s="1" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="F452" s="3" t="n">
+        <v>-0.0009458053532583265</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -7685,6 +10403,12 @@
       <c r="D453" s="3" t="n">
         <v>-0.004959702417854942</v>
       </c>
+      <c r="E453" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="F453" s="3" t="n">
+        <v>-0.001869158878504597</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -7701,6 +10425,12 @@
       <c r="D454" s="2" t="n">
         <v>0.002111932418162542</v>
       </c>
+      <c r="E454" s="1" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="F454" s="2" t="n">
+        <v>0.0003512469265893537</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7717,6 +10447,12 @@
       <c r="D455" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E455" s="1" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="F455" s="2" t="n">
+        <v>0.001119820828667414</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -7733,6 +10469,12 @@
       <c r="D456" s="3" t="n">
         <v>-0.0006791171477079049</v>
       </c>
+      <c r="E456" s="1" t="n">
+        <v>2.941</v>
+      </c>
+      <c r="F456" s="3" t="n">
+        <v>-0.0006795786612301134</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -7749,6 +10491,12 @@
       <c r="D457" s="3" t="n">
         <v>-0.00202634245187446</v>
       </c>
+      <c r="E457" s="1" t="n">
+        <v>0.00983</v>
+      </c>
+      <c r="F457" s="3" t="n">
+        <v>-0.002030456852791795</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -7765,6 +10513,12 @@
       <c r="D458" s="3" t="n">
         <v>-0.003046824887748488</v>
       </c>
+      <c r="E458" s="1" t="n">
+        <v>0.06202</v>
+      </c>
+      <c r="F458" s="3" t="n">
+        <v>-0.002412739263310347</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -7781,6 +10535,12 @@
       <c r="D459" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E459" s="1" t="n">
+        <v>0.01437</v>
+      </c>
+      <c r="F459" s="3" t="n">
+        <v>-0.001389854065323084</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -7797,6 +10557,12 @@
       <c r="D460" s="2" t="n">
         <v>0.001563868384836777</v>
       </c>
+      <c r="E460" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F460" s="3" t="n">
+        <v>-0.0006870276684779584</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -7813,6 +10579,12 @@
       <c r="D461" s="2" t="n">
         <v>0.001832620647526099</v>
       </c>
+      <c r="E461" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>0.0006097560975609507</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7829,6 +10601,12 @@
       <c r="D462" s="2" t="n">
         <v>0.0009596928982725762</v>
       </c>
+      <c r="E462" s="1" t="n">
+        <v>0.0002088</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>0.000958772770853331</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -7845,6 +10623,12 @@
       <c r="D463" s="2" t="n">
         <v>0.001020408163265335</v>
       </c>
+      <c r="E463" s="1" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>0.002038735983690029</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -7861,6 +10645,12 @@
       <c r="D464" s="3" t="n">
         <v>-0.004204892966360818</v>
       </c>
+      <c r="E464" s="1" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="F464" s="3" t="n">
+        <v>-0.0003838771593090055</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -7877,6 +10667,12 @@
       <c r="D465" s="3" t="n">
         <v>-0.004010695187165728</v>
       </c>
+      <c r="E465" s="1" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>0.008053691275167807</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -7893,6 +10689,12 @@
       <c r="D466" s="3" t="n">
         <v>-0.003828623518687363</v>
       </c>
+      <c r="E466" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="F466" s="2" t="n">
+        <v>0.001098096632503615</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -7909,6 +10711,12 @@
       <c r="D467" s="2" t="n">
         <v>0.009074941451990566</v>
       </c>
+      <c r="E467" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="F467" s="3" t="n">
+        <v>-0.007252683492892376</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -7925,6 +10733,12 @@
       <c r="D468" s="2" t="n">
         <v>0.0003716090672612992</v>
       </c>
+      <c r="E468" s="1" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="F468" s="2" t="n">
+        <v>0.001857355126300043</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -7941,6 +10755,12 @@
       <c r="D469" s="2" t="n">
         <v>0.0005365526492287187</v>
       </c>
+      <c r="E469" s="1" t="n">
+        <v>0.0007499</v>
+      </c>
+      <c r="F469" s="2" t="n">
+        <v>0.005362649148679433</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -7957,6 +10777,12 @@
       <c r="D470" s="2" t="n">
         <v>0.002290950744558994</v>
       </c>
+      <c r="E470" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="F470" s="2" t="n">
+        <v>0.001142857142857144</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -7973,6 +10799,12 @@
       <c r="D471" s="3" t="n">
         <v>-0.001011122345803801</v>
       </c>
+      <c r="E471" s="1" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="F471" s="2" t="n">
+        <v>0.002024291497975802</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -7989,6 +10821,12 @@
       <c r="D472" s="2" t="n">
         <v>0.002347417840375565</v>
       </c>
+      <c r="E472" s="1" t="n">
+        <v>0.04672</v>
+      </c>
+      <c r="F472" s="3" t="n">
+        <v>-0.005322546306152869</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -8005,6 +10843,12 @@
       <c r="D473" s="3" t="n">
         <v>-0.0003663003663005293</v>
       </c>
+      <c r="E473" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="F473" s="3" t="n">
+        <v>-0.0003664345914253902</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8021,6 +10865,12 @@
       <c r="D474" s="2" t="n">
         <v>0.006460544531610579</v>
       </c>
+      <c r="E474" s="1" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>0.002292526364053252</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8037,6 +10887,12 @@
       <c r="D475" s="3" t="n">
         <v>-0.001308122249970341</v>
       </c>
+      <c r="E475" s="1" t="n">
+        <v>0.008416</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>0.002143367468444946</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8053,6 +10909,12 @@
       <c r="D476" s="3" t="n">
         <v>-0.0001223241590215291</v>
       </c>
+      <c r="E476" s="1" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="F476" s="3" t="n">
+        <v>-0.002446782481037336</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -8069,6 +10931,12 @@
       <c r="D477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E477" s="1" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="F477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -8085,6 +10953,12 @@
       <c r="D478" s="2" t="n">
         <v>0.002775674993691622</v>
       </c>
+      <c r="E478" s="1" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="F478" s="3" t="n">
+        <v>-0.003019627579265171</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -8101,6 +10975,12 @@
       <c r="D479" s="2" t="n">
         <v>0.002871500358937511</v>
       </c>
+      <c r="E479" s="1" t="n">
+        <v>0.008385999999999999</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>0.0004772130756381288</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -8117,6 +10997,12 @@
       <c r="D480" s="2" t="n">
         <v>0.0006281407035175624</v>
       </c>
+      <c r="E480" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>0.0006277463904582293</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -8133,6 +11019,12 @@
       <c r="D481" s="2" t="n">
         <v>0.0007789173049461832</v>
       </c>
+      <c r="E481" s="1" t="n">
+        <v>0.07696</v>
+      </c>
+      <c r="F481" s="3" t="n">
+        <v>-0.00168634064080951</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -8149,6 +11041,12 @@
       <c r="D482" s="3" t="n">
         <v>-0.0007928642220019498</v>
       </c>
+      <c r="E482" s="1" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="F482" s="2" t="n">
+        <v>0.001785360047609597</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -8165,6 +11063,12 @@
       <c r="D483" s="3" t="n">
         <v>-0.004119464469618961</v>
       </c>
+      <c r="E483" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="F483" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -8181,6 +11085,12 @@
       <c r="D484" s="2" t="n">
         <v>0.001325869180907583</v>
       </c>
+      <c r="E484" s="1" t="n">
+        <v>0.06793</v>
+      </c>
+      <c r="F484" s="3" t="n">
+        <v>-0.0005884949242312545</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -8197,6 +11107,12 @@
       <c r="D485" s="2" t="n">
         <v>0.003798882681564338</v>
       </c>
+      <c r="E485" s="1" t="n">
+        <v>0.0004495</v>
+      </c>
+      <c r="F485" s="2" t="n">
+        <v>0.0006678539626000736</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -8213,6 +11129,12 @@
       <c r="D486" s="2" t="n">
         <v>0.006021829130598347</v>
       </c>
+      <c r="E486" s="1" t="n">
+        <v>0.07964</v>
+      </c>
+      <c r="F486" s="3" t="n">
+        <v>-0.006858710562414203</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -8229,6 +11151,12 @@
       <c r="D487" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E487" s="1" t="n">
+        <v>0.0001728</v>
+      </c>
+      <c r="F487" s="3" t="n">
+        <v>-0.001156069364161878</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -8245,6 +11173,12 @@
       <c r="D488" s="3" t="n">
         <v>-0.001600731763091713</v>
       </c>
+      <c r="E488" s="1" t="n">
+        <v>0.08766</v>
+      </c>
+      <c r="F488" s="2" t="n">
+        <v>0.003893724232707364</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -8261,6 +11195,12 @@
       <c r="D489" s="3" t="n">
         <v>-0.008786610878661165</v>
       </c>
+      <c r="E489" s="1" t="n">
+        <v>0.04746</v>
+      </c>
+      <c r="F489" s="2" t="n">
+        <v>0.001688476150274455</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -8277,6 +11217,12 @@
       <c r="D490" s="3" t="n">
         <v>-0.01597276774024612</v>
       </c>
+      <c r="E490" s="1" t="n">
+        <v>0.03809</v>
+      </c>
+      <c r="F490" s="2" t="n">
+        <v>0.01357104843001587</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -8293,6 +11239,12 @@
       <c r="D491" s="2" t="n">
         <v>0.002441845521141186</v>
       </c>
+      <c r="E491" s="1" t="n">
+        <v>0.07789</v>
+      </c>
+      <c r="F491" s="3" t="n">
+        <v>-0.001410256410256397</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -8309,6 +11261,12 @@
       <c r="D492" s="3" t="n">
         <v>-0.0001580278128950083</v>
       </c>
+      <c r="E492" s="1" t="n">
+        <v>0.06351</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>0.003793266951161533</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -8325,6 +11283,12 @@
       <c r="D493" s="3" t="n">
         <v>-0.001926782273603171</v>
       </c>
+      <c r="E493" s="1" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F493" s="2" t="n">
+        <v>0.003861003861003872</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -8341,6 +11305,12 @@
       <c r="D494" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E494" s="1" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="F494" s="3" t="n">
+        <v>-0.0003619254433586283</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -8357,6 +11327,12 @@
       <c r="D495" s="2" t="n">
         <v>0.001257663889325526</v>
       </c>
+      <c r="E495" s="1" t="n">
+        <v>0.06361</v>
+      </c>
+      <c r="F495" s="3" t="n">
+        <v>-0.001256084157638511</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -8373,6 +11349,12 @@
       <c r="D496" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E496" s="1" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="F496" s="2" t="n">
+        <v>0.000341296928327797</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -8389,6 +11371,12 @@
       <c r="D497" s="3" t="n">
         <v>-0.02304921968787521</v>
       </c>
+      <c r="E497" s="1" t="n">
+        <v>0.07988000000000001</v>
+      </c>
+      <c r="F497" s="3" t="n">
+        <v>-0.01843204718604064</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -8405,6 +11393,12 @@
       <c r="D498" s="3" t="n">
         <v>-0.003868471953578447</v>
       </c>
+      <c r="E498" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="F498" s="2" t="n">
+        <v>0.0009708737864077948</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -8421,6 +11415,12 @@
       <c r="D499" s="3" t="n">
         <v>-0.0007232401157184727</v>
       </c>
+      <c r="E499" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="F499" s="3" t="n">
+        <v>-0.001688781664656227</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -8437,6 +11437,12 @@
       <c r="D500" s="3" t="n">
         <v>-0.002669902912621334</v>
       </c>
+      <c r="E500" s="1" t="n">
+        <v>0.04103</v>
+      </c>
+      <c r="F500" s="3" t="n">
+        <v>-0.001460209296665965</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -8453,6 +11459,12 @@
       <c r="D501" s="2" t="n">
         <v>0.001004016064257057</v>
       </c>
+      <c r="E501" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="F501" s="3" t="n">
+        <v>-0.001003009027081273</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -8469,6 +11481,12 @@
       <c r="D502" s="3" t="n">
         <v>-0.0003025718608169842</v>
       </c>
+      <c r="E502" s="1" t="n">
+        <v>0.003303</v>
+      </c>
+      <c r="F502" s="3" t="n">
+        <v>-0.0003026634382566988</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -8485,6 +11503,12 @@
       <c r="D503" s="2" t="n">
         <v>0.01096491228070188</v>
       </c>
+      <c r="E503" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="F503" s="3" t="n">
+        <v>-0.009761388286334223</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -8501,6 +11525,12 @@
       <c r="D504" s="2" t="n">
         <v>0.004458598726114689</v>
       </c>
+      <c r="E504" s="1" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="F504" s="3" t="n">
+        <v>-0.002536461636017828</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -8517,6 +11547,12 @@
       <c r="D505" s="2" t="n">
         <v>0.0007633587786258701</v>
       </c>
+      <c r="E505" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="F505" s="3" t="n">
+        <v>-0.001525553012967244</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -8533,6 +11569,12 @@
       <c r="D506" s="3" t="n">
         <v>-0.00177409816676536</v>
       </c>
+      <c r="E506" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="F506" s="3" t="n">
+        <v>-0.003554502369668102</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -8549,6 +11591,12 @@
       <c r="D507" s="2" t="n">
         <v>0.001384083044982582</v>
       </c>
+      <c r="E507" s="1" t="n">
+        <v>0.002884</v>
+      </c>
+      <c r="F507" s="3" t="n">
+        <v>-0.003455425017277134</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -8565,6 +11613,12 @@
       <c r="D508" s="2" t="n">
         <v>0.002737226277372164</v>
       </c>
+      <c r="E508" s="1" t="n">
+        <v>2.206</v>
+      </c>
+      <c r="F508" s="2" t="n">
+        <v>0.00363967242948135</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -8581,6 +11635,12 @@
       <c r="D509" s="3" t="n">
         <v>-0.0003620564808109918</v>
       </c>
+      <c r="E509" s="1" t="n">
+        <v>0.05487</v>
+      </c>
+      <c r="F509" s="3" t="n">
+        <v>-0.00633828323071344</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -8597,6 +11657,12 @@
       <c r="D510" s="3" t="n">
         <v>-0.001363326516700813</v>
       </c>
+      <c r="E510" s="1" t="n">
+        <v>0.02925</v>
+      </c>
+      <c r="F510" s="3" t="n">
+        <v>-0.001706484641638156</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -8613,6 +11679,12 @@
       <c r="D511" s="3" t="n">
         <v>-0.002718062762540128</v>
       </c>
+      <c r="E511" s="1" t="n">
+        <v>0.04037</v>
+      </c>
+      <c r="F511" s="2" t="n">
+        <v>0.0002477700693756953</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -8629,6 +11701,12 @@
       <c r="D512" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E512" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F512" s="3" t="n">
+        <v>-0.01162790697674404</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -8645,6 +11723,12 @@
       <c r="D513" s="3" t="n">
         <v>-0.000337518563521097</v>
       </c>
+      <c r="E513" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="F513" s="3" t="n">
+        <v>-0.001958268620433487</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -8661,6 +11745,12 @@
       <c r="D514" s="2" t="n">
         <v>0.0005740528128588792</v>
       </c>
+      <c r="E514" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="F514" s="3" t="n">
+        <v>-0.00172117039586932</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -8677,6 +11767,12 @@
       <c r="D515" s="2" t="n">
         <v>0.002798507462686518</v>
       </c>
+      <c r="E515" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="F515" s="3" t="n">
+        <v>-0.0009302325581395615</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -8693,6 +11789,12 @@
       <c r="D516" s="3" t="n">
         <v>-0.003773584905660387</v>
       </c>
+      <c r="E516" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="F516" s="2" t="n">
+        <v>0.007575757575757596</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -8709,6 +11811,12 @@
       <c r="D517" s="3" t="n">
         <v>-0.00285603011813572</v>
       </c>
+      <c r="E517" s="1" t="n">
+        <v>0.007688</v>
+      </c>
+      <c r="F517" s="2" t="n">
+        <v>0.0009113396693138994</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -8725,6 +11833,12 @@
       <c r="D518" s="2" t="n">
         <v>0.003919007184846459</v>
       </c>
+      <c r="E518" s="1" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="F518" s="2" t="n">
+        <v>0.002602472348731301</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -8741,6 +11855,12 @@
       <c r="D519" s="3" t="n">
         <v>-0.002429543245869678</v>
       </c>
+      <c r="E519" s="1" t="n">
+        <v>0.004086</v>
+      </c>
+      <c r="F519" s="3" t="n">
+        <v>-0.004870920603994167</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -8757,6 +11877,12 @@
       <c r="D520" s="3" t="n">
         <v>-0.001721170395869233</v>
       </c>
+      <c r="E520" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="F520" s="3" t="n">
+        <v>-0.001724137931034525</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -8773,6 +11899,12 @@
       <c r="D521" s="3" t="n">
         <v>-0.009658246656760766</v>
       </c>
+      <c r="E521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="F521" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -8789,6 +11921,12 @@
       <c r="D522" s="2" t="n">
         <v>0.002044989775051224</v>
       </c>
+      <c r="E522" s="1" t="n">
+        <v>0.6839</v>
+      </c>
+      <c r="F522" s="3" t="n">
+        <v>-0.003061224489796067</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -8805,6 +11943,12 @@
       <c r="D523" s="3" t="n">
         <v>-0.004847447961220318</v>
       </c>
+      <c r="E523" s="1" t="n">
+        <v>0.06975000000000001</v>
+      </c>
+      <c r="F523" s="3" t="n">
+        <v>-0.0007163323782234168</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -8821,6 +11965,12 @@
       <c r="D524" s="2" t="n">
         <v>0.001734605377276599</v>
       </c>
+      <c r="E524" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="F524" s="3" t="n">
+        <v>-0.0008658008658008306</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -8837,6 +11987,12 @@
       <c r="D525" s="2" t="n">
         <v>0.002447980416156571</v>
       </c>
+      <c r="E525" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="F525" s="3" t="n">
+        <v>-0.006105006105006069</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -8853,6 +12009,12 @@
       <c r="D526" s="3" t="n">
         <v>-0.001027900146842887</v>
       </c>
+      <c r="E526" s="1" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="F526" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -8869,6 +12031,12 @@
       <c r="D527" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E527" s="1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="F527" s="2" t="n">
+        <v>0.0004664179104477422</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -8885,6 +12053,12 @@
       <c r="D528" s="3" t="n">
         <v>-0.00147221199852783</v>
       </c>
+      <c r="E528" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="F528" s="2" t="n">
+        <v>0.00073719130114277</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -8901,6 +12075,12 @@
       <c r="D529" s="3" t="n">
         <v>-0.0002774694783573875</v>
       </c>
+      <c r="E529" s="1" t="n">
+        <v>0.000719</v>
+      </c>
+      <c r="F529" s="3" t="n">
+        <v>-0.002220371912295213</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -8917,6 +12097,12 @@
       <c r="D530" s="3" t="n">
         <v>-0.0007187350263535053</v>
       </c>
+      <c r="E530" s="1" t="n">
+        <v>0.00416</v>
+      </c>
+      <c r="F530" s="3" t="n">
+        <v>-0.002637257252457586</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -8933,6 +12119,12 @@
       <c r="D531" s="3" t="n">
         <v>-0.0007656967840735926</v>
       </c>
+      <c r="E531" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="F531" s="2" t="n">
+        <v>0.002298850574712731</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -8949,6 +12141,12 @@
       <c r="D532" s="2" t="n">
         <v>0.0008460236886633068</v>
       </c>
+      <c r="E532" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="F532" s="3" t="n">
+        <v>-0.003381234150464899</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -8965,6 +12163,12 @@
       <c r="D533" s="3" t="n">
         <v>-0.002814787014449191</v>
       </c>
+      <c r="E533" s="1" t="n">
+        <v>0.05333</v>
+      </c>
+      <c r="F533" s="2" t="n">
+        <v>0.003575461046292862</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -8981,6 +12185,12 @@
       <c r="D534" s="2" t="n">
         <v>0.001996007984032086</v>
       </c>
+      <c r="E534" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="F534" s="3" t="n">
+        <v>-0.001992031872510109</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -8997,6 +12207,12 @@
       <c r="D535" s="3" t="n">
         <v>-0.001173708920187746</v>
       </c>
+      <c r="E535" s="1" t="n">
+        <v>0.01704</v>
+      </c>
+      <c r="F535" s="2" t="n">
+        <v>0.001175088131609823</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -9013,6 +12229,12 @@
       <c r="D536" s="2" t="n">
         <v>0.003433649767723798</v>
       </c>
+      <c r="E536" s="1" t="n">
+        <v>0.004956</v>
+      </c>
+      <c r="F536" s="3" t="n">
+        <v>-0.002415458937198039</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -9029,6 +12251,12 @@
       <c r="D537" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E537" s="1" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="F537" s="3" t="n">
+        <v>-0.0006894174422614046</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -9045,6 +12273,12 @@
       <c r="D538" s="3" t="n">
         <v>-0.0007598784194528566</v>
       </c>
+      <c r="E538" s="1" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="F538" s="3" t="n">
+        <v>-0.001520912547528587</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -9061,6 +12295,12 @@
       <c r="D539" s="3" t="n">
         <v>-0.001225490196078381</v>
       </c>
+      <c r="E539" s="1" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="F539" s="3" t="n">
+        <v>-0.0008179959100204166</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -9077,6 +12317,12 @@
       <c r="D540" s="2" t="n">
         <v>0.0008824567596188039</v>
       </c>
+      <c r="E540" s="1" t="n">
+        <v>0.05666</v>
+      </c>
+      <c r="F540" s="3" t="n">
+        <v>-0.0008816787162758143</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -9093,6 +12339,12 @@
       <c r="D541" s="3" t="n">
         <v>-0.008620689655172362</v>
       </c>
+      <c r="E541" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -9109,6 +12361,12 @@
       <c r="D542" s="2" t="n">
         <v>0.009090909090909158</v>
       </c>
+      <c r="E542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="F542" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9124,6 +12382,12 @@
       </c>
       <c r="D543" s="3" t="n">
         <v>-0.0005448106782892487</v>
+      </c>
+      <c r="E543" s="1" t="n">
+        <v>0.003661</v>
+      </c>
+      <c r="F543" s="3" t="n">
+        <v>-0.002180430635050357</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>change_00:30</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>price_00:45</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change_00:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +499,12 @@
       <c r="F2" s="2" t="n">
         <v>6.107408001844878e-05</v>
       </c>
+      <c r="G2" s="1" t="n">
+        <v>70710</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.004252200662968277</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +527,12 @@
       <c r="F3" s="2" t="n">
         <v>0.0007304957631245738</v>
       </c>
+      <c r="G3" s="1" t="n">
+        <v>2068.37</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.006555063506739889</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,6 +555,12 @@
       <c r="F4" s="2" t="n">
         <v>0.0004662004662005391</v>
       </c>
+      <c r="G4" s="1" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.007106244175209686</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,6 +583,12 @@
       <c r="F5" s="2" t="n">
         <v>0.01778589301413399</v>
       </c>
+      <c r="G5" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.02724252491694345</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -575,6 +611,12 @@
       <c r="F6" s="3" t="n">
         <v>-0.001187520241822293</v>
       </c>
+      <c r="G6" s="1" t="n">
+        <v>0.09297</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.004863813229571899</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -597,6 +639,12 @@
       <c r="F7" s="2" t="n">
         <v>0.0001446131597975256</v>
       </c>
+      <c r="G7" s="1" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.004120879120879149</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,6 +667,12 @@
       <c r="F8" s="2" t="n">
         <v>0.006819504892856214</v>
       </c>
+      <c r="G8" s="1" t="n">
+        <v>36.349</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.0008260139321014904</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -641,6 +695,12 @@
       <c r="F9" s="3" t="n">
         <v>-0.00143434405749707</v>
       </c>
+      <c r="G9" s="1" t="n">
+        <v>649.1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.002548459340489578</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,6 +723,12 @@
       <c r="F10" s="3" t="n">
         <v>-0.008541875208541883</v>
       </c>
+      <c r="G10" s="1" t="n">
+        <v>15.179</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.02167328532005122</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,6 +751,12 @@
       <c r="F11" s="3" t="n">
         <v>-0.005460588793922154</v>
       </c>
+      <c r="G11" s="1" t="n">
+        <v>210.39</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.004487944616853654</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +779,12 @@
       <c r="F12" s="3" t="n">
         <v>-0.000449545958581892</v>
       </c>
+      <c r="G12" s="1" t="n">
+        <v>0.0033486</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.004017750059966484</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -729,6 +807,12 @@
       <c r="F13" s="3" t="n">
         <v>-0.0247238295633876</v>
       </c>
+      <c r="G13" s="1" t="n">
+        <v>0.03707</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-0.0002696871628911289</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -751,6 +835,12 @@
       <c r="F14" s="3" t="n">
         <v>-0.01636904761904763</v>
       </c>
+      <c r="G14" s="1" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.0007564296520422767</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -773,6 +863,12 @@
       <c r="F15" s="3" t="n">
         <v>-0.00215605749486652</v>
       </c>
+      <c r="G15" s="1" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.007613952052680278</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -795,6 +891,12 @@
       <c r="F16" s="3" t="n">
         <v>-0.02277039848197347</v>
       </c>
+      <c r="G16" s="1" t="n">
+        <v>0.05605</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-0.01059135039717558</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -817,6 +919,12 @@
       <c r="F17" s="3" t="n">
         <v>-0.001135073779795688</v>
       </c>
+      <c r="G17" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.003409090909090912</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -839,6 +947,12 @@
       <c r="F18" s="3" t="n">
         <v>-0.001903311762466694</v>
       </c>
+      <c r="G18" s="1" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.006102212051868765</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -861,6 +975,12 @@
       <c r="F19" s="2" t="n">
         <v>0.003542299220098734</v>
       </c>
+      <c r="G19" s="1" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.006940942663067685</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -883,6 +1003,12 @@
       <c r="F20" s="2" t="n">
         <v>0.0001041883725775626</v>
       </c>
+      <c r="G20" s="1" t="n">
+        <v>9.654999999999999</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.005833941035524447</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -905,6 +1031,12 @@
       <c r="F21" s="2" t="n">
         <v>0.008116146594747116</v>
       </c>
+      <c r="G21" s="1" t="n">
+        <v>199.93</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-0.0002500250025001648</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -927,6 +1059,12 @@
       <c r="F22" s="2" t="n">
         <v>0.01730543605788034</v>
       </c>
+      <c r="G22" s="1" t="n">
+        <v>0.021069</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.01244593945218656</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -949,6 +1087,12 @@
       <c r="F23" s="3" t="n">
         <v>-0.00048246672076148</v>
       </c>
+      <c r="G23" s="1" t="n">
+        <v>457.02</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0.002742611404875266</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -971,6 +1115,12 @@
       <c r="F24" s="3" t="n">
         <v>-0.0009901832612613794</v>
       </c>
+      <c r="G24" s="1" t="n">
+        <v>5172.59</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.001345428640013593</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -993,6 +1143,12 @@
       <c r="F25" s="3" t="n">
         <v>-0.000889086463658493</v>
       </c>
+      <c r="G25" s="1" t="n">
+        <v>9.061999999999999</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0.008008898776418151</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1015,6 +1171,12 @@
       <c r="F26" s="2" t="n">
         <v>0.001042084168336714</v>
       </c>
+      <c r="G26" s="1" t="n">
+        <v>0.12071</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-0.03339205637411921</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1037,6 +1199,12 @@
       <c r="F27" s="3" t="n">
         <v>-0.005631536604987982</v>
       </c>
+      <c r="G27" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-0.002427184466019319</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1059,6 +1227,12 @@
       <c r="F28" s="2" t="n">
         <v>0.001550387596899226</v>
       </c>
+      <c r="G28" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0.003869969040247595</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1081,6 +1255,12 @@
       <c r="F29" s="3" t="n">
         <v>-0.02075313807531378</v>
       </c>
+      <c r="G29" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0.02546573235344383</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1103,6 +1283,12 @@
       <c r="F30" s="3" t="n">
         <v>-0.000658327847267867</v>
       </c>
+      <c r="G30" s="1" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0.003952569169960478</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1125,6 +1311,12 @@
       <c r="F31" s="3" t="n">
         <v>-0.00687960687960694</v>
       </c>
+      <c r="G31" s="1" t="n">
+        <v>0.002037</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.007916872835230277</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1147,6 +1339,12 @@
       <c r="F32" s="3" t="n">
         <v>-0.004449938195302833</v>
       </c>
+      <c r="G32" s="1" t="n">
+        <v>0.04052</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.006208095356344679</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1169,6 +1367,12 @@
       <c r="F33" s="3" t="n">
         <v>-0.003054989816700557</v>
       </c>
+      <c r="G33" s="1" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0.005107252298263538</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1191,6 +1395,12 @@
       <c r="F34" s="3" t="n">
         <v>-0.001912045889101261</v>
       </c>
+      <c r="G34" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.006704980842911803</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1213,6 +1423,12 @@
       <c r="F35" s="2" t="n">
         <v>0.0122767857142858</v>
       </c>
+      <c r="G35" s="1" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>-0.00882028665931645</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1235,6 +1451,12 @@
       <c r="F36" s="3" t="n">
         <v>-0.002796420581655484</v>
       </c>
+      <c r="G36" s="1" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.003925967470555279</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1257,6 +1479,12 @@
       <c r="F37" s="3" t="n">
         <v>-0.005141388174807137</v>
       </c>
+      <c r="G37" s="1" t="n">
+        <v>0.005819</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0.002411714039621037</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1279,6 +1507,12 @@
       <c r="F38" s="3" t="n">
         <v>-0.004572421872047723</v>
       </c>
+      <c r="G38" s="1" t="n">
+        <v>0.26365</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.0008731303621593196</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1301,6 +1535,12 @@
       <c r="F39" s="2" t="n">
         <v>0.003564356435643556</v>
       </c>
+      <c r="G39" s="1" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.004538279400157737</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1323,6 +1563,12 @@
       <c r="F40" s="3" t="n">
         <v>-0.004812580492103223</v>
       </c>
+      <c r="G40" s="1" t="n">
+        <v>0.14908</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.01539299822912399</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1345,6 +1591,12 @@
       <c r="F41" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="G41" s="1" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0.008373205741626869</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1367,6 +1619,12 @@
       <c r="F42" s="2" t="n">
         <v>0.0005397139516056694</v>
       </c>
+      <c r="G42" s="1" t="n">
+        <v>112.12</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.008001438460846898</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1389,6 +1647,12 @@
       <c r="F43" s="2" t="n">
         <v>0.04135278089437417</v>
       </c>
+      <c r="G43" s="1" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0.05156225950438659</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1411,6 +1675,12 @@
       <c r="F44" s="2" t="n">
         <v>0.0001829826166513817</v>
       </c>
+      <c r="G44" s="1" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.004756677643615169</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1433,6 +1703,12 @@
       <c r="F45" s="2" t="n">
         <v>0.006420297422211889</v>
       </c>
+      <c r="G45" s="1" t="n">
+        <v>0.52898</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.01642872240262871</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1455,6 +1731,12 @@
       <c r="F46" s="3" t="n">
         <v>-0.0002849002849002535</v>
       </c>
+      <c r="G46" s="1" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.002992305500142478</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1477,6 +1759,12 @@
       <c r="F47" s="3" t="n">
         <v>-0.0005134788189987738</v>
       </c>
+      <c r="G47" s="1" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.005394297456974147</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1499,6 +1787,12 @@
       <c r="F48" s="3" t="n">
         <v>-0.002012325493648516</v>
       </c>
+      <c r="G48" s="1" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.008695652173912995</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1521,6 +1815,12 @@
       <c r="F49" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G49" s="1" t="n">
+        <v>0.06058</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.004643449419568863</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1543,6 +1843,12 @@
       <c r="F50" s="3" t="n">
         <v>-0.002597402597402672</v>
       </c>
+      <c r="G50" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.005208333333333483</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1565,6 +1871,12 @@
       <c r="F51" s="2" t="n">
         <v>0.0279581694563859</v>
       </c>
+      <c r="G51" s="1" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0.001868549056827512</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1587,6 +1899,12 @@
       <c r="F52" s="3" t="n">
         <v>-0.01127819548872189</v>
       </c>
+      <c r="G52" s="1" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0.01140684410646397</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1609,6 +1927,12 @@
       <c r="F53" s="3" t="n">
         <v>-0.004424778761061986</v>
       </c>
+      <c r="G53" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0.01269841269841271</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1631,6 +1955,12 @@
       <c r="F54" s="3" t="n">
         <v>-0.0001032737787876691</v>
       </c>
+      <c r="G54" s="1" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0.000378709632995934</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1653,6 +1983,12 @@
       <c r="F55" s="3" t="n">
         <v>-0.002939529675251986</v>
       </c>
+      <c r="G55" s="1" t="n">
+        <v>0.007188</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0.009125368524498098</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1675,6 +2011,12 @@
       <c r="F56" s="2" t="n">
         <v>0.0018050541516246</v>
       </c>
+      <c r="G56" s="1" t="n">
+        <v>0.02833</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0.02090090090090092</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1697,6 +2039,12 @@
       <c r="F57" s="3" t="n">
         <v>-0.001429252024773809</v>
       </c>
+      <c r="G57" s="1" t="n">
+        <v>0.04213</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0.005009541984732868</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1719,6 +2067,12 @@
       <c r="F58" s="3" t="n">
         <v>-0.02553281282971097</v>
       </c>
+      <c r="G58" s="1" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.01559116500649628</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1741,6 +2095,12 @@
       <c r="F59" s="3" t="n">
         <v>-0.001974983541803747</v>
       </c>
+      <c r="G59" s="1" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.007915567282321907</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1763,6 +2123,12 @@
       <c r="F60" s="3" t="n">
         <v>-0.005830903790087479</v>
       </c>
+      <c r="G60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.005865102639296203</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1785,6 +2151,12 @@
       <c r="F61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G61" s="1" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.005201560468140411</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1807,6 +2179,12 @@
       <c r="F62" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G62" s="1" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1829,6 +2207,12 @@
       <c r="F63" s="3" t="n">
         <v>-0.004725085910652877</v>
       </c>
+      <c r="G63" s="1" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0.00848798733995095</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1851,6 +2235,12 @@
       <c r="F64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G64" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.001364256480218282</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1873,6 +2263,12 @@
       <c r="F65" s="2" t="n">
         <v>0.003357112882920697</v>
       </c>
+      <c r="G65" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-0.001254705144291186</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1895,6 +2291,12 @@
       <c r="F66" s="3" t="n">
         <v>-0.001980198019802037</v>
       </c>
+      <c r="G66" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.006944444444444506</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1917,6 +2319,12 @@
       <c r="F67" s="3" t="n">
         <v>-0.001352630867036448</v>
       </c>
+      <c r="G67" s="1" t="n">
+        <v>0.007409</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0.003521603684139236</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1939,6 +2347,12 @@
       <c r="F68" s="3" t="n">
         <v>-0.01182160128962917</v>
       </c>
+      <c r="G68" s="1" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.008156606851549678</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1961,6 +2375,12 @@
       <c r="F69" s="2" t="n">
         <v>0.002041573867854602</v>
       </c>
+      <c r="G69" s="1" t="n">
+        <v>0.05413</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.002593072791257534</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1983,6 +2403,12 @@
       <c r="F70" s="3" t="n">
         <v>-0.008333333333333342</v>
       </c>
+      <c r="G70" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.004201680672268912</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2005,6 +2431,12 @@
       <c r="F71" s="3" t="n">
         <v>-0.007430447554864377</v>
       </c>
+      <c r="G71" s="1" t="n">
+        <v>5.853</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0.01897632311977716</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2027,6 +2459,12 @@
       <c r="F72" s="3" t="n">
         <v>-0.004310344827586156</v>
       </c>
+      <c r="G72" s="1" t="n">
+        <v>0.002075</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>-0.001924001924001971</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2049,6 +2487,12 @@
       <c r="F73" s="3" t="n">
         <v>-0.00180889550968283</v>
       </c>
+      <c r="G73" s="1" t="n">
+        <v>0.9437</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0.005969512845112396</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2071,6 +2515,12 @@
       <c r="F74" s="3" t="n">
         <v>-0.001659751037344331</v>
       </c>
+      <c r="G74" s="1" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0.003325020781379863</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2093,6 +2543,12 @@
       <c r="F75" s="2" t="n">
         <v>0.00399954290938172</v>
       </c>
+      <c r="G75" s="1" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0.0003414523104939806</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2115,6 +2571,12 @@
       <c r="F76" s="2" t="n">
         <v>0.007845812723861421</v>
       </c>
+      <c r="G76" s="1" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0.004823151125401938</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2137,6 +2599,12 @@
       <c r="F77" s="2" t="n">
         <v>0.004341534008683058</v>
       </c>
+      <c r="G77" s="1" t="n">
+        <v>0.06315</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.01104707012487986</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2159,6 +2627,12 @@
       <c r="F78" s="3" t="n">
         <v>-0.002453071672354886</v>
       </c>
+      <c r="G78" s="1" t="n">
+        <v>0.09406</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0.005666631027477843</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2181,6 +2655,12 @@
       <c r="F79" s="2" t="n">
         <v>0.01579203109815356</v>
       </c>
+      <c r="G79" s="1" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>-0.001913417842621437</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2203,6 +2683,12 @@
       <c r="F80" s="3" t="n">
         <v>-0.001338464112430873</v>
       </c>
+      <c r="G80" s="1" t="n">
+        <v>0.00601</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0.006868822248282689</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2225,6 +2711,12 @@
       <c r="F81" s="2" t="n">
         <v>0.003868471953578313</v>
       </c>
+      <c r="G81" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>-0.003853564547206142</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2247,6 +2739,12 @@
       <c r="F82" s="3" t="n">
         <v>-0.0009852216748768754</v>
       </c>
+      <c r="G82" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0.008875739644970394</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2269,6 +2767,12 @@
       <c r="F83" s="2" t="n">
         <v>0.0005065856129685125</v>
       </c>
+      <c r="G83" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>-0.01333333333333332</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2291,6 +2795,12 @@
       <c r="F84" s="2" t="n">
         <v>0.004170822377368698</v>
       </c>
+      <c r="G84" s="1" t="n">
+        <v>1.1142</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.006049661399548669</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2313,6 +2823,12 @@
       <c r="F85" s="3" t="n">
         <v>-0.002201027146001505</v>
       </c>
+      <c r="G85" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>-0.01985294117647055</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2335,6 +2851,12 @@
       <c r="F86" s="2" t="n">
         <v>0.002995805871779595</v>
       </c>
+      <c r="G86" s="1" t="n">
+        <v>0.01676</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0.001194743130226952</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2357,6 +2879,12 @@
       <c r="F87" s="3" t="n">
         <v>-0.001690821256038569</v>
       </c>
+      <c r="G87" s="1" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0.00532300992015491</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2379,6 +2907,12 @@
       <c r="F88" s="2" t="n">
         <v>0.00316022829111831</v>
       </c>
+      <c r="G88" s="1" t="n">
+        <v>2.1066</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>-0.009497837126198984</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2401,6 +2935,12 @@
       <c r="F89" s="3" t="n">
         <v>-0.002896032435563286</v>
       </c>
+      <c r="G89" s="1" t="n">
+        <v>0.006814</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>-0.01045599767644496</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2423,6 +2963,12 @@
       <c r="F90" s="3" t="n">
         <v>-0.001312335958005221</v>
       </c>
+      <c r="G90" s="1" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.001314060446780524</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2445,6 +2991,12 @@
       <c r="F91" s="3" t="n">
         <v>-0.004484304932735414</v>
       </c>
+      <c r="G91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2467,6 +3019,12 @@
       <c r="F92" s="2" t="n">
         <v>0.019423076923077</v>
       </c>
+      <c r="G92" s="1" t="n">
+        <v>0.05275</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>-0.004904734955668804</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2489,6 +3047,12 @@
       <c r="F93" s="3" t="n">
         <v>-7.601094557632336e-05</v>
       </c>
+      <c r="G93" s="1" t="n">
+        <v>1.3204</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0.003724819460281358</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2511,6 +3075,12 @@
       <c r="F94" s="2" t="n">
         <v>0.001290584265934118</v>
       </c>
+      <c r="G94" s="1" t="n">
+        <v>0.053855</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>-0.008359572078292788</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2533,6 +3103,12 @@
       <c r="F95" s="2" t="n">
         <v>0.002067824648469811</v>
       </c>
+      <c r="G95" s="1" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2555,6 +3131,12 @@
       <c r="F96" s="3" t="n">
         <v>-0.0006451612903225096</v>
       </c>
+      <c r="G96" s="1" t="n">
+        <v>1.0857</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0.001291155584247964</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2577,6 +3159,12 @@
       <c r="F97" s="3" t="n">
         <v>-0.002730109204368307</v>
       </c>
+      <c r="G97" s="1" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0.006648416112632127</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2599,6 +3187,12 @@
       <c r="F98" s="3" t="n">
         <v>-0.003995136355740783</v>
       </c>
+      <c r="G98" s="1" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0.01081269619811647</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2621,6 +3215,12 @@
       <c r="F99" s="3" t="n">
         <v>-0.02072059242381085</v>
       </c>
+      <c r="G99" s="1" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-0.01301534210717671</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2643,6 +3243,12 @@
       <c r="F100" s="2" t="n">
         <v>0.0003292723081988671</v>
       </c>
+      <c r="G100" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0.006583278472679355</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2665,6 +3271,12 @@
       <c r="F101" s="3" t="n">
         <v>-0.002923976608187245</v>
       </c>
+      <c r="G101" s="1" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>-0.001955034213098731</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2687,6 +3299,12 @@
       <c r="F102" s="3" t="n">
         <v>-0.00586907449209924</v>
       </c>
+      <c r="G102" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0.002724795640326864</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2709,6 +3327,12 @@
       <c r="F103" s="2" t="n">
         <v>0.01290655653071762</v>
       </c>
+      <c r="G103" s="1" t="n">
+        <v>0.01963</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0.0005096839959226841</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2731,6 +3355,12 @@
       <c r="F104" s="3" t="n">
         <v>-0.0006718172657036546</v>
       </c>
+      <c r="G104" s="1" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0.004033613445378155</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2753,6 +3383,12 @@
       <c r="F105" s="3" t="n">
         <v>-0.003422526446795253</v>
       </c>
+      <c r="G105" s="1" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.005931938807368021</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2775,6 +3411,12 @@
       <c r="F106" s="3" t="n">
         <v>-0.004247572815534018</v>
       </c>
+      <c r="G106" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0.01096892138939669</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2797,6 +3439,12 @@
       <c r="F107" s="2" t="n">
         <v>0.005662514156285396</v>
       </c>
+      <c r="G107" s="1" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0.003153153153153181</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2819,6 +3467,12 @@
       <c r="F108" s="3" t="n">
         <v>-0.001198681450404589</v>
       </c>
+      <c r="G108" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0.005100510051005205</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2841,6 +3495,12 @@
       <c r="F109" s="2" t="n">
         <v>0.01513840830449828</v>
       </c>
+      <c r="G109" s="1" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0.007669365146996149</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2863,6 +3523,12 @@
       <c r="F110" s="3" t="n">
         <v>-0.003309066843150211</v>
       </c>
+      <c r="G110" s="1" t="n">
+        <v>0.01524</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>0.01195219123505973</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2885,6 +3551,12 @@
       <c r="F111" s="2" t="n">
         <v>0.001093493712411155</v>
       </c>
+      <c r="G111" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0.002730748225013717</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2907,6 +3579,12 @@
       <c r="F112" s="2" t="n">
         <v>0.0002610966057440241</v>
       </c>
+      <c r="G112" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>0.004176455233620476</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2929,6 +3607,12 @@
       <c r="F113" s="3" t="n">
         <v>-0.001396973224679913</v>
       </c>
+      <c r="G113" s="1" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>0.0006994637444626053</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2951,6 +3635,12 @@
       <c r="F114" s="3" t="n">
         <v>-0.006676458806249125</v>
       </c>
+      <c r="G114" s="1" t="n">
+        <v>0.007455</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0.002150826724021981</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2973,6 +3663,12 @@
       <c r="F115" s="2" t="n">
         <v>0.006258335898225089</v>
       </c>
+      <c r="G115" s="1" t="n">
+        <v>0.09894</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0.008768352365415984</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2995,6 +3691,12 @@
       <c r="F116" s="3" t="n">
         <v>-0.001332525741974549</v>
       </c>
+      <c r="G116" s="1" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0.004366812227074226</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3017,6 +3719,12 @@
       <c r="F117" s="3" t="n">
         <v>-0.001675041876046903</v>
       </c>
+      <c r="G117" s="1" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0.005369127516778491</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3039,6 +3747,12 @@
       <c r="F118" s="3" t="n">
         <v>-0.0004393673110720384</v>
       </c>
+      <c r="G118" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0.001318681318681418</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3061,6 +3775,12 @@
       <c r="F119" s="3" t="n">
         <v>-0.008980115458627404</v>
       </c>
+      <c r="G119" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>-0.003236245954692559</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3083,6 +3803,12 @@
       <c r="F120" s="2" t="n">
         <v>0.05046639559913903</v>
       </c>
+      <c r="G120" s="1" t="n">
+        <v>0.004372</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>-0.004553734061930795</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3105,6 +3831,12 @@
       <c r="F121" s="3" t="n">
         <v>-0.008033050263943088</v>
       </c>
+      <c r="G121" s="1" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>-0.002082369273484397</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3127,6 +3859,12 @@
       <c r="F122" s="3" t="n">
         <v>-0.001290322580645162</v>
       </c>
+      <c r="G122" s="1" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0.002583979328165377</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3149,6 +3887,12 @@
       <c r="F123" s="3" t="n">
         <v>-0.002322880371660765</v>
       </c>
+      <c r="G123" s="1" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>0.003492433061699589</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3171,6 +3915,12 @@
       <c r="F124" s="2" t="n">
         <v>0.009038619556285866</v>
       </c>
+      <c r="G124" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0.01954397394136813</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3193,6 +3943,12 @@
       <c r="F125" s="2" t="n">
         <v>0.001750772399587946</v>
       </c>
+      <c r="G125" s="1" t="n">
+        <v>0.09772</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0.004626297933586984</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3215,6 +3971,12 @@
       <c r="F126" s="3" t="n">
         <v>-0.004416403785488998</v>
       </c>
+      <c r="G126" s="1" t="n">
+        <v>0.04724</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>-0.002112378538234112</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3237,6 +3999,12 @@
       <c r="F127" s="2" t="n">
         <v>0.003194888178913599</v>
       </c>
+      <c r="G127" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>0.006369426751592512</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3259,6 +4027,12 @@
       <c r="F128" s="3" t="n">
         <v>-0.00814981792959951</v>
       </c>
+      <c r="G128" s="1" t="n">
+        <v>0.5736</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>0.002797202797202877</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3281,6 +4055,12 @@
       <c r="F129" s="3" t="n">
         <v>-0.007708585247883867</v>
       </c>
+      <c r="G129" s="1" t="n">
+        <v>0.06579</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0.002132520944402151</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3303,6 +4083,12 @@
       <c r="F130" s="3" t="n">
         <v>-0.009484193011647215</v>
       </c>
+      <c r="G130" s="1" t="n">
+        <v>0.0005959</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>0.001007895178901419</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3325,6 +4111,12 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3347,6 +4139,12 @@
       <c r="F132" s="3" t="n">
         <v>-0.006955945677376584</v>
       </c>
+      <c r="G132" s="1" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>0.009339559706470877</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3369,6 +4167,12 @@
       <c r="F133" s="3" t="n">
         <v>-0.009506833036244826</v>
       </c>
+      <c r="G133" s="1" t="n">
+        <v>0.03329</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>-0.001499700059988045</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3391,6 +4195,12 @@
       <c r="F134" s="3" t="n">
         <v>-0.001914791766395421</v>
       </c>
+      <c r="G134" s="1" t="n">
+        <v>0.14614</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0.00130181569030487</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3413,6 +4223,12 @@
       <c r="F135" s="3" t="n">
         <v>-0.001360081604896239</v>
       </c>
+      <c r="G135" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0.006809669731018005</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3435,6 +4251,12 @@
       <c r="F136" s="2" t="n">
         <v>0.001790830945558637</v>
       </c>
+      <c r="G136" s="1" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0.01036825169824822</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3457,6 +4279,12 @@
       <c r="F137" s="3" t="n">
         <v>-0.001173984503404584</v>
       </c>
+      <c r="G137" s="1" t="n">
+        <v>0.000428</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>0.006111894687353101</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3479,6 +4307,12 @@
       <c r="F138" s="3" t="n">
         <v>-0.001797036584952277</v>
       </c>
+      <c r="G138" s="1" t="n">
+        <v>0.029789</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>0.01185461956521734</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3501,6 +4335,12 @@
       <c r="F139" s="2" t="n">
         <v>0.01337546076882563</v>
       </c>
+      <c r="G139" s="1" t="n">
+        <v>0.09596</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>-0.002702140927042157</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3523,6 +4363,12 @@
       <c r="F140" s="2" t="n">
         <v>0.004264998578333811</v>
       </c>
+      <c r="G140" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0.02208380520951295</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3545,6 +4391,12 @@
       <c r="F141" s="3" t="n">
         <v>-0.01248622842453177</v>
       </c>
+      <c r="G141" s="1" t="n">
+        <v>0.02732</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>0.01599107474897731</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3567,6 +4419,12 @@
       <c r="F142" s="2" t="n">
         <v>0.005921831819976208</v>
       </c>
+      <c r="G142" s="1" t="n">
+        <v>0.07675</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>0.004055468341182689</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3589,6 +4447,12 @@
       <c r="F143" s="3" t="n">
         <v>-0.005086469989826971</v>
       </c>
+      <c r="G143" s="1" t="n">
+        <v>0.08857</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0.006248579868211712</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3611,6 +4475,12 @@
       <c r="F144" s="3" t="n">
         <v>-0.003938946331856238</v>
       </c>
+      <c r="G144" s="1" t="n">
+        <v>0.02015</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>-0.003954522985664864</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3633,6 +4503,12 @@
       <c r="F145" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G145" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>0.0007004027315706245</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3655,6 +4531,12 @@
       <c r="F146" s="3" t="n">
         <v>-0.0003321155762204882</v>
       </c>
+      <c r="G146" s="1" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>0.009302325581395432</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3677,6 +4559,12 @@
       <c r="F147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G147" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>-0.008196721311475417</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3699,6 +4587,12 @@
       <c r="F148" s="2" t="n">
         <v>0.005396515392917692</v>
       </c>
+      <c r="G148" s="1" t="n">
+        <v>1.9532</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>-0.001533585522952608</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3721,6 +4615,12 @@
       <c r="F149" s="3" t="n">
         <v>-0.001449042022218641</v>
       </c>
+      <c r="G149" s="1" t="n">
+        <v>0.06205</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>0.0004837149306675629</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3743,6 +4643,12 @@
       <c r="F150" s="2" t="n">
         <v>0.0814332247557004</v>
       </c>
+      <c r="G150" s="1" t="n">
+        <v>0.1642</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>-0.01084337349397588</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3765,6 +4671,12 @@
       <c r="F151" s="3" t="n">
         <v>-0.002256317689530741</v>
       </c>
+      <c r="G151" s="1" t="n">
+        <v>6.681000000000001e-05</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>0.007236544549977521</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3787,6 +4699,12 @@
       <c r="F152" s="3" t="n">
         <v>-0.02073578595317722</v>
       </c>
+      <c r="G152" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>0.005464480874316954</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3809,6 +4727,12 @@
       <c r="F153" s="3" t="n">
         <v>-0.002405002405002307</v>
       </c>
+      <c r="G153" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>0.007232401157184057</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3831,6 +4755,12 @@
       <c r="F154" s="2" t="n">
         <v>0.0005037783375314073</v>
       </c>
+      <c r="G154" s="1" t="n">
+        <v>0.0005974</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>0.002685464921114533</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3853,6 +4783,12 @@
       <c r="F155" s="3" t="n">
         <v>-0.00273904382470117</v>
       </c>
+      <c r="G155" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>0.003745318352059859</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3875,6 +4811,12 @@
       <c r="F156" s="3" t="n">
         <v>-0.002649708532061549</v>
       </c>
+      <c r="G156" s="1" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>0.003719447396386855</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3897,6 +4839,12 @@
       <c r="F157" s="3" t="n">
         <v>-0.006386861313868512</v>
       </c>
+      <c r="G157" s="1" t="n">
+        <v>0.08713</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>0.0001147842056932521</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3919,6 +4867,12 @@
       <c r="F158" s="3" t="n">
         <v>-0.007154984234780503</v>
       </c>
+      <c r="G158" s="1" t="n">
+        <v>0.008258</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>0.008672285330401843</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3941,6 +4895,12 @@
       <c r="F159" s="3" t="n">
         <v>-0.001606425702811246</v>
       </c>
+      <c r="G159" s="1" t="n">
+        <v>2.494</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>0.003218020917135964</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3963,6 +4923,12 @@
       <c r="F160" s="3" t="n">
         <v>-0.0009422850412250411</v>
       </c>
+      <c r="G160" s="1" t="n">
+        <v>1.2793</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>0.005501847048652139</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3985,6 +4951,12 @@
       <c r="F161" s="2" t="n">
         <v>0.0006545359340227512</v>
       </c>
+      <c r="G161" s="1" t="n">
+        <v>0.007618</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>-0.003401360544217685</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4007,6 +4979,12 @@
       <c r="F162" s="3" t="n">
         <v>-0.007659995058067863</v>
       </c>
+      <c r="G162" s="1" t="n">
+        <v>0.004084</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>0.01693227091633475</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4029,6 +5007,12 @@
       <c r="F163" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G163" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>0.001042752867570416</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4051,6 +5035,12 @@
       <c r="F164" s="3" t="n">
         <v>-0.001597444089456854</v>
       </c>
+      <c r="G164" s="1" t="n">
+        <v>1.3808</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>0.004218181818181838</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4073,6 +5063,12 @@
       <c r="F165" s="2" t="n">
         <v>0.001482773658962028</v>
       </c>
+      <c r="G165" s="1" t="n">
+        <v>0.023081</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>0.005094931196655745</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4095,6 +5091,12 @@
       <c r="F166" s="3" t="n">
         <v>-0.01420765027322403</v>
       </c>
+      <c r="G166" s="1" t="n">
+        <v>0.005439</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>0.004988913525498912</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4117,6 +5119,12 @@
       <c r="F167" s="3" t="n">
         <v>-0.005161682101108139</v>
       </c>
+      <c r="G167" s="1" t="n">
+        <v>0.06551999999999999</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>-0.0001526018617428659</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4139,6 +5147,12 @@
       <c r="F168" s="3" t="n">
         <v>-0.001054852320674989</v>
       </c>
+      <c r="G168" s="1" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>0.001055966209081193</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4161,6 +5175,12 @@
       <c r="F169" s="3" t="n">
         <v>-0.001040041601664024</v>
       </c>
+      <c r="G169" s="1" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>-0.0007808433107756961</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4183,6 +5203,12 @@
       <c r="F170" s="3" t="n">
         <v>-0.001549732318963049</v>
       </c>
+      <c r="G170" s="1" t="n">
+        <v>0.007117</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>0.004233102864399554</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4205,6 +5231,12 @@
       <c r="F171" s="3" t="n">
         <v>-0.0002956830277941721</v>
       </c>
+      <c r="G171" s="1" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>0.008577343981070729</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4227,6 +5259,12 @@
       <c r="F172" s="3" t="n">
         <v>-0.002950396459524251</v>
       </c>
+      <c r="G172" s="1" t="n">
+        <v>5.434</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>0.004993526909561704</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4249,6 +5287,12 @@
       <c r="F173" s="3" t="n">
         <v>-0.002426649018310148</v>
       </c>
+      <c r="G173" s="1" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>0.006855373728438694</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4271,6 +5315,12 @@
       <c r="F174" s="3" t="n">
         <v>-0.001275510204081669</v>
       </c>
+      <c r="G174" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.001277139208173728</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4293,6 +5343,12 @@
       <c r="F175" s="3" t="n">
         <v>-0.01282736504543025</v>
       </c>
+      <c r="G175" s="1" t="n">
+        <v>0.005593</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>0.009384587619563249</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4315,6 +5371,12 @@
       <c r="F176" s="3" t="n">
         <v>-0.00263852242744064</v>
       </c>
+      <c r="G176" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>0.005291005291005305</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4337,6 +5399,12 @@
       <c r="F177" s="2" t="n">
         <v>0.009302325581395357</v>
       </c>
+      <c r="G177" s="1" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>0.01036866359447005</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4359,6 +5427,12 @@
       <c r="F178" s="3" t="n">
         <v>-0.003519549497664394</v>
       </c>
+      <c r="G178" s="1" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0.006293347033136447</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4381,6 +5455,12 @@
       <c r="F179" s="3" t="n">
         <v>-0.006430868167202578</v>
       </c>
+      <c r="G179" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>0.003236245954692559</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4403,6 +5483,12 @@
       <c r="F180" s="2" t="n">
         <v>0.001596593932943027</v>
       </c>
+      <c r="G180" s="1" t="n">
+        <v>0.09419</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>0.0009564293304993928</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4425,6 +5511,12 @@
       <c r="F181" s="3" t="n">
         <v>-0.002665245202558638</v>
       </c>
+      <c r="G181" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>0.002672367717797971</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4447,6 +5539,12 @@
       <c r="F182" s="2" t="n">
         <v>0.003196500672947555</v>
       </c>
+      <c r="G182" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>-0.0005031024652021171</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4469,6 +5567,12 @@
       <c r="F183" s="2" t="n">
         <v>0.004983388704318878</v>
       </c>
+      <c r="G183" s="1" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>-0.001652892561983404</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4491,6 +5595,12 @@
       <c r="F184" s="2" t="n">
         <v>0.001872659176029886</v>
       </c>
+      <c r="G184" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>0.005607476635514115</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4513,6 +5623,12 @@
       <c r="F185" s="3" t="n">
         <v>-0.005509641873278242</v>
       </c>
+      <c r="G185" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>0.005540166204986155</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4535,6 +5651,12 @@
       <c r="F186" s="3" t="n">
         <v>-0.003780964797913887</v>
       </c>
+      <c r="G186" s="1" t="n">
+        <v>0.007633</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>-0.001046983379138882</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4557,6 +5679,12 @@
       <c r="F187" s="2" t="n">
         <v>0.001112347052280395</v>
       </c>
+      <c r="G187" s="1" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>0.004444444444444366</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4579,6 +5707,12 @@
       <c r="F188" s="3" t="n">
         <v>-0.001228249744114587</v>
       </c>
+      <c r="G188" s="1" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>0.006353761016601717</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4601,6 +5735,12 @@
       <c r="F189" s="3" t="n">
         <v>-0.00235386426049427</v>
       </c>
+      <c r="G189" s="1" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>0.007078254030672308</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4623,6 +5763,12 @@
       <c r="F190" s="2" t="n">
         <v>0.001067425724959854</v>
       </c>
+      <c r="G190" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>0.002843433445885989</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4645,6 +5791,12 @@
       <c r="F191" s="3" t="n">
         <v>-0.002160545122154028</v>
       </c>
+      <c r="G191" s="1" t="n">
+        <v>6.037</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>0.005496335776149295</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4667,6 +5819,12 @@
       <c r="F192" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G192" s="1" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>-0.0002862868594331205</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4689,6 +5847,12 @@
       <c r="F193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G193" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>0.001560062402495928</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4711,6 +5875,12 @@
       <c r="F194" s="3" t="n">
         <v>-0.006916426512968418</v>
       </c>
+      <c r="G194" s="1" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>0.009866511897852584</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4733,6 +5903,12 @@
       <c r="F195" s="3" t="n">
         <v>-0.008704615737029065</v>
       </c>
+      <c r="G195" s="1" t="n">
+        <v>0.0008685</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>0.003466204506065942</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4755,6 +5931,12 @@
       <c r="F196" s="2" t="n">
         <v>0.001968503937007922</v>
       </c>
+      <c r="G196" s="1" t="n">
+        <v>0.001018</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4777,6 +5959,12 @@
       <c r="F197" s="3" t="n">
         <v>-0.003715170278637693</v>
       </c>
+      <c r="G197" s="1" t="n">
+        <v>0.0001617</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>0.00497203231821002</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4799,6 +5987,12 @@
       <c r="F198" s="3" t="n">
         <v>-0.002996082046554687</v>
       </c>
+      <c r="G198" s="1" t="n">
+        <v>4.339</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>0.003005085529357557</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4821,6 +6015,12 @@
       <c r="F199" s="3" t="n">
         <v>-0.002460024600245902</v>
       </c>
+      <c r="G199" s="1" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>0.008014796547472228</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4843,6 +6043,12 @@
       <c r="F200" s="3" t="n">
         <v>-0.003999158071984756</v>
       </c>
+      <c r="G200" s="1" t="n">
+        <v>0.023636</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>-0.001014370245139464</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4865,6 +6071,12 @@
       <c r="F201" s="2" t="n">
         <v>0.006200538467814284</v>
       </c>
+      <c r="G201" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>0.01597340468661315</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4887,6 +6099,12 @@
       <c r="F202" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G202" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>-0.001447178002894422</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4909,6 +6127,12 @@
       <c r="F203" s="3" t="n">
         <v>-0.01036144578313253</v>
       </c>
+      <c r="G203" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>-0.004139274409544764</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4931,6 +6155,12 @@
       <c r="F204" s="3" t="n">
         <v>-0.001947798987144447</v>
       </c>
+      <c r="G204" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>0.003903200624512076</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4953,6 +6183,12 @@
       <c r="F205" s="3" t="n">
         <v>-0.00186393289841571</v>
       </c>
+      <c r="G205" s="1" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>0.00536881419234366</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4975,6 +6211,12 @@
       <c r="F206" s="3" t="n">
         <v>-0.001745962461807</v>
       </c>
+      <c r="G206" s="1" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>0.003498032356799309</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4997,6 +6239,12 @@
       <c r="F207" s="2" t="n">
         <v>0.0004819277108433204</v>
       </c>
+      <c r="G207" s="1" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>0.003853564547206169</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5019,6 +6267,12 @@
       <c r="F208" s="2" t="n">
         <v>0.0009468416069254784</v>
       </c>
+      <c r="G208" s="1" t="n">
+        <v>0.07393</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>-0.0009459459459459543</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5041,6 +6295,12 @@
       <c r="F209" s="2" t="n">
         <v>0.00214030915576694</v>
       </c>
+      <c r="G209" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>0.001661129568106327</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5063,6 +6323,12 @@
       <c r="F210" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G210" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>0.002724795640326978</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5085,6 +6351,12 @@
       <c r="F211" s="2" t="n">
         <v>0.006315789473684216</v>
       </c>
+      <c r="G211" s="1" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>0.001255230125523107</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5107,6 +6379,12 @@
       <c r="F212" s="2" t="n">
         <v>0.002409638554216769</v>
       </c>
+      <c r="G212" s="1" t="n">
+        <v>0.002083</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>0.001442307692307884</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5129,6 +6407,12 @@
       <c r="F213" s="3" t="n">
         <v>-0.00751879699248121</v>
       </c>
+      <c r="G213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>0.005411255411255416</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5151,6 +6435,12 @@
       <c r="F214" s="3" t="n">
         <v>-0.002806032970887324</v>
       </c>
+      <c r="G214" s="1" t="n">
+        <v>0.005718</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>0.005627857896588095</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5173,6 +6463,12 @@
       <c r="F215" s="3" t="n">
         <v>-0.003467786092352541</v>
       </c>
+      <c r="G215" s="1" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>0.002014652014651996</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5195,6 +6491,12 @@
       <c r="F216" s="3" t="n">
         <v>-0.004731861198738087</v>
       </c>
+      <c r="G216" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>0.003169572107765323</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5217,6 +6519,12 @@
       <c r="F217" s="3" t="n">
         <v>-0.001084598698481593</v>
       </c>
+      <c r="G217" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>0.004343105320303991</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5239,6 +6547,12 @@
       <c r="F218" s="3" t="n">
         <v>-0.008613854249261166</v>
       </c>
+      <c r="G218" s="1" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>0.001745010360999149</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5261,6 +6575,12 @@
       <c r="F219" s="2" t="n">
         <v>0.0009285051067780763</v>
       </c>
+      <c r="G219" s="1" t="n">
+        <v>0.003249</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>0.004638218923933289</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5283,6 +6603,12 @@
       <c r="F220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5305,6 +6631,12 @@
       <c r="F221" s="3" t="n">
         <v>-0.002604845011721877</v>
       </c>
+      <c r="G221" s="1" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>0.009401932619482873</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5327,6 +6659,12 @@
       <c r="F222" s="3" t="n">
         <v>-0.002376323179952452</v>
       </c>
+      <c r="G222" s="1" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>0.006063230835859733</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5349,6 +6687,12 @@
       <c r="F223" s="3" t="n">
         <v>-0.001906577693040914</v>
       </c>
+      <c r="G223" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>0.001910219675262577</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5371,6 +6715,12 @@
       <c r="F224" s="3" t="n">
         <v>-0.01142712036566795</v>
       </c>
+      <c r="G224" s="1" t="n">
+        <v>3.883</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>-0.002568713074749496</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5393,6 +6743,12 @@
       <c r="F225" s="3" t="n">
         <v>-0.001199171481521828</v>
       </c>
+      <c r="G225" s="1" t="n">
+        <v>0.0009229</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>0.007312813796114386</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5415,6 +6771,12 @@
       <c r="F226" s="2" t="n">
         <v>0.006266997753340543</v>
       </c>
+      <c r="G226" s="1" t="n">
+        <v>0.008503999999999999</v>
+      </c>
+      <c r="H226" s="3" t="n">
+        <v>-0.000705052878966016</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5437,6 +6799,12 @@
       <c r="F227" s="3" t="n">
         <v>-0.001932367149758375</v>
       </c>
+      <c r="G227" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>0.001936108422071557</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5459,6 +6827,12 @@
       <c r="F228" s="2" t="n">
         <v>0.0008467400508042705</v>
       </c>
+      <c r="G228" s="1" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>0.003384094754653188</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5481,6 +6855,12 @@
       <c r="F229" s="3" t="n">
         <v>-0.004855311711011851</v>
       </c>
+      <c r="G229" s="1" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>0.006049960967993711</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5503,6 +6883,12 @@
       <c r="F230" s="3" t="n">
         <v>-0.0005797101449274874</v>
       </c>
+      <c r="G230" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>-0.001160092807424622</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5525,6 +6911,12 @@
       <c r="F231" s="2" t="n">
         <v>0.005943840951014523</v>
       </c>
+      <c r="G231" s="1" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>-0.005297473512632362</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5547,6 +6939,12 @@
       <c r="F232" s="2" t="n">
         <v>0.002324500232449928</v>
       </c>
+      <c r="G232" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>0.01159554730983304</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5569,6 +6967,12 @@
       <c r="F233" s="3" t="n">
         <v>-0.001199451679232287</v>
       </c>
+      <c r="G233" s="1" t="n">
+        <v>0.0005839</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>0.001715560130382611</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5591,6 +6995,12 @@
       <c r="F234" s="2" t="n">
         <v>0.01838168217478565</v>
       </c>
+      <c r="G234" s="1" t="n">
+        <v>0.22226</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>-0.004523670891745345</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5613,6 +7023,12 @@
       <c r="F235" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G235" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>0.005813953488372109</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5635,6 +7051,12 @@
       <c r="F236" s="3" t="n">
         <v>-0.002421307506053338</v>
       </c>
+      <c r="G236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5657,6 +7079,12 @@
       <c r="F237" s="3" t="n">
         <v>-0.002392344497607558</v>
       </c>
+      <c r="G237" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>0.002398081534772085</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5679,6 +7107,12 @@
       <c r="F238" s="2" t="n">
         <v>0.004016064257028227</v>
       </c>
+      <c r="G238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>-0.004000000000000115</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5701,6 +7135,12 @@
       <c r="F239" s="3" t="n">
         <v>-0.006028131279303402</v>
       </c>
+      <c r="G239" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>0.003369272237196745</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5723,6 +7163,12 @@
       <c r="F240" s="3" t="n">
         <v>-0.002300025555839565</v>
       </c>
+      <c r="G240" s="1" t="n">
+        <v>0.0003919</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>0.003842213114754053</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5745,6 +7191,12 @@
       <c r="F241" s="3" t="n">
         <v>-0.009009009009009058</v>
       </c>
+      <c r="G241" s="1" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>0.006060606060606023</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5767,6 +7219,12 @@
       <c r="F242" s="2" t="n">
         <v>0.00278995615783183</v>
       </c>
+      <c r="G242" s="1" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>0.01311605723370417</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5789,6 +7247,12 @@
       <c r="F243" s="3" t="n">
         <v>-0.001532175689478998</v>
       </c>
+      <c r="G243" s="1" t="n">
+        <v>0.01968</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>0.006649616368286351</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5811,6 +7275,12 @@
       <c r="F244" s="2" t="n">
         <v>0.002385550380552106</v>
       </c>
+      <c r="G244" s="1" t="n">
+        <v>0.08766</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>-0.006572982774252008</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5833,6 +7303,12 @@
       <c r="F245" s="3" t="n">
         <v>-0.01892701525054469</v>
       </c>
+      <c r="G245" s="1" t="n">
+        <v>1.4284</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>-0.008743927827897409</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5855,6 +7331,12 @@
       <c r="F246" s="3" t="n">
         <v>-0.001116071428571383</v>
       </c>
+      <c r="G246" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>0.00167597765363141</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5877,6 +7359,12 @@
       <c r="F247" s="3" t="n">
         <v>-0.0003039051815833863</v>
       </c>
+      <c r="G247" s="1" t="n">
+        <v>0.006606</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>0.004103967168262671</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5899,6 +7387,12 @@
       <c r="F248" s="3" t="n">
         <v>-0.008276533592989122</v>
       </c>
+      <c r="G248" s="1" t="n">
+        <v>0.004192</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>0.02896416298478155</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5921,6 +7415,12 @@
       <c r="F249" s="3" t="n">
         <v>-0.001821493624772239</v>
       </c>
+      <c r="G249" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5943,6 +7443,12 @@
       <c r="F250" s="3" t="n">
         <v>-0.004666083406240898</v>
       </c>
+      <c r="G250" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>0.002636976267213589</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5965,6 +7471,12 @@
       <c r="F251" s="3" t="n">
         <v>-0.003228782287822906</v>
       </c>
+      <c r="G251" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>0.002082369273484493</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5987,6 +7499,12 @@
       <c r="F252" s="2" t="n">
         <v>0.05626510182947875</v>
       </c>
+      <c r="G252" s="1" t="n">
+        <v>0.005835</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>-0.04656862745098034</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6009,6 +7527,12 @@
       <c r="F253" s="2" t="n">
         <v>0.0005991611743558774</v>
       </c>
+      <c r="G253" s="1" t="n">
+        <v>0.01676</v>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>0.003592814371257547</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6031,6 +7555,12 @@
       <c r="F254" s="3" t="n">
         <v>-0.0007668711656440873</v>
       </c>
+      <c r="G254" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>0.00920951650038378</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6053,6 +7583,12 @@
       <c r="F255" s="3" t="n">
         <v>-0.0004823926676314324</v>
       </c>
+      <c r="G255" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>0.0009652509652510934</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6075,6 +7611,12 @@
       <c r="F256" s="3" t="n">
         <v>-0.001430615164520686</v>
       </c>
+      <c r="G256" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>0.002865329512894032</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6097,6 +7639,12 @@
       <c r="F257" s="3" t="n">
         <v>-0.004709576138147511</v>
       </c>
+      <c r="G257" s="1" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>0.002365930599369126</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6119,6 +7667,12 @@
       <c r="F258" s="2" t="n">
         <v>0.0004055150040551804</v>
       </c>
+      <c r="G258" s="1" t="n">
+        <v>0.14791</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>-0.0007431428185380285</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6141,6 +7695,12 @@
       <c r="F259" s="2" t="n">
         <v>0.001770607908715322</v>
       </c>
+      <c r="G259" s="1" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H259" s="3" t="n">
+        <v>-0.0001963864886096438</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6163,6 +7723,12 @@
       <c r="F260" s="2" t="n">
         <v>0.0004837929366231056</v>
       </c>
+      <c r="G260" s="1" t="n">
+        <v>0.08294</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>0.002659574468085082</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6185,6 +7751,12 @@
       <c r="F261" s="2" t="n">
         <v>0.01109215017064843</v>
       </c>
+      <c r="G261" s="1" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>0.01729957805907182</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6207,6 +7779,12 @@
       <c r="F262" s="3" t="n">
         <v>-0.00140350877192967</v>
       </c>
+      <c r="G262" s="1" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6229,6 +7807,12 @@
       <c r="F263" s="3" t="n">
         <v>-0.0003868471953576837</v>
       </c>
+      <c r="G263" s="1" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="H263" s="3" t="n">
+        <v>-0.0002579979360165908</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6251,6 +7835,12 @@
       <c r="F264" s="2" t="n">
         <v>0.005720228809152314</v>
       </c>
+      <c r="G264" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>0.01758014477766288</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6273,6 +7863,12 @@
       <c r="F265" s="3" t="n">
         <v>-0.001950585175552586</v>
       </c>
+      <c r="G265" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>0.0006514657980455761</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6295,6 +7891,12 @@
       <c r="F266" s="3" t="n">
         <v>-0.002009040683073809</v>
       </c>
+      <c r="G266" s="1" t="n">
+        <v>0.006011</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>0.008387854386847794</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6317,6 +7919,12 @@
       <c r="F267" s="2" t="n">
         <v>0.003509719222462341</v>
       </c>
+      <c r="G267" s="1" t="n">
+        <v>0.03739</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>0.005918751681463491</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6339,6 +7947,12 @@
       <c r="F268" s="3" t="n">
         <v>-0.001312766655727005</v>
       </c>
+      <c r="G268" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>0.00197173841603684</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6361,6 +7975,12 @@
       <c r="F269" s="3" t="n">
         <v>-0.004967469667663057</v>
       </c>
+      <c r="G269" s="1" t="n">
+        <v>0.22733</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>0.004329578087033394</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6383,6 +8003,12 @@
       <c r="F270" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G270" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>0.0130576713819369</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6405,6 +8031,12 @@
       <c r="F271" s="2" t="n">
         <v>0.001936483346243353</v>
       </c>
+      <c r="G271" s="1" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>0.004252029377657393</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6427,6 +8059,12 @@
       <c r="F272" s="2" t="n">
         <v>0.003262642740619845</v>
       </c>
+      <c r="G272" s="1" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>-0.001084010840108432</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6449,6 +8087,12 @@
       <c r="F273" s="3" t="n">
         <v>-0.001625487646293822</v>
       </c>
+      <c r="G273" s="1" t="n">
+        <v>0.03084</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>0.004233148811462005</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6471,6 +8115,12 @@
       <c r="F274" s="2" t="n">
         <v>0.002631578947368423</v>
       </c>
+      <c r="G274" s="1" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>-0.00472440944881896</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6493,6 +8143,12 @@
       <c r="F275" s="3" t="n">
         <v>-0.004479121514231916</v>
       </c>
+      <c r="G275" s="1" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="H275" s="3" t="n">
+        <v>-0.0005805515239477267</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6515,6 +8171,12 @@
       <c r="F276" s="2" t="n">
         <v>0.0008684863523573277</v>
       </c>
+      <c r="G276" s="1" t="n">
+        <v>0.08094999999999999</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>0.003470930953266253</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6537,6 +8199,12 @@
       <c r="F277" s="3" t="n">
         <v>-0.008494572911750726</v>
       </c>
+      <c r="G277" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>0.001903855306996715</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6559,6 +8227,12 @@
       <c r="F278" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G278" s="1" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>0.001290322580645162</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6581,6 +8255,12 @@
       <c r="F279" s="3" t="n">
         <v>-0.0009082652134424457</v>
       </c>
+      <c r="G279" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>0.005454545454545548</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6603,6 +8283,12 @@
       <c r="F280" s="2" t="n">
         <v>0.0007664793050588208</v>
       </c>
+      <c r="G280" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>0.005616543272912892</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6625,6 +8311,12 @@
       <c r="F281" s="2" t="n">
         <v>0.001183011948420713</v>
       </c>
+      <c r="G281" s="1" t="n">
+        <v>0.08538</v>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>0.008862105636299192</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6647,6 +8339,12 @@
       <c r="F282" s="3" t="n">
         <v>-0.003759398496240579</v>
       </c>
+      <c r="G282" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>0.003773584905660355</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6669,6 +8367,12 @@
       <c r="F283" s="2" t="n">
         <v>0.001451187335092335</v>
       </c>
+      <c r="G283" s="1" t="n">
+        <v>0.07613</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>0.002898168884204953</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6691,6 +8395,12 @@
       <c r="F284" s="3" t="n">
         <v>-0.003082614056720107</v>
       </c>
+      <c r="G284" s="1" t="n">
+        <v>0.001621</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>0.002473716759431105</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6713,6 +8423,12 @@
       <c r="F285" s="3" t="n">
         <v>-0.0004965243296921003</v>
       </c>
+      <c r="G285" s="1" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>0.003477396920019901</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6735,6 +8451,12 @@
       <c r="F286" s="2" t="n">
         <v>0.00423409860745207</v>
       </c>
+      <c r="G286" s="1" t="n">
+        <v>0.10783</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>0.01030638058652665</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6757,6 +8479,12 @@
       <c r="F287" s="3" t="n">
         <v>-0.001748251748251879</v>
       </c>
+      <c r="G287" s="1" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>0.004086398131932319</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6779,6 +8507,12 @@
       <c r="F288" s="3" t="n">
         <v>-0.002607561929595835</v>
       </c>
+      <c r="G288" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>0.001960784313725524</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6801,6 +8535,12 @@
       <c r="F289" s="3" t="n">
         <v>-0.003722084367245506</v>
       </c>
+      <c r="G289" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="H289" s="3" t="n">
+        <v>-0.00186799501868009</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6823,6 +8563,12 @@
       <c r="F290" s="3" t="n">
         <v>-0.005288673424416046</v>
       </c>
+      <c r="G290" s="1" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>0.004430660168364992</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6845,6 +8591,12 @@
       <c r="F291" s="3" t="n">
         <v>-0.0004540295119182247</v>
       </c>
+      <c r="G291" s="1" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>0.005677946854417447</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6867,6 +8619,12 @@
       <c r="F292" s="3" t="n">
         <v>-0.002871912693854173</v>
       </c>
+      <c r="G292" s="1" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>0.001728110599078407</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6889,6 +8647,12 @@
       <c r="F293" s="3" t="n">
         <v>-0.008823529411764687</v>
       </c>
+      <c r="G293" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="H293" s="3" t="n">
+        <v>-0.007121661721068234</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6911,6 +8675,12 @@
       <c r="F294" s="3" t="n">
         <v>-0.001103404791929392</v>
       </c>
+      <c r="G294" s="1" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>0.002524854031876399</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6933,6 +8703,12 @@
       <c r="F295" s="3" t="n">
         <v>-0.0002438429651304619</v>
       </c>
+      <c r="G295" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>0.004878048780487791</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6955,6 +8731,12 @@
       <c r="F296" s="2" t="n">
         <v>0.002881844380403454</v>
       </c>
+      <c r="G296" s="1" t="n">
+        <v>62.57</v>
+      </c>
+      <c r="H296" s="3" t="n">
+        <v>-0.001117496807151984</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6977,6 +8759,12 @@
       <c r="F297" s="3" t="n">
         <v>-0.001021450459652736</v>
       </c>
+      <c r="G297" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>0.003067484662576775</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6999,6 +8787,12 @@
       <c r="F298" s="3" t="n">
         <v>-0.003131524008350676</v>
       </c>
+      <c r="G298" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>0.00209424083769625</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7021,6 +8815,12 @@
       <c r="F299" s="3" t="n">
         <v>-0.002886597938144355</v>
       </c>
+      <c r="G299" s="1" t="n">
+        <v>0.09607</v>
+      </c>
+      <c r="H299" s="3" t="n">
+        <v>-0.006720430107526859</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7043,6 +8843,12 @@
       <c r="F300" s="3" t="n">
         <v>-0.001621621621621556</v>
       </c>
+      <c r="G300" s="1" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="H300" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7065,6 +8871,12 @@
       <c r="F301" s="3" t="n">
         <v>-0.00150150150150157</v>
       </c>
+      <c r="G301" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>0.0022556390977444</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7087,6 +8899,12 @@
       <c r="F302" s="3" t="n">
         <v>-0.0009184845005741747</v>
       </c>
+      <c r="G302" s="1" t="n">
+        <v>0.004359</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>0.001838657779820776</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7109,6 +8927,12 @@
       <c r="F303" s="2" t="n">
         <v>0.006458557588805277</v>
       </c>
+      <c r="G303" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="H303" s="3" t="n">
+        <v>-0.001069518716577682</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7131,6 +8955,12 @@
       <c r="F304" s="3" t="n">
         <v>-0.001271725307333664</v>
       </c>
+      <c r="G304" s="1" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>0.002971137521222461</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7153,6 +8983,12 @@
       <c r="F305" s="3" t="n">
         <v>-0.001505740636175358</v>
       </c>
+      <c r="G305" s="1" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>0.002827521206408998</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7175,6 +9011,12 @@
       <c r="F306" s="2" t="n">
         <v>0.001199657240788357</v>
       </c>
+      <c r="G306" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="H306" s="3" t="n">
+        <v>-0.0003423485107839641</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7197,6 +9039,12 @@
       <c r="F307" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G307" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>0.001138952164009144</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7219,6 +9067,12 @@
       <c r="F308" s="2" t="n">
         <v>0.001013993104846916</v>
       </c>
+      <c r="G308" s="1" t="n">
+        <v>0.04937</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>0.0002025931928686411</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7241,6 +9095,12 @@
       <c r="F309" s="3" t="n">
         <v>-0.002767527675276858</v>
       </c>
+      <c r="G309" s="1" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>0.002775208140610651</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7263,6 +9123,12 @@
       <c r="F310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="H310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7285,6 +9151,12 @@
       <c r="F311" s="3" t="n">
         <v>-0.0002780481023215939</v>
       </c>
+      <c r="G311" s="1" t="n">
+        <v>0.07166</v>
+      </c>
+      <c r="H311" s="3" t="n">
+        <v>-0.003476567932137397</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7307,6 +9179,12 @@
       <c r="F312" s="3" t="n">
         <v>-0.008932509925010971</v>
       </c>
+      <c r="G312" s="1" t="n">
+        <v>0.008992</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>0.0005563591854901297</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7329,6 +9207,12 @@
       <c r="F313" s="2" t="n">
         <v>0.00210225361587628</v>
       </c>
+      <c r="G313" s="1" t="n">
+        <v>0.012062</v>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>0.01216749181841061</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7351,6 +9235,12 @@
       <c r="F314" s="3" t="n">
         <v>-0.004299226139294901</v>
       </c>
+      <c r="G314" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>0.00863557858376506</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7373,6 +9263,12 @@
       <c r="F315" s="2" t="n">
         <v>0.001412429378531016</v>
       </c>
+      <c r="G315" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>0.002820874471086044</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7395,6 +9291,12 @@
       <c r="F316" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G316" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>0.001533742331288388</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7417,6 +9319,12 @@
       <c r="F317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="H317" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7439,6 +9347,12 @@
       <c r="F318" s="2" t="n">
         <v>0.0007034354265290654</v>
       </c>
+      <c r="G318" s="1" t="n">
+        <v>0.05278</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>0.002735770195303562</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7461,6 +9375,12 @@
       <c r="F319" s="2" t="n">
         <v>0.004489041457618076</v>
       </c>
+      <c r="G319" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H319" s="3" t="n">
+        <v>-0.001051524710830662</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7483,6 +9403,12 @@
       <c r="F320" s="3" t="n">
         <v>-0.001473187978786033</v>
       </c>
+      <c r="G320" s="1" t="n">
+        <v>0.006812</v>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>0.00501622897609917</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7505,6 +9431,12 @@
       <c r="F321" s="3" t="n">
         <v>-0.001766004415011039</v>
       </c>
+      <c r="G321" s="1" t="n">
+        <v>4.527</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>0.001105705440070742</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7527,6 +9459,12 @@
       <c r="F322" s="3" t="n">
         <v>-0.002092050209205023</v>
       </c>
+      <c r="G322" s="1" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>0.003144654088050317</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7549,6 +9487,12 @@
       <c r="F323" s="3" t="n">
         <v>-0.001973776963203175</v>
       </c>
+      <c r="G323" s="1" t="n">
+        <v>0.007069</v>
+      </c>
+      <c r="H323" s="3" t="n">
+        <v>-0.001412628902387408</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7571,6 +9515,12 @@
       <c r="F324" s="3" t="n">
         <v>-0.001100110011001246</v>
       </c>
+      <c r="G324" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>0.005506607929515386</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7593,6 +9543,12 @@
       <c r="F325" s="3" t="n">
         <v>-0.001708984375000083</v>
       </c>
+      <c r="G325" s="1" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>0.003179261433113288</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7615,6 +9571,12 @@
       <c r="F326" s="3" t="n">
         <v>-0.001661589587371899</v>
       </c>
+      <c r="G326" s="1" t="n">
+        <v>0.007237</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>0.003744798890429974</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7637,6 +9599,12 @@
       <c r="F327" s="2" t="n">
         <v>0.001565762004175338</v>
       </c>
+      <c r="G327" s="1" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="H327" s="3" t="n">
+        <v>-0.004689942678478292</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7659,6 +9627,12 @@
       <c r="F328" s="3" t="n">
         <v>-0.01436720895837729</v>
       </c>
+      <c r="G328" s="1" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>0.002572347266880983</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7681,6 +9655,12 @@
       <c r="F329" s="3" t="n">
         <v>-0.001482579688658334</v>
       </c>
+      <c r="G329" s="1" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>0.0141054194506311</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7703,6 +9683,12 @@
       <c r="F330" s="3" t="n">
         <v>-0.002645502645502599</v>
       </c>
+      <c r="G330" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>0.001768346595932731</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7725,6 +9711,12 @@
       <c r="F331" s="3" t="n">
         <v>-0.00100654252642163</v>
       </c>
+      <c r="G331" s="1" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>0.007724601175482682</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7747,6 +9739,12 @@
       <c r="F332" s="2" t="n">
         <v>0.0002005213555243784</v>
       </c>
+      <c r="G332" s="1" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="H332" s="3" t="n">
+        <v>-0.001537022186581181</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7769,6 +9767,12 @@
       <c r="F333" s="3" t="n">
         <v>-0.002130681818181781</v>
       </c>
+      <c r="G333" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>0.001138790035587142</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7791,6 +9795,12 @@
       <c r="F334" s="2" t="n">
         <v>0.00443737995893752</v>
       </c>
+      <c r="G334" s="1" t="n">
+        <v>0.15585</v>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>0.02762758802584729</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7813,6 +9823,12 @@
       <c r="F335" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G335" s="1" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="H335" s="3" t="n">
+        <v>-0.001915708812260503</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7835,6 +9851,12 @@
       <c r="F336" s="2" t="n">
         <v>0.001151410477835381</v>
       </c>
+      <c r="G336" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>0.004025301897642359</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7857,6 +9879,12 @@
       <c r="F337" s="3" t="n">
         <v>-0.0007479431563201757</v>
       </c>
+      <c r="G337" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>0.009980039920159793</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7879,6 +9907,12 @@
       <c r="F338" s="3" t="n">
         <v>-0.0003786444528588159</v>
       </c>
+      <c r="G338" s="1" t="n">
+        <v>0.005291</v>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>0.002083333333333281</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7901,6 +9935,12 @@
       <c r="F339" s="3" t="n">
         <v>-0.001952362358453785</v>
       </c>
+      <c r="G339" s="1" t="n">
+        <v>0.05137</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>0.004890453834115811</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7923,6 +9963,12 @@
       <c r="F340" s="2" t="n">
         <v>0.002983491347875131</v>
       </c>
+      <c r="G340" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>0.003437334743521898</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7945,6 +9991,12 @@
       <c r="F341" s="3" t="n">
         <v>-0.00144965735371641</v>
       </c>
+      <c r="G341" s="1" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>0.003035502177642825</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7967,6 +10019,12 @@
       <c r="F342" s="3" t="n">
         <v>-0.00326603325415674</v>
       </c>
+      <c r="G342" s="1" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="H342" s="3" t="n">
+        <v>-0.003872505212987856</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7989,6 +10047,12 @@
       <c r="F343" s="3" t="n">
         <v>-0.006069802731411157</v>
       </c>
+      <c r="G343" s="1" t="n">
+        <v>0.01964</v>
+      </c>
+      <c r="H343" s="3" t="n">
+        <v>-0.0005089058524172821</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8011,6 +10075,12 @@
       <c r="F344" s="2" t="n">
         <v>0.0009107468123860563</v>
       </c>
+      <c r="G344" s="1" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="H344" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8033,6 +10103,12 @@
       <c r="F345" s="2" t="n">
         <v>0.003162055335968382</v>
       </c>
+      <c r="G345" s="1" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>0.00315208825847124</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8055,6 +10131,12 @@
       <c r="F346" s="2" t="n">
         <v>0.0001923816852634216</v>
       </c>
+      <c r="G346" s="1" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="H346" s="3" t="n">
+        <v>-0.00365454895172147</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8077,6 +10159,12 @@
       <c r="F347" s="2" t="n">
         <v>0.001231960577261539</v>
       </c>
+      <c r="G347" s="1" t="n">
+        <v>0.05725</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>0.006328001406222521</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8099,6 +10187,12 @@
       <c r="F348" s="3" t="n">
         <v>-0.004662004662004796</v>
       </c>
+      <c r="G348" s="1" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="H348" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8121,6 +10215,12 @@
       <c r="F349" s="3" t="n">
         <v>-0.0002680400528422863</v>
       </c>
+      <c r="G349" s="1" t="n">
+        <v>5216.3</v>
+      </c>
+      <c r="H349" s="3" t="n">
+        <v>-0.001034145967788199</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8143,6 +10243,12 @@
       <c r="F350" s="3" t="n">
         <v>-0.0098870056497176</v>
       </c>
+      <c r="G350" s="1" t="n">
+        <v>0.02821</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>0.006062767475035664</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8165,6 +10271,12 @@
       <c r="F351" s="2" t="n">
         <v>0.004470938897168352</v>
       </c>
+      <c r="G351" s="1" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>0.006676557863501405</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8187,6 +10299,12 @@
       <c r="F352" s="2" t="n">
         <v>0.001273074474856948</v>
       </c>
+      <c r="G352" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>0.0006357279084551553</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8209,6 +10327,12 @@
       <c r="F353" s="3" t="n">
         <v>-0.00287631831255989</v>
       </c>
+      <c r="G353" s="1" t="n">
+        <v>6.247</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>0.001121794871794819</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8231,6 +10355,12 @@
       <c r="F354" s="3" t="n">
         <v>-0.002791346824843066</v>
       </c>
+      <c r="G354" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>0.002799160251924503</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8253,6 +10383,12 @@
       <c r="F355" s="3" t="n">
         <v>-0.003853564547206176</v>
       </c>
+      <c r="G355" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="H355" s="3" t="n">
+        <v>-0.0007253384912959925</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8275,6 +10411,12 @@
       <c r="F356" s="3" t="n">
         <v>-0.002900588907444818</v>
       </c>
+      <c r="G356" s="1" t="n">
+        <v>0.11424</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>0.007052186177715049</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8297,6 +10439,12 @@
       <c r="F357" s="2" t="n">
         <v>0.0007676069852235009</v>
       </c>
+      <c r="G357" s="1" t="n">
+        <v>0.005256</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>0.00786193672099717</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8319,6 +10467,12 @@
       <c r="F358" s="2" t="n">
         <v>0.001082251082251113</v>
       </c>
+      <c r="G358" s="1" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>0.009729729729729708</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8341,6 +10495,12 @@
       <c r="F359" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G359" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>0.001849568434032026</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8363,6 +10523,12 @@
       <c r="F360" s="3" t="n">
         <v>-0.0001175226231049021</v>
       </c>
+      <c r="G360" s="1" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>0.001645510108133536</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8385,6 +10551,12 @@
       <c r="F361" s="2" t="n">
         <v>0.003778337531486211</v>
       </c>
+      <c r="G361" s="1" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>0.0138017565872021</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8407,6 +10579,12 @@
       <c r="F362" s="3" t="n">
         <v>-0.0002354048964218197</v>
       </c>
+      <c r="G362" s="1" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="H362" s="3" t="n">
+        <v>-0.003060984224158284</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8429,6 +10607,12 @@
       <c r="F363" s="2" t="n">
         <v>0.007925662749385177</v>
       </c>
+      <c r="G363" s="1" t="n">
+        <v>3.739</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>0.01382863340563983</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8451,6 +10635,12 @@
       <c r="F364" s="3" t="n">
         <v>-0.001828153564899536</v>
       </c>
+      <c r="G364" s="1" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>0.002747252747252794</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8473,6 +10663,12 @@
       <c r="F365" s="3" t="n">
         <v>-0.001090512540894176</v>
       </c>
+      <c r="G365" s="1" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="H365" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8495,6 +10691,12 @@
       <c r="F366" s="2" t="n">
         <v>0.02106227106227116</v>
       </c>
+      <c r="G366" s="1" t="n">
+        <v>0.02223</v>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>-0.003139013452914826</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8517,6 +10719,12 @@
       <c r="F367" s="2" t="n">
         <v>0.005219985085756944</v>
       </c>
+      <c r="G367" s="1" t="n">
+        <v>0.001355</v>
+      </c>
+      <c r="H367" s="2" t="n">
+        <v>0.005192878338278977</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8539,6 +10747,12 @@
       <c r="F368" s="2" t="n">
         <v>0.000696621386276482</v>
       </c>
+      <c r="G368" s="1" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>-0.001740341106856945</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8561,6 +10775,12 @@
       <c r="F369" s="3" t="n">
         <v>-0.008064516129032117</v>
       </c>
+      <c r="G369" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="H369" s="3" t="n">
+        <v>-0.00271002710027108</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8583,6 +10803,12 @@
       <c r="F370" s="3" t="n">
         <v>-0.0007919615898628594</v>
       </c>
+      <c r="G370" s="1" t="n">
+        <v>0.19781</v>
+      </c>
+      <c r="H370" s="3" t="n">
+        <v>-0.02011195323723178</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8605,6 +10831,12 @@
       <c r="F371" s="3" t="n">
         <v>-0.01315789473684212</v>
       </c>
+      <c r="G371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8627,6 +10859,12 @@
       <c r="F372" s="3" t="n">
         <v>-0.00095419847328247</v>
       </c>
+      <c r="G372" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>0.003820439350525287</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8649,6 +10887,12 @@
       <c r="F373" s="3" t="n">
         <v>-0.004827274098657427</v>
       </c>
+      <c r="G373" s="1" t="n">
+        <v>0.06591</v>
+      </c>
+      <c r="H373" s="3" t="n">
+        <v>-0.0009095043201455889</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8671,6 +10915,12 @@
       <c r="F374" s="2" t="n">
         <v>0.0007952286282307219</v>
       </c>
+      <c r="G374" s="1" t="n">
+        <v>0.007578</v>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>0.003575685339690007</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8693,6 +10943,12 @@
       <c r="F375" s="3" t="n">
         <v>-0.001261034047919155</v>
       </c>
+      <c r="G375" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>0.002525252525252422</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8715,6 +10971,12 @@
       <c r="F376" s="3" t="n">
         <v>-0.003242924528301934</v>
       </c>
+      <c r="G376" s="1" t="n">
+        <v>0.003397</v>
+      </c>
+      <c r="H376" s="2" t="n">
+        <v>0.00473232771369416</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8737,6 +10999,12 @@
       <c r="F377" s="2" t="n">
         <v>0.00628930817610059</v>
       </c>
+      <c r="G377" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="H377" s="3" t="n">
+        <v>-0.006249999999999962</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8759,6 +11027,12 @@
       <c r="F378" s="2" t="n">
         <v>0.007104795737122577</v>
       </c>
+      <c r="G378" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="H378" s="3" t="n">
+        <v>-0.01763668430335086</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8781,6 +11055,12 @@
       <c r="F379" s="2" t="n">
         <v>0.01110083256244221</v>
       </c>
+      <c r="G379" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>0.001829826166514106</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8803,6 +11083,12 @@
       <c r="F380" s="3" t="n">
         <v>-0.003198294243070232</v>
       </c>
+      <c r="G380" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>0.001604278074866245</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8825,6 +11111,12 @@
       <c r="F381" s="2" t="n">
         <v>0.00167644593461854</v>
       </c>
+      <c r="G381" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>0.00334728033472813</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8847,6 +11139,12 @@
       <c r="F382" s="3" t="n">
         <v>-0.004817618719889806</v>
       </c>
+      <c r="G382" s="1" t="n">
+        <v>0.02905</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>0.004495159059474348</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8869,6 +11167,12 @@
       <c r="F383" s="3" t="n">
         <v>-0.001837672281776395</v>
       </c>
+      <c r="G383" s="1" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>0.003375268487265948</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8891,6 +11195,12 @@
       <c r="F384" s="3" t="n">
         <v>-0.01042160113690201</v>
       </c>
+      <c r="G384" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>0.0004786979415988317</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8913,6 +11223,12 @@
       <c r="F385" s="2" t="n">
         <v>0.001587931718936086</v>
       </c>
+      <c r="G385" s="1" t="n">
+        <v>2520</v>
+      </c>
+      <c r="H385" s="3" t="n">
+        <v>-0.001189060642092747</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8935,6 +11251,12 @@
       <c r="F386" s="3" t="n">
         <v>-0.001512096774193522</v>
       </c>
+      <c r="G386" s="1" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>0.002523977788995459</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8957,6 +11279,12 @@
       <c r="F387" s="2" t="n">
         <v>0.002466236054022335</v>
       </c>
+      <c r="G387" s="1" t="n">
+        <v>0.0852</v>
+      </c>
+      <c r="H387" s="3" t="n">
+        <v>-0.001874414245548352</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8979,6 +11307,12 @@
       <c r="F388" s="3" t="n">
         <v>-0.003379721669980051</v>
       </c>
+      <c r="G388" s="1" t="n">
+        <v>0.005023</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>0.001994813484939077</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9001,6 +11335,12 @@
       <c r="F389" s="2" t="n">
         <v>0.00227066303360572</v>
       </c>
+      <c r="G389" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>0.0004531037607611958</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9023,6 +11363,12 @@
       <c r="F390" s="3" t="n">
         <v>-0.004225352112676038</v>
       </c>
+      <c r="G390" s="1" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>0.01980198019801986</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9045,6 +11391,12 @@
       <c r="F391" s="3" t="n">
         <v>-0.0005053908355796184</v>
       </c>
+      <c r="G391" s="1" t="n">
+        <v>0.0005984</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>0.008595988538682067</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9067,6 +11419,12 @@
       <c r="F392" s="3" t="n">
         <v>-0.0008560178051702533</v>
       </c>
+      <c r="G392" s="1" t="n">
+        <v>0.05844</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>0.001370801919122631</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9089,6 +11447,12 @@
       <c r="F393" s="2" t="n">
         <v>0.001500375093773486</v>
       </c>
+      <c r="G393" s="1" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>0.0007490636704119024</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9111,6 +11475,12 @@
       <c r="F394" s="3" t="n">
         <v>-0.0003061849357010713</v>
       </c>
+      <c r="G394" s="1" t="n">
+        <v>0.006553</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>0.003522205206738068</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9133,6 +11503,12 @@
       <c r="F395" s="3" t="n">
         <v>-0.0008726003490400436</v>
       </c>
+      <c r="G395" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>0.006113537117903863</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9155,6 +11531,12 @@
       <c r="F396" s="2" t="n">
         <v>0.0003237293622531431</v>
       </c>
+      <c r="G396" s="1" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="H396" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9177,6 +11559,12 @@
       <c r="F397" s="2" t="n">
         <v>0.001986754966887382</v>
       </c>
+      <c r="G397" s="1" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>0.001982815598149521</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9199,6 +11587,12 @@
       <c r="F398" s="2" t="n">
         <v>0.001222867624579669</v>
       </c>
+      <c r="G398" s="1" t="n">
+        <v>0.003303</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>0.00854961832061063</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9221,6 +11615,12 @@
       <c r="F399" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="H399" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9243,6 +11643,12 @@
       <c r="F400" s="2" t="n">
         <v>0.00254488901456239</v>
       </c>
+      <c r="G400" s="1" t="n">
+        <v>0.007135</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>0.006205048653222362</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9265,6 +11671,12 @@
       <c r="F401" s="2" t="n">
         <v>0.004344677769732153</v>
       </c>
+      <c r="G401" s="1" t="n">
+        <v>0.006973</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>0.005479452054794497</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9287,6 +11699,12 @@
       <c r="F402" s="2" t="n">
         <v>0.001622971285892741</v>
       </c>
+      <c r="G402" s="1" t="n">
+        <v>0.008033</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>0.001246416552411765</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9309,6 +11727,12 @@
       <c r="F403" s="2" t="n">
         <v>0.004539826661163805</v>
       </c>
+      <c r="G403" s="1" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>0.01109285127362364</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9331,6 +11755,12 @@
       <c r="F404" s="2" t="n">
         <v>0.006583962852588581</v>
       </c>
+      <c r="G404" s="1" t="n">
+        <v>0.14652</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>0.008812999173781351</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9353,6 +11783,12 @@
       <c r="F405" s="3" t="n">
         <v>-0.005370067709549405</v>
       </c>
+      <c r="G405" s="1" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>0.002582159624413122</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9375,6 +11811,12 @@
       <c r="F406" s="3" t="n">
         <v>-0.0008369951872776971</v>
       </c>
+      <c r="G406" s="1" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>0.002722513089005285</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9397,6 +11839,12 @@
       <c r="F407" s="3" t="n">
         <v>-0.001840490797545946</v>
       </c>
+      <c r="G407" s="1" t="n">
+        <v>0.0004871</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>-0.002048760499897501</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9419,6 +11867,12 @@
       <c r="F408" s="2" t="n">
         <v>0.0008230452674898212</v>
       </c>
+      <c r="G408" s="1" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>0.003289473684210535</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9441,6 +11895,12 @@
       <c r="F409" s="3" t="n">
         <v>-0.002835538752362986</v>
       </c>
+      <c r="G409" s="1" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>0.006635071090047364</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9463,6 +11923,12 @@
       <c r="F410" s="3" t="n">
         <v>-0.0007213272421255649</v>
       </c>
+      <c r="G410" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="H410" s="3" t="n">
+        <v>-0.0007218479307026527</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9485,6 +11951,12 @@
       <c r="F411" s="2" t="n">
         <v>0.0003368137420006599</v>
       </c>
+      <c r="G411" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>0.003030303030303023</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9507,6 +11979,12 @@
       <c r="F412" s="3" t="n">
         <v>-0.0004387889425187067</v>
       </c>
+      <c r="G412" s="1" t="n">
+        <v>0.004571</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>0.003292361720807782</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9529,6 +12007,12 @@
       <c r="F413" s="2" t="n">
         <v>0.0003958828186856254</v>
       </c>
+      <c r="G413" s="1" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.0007914523149979343</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9551,6 +12035,12 @@
       <c r="F414" s="3" t="n">
         <v>-0.003132341425215352</v>
       </c>
+      <c r="G414" s="1" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0.0007855459544384226</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9573,6 +12063,12 @@
       <c r="F415" s="3" t="n">
         <v>-0.0007432181345224005</v>
       </c>
+      <c r="G415" s="1" t="n">
+        <v>2.706</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0.006322052807735182</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9595,6 +12091,12 @@
       <c r="F416" s="2" t="n">
         <v>0.001852423587526939</v>
       </c>
+      <c r="G416" s="1" t="n">
+        <v>0.03218</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>-0.00832049306625576</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9617,6 +12119,12 @@
       <c r="F417" s="2" t="n">
         <v>0.001765002521432189</v>
       </c>
+      <c r="G417" s="1" t="n">
+        <v>0.03995</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>0.005537377296753032</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9639,6 +12147,12 @@
       <c r="F418" s="2" t="n">
         <v>0.001708278580814785</v>
       </c>
+      <c r="G418" s="1" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="H418" s="3" t="n">
+        <v>-0.001180637544273996</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9661,6 +12175,12 @@
       <c r="F419" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G419" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>0.001508295625942754</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9683,6 +12203,12 @@
       <c r="F420" s="3" t="n">
         <v>-0.003382187147688779</v>
       </c>
+      <c r="G420" s="1" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>0.005656108597285072</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9705,6 +12231,12 @@
       <c r="F421" s="2" t="n">
         <v>0.002494802494802566</v>
       </c>
+      <c r="G421" s="1" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>0.003732890916632037</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9727,6 +12259,12 @@
       <c r="F422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="H422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9749,6 +12287,12 @@
       <c r="F423" s="2" t="n">
         <v>0.0006657789613847469</v>
       </c>
+      <c r="G423" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>0.001330671989354662</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9771,6 +12315,12 @@
       <c r="F424" s="3" t="n">
         <v>-0.0004755111745126126</v>
       </c>
+      <c r="G424" s="1" t="n">
+        <v>0.0002098</v>
+      </c>
+      <c r="H424" s="3" t="n">
+        <v>-0.001902949571836264</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9793,6 +12343,12 @@
       <c r="F425" s="2" t="n">
         <v>0.0008110300081102107</v>
       </c>
+      <c r="G425" s="1" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>0.003241491085899517</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9815,6 +12371,12 @@
       <c r="F426" s="3" t="n">
         <v>-0.002133712660028373</v>
       </c>
+      <c r="G426" s="1" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>0.004989308624376261</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9837,6 +12399,12 @@
       <c r="F427" s="3" t="n">
         <v>-0.0005154639175257522</v>
       </c>
+      <c r="G427" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>0.002578648788034964</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9859,6 +12427,12 @@
       <c r="F428" s="3" t="n">
         <v>-0.001671732522796337</v>
       </c>
+      <c r="G428" s="1" t="n">
+        <v>0.06591</v>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>0.003349063784442046</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9881,6 +12455,12 @@
       <c r="F429" s="3" t="n">
         <v>-0.0007547169811322017</v>
       </c>
+      <c r="G429" s="1" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>0.001510574018126932</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9903,6 +12483,12 @@
       <c r="F430" s="2" t="n">
         <v>0.002619456237015739</v>
       </c>
+      <c r="G430" s="1" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>0.0009009009009008642</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9925,6 +12511,12 @@
       <c r="F431" s="2" t="n">
         <v>0.008809234507898051</v>
       </c>
+      <c r="G431" s="1" t="n">
+        <v>0.006677</v>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>0.005269497139415754</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9947,6 +12539,12 @@
       <c r="F432" s="3" t="n">
         <v>-0.001142204454597401</v>
       </c>
+      <c r="G432" s="1" t="n">
+        <v>0.001756</v>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>0.004002287021154982</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9969,6 +12567,12 @@
       <c r="F433" s="3" t="n">
         <v>-0.01764290755116448</v>
       </c>
+      <c r="G433" s="1" t="n">
+        <v>0.001371</v>
+      </c>
+      <c r="H433" s="3" t="n">
+        <v>-0.0150862068965517</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9991,6 +12595,12 @@
       <c r="F434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G434" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="H434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10013,6 +12623,12 @@
       <c r="F435" s="3" t="n">
         <v>-0.00102734313260644</v>
       </c>
+      <c r="G435" s="1" t="n">
+        <v>0.12678</v>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>0.002926983624713308</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10035,6 +12651,12 @@
       <c r="F436" s="3" t="n">
         <v>-0.002194397831418659</v>
       </c>
+      <c r="G436" s="1" t="n">
+        <v>0.07747</v>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>0.002199223803363564</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10057,6 +12679,12 @@
       <c r="F437" s="3" t="n">
         <v>-0.004249291784702431</v>
       </c>
+      <c r="G437" s="1" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>0.009325114588272333</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10079,6 +12707,12 @@
       <c r="F438" s="2" t="n">
         <v>0.0002267059623667223</v>
       </c>
+      <c r="G438" s="1" t="n">
+        <v>0.04345</v>
+      </c>
+      <c r="H438" s="3" t="n">
+        <v>-0.01518585675430637</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10101,6 +12735,12 @@
       <c r="F439" s="3" t="n">
         <v>-0.002279851809632479</v>
       </c>
+      <c r="G439" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>0.00485575549842912</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10123,6 +12763,12 @@
       <c r="F440" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G440" s="1" t="n">
+        <v>0.001518</v>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>0.001980198019801957</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10145,6 +12791,12 @@
       <c r="F441" s="2" t="n">
         <v>0.002002529510961206</v>
       </c>
+      <c r="G441" s="1" t="n">
+        <v>0.009502999999999999</v>
+      </c>
+      <c r="H441" s="3" t="n">
+        <v>-0.0004207426107079553</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10167,6 +12819,12 @@
       <c r="F442" s="2" t="n">
         <v>0.002832861189801807</v>
       </c>
+      <c r="G442" s="1" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H442" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10189,6 +12847,12 @@
       <c r="F443" s="3" t="n">
         <v>-0.004048582995951408</v>
       </c>
+      <c r="G443" s="1" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="H443" s="3" t="n">
+        <v>-0.004516711833784977</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10211,6 +12875,12 @@
       <c r="F444" s="3" t="n">
         <v>-0.00552340873224632</v>
       </c>
+      <c r="G444" s="1" t="n">
+        <v>0.0003818</v>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>0.009785770960063571</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10233,6 +12903,12 @@
       <c r="F445" s="2" t="n">
         <v>0.002572898799313888</v>
       </c>
+      <c r="G445" s="1" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="H445" s="2" t="n">
+        <v>0.004277159965782843</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10255,6 +12931,12 @@
       <c r="F446" s="3" t="n">
         <v>-0.00768782760628997</v>
       </c>
+      <c r="G446" s="1" t="n">
+        <v>0.08534</v>
+      </c>
+      <c r="H446" s="2" t="n">
+        <v>0.001760770043432297</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10277,6 +12959,12 @@
       <c r="F447" s="3" t="n">
         <v>-0.002772643253234719</v>
       </c>
+      <c r="G447" s="1" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="H447" s="2" t="n">
+        <v>0.003707136237256722</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10299,6 +12987,12 @@
       <c r="F448" s="2" t="n">
         <v>0.001095976201659631</v>
       </c>
+      <c r="G448" s="1" t="n">
+        <v>0.06404</v>
+      </c>
+      <c r="H448" s="2" t="n">
+        <v>0.001563966218329729</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10321,6 +13015,12 @@
       <c r="F449" s="3" t="n">
         <v>-0.003490759753593387</v>
       </c>
+      <c r="G449" s="1" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="H449" s="2" t="n">
+        <v>0.0008242324335462837</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10343,6 +13043,12 @@
       <c r="F450" s="2" t="n">
         <v>0.004010695187165705</v>
       </c>
+      <c r="G450" s="1" t="n">
+        <v>0.03741</v>
+      </c>
+      <c r="H450" s="3" t="n">
+        <v>-0.003728362183755026</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10365,6 +13071,12 @@
       <c r="F451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G451" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="H451" s="2" t="n">
+        <v>0.001838235294117572</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10387,6 +13099,12 @@
       <c r="F452" s="3" t="n">
         <v>-0.0009458053532583265</v>
       </c>
+      <c r="G452" s="1" t="n">
+        <v>0.10554</v>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>-0.0008520306731042955</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10409,6 +13127,12 @@
       <c r="F453" s="3" t="n">
         <v>-0.001869158878504597</v>
       </c>
+      <c r="G453" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="H453" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10431,6 +13155,12 @@
       <c r="F454" s="2" t="n">
         <v>0.0003512469265893537</v>
       </c>
+      <c r="G454" s="1" t="n">
+        <v>2.878</v>
+      </c>
+      <c r="H454" s="2" t="n">
+        <v>0.01053370786516863</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10453,6 +13183,12 @@
       <c r="F455" s="2" t="n">
         <v>0.001119820828667414</v>
       </c>
+      <c r="G455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="H455" s="2" t="n">
+        <v>0.001118568232662193</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10475,6 +13211,12 @@
       <c r="F456" s="3" t="n">
         <v>-0.0006795786612301134</v>
       </c>
+      <c r="G456" s="1" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="H456" s="2" t="n">
+        <v>0.001020061203672259</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10497,6 +13239,12 @@
       <c r="F457" s="3" t="n">
         <v>-0.002030456852791795</v>
       </c>
+      <c r="G457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="H457" s="2" t="n">
+        <v>0.003051881993896288</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10519,6 +13267,12 @@
       <c r="F458" s="3" t="n">
         <v>-0.002412739263310347</v>
       </c>
+      <c r="G458" s="1" t="n">
+        <v>0.06227</v>
+      </c>
+      <c r="H458" s="2" t="n">
+        <v>0.004030957755562725</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10541,6 +13295,12 @@
       <c r="F459" s="3" t="n">
         <v>-0.001389854065323084</v>
       </c>
+      <c r="G459" s="1" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="H459" s="2" t="n">
+        <v>0.0006958942240779118</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10563,6 +13323,12 @@
       <c r="F460" s="3" t="n">
         <v>-0.0006870276684779584</v>
       </c>
+      <c r="G460" s="1" t="n">
+        <v>0.015989</v>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>-0.000687500000000037</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10585,6 +13351,12 @@
       <c r="F461" s="2" t="n">
         <v>0.0006097560975609507</v>
       </c>
+      <c r="G461" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="H461" s="2" t="n">
+        <v>0.009140767824497097</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10607,6 +13379,12 @@
       <c r="F462" s="2" t="n">
         <v>0.000958772770853331</v>
       </c>
+      <c r="G462" s="1" t="n">
+        <v>0.0002093</v>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>0.002394636015325599</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10629,6 +13407,12 @@
       <c r="F463" s="2" t="n">
         <v>0.002038735983690029</v>
       </c>
+      <c r="G463" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="H463" s="2" t="n">
+        <v>0.003051881993896182</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -10651,6 +13435,12 @@
       <c r="F464" s="3" t="n">
         <v>-0.0003838771593090055</v>
       </c>
+      <c r="G464" s="1" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="H464" s="2" t="n">
+        <v>0.003456221198156674</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10673,6 +13463,12 @@
       <c r="F465" s="2" t="n">
         <v>0.008053691275167807</v>
       </c>
+      <c r="G465" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="H465" s="2" t="n">
+        <v>0.006657789613848162</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10695,6 +13491,12 @@
       <c r="F466" s="2" t="n">
         <v>0.001098096632503615</v>
       </c>
+      <c r="G466" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10717,6 +13519,12 @@
       <c r="F467" s="3" t="n">
         <v>-0.007252683492892376</v>
       </c>
+      <c r="G467" s="1" t="n">
+        <v>0.03436</v>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>0.004091174751607283</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10739,6 +13547,12 @@
       <c r="F468" s="2" t="n">
         <v>0.001857355126300043</v>
       </c>
+      <c r="G468" s="1" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>0.02484241750092702</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10761,6 +13575,12 @@
       <c r="F469" s="2" t="n">
         <v>0.005362649148679433</v>
       </c>
+      <c r="G469" s="1" t="n">
+        <v>0.0007471</v>
+      </c>
+      <c r="H469" s="3" t="n">
+        <v>-0.003733831177490279</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10783,6 +13603,12 @@
       <c r="F470" s="2" t="n">
         <v>0.001142857142857144</v>
       </c>
+      <c r="G470" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H470" s="2" t="n">
+        <v>0.002283105022831052</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10805,6 +13631,12 @@
       <c r="F471" s="2" t="n">
         <v>0.002024291497975802</v>
       </c>
+      <c r="G471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="H471" s="3" t="n">
+        <v>-0.002020202020202113</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10827,6 +13659,12 @@
       <c r="F472" s="3" t="n">
         <v>-0.005322546306152869</v>
       </c>
+      <c r="G472" s="1" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="H472" s="3" t="n">
+        <v>-0.002568493150684827</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10849,6 +13687,12 @@
       <c r="F473" s="3" t="n">
         <v>-0.0003664345914253902</v>
       </c>
+      <c r="G473" s="1" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="H473" s="2" t="n">
+        <v>0.00183284457478006</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10871,6 +13715,12 @@
       <c r="F474" s="2" t="n">
         <v>0.002292526364053252</v>
       </c>
+      <c r="G474" s="1" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="H474" s="3" t="n">
+        <v>-0.002516010978956976</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10893,6 +13743,12 @@
       <c r="F475" s="2" t="n">
         <v>0.002143367468444946</v>
       </c>
+      <c r="G475" s="1" t="n">
+        <v>0.008446</v>
+      </c>
+      <c r="H475" s="2" t="n">
+        <v>0.003564638783270023</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10915,6 +13771,12 @@
       <c r="F476" s="3" t="n">
         <v>-0.002446782481037336</v>
       </c>
+      <c r="G476" s="1" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="H476" s="2" t="n">
+        <v>0.001226391954868811</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10937,6 +13799,12 @@
       <c r="F477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G477" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>0.002954209748892256</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10959,6 +13827,12 @@
       <c r="F478" s="3" t="n">
         <v>-0.003019627579265171</v>
       </c>
+      <c r="G478" s="1" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="H478" s="2" t="n">
+        <v>0.002271580010095941</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10981,6 +13855,12 @@
       <c r="F479" s="2" t="n">
         <v>0.0004772130756381288</v>
       </c>
+      <c r="G479" s="1" t="n">
+        <v>0.008415000000000001</v>
+      </c>
+      <c r="H479" s="2" t="n">
+        <v>0.003458144526592088</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11003,6 +13883,12 @@
       <c r="F480" s="2" t="n">
         <v>0.0006277463904582293</v>
       </c>
+      <c r="G480" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>0.0006273525721455203</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11025,6 +13911,12 @@
       <c r="F481" s="3" t="n">
         <v>-0.00168634064080951</v>
       </c>
+      <c r="G481" s="1" t="n">
+        <v>0.07709000000000001</v>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>0.001689189189189256</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11047,6 +13939,12 @@
       <c r="F482" s="2" t="n">
         <v>0.001785360047609597</v>
       </c>
+      <c r="G482" s="1" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="H482" s="2" t="n">
+        <v>0.002178217821782158</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11069,6 +13967,12 @@
       <c r="F483" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="H483" s="2" t="n">
+        <v>0.003102378490175855</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11091,6 +13995,12 @@
       <c r="F484" s="3" t="n">
         <v>-0.0005884949242312545</v>
       </c>
+      <c r="G484" s="1" t="n">
+        <v>0.06802999999999999</v>
+      </c>
+      <c r="H484" s="2" t="n">
+        <v>0.001472103636095819</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -11113,6 +14023,12 @@
       <c r="F485" s="2" t="n">
         <v>0.0006678539626000736</v>
       </c>
+      <c r="G485" s="1" t="n">
+        <v>0.000449</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>-0.001112347052280218</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11135,6 +14051,12 @@
       <c r="F486" s="3" t="n">
         <v>-0.006858710562414203</v>
       </c>
+      <c r="G486" s="1" t="n">
+        <v>0.07957</v>
+      </c>
+      <c r="H486" s="3" t="n">
+        <v>-0.0008789552988448093</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11157,6 +14079,12 @@
       <c r="F487" s="3" t="n">
         <v>-0.001156069364161878</v>
       </c>
+      <c r="G487" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="H487" s="2" t="n">
+        <v>0.001157407407407436</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11179,6 +14107,12 @@
       <c r="F488" s="2" t="n">
         <v>0.003893724232707364</v>
       </c>
+      <c r="G488" s="1" t="n">
+        <v>0.08767999999999999</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>0.00022815423226092</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11201,6 +14135,12 @@
       <c r="F489" s="2" t="n">
         <v>0.001688476150274455</v>
       </c>
+      <c r="G489" s="1" t="n">
+        <v>0.04757</v>
+      </c>
+      <c r="H489" s="2" t="n">
+        <v>0.002317741255794332</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11223,6 +14163,12 @@
       <c r="F490" s="2" t="n">
         <v>0.01357104843001587</v>
       </c>
+      <c r="G490" s="1" t="n">
+        <v>0.03834</v>
+      </c>
+      <c r="H490" s="2" t="n">
+        <v>0.006563402467839334</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11245,6 +14191,12 @@
       <c r="F491" s="3" t="n">
         <v>-0.001410256410256397</v>
       </c>
+      <c r="G491" s="1" t="n">
+        <v>0.07797</v>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>0.001027089485171354</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11267,6 +14219,12 @@
       <c r="F492" s="2" t="n">
         <v>0.003793266951161533</v>
       </c>
+      <c r="G492" s="1" t="n">
+        <v>0.06363000000000001</v>
+      </c>
+      <c r="H492" s="2" t="n">
+        <v>0.001889466225791356</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11289,6 +14247,12 @@
       <c r="F493" s="2" t="n">
         <v>0.003861003861003872</v>
       </c>
+      <c r="G493" s="1" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>0.001923076923077012</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11311,6 +14275,12 @@
       <c r="F494" s="3" t="n">
         <v>-0.0003619254433586283</v>
       </c>
+      <c r="G494" s="1" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="H494" s="2" t="n">
+        <v>0.0007241129616219333</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11333,6 +14303,12 @@
       <c r="F495" s="3" t="n">
         <v>-0.001256084157638511</v>
       </c>
+      <c r="G495" s="1" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="H495" s="2" t="n">
+        <v>0.000943247916994254</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11355,6 +14331,12 @@
       <c r="F496" s="2" t="n">
         <v>0.000341296928327797</v>
       </c>
+      <c r="G496" s="1" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>0.001364721937905001</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11377,6 +14359,12 @@
       <c r="F497" s="3" t="n">
         <v>-0.01843204718604064</v>
       </c>
+      <c r="G497" s="1" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="H497" s="3" t="n">
+        <v>-0.01214321482223351</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11399,6 +14387,12 @@
       <c r="F498" s="2" t="n">
         <v>0.0009708737864077948</v>
       </c>
+      <c r="G498" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="H498" s="2" t="n">
+        <v>0.0009699321047526951</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11421,6 +14415,12 @@
       <c r="F499" s="3" t="n">
         <v>-0.001688781664656227</v>
       </c>
+      <c r="G499" s="1" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="H499" s="2" t="n">
+        <v>0.004349927501208304</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11443,6 +14443,12 @@
       <c r="F500" s="3" t="n">
         <v>-0.001460209296665965</v>
       </c>
+      <c r="G500" s="1" t="n">
+        <v>0.04115</v>
+      </c>
+      <c r="H500" s="2" t="n">
+        <v>0.00292468925176705</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11465,6 +14471,12 @@
       <c r="F501" s="3" t="n">
         <v>-0.001003009027081273</v>
       </c>
+      <c r="G501" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>0.001004016064257057</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11487,6 +14499,12 @@
       <c r="F502" s="3" t="n">
         <v>-0.0003026634382566988</v>
       </c>
+      <c r="G502" s="1" t="n">
+        <v>0.003306</v>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>0.0009082652134423144</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -11509,6 +14527,12 @@
       <c r="F503" s="3" t="n">
         <v>-0.009761388286334223</v>
       </c>
+      <c r="G503" s="1" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="H503" s="3" t="n">
+        <v>-0.001095290251916713</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11531,6 +14555,12 @@
       <c r="F504" s="3" t="n">
         <v>-0.002536461636017828</v>
       </c>
+      <c r="G504" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>0.006993006993007105</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11553,6 +14583,12 @@
       <c r="F505" s="3" t="n">
         <v>-0.001525553012967244</v>
       </c>
+      <c r="G505" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="H505" s="2" t="n">
+        <v>0.002291825821237758</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -11575,6 +14611,12 @@
       <c r="F506" s="3" t="n">
         <v>-0.003554502369668102</v>
       </c>
+      <c r="G506" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="H506" s="2" t="n">
+        <v>0.002972651605231746</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11597,6 +14639,12 @@
       <c r="F507" s="3" t="n">
         <v>-0.003455425017277134</v>
       </c>
+      <c r="G507" s="1" t="n">
+        <v>0.002884</v>
+      </c>
+      <c r="H507" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -11619,6 +14667,12 @@
       <c r="F508" s="2" t="n">
         <v>0.00363967242948135</v>
       </c>
+      <c r="G508" s="1" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>0.00362647325475975</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -11641,6 +14695,12 @@
       <c r="F509" s="3" t="n">
         <v>-0.00633828323071344</v>
       </c>
+      <c r="G509" s="1" t="n">
+        <v>0.05498</v>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>0.002004738472753763</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -11663,6 +14723,12 @@
       <c r="F510" s="3" t="n">
         <v>-0.001706484641638156</v>
       </c>
+      <c r="G510" s="1" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="H510" s="2" t="n">
+        <v>0.006837606837606796</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -11685,6 +14751,12 @@
       <c r="F511" s="2" t="n">
         <v>0.0002477700693756953</v>
       </c>
+      <c r="G511" s="1" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>0.001981669556601356</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -11707,6 +14779,12 @@
       <c r="F512" s="3" t="n">
         <v>-0.01162790697674404</v>
       </c>
+      <c r="G512" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="H512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -11729,6 +14807,12 @@
       <c r="F513" s="3" t="n">
         <v>-0.001958268620433487</v>
       </c>
+      <c r="G513" s="1" t="n">
+        <v>0.014832</v>
+      </c>
+      <c r="H513" s="2" t="n">
+        <v>0.003518267929634639</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -11751,6 +14835,12 @@
       <c r="F514" s="3" t="n">
         <v>-0.00172117039586932</v>
       </c>
+      <c r="G514" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="H514" s="2" t="n">
+        <v>0.0005747126436782572</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11773,6 +14863,12 @@
       <c r="F515" s="3" t="n">
         <v>-0.0009302325581395615</v>
       </c>
+      <c r="G515" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>0.0009310986964618516</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11795,6 +14891,12 @@
       <c r="F516" s="2" t="n">
         <v>0.007575757575757596</v>
       </c>
+      <c r="G516" s="1" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="H516" s="3" t="n">
+        <v>-0.003759398496240611</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11817,6 +14919,12 @@
       <c r="F517" s="2" t="n">
         <v>0.0009113396693138994</v>
       </c>
+      <c r="G517" s="1" t="n">
+        <v>0.007748</v>
+      </c>
+      <c r="H517" s="2" t="n">
+        <v>0.007804370447450479</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11839,6 +14947,12 @@
       <c r="F518" s="2" t="n">
         <v>0.002602472348731301</v>
       </c>
+      <c r="G518" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="H518" s="2" t="n">
+        <v>0.001297858533419804</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11861,6 +14975,12 @@
       <c r="F519" s="3" t="n">
         <v>-0.004870920603994167</v>
       </c>
+      <c r="G519" s="1" t="n">
+        <v>0.004108</v>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>0.005384238864414941</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11883,6 +15003,12 @@
       <c r="F520" s="3" t="n">
         <v>-0.001724137931034525</v>
       </c>
+      <c r="G520" s="1" t="n">
+        <v>0.001159</v>
+      </c>
+      <c r="H520" s="2" t="n">
+        <v>0.0008635578583766259</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -11905,6 +15031,12 @@
       <c r="F521" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G521" s="1" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="H521" s="2" t="n">
+        <v>0.002250562640660203</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11927,6 +15059,12 @@
       <c r="F522" s="3" t="n">
         <v>-0.003061224489796067</v>
       </c>
+      <c r="G522" s="1" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H522" s="2" t="n">
+        <v>0.0001462202076328411</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11949,6 +15087,12 @@
       <c r="F523" s="3" t="n">
         <v>-0.0007163323782234168</v>
       </c>
+      <c r="G523" s="1" t="n">
+        <v>0.06992</v>
+      </c>
+      <c r="H523" s="2" t="n">
+        <v>0.002437275985662933</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11971,6 +15115,12 @@
       <c r="F524" s="3" t="n">
         <v>-0.0008658008658008306</v>
       </c>
+      <c r="G524" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="H524" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11993,6 +15143,12 @@
       <c r="F525" s="3" t="n">
         <v>-0.006105006105006069</v>
       </c>
+      <c r="G525" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="H525" s="2" t="n">
+        <v>0.0006142506142505893</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -12015,6 +15171,12 @@
       <c r="F526" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G526" s="1" t="n">
+        <v>0.13617</v>
+      </c>
+      <c r="H526" s="2" t="n">
+        <v>0.0008084668528592294</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -12037,6 +15199,12 @@
       <c r="F527" s="2" t="n">
         <v>0.0004664179104477422</v>
       </c>
+      <c r="G527" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H527" s="2" t="n">
+        <v>0.002331002331002236</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -12059,6 +15227,12 @@
       <c r="F528" s="2" t="n">
         <v>0.00073719130114277</v>
       </c>
+      <c r="G528" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="H528" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -12081,6 +15255,12 @@
       <c r="F529" s="3" t="n">
         <v>-0.002220371912295213</v>
       </c>
+      <c r="G529" s="1" t="n">
+        <v>0.0007207</v>
+      </c>
+      <c r="H529" s="2" t="n">
+        <v>0.002364394993045879</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -12103,6 +15283,12 @@
       <c r="F530" s="3" t="n">
         <v>-0.002637257252457586</v>
       </c>
+      <c r="G530" s="1" t="n">
+        <v>0.004164</v>
+      </c>
+      <c r="H530" s="2" t="n">
+        <v>0.0009615384615385892</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -12125,6 +15311,12 @@
       <c r="F531" s="2" t="n">
         <v>0.002298850574712731</v>
       </c>
+      <c r="G531" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="H531" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -12147,6 +15339,12 @@
       <c r="F532" s="3" t="n">
         <v>-0.003381234150464899</v>
       </c>
+      <c r="G532" s="1" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="H532" s="3" t="n">
+        <v>-0.003392705682782116</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -12169,6 +15367,12 @@
       <c r="F533" s="2" t="n">
         <v>0.003575461046292862</v>
       </c>
+      <c r="G533" s="1" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>0.003937746109131725</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -12191,6 +15395,12 @@
       <c r="F534" s="3" t="n">
         <v>-0.001992031872510109</v>
       </c>
+      <c r="G534" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="H534" s="2" t="n">
+        <v>0.001330671989354662</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -12213,6 +15423,12 @@
       <c r="F535" s="2" t="n">
         <v>0.001175088131609823</v>
       </c>
+      <c r="G535" s="1" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="H535" s="2" t="n">
+        <v>0.003521126760563441</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -12235,6 +15451,12 @@
       <c r="F536" s="3" t="n">
         <v>-0.002415458937198039</v>
       </c>
+      <c r="G536" s="1" t="n">
+        <v>0.004971</v>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>0.003026634382566462</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -12257,6 +15479,12 @@
       <c r="F537" s="3" t="n">
         <v>-0.0006894174422614046</v>
       </c>
+      <c r="G537" s="1" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="H537" s="2" t="n">
+        <v>0.002759572266298803</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -12279,6 +15507,12 @@
       <c r="F538" s="3" t="n">
         <v>-0.001520912547528587</v>
       </c>
+      <c r="G538" s="1" t="n">
+        <v>0.01318</v>
+      </c>
+      <c r="H538" s="2" t="n">
+        <v>0.003808073115003917</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12301,6 +15535,12 @@
       <c r="F539" s="3" t="n">
         <v>-0.0008179959100204166</v>
       </c>
+      <c r="G539" s="1" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="H539" s="2" t="n">
+        <v>0.003274662300450275</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12323,6 +15563,12 @@
       <c r="F540" s="3" t="n">
         <v>-0.0008816787162758143</v>
       </c>
+      <c r="G540" s="1" t="n">
+        <v>0.05677</v>
+      </c>
+      <c r="H540" s="2" t="n">
+        <v>0.001941404871161295</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12345,6 +15591,12 @@
       <c r="F541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G541" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="H541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12367,6 +15619,12 @@
       <c r="F542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="H542" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12388,6 +15646,12 @@
       </c>
       <c r="F543" s="3" t="n">
         <v>-0.002180430635050357</v>
+      </c>
+      <c r="G543" s="1" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="H543" s="2" t="n">
+        <v>0.002458344714558834</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB543"/>
+  <dimension ref="A1:AD543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,8 @@
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,6 +599,16 @@
           <t>change_03:15</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>price_03:30</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>change_03:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -685,6 +697,12 @@
       <c r="AB2" s="3" t="n">
         <v>-0.002051604658049196</v>
       </c>
+      <c r="AC2" s="1" t="n">
+        <v>70486.7</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>0.0007467973609372628</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -773,6 +791,12 @@
       <c r="AB3" s="3" t="n">
         <v>-0.002336977733661591</v>
       </c>
+      <c r="AC3" s="1" t="n">
+        <v>2071.15</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>0.0003235964607241185</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +885,12 @@
       <c r="AB4" s="3" t="n">
         <v>-0.005468839011051496</v>
       </c>
+      <c r="AC4" s="1" t="n">
+        <v>87.18000000000001</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>-0.001260167258563403</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -949,6 +979,12 @@
       <c r="AB5" s="3" t="n">
         <v>-0.01523023272364949</v>
       </c>
+      <c r="AC5" s="1" t="n">
+        <v>0.013797</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>-0.002890800028908008</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1037,6 +1073,12 @@
       <c r="AB6" s="3" t="n">
         <v>-0.0004239983040067667</v>
       </c>
+      <c r="AC6" s="1" t="n">
+        <v>0.09397</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>-0.003499469777306437</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1125,6 +1167,12 @@
       <c r="AB7" s="3" t="n">
         <v>-0.005058421202621747</v>
       </c>
+      <c r="AC7" s="1" t="n">
+        <v>1.3921</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>-0.003150733977801777</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1213,6 +1261,12 @@
       <c r="AB8" s="3" t="n">
         <v>-0.007723387296264901</v>
       </c>
+      <c r="AC8" s="1" t="n">
+        <v>36.142</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.001107971857514993</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1301,6 +1355,12 @@
       <c r="AB9" s="3" t="n">
         <v>-0.001531768886710373</v>
       </c>
+      <c r="AC9" s="1" t="n">
+        <v>651.77</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>-0.0001073883161512795</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1389,6 +1449,12 @@
       <c r="AB10" s="3" t="n">
         <v>-0.0130431750017437</v>
       </c>
+      <c r="AC10" s="1" t="n">
+        <v>14.049</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>-0.007137809187279213</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1477,6 +1543,12 @@
       <c r="AB11" s="3" t="n">
         <v>-0.002815315315315289</v>
       </c>
+      <c r="AC11" s="1" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>0.005081874647091963</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1565,6 +1637,12 @@
       <c r="AB12" s="3" t="n">
         <v>-0.003897484351009833</v>
       </c>
+      <c r="AC12" s="1" t="n">
+        <v>0.0033656</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>-0.002371354043158701</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1653,6 +1731,12 @@
       <c r="AB13" s="2" t="n">
         <v>0.02485267742761974</v>
       </c>
+      <c r="AC13" s="1" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>0.001999999999999919</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1741,6 +1825,12 @@
       <c r="AB14" s="2" t="n">
         <v>0.005329272934906828</v>
       </c>
+      <c r="AC14" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>0.003407800075728851</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1829,6 +1919,12 @@
       <c r="AB15" s="3" t="n">
         <v>-0.003429147755925436</v>
       </c>
+      <c r="AC15" s="1" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>0.005667442566541898</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1917,6 +2013,12 @@
       <c r="AB16" s="3" t="n">
         <v>-0.002281902755836373</v>
       </c>
+      <c r="AC16" s="1" t="n">
+        <v>0.05631</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>-0.009324419422941637</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2005,6 +2107,12 @@
       <c r="AB17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC17" s="1" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>0.002249718785151858</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2093,6 +2201,12 @@
       <c r="AB18" s="3" t="n">
         <v>-0.001502065339842118</v>
       </c>
+      <c r="AC18" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>-0.001504324934185827</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2181,6 +2295,12 @@
       <c r="AB19" s="2" t="n">
         <v>0.01177321940493755</v>
       </c>
+      <c r="AC19" s="1" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>-0.01848591549295776</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2269,6 +2389,12 @@
       <c r="AB20" s="3" t="n">
         <v>-0.002569109032987397</v>
       </c>
+      <c r="AC20" s="1" t="n">
+        <v>9.707000000000001</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>0.0001030290541934084</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2357,6 +2483,12 @@
       <c r="AB21" s="3" t="n">
         <v>-0.001593228777694763</v>
       </c>
+      <c r="AC21" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>0.004887049319303794</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2445,6 +2577,12 @@
       <c r="AB22" s="3" t="n">
         <v>-0.02488151658767778</v>
       </c>
+      <c r="AC22" s="1" t="n">
+        <v>0.020797</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>0.01078979343863912</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2533,6 +2671,12 @@
       <c r="AB23" s="3" t="n">
         <v>-0.00135700059095188</v>
       </c>
+      <c r="AC23" s="1" t="n">
+        <v>456.98</v>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>0.001556096171126825</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2621,6 +2765,12 @@
       <c r="AB24" s="2" t="n">
         <v>0.0001024986462442456</v>
       </c>
+      <c r="AC24" s="1" t="n">
+        <v>5175.24</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>0.0007560917597600336</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2709,6 +2859,12 @@
       <c r="AB25" s="3" t="n">
         <v>-0.002639973600263902</v>
       </c>
+      <c r="AC25" s="1" t="n">
+        <v>9.076000000000001</v>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>0.0009926105657880602</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2797,6 +2953,12 @@
       <c r="AB26" s="3" t="n">
         <v>-0.02551769117886848</v>
       </c>
+      <c r="AC26" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>0.007278507487659966</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2885,6 +3047,12 @@
       <c r="AB27" s="3" t="n">
         <v>-0.004219409282700396</v>
       </c>
+      <c r="AC27" s="1" t="n">
+        <v>0.01167</v>
+      </c>
+      <c r="AD27" s="3" t="n">
+        <v>-0.01101694915254237</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2973,6 +3141,12 @@
       <c r="AB28" s="3" t="n">
         <v>-0.003091190108191656</v>
       </c>
+      <c r="AC28" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3061,6 +3235,12 @@
       <c r="AB29" s="3" t="n">
         <v>-0.00771035869929593</v>
       </c>
+      <c r="AC29" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="AD29" s="3" t="n">
+        <v>-0.007601351351351452</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3149,6 +3329,12 @@
       <c r="AB30" s="3" t="n">
         <v>-0.0006510416666667395</v>
       </c>
+      <c r="AC30" s="1" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>0.002605863192182413</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3237,6 +3423,12 @@
       <c r="AB31" s="3" t="n">
         <v>-0.006910167818361364</v>
       </c>
+      <c r="AC31" s="1" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="AD31" s="3" t="n">
+        <v>-0.0004970178926439856</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3325,6 +3517,12 @@
       <c r="AB32" s="3" t="n">
         <v>-0.001237930180737842</v>
       </c>
+      <c r="AC32" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="AD32" s="3" t="n">
+        <v>-0.002974714923153249</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3413,6 +3611,12 @@
       <c r="AB33" s="3" t="n">
         <v>-0.003030303030303117</v>
       </c>
+      <c r="AC33" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AD33" s="3" t="n">
+        <v>-0.001013171225937213</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3501,6 +3705,12 @@
       <c r="AB34" s="3" t="n">
         <v>-0.00283822138126782</v>
       </c>
+      <c r="AC34" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>-0.0009487666034154554</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3589,6 +3799,12 @@
       <c r="AB35" s="2" t="n">
         <v>0.01450892857142876</v>
       </c>
+      <c r="AC35" s="1" t="n">
+        <v>0.009039999999999999</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>-0.005500550055005658</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3677,6 +3893,12 @@
       <c r="AB36" s="3" t="n">
         <v>-0.004724847137298596</v>
       </c>
+      <c r="AC36" s="1" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AD36" s="2" t="n">
+        <v>0.000279251605696857</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3765,6 +3987,12 @@
       <c r="AB37" s="3" t="n">
         <v>-0.002913453299057353</v>
       </c>
+      <c r="AC37" s="1" t="n">
+        <v>0.005812</v>
+      </c>
+      <c r="AD37" s="3" t="n">
+        <v>-0.001031282227569599</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3853,6 +4081,12 @@
       <c r="AB38" s="3" t="n">
         <v>-0.009080503624570749</v>
       </c>
+      <c r="AC38" s="1" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="AD38" s="3" t="n">
+        <v>-0.001540120129370135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3941,6 +4175,12 @@
       <c r="AB39" s="3" t="n">
         <v>-0.002945797329143703</v>
       </c>
+      <c r="AC39" s="1" t="n">
+        <v>0.05055</v>
+      </c>
+      <c r="AD39" s="3" t="n">
+        <v>-0.004333267677762554</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4029,6 +4269,12 @@
       <c r="AB40" s="3" t="n">
         <v>-0.01014454316403662</v>
       </c>
+      <c r="AC40" s="1" t="n">
+        <v>0.14929</v>
+      </c>
+      <c r="AD40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4117,6 +4363,12 @@
       <c r="AB41" s="3" t="n">
         <v>-0.009935710111046213</v>
       </c>
+      <c r="AC41" s="1" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="AD41" s="2" t="n">
+        <v>0.0005903187721370528</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4205,6 +4457,12 @@
       <c r="AB42" s="3" t="n">
         <v>-0.003914242505115183</v>
       </c>
+      <c r="AC42" s="1" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>0.00232205054925431</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4293,6 +4551,12 @@
       <c r="AB43" s="2" t="n">
         <v>0.02269601100412659</v>
       </c>
+      <c r="AC43" s="1" t="n">
+        <v>0.8724</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>-0.02219233355749837</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4381,6 +4645,12 @@
       <c r="AB44" s="3" t="n">
         <v>-0.002540834845735038</v>
       </c>
+      <c r="AC44" s="1" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>0.0010917030567686</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4469,6 +4739,12 @@
       <c r="AB45" s="2" t="n">
         <v>0.0004238675991753809</v>
       </c>
+      <c r="AC45" s="1" t="n">
+        <v>0.52189</v>
+      </c>
+      <c r="AD45" s="2" t="n">
+        <v>0.005084256138661485</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4557,6 +4833,12 @@
       <c r="AB46" s="3" t="n">
         <v>-0.006125356125356083</v>
       </c>
+      <c r="AC46" s="1" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>0.003153217715350408</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4645,6 +4927,12 @@
       <c r="AB47" s="3" t="n">
         <v>-0.002290076335877949</v>
       </c>
+      <c r="AC47" s="1" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AD47" s="2" t="n">
+        <v>0.002295332823259459</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4733,6 +5021,12 @@
       <c r="AB48" s="3" t="n">
         <v>-0.003358835603657305</v>
       </c>
+      <c r="AC48" s="1" t="n">
+        <v>0.16003</v>
+      </c>
+      <c r="AD48" s="3" t="n">
+        <v>-0.001248205704300104</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4821,6 +5115,12 @@
       <c r="AB49" s="3" t="n">
         <v>-0.01828589600890441</v>
       </c>
+      <c r="AC49" s="1" t="n">
+        <v>0.06137</v>
+      </c>
+      <c r="AD49" s="3" t="n">
+        <v>-0.005992873339812152</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4909,6 +5209,12 @@
       <c r="AB50" s="2" t="n">
         <v>0.002577319587628761</v>
       </c>
+      <c r="AC50" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AD50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4997,6 +5303,12 @@
       <c r="AB51" s="3" t="n">
         <v>-0.04693864144002093</v>
       </c>
+      <c r="AC51" s="1" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="AD51" s="2" t="n">
+        <v>0.008719627778735056</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5085,6 +5397,12 @@
       <c r="AB52" s="2" t="n">
         <v>0.003434065934065937</v>
       </c>
+      <c r="AC52" s="1" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>0.006160164271047119</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5173,6 +5491,12 @@
       <c r="AB53" s="3" t="n">
         <v>-0.004380475594493155</v>
       </c>
+      <c r="AC53" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="AD53" s="2" t="n">
+        <v>0.0006285355122565478</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5261,6 +5585,12 @@
       <c r="AB54" s="3" t="n">
         <v>-0.001550120564932849</v>
       </c>
+      <c r="AC54" s="1" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="AD54" s="2" t="n">
+        <v>0.0002070036225634104</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5349,6 +5679,12 @@
       <c r="AB55" s="3" t="n">
         <v>-0.003905160390516073</v>
       </c>
+      <c r="AC55" s="1" t="n">
+        <v>0.007135</v>
+      </c>
+      <c r="AD55" s="3" t="n">
+        <v>-0.0009801176141137023</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5437,6 +5773,12 @@
       <c r="AB56" s="3" t="n">
         <v>-0.003165670066830805</v>
       </c>
+      <c r="AC56" s="1" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="AD56" s="3" t="n">
+        <v>-0.004940014114326085</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5525,6 +5867,12 @@
       <c r="AB57" s="3" t="n">
         <v>-0.008528784648187616</v>
       </c>
+      <c r="AC57" s="1" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="AD57" s="2" t="n">
+        <v>0.005734767025089704</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5613,6 +5961,12 @@
       <c r="AB58" s="3" t="n">
         <v>-0.009981666327154293</v>
       </c>
+      <c r="AC58" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>-0.0002057613168723482</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5701,6 +6055,12 @@
       <c r="AB59" s="3" t="n">
         <v>-0.005802707930367438</v>
       </c>
+      <c r="AC59" s="1" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="AD59" s="2" t="n">
+        <v>0.00324254215304792</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5789,6 +6149,12 @@
       <c r="AB60" s="3" t="n">
         <v>-0.008695652173913066</v>
       </c>
+      <c r="AC60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="AD60" s="2" t="n">
+        <v>0.005847953216374284</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5877,6 +6243,12 @@
       <c r="AB61" s="3" t="n">
         <v>-0.003846153846153778</v>
       </c>
+      <c r="AC61" s="1" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="AD61" s="2" t="n">
+        <v>0.001287001287001145</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5965,6 +6337,12 @@
       <c r="AB62" s="3" t="n">
         <v>-0.002615518744551102</v>
       </c>
+      <c r="AC62" s="1" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>-0.000874125874125778</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6053,6 +6431,12 @@
       <c r="AB63" s="3" t="n">
         <v>-0.004550625711035397</v>
       </c>
+      <c r="AC63" s="1" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="AD63" s="2" t="n">
+        <v>0.002285714285714351</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6141,6 +6525,12 @@
       <c r="AB64" s="3" t="n">
         <v>-0.0006798096532971529</v>
       </c>
+      <c r="AC64" s="1" t="n">
+        <v>2.937</v>
+      </c>
+      <c r="AD64" s="3" t="n">
+        <v>-0.001020408163265345</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6229,6 +6619,12 @@
       <c r="AB65" s="3" t="n">
         <v>-0.004206983592763963</v>
       </c>
+      <c r="AC65" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="AD65" s="3" t="n">
+        <v>-0.002957329953527698</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6317,6 +6713,12 @@
       <c r="AB66" s="3" t="n">
         <v>-0.00588812561334645</v>
       </c>
+      <c r="AC66" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="AD66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6405,6 +6807,12 @@
       <c r="AB67" s="3" t="n">
         <v>-0.0004065591543570129</v>
       </c>
+      <c r="AC67" s="1" t="n">
+        <v>0.007339</v>
+      </c>
+      <c r="AD67" s="3" t="n">
+        <v>-0.005016268980477184</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6493,6 +6901,12 @@
       <c r="AB68" s="3" t="n">
         <v>-0.00163220892274198</v>
       </c>
+      <c r="AC68" s="1" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AD68" s="2" t="n">
+        <v>0.0032697547683923</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6581,6 +6995,12 @@
       <c r="AB69" s="3" t="n">
         <v>-0.003127299484915315</v>
       </c>
+      <c r="AC69" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="AD69" s="2" t="n">
+        <v>0.004797933198006945</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6669,6 +7089,12 @@
       <c r="AB70" s="3" t="n">
         <v>-0.004237288135593225</v>
       </c>
+      <c r="AC70" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AD70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6757,6 +7183,12 @@
       <c r="AB71" s="3" t="n">
         <v>-0.005051384776171384</v>
       </c>
+      <c r="AC71" s="1" t="n">
+        <v>5.691</v>
+      </c>
+      <c r="AD71" s="3" t="n">
+        <v>-0.003676470588235278</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6845,6 +7277,12 @@
       <c r="AB72" s="3" t="n">
         <v>-0.02573932092004378</v>
       </c>
+      <c r="AC72" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="AD72" s="2" t="n">
+        <v>0.00112422709387299</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6933,6 +7371,12 @@
       <c r="AB73" s="3" t="n">
         <v>-0.003069432684165976</v>
       </c>
+      <c r="AC73" s="1" t="n">
+        <v>0.9422</v>
+      </c>
+      <c r="AD73" s="2" t="n">
+        <v>0.000318505149166661</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7021,6 +7465,12 @@
       <c r="AB74" s="3" t="n">
         <v>-0.002485501242750693</v>
       </c>
+      <c r="AC74" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7109,6 +7559,12 @@
       <c r="AB75" s="2" t="n">
         <v>0.00248517367975147</v>
       </c>
+      <c r="AC75" s="1" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>-0.001859259676601569</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7197,6 +7653,12 @@
       <c r="AB76" s="3" t="n">
         <v>-0.004535909281814353</v>
       </c>
+      <c r="AC76" s="1" t="n">
+        <v>0.11784</v>
+      </c>
+      <c r="AD76" s="3" t="n">
+        <v>-0.005653531347565639</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7285,6 +7747,12 @@
       <c r="AB77" s="3" t="n">
         <v>-0.00126843190106226</v>
       </c>
+      <c r="AC77" s="1" t="n">
+        <v>0.06295000000000001</v>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>-0.0006350214319733032</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7373,6 +7841,12 @@
       <c r="AB78" s="3" t="n">
         <v>-0.002521803089208827</v>
       </c>
+      <c r="AC78" s="1" t="n">
+        <v>0.09456000000000001</v>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>-0.003897608764352632</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7461,6 +7935,12 @@
       <c r="AB79" s="2" t="n">
         <v>0.004253189892419263</v>
       </c>
+      <c r="AC79" s="1" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7549,6 +8029,12 @@
       <c r="AB80" s="3" t="n">
         <v>-0.00479418085633981</v>
       </c>
+      <c r="AC80" s="1" t="n">
+        <v>0.00601</v>
+      </c>
+      <c r="AD80" s="3" t="n">
+        <v>-0.001661129568106389</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7637,6 +8123,12 @@
       <c r="AB81" s="2" t="n">
         <v>0.004840271055179094</v>
       </c>
+      <c r="AC81" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>-0.00578034682080928</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7725,6 +8217,12 @@
       <c r="AB82" s="3" t="n">
         <v>-0.001968503937007794</v>
       </c>
+      <c r="AC82" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="AD82" s="2" t="n">
+        <v>0.0009861932938856298</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7813,6 +8311,12 @@
       <c r="AB83" s="3" t="n">
         <v>-0.003677646306363944</v>
       </c>
+      <c r="AC83" s="1" t="n">
+        <v>0.06149</v>
+      </c>
+      <c r="AD83" s="3" t="n">
+        <v>-0.01316000641951524</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7901,6 +8405,12 @@
       <c r="AB84" s="3" t="n">
         <v>-0.004451566951566857</v>
       </c>
+      <c r="AC84" s="1" t="n">
+        <v>1.1174</v>
+      </c>
+      <c r="AD84" s="3" t="n">
+        <v>-0.000715435521373756</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7989,6 +8499,12 @@
       <c r="AB85" s="3" t="n">
         <v>-0.005323193916349857</v>
       </c>
+      <c r="AC85" s="1" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="AD85" s="3" t="n">
+        <v>-0.003058103975535176</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8077,6 +8593,12 @@
       <c r="AB86" s="3" t="n">
         <v>-0.005955926146515748</v>
       </c>
+      <c r="AC86" s="1" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="AD86" s="2" t="n">
+        <v>0.002396644697423509</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8165,6 +8687,12 @@
       <c r="AB87" s="3" t="n">
         <v>-0.004310860974733727</v>
       </c>
+      <c r="AC87" s="1" t="n">
+        <v>8.315</v>
+      </c>
+      <c r="AD87" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8253,6 +8781,12 @@
       <c r="AB88" s="3" t="n">
         <v>-0.0002807805699845262</v>
       </c>
+      <c r="AC88" s="1" t="n">
+        <v>2.1443</v>
+      </c>
+      <c r="AD88" s="2" t="n">
+        <v>0.003744792398071435</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8341,6 +8875,12 @@
       <c r="AB89" s="3" t="n">
         <v>-0.006571428571428576</v>
       </c>
+      <c r="AC89" s="1" t="n">
+        <v>0.007017</v>
+      </c>
+      <c r="AD89" s="2" t="n">
+        <v>0.009059534081104355</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8429,6 +8969,12 @@
       <c r="AB90" s="3" t="n">
         <v>-0.001959503592423327</v>
       </c>
+      <c r="AC90" s="1" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AD90" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8517,6 +9063,12 @@
       <c r="AB91" s="3" t="n">
         <v>-0.004464285714285702</v>
       </c>
+      <c r="AC91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="AD91" s="3" t="n">
+        <v>-0.004484304932735414</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8605,6 +9157,12 @@
       <c r="AB92" s="2" t="n">
         <v>0.004024530471445034</v>
       </c>
+      <c r="AC92" s="1" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="AD92" s="2" t="n">
+        <v>0.003054017942355419</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8693,6 +9251,12 @@
       <c r="AB93" s="2" t="n">
         <v>0.0009803182263779932</v>
       </c>
+      <c r="AC93" s="1" t="n">
+        <v>1.3289</v>
+      </c>
+      <c r="AD93" s="2" t="n">
+        <v>0.001130028627391937</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8781,6 +9345,12 @@
       <c r="AB94" s="3" t="n">
         <v>-0.002156642273875118</v>
       </c>
+      <c r="AC94" s="1" t="n">
+        <v>0.054219</v>
+      </c>
+      <c r="AD94" s="2" t="n">
+        <v>0.001570177707171126</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8869,6 +9439,12 @@
       <c r="AB95" s="3" t="n">
         <v>-0.004977187888842831</v>
       </c>
+      <c r="AC95" s="1" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="AD95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8957,6 +9533,12 @@
       <c r="AB96" s="2" t="n">
         <v>0.005122473689112264</v>
       </c>
+      <c r="AC96" s="1" t="n">
+        <v>1.0798</v>
+      </c>
+      <c r="AD96" s="2" t="n">
+        <v>0.000555967383246994</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9045,6 +9627,12 @@
       <c r="AB97" s="3" t="n">
         <v>-0.001938735944164406</v>
       </c>
+      <c r="AC97" s="1" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AD97" s="2" t="n">
+        <v>0.001554001554001383</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9133,6 +9721,12 @@
       <c r="AB98" s="3" t="n">
         <v>-0.005840920803985499</v>
       </c>
+      <c r="AC98" s="1" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="AD98" s="2" t="n">
+        <v>0.004838430965958225</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9221,6 +9815,12 @@
       <c r="AB99" s="3" t="n">
         <v>-0.00439721509710509</v>
       </c>
+      <c r="AC99" s="1" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="AD99" s="3" t="n">
+        <v>-0.00404858299595138</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9309,6 +9909,12 @@
       <c r="AB100" s="2" t="n">
         <v>0.0003219575016097744</v>
       </c>
+      <c r="AC100" s="1" t="n">
+        <v>0.03127</v>
+      </c>
+      <c r="AD100" s="2" t="n">
+        <v>0.00643707756678464</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9397,6 +10003,12 @@
       <c r="AB101" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC101" s="1" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="AD101" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9485,6 +10097,12 @@
       <c r="AB102" s="2" t="n">
         <v>0.003623188405797111</v>
       </c>
+      <c r="AC102" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="AD102" s="2" t="n">
+        <v>0.001805054151624632</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9573,6 +10191,12 @@
       <c r="AB103" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC103" s="1" t="n">
+        <v>0.01961</v>
+      </c>
+      <c r="AD103" s="3" t="n">
+        <v>-0.001018848700968041</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9661,6 +10285,12 @@
       <c r="AB104" s="3" t="n">
         <v>-0.004973474801061049</v>
       </c>
+      <c r="AC104" s="1" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="AD104" s="2" t="n">
+        <v>0.001332889036987672</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9749,6 +10379,12 @@
       <c r="AB105" s="3" t="n">
         <v>-0.001839926402943952</v>
       </c>
+      <c r="AC105" s="1" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="AD105" s="3" t="n">
+        <v>-0.001228878648233461</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9837,6 +10473,12 @@
       <c r="AB106" s="3" t="n">
         <v>-0.007202881152461024</v>
       </c>
+      <c r="AC106" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="AD106" s="3" t="n">
+        <v>-0.001209189842805187</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9925,6 +10567,12 @@
       <c r="AB107" s="3" t="n">
         <v>-0.01161040636422278</v>
       </c>
+      <c r="AC107" s="1" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="AD107" s="3" t="n">
+        <v>-0.01392212312377641</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10013,6 +10661,12 @@
       <c r="AB108" s="3" t="n">
         <v>-0.005619639160011868</v>
       </c>
+      <c r="AC108" s="1" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AD108" s="2" t="n">
+        <v>0.00208209399167156</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10101,6 +10755,12 @@
       <c r="AB109" s="3" t="n">
         <v>-0.004830917874396212</v>
       </c>
+      <c r="AC109" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AD109" s="2" t="n">
+        <v>0.006178287731685845</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10189,6 +10849,12 @@
       <c r="AB110" s="2" t="n">
         <v>0.001328903654485111</v>
       </c>
+      <c r="AC110" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="AD110" s="2" t="n">
+        <v>0.002654280026542807</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10277,6 +10943,12 @@
       <c r="AB111" s="3" t="n">
         <v>-0.003253796095444688</v>
       </c>
+      <c r="AC111" s="1" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="AD111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10365,6 +11037,12 @@
       <c r="AB112" s="3" t="n">
         <v>-0.003396029258098176</v>
       </c>
+      <c r="AC112" s="1" t="n">
+        <v>0.03813</v>
+      </c>
+      <c r="AD112" s="3" t="n">
+        <v>-0.0005242463958061893</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10453,6 +11131,12 @@
       <c r="AB113" s="3" t="n">
         <v>-0.00162639405204474</v>
       </c>
+      <c r="AC113" s="1" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="AD113" s="3" t="n">
+        <v>-0.006050733069583384</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10541,6 +11225,12 @@
       <c r="AB114" s="2" t="n">
         <v>0.01225359616409165</v>
       </c>
+      <c r="AC114" s="1" t="n">
+        <v>0.007592</v>
+      </c>
+      <c r="AD114" s="3" t="n">
+        <v>-0.001052631578947394</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10629,6 +11319,12 @@
       <c r="AB115" s="2" t="n">
         <v>0.002999700029996947</v>
       </c>
+      <c r="AC115" s="1" t="n">
+        <v>0.10064</v>
+      </c>
+      <c r="AD115" s="2" t="n">
+        <v>0.00328980161499349</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10717,6 +11413,12 @@
       <c r="AB116" s="3" t="n">
         <v>-0.003600576092174851</v>
       </c>
+      <c r="AC116" s="1" t="n">
+        <v>0.08312</v>
+      </c>
+      <c r="AD116" s="2" t="n">
+        <v>0.001204529029149637</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10805,6 +11507,12 @@
       <c r="AB117" s="3" t="n">
         <v>-0.003661784287616477</v>
       </c>
+      <c r="AC117" s="1" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AD117" s="2" t="n">
+        <v>0.00200467758102235</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10893,6 +11601,12 @@
       <c r="AB118" s="3" t="n">
         <v>-0.00530035335689055</v>
       </c>
+      <c r="AC118" s="1" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="AD118" s="3" t="n">
+        <v>-0.001776198934280567</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10981,6 +11695,12 @@
       <c r="AB119" s="3" t="n">
         <v>-0.004533678756476723</v>
       </c>
+      <c r="AC119" s="1" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="AD119" s="3" t="n">
+        <v>-0.009759271307742364</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11069,6 +11789,12 @@
       <c r="AB120" s="3" t="n">
         <v>-0.004519774011299446</v>
       </c>
+      <c r="AC120" s="1" t="n">
+        <v>0.004542</v>
+      </c>
+      <c r="AD120" s="2" t="n">
+        <v>0.03110102156640181</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11157,6 +11883,12 @@
       <c r="AB121" s="2" t="n">
         <v>0.004803293687099832</v>
       </c>
+      <c r="AC121" s="1" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="AD121" s="3" t="n">
+        <v>-0.01001593444115642</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11245,6 +11977,12 @@
       <c r="AB122" s="3" t="n">
         <v>-0.002570694087403601</v>
       </c>
+      <c r="AC122" s="1" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AD122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11333,6 +12071,12 @@
       <c r="AB123" s="3" t="n">
         <v>-0.004608294930875548</v>
       </c>
+      <c r="AC123" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="AD123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11421,6 +12165,12 @@
       <c r="AB124" s="3" t="n">
         <v>-0.0008136696501221584</v>
       </c>
+      <c r="AC124" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="AD124" s="2" t="n">
+        <v>0.003257328990228022</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11509,6 +12259,12 @@
       <c r="AB125" s="3" t="n">
         <v>-0.002042900919305472</v>
       </c>
+      <c r="AC125" s="1" t="n">
+        <v>0.09778000000000001</v>
+      </c>
+      <c r="AD125" s="2" t="n">
+        <v>0.0008188331627431998</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11597,6 +12353,12 @@
       <c r="AB126" s="2" t="n">
         <v>0.002348420153714752</v>
       </c>
+      <c r="AC126" s="1" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="AD126" s="3" t="n">
+        <v>-0.001916932907348239</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11685,6 +12447,12 @@
       <c r="AB127" s="3" t="n">
         <v>-0.003086419753086495</v>
       </c>
+      <c r="AC127" s="1" t="n">
+        <v>3.21e-05</v>
+      </c>
+      <c r="AD127" s="3" t="n">
+        <v>-0.006191950464396225</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11773,6 +12541,12 @@
       <c r="AB128" s="3" t="n">
         <v>-0.002812445069432123</v>
       </c>
+      <c r="AC128" s="1" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="AD128" s="3" t="n">
+        <v>-0.0008813678829544437</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11861,6 +12635,12 @@
       <c r="AB129" s="3" t="n">
         <v>-0.00077160493827152</v>
       </c>
+      <c r="AC129" s="1" t="n">
+        <v>0.06465</v>
+      </c>
+      <c r="AD129" s="3" t="n">
+        <v>-0.001544401544401589</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11949,6 +12729,12 @@
       <c r="AB130" s="3" t="n">
         <v>-0.002452984464431696</v>
       </c>
+      <c r="AC130" s="1" t="n">
+        <v>0.0006079</v>
+      </c>
+      <c r="AD130" s="3" t="n">
+        <v>-0.003442622950819667</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12037,6 +12823,12 @@
       <c r="AB131" s="3" t="n">
         <v>-0.01136363636363637</v>
       </c>
+      <c r="AC131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AD131" s="2" t="n">
+        <v>0.01149425287356323</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12125,6 +12917,12 @@
       <c r="AB132" s="3" t="n">
         <v>-0.004952129415648734</v>
       </c>
+      <c r="AC132" s="1" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AD132" s="3" t="n">
+        <v>-0.002654280026542876</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12213,6 +13011,12 @@
       <c r="AB133" s="3" t="n">
         <v>-0.005010315355143044</v>
       </c>
+      <c r="AC133" s="1" t="n">
+        <v>0.03387</v>
+      </c>
+      <c r="AD133" s="2" t="n">
+        <v>0.00325829383886253</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12301,6 +13105,12 @@
       <c r="AB134" s="2" t="n">
         <v>0.001949724949516068</v>
       </c>
+      <c r="AC134" s="1" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="AD134" s="2" t="n">
+        <v>0.002015428452290031</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12389,6 +13199,12 @@
       <c r="AB135" s="3" t="n">
         <v>-0.005700871898054997</v>
       </c>
+      <c r="AC135" s="1" t="n">
+        <v>0.02964</v>
+      </c>
+      <c r="AD135" s="3" t="n">
+        <v>-0.000337268128161875</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12477,6 +13293,12 @@
       <c r="AB136" s="3" t="n">
         <v>-0.002479631597591225</v>
       </c>
+      <c r="AC136" s="1" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AD136" s="2" t="n">
+        <v>0.00284090909090903</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12565,6 +13387,12 @@
       <c r="AB137" s="3" t="n">
         <v>-0.003635537377868754</v>
       </c>
+      <c r="AC137" s="1" t="n">
+        <v>0.0004372</v>
+      </c>
+      <c r="AD137" s="3" t="n">
+        <v>-0.002964652223489116</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12653,6 +13481,12 @@
       <c r="AB138" s="3" t="n">
         <v>-0.01305660121409434</v>
       </c>
+      <c r="AC138" s="1" t="n">
+        <v>0.028982</v>
+      </c>
+      <c r="AD138" s="3" t="n">
+        <v>-0.004123427943096646</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12741,6 +13575,12 @@
       <c r="AB139" s="3" t="n">
         <v>-0.003828642384106055</v>
       </c>
+      <c r="AC139" s="1" t="n">
+        <v>0.09653</v>
+      </c>
+      <c r="AD139" s="2" t="n">
+        <v>0.002700737509089127</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12829,6 +13669,12 @@
       <c r="AB140" s="3" t="n">
         <v>-0.003046247576848491</v>
       </c>
+      <c r="AC140" s="1" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AD140" s="2" t="n">
+        <v>0.003611111111111176</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12917,6 +13763,12 @@
       <c r="AB141" s="3" t="n">
         <v>-0.0003795066413662085</v>
       </c>
+      <c r="AC141" s="1" t="n">
+        <v>0.02648</v>
+      </c>
+      <c r="AD141" s="2" t="n">
+        <v>0.005315110098709235</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13005,6 +13857,12 @@
       <c r="AB142" s="2" t="n">
         <v>0.0002518891687658202</v>
       </c>
+      <c r="AC142" s="1" t="n">
+        <v>0.07944</v>
+      </c>
+      <c r="AD142" s="2" t="n">
+        <v>0.0002518257365901819</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13093,6 +13951,12 @@
       <c r="AB143" s="3" t="n">
         <v>-0.006894992652876675</v>
       </c>
+      <c r="AC143" s="1" t="n">
+        <v>0.08807</v>
+      </c>
+      <c r="AD143" s="2" t="n">
+        <v>0.002390166173457795</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13181,6 +14045,12 @@
       <c r="AB144" s="2" t="n">
         <v>0.0009689922480621442</v>
       </c>
+      <c r="AC144" s="1" t="n">
+        <v>0.02047</v>
+      </c>
+      <c r="AD144" s="3" t="n">
+        <v>-0.0091965150048404</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13269,6 +14139,12 @@
       <c r="AB145" s="2" t="n">
         <v>0.00130707563611012</v>
       </c>
+      <c r="AC145" s="1" t="n">
+        <v>0.11432</v>
+      </c>
+      <c r="AD145" s="3" t="n">
+        <v>-0.005134453050213152</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13357,6 +14233,12 @@
       <c r="AB146" s="3" t="n">
         <v>-0.002635914332784077</v>
       </c>
+      <c r="AC146" s="1" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AD146" s="3" t="n">
+        <v>-0.0003303600925009729</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13445,6 +14327,12 @@
       <c r="AB147" s="2" t="n">
         <v>0.008130081300813016</v>
       </c>
+      <c r="AC147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AD147" s="3" t="n">
+        <v>-0.008064516129032265</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13533,6 +14421,12 @@
       <c r="AB148" s="3" t="n">
         <v>-0.0009670195439739479</v>
       </c>
+      <c r="AC148" s="1" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="AD148" s="2" t="n">
+        <v>0.001069845636558149</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13621,6 +14515,12 @@
       <c r="AB149" s="3" t="n">
         <v>-0.0003242542153047858</v>
       </c>
+      <c r="AC149" s="1" t="n">
+        <v>0.06176</v>
+      </c>
+      <c r="AD149" s="2" t="n">
+        <v>0.001621796951021778</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13709,6 +14609,12 @@
       <c r="AB150" s="2" t="n">
         <v>0.00123533045089565</v>
       </c>
+      <c r="AC150" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="AD150" s="2" t="n">
+        <v>0.005552128315854485</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13797,6 +14703,12 @@
       <c r="AB151" s="3" t="n">
         <v>-0.002970885323826573</v>
       </c>
+      <c r="AC151" s="1" t="n">
+        <v>6.719999999999999e-05</v>
+      </c>
+      <c r="AD151" s="2" t="n">
+        <v>0.001191895113230024</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13885,6 +14797,12 @@
       <c r="AB152" s="3" t="n">
         <v>-0.006724949562878238</v>
       </c>
+      <c r="AC152" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="AD152" s="3" t="n">
+        <v>-0.006770480704129952</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13973,6 +14891,12 @@
       <c r="AB153" s="3" t="n">
         <v>-0.004261363636363627</v>
       </c>
+      <c r="AC153" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="AD153" s="2" t="n">
+        <v>0.001902044698050327</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14061,6 +14985,12 @@
       <c r="AB154" s="3" t="n">
         <v>-0.003355704697986477</v>
       </c>
+      <c r="AC154" s="1" t="n">
+        <v>0.0005943</v>
+      </c>
+      <c r="AD154" s="2" t="n">
+        <v>0.000505050505050426</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14149,6 +15079,12 @@
       <c r="AB155" s="3" t="n">
         <v>-0.003227408142999134</v>
       </c>
+      <c r="AC155" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="AD155" s="2" t="n">
+        <v>0.001494396014944072</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14237,6 +15173,12 @@
       <c r="AB156" s="2" t="n">
         <v>0.000526870389884067</v>
       </c>
+      <c r="AC156" s="1" t="n">
+        <v>0.01895</v>
+      </c>
+      <c r="AD156" s="3" t="n">
+        <v>-0.002106371774618135</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14325,6 +15267,12 @@
       <c r="AB157" s="3" t="n">
         <v>-0.005010248235026145</v>
       </c>
+      <c r="AC157" s="1" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AD157" s="3" t="n">
+        <v>-0.004806591897459416</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14413,6 +15361,12 @@
       <c r="AB158" s="3" t="n">
         <v>-0.007683215130023738</v>
       </c>
+      <c r="AC158" s="1" t="n">
+        <v>0.008411999999999999</v>
+      </c>
+      <c r="AD158" s="2" t="n">
+        <v>0.002025014889815325</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14501,6 +15455,12 @@
       <c r="AB159" s="3" t="n">
         <v>-0.003574265289912588</v>
       </c>
+      <c r="AC159" s="1" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="AD159" s="2" t="n">
+        <v>0.001992825827022676</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14589,6 +15549,12 @@
       <c r="AB160" s="3" t="n">
         <v>-0.002253827621046011</v>
       </c>
+      <c r="AC160" s="1" t="n">
+        <v>1.2834</v>
+      </c>
+      <c r="AD160" s="3" t="n">
+        <v>-0.0003115750116840286</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14677,6 +15643,12 @@
       <c r="AB161" s="2" t="n">
         <v>0.0003996270147862526</v>
       </c>
+      <c r="AC161" s="1" t="n">
+        <v>0.007538</v>
+      </c>
+      <c r="AD161" s="2" t="n">
+        <v>0.003728362183755026</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14765,6 +15737,12 @@
       <c r="AB162" s="3" t="n">
         <v>-0.0009811135638949384</v>
       </c>
+      <c r="AC162" s="1" t="n">
+        <v>0.004108</v>
+      </c>
+      <c r="AD162" s="2" t="n">
+        <v>0.008593174564203152</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14853,6 +15831,12 @@
       <c r="AB163" s="3" t="n">
         <v>-0.004145077720207229</v>
       </c>
+      <c r="AC163" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="AD163" s="2" t="n">
+        <v>0.006243496357960347</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14941,6 +15925,12 @@
       <c r="AB164" s="3" t="n">
         <v>-0.003315315315315271</v>
       </c>
+      <c r="AC164" s="1" t="n">
+        <v>1.3821</v>
+      </c>
+      <c r="AD164" s="3" t="n">
+        <v>-0.0005784944681465846</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15029,6 +16019,12 @@
       <c r="AB165" s="3" t="n">
         <v>-0.00310859063222017</v>
       </c>
+      <c r="AC165" s="1" t="n">
+        <v>0.023607</v>
+      </c>
+      <c r="AD165" s="3" t="n">
+        <v>-0.005225232817833177</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15117,6 +16113,12 @@
       <c r="AB166" s="2" t="n">
         <v>0.002529675034053316</v>
       </c>
+      <c r="AC166" s="1" t="n">
+        <v>0.005149</v>
+      </c>
+      <c r="AD166" s="3" t="n">
+        <v>-0.0005822981366460399</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15205,6 +16207,12 @@
       <c r="AB167" s="3" t="n">
         <v>-0.00726172465960678</v>
       </c>
+      <c r="AC167" s="1" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="AD167" s="3" t="n">
+        <v>-0.0003047851264857093</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15293,6 +16301,12 @@
       <c r="AB168" s="3" t="n">
         <v>-0.001042752867570416</v>
       </c>
+      <c r="AC168" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AD168" s="3" t="n">
+        <v>-0.002087682672233736</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15381,6 +16395,12 @@
       <c r="AB169" s="2" t="n">
         <v>0.004677754677754668</v>
       </c>
+      <c r="AC169" s="1" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AD169" s="3" t="n">
+        <v>-0.003879979306776962</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15469,6 +16489,12 @@
       <c r="AB170" s="3" t="n">
         <v>-0.003492107836290084</v>
       </c>
+      <c r="AC170" s="1" t="n">
+        <v>0.007135</v>
+      </c>
+      <c r="AD170" s="2" t="n">
+        <v>0.0001401738155312774</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15557,6 +16583,12 @@
       <c r="AB171" s="3" t="n">
         <v>-0.003222026947861716</v>
       </c>
+      <c r="AC171" s="1" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AD171" s="3" t="n">
+        <v>-0.00146929180135175</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15645,6 +16677,12 @@
       <c r="AB172" s="3" t="n">
         <v>-0.001280409731113897</v>
       </c>
+      <c r="AC172" s="1" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AD172" s="2" t="n">
+        <v>0.001831501831501792</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15733,6 +16771,12 @@
       <c r="AB173" s="3" t="n">
         <v>-0.003056768558951992</v>
       </c>
+      <c r="AC173" s="1" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="AD173" s="2" t="n">
+        <v>0.001314060446780498</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15821,6 +16865,12 @@
       <c r="AB174" s="3" t="n">
         <v>-0.00153022188217303</v>
       </c>
+      <c r="AC174" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="AD174" s="2" t="n">
+        <v>0.001277139208173728</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15909,6 +16959,12 @@
       <c r="AB175" s="2" t="n">
         <v>0.006064930431680374</v>
       </c>
+      <c r="AC175" s="1" t="n">
+        <v>0.005595</v>
+      </c>
+      <c r="AD175" s="3" t="n">
+        <v>-0.007978723404255301</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15997,6 +17053,12 @@
       <c r="AB176" s="3" t="n">
         <v>-0.003957783641160903</v>
       </c>
+      <c r="AC176" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="AD176" s="3" t="n">
+        <v>-0.001324503311258339</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16085,6 +17147,12 @@
       <c r="AB177" s="2" t="n">
         <v>0.001682557487380883</v>
       </c>
+      <c r="AC177" s="1" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="AD177" s="2" t="n">
+        <v>0.01063829787234037</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16173,6 +17241,12 @@
       <c r="AB178" s="3" t="n">
         <v>-0.004128556910569074</v>
       </c>
+      <c r="AC178" s="1" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="AD178" s="2" t="n">
+        <v>0.00325275846673896</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16261,6 +17335,12 @@
       <c r="AB179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC179" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AD179" s="2" t="n">
+        <v>0.003184713375796181</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16349,6 +17429,12 @@
       <c r="AB180" s="2" t="n">
         <v>0.008667278474558882</v>
       </c>
+      <c r="AC180" s="1" t="n">
+        <v>0.09804</v>
+      </c>
+      <c r="AD180" s="3" t="n">
+        <v>-0.008896077638495673</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16437,6 +17523,12 @@
       <c r="AB181" s="3" t="n">
         <v>-0.004774535809018631</v>
       </c>
+      <c r="AC181" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="AD181" s="2" t="n">
+        <v>0.002665245202558638</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16525,6 +17617,12 @@
       <c r="AB182" s="3" t="n">
         <v>-0.001011463250168536</v>
       </c>
+      <c r="AC182" s="1" t="n">
+        <v>0.05953</v>
+      </c>
+      <c r="AD182" s="2" t="n">
+        <v>0.004556193047586895</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16613,6 +17711,12 @@
       <c r="AB183" s="3" t="n">
         <v>-0.0008333333333332993</v>
       </c>
+      <c r="AC183" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="AD183" s="2" t="n">
+        <v>0.002502085070892308</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16701,6 +17805,12 @@
       <c r="AB184" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC184" s="1" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="AD184" s="3" t="n">
+        <v>-0.0004655493482308936</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16789,6 +17899,12 @@
       <c r="AB185" s="3" t="n">
         <v>-0.005434782608695657</v>
       </c>
+      <c r="AC185" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AD185" s="2" t="n">
+        <v>0.002732240437158473</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16877,6 +17993,12 @@
       <c r="AB186" s="3" t="n">
         <v>-0.002614720878546222</v>
       </c>
+      <c r="AC186" s="1" t="n">
+        <v>0.007622</v>
+      </c>
+      <c r="AD186" s="3" t="n">
+        <v>-0.0009175514484205088</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16965,6 +18087,12 @@
       <c r="AB187" s="3" t="n">
         <v>-0.006270748801180504</v>
       </c>
+      <c r="AC187" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD187" s="2" t="n">
+        <v>0.002227171492205067</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17053,6 +18181,12 @@
       <c r="AB188" s="3" t="n">
         <v>-0.00485240598463399</v>
       </c>
+      <c r="AC188" s="1" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="AD188" s="2" t="n">
+        <v>0.001219016659894302</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17141,6 +18275,12 @@
       <c r="AB189" s="3" t="n">
         <v>-0.006235385814497235</v>
       </c>
+      <c r="AC189" s="1" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AD189" s="2" t="n">
+        <v>0.001960784313725492</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17229,6 +18369,12 @@
       <c r="AB190" s="2" t="n">
         <v>0.003506926179203931</v>
       </c>
+      <c r="AC190" s="1" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="AD190" s="3" t="n">
+        <v>-0.001397868250917391</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17317,6 +18463,12 @@
       <c r="AB191" s="3" t="n">
         <v>-0.004950495049504846</v>
       </c>
+      <c r="AC191" s="1" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AD191" s="2" t="n">
+        <v>0.001658374792703115</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17405,6 +18557,12 @@
       <c r="AB192" s="3" t="n">
         <v>-0.004847447961220515</v>
       </c>
+      <c r="AC192" s="1" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="AD192" s="2" t="n">
+        <v>0.0005730659025788926</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -17493,6 +18651,12 @@
       <c r="AB193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC193" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AD193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17581,6 +18745,12 @@
       <c r="AB194" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC194" s="1" t="n">
+        <v>0.01721</v>
+      </c>
+      <c r="AD194" s="3" t="n">
+        <v>-0.00347423277359589</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17669,6 +18839,12 @@
       <c r="AB195" s="2" t="n">
         <v>0.0008260561718196398</v>
       </c>
+      <c r="AC195" s="1" t="n">
+        <v>0.0008522</v>
+      </c>
+      <c r="AD195" s="2" t="n">
+        <v>0.004834335573635239</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17757,6 +18933,12 @@
       <c r="AB196" s="3" t="n">
         <v>-0.0133715377268385</v>
       </c>
+      <c r="AC196" s="1" t="n">
+        <v>0.001038</v>
+      </c>
+      <c r="AD196" s="2" t="n">
+        <v>0.004840271055179103</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17845,6 +19027,12 @@
       <c r="AB197" s="3" t="n">
         <v>-0.002467612584824243</v>
       </c>
+      <c r="AC197" s="1" t="n">
+        <v>0.0001621</v>
+      </c>
+      <c r="AD197" s="2" t="n">
+        <v>0.002473716759431105</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17933,6 +19121,12 @@
       <c r="AB198" s="3" t="n">
         <v>-0.00092208390963588</v>
       </c>
+      <c r="AC198" s="1" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AD198" s="2" t="n">
+        <v>0.0002307337332718814</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18021,6 +19215,12 @@
       <c r="AB199" s="3" t="n">
         <v>-0.003065603923973025</v>
       </c>
+      <c r="AC199" s="1" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="AD199" s="2" t="n">
+        <v>0.004920049200491976</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18109,6 +19309,12 @@
       <c r="AB200" s="3" t="n">
         <v>-0.0006948666724573145</v>
       </c>
+      <c r="AC200" s="1" t="n">
+        <v>0.023152</v>
+      </c>
+      <c r="AD200" s="2" t="n">
+        <v>0.00617122990004345</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18197,6 +19403,12 @@
       <c r="AB201" s="3" t="n">
         <v>-0.004351680232089715</v>
       </c>
+      <c r="AC201" s="1" t="n">
+        <v>0.12366</v>
+      </c>
+      <c r="AD201" s="2" t="n">
+        <v>0.0008903278025092098</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18285,6 +19497,12 @@
       <c r="AB202" s="2" t="n">
         <v>0.002152080344332892</v>
       </c>
+      <c r="AC202" s="1" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AD202" s="3" t="n">
+        <v>-0.005010737294201905</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18373,6 +19591,12 @@
       <c r="AB203" s="3" t="n">
         <v>-0.005093378607809892</v>
       </c>
+      <c r="AC203" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AD203" s="3" t="n">
+        <v>-0.0004875670404680445</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18461,6 +19685,12 @@
       <c r="AB204" s="3" t="n">
         <v>-0.005392912172573237</v>
       </c>
+      <c r="AC204" s="1" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="AD204" s="2" t="n">
+        <v>0.003098373353989164</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18549,6 +19779,12 @@
       <c r="AB205" s="3" t="n">
         <v>-0.00324299281908723</v>
       </c>
+      <c r="AC205" s="1" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="AD205" s="2" t="n">
+        <v>0.002556356030676249</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18637,6 +19873,12 @@
       <c r="AB206" s="3" t="n">
         <v>-0.009602793539938955</v>
       </c>
+      <c r="AC206" s="1" t="n">
+        <v>0.02272</v>
+      </c>
+      <c r="AD206" s="2" t="n">
+        <v>0.00132216835610411</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18725,6 +19967,12 @@
       <c r="AB207" s="3" t="n">
         <v>-0.002862595419847437</v>
       </c>
+      <c r="AC207" s="1" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AD207" s="2" t="n">
+        <v>0.002392344497607817</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18813,6 +20061,12 @@
       <c r="AB208" s="3" t="n">
         <v>-0.001897276053665825</v>
       </c>
+      <c r="AC208" s="1" t="n">
+        <v>0.07369000000000001</v>
+      </c>
+      <c r="AD208" s="2" t="n">
+        <v>0.0005431093007469416</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18901,6 +20155,12 @@
       <c r="AB209" s="2" t="n">
         <v>0.001424501424501531</v>
       </c>
+      <c r="AC209" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="AD209" s="2" t="n">
+        <v>0.0007112375533427052</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18989,6 +20249,12 @@
       <c r="AB210" s="3" t="n">
         <v>-0.003769520732364061</v>
       </c>
+      <c r="AC210" s="1" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="AD210" s="2" t="n">
+        <v>0.001621621621621593</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19077,6 +20343,12 @@
       <c r="AB211" s="2" t="n">
         <v>0.001271725307333593</v>
       </c>
+      <c r="AC211" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="AD211" s="2" t="n">
+        <v>0.005503810330228601</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -19165,6 +20437,12 @@
       <c r="AB212" s="3" t="n">
         <v>-0.002400384061449942</v>
       </c>
+      <c r="AC212" s="1" t="n">
+        <v>0.002128</v>
+      </c>
+      <c r="AD212" s="2" t="n">
+        <v>0.02406159769008669</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -19253,6 +20531,12 @@
       <c r="AB213" s="3" t="n">
         <v>-0.003215434083601289</v>
       </c>
+      <c r="AC213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AD213" s="3" t="n">
+        <v>-0.001075268817204302</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -19341,6 +20625,12 @@
       <c r="AB214" s="3" t="n">
         <v>-0.001923749562784142</v>
       </c>
+      <c r="AC214" s="1" t="n">
+        <v>0.005742</v>
+      </c>
+      <c r="AD214" s="2" t="n">
+        <v>0.006132819344664349</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19429,6 +20719,12 @@
       <c r="AB215" s="3" t="n">
         <v>-0.002919708029197088</v>
       </c>
+      <c r="AC215" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="AD215" s="2" t="n">
+        <v>0.0007320644216690771</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -19517,6 +20813,12 @@
       <c r="AB216" s="3" t="n">
         <v>-0.003159557661927202</v>
       </c>
+      <c r="AC216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AD216" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -19605,6 +20907,12 @@
       <c r="AB217" s="3" t="n">
         <v>-0.002150537634408664</v>
       </c>
+      <c r="AC217" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AD217" s="2" t="n">
+        <v>0.002155172413793165</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -19693,6 +21001,12 @@
       <c r="AB218" s="2" t="n">
         <v>0.003096086690427231</v>
       </c>
+      <c r="AC218" s="1" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="AD218" s="2" t="n">
+        <v>0.001722714711265966</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19781,6 +21095,12 @@
       <c r="AB219" s="3" t="n">
         <v>-0.003353658536585282</v>
       </c>
+      <c r="AC219" s="1" t="n">
+        <v>0.003283</v>
+      </c>
+      <c r="AD219" s="2" t="n">
+        <v>0.004282655246252581</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19869,6 +21189,12 @@
       <c r="AB220" s="2" t="n">
         <v>1.00062739340442e-06</v>
       </c>
+      <c r="AC220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="AD220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -19957,6 +21283,12 @@
       <c r="AB221" s="3" t="n">
         <v>-0.01403061224489801</v>
       </c>
+      <c r="AC221" s="1" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="AD221" s="2" t="n">
+        <v>0.002328589909443721</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -20045,6 +21377,12 @@
       <c r="AB222" s="3" t="n">
         <v>-0.003418803418803427</v>
       </c>
+      <c r="AC222" s="1" t="n">
+        <v>0.04677</v>
+      </c>
+      <c r="AD222" s="2" t="n">
+        <v>0.002787307032590012</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -20133,6 +21471,12 @@
       <c r="AB223" s="3" t="n">
         <v>-0.001886792452830112</v>
       </c>
+      <c r="AC223" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="AD223" s="2" t="n">
+        <v>0.003780718336483909</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -20221,6 +21565,12 @@
       <c r="AB224" s="2" t="n">
         <v>0.007397959183673448</v>
       </c>
+      <c r="AC224" s="1" t="n">
+        <v>3.946</v>
+      </c>
+      <c r="AD224" s="3" t="n">
+        <v>-0.000759685996454715</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -20309,6 +21659,12 @@
       <c r="AB225" s="2" t="n">
         <v>0.0007560211685926805</v>
       </c>
+      <c r="AC225" s="1" t="n">
+        <v>0.0009272</v>
+      </c>
+      <c r="AD225" s="2" t="n">
+        <v>0.0006475285991798128</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -20397,6 +21753,12 @@
       <c r="AB226" s="3" t="n">
         <v>-0.009333800023334523</v>
       </c>
+      <c r="AC226" s="1" t="n">
+        <v>0.008496</v>
+      </c>
+      <c r="AD226" s="2" t="n">
+        <v>0.0005888587916617355</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -20485,6 +21847,12 @@
       <c r="AB227" s="3" t="n">
         <v>-0.001687153530971333</v>
       </c>
+      <c r="AC227" s="1" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="AD227" s="3" t="n">
+        <v>-0.004828585224529184</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20573,6 +21941,12 @@
       <c r="AB228" s="3" t="n">
         <v>-0.003085553997194923</v>
       </c>
+      <c r="AC228" s="1" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="AD228" s="2" t="n">
+        <v>0.001969611705121008</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -20661,6 +22035,12 @@
       <c r="AB229" s="3" t="n">
         <v>-0.004238104411481371</v>
       </c>
+      <c r="AC229" s="1" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="AD229" s="2" t="n">
+        <v>0.00309537628167925</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20749,6 +22129,12 @@
       <c r="AB230" s="3" t="n">
         <v>-0.002292263610315242</v>
       </c>
+      <c r="AC230" s="1" t="n">
+        <v>0.001741</v>
+      </c>
+      <c r="AD230" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20837,6 +22223,12 @@
       <c r="AB231" s="2" t="n">
         <v>0.004323656578134546</v>
       </c>
+      <c r="AC231" s="1" t="n">
+        <v>0.04868</v>
+      </c>
+      <c r="AD231" s="3" t="n">
+        <v>-0.002050020500204919</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20925,6 +22317,12 @@
       <c r="AB232" s="3" t="n">
         <v>-0.004109589041095881</v>
       </c>
+      <c r="AC232" s="1" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="AD232" s="3" t="n">
+        <v>-0.003668042182485108</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -21013,6 +22411,12 @@
       <c r="AB233" s="2" t="n">
         <v>0.0008490405841400346</v>
       </c>
+      <c r="AC233" s="1" t="n">
+        <v>0.0005899</v>
+      </c>
+      <c r="AD233" s="2" t="n">
+        <v>0.0008483203257549337</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -21101,6 +22505,12 @@
       <c r="AB234" s="3" t="n">
         <v>-0.005927572473835341</v>
       </c>
+      <c r="AC234" s="1" t="n">
+        <v>0.21396</v>
+      </c>
+      <c r="AD234" s="3" t="n">
+        <v>-0.003260970837603552</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -21189,6 +22599,12 @@
       <c r="AB235" s="2" t="n">
         <v>0.01847903340440665</v>
       </c>
+      <c r="AC235" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="AD235" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -21277,6 +22693,12 @@
       <c r="AB236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC236" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AD236" s="2" t="n">
+        <v>0.002409638554216769</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -21365,6 +22787,12 @@
       <c r="AB237" s="3" t="n">
         <v>-0.004773269689737483</v>
       </c>
+      <c r="AC237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="AD237" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -21453,6 +22881,12 @@
       <c r="AB238" s="2" t="n">
         <v>0.008032128514056316</v>
       </c>
+      <c r="AC238" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="AD238" s="2" t="n">
+        <v>0.003984063745019896</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -21541,6 +22975,12 @@
       <c r="AB239" s="2" t="n">
         <v>0.001332445036642184</v>
       </c>
+      <c r="AC239" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AD239" s="2" t="n">
+        <v>0.00332667997338654</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -21629,6 +23069,12 @@
       <c r="AB240" s="2" t="n">
         <v>0.003810975609756052</v>
       </c>
+      <c r="AC240" s="1" t="n">
+        <v>0.0003948</v>
+      </c>
+      <c r="AD240" s="3" t="n">
+        <v>-0.0007593014426727595</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -21717,6 +23163,12 @@
       <c r="AB241" s="2" t="n">
         <v>0.003713330857779432</v>
       </c>
+      <c r="AC241" s="1" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="AD241" s="2" t="n">
+        <v>0.004809470958194686</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -21805,6 +23257,12 @@
       <c r="AB242" s="2" t="n">
         <v>0.006037537734610869</v>
       </c>
+      <c r="AC242" s="1" t="n">
+        <v>0.07650999999999999</v>
+      </c>
+      <c r="AD242" s="3" t="n">
+        <v>-0.001826484018264856</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -21893,6 +23351,12 @@
       <c r="AB243" s="3" t="n">
         <v>-0.006480558325025007</v>
       </c>
+      <c r="AC243" s="1" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="AD243" s="2" t="n">
+        <v>0.001003512293025549</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -21981,6 +23445,12 @@
       <c r="AB244" s="3" t="n">
         <v>-0.008687594115602926</v>
       </c>
+      <c r="AC244" s="1" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="AD244" s="3" t="n">
+        <v>-0.003622341668614217</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -22069,6 +23539,12 @@
       <c r="AB245" s="3" t="n">
         <v>-0.000625782227784662</v>
       </c>
+      <c r="AC245" s="1" t="n">
+        <v>1.4321</v>
+      </c>
+      <c r="AD245" s="3" t="n">
+        <v>-0.003617894663605436</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -22157,6 +23633,12 @@
       <c r="AB246" s="3" t="n">
         <v>-0.004461795872838829</v>
       </c>
+      <c r="AC246" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="AD246" s="3" t="n">
+        <v>-0.0005602240896358314</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22245,6 +23727,12 @@
       <c r="AB247" s="3" t="n">
         <v>-0.004374057315233712</v>
       </c>
+      <c r="AC247" s="1" t="n">
+        <v>0.006614</v>
+      </c>
+      <c r="AD247" s="2" t="n">
+        <v>0.001969398575973336</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -22333,6 +23821,12 @@
       <c r="AB248" s="3" t="n">
         <v>-0.009903381642511927</v>
       </c>
+      <c r="AC248" s="1" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="AD248" s="3" t="n">
+        <v>-0.004635276896804079</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -22421,6 +23915,12 @@
       <c r="AB249" s="2" t="n">
         <v>0.0009074410163338383</v>
       </c>
+      <c r="AC249" s="1" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="AD249" s="2" t="n">
+        <v>0.00362647325475985</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -22509,6 +24009,12 @@
       <c r="AB250" s="3" t="n">
         <v>-0.0005787037037036801</v>
       </c>
+      <c r="AC250" s="1" t="n">
+        <v>0.03462</v>
+      </c>
+      <c r="AD250" s="2" t="n">
+        <v>0.002316155182397126</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -22597,6 +24103,12 @@
       <c r="AB251" s="3" t="n">
         <v>-0.00464468183929398</v>
       </c>
+      <c r="AC251" s="1" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="AD251" s="3" t="n">
+        <v>-0.003033131124591813</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -22685,6 +24197,12 @@
       <c r="AB252" s="3" t="n">
         <v>-0.01142951797250284</v>
       </c>
+      <c r="AC252" s="1" t="n">
+        <v>0.005853</v>
+      </c>
+      <c r="AD252" s="3" t="n">
+        <v>-0.01926943699731912</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -22773,6 +24291,12 @@
       <c r="AB253" s="3" t="n">
         <v>-0.002321532211259337</v>
       </c>
+      <c r="AC253" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="AD253" s="3" t="n">
+        <v>-0.002326934264107146</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -22861,6 +24385,12 @@
       <c r="AB254" s="3" t="n">
         <v>-0.005392912172573238</v>
       </c>
+      <c r="AC254" s="1" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AD254" s="2" t="n">
+        <v>0.0007745933384974186</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -22949,6 +24479,12 @@
       <c r="AB255" s="2" t="n">
         <v>0.004261363636363627</v>
       </c>
+      <c r="AC255" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AD255" s="2" t="n">
+        <v>0.002357378595002425</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -23037,6 +24573,12 @@
       <c r="AB256" s="3" t="n">
         <v>-0.003789673140691625</v>
       </c>
+      <c r="AC256" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="AD256" s="2" t="n">
+        <v>0.004755111745125982</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -23125,6 +24667,12 @@
       <c r="AB257" s="2" t="n">
         <v>0.01029295328582739</v>
       </c>
+      <c r="AC257" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AD257" s="3" t="n">
+        <v>-0.0007836990595612325</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -23213,6 +24761,12 @@
       <c r="AB258" s="3" t="n">
         <v>-0.0004646223284215236</v>
       </c>
+      <c r="AC258" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="AD258" s="2" t="n">
+        <v>0.00411713925227445</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -23301,6 +24855,12 @@
       <c r="AB259" s="3" t="n">
         <v>-0.0005889281507656507</v>
       </c>
+      <c r="AC259" s="1" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="AD259" s="2" t="n">
+        <v>0.0007857002553526873</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -23389,6 +24949,12 @@
       <c r="AB260" s="2" t="n">
         <v>0.001073345259391851</v>
       </c>
+      <c r="AC260" s="1" t="n">
+        <v>0.08492</v>
+      </c>
+      <c r="AD260" s="2" t="n">
+        <v>0.01167500595663563</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -23477,6 +25043,12 @@
       <c r="AB261" s="3" t="n">
         <v>-0.003249390739236374</v>
       </c>
+      <c r="AC261" s="1" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="AD261" s="2" t="n">
+        <v>0.01263243683781578</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23565,6 +25137,12 @@
       <c r="AB262" s="2" t="n">
         <v>0.0006930006930006167</v>
       </c>
+      <c r="AC262" s="1" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AD262" s="2" t="n">
+        <v>0.007617728531855886</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -23653,6 +25231,12 @@
       <c r="AB263" s="3" t="n">
         <v>-0.007779074290159513</v>
       </c>
+      <c r="AC263" s="1" t="n">
+        <v>0.07654</v>
+      </c>
+      <c r="AD263" s="2" t="n">
+        <v>0.0001306677120083121</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -23741,6 +25325,12 @@
       <c r="AB264" s="2" t="n">
         <v>0.0007623888182972123</v>
       </c>
+      <c r="AC264" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AD264" s="3" t="n">
+        <v>-0.002793296089385449</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -23829,6 +25419,12 @@
       <c r="AB265" s="2" t="n">
         <v>0.001302931596091152</v>
       </c>
+      <c r="AC265" s="1" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AD265" s="2" t="n">
+        <v>0.001951854261548504</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -23917,6 +25513,12 @@
       <c r="AB266" s="3" t="n">
         <v>-0.004979253112033136</v>
       </c>
+      <c r="AC266" s="1" t="n">
+        <v>0.005987</v>
+      </c>
+      <c r="AD266" s="3" t="n">
+        <v>-0.001334445371142651</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -24005,6 +25607,12 @@
       <c r="AB267" s="3" t="n">
         <v>-0.001608147949611485</v>
       </c>
+      <c r="AC267" s="1" t="n">
+        <v>0.03735</v>
+      </c>
+      <c r="AD267" s="2" t="n">
+        <v>0.002684563758389339</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -24093,6 +25701,12 @@
       <c r="AB268" s="3" t="n">
         <v>-0.001306335728282229</v>
       </c>
+      <c r="AC268" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="AD268" s="2" t="n">
+        <v>0.0006540222367560231</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -24181,6 +25795,12 @@
       <c r="AB269" s="3" t="n">
         <v>-0.004148095847491268</v>
       </c>
+      <c r="AC269" s="1" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="AD269" s="2" t="n">
+        <v>0.0001329374750742334</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -24269,6 +25889,12 @@
       <c r="AB270" s="3" t="n">
         <v>-0.00428265524625268</v>
       </c>
+      <c r="AC270" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AD270" s="2" t="n">
+        <v>0.001075268817204302</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -24357,6 +25983,12 @@
       <c r="AB271" s="3" t="n">
         <v>-0.004988488104374482</v>
       </c>
+      <c r="AC271" s="1" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="AD271" s="2" t="n">
+        <v>0.0007713073659854315</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -24445,6 +26077,12 @@
       <c r="AB272" s="2" t="n">
         <v>0.001612036539495016</v>
       </c>
+      <c r="AC272" s="1" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="AD272" s="2" t="n">
+        <v>0.004828326180257425</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -24533,6 +26171,12 @@
       <c r="AB273" s="3" t="n">
         <v>-0.006739409499358211</v>
       </c>
+      <c r="AC273" s="1" t="n">
+        <v>0.03114</v>
+      </c>
+      <c r="AD273" s="2" t="n">
+        <v>0.006138933764135789</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -24621,6 +26265,12 @@
       <c r="AB274" s="3" t="n">
         <v>-0.002608242044861766</v>
       </c>
+      <c r="AC274" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AD274" s="2" t="n">
+        <v>0.004184100418410016</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -24709,6 +26359,12 @@
       <c r="AB275" s="3" t="n">
         <v>-0.0007219174126481139</v>
       </c>
+      <c r="AC275" s="1" t="n">
+        <v>0.06919</v>
+      </c>
+      <c r="AD275" s="3" t="n">
+        <v>-0.0002889755815632459</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -24797,6 +26453,12 @@
       <c r="AB276" s="3" t="n">
         <v>-0.003103662321539419</v>
       </c>
+      <c r="AC276" s="1" t="n">
+        <v>0.08039</v>
+      </c>
+      <c r="AD276" s="2" t="n">
+        <v>0.001120797011208054</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -24885,6 +26547,12 @@
       <c r="AB277" s="3" t="n">
         <v>-0.009920634920634946</v>
       </c>
+      <c r="AC277" s="1" t="n">
+        <v>0.003935</v>
+      </c>
+      <c r="AD277" s="3" t="n">
+        <v>-0.0142785571142284</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -24973,6 +26641,12 @@
       <c r="AB278" s="3" t="n">
         <v>-0.001926782273603013</v>
       </c>
+      <c r="AC278" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="AD278" s="3" t="n">
+        <v>-0.0006435006435007155</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -25061,6 +26735,12 @@
       <c r="AB279" s="3" t="n">
         <v>-0.002710027100271049</v>
       </c>
+      <c r="AC279" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AD279" s="2" t="n">
+        <v>0.0009057971014493956</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -25149,6 +26829,12 @@
       <c r="AB280" s="3" t="n">
         <v>-0.007409236848604635</v>
       </c>
+      <c r="AC280" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="AD280" s="3" t="n">
+        <v>-0.001990544911669489</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -25237,6 +26923,12 @@
       <c r="AB281" s="3" t="n">
         <v>-0.001902723272683952</v>
       </c>
+      <c r="AC281" s="1" t="n">
+        <v>0.08414000000000001</v>
+      </c>
+      <c r="AD281" s="2" t="n">
+        <v>0.002502085070892432</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -25325,6 +27017,12 @@
       <c r="AB282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC282" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="AD282" s="2" t="n">
+        <v>0.01865671641791046</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -25413,6 +27111,12 @@
       <c r="AB283" s="3" t="n">
         <v>-0.004176455233620295</v>
       </c>
+      <c r="AC283" s="1" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="AD283" s="2" t="n">
+        <v>0.002228047182175486</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -25501,6 +27205,12 @@
       <c r="AB284" s="3" t="n">
         <v>-0.006790123456790088</v>
       </c>
+      <c r="AC284" s="1" t="n">
+        <v>0.001611</v>
+      </c>
+      <c r="AD284" s="2" t="n">
+        <v>0.001243008079552547</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -25589,6 +27299,12 @@
       <c r="AB285" s="3" t="n">
         <v>-0.002464268112370628</v>
       </c>
+      <c r="AC285" s="1" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="AD285" s="2" t="n">
+        <v>0.002470355731225299</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -25677,6 +27393,12 @@
       <c r="AB286" s="3" t="n">
         <v>-0.002708255509899128</v>
       </c>
+      <c r="AC286" s="1" t="n">
+        <v>0.10643</v>
+      </c>
+      <c r="AD286" s="3" t="n">
+        <v>-0.003371102163123881</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -25765,6 +27487,12 @@
       <c r="AB287" s="3" t="n">
         <v>-0.001722158438576478</v>
       </c>
+      <c r="AC287" s="1" t="n">
+        <v>0.01742</v>
+      </c>
+      <c r="AD287" s="2" t="n">
+        <v>0.001725129384703982</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -25853,6 +27581,12 @@
       <c r="AB288" s="3" t="n">
         <v>-0.001325381047050973</v>
       </c>
+      <c r="AC288" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="AD288" s="2" t="n">
+        <v>0.001990710019907134</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -25941,6 +27675,12 @@
       <c r="AB289" s="2" t="n">
         <v>0.004929143561306235</v>
       </c>
+      <c r="AC289" s="1" t="n">
+        <v>0.01619</v>
+      </c>
+      <c r="AD289" s="3" t="n">
+        <v>-0.00735744941753538</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -26029,6 +27769,12 @@
       <c r="AB290" s="3" t="n">
         <v>-0.006178287731685893</v>
       </c>
+      <c r="AC290" s="1" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="AD290" s="2" t="n">
+        <v>0.002220248667850949</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -26117,6 +27863,12 @@
       <c r="AB291" s="3" t="n">
         <v>-0.0009043635541487936</v>
       </c>
+      <c r="AC291" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="AD291" s="2" t="n">
+        <v>0.000905182167911318</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -26205,6 +27957,12 @@
       <c r="AB292" s="2" t="n">
         <v>0.002317497103128623</v>
       </c>
+      <c r="AC292" s="1" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="AD292" s="3" t="n">
+        <v>-0.002312138728323701</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -26293,6 +28051,12 @@
       <c r="AB293" s="3" t="n">
         <v>-0.001000000000000029</v>
       </c>
+      <c r="AC293" s="1" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="AD293" s="2" t="n">
+        <v>0.01921921921921913</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -26381,6 +28145,12 @@
       <c r="AB294" s="3" t="n">
         <v>-0.001890061426996519</v>
       </c>
+      <c r="AC294" s="1" t="n">
+        <v>0.06328</v>
+      </c>
+      <c r="AD294" s="3" t="n">
+        <v>-0.001420230392930296</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -26469,6 +28239,12 @@
       <c r="AB295" s="3" t="n">
         <v>-0.003858210754762442</v>
       </c>
+      <c r="AC295" s="1" t="n">
+        <v>0.0004136</v>
+      </c>
+      <c r="AD295" s="2" t="n">
+        <v>0.0012103606874849</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -26557,6 +28333,12 @@
       <c r="AB296" s="3" t="n">
         <v>-0.003193357815743299</v>
       </c>
+      <c r="AC296" s="1" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="AD296" s="2" t="n">
+        <v>0.0009610764055742796</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -26645,6 +28427,12 @@
       <c r="AB297" s="3" t="n">
         <v>-0.004085801838610802</v>
       </c>
+      <c r="AC297" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AD297" s="2" t="n">
+        <v>0.005128205128205133</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -26733,6 +28521,12 @@
       <c r="AB298" s="3" t="n">
         <v>-0.005213764337851934</v>
       </c>
+      <c r="AC298" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AD298" s="2" t="n">
+        <v>0.003144654088050259</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -26821,6 +28615,12 @@
       <c r="AB299" s="2" t="n">
         <v>0.0007295466388744202</v>
       </c>
+      <c r="AC299" s="1" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="AD299" s="2" t="n">
+        <v>0.001770464486565335</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -26909,6 +28709,12 @@
       <c r="AB300" s="3" t="n">
         <v>-0.002676659528907814</v>
       </c>
+      <c r="AC300" s="1" t="n">
+        <v>0.01865</v>
+      </c>
+      <c r="AD300" s="2" t="n">
+        <v>0.00107353730542132</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -26997,6 +28803,12 @@
       <c r="AB301" s="3" t="n">
         <v>-0.0007440476190477178</v>
       </c>
+      <c r="AC301" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="AD301" s="2" t="n">
+        <v>0.001489203276247276</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -27085,6 +28897,12 @@
       <c r="AB302" s="2" t="n">
         <v>0.0009117848187826905</v>
       </c>
+      <c r="AC302" s="1" t="n">
+        <v>0.00441</v>
+      </c>
+      <c r="AD302" s="2" t="n">
+        <v>0.004327032566613509</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -27173,6 +28991,12 @@
       <c r="AB303" s="3" t="n">
         <v>-0.002162162162162074</v>
       </c>
+      <c r="AC303" s="1" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="AD303" s="2" t="n">
+        <v>0.002166847237269684</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -27261,6 +29085,12 @@
       <c r="AB304" s="3" t="n">
         <v>-0.002117746717492731</v>
       </c>
+      <c r="AC304" s="1" t="n">
+        <v>4.721</v>
+      </c>
+      <c r="AD304" s="2" t="n">
+        <v>0.001910016977928765</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -27349,6 +29179,12 @@
       <c r="AB305" s="2" t="n">
         <v>0.0007530120481927404</v>
       </c>
+      <c r="AC305" s="1" t="n">
+        <v>0.05336</v>
+      </c>
+      <c r="AD305" s="2" t="n">
+        <v>0.003762227238525184</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -27437,6 +29273,12 @@
       <c r="AB306" s="2" t="n">
         <v>0.0006849315068492871</v>
       </c>
+      <c r="AC306" s="1" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="AD306" s="2" t="n">
+        <v>0.002224503764544801</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -27525,6 +29367,12 @@
       <c r="AB307" s="2" t="n">
         <v>0.001146788990825721</v>
       </c>
+      <c r="AC307" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="AD307" s="2" t="n">
+        <v>0.001718213058419214</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -27613,6 +29461,12 @@
       <c r="AB308" s="2" t="n">
         <v>0.001408167370750365</v>
       </c>
+      <c r="AC308" s="1" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="AD308" s="3" t="n">
+        <v>-0.0032141422257935</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -27701,6 +29555,12 @@
       <c r="AB309" s="2" t="n">
         <v>0.003669724770642205</v>
       </c>
+      <c r="AC309" s="1" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="AD309" s="2" t="n">
+        <v>0.002925045703839003</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -27789,6 +29649,12 @@
       <c r="AB310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC310" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="AD310" s="2" t="n">
+        <v>0.004098360655737716</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -27877,6 +29743,12 @@
       <c r="AB311" s="3" t="n">
         <v>-0.0004221190375684307</v>
       </c>
+      <c r="AC311" s="1" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="AD311" s="3" t="n">
+        <v>-0.00760135135135153</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -27965,6 +29837,12 @@
       <c r="AB312" s="3" t="n">
         <v>-0.006665926008221423</v>
       </c>
+      <c r="AC312" s="1" t="n">
+        <v>0.008918000000000001</v>
+      </c>
+      <c r="AD312" s="3" t="n">
+        <v>-0.002572419192483919</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -28053,6 +29931,12 @@
       <c r="AB313" s="3" t="n">
         <v>-0.0006624710168929552</v>
       </c>
+      <c r="AC313" s="1" t="n">
+        <v>0.012116</v>
+      </c>
+      <c r="AD313" s="2" t="n">
+        <v>0.003977461054027132</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -28141,6 +30025,12 @@
       <c r="AB314" s="2" t="n">
         <v>0.004659042778483798</v>
       </c>
+      <c r="AC314" s="1" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="AD314" s="2" t="n">
+        <v>0.0008431703204046873</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -28229,6 +30119,12 @@
       <c r="AB315" s="2" t="n">
         <v>0.001404494382022536</v>
       </c>
+      <c r="AC315" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="AD315" s="3" t="n">
+        <v>-0.001402524544179588</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -28317,6 +30213,12 @@
       <c r="AB316" s="3" t="n">
         <v>-0.003058103975535256</v>
       </c>
+      <c r="AC316" s="1" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="AD316" s="2" t="n">
+        <v>0.004217791411043119</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -28405,6 +30307,12 @@
       <c r="AB317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AD317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -28493,6 +30401,12 @@
       <c r="AB318" s="2" t="n">
         <v>0.0002276564663921785</v>
       </c>
+      <c r="AC318" s="1" t="n">
+        <v>0.052733</v>
+      </c>
+      <c r="AD318" s="2" t="n">
+        <v>0.0001896705422681384</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -28581,6 +30495,12 @@
       <c r="AB319" s="2" t="n">
         <v>0.001044932079414795</v>
       </c>
+      <c r="AC319" s="1" t="n">
+        <v>0.03844</v>
+      </c>
+      <c r="AD319" s="2" t="n">
+        <v>0.003131524008350784</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -28669,6 +30589,12 @@
       <c r="AB320" s="3" t="n">
         <v>-0.001609128145114062</v>
       </c>
+      <c r="AC320" s="1" t="n">
+        <v>0.00681</v>
+      </c>
+      <c r="AD320" s="3" t="n">
+        <v>-0.002197802197802235</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -28757,6 +30683,12 @@
       <c r="AB321" s="3" t="n">
         <v>-0.0004404316229906778</v>
       </c>
+      <c r="AC321" s="1" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="AD321" s="2" t="n">
+        <v>0.00220312844238834</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -28845,6 +30777,12 @@
       <c r="AB322" s="3" t="n">
         <v>-0.002073613271124937</v>
       </c>
+      <c r="AC322" s="1" t="n">
+        <v>1.936</v>
+      </c>
+      <c r="AD322" s="2" t="n">
+        <v>0.005714285714285661</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -28933,6 +30871,12 @@
       <c r="AB323" s="3" t="n">
         <v>-0.006002233389168133</v>
       </c>
+      <c r="AC323" s="1" t="n">
+        <v>0.007099</v>
+      </c>
+      <c r="AD323" s="3" t="n">
+        <v>-0.003089453728408854</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -29021,6 +30965,12 @@
       <c r="AB324" s="3" t="n">
         <v>-0.004880694143167017</v>
       </c>
+      <c r="AC324" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="AD324" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -29109,6 +31059,12 @@
       <c r="AB325" s="3" t="n">
         <v>-0.004107272287992219</v>
       </c>
+      <c r="AC325" s="1" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AD325" s="2" t="n">
+        <v>0.005579815623483669</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -29197,6 +31153,12 @@
       <c r="AB326" s="3" t="n">
         <v>-0.004147656574035621</v>
       </c>
+      <c r="AC326" s="1" t="n">
+        <v>0.007206</v>
+      </c>
+      <c r="AD326" s="2" t="n">
+        <v>0.0004164931278633251</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -29285,6 +31247,12 @@
       <c r="AB327" s="2" t="n">
         <v>0.005235602094240842</v>
       </c>
+      <c r="AC327" s="1" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="AD327" s="2" t="n">
+        <v>0.003124999999999945</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -29373,6 +31341,12 @@
       <c r="AB328" s="3" t="n">
         <v>-0.003402083776312971</v>
       </c>
+      <c r="AC328" s="1" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="AD328" s="2" t="n">
+        <v>0.0002133560913163836</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -29461,6 +31435,12 @@
       <c r="AB329" s="3" t="n">
         <v>-0.0007440476190477178</v>
       </c>
+      <c r="AC329" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="AD329" s="2" t="n">
+        <v>0.002978406552494423</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -29549,6 +31529,12 @@
       <c r="AB330" s="3" t="n">
         <v>-0.003524229074889846</v>
       </c>
+      <c r="AC330" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AD330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -29637,6 +31623,12 @@
       <c r="AB331" s="3" t="n">
         <v>-0.005936675461741502</v>
       </c>
+      <c r="AC331" s="1" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="AD331" s="3" t="n">
+        <v>-0.0003317850033178135</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -29725,6 +31717,12 @@
       <c r="AB332" s="3" t="n">
         <v>-0.0001968891514077722</v>
       </c>
+      <c r="AC332" s="1" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="AD332" s="2" t="n">
+        <v>0.0003938558487593836</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -29813,6 +31811,12 @@
       <c r="AB333" s="3" t="n">
         <v>-0.001275148767356287</v>
       </c>
+      <c r="AC333" s="1" t="n">
+        <v>0.07077</v>
+      </c>
+      <c r="AD333" s="2" t="n">
+        <v>0.003972194637537275</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -29901,6 +31905,12 @@
       <c r="AB334" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC334" s="1" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="AD334" s="3" t="n">
+        <v>-0.001853445422651767</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -29989,6 +31999,12 @@
       <c r="AB335" s="3" t="n">
         <v>-0.0006377551020407461</v>
       </c>
+      <c r="AC335" s="1" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="AD335" s="3" t="n">
+        <v>-0.001276324186343368</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -30077,6 +32093,12 @@
       <c r="AB336" s="3" t="n">
         <v>-0.001718213058419214</v>
       </c>
+      <c r="AC336" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="AD336" s="2" t="n">
+        <v>0.001721170395869161</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -30165,6 +32187,12 @@
       <c r="AB337" s="2" t="n">
         <v>0.0004992511233150071</v>
       </c>
+      <c r="AC337" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AD337" s="2" t="n">
+        <v>0.003992015968063883</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -30253,6 +32281,12 @@
       <c r="AB338" s="3" t="n">
         <v>-0.002454219369454406</v>
       </c>
+      <c r="AC338" s="1" t="n">
+        <v>0.005288</v>
+      </c>
+      <c r="AD338" s="2" t="n">
+        <v>0.0007570022710069135</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -30341,6 +32375,12 @@
       <c r="AB339" s="3" t="n">
         <v>-0.004053271569195172</v>
       </c>
+      <c r="AC339" s="1" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="AD339" s="2" t="n">
+        <v>0.001744186046511624</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -30429,6 +32469,12 @@
       <c r="AB340" s="3" t="n">
         <v>-0.004231404958677697</v>
       </c>
+      <c r="AC340" s="1" t="n">
+        <v>0.15089</v>
+      </c>
+      <c r="AD340" s="2" t="n">
+        <v>0.001859106301042444</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -30517,6 +32563,12 @@
       <c r="AB341" s="3" t="n">
         <v>-0.0007852375343541718</v>
       </c>
+      <c r="AC341" s="1" t="n">
+        <v>7.641</v>
+      </c>
+      <c r="AD341" s="2" t="n">
+        <v>0.000785854616895904</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -30605,6 +32657,12 @@
       <c r="AB342" s="2" t="n">
         <v>0.003043213633597081</v>
       </c>
+      <c r="AC342" s="1" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AD342" s="3" t="n">
+        <v>-0.004550970873786412</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -30693,6 +32751,12 @@
       <c r="AB343" s="3" t="n">
         <v>-0.002977667493796577</v>
       </c>
+      <c r="AC343" s="1" t="n">
+        <v>0.02028</v>
+      </c>
+      <c r="AD343" s="2" t="n">
+        <v>0.009457441513190602</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -30781,6 +32845,12 @@
       <c r="AB344" s="2" t="n">
         <v>0.0009191176470587223</v>
       </c>
+      <c r="AC344" s="1" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="AD344" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -30869,6 +32939,12 @@
       <c r="AB345" s="3" t="n">
         <v>-0.003937007874015839</v>
       </c>
+      <c r="AC345" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD345" s="2" t="n">
+        <v>0.003952569169960566</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -30957,6 +33033,12 @@
       <c r="AB346" s="3" t="n">
         <v>-0.002125193199381709</v>
       </c>
+      <c r="AC346" s="1" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="AD346" s="2" t="n">
+        <v>0.0009680542110357785</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -31045,6 +33127,12 @@
       <c r="AB347" s="3" t="n">
         <v>-0.006085898104677381</v>
       </c>
+      <c r="AC347" s="1" t="n">
+        <v>0.05705</v>
+      </c>
+      <c r="AD347" s="3" t="n">
+        <v>-0.001924422673198144</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -31133,6 +33221,12 @@
       <c r="AB348" s="3" t="n">
         <v>-0.003132341425215438</v>
       </c>
+      <c r="AC348" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="AD348" s="2" t="n">
+        <v>0.0007855459544384662</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -31221,6 +33315,12 @@
       <c r="AB349" s="2" t="n">
         <v>0.0007534339199813836</v>
       </c>
+      <c r="AC349" s="1" t="n">
+        <v>5185.5</v>
+      </c>
+      <c r="AD349" s="2" t="n">
+        <v>0.00102312652021161</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -31309,6 +33409,12 @@
       <c r="AB350" s="3" t="n">
         <v>-0.005366726296958885</v>
       </c>
+      <c r="AC350" s="1" t="n">
+        <v>0.02783</v>
+      </c>
+      <c r="AD350" s="2" t="n">
+        <v>0.001079136690647563</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -31397,6 +33503,12 @@
       <c r="AB351" s="3" t="n">
         <v>-0.005726556907659254</v>
       </c>
+      <c r="AC351" s="1" t="n">
+        <v>0.001406</v>
+      </c>
+      <c r="AD351" s="2" t="n">
+        <v>0.01223902087832964</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -31485,6 +33597,12 @@
       <c r="AB352" s="2" t="n">
         <v>0.03962264150943387</v>
       </c>
+      <c r="AC352" s="1" t="n">
+        <v>0.01721</v>
+      </c>
+      <c r="AD352" s="2" t="n">
+        <v>0.04113732607380521</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -31573,6 +33691,12 @@
       <c r="AB353" s="2" t="n">
         <v>0.002861230329041455</v>
       </c>
+      <c r="AC353" s="1" t="n">
+        <v>6.319</v>
+      </c>
+      <c r="AD353" s="2" t="n">
+        <v>0.001585037248375303</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -31661,6 +33785,12 @@
       <c r="AB354" s="3" t="n">
         <v>-0.0006954102920724391</v>
       </c>
+      <c r="AC354" s="1" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AD354" s="2" t="n">
+        <v>0.01043841336116911</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -31749,6 +33879,12 @@
       <c r="AB355" s="2" t="n">
         <v>0.001445086705202253</v>
       </c>
+      <c r="AC355" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="AD355" s="2" t="n">
+        <v>0.004088504088504172</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -31837,6 +33973,12 @@
       <c r="AB356" s="3" t="n">
         <v>-0.003865413335675973</v>
       </c>
+      <c r="AC356" s="1" t="n">
+        <v>0.11293</v>
+      </c>
+      <c r="AD356" s="3" t="n">
+        <v>-0.00405679513184586</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -31925,6 +34067,12 @@
       <c r="AB357" s="2" t="n">
         <v>0.002086098994879523</v>
       </c>
+      <c r="AC357" s="1" t="n">
+        <v>0.005266</v>
+      </c>
+      <c r="AD357" s="3" t="n">
+        <v>-0.003406510219530619</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -32013,6 +34161,12 @@
       <c r="AB358" s="3" t="n">
         <v>-0.001616379310344799</v>
       </c>
+      <c r="AC358" s="1" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AD358" s="2" t="n">
+        <v>0.002698327037236916</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -32101,6 +34255,12 @@
       <c r="AB359" s="2" t="n">
         <v>0.004907975460122669</v>
       </c>
+      <c r="AC359" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="AD359" s="2" t="n">
+        <v>0.01282051282051276</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -32189,6 +34349,12 @@
       <c r="AB360" s="3" t="n">
         <v>-0.001877713883346949</v>
       </c>
+      <c r="AC360" s="1" t="n">
+        <v>0.08517</v>
+      </c>
+      <c r="AD360" s="2" t="n">
+        <v>0.00141093474426802</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -32277,6 +34443,12 @@
       <c r="AB361" s="3" t="n">
         <v>-0.002614379084967327</v>
       </c>
+      <c r="AC361" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="AD361" s="3" t="n">
+        <v>-0.001310615989515019</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -32365,6 +34537,12 @@
       <c r="AB362" s="2" t="n">
         <v>0.0002347417840375328</v>
       </c>
+      <c r="AC362" s="1" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="AD362" s="3" t="n">
+        <v>-0.001642806852851393</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -32453,6 +34631,12 @@
       <c r="AB363" s="2" t="n">
         <v>0.001847940865892322</v>
       </c>
+      <c r="AC363" s="1" t="n">
+        <v>3.765</v>
+      </c>
+      <c r="AD363" s="3" t="n">
+        <v>-0.007905138339920898</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -32541,6 +34725,12 @@
       <c r="AB364" s="2" t="n">
         <v>0.0009090909090910298</v>
       </c>
+      <c r="AC364" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="AD364" s="2" t="n">
+        <v>0.007266121707538462</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -32629,6 +34819,12 @@
       <c r="AB365" s="2" t="n">
         <v>0.000181290790427776</v>
       </c>
+      <c r="AC365" s="1" t="n">
+        <v>0.05532</v>
+      </c>
+      <c r="AD365" s="2" t="n">
+        <v>0.002718868950516663</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -32717,6 +34913,12 @@
       <c r="AB366" s="3" t="n">
         <v>-0.0004351610095735245</v>
       </c>
+      <c r="AC366" s="1" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="AD366" s="3" t="n">
+        <v>-0.005224205485415849</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -32805,6 +35007,12 @@
       <c r="AB367" s="3" t="n">
         <v>-0.008100147275404965</v>
       </c>
+      <c r="AC367" s="1" t="n">
+        <v>0.001352</v>
+      </c>
+      <c r="AD367" s="2" t="n">
+        <v>0.003711952487008015</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -32893,6 +35101,12 @@
       <c r="AB368" s="2" t="n">
         <v>0.0003467406380027358</v>
       </c>
+      <c r="AC368" s="1" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AD368" s="2" t="n">
+        <v>0.003812824956672601</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -32981,6 +35195,12 @@
       <c r="AB369" s="2" t="n">
         <v>0.001616379310344762</v>
       </c>
+      <c r="AC369" s="1" t="n">
+        <v>0.01864</v>
+      </c>
+      <c r="AD369" s="2" t="n">
+        <v>0.002689618074233536</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -33069,6 +35289,12 @@
       <c r="AB370" s="3" t="n">
         <v>-0.001672071341710564</v>
       </c>
+      <c r="AC370" s="1" t="n">
+        <v>0.19759</v>
+      </c>
+      <c r="AD370" s="2" t="n">
+        <v>0.002842206770542441</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -33157,6 +35383,12 @@
       <c r="AB371" s="2" t="n">
         <v>0.01333333333333335</v>
       </c>
+      <c r="AC371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AD371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -33245,6 +35477,12 @@
       <c r="AB372" s="3" t="n">
         <v>-0.003795066413662216</v>
       </c>
+      <c r="AC372" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AD372" s="2" t="n">
+        <v>0.002857142857142939</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -33333,6 +35571,12 @@
       <c r="AB373" s="3" t="n">
         <v>-0.001059001512859313</v>
       </c>
+      <c r="AC373" s="1" t="n">
+        <v>0.06569</v>
+      </c>
+      <c r="AD373" s="3" t="n">
+        <v>-0.005149174617598166</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -33421,6 +35665,12 @@
       <c r="AB374" s="3" t="n">
         <v>-0.002494420375475899</v>
       </c>
+      <c r="AC374" s="1" t="n">
+        <v>0.007626</v>
+      </c>
+      <c r="AD374" s="2" t="n">
+        <v>0.003685180310608088</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -33509,6 +35759,12 @@
       <c r="AB375" s="2" t="n">
         <v>0.004385964912280741</v>
       </c>
+      <c r="AC375" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="AD375" s="3" t="n">
+        <v>-0.0006238303181533935</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -33597,6 +35853,12 @@
       <c r="AB376" s="3" t="n">
         <v>-0.006133177570093386</v>
       </c>
+      <c r="AC376" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="AD376" s="2" t="n">
+        <v>0.0002938583602702612</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -33685,6 +35947,12 @@
       <c r="AB377" s="2" t="n">
         <v>0.05421686746987961</v>
       </c>
+      <c r="AC377" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="AD377" s="3" t="n">
+        <v>-0.04000000000000015</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -33773,6 +36041,12 @@
       <c r="AB378" s="2" t="n">
         <v>0.0008968609865470487</v>
       </c>
+      <c r="AC378" s="1" t="n">
+        <v>0.01134</v>
+      </c>
+      <c r="AD378" s="2" t="n">
+        <v>0.01612903225806448</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -33861,6 +36135,12 @@
       <c r="AB379" s="2" t="n">
         <v>0.006976744186046551</v>
       </c>
+      <c r="AC379" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AD379" s="3" t="n">
+        <v>-0.001847575057736645</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -33949,6 +36229,12 @@
       <c r="AB380" s="3" t="n">
         <v>-0.003713527851458735</v>
       </c>
+      <c r="AC380" s="1" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="AD380" s="2" t="n">
+        <v>0.003194888178913608</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -34037,6 +36323,12 @@
       <c r="AB381" s="3" t="n">
         <v>-0.004987531172069853</v>
       </c>
+      <c r="AC381" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="AD381" s="2" t="n">
+        <v>0.001670843776106982</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -34125,6 +36417,12 @@
       <c r="AB382" s="3" t="n">
         <v>-0.01111859838274934</v>
       </c>
+      <c r="AC382" s="1" t="n">
+        <v>0.02927</v>
+      </c>
+      <c r="AD382" s="3" t="n">
+        <v>-0.002725724020442937</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -34213,6 +36511,12 @@
       <c r="AB383" s="3" t="n">
         <v>-0.0009139375476009032</v>
       </c>
+      <c r="AC383" s="1" t="n">
+        <v>0.006579</v>
+      </c>
+      <c r="AD383" s="2" t="n">
+        <v>0.003049245311785341</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -34301,6 +36605,12 @@
       <c r="AB384" s="2" t="n">
         <v>0.002394636015325739</v>
       </c>
+      <c r="AC384" s="1" t="n">
+        <v>0.02087</v>
+      </c>
+      <c r="AD384" s="3" t="n">
+        <v>-0.002866698518872481</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -34389,6 +36699,12 @@
       <c r="AB385" s="3" t="n">
         <v>-0.001967729240456513</v>
       </c>
+      <c r="AC385" s="1" t="n">
+        <v>2545</v>
+      </c>
+      <c r="AD385" s="2" t="n">
+        <v>0.003548895899053628</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -34477,6 +36793,12 @@
       <c r="AB386" s="3" t="n">
         <v>-0.00251382604323781</v>
       </c>
+      <c r="AC386" s="1" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="AD386" s="2" t="n">
+        <v>0.007560483870967749</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -34565,6 +36887,12 @@
       <c r="AB387" s="2" t="n">
         <v>0.002583979328165514</v>
       </c>
+      <c r="AC387" s="1" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="AD387" s="3" t="n">
+        <v>-0.003280224929709495</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -34653,6 +36981,12 @@
       <c r="AB388" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC388" s="1" t="n">
+        <v>0.004998</v>
+      </c>
+      <c r="AD388" s="2" t="n">
+        <v>0.002406738868832703</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -34741,6 +37075,12 @@
       <c r="AB389" s="3" t="n">
         <v>-0.001333926189417465</v>
       </c>
+      <c r="AC389" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="AD389" s="2" t="n">
+        <v>0.01424755120213717</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -34829,6 +37169,12 @@
       <c r="AB390" s="3" t="n">
         <v>-0.006720695789681892</v>
       </c>
+      <c r="AC390" s="1" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AD390" s="2" t="n">
+        <v>0.002985074626865785</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -34917,6 +37263,12 @@
       <c r="AB391" s="3" t="n">
         <v>-0.002634612218014047</v>
       </c>
+      <c r="AC391" s="1" t="n">
+        <v>0.0006076</v>
+      </c>
+      <c r="AD391" s="2" t="n">
+        <v>0.003136866435529127</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -35005,6 +37357,12 @@
       <c r="AB392" s="3" t="n">
         <v>-0.004089282671664631</v>
       </c>
+      <c r="AC392" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="AD392" s="2" t="n">
+        <v>0.002566295979469587</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -35093,6 +37451,12 @@
       <c r="AB393" s="3" t="n">
         <v>-0.004437869822485129</v>
       </c>
+      <c r="AC393" s="1" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="AD393" s="3" t="n">
+        <v>-0.0003714710252599888</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -35181,6 +37545,12 @@
       <c r="AB394" s="3" t="n">
         <v>-0.006586826347305354</v>
       </c>
+      <c r="AC394" s="1" t="n">
+        <v>0.006651</v>
+      </c>
+      <c r="AD394" s="2" t="n">
+        <v>0.002260397830017991</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -35269,6 +37639,12 @@
       <c r="AB395" s="2" t="n">
         <v>0.001739130434782538</v>
       </c>
+      <c r="AC395" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AD395" s="2" t="n">
+        <v>0.0008680555555555804</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -35357,6 +37733,12 @@
       <c r="AB396" s="3" t="n">
         <v>-0.002261712439418325</v>
       </c>
+      <c r="AC396" s="1" t="n">
+        <v>0.03138</v>
+      </c>
+      <c r="AD396" s="2" t="n">
+        <v>0.01619170984455949</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -35445,6 +37827,12 @@
       <c r="AB397" s="2" t="n">
         <v>0.002656042496679838</v>
       </c>
+      <c r="AC397" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AD397" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -35533,6 +37921,12 @@
       <c r="AB398" s="2" t="n">
         <v>0.0006069802731410718</v>
       </c>
+      <c r="AC398" s="1" t="n">
+        <v>0.003316</v>
+      </c>
+      <c r="AD398" s="2" t="n">
+        <v>0.005762814680012108</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -35621,6 +38015,12 @@
       <c r="AB399" s="3" t="n">
         <v>-0.002689618074233349</v>
       </c>
+      <c r="AC399" s="1" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="AD399" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -35709,6 +38109,12 @@
       <c r="AB400" s="3" t="n">
         <v>-0.002732240437158458</v>
       </c>
+      <c r="AC400" s="1" t="n">
+        <v>0.006935</v>
+      </c>
+      <c r="AD400" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -35797,6 +38203,12 @@
       <c r="AB401" s="3" t="n">
         <v>-0.002151154452889754</v>
       </c>
+      <c r="AC401" s="1" t="n">
+        <v>0.006966</v>
+      </c>
+      <c r="AD401" s="2" t="n">
+        <v>0.001149755676918683</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -35885,6 +38297,12 @@
       <c r="AB402" s="3" t="n">
         <v>-0.003608311559039597</v>
       </c>
+      <c r="AC402" s="1" t="n">
+        <v>0.008000999999999999</v>
+      </c>
+      <c r="AD402" s="3" t="n">
+        <v>-0.0008741258741258819</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -35973,6 +38391,12 @@
       <c r="AB403" s="3" t="n">
         <v>-0.002832288084159442</v>
       </c>
+      <c r="AC403" s="1" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="AD403" s="2" t="n">
+        <v>0.006492189085007117</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -36061,6 +38485,12 @@
       <c r="AB404" s="3" t="n">
         <v>-0.002893479577417307</v>
       </c>
+      <c r="AC404" s="1" t="n">
+        <v>0.14815</v>
+      </c>
+      <c r="AD404" s="3" t="n">
+        <v>-0.0002024564718585656</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -36149,6 +38579,12 @@
       <c r="AB405" s="3" t="n">
         <v>-0.007212657049790549</v>
       </c>
+      <c r="AC405" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AD405" s="2" t="n">
+        <v>0.002812280290602345</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -36237,6 +38673,12 @@
       <c r="AB406" s="3" t="n">
         <v>-0.00146015853149766</v>
       </c>
+      <c r="AC406" s="1" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="AD406" s="2" t="n">
+        <v>0.001462293712136993</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -36325,6 +38767,12 @@
       <c r="AB407" s="2" t="n">
         <v>0.0002016535591854339</v>
       </c>
+      <c r="AC407" s="1" t="n">
+        <v>0.0004961</v>
+      </c>
+      <c r="AD407" s="2" t="n">
+        <v>0.000201612903225702</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -36413,6 +38861,12 @@
       <c r="AB408" s="3" t="n">
         <v>-0.005622489959839268</v>
       </c>
+      <c r="AC408" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="AD408" s="3" t="n">
+        <v>-0.004038772213247149</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -36501,6 +38955,12 @@
       <c r="AB409" s="3" t="n">
         <v>-0.0009404388714734246</v>
       </c>
+      <c r="AC409" s="1" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AD409" s="3" t="n">
+        <v>-0.001882648258550328</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -36589,6 +39049,12 @@
       <c r="AB410" s="3" t="n">
         <v>-0.0004776689754000283</v>
       </c>
+      <c r="AC410" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="AD410" s="2" t="n">
+        <v>0.001433691756272509</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -36677,6 +39143,12 @@
       <c r="AB411" s="3" t="n">
         <v>-0.0006720430107527773</v>
       </c>
+      <c r="AC411" s="1" t="n">
+        <v>0.02976</v>
+      </c>
+      <c r="AD411" s="2" t="n">
+        <v>0.0006724949562879172</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -36765,6 +39237,12 @@
       <c r="AB412" s="3" t="n">
         <v>-0.002401222440515112</v>
       </c>
+      <c r="AC412" s="1" t="n">
+        <v>0.004569</v>
+      </c>
+      <c r="AD412" s="3" t="n">
+        <v>-0.0002188183807440115</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -36853,6 +39331,12 @@
       <c r="AB413" s="3" t="n">
         <v>-0.00395726157499011</v>
       </c>
+      <c r="AC413" s="1" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AD413" s="2" t="n">
+        <v>0.001191895113230125</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -36941,6 +39425,12 @@
       <c r="AB414" s="2" t="n">
         <v>0.002343749999999915</v>
       </c>
+      <c r="AC414" s="1" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="AD414" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -37029,6 +39519,12 @@
       <c r="AB415" s="2" t="n">
         <v>0.004371584699453555</v>
       </c>
+      <c r="AC415" s="1" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="AD415" s="2" t="n">
+        <v>0.009793253536452554</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -37117,6 +39613,12 @@
       <c r="AB416" s="2" t="n">
         <v>0.0009244992295840446</v>
       </c>
+      <c r="AC416" s="1" t="n">
+        <v>0.03254</v>
+      </c>
+      <c r="AD416" s="2" t="n">
+        <v>0.001847290640394013</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -37205,6 +39707,12 @@
       <c r="AB417" s="3" t="n">
         <v>-0.002259603314084856</v>
       </c>
+      <c r="AC417" s="1" t="n">
+        <v>0.03967</v>
+      </c>
+      <c r="AD417" s="3" t="n">
+        <v>-0.001761449421238063</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -37293,6 +39801,12 @@
       <c r="AB418" s="2" t="n">
         <v>0.000787504921905821</v>
       </c>
+      <c r="AC418" s="1" t="n">
+        <v>0.07639</v>
+      </c>
+      <c r="AD418" s="2" t="n">
+        <v>0.001836065573770508</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -37381,6 +39895,12 @@
       <c r="AB419" s="3" t="n">
         <v>-0.001503759398496179</v>
       </c>
+      <c r="AC419" s="1" t="n">
+        <v>0.00667</v>
+      </c>
+      <c r="AD419" s="2" t="n">
+        <v>0.004518072289156573</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -37469,6 +39989,12 @@
       <c r="AB420" s="3" t="n">
         <v>-0.00226757369614519</v>
       </c>
+      <c r="AC420" s="1" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="AD420" s="2" t="n">
+        <v>0.002272727272727338</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -37557,6 +40083,12 @@
       <c r="AB421" s="2" t="n">
         <v>0.002075550020755502</v>
       </c>
+      <c r="AC421" s="1" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="AD421" s="3" t="n">
+        <v>-0.001242750621375289</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -37645,6 +40177,12 @@
       <c r="AB422" s="2" t="n">
         <v>0.0647773279352227</v>
       </c>
+      <c r="AC422" s="1" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="AD422" s="2" t="n">
+        <v>0.02281368821292775</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -37733,6 +40271,12 @@
       <c r="AB423" s="2" t="n">
         <v>0.001322751322751361</v>
       </c>
+      <c r="AC423" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="AD423" s="2" t="n">
+        <v>0.001981505944517799</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -37821,6 +40365,12 @@
       <c r="AB424" s="2" t="n">
         <v>0.001429933269780778</v>
       </c>
+      <c r="AC424" s="1" t="n">
+        <v>0.0002093</v>
+      </c>
+      <c r="AD424" s="3" t="n">
+        <v>-0.003807710613993429</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -37909,6 +40459,12 @@
       <c r="AB425" s="3" t="n">
         <v>-0.0008038585209002331</v>
       </c>
+      <c r="AC425" s="1" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AD425" s="2" t="n">
+        <v>0.003218020917135964</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -37997,6 +40553,12 @@
       <c r="AB426" s="3" t="n">
         <v>-0.002820874471086039</v>
       </c>
+      <c r="AC426" s="1" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="AD426" s="2" t="n">
+        <v>0.001414427157001416</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -38085,6 +40647,12 @@
       <c r="AB427" s="2" t="n">
         <v>0.0005130836326320981</v>
       </c>
+      <c r="AC427" s="1" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="AD427" s="2" t="n">
+        <v>0.001025641025640984</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -38173,6 +40741,12 @@
       <c r="AB428" s="3" t="n">
         <v>-0.005741048496751856</v>
       </c>
+      <c r="AC428" s="1" t="n">
+        <v>0.06587</v>
+      </c>
+      <c r="AD428" s="2" t="n">
+        <v>0.0009117155447501064</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -38261,6 +40835,12 @@
       <c r="AB429" s="3" t="n">
         <v>-0.001510574018126722</v>
       </c>
+      <c r="AC429" s="1" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="AD429" s="2" t="n">
+        <v>0.00226928895612704</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -38349,6 +40929,12 @@
       <c r="AB430" s="2" t="n">
         <v>0.001266968325791709</v>
       </c>
+      <c r="AC430" s="1" t="n">
+        <v>0.011067</v>
+      </c>
+      <c r="AD430" s="2" t="n">
+        <v>0.0002711496746205048</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -38437,6 +41023,12 @@
       <c r="AB431" s="2" t="n">
         <v>0.0004480286738351849</v>
       </c>
+      <c r="AC431" s="1" t="n">
+        <v>0.006689</v>
+      </c>
+      <c r="AD431" s="3" t="n">
+        <v>-0.001492760113449837</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -38525,6 +41117,12 @@
       <c r="AB432" s="3" t="n">
         <v>-0.0005640157924422632</v>
       </c>
+      <c r="AC432" s="1" t="n">
+        <v>0.001773</v>
+      </c>
+      <c r="AD432" s="2" t="n">
+        <v>0.000564334085778856</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -38613,6 +41211,12 @@
       <c r="AB433" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC433" s="1" t="n">
+        <v>0.001363</v>
+      </c>
+      <c r="AD433" s="2" t="n">
+        <v>0.00220588235294115</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -38701,6 +41305,12 @@
       <c r="AB434" s="2" t="n">
         <v>0.002421307506053196</v>
       </c>
+      <c r="AC434" s="1" t="n">
+        <v>0.000417</v>
+      </c>
+      <c r="AD434" s="2" t="n">
+        <v>0.007246376811594248</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -38789,6 +41399,12 @@
       <c r="AB435" s="3" t="n">
         <v>-0.003384494293585092</v>
       </c>
+      <c r="AC435" s="1" t="n">
+        <v>0.12687</v>
+      </c>
+      <c r="AD435" s="2" t="n">
+        <v>0.001974411625335651</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -38877,6 +41493,12 @@
       <c r="AB436" s="3" t="n">
         <v>-0.004479713298348945</v>
       </c>
+      <c r="AC436" s="1" t="n">
+        <v>0.07802000000000001</v>
+      </c>
+      <c r="AD436" s="2" t="n">
+        <v>0.003085626124967911</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -38965,6 +41587,12 @@
       <c r="AB437" s="3" t="n">
         <v>-0.002069404648201158</v>
       </c>
+      <c r="AC437" s="1" t="n">
+        <v>0.6287</v>
+      </c>
+      <c r="AD437" s="2" t="n">
+        <v>0.002871271335141209</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -39053,6 +41681,12 @@
       <c r="AB438" s="3" t="n">
         <v>-0.001594169892962893</v>
       </c>
+      <c r="AC438" s="1" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="AD438" s="3" t="n">
+        <v>-0.0002281021897809335</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -39141,6 +41775,12 @@
       <c r="AB439" s="2" t="n">
         <v>0.002994011976047931</v>
       </c>
+      <c r="AC439" s="1" t="n">
+        <v>0.07035</v>
+      </c>
+      <c r="AD439" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -39229,6 +41869,12 @@
       <c r="AB440" s="3" t="n">
         <v>-0.001974983541803795</v>
       </c>
+      <c r="AC440" s="1" t="n">
+        <v>0.001516</v>
+      </c>
+      <c r="AD440" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -39317,6 +41963,12 @@
       <c r="AB441" s="2" t="n">
         <v>0.0009513742071881953</v>
       </c>
+      <c r="AC441" s="1" t="n">
+        <v>0.009447000000000001</v>
+      </c>
+      <c r="AD441" s="3" t="n">
+        <v>-0.00232337100010555</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -39405,6 +42057,12 @@
       <c r="AB442" s="3" t="n">
         <v>-0.002843601895734495</v>
       </c>
+      <c r="AC442" s="1" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD442" s="2" t="n">
+        <v>0.007604562737642592</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -39493,6 +42151,12 @@
       <c r="AB443" s="3" t="n">
         <v>-0.002271694684234347</v>
       </c>
+      <c r="AC443" s="1" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AD443" s="2" t="n">
+        <v>0.003187613843351576</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -39581,6 +42245,12 @@
       <c r="AB444" s="3" t="n">
         <v>-0.0002615746795710238</v>
       </c>
+      <c r="AC444" s="1" t="n">
+        <v>0.000383</v>
+      </c>
+      <c r="AD444" s="2" t="n">
+        <v>0.002093144950287716</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -39669,6 +42339,12 @@
       <c r="AB445" s="3" t="n">
         <v>-0.0008434073657575291</v>
       </c>
+      <c r="AC445" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="AD445" s="2" t="n">
+        <v>0.001406865503657695</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -39757,6 +42433,12 @@
       <c r="AB446" s="2" t="n">
         <v>0.001396485511462762</v>
       </c>
+      <c r="AC446" s="1" t="n">
+        <v>0.08658</v>
+      </c>
+      <c r="AD446" s="2" t="n">
+        <v>0.006159209761766446</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -39845,6 +42527,12 @@
       <c r="AB447" s="3" t="n">
         <v>-0.0009168704156478208</v>
       </c>
+      <c r="AC447" s="1" t="n">
+        <v>3.273</v>
+      </c>
+      <c r="AD447" s="2" t="n">
+        <v>0.001223615784643623</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -39933,6 +42621,12 @@
       <c r="AB448" s="2" t="n">
         <v>0.0007810059356452417</v>
       </c>
+      <c r="AC448" s="1" t="n">
+        <v>0.06417</v>
+      </c>
+      <c r="AD448" s="2" t="n">
+        <v>0.001560792882784499</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -40021,6 +42715,12 @@
       <c r="AB449" s="2" t="n">
         <v>0.003075661267172445</v>
       </c>
+      <c r="AC449" s="1" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="AD449" s="2" t="n">
+        <v>0.001226492232215841</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -40109,6 +42809,12 @@
       <c r="AB450" s="2" t="n">
         <v>0.00185873605947957</v>
       </c>
+      <c r="AC450" s="1" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="AD450" s="3" t="n">
+        <v>-0.0007951232441028955</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -40197,6 +42903,12 @@
       <c r="AB451" s="2" t="n">
         <v>0.001824817518248259</v>
       </c>
+      <c r="AC451" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="AD451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -40285,6 +42997,12 @@
       <c r="AB452" s="2" t="n">
         <v>0.001537279016141367</v>
       </c>
+      <c r="AC452" s="1" t="n">
+        <v>0.10439</v>
+      </c>
+      <c r="AD452" s="2" t="n">
+        <v>0.001438986953184932</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -40373,6 +43091,12 @@
       <c r="AB453" s="3" t="n">
         <v>-0.007941356139279057</v>
       </c>
+      <c r="AC453" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AD453" s="3" t="n">
+        <v>-0.00369458128078824</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -40461,6 +43185,12 @@
       <c r="AB454" s="3" t="n">
         <v>-0.001392272885485556</v>
       </c>
+      <c r="AC454" s="1" t="n">
+        <v>2.879</v>
+      </c>
+      <c r="AD454" s="2" t="n">
+        <v>0.003485535029626973</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -40549,6 +43279,12 @@
       <c r="AB455" s="3" t="n">
         <v>-0.003344481605351174</v>
       </c>
+      <c r="AC455" s="1" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AD455" s="2" t="n">
+        <v>0.002237136465324387</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -40637,6 +43373,12 @@
       <c r="AB456" s="3" t="n">
         <v>-0.000338753387533838</v>
       </c>
+      <c r="AC456" s="1" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="AD456" s="3" t="n">
+        <v>-0.0006777363605558196</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -40725,6 +43467,12 @@
       <c r="AB457" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC457" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="AD457" s="2" t="n">
+        <v>0.001012145748987813</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -40813,6 +43561,12 @@
       <c r="AB458" s="2" t="n">
         <v>0.0008028259473346408</v>
       </c>
+      <c r="AC458" s="1" t="n">
+        <v>0.06259000000000001</v>
+      </c>
+      <c r="AD458" s="2" t="n">
+        <v>0.004171346061286752</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -40901,6 +43655,12 @@
       <c r="AB459" s="2" t="n">
         <v>0.002793296089385482</v>
       </c>
+      <c r="AC459" s="1" t="n">
+        <v>0.01436</v>
+      </c>
+      <c r="AD459" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -40989,6 +43749,12 @@
       <c r="AB460" s="3" t="n">
         <v>-0.0003748594277145484</v>
       </c>
+      <c r="AC460" s="1" t="n">
+        <v>0.016009</v>
+      </c>
+      <c r="AD460" s="2" t="n">
+        <v>0.000562499999999912</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -41077,6 +43843,12 @@
       <c r="AB461" s="2" t="n">
         <v>0.0005984440454817232</v>
       </c>
+      <c r="AC461" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="AD461" s="2" t="n">
+        <v>0.001196172248803987</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -41165,6 +43937,12 @@
       <c r="AB462" s="3" t="n">
         <v>-0.00381861575178994</v>
       </c>
+      <c r="AC462" s="1" t="n">
+        <v>0.0002084</v>
+      </c>
+      <c r="AD462" s="3" t="n">
+        <v>-0.00143747005270727</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -41253,6 +44031,12 @@
       <c r="AB463" s="2" t="n">
         <v>0.008032128514056316</v>
       </c>
+      <c r="AC463" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="AD463" s="3" t="n">
+        <v>-0.004980079681274905</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -41341,6 +44125,12 @@
       <c r="AB464" s="2" t="n">
         <v>0.001890359168241889</v>
       </c>
+      <c r="AC464" s="1" t="n">
+        <v>0.02717</v>
+      </c>
+      <c r="AD464" s="2" t="n">
+        <v>0.02528301886792455</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -41429,6 +44219,12 @@
       <c r="AB465" s="2" t="n">
         <v>0.001334222815210202</v>
       </c>
+      <c r="AC465" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="AD465" s="2" t="n">
+        <v>0.007994670219853336</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -41517,6 +44313,12 @@
       <c r="AB466" s="3" t="n">
         <v>-0.001095490231878721</v>
       </c>
+      <c r="AC466" s="1" t="n">
+        <v>0.05478</v>
+      </c>
+      <c r="AD466" s="2" t="n">
+        <v>0.001279473588009516</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -41605,6 +44407,12 @@
       <c r="AB467" s="3" t="n">
         <v>-0.003755054881571294</v>
       </c>
+      <c r="AC467" s="1" t="n">
+        <v>0.03473</v>
+      </c>
+      <c r="AD467" s="2" t="n">
+        <v>0.006958538706871475</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -41693,6 +44501,12 @@
       <c r="AB468" s="2" t="n">
         <v>0.0003650967506388467</v>
       </c>
+      <c r="AC468" s="1" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="AD468" s="3" t="n">
+        <v>-0.00328467153284671</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -41781,6 +44595,12 @@
       <c r="AB469" s="2" t="n">
         <v>0.0002672010688042817</v>
       </c>
+      <c r="AC469" s="1" t="n">
+        <v>0.0007494</v>
+      </c>
+      <c r="AD469" s="2" t="n">
+        <v>0.0009349539201281725</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -41869,6 +44689,12 @@
       <c r="AB470" s="3" t="n">
         <v>-0.001126126126126127</v>
       </c>
+      <c r="AC470" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AD470" s="2" t="n">
+        <v>0.02029312288613305</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -41957,6 +44783,12 @@
       <c r="AB471" s="2" t="n">
         <v>0.001009081735620544</v>
       </c>
+      <c r="AC471" s="1" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="AD471" s="2" t="n">
+        <v>0.005040322580645131</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -42045,6 +44877,12 @@
       <c r="AB472" s="2" t="n">
         <v>0.001285347043701747</v>
       </c>
+      <c r="AC472" s="1" t="n">
+        <v>0.04692</v>
+      </c>
+      <c r="AD472" s="2" t="n">
+        <v>0.003851091142490513</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -42133,6 +44971,12 @@
       <c r="AB473" s="3" t="n">
         <v>-0.002548234437568178</v>
       </c>
+      <c r="AC473" s="1" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AD473" s="2" t="n">
+        <v>0.001459854014598379</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -42221,6 +45065,12 @@
       <c r="AB474" s="2" t="n">
         <v>0.0009124087591242088</v>
       </c>
+      <c r="AC474" s="1" t="n">
+        <v>0.04397</v>
+      </c>
+      <c r="AD474" s="2" t="n">
+        <v>0.002051048313582493</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -42309,6 +45159,12 @@
       <c r="AB475" s="3" t="n">
         <v>-0.002480217314278987</v>
       </c>
+      <c r="AC475" s="1" t="n">
+        <v>0.008463</v>
+      </c>
+      <c r="AD475" s="2" t="n">
+        <v>0.002012787118162403</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -42397,6 +45253,12 @@
       <c r="AB476" s="3" t="n">
         <v>-0.004252733900364558</v>
       </c>
+      <c r="AC476" s="1" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="AD476" s="3" t="n">
+        <v>-0.002562538133007955</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -42485,6 +45347,12 @@
       <c r="AB477" s="3" t="n">
         <v>-0.002939015429831091</v>
       </c>
+      <c r="AC477" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="AD477" s="2" t="n">
+        <v>0.001473839351510728</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -42573,6 +45441,12 @@
       <c r="AB478" s="2" t="n">
         <v>0.005269761606022562</v>
       </c>
+      <c r="AC478" s="1" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="AD478" s="2" t="n">
+        <v>0.002246630054917653</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -42661,6 +45535,12 @@
       <c r="AB479" s="3" t="n">
         <v>-0.02261918570931455</v>
       </c>
+      <c r="AC479" s="1" t="n">
+        <v>0.008463999999999999</v>
+      </c>
+      <c r="AD479" s="2" t="n">
+        <v>0.004509850462853055</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -42749,6 +45629,12 @@
       <c r="AB480" s="2" t="n">
         <v>0.041796631316282</v>
       </c>
+      <c r="AC480" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="AD480" s="2" t="n">
+        <v>0.2640718562874252</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -42837,6 +45723,12 @@
       <c r="AB481" s="3" t="n">
         <v>-0.001658586374075084</v>
       </c>
+      <c r="AC481" s="1" t="n">
+        <v>0.07761999999999999</v>
+      </c>
+      <c r="AD481" s="3" t="n">
+        <v>-0.008051118210862691</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -42925,6 +45817,12 @@
       <c r="AB482" s="3" t="n">
         <v>-0.003959611958028089</v>
       </c>
+      <c r="AC482" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="AD482" s="3" t="n">
+        <v>-0.002186444046909143</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -43013,6 +45911,12 @@
       <c r="AB483" s="3" t="n">
         <v>-0.005149330587023656</v>
       </c>
+      <c r="AC483" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="AD483" s="2" t="n">
+        <v>0.001035196687370558</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -43101,6 +46005,12 @@
       <c r="AB484" s="3" t="n">
         <v>-0.001764965436093471</v>
       </c>
+      <c r="AC484" s="1" t="n">
+        <v>0.06811</v>
+      </c>
+      <c r="AD484" s="2" t="n">
+        <v>0.003536172093708621</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -43189,6 +46099,12 @@
       <c r="AB485" s="3" t="n">
         <v>-0.00837927232635069</v>
       </c>
+      <c r="AC485" s="1" t="n">
+        <v>0.0004512</v>
+      </c>
+      <c r="AD485" s="2" t="n">
+        <v>0.003335557038025432</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -43277,6 +46193,12 @@
       <c r="AB486" s="3" t="n">
         <v>-0.0003783579265985906</v>
       </c>
+      <c r="AC486" s="1" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="AD486" s="3" t="n">
+        <v>-0.0007570022710066946</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -43365,6 +46287,12 @@
       <c r="AB487" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC487" s="1" t="n">
+        <v>0.0001757</v>
+      </c>
+      <c r="AD487" s="2" t="n">
+        <v>0.01151410477835345</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -43453,6 +46381,12 @@
       <c r="AB488" s="2" t="n">
         <v>0.004012930554007348</v>
       </c>
+      <c r="AC488" s="1" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="AD488" s="3" t="n">
+        <v>-0.002886643721549865</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -43541,6 +46475,12 @@
       <c r="AB489" s="2" t="n">
         <v>0.005003126954346552</v>
       </c>
+      <c r="AC489" s="1" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="AD489" s="2" t="n">
+        <v>0.002281684297863493</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -43629,6 +46569,12 @@
       <c r="AB490" s="2" t="n">
         <v>0.009923664122137441</v>
       </c>
+      <c r="AC490" s="1" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="AD490" s="3" t="n">
+        <v>-0.01486520534139582</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -43717,6 +46663,12 @@
       <c r="AB491" s="3" t="n">
         <v>-0.02200875486381314</v>
       </c>
+      <c r="AC491" s="1" t="n">
+        <v>0.08166</v>
+      </c>
+      <c r="AD491" s="2" t="n">
+        <v>0.01529280119358442</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -43805,6 +46757,12 @@
       <c r="AB492" s="2" t="n">
         <v>0.004442329049658932</v>
       </c>
+      <c r="AC492" s="1" t="n">
+        <v>0.06325</v>
+      </c>
+      <c r="AD492" s="3" t="n">
+        <v>-0.0009477175801611829</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -43893,6 +46851,12 @@
       <c r="AB493" s="3" t="n">
         <v>-0.001912045889101426</v>
       </c>
+      <c r="AC493" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="AD493" s="2" t="n">
+        <v>0.001915708812260625</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -43981,6 +46945,12 @@
       <c r="AB494" s="3" t="n">
         <v>-0.003266787658802221</v>
       </c>
+      <c r="AC494" s="1" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AD494" s="2" t="n">
+        <v>0.0007283321194463874</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -44069,6 +47039,12 @@
       <c r="AB495" s="3" t="n">
         <v>-0.002813379180994055</v>
       </c>
+      <c r="AC495" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AD495" s="2" t="n">
+        <v>0.003134796238244604</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -44157,6 +47133,12 @@
       <c r="AB496" s="3" t="n">
         <v>-0.0013614703880191</v>
       </c>
+      <c r="AC496" s="1" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AD496" s="2" t="n">
+        <v>0.0003408316291751499</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -44245,6 +47227,12 @@
       <c r="AB497" s="3" t="n">
         <v>-0.01443816698053984</v>
       </c>
+      <c r="AC497" s="1" t="n">
+        <v>0.07869</v>
+      </c>
+      <c r="AD497" s="2" t="n">
+        <v>0.002420382165605041</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -44333,6 +47321,12 @@
       <c r="AB498" s="3" t="n">
         <v>-0.003872216844143248</v>
       </c>
+      <c r="AC498" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AD498" s="2" t="n">
+        <v>0.0009718172983478035</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -44421,6 +47415,12 @@
       <c r="AB499" s="3" t="n">
         <v>-0.003098927294398049</v>
       </c>
+      <c r="AC499" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AD499" s="2" t="n">
+        <v>0.006695361071257664</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -44509,6 +47509,12 @@
       <c r="AB500" s="3" t="n">
         <v>-0.003968253968253978</v>
       </c>
+      <c r="AC500" s="1" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="AD500" s="3" t="n">
+        <v>-0.003735059760956282</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -44597,6 +47603,12 @@
       <c r="AB501" s="3" t="n">
         <v>-0.001007049345417954</v>
       </c>
+      <c r="AC501" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="AD501" s="2" t="n">
+        <v>0.003024193548387183</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -44685,6 +47697,12 @@
       <c r="AB502" s="2" t="n">
         <v>0.002416188462700018</v>
       </c>
+      <c r="AC502" s="1" t="n">
+        <v>0.003324</v>
+      </c>
+      <c r="AD502" s="2" t="n">
+        <v>0.001506477854775604</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -44773,6 +47791,12 @@
       <c r="AB503" s="3" t="n">
         <v>-0.003275109170305733</v>
       </c>
+      <c r="AC503" s="1" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="AD503" s="3" t="n">
+        <v>-0.001095290251916713</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -44861,6 +47885,12 @@
       <c r="AB504" s="3" t="n">
         <v>-0.001253132832080236</v>
       </c>
+      <c r="AC504" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AD504" s="2" t="n">
+        <v>0.002509410288582255</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -44949,6 +47979,12 @@
       <c r="AB505" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC505" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AD505" s="2" t="n">
+        <v>0.002277904328018183</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -45037,6 +48073,12 @@
       <c r="AB506" s="2" t="n">
         <v>0.004689331770222756</v>
       </c>
+      <c r="AC506" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="AD506" s="2" t="n">
+        <v>0.0005834305717619366</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -45125,6 +48167,12 @@
       <c r="AB507" s="2" t="n">
         <v>0.002102312543798153</v>
       </c>
+      <c r="AC507" s="1" t="n">
+        <v>0.002861</v>
+      </c>
+      <c r="AD507" s="2" t="n">
+        <v>0.0003496503496502444</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -45213,6 +48261,12 @@
       <c r="AB508" s="2" t="n">
         <v>0.001359311282283695</v>
       </c>
+      <c r="AC508" s="1" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="AD508" s="3" t="n">
+        <v>-0.001357466063348468</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -45301,6 +48355,12 @@
       <c r="AB509" s="3" t="n">
         <v>-0.002177858439201489</v>
       </c>
+      <c r="AC509" s="1" t="n">
+        <v>0.05498</v>
+      </c>
+      <c r="AD509" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -45389,6 +48449,12 @@
       <c r="AB510" s="3" t="n">
         <v>-0.002378525314305152</v>
       </c>
+      <c r="AC510" s="1" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="AD510" s="3" t="n">
+        <v>-0.002384196185286124</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -45477,6 +48543,12 @@
       <c r="AB511" s="3" t="n">
         <v>-0.00148441365660558</v>
       </c>
+      <c r="AC511" s="1" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="AD511" s="2" t="n">
+        <v>0.002725470763131788</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -45565,6 +48637,12 @@
       <c r="AB512" s="2" t="n">
         <v>0.0454545454545455</v>
       </c>
+      <c r="AC512" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD512" s="3" t="n">
+        <v>-0.02173913043478263</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -45653,6 +48731,12 @@
       <c r="AB513" s="2" t="n">
         <v>0.006780798925814058</v>
       </c>
+      <c r="AC513" s="1" t="n">
+        <v>0.015027</v>
+      </c>
+      <c r="AD513" s="2" t="n">
+        <v>0.002067217924779926</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -45741,6 +48825,12 @@
       <c r="AB514" s="3" t="n">
         <v>-0.002853881278538815</v>
       </c>
+      <c r="AC514" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="AD514" s="2" t="n">
+        <v>0.001144819690898716</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -45829,6 +48919,12 @@
       <c r="AB515" s="3" t="n">
         <v>-0.003703703703703681</v>
       </c>
+      <c r="AC515" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="AD515" s="2" t="n">
+        <v>0.001858736059479607</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -45917,6 +49013,12 @@
       <c r="AB516" s="3" t="n">
         <v>-0.007434944237918235</v>
       </c>
+      <c r="AC516" s="1" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="AD516" s="2" t="n">
+        <v>0.01498127340823974</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -46005,6 +49107,12 @@
       <c r="AB517" s="3" t="n">
         <v>-0.007501293326435578</v>
       </c>
+      <c r="AC517" s="1" t="n">
+        <v>0.007716</v>
+      </c>
+      <c r="AD517" s="2" t="n">
+        <v>0.005473025801407285</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -46093,6 +49201,12 @@
       <c r="AB518" s="3" t="n">
         <v>-0.02784360189573449</v>
       </c>
+      <c r="AC518" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="AD518" s="3" t="n">
+        <v>-0.03900060938452173</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -46181,6 +49295,12 @@
       <c r="AB519" s="2" t="n">
         <v>0.002140818268315761</v>
       </c>
+      <c r="AC519" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AD519" s="3" t="n">
+        <v>-0.005459292665558886</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -46269,6 +49389,12 @@
       <c r="AB520" s="3" t="n">
         <v>-0.0008598452278589131</v>
       </c>
+      <c r="AC520" s="1" t="n">
+        <v>0.001163</v>
+      </c>
+      <c r="AD520" s="2" t="n">
+        <v>0.0008605851979345231</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -46357,6 +49483,12 @@
       <c r="AB521" s="3" t="n">
         <v>-0.003739715781600576</v>
       </c>
+      <c r="AC521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="AD521" s="2" t="n">
+        <v>0.0007507507507507202</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -46445,6 +49577,12 @@
       <c r="AB522" s="3" t="n">
         <v>-0.001163467132053553</v>
       </c>
+      <c r="AC522" s="1" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="AD522" s="2" t="n">
+        <v>0.00189283634245789</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -46533,6 +49671,12 @@
       <c r="AB523" s="2" t="n">
         <v>0.0005709391949757118</v>
       </c>
+      <c r="AC523" s="1" t="n">
+        <v>0.07062</v>
+      </c>
+      <c r="AD523" s="2" t="n">
+        <v>0.00741797432239667</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -46621,6 +49765,12 @@
       <c r="AB524" s="2" t="n">
         <v>0.003418803418803427</v>
       </c>
+      <c r="AC524" s="1" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="AD524" s="2" t="n">
+        <v>0.0008517887563883809</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -46709,6 +49859,12 @@
       <c r="AB525" s="2" t="n">
         <v>0.0012165450121654</v>
       </c>
+      <c r="AC525" s="1" t="n">
+        <v>0.01645</v>
+      </c>
+      <c r="AD525" s="3" t="n">
+        <v>-0.0006075334143377639</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -46797,6 +49953,12 @@
       <c r="AB526" s="3" t="n">
         <v>-0.002156775249144613</v>
       </c>
+      <c r="AC526" s="1" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="AD526" s="3" t="n">
+        <v>-0.00372661548781397</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -46885,6 +50047,12 @@
       <c r="AB527" s="3" t="n">
         <v>-0.00139405204460977</v>
       </c>
+      <c r="AC527" s="1" t="n">
+        <v>0.04295</v>
+      </c>
+      <c r="AD527" s="3" t="n">
+        <v>-0.0006979990693344651</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -46973,6 +50141,12 @@
       <c r="AB528" s="2" t="n">
         <v>0.0007304601899197717</v>
       </c>
+      <c r="AC528" s="1" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AD528" s="2" t="n">
+        <v>0.004379562043795543</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -47061,6 +50235,12 @@
       <c r="AB529" s="3" t="n">
         <v>-0.001649031194173314</v>
       </c>
+      <c r="AC529" s="1" t="n">
+        <v>0.0007266</v>
+      </c>
+      <c r="AD529" s="2" t="n">
+        <v>0.0001376462491396397</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -47149,6 +50329,12 @@
       <c r="AB530" s="3" t="n">
         <v>-0.001195886151638315</v>
       </c>
+      <c r="AC530" s="1" t="n">
+        <v>0.004194</v>
+      </c>
+      <c r="AD530" s="2" t="n">
+        <v>0.004310344827586156</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -47237,6 +50423,12 @@
       <c r="AB531" s="3" t="n">
         <v>-0.003796507213363625</v>
       </c>
+      <c r="AC531" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AD531" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -47325,6 +50517,12 @@
       <c r="AB532" s="3" t="n">
         <v>-0.0008467400508044273</v>
       </c>
+      <c r="AC532" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AD532" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -47413,6 +50611,12 @@
       <c r="AB533" s="3" t="n">
         <v>-0.005585552038726525</v>
       </c>
+      <c r="AC533" s="1" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="AD533" s="2" t="n">
+        <v>0.002808462834675235</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -47501,6 +50705,12 @@
       <c r="AB534" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC534" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="AD534" s="2" t="n">
+        <v>0.0006648936170212034</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -47589,6 +50799,12 @@
       <c r="AB535" s="2" t="n">
         <v>0.004640371229698389</v>
       </c>
+      <c r="AC535" s="1" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="AD535" s="2" t="n">
+        <v>0.008660508083140925</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -47677,6 +50893,12 @@
       <c r="AB536" s="3" t="n">
         <v>-0.001396926761125536</v>
       </c>
+      <c r="AC536" s="1" t="n">
+        <v>0.005014</v>
+      </c>
+      <c r="AD536" s="2" t="n">
+        <v>0.00199840127897691</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -47765,6 +50987,12 @@
       <c r="AB537" s="3" t="n">
         <v>-0.003414134516899969</v>
       </c>
+      <c r="AC537" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AD537" s="2" t="n">
+        <v>0.00205549845837612</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -47853,6 +51081,12 @@
       <c r="AB538" s="3" t="n">
         <v>-0.005243445692883941</v>
       </c>
+      <c r="AC538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AD538" s="3" t="n">
+        <v>-0.0007530120481927404</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -47941,6 +51175,12 @@
       <c r="AB539" s="3" t="n">
         <v>-0.003168316831683176</v>
       </c>
+      <c r="AC539" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="AD539" s="2" t="n">
+        <v>0.001191895113229987</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -48029,6 +51269,12 @@
       <c r="AB540" s="2" t="n">
         <v>0.00017599436818015</v>
       </c>
+      <c r="AC540" s="1" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="AD540" s="2" t="n">
+        <v>0.004575048389934951</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -48117,6 +51363,12 @@
       <c r="AB541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AC541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="AD541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -48205,6 +51457,12 @@
       <c r="AB542" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="AC542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AD542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -48292,6 +51550,12 @@
       </c>
       <c r="AB543" s="3" t="n">
         <v>-0.0005433306166802043</v>
+      </c>
+      <c r="AC543" s="1" t="n">
+        <v>0.003683</v>
+      </c>
+      <c r="AD543" s="2" t="n">
+        <v>0.001087251970644223</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ543"/>
+  <dimension ref="A1:AL543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,8 @@
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,6 +647,16 @@
           <t>change_04:15</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>price_04:30</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>change_04:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -757,6 +769,12 @@
       <c r="AJ2" s="3" t="n">
         <v>-0.002993910211018187</v>
       </c>
+      <c r="AK2" s="1" t="n">
+        <v>70399.2</v>
+      </c>
+      <c r="AL2" s="2" t="n">
+        <v>8.522896762027496e-06</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -869,6 +887,12 @@
       <c r="AJ3" s="3" t="n">
         <v>-0.003680916567497279</v>
       </c>
+      <c r="AK3" s="1" t="n">
+        <v>2068.62</v>
+      </c>
+      <c r="AL3" s="2" t="n">
+        <v>0.0003336670003336934</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -981,6 +1005,12 @@
       <c r="AJ4" s="3" t="n">
         <v>-0.001375831231369004</v>
       </c>
+      <c r="AK4" s="1" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>-0.0005740528128587504</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1093,6 +1123,12 @@
       <c r="AJ5" s="3" t="n">
         <v>-0.0101408039687751</v>
       </c>
+      <c r="AK5" s="1" t="n">
+        <v>0.013701</v>
+      </c>
+      <c r="AL5" s="2" t="n">
+        <v>0.009802476415094298</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1205,6 +1241,12 @@
       <c r="AJ6" s="3" t="n">
         <v>-0.00287785120443409</v>
       </c>
+      <c r="AK6" s="1" t="n">
+        <v>0.09343</v>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>-0.001282736504542973</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1317,6 +1359,12 @@
       <c r="AJ7" s="3" t="n">
         <v>-0.0002879562306529091</v>
       </c>
+      <c r="AK7" s="1" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <v>-0.0005040685533233563</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1429,6 +1477,12 @@
       <c r="AJ8" s="3" t="n">
         <v>-0.005065242526014356</v>
       </c>
+      <c r="AK8" s="1" t="n">
+        <v>35.975</v>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <v>-0.004620662940623141</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1541,6 +1595,12 @@
       <c r="AJ9" s="3" t="n">
         <v>-0.001882547408053658</v>
       </c>
+      <c r="AK9" s="1" t="n">
+        <v>652.09</v>
+      </c>
+      <c r="AL9" s="3" t="n">
+        <v>-7.667065354058105e-05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1653,6 +1713,12 @@
       <c r="AJ10" s="2" t="n">
         <v>0.002069211559043875</v>
       </c>
+      <c r="AK10" s="1" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>0.001139276559384792</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1765,6 +1831,12 @@
       <c r="AJ11" s="3" t="n">
         <v>-0.005004209147881364</v>
       </c>
+      <c r="AK11" s="1" t="n">
+        <v>212.94</v>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>0.000893066980023491</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1877,6 +1949,12 @@
       <c r="AJ12" s="3" t="n">
         <v>-0.003505540536525874</v>
       </c>
+      <c r="AK12" s="1" t="n">
+        <v>0.0033469</v>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>-0.002206123483290191</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1989,6 +2067,12 @@
       <c r="AJ13" s="3" t="n">
         <v>-0.007992007992008013</v>
       </c>
+      <c r="AK13" s="1" t="n">
+        <v>0.04004</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>0.008056394763343425</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2101,6 +2185,12 @@
       <c r="AJ14" s="2" t="n">
         <v>0.003767897513187729</v>
       </c>
+      <c r="AK14" s="1" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>0.001501501501501503</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2213,6 +2303,12 @@
       <c r="AJ15" s="3" t="n">
         <v>-0.006050216799435318</v>
       </c>
+      <c r="AK15" s="1" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <v>-0.002840620878563482</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2325,6 +2421,12 @@
       <c r="AJ16" s="2" t="n">
         <v>0.006411398040961695</v>
       </c>
+      <c r="AK16" s="1" t="n">
+        <v>0.05666</v>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>0.002654397451778522</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2437,6 +2539,12 @@
       <c r="AJ17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK17" s="1" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>-0.002257336343115126</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2549,6 +2657,12 @@
       <c r="AJ18" s="3" t="n">
         <v>-0.003770739064856715</v>
       </c>
+      <c r="AK18" s="1" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>-0.001892505677517034</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2661,6 +2775,12 @@
       <c r="AJ19" s="3" t="n">
         <v>-0.01332886243608013</v>
       </c>
+      <c r="AK19" s="1" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>0.01294250920419134</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2773,6 +2893,12 @@
       <c r="AJ20" s="3" t="n">
         <v>-0.003092783505154574</v>
       </c>
+      <c r="AK20" s="1" t="n">
+        <v>9.651</v>
+      </c>
+      <c r="AL20" s="3" t="n">
+        <v>-0.001964839710444687</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2885,6 +3011,12 @@
       <c r="AJ21" s="2" t="n">
         <v>0.002628446736758586</v>
       </c>
+      <c r="AK21" s="1" t="n">
+        <v>200.61</v>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>-0.007716278379581411</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2997,6 +3129,12 @@
       <c r="AJ22" s="3" t="n">
         <v>-0.02336357428543558</v>
       </c>
+      <c r="AK22" s="1" t="n">
+        <v>0.019845</v>
+      </c>
+      <c r="AL22" s="3" t="n">
+        <v>-0.008889776756729641</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3109,6 +3247,12 @@
       <c r="AJ23" s="3" t="n">
         <v>-0.0004371106982843157</v>
       </c>
+      <c r="AK23" s="1" t="n">
+        <v>456.63</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>-0.001574286651361162</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3221,6 +3365,12 @@
       <c r="AJ24" s="3" t="n">
         <v>-0.0009476203342725624</v>
       </c>
+      <c r="AK24" s="1" t="n">
+        <v>5176.33</v>
+      </c>
+      <c r="AL24" s="3" t="n">
+        <v>-3.090897500040655e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3333,6 +3483,12 @@
       <c r="AJ25" s="3" t="n">
         <v>-0.002972586149950569</v>
       </c>
+      <c r="AK25" s="1" t="n">
+        <v>9.041</v>
+      </c>
+      <c r="AL25" s="3" t="n">
+        <v>-0.001656360424028135</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3445,6 +3601,12 @@
       <c r="AJ26" s="2" t="n">
         <v>0.008181511470985144</v>
       </c>
+      <c r="AK26" s="1" t="n">
+        <v>0.11874</v>
+      </c>
+      <c r="AL26" s="3" t="n">
+        <v>-0.006609219442817694</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3557,6 +3719,12 @@
       <c r="AJ27" s="3" t="n">
         <v>-0.008583690987124561</v>
       </c>
+      <c r="AK27" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>0.004329004329004303</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3669,6 +3837,12 @@
       <c r="AJ28" s="3" t="n">
         <v>-0.0007722007722006872</v>
       </c>
+      <c r="AK28" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AL28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3781,6 +3955,12 @@
       <c r="AJ29" s="2" t="n">
         <v>0.001565489650373975</v>
       </c>
+      <c r="AK29" s="1" t="n">
+        <v>0.05854</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>0.01667245571378955</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3893,6 +4073,12 @@
       <c r="AJ30" s="2" t="n">
         <v>0.001300390117035112</v>
       </c>
+      <c r="AK30" s="1" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>-0.005844155844155922</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4005,6 +4191,12 @@
       <c r="AJ31" s="2" t="n">
         <v>0.0004955401387513047</v>
       </c>
+      <c r="AK31" s="1" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>0.0009905894006933293</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4117,6 +4309,12 @@
       <c r="AJ32" s="3" t="n">
         <v>-0.003741581441755983</v>
       </c>
+      <c r="AK32" s="1" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>-0.0005007511266901883</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4229,6 +4427,12 @@
       <c r="AJ33" s="3" t="n">
         <v>-0.004060913705583731</v>
       </c>
+      <c r="AK33" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4341,6 +4545,12 @@
       <c r="AJ34" s="3" t="n">
         <v>-0.002840909090909041</v>
       </c>
+      <c r="AK34" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AL34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4453,6 +4663,12 @@
       <c r="AJ35" s="2" t="n">
         <v>0.006764374295377793</v>
       </c>
+      <c r="AK35" s="1" t="n">
+        <v>0.00891</v>
+      </c>
+      <c r="AL35" s="3" t="n">
+        <v>-0.002239641657334929</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4565,6 +4781,12 @@
       <c r="AJ36" s="3" t="n">
         <v>-0.001950947603121611</v>
       </c>
+      <c r="AK36" s="1" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>-0.001954761239877069</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4677,6 +4899,12 @@
       <c r="AJ37" s="3" t="n">
         <v>-0.001035018112816962</v>
       </c>
+      <c r="AK37" s="1" t="n">
+        <v>0.005777</v>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>-0.002417544465550013</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4789,6 +5017,12 @@
       <c r="AJ38" s="2" t="n">
         <v>0.001768482565068686</v>
       </c>
+      <c r="AK38" s="1" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="AL38" s="3" t="n">
+        <v>-0.001573473538780448</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4901,6 +5135,12 @@
       <c r="AJ39" s="3" t="n">
         <v>-0.000595001983339989</v>
       </c>
+      <c r="AK39" s="1" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="AL39" s="3" t="n">
+        <v>-0.003373685255010847</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5013,6 +5253,12 @@
       <c r="AJ40" s="2" t="n">
         <v>0.006043107500167758</v>
       </c>
+      <c r="AK40" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="AL40" s="3" t="n">
+        <v>-0.0002002269238470416</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5125,6 +5371,12 @@
       <c r="AJ41" s="3" t="n">
         <v>-0.005906674542232728</v>
       </c>
+      <c r="AK41" s="1" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>-0.001782531194295869</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5237,6 +5489,12 @@
       <c r="AJ42" s="3" t="n">
         <v>-0.003119707638826939</v>
       </c>
+      <c r="AK42" s="1" t="n">
+        <v>111.16</v>
+      </c>
+      <c r="AL42" s="3" t="n">
+        <v>-0.006080114449213222</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5349,6 +5607,12 @@
       <c r="AJ43" s="2" t="n">
         <v>0.04143678835544078</v>
       </c>
+      <c r="AK43" s="1" t="n">
+        <v>0.8498</v>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>-0.04215509467989178</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5461,6 +5725,12 @@
       <c r="AJ44" s="3" t="n">
         <v>-0.001090512540894262</v>
       </c>
+      <c r="AK44" s="1" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AL44" s="3" t="n">
+        <v>-0.001273653566229991</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5573,6 +5843,12 @@
       <c r="AJ45" s="3" t="n">
         <v>-0.001104740862078865</v>
       </c>
+      <c r="AK45" s="1" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>0.008733291383025435</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5685,6 +5961,12 @@
       <c r="AJ46" s="2" t="n">
         <v>0.0005721642111285309</v>
       </c>
+      <c r="AK46" s="1" t="n">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>0.0008577555396710992</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5797,6 +6079,12 @@
       <c r="AJ47" s="3" t="n">
         <v>-0.000254841997961236</v>
       </c>
+      <c r="AK47" s="1" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="AL47" s="3" t="n">
+        <v>-0.001529441753759936</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5909,6 +6197,12 @@
       <c r="AJ48" s="3" t="n">
         <v>-0.001813406703351754</v>
       </c>
+      <c r="AK48" s="1" t="n">
+        <v>0.15957</v>
+      </c>
+      <c r="AL48" s="3" t="n">
+        <v>-0.0003758691975192915</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6021,6 +6315,12 @@
       <c r="AJ49" s="3" t="n">
         <v>-0.01436410587475794</v>
       </c>
+      <c r="AK49" s="1" t="n">
+        <v>0.06074</v>
+      </c>
+      <c r="AL49" s="3" t="n">
+        <v>-0.00540363517275253</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6133,6 +6433,12 @@
       <c r="AJ50" s="3" t="n">
         <v>-0.005128205128205097</v>
       </c>
+      <c r="AK50" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>0.002577319587628761</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6245,6 +6551,12 @@
       <c r="AJ51" s="3" t="n">
         <v>-0.02340448201157789</v>
       </c>
+      <c r="AK51" s="1" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="AL51" s="2" t="n">
+        <v>0.00101825587315442</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6357,6 +6669,12 @@
       <c r="AJ52" s="2" t="n">
         <v>0.0006818956699624206</v>
       </c>
+      <c r="AK52" s="1" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>0.004088586030664513</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6469,6 +6787,12 @@
       <c r="AJ53" s="3" t="n">
         <v>-0.0006246096189880636</v>
       </c>
+      <c r="AK53" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="AL53" s="3" t="n">
+        <v>-0.003750000000000107</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6581,6 +6905,12 @@
       <c r="AJ54" s="2" t="n">
         <v>0.001206272617611447</v>
       </c>
+      <c r="AK54" s="1" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AL54" s="2" t="n">
+        <v>0.001652323580034547</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6693,6 +7023,12 @@
       <c r="AJ55" s="3" t="n">
         <v>-0.002242466713384656</v>
       </c>
+      <c r="AK55" s="1" t="n">
+        <v>0.007118</v>
+      </c>
+      <c r="AL55" s="3" t="n">
+        <v>-0.0001404691670178582</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6805,6 +7141,12 @@
       <c r="AJ56" s="3" t="n">
         <v>-0.01615675489859064</v>
       </c>
+      <c r="AK56" s="1" t="n">
+        <v>0.02878</v>
+      </c>
+      <c r="AL56" s="2" t="n">
+        <v>0.005590496156533907</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6917,6 +7259,12 @@
       <c r="AJ57" s="3" t="n">
         <v>-0.00379957254808835</v>
       </c>
+      <c r="AK57" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AL57" s="2" t="n">
+        <v>0.001907032181167979</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7029,6 +7377,12 @@
       <c r="AJ58" s="3" t="n">
         <v>-0.006580300226197837</v>
       </c>
+      <c r="AK58" s="1" t="n">
+        <v>0.04819</v>
+      </c>
+      <c r="AL58" s="3" t="n">
+        <v>-0.002483957772717906</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7141,6 +7495,12 @@
       <c r="AJ59" s="3" t="n">
         <v>-0.004530744336569512</v>
       </c>
+      <c r="AK59" s="1" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="AL59" s="3" t="n">
+        <v>-0.003901170351105335</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7253,6 +7613,12 @@
       <c r="AJ60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AL60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7365,6 +7731,12 @@
       <c r="AJ61" s="3" t="n">
         <v>-0.001928020565552665</v>
       </c>
+      <c r="AK61" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="AL61" s="3" t="n">
+        <v>-0.001287830006439187</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7477,6 +7849,12 @@
       <c r="AJ62" s="3" t="n">
         <v>-0.0008771929824560438</v>
       </c>
+      <c r="AK62" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="AL62" s="2" t="n">
+        <v>0.002633889376646086</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7589,6 +7967,12 @@
       <c r="AJ63" s="3" t="n">
         <v>-0.001567621490665512</v>
       </c>
+      <c r="AK63" s="1" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="AL63" s="2" t="n">
+        <v>0.0004282043962317542</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7701,6 +8085,12 @@
       <c r="AJ64" s="3" t="n">
         <v>-0.003072721065209934</v>
       </c>
+      <c r="AK64" s="1" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="AL64" s="3" t="n">
+        <v>-0.002054794520547871</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7813,6 +8203,12 @@
       <c r="AJ65" s="3" t="n">
         <v>-0.002119542178889421</v>
       </c>
+      <c r="AK65" s="1" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="AL65" s="3" t="n">
+        <v>-0.000849617672047544</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7925,6 +8321,12 @@
       <c r="AJ66" s="3" t="n">
         <v>-0.0009881422924901469</v>
       </c>
+      <c r="AK66" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="AL66" s="3" t="n">
+        <v>-0.001978239366963322</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8037,6 +8439,12 @@
       <c r="AJ67" s="3" t="n">
         <v>-0.005376344086021501</v>
       </c>
+      <c r="AK67" s="1" t="n">
+        <v>0.007233</v>
+      </c>
+      <c r="AL67" s="2" t="n">
+        <v>0.002494802494802465</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8149,6 +8557,12 @@
       <c r="AJ68" s="2" t="n">
         <v>0.0005428881650378941</v>
       </c>
+      <c r="AK68" s="1" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="AL68" s="3" t="n">
+        <v>-0.002712967986977792</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8261,6 +8675,12 @@
       <c r="AJ69" s="2" t="n">
         <v>0.001288659793814444</v>
       </c>
+      <c r="AK69" s="1" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="AL69" s="2" t="n">
+        <v>0.007538150395293264</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8373,6 +8793,12 @@
       <c r="AJ70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK70" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AL70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8485,6 +8911,12 @@
       <c r="AJ71" s="2" t="n">
         <v>0.0005263157894737041</v>
       </c>
+      <c r="AK71" s="1" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="AL71" s="2" t="n">
+        <v>0.007013852358407862</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8597,6 +9029,12 @@
       <c r="AJ72" s="3" t="n">
         <v>-0.02522935779816525</v>
       </c>
+      <c r="AK72" s="1" t="n">
+        <v>0.001728</v>
+      </c>
+      <c r="AL72" s="2" t="n">
+        <v>0.01647058823529414</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8709,6 +9147,12 @@
       <c r="AJ73" s="3" t="n">
         <v>-0.001485884101040191</v>
       </c>
+      <c r="AK73" s="1" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="AL73" s="3" t="n">
+        <v>-0.002125850340136056</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8821,6 +9265,12 @@
       <c r="AJ74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK74" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>-0.001659751037344331</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8933,6 +9383,12 @@
       <c r="AJ75" s="3" t="n">
         <v>-0.0004785227720543149</v>
       </c>
+      <c r="AK75" s="1" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="AL75" s="2" t="n">
+        <v>0.002872511194345205</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9045,6 +9501,12 @@
       <c r="AJ76" s="3" t="n">
         <v>-0.0007694938440491867</v>
       </c>
+      <c r="AK76" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="AL76" s="2" t="n">
+        <v>0.007101908103020428</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9157,6 +9619,12 @@
       <c r="AJ77" s="3" t="n">
         <v>-0.003339694656488579</v>
       </c>
+      <c r="AK77" s="1" t="n">
+        <v>0.06272</v>
+      </c>
+      <c r="AL77" s="2" t="n">
+        <v>0.0007978299026646639</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9269,6 +9737,12 @@
       <c r="AJ78" s="3" t="n">
         <v>-0.003900896151818758</v>
       </c>
+      <c r="AK78" s="1" t="n">
+        <v>0.09458</v>
+      </c>
+      <c r="AL78" s="2" t="n">
+        <v>0.001058425063505534</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9381,6 +9855,12 @@
       <c r="AJ79" s="2" t="n">
         <v>0.004699480583724988</v>
       </c>
+      <c r="AK79" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AL79" s="2" t="n">
+        <v>0.004431314623338179</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9493,6 +9973,12 @@
       <c r="AJ80" s="3" t="n">
         <v>-0.003501750875437605</v>
       </c>
+      <c r="AK80" s="1" t="n">
+        <v>0.005975</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>-0.0001673360107095269</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9605,6 +10091,12 @@
       <c r="AJ81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK81" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>-0.002941176470588184</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9717,6 +10209,12 @@
       <c r="AJ82" s="3" t="n">
         <v>-0.002961500493583364</v>
       </c>
+      <c r="AK82" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9829,6 +10327,12 @@
       <c r="AJ83" s="3" t="n">
         <v>-0.002260981912144723</v>
       </c>
+      <c r="AK83" s="1" t="n">
+        <v>0.06141</v>
+      </c>
+      <c r="AL83" s="3" t="n">
+        <v>-0.005988993201683429</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9941,6 +10445,12 @@
       <c r="AJ84" s="3" t="n">
         <v>-0.0005409304002884366</v>
       </c>
+      <c r="AK84" s="1" t="n">
+        <v>1.1059</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>-0.002435504239581386</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10053,6 +10563,12 @@
       <c r="AJ85" s="2" t="n">
         <v>0.001547987616099142</v>
       </c>
+      <c r="AK85" s="1" t="n">
+        <v>0.01291</v>
+      </c>
+      <c r="AL85" s="3" t="n">
+        <v>-0.00231839258114378</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10165,6 +10681,12 @@
       <c r="AJ86" s="3" t="n">
         <v>-0.002389486260454112</v>
       </c>
+      <c r="AK86" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10277,6 +10799,12 @@
       <c r="AJ87" s="3" t="n">
         <v>-0.0001201634222541992</v>
       </c>
+      <c r="AK87" s="1" t="n">
+        <v>8.311999999999999</v>
+      </c>
+      <c r="AL87" s="3" t="n">
+        <v>-0.001081600769138366</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10389,6 +10917,12 @@
       <c r="AJ88" s="2" t="n">
         <v>0.000606032352804102</v>
       </c>
+      <c r="AK88" s="1" t="n">
+        <v>2.1503</v>
+      </c>
+      <c r="AL88" s="2" t="n">
+        <v>0.001816995900111925</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10501,6 +11035,12 @@
       <c r="AJ89" s="2" t="n">
         <v>0.009982886480319416</v>
       </c>
+      <c r="AK89" s="1" t="n">
+        <v>0.007075</v>
+      </c>
+      <c r="AL89" s="3" t="n">
+        <v>-0.0009884213499011666</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10613,6 +11153,12 @@
       <c r="AJ90" s="3" t="n">
         <v>-0.001965923984272566</v>
       </c>
+      <c r="AK90" s="1" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AL90" s="3" t="n">
+        <v>-0.003939592908732797</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10725,6 +11271,12 @@
       <c r="AJ91" s="2" t="n">
         <v>0.004504504504504491</v>
       </c>
+      <c r="AK91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>-0.004484304932735414</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10837,6 +11389,12 @@
       <c r="AJ92" s="2" t="n">
         <v>0.004225081620895044</v>
       </c>
+      <c r="AK92" s="1" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="AL92" s="3" t="n">
+        <v>-0.003442340791738507</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10949,6 +11507,12 @@
       <c r="AJ93" s="3" t="n">
         <v>-0.001802072383240862</v>
       </c>
+      <c r="AK93" s="1" t="n">
+        <v>1.3295</v>
+      </c>
+      <c r="AL93" s="2" t="n">
+        <v>7.522190461861666e-05</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11061,6 +11625,12 @@
       <c r="AJ94" s="2" t="n">
         <v>0.005694907757238371</v>
       </c>
+      <c r="AK94" s="1" t="n">
+        <v>0.054415</v>
+      </c>
+      <c r="AL94" s="3" t="n">
+        <v>-0.002803841079020678</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11173,6 +11743,12 @@
       <c r="AJ95" s="2" t="n">
         <v>0.003331945022907102</v>
       </c>
+      <c r="AK95" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="AL95" s="2" t="n">
+        <v>0.003735990037359835</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11285,6 +11861,12 @@
       <c r="AJ96" s="2" t="n">
         <v>0.003727518404622126</v>
       </c>
+      <c r="AK96" s="1" t="n">
+        <v>1.0777</v>
+      </c>
+      <c r="AL96" s="2" t="n">
+        <v>0.0005570513415654591</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11397,6 +11979,12 @@
       <c r="AJ97" s="3" t="n">
         <v>-0.003101977510663136</v>
       </c>
+      <c r="AK97" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AL97" s="3" t="n">
+        <v>-0.00427849085958767</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11509,6 +12097,12 @@
       <c r="AJ98" s="2" t="n">
         <v>0.00242424242424235</v>
       </c>
+      <c r="AK98" s="1" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="AL98" s="2" t="n">
+        <v>0.007773363275177163</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11621,6 +12215,12 @@
       <c r="AJ99" s="3" t="n">
         <v>-0.003669587358646133</v>
       </c>
+      <c r="AK99" s="1" t="n">
+        <v>0.13241</v>
+      </c>
+      <c r="AL99" s="3" t="n">
+        <v>-0.004735417919422668</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11733,6 +12333,12 @@
       <c r="AJ100" s="2" t="n">
         <v>0.003511011809767186</v>
       </c>
+      <c r="AK100" s="1" t="n">
+        <v>0.03127</v>
+      </c>
+      <c r="AL100" s="3" t="n">
+        <v>-0.005407124681933952</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11845,6 +12451,12 @@
       <c r="AJ101" s="3" t="n">
         <v>-0.00286532951289388</v>
       </c>
+      <c r="AK101" s="1" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="AL101" s="3" t="n">
+        <v>-0.0009578544061303754</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11957,6 +12569,12 @@
       <c r="AJ102" s="2" t="n">
         <v>0.008163265306122431</v>
       </c>
+      <c r="AK102" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="AL102" s="3" t="n">
+        <v>-0.007197480881691427</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12069,6 +12687,12 @@
       <c r="AJ103" s="2" t="n">
         <v>0.003069053708439773</v>
       </c>
+      <c r="AK103" s="1" t="n">
+        <v>0.01957</v>
+      </c>
+      <c r="AL103" s="3" t="n">
+        <v>-0.002039775624681202</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12181,6 +12805,12 @@
       <c r="AJ104" s="3" t="n">
         <v>-0.0003327787021630249</v>
       </c>
+      <c r="AK104" s="1" t="n">
+        <v>3.002</v>
+      </c>
+      <c r="AL104" s="3" t="n">
+        <v>-0.0006657789613848948</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12293,6 +12923,12 @@
       <c r="AJ105" s="3" t="n">
         <v>-0.002461538461538409</v>
       </c>
+      <c r="AK105" s="1" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AL105" s="3" t="n">
+        <v>-0.0006169031462061421</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12405,6 +13041,12 @@
       <c r="AJ106" s="2" t="n">
         <v>0.001811594202898519</v>
       </c>
+      <c r="AK106" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="AL106" s="3" t="n">
+        <v>-0.001205545509343012</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12517,6 +13159,12 @@
       <c r="AJ107" s="3" t="n">
         <v>-0.005125919322487116</v>
       </c>
+      <c r="AK107" s="1" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="AL107" s="2" t="n">
+        <v>0.004928315412186334</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12629,6 +13277,12 @@
       <c r="AJ108" s="3" t="n">
         <v>-0.0002970885323826173</v>
       </c>
+      <c r="AK108" s="1" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AL108" s="2" t="n">
+        <v>0.000297176820207991</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12741,6 +13395,12 @@
       <c r="AJ109" s="3" t="n">
         <v>-0.01458241272646928</v>
       </c>
+      <c r="AK109" s="1" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="AL109" s="2" t="n">
+        <v>0.005381165919282541</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12853,6 +13513,12 @@
       <c r="AJ110" s="3" t="n">
         <v>-0.00397877984084876</v>
       </c>
+      <c r="AK110" s="1" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="AL110" s="2" t="n">
+        <v>0.0006657789613847931</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12965,6 +13631,12 @@
       <c r="AJ111" s="3" t="n">
         <v>-0.001633986928104637</v>
       </c>
+      <c r="AK111" s="1" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="AL111" s="3" t="n">
+        <v>-0.0005455537370430386</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13077,6 +13749,12 @@
       <c r="AJ112" s="2" t="n">
         <v>0.001308215593929917</v>
       </c>
+      <c r="AK112" s="1" t="n">
+        <v>0.03827</v>
+      </c>
+      <c r="AL112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13189,6 +13867,12 @@
       <c r="AJ113" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK113" s="1" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AL113" s="3" t="n">
+        <v>-0.0103189493433397</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13301,6 +13985,12 @@
       <c r="AJ114" s="2" t="n">
         <v>0.0009245806366398181</v>
       </c>
+      <c r="AK114" s="1" t="n">
+        <v>0.007504</v>
+      </c>
+      <c r="AL114" s="3" t="n">
+        <v>-0.009765109527579759</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13413,6 +14103,12 @@
       <c r="AJ115" s="3" t="n">
         <v>-0.004988526389304604</v>
       </c>
+      <c r="AK115" s="1" t="n">
+        <v>0.09977</v>
+      </c>
+      <c r="AL115" s="2" t="n">
+        <v>0.0004010829238944989</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13525,6 +14221,12 @@
       <c r="AJ116" s="3" t="n">
         <v>-0.001686340640809458</v>
       </c>
+      <c r="AK116" s="1" t="n">
+        <v>0.08276</v>
+      </c>
+      <c r="AL116" s="3" t="n">
+        <v>-0.001447876447876389</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13637,6 +14339,12 @@
       <c r="AJ117" s="3" t="n">
         <v>-0.001999333555481471</v>
       </c>
+      <c r="AK117" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL117" s="2" t="n">
+        <v>0.001669449081803007</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13749,6 +14457,12 @@
       <c r="AJ118" s="3" t="n">
         <v>-0.0008912655971480683</v>
       </c>
+      <c r="AK118" s="1" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="AL118" s="2" t="n">
+        <v>0.004906333630686996</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13861,6 +14575,12 @@
       <c r="AJ119" s="2" t="n">
         <v>0.002640264026402716</v>
       </c>
+      <c r="AK119" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="AL119" s="3" t="n">
+        <v>-0.001316655694535917</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13973,6 +14693,12 @@
       <c r="AJ120" s="2" t="n">
         <v>0.005383895131086248</v>
       </c>
+      <c r="AK120" s="1" t="n">
+        <v>0.004358</v>
+      </c>
+      <c r="AL120" s="2" t="n">
+        <v>0.01466821885913846</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14085,6 +14811,12 @@
       <c r="AJ121" s="3" t="n">
         <v>-0.001155802126675914</v>
       </c>
+      <c r="AK121" s="1" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="AL121" s="3" t="n">
+        <v>-0.005322841934737257</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14197,6 +14929,12 @@
       <c r="AJ122" s="3" t="n">
         <v>-0.001290322580645162</v>
       </c>
+      <c r="AK122" s="1" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AL122" s="3" t="n">
+        <v>-0.001291989664082688</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14309,6 +15047,12 @@
       <c r="AJ123" s="3" t="n">
         <v>-0.001156069364161722</v>
       </c>
+      <c r="AK123" s="1" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="AL123" s="3" t="n">
+        <v>-0.001157407407407441</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14421,6 +15165,12 @@
       <c r="AJ124" s="2" t="n">
         <v>0.006546644844517202</v>
       </c>
+      <c r="AK124" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="AL124" s="3" t="n">
+        <v>-0.005691056910569156</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14533,6 +15283,12 @@
       <c r="AJ125" s="3" t="n">
         <v>-0.00193936919465138</v>
       </c>
+      <c r="AK125" s="1" t="n">
+        <v>0.09782</v>
+      </c>
+      <c r="AL125" s="2" t="n">
+        <v>0.0004090816117815337</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14645,6 +15401,12 @@
       <c r="AJ126" s="2" t="n">
         <v>0.009001285897985357</v>
       </c>
+      <c r="AK126" s="1" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="AL126" s="2" t="n">
+        <v>0.0008496176720476914</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14757,6 +15519,12 @@
       <c r="AJ127" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK127" s="1" t="n">
+        <v>3.21e-05</v>
+      </c>
+      <c r="AL127" s="2" t="n">
+        <v>0.003125000000000076</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14869,6 +15637,12 @@
       <c r="AJ128" s="3" t="n">
         <v>-0.0005290072297656109</v>
       </c>
+      <c r="AK128" s="1" t="n">
+        <v>0.5671</v>
+      </c>
+      <c r="AL128" s="2" t="n">
+        <v>0.0005292872265350706</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14981,6 +15755,12 @@
       <c r="AJ129" s="2" t="n">
         <v>0.001547269070091118</v>
       </c>
+      <c r="AK129" s="1" t="n">
+        <v>0.06468</v>
+      </c>
+      <c r="AL129" s="3" t="n">
+        <v>-0.0007724393635098794</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15093,6 +15873,12 @@
       <c r="AJ130" s="3" t="n">
         <v>-0.005239030779305778</v>
       </c>
+      <c r="AK130" s="1" t="n">
+        <v>0.0006096</v>
+      </c>
+      <c r="AL130" s="2" t="n">
+        <v>0.003291639236339599</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15205,6 +15991,12 @@
       <c r="AJ131" s="2" t="n">
         <v>0.01149425287356323</v>
       </c>
+      <c r="AK131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AL131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15317,6 +16109,12 @@
       <c r="AJ132" s="3" t="n">
         <v>-0.002664890073284553</v>
       </c>
+      <c r="AK132" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL132" s="2" t="n">
+        <v>0.002004008016032029</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15429,6 +16227,12 @@
       <c r="AJ133" s="2" t="n">
         <v>0.0005871990604814793</v>
       </c>
+      <c r="AK133" s="1" t="n">
+        <v>0.03388</v>
+      </c>
+      <c r="AL133" s="3" t="n">
+        <v>-0.005868544600938932</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15541,6 +16345,12 @@
       <c r="AJ134" s="3" t="n">
         <v>-0.009206700816835094</v>
       </c>
+      <c r="AK134" s="1" t="n">
+        <v>0.14321</v>
+      </c>
+      <c r="AL134" s="2" t="n">
+        <v>0.0005589324390414081</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -15653,6 +16463,12 @@
       <c r="AJ135" s="3" t="n">
         <v>-0.002367264119039588</v>
       </c>
+      <c r="AK135" s="1" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="AL135" s="3" t="n">
+        <v>-0.001694915254237219</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15765,6 +16581,12 @@
       <c r="AJ136" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK136" s="1" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="AL136" s="2" t="n">
+        <v>0.004987531172069845</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15877,6 +16699,12 @@
       <c r="AJ137" s="3" t="n">
         <v>-0.0004606172270843042</v>
       </c>
+      <c r="AK137" s="1" t="n">
+        <v>0.0004341</v>
+      </c>
+      <c r="AL137" s="2" t="n">
+        <v>0.0002304147465437844</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15989,6 +16817,12 @@
       <c r="AJ138" s="3" t="n">
         <v>-0.003485170599100805</v>
       </c>
+      <c r="AK138" s="1" t="n">
+        <v>0.028711</v>
+      </c>
+      <c r="AL138" s="2" t="n">
+        <v>0.00412688420242717</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16101,6 +16935,12 @@
       <c r="AJ139" s="3" t="n">
         <v>-0.002693742229589685</v>
       </c>
+      <c r="AK139" s="1" t="n">
+        <v>0.09603</v>
+      </c>
+      <c r="AL139" s="3" t="n">
+        <v>-0.00238936214419275</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16213,6 +17053,12 @@
       <c r="AJ140" s="3" t="n">
         <v>-0.00332317917474378</v>
       </c>
+      <c r="AK140" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AL140" s="3" t="n">
+        <v>-0.003612114476243466</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16325,6 +17171,12 @@
       <c r="AJ141" s="3" t="n">
         <v>-0.0003772161448509843</v>
       </c>
+      <c r="AK141" s="1" t="n">
+        <v>0.02662</v>
+      </c>
+      <c r="AL141" s="2" t="n">
+        <v>0.00452830188679253</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16437,6 +17289,12 @@
       <c r="AJ142" s="3" t="n">
         <v>-0.002635872976026131</v>
       </c>
+      <c r="AK142" s="1" t="n">
+        <v>0.07944</v>
+      </c>
+      <c r="AL142" s="3" t="n">
+        <v>-0.0002516989680343081</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16549,6 +17407,12 @@
       <c r="AJ143" s="2" t="n">
         <v>0.001132887730825908</v>
       </c>
+      <c r="AK143" s="1" t="n">
+        <v>0.08833000000000001</v>
+      </c>
+      <c r="AL143" s="3" t="n">
+        <v>-0.0004526422994228626</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16661,6 +17525,12 @@
       <c r="AJ144" s="3" t="n">
         <v>-0.004852013585638011</v>
       </c>
+      <c r="AK144" s="1" t="n">
+        <v>0.02057</v>
+      </c>
+      <c r="AL144" s="2" t="n">
+        <v>0.002925402242808436</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -16773,6 +17643,12 @@
       <c r="AJ145" s="3" t="n">
         <v>-0.001225919439579696</v>
       </c>
+      <c r="AK145" s="1" t="n">
+        <v>0.11478</v>
+      </c>
+      <c r="AL145" s="2" t="n">
+        <v>0.006312467122567057</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -16885,6 +17761,12 @@
       <c r="AJ146" s="3" t="n">
         <v>-0.003284072249589494</v>
       </c>
+      <c r="AK146" s="1" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AL146" s="2" t="n">
+        <v>0.003294892915980234</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16997,6 +17879,12 @@
       <c r="AJ147" s="3" t="n">
         <v>-0.008064516129032265</v>
       </c>
+      <c r="AK147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AL147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -17109,6 +17997,12 @@
       <c r="AJ148" s="3" t="n">
         <v>-0.005621422730989432</v>
       </c>
+      <c r="AK148" s="1" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="AL148" s="2" t="n">
+        <v>0.005755987254599701</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -17221,6 +18115,12 @@
       <c r="AJ149" s="2" t="n">
         <v>0.003726506804925487</v>
       </c>
+      <c r="AK149" s="1" t="n">
+        <v>0.06184</v>
+      </c>
+      <c r="AL149" s="3" t="n">
+        <v>-0.001775625504439047</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -17333,6 +18233,12 @@
       <c r="AJ150" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK150" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="AL150" s="2" t="n">
+        <v>0.007384615384615425</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -17445,6 +18351,12 @@
       <c r="AJ151" s="3" t="n">
         <v>-0.00313012371441347</v>
       </c>
+      <c r="AK151" s="1" t="n">
+        <v>6.683e-05</v>
+      </c>
+      <c r="AL151" s="3" t="n">
+        <v>-0.0007476076555024106</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17557,6 +18469,12 @@
       <c r="AJ152" s="2" t="n">
         <v>0.007544581618655743</v>
       </c>
+      <c r="AK152" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="AL152" s="3" t="n">
+        <v>-0.002722940776038128</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -17669,6 +18587,12 @@
       <c r="AJ153" s="2" t="n">
         <v>0.006164058795637656</v>
       </c>
+      <c r="AK153" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="AL153" s="3" t="n">
+        <v>-0.004241281809613563</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17781,6 +18705,12 @@
       <c r="AJ154" s="3" t="n">
         <v>-0.0006740815638692446</v>
       </c>
+      <c r="AK154" s="1" t="n">
+        <v>0.0005929</v>
+      </c>
+      <c r="AL154" s="3" t="n">
+        <v>-0.000168634064080857</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -17893,6 +18823,12 @@
       <c r="AJ155" s="3" t="n">
         <v>-0.0009945300845350168</v>
       </c>
+      <c r="AK155" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AL155" s="3" t="n">
+        <v>-0.0002488800398208826</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18005,6 +18941,12 @@
       <c r="AJ156" s="3" t="n">
         <v>-0.003159557661927384</v>
       </c>
+      <c r="AK156" s="1" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="AL156" s="3" t="n">
+        <v>-0.002113048071843549</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -18117,6 +19059,12 @@
       <c r="AJ157" s="3" t="n">
         <v>-0.002972107910379474</v>
       </c>
+      <c r="AK157" s="1" t="n">
+        <v>0.08735</v>
+      </c>
+      <c r="AL157" s="2" t="n">
+        <v>0.001490483833982931</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -18229,6 +19177,12 @@
       <c r="AJ158" s="2" t="n">
         <v>0.005231244798478259</v>
       </c>
+      <c r="AK158" s="1" t="n">
+        <v>0.008390999999999999</v>
+      </c>
+      <c r="AL158" s="3" t="n">
+        <v>-0.007569485511531821</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -18341,6 +19295,12 @@
       <c r="AJ159" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK159" s="1" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AL159" s="2" t="n">
+        <v>0.001988071570576498</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -18453,6 +19413,12 @@
       <c r="AJ160" s="3" t="n">
         <v>-0.001553156791178071</v>
       </c>
+      <c r="AK160" s="1" t="n">
+        <v>1.2845</v>
+      </c>
+      <c r="AL160" s="3" t="n">
+        <v>-0.0009333437038190012</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -18565,6 +19531,12 @@
       <c r="AJ161" s="2" t="n">
         <v>0.003986710963455218</v>
       </c>
+      <c r="AK161" s="1" t="n">
+        <v>0.007553</v>
+      </c>
+      <c r="AL161" s="3" t="n">
+        <v>-0.0002647253474520537</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -18677,6 +19649,12 @@
       <c r="AJ162" s="2" t="n">
         <v>0.008054674151818415</v>
       </c>
+      <c r="AK162" s="1" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="AL162" s="3" t="n">
+        <v>-0.02663438256658592</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -18789,6 +19767,12 @@
       <c r="AJ163" s="3" t="n">
         <v>-0.00103412616339182</v>
       </c>
+      <c r="AK163" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="AL163" s="3" t="n">
+        <v>-0.00103519668737063</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -18901,6 +19885,12 @@
       <c r="AJ164" s="3" t="n">
         <v>-0.001011414535471802</v>
       </c>
+      <c r="AK164" s="1" t="n">
+        <v>1.3816</v>
+      </c>
+      <c r="AL164" s="3" t="n">
+        <v>-0.0008678044547295993</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19013,6 +20003,12 @@
       <c r="AJ165" s="2" t="n">
         <v>0.00622946622861289</v>
       </c>
+      <c r="AK165" s="1" t="n">
+        <v>0.023516</v>
+      </c>
+      <c r="AL165" s="3" t="n">
+        <v>-0.002841029555188105</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19125,6 +20121,12 @@
       <c r="AJ166" s="2" t="n">
         <v>0.005819592628516103</v>
       </c>
+      <c r="AK166" s="1" t="n">
+        <v>0.005188</v>
+      </c>
+      <c r="AL166" s="2" t="n">
+        <v>0.0005785920925746443</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -19237,6 +20239,12 @@
       <c r="AJ167" s="2" t="n">
         <v>0.007265021946420377</v>
       </c>
+      <c r="AK167" s="1" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="AL167" s="2" t="n">
+        <v>0.005409466566491349</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -19349,6 +20357,12 @@
       <c r="AJ168" s="3" t="n">
         <v>-0.00104602510460254</v>
       </c>
+      <c r="AK168" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AL168" s="2" t="n">
+        <v>0.00209424083769625</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -19461,6 +20475,12 @@
       <c r="AJ169" s="2" t="n">
         <v>0.002329192546583846</v>
       </c>
+      <c r="AK169" s="1" t="n">
+        <v>0.03869</v>
+      </c>
+      <c r="AL169" s="3" t="n">
+        <v>-0.001032791117996343</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19573,6 +20593,12 @@
       <c r="AJ170" s="3" t="n">
         <v>-0.001259269623618226</v>
       </c>
+      <c r="AK170" s="1" t="n">
+        <v>0.007132</v>
+      </c>
+      <c r="AL170" s="3" t="n">
+        <v>-0.0008405715886802926</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -19685,6 +20711,12 @@
       <c r="AJ171" s="3" t="n">
         <v>-0.003805620608899366</v>
       </c>
+      <c r="AK171" s="1" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AL171" s="3" t="n">
+        <v>-0.0005877167205406347</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -19797,6 +20829,12 @@
       <c r="AJ172" s="3" t="n">
         <v>-0.002927186242224664</v>
       </c>
+      <c r="AK172" s="1" t="n">
+        <v>5.439</v>
+      </c>
+      <c r="AL172" s="3" t="n">
+        <v>-0.002018348623853233</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19909,6 +20947,12 @@
       <c r="AJ173" s="3" t="n">
         <v>-0.001533070521243991</v>
       </c>
+      <c r="AK173" s="1" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="AL173" s="3" t="n">
+        <v>-0.002412809826716363</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20021,6 +21065,12 @@
       <c r="AJ174" s="2" t="n">
         <v>0.0005111167901865368</v>
       </c>
+      <c r="AK174" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="AL174" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -20133,6 +21183,12 @@
       <c r="AJ175" s="3" t="n">
         <v>-0.007637655417406686</v>
       </c>
+      <c r="AK175" s="1" t="n">
+        <v>0.005561</v>
+      </c>
+      <c r="AL175" s="3" t="n">
+        <v>-0.004653660282799352</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -20245,6 +21301,12 @@
       <c r="AJ176" s="3" t="n">
         <v>-0.001322751322751269</v>
       </c>
+      <c r="AK176" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="AL176" s="3" t="n">
+        <v>-0.001324503311258339</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -20357,6 +21419,12 @@
       <c r="AJ177" s="2" t="n">
         <v>0.001114206128133706</v>
       </c>
+      <c r="AK177" s="1" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="AL177" s="3" t="n">
+        <v>-0.002225932109070676</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -20469,6 +21537,12 @@
       <c r="AJ178" s="3" t="n">
         <v>-0.001457725947521846</v>
       </c>
+      <c r="AK178" s="1" t="n">
+        <v>15.732</v>
+      </c>
+      <c r="AL178" s="3" t="n">
+        <v>-0.001459854014598633</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -20581,6 +21655,12 @@
       <c r="AJ179" s="2" t="n">
         <v>0.003174603174603177</v>
       </c>
+      <c r="AK179" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AL179" s="3" t="n">
+        <v>-0.009493670886075958</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -20693,6 +21773,12 @@
       <c r="AJ180" s="2" t="n">
         <v>0.005926228670685574</v>
       </c>
+      <c r="AK180" s="1" t="n">
+        <v>0.09854</v>
+      </c>
+      <c r="AL180" s="2" t="n">
+        <v>0.0009141696292534967</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -20805,6 +21891,12 @@
       <c r="AJ181" s="3" t="n">
         <v>-0.0005310674455655284</v>
       </c>
+      <c r="AK181" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="AL181" s="3" t="n">
+        <v>-0.0005313496280553493</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -20917,6 +22009,12 @@
       <c r="AJ182" s="2" t="n">
         <v>0.0003346160281078488</v>
       </c>
+      <c r="AK182" s="1" t="n">
+        <v>0.05982</v>
+      </c>
+      <c r="AL182" s="2" t="n">
+        <v>0.0005017561465127163</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -21029,6 +22127,12 @@
       <c r="AJ183" s="3" t="n">
         <v>-0.002493765586034955</v>
       </c>
+      <c r="AK183" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AL183" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -21141,6 +22245,12 @@
       <c r="AJ184" s="3" t="n">
         <v>-0.001395348837209246</v>
       </c>
+      <c r="AK184" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="AL184" s="3" t="n">
+        <v>-0.003260363297624621</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -21253,6 +22363,12 @@
       <c r="AJ185" s="3" t="n">
         <v>-0.005449591280653956</v>
       </c>
+      <c r="AK185" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AL185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -21365,6 +22481,12 @@
       <c r="AJ186" s="2" t="n">
         <v>0.0003941145559643193</v>
       </c>
+      <c r="AK186" s="1" t="n">
+        <v>0.007596</v>
+      </c>
+      <c r="AL186" s="3" t="n">
+        <v>-0.002495075508864074</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -21477,6 +22599,12 @@
       <c r="AJ187" s="2" t="n">
         <v>0.001859427296392713</v>
       </c>
+      <c r="AK187" s="1" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="AL187" s="3" t="n">
+        <v>-0.0003711952487007758</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -21589,6 +22717,12 @@
       <c r="AJ188" s="3" t="n">
         <v>-0.002842639593908655</v>
       </c>
+      <c r="AK188" s="1" t="n">
+        <v>0.04896</v>
+      </c>
+      <c r="AL188" s="3" t="n">
+        <v>-0.003054367745876691</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -21701,6 +22835,12 @@
       <c r="AJ189" s="2" t="n">
         <v>0.001174628034455626</v>
       </c>
+      <c r="AK189" s="1" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="AL189" s="3" t="n">
+        <v>-0.001173249902229046</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -21813,6 +22953,12 @@
       <c r="AJ190" s="2" t="n">
         <v>0.0008768853034022184</v>
       </c>
+      <c r="AK190" s="1" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="AL190" s="3" t="n">
+        <v>-0.0003504468196950727</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -21925,6 +23071,12 @@
       <c r="AJ191" s="3" t="n">
         <v>-0.002812241521918999</v>
       </c>
+      <c r="AK191" s="1" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="AL191" s="3" t="n">
+        <v>-0.001161247511612421</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -22037,6 +23189,12 @@
       <c r="AJ192" s="3" t="n">
         <v>-0.001431844215349371</v>
       </c>
+      <c r="AK192" s="1" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AL192" s="3" t="n">
+        <v>-0.002294235732721603</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -22149,6 +23307,12 @@
       <c r="AJ193" s="3" t="n">
         <v>-0.001560062402496144</v>
       </c>
+      <c r="AK193" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="AL193" s="3" t="n">
+        <v>-0.001562500000000045</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -22261,6 +23425,12 @@
       <c r="AJ194" s="3" t="n">
         <v>-0.006413994169096151</v>
       </c>
+      <c r="AK194" s="1" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="AL194" s="2" t="n">
+        <v>0.001173708920187746</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -22373,6 +23543,12 @@
       <c r="AJ195" s="3" t="n">
         <v>-0.00209961507057032</v>
       </c>
+      <c r="AK195" s="1" t="n">
+        <v>0.0008595</v>
+      </c>
+      <c r="AL195" s="2" t="n">
+        <v>0.004675628287551126</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -22485,6 +23661,12 @@
       <c r="AJ196" s="3" t="n">
         <v>-0.0154440154440154</v>
       </c>
+      <c r="AK196" s="1" t="n">
+        <v>0.001017</v>
+      </c>
+      <c r="AL196" s="3" t="n">
+        <v>-0.002941176470588413</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -22597,6 +23779,12 @@
       <c r="AJ197" s="2" t="n">
         <v>0.001854140914709563</v>
       </c>
+      <c r="AK197" s="1" t="n">
+        <v>0.0001618</v>
+      </c>
+      <c r="AL197" s="3" t="n">
+        <v>-0.001850709438618182</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -22709,6 +23897,12 @@
       <c r="AJ198" s="2" t="n">
         <v>0.001848856020337418</v>
       </c>
+      <c r="AK198" s="1" t="n">
+        <v>4.328</v>
+      </c>
+      <c r="AL198" s="3" t="n">
+        <v>-0.00161476355247974</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -22821,6 +24015,12 @@
       <c r="AJ199" s="2" t="n">
         <v>0.003061849357011638</v>
       </c>
+      <c r="AK199" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="AL199" s="3" t="n">
+        <v>-0.0006105006105005433</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -22933,6 +24133,12 @@
       <c r="AJ200" s="3" t="n">
         <v>-0.005039534277522005</v>
       </c>
+      <c r="AK200" s="1" t="n">
+        <v>0.022861</v>
+      </c>
+      <c r="AL200" s="3" t="n">
+        <v>-0.001790236660553636</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -23045,6 +24251,12 @@
       <c r="AJ201" s="2" t="n">
         <v>0.003558718861209932</v>
       </c>
+      <c r="AK201" s="1" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="AL201" s="2" t="n">
+        <v>0.0001611863313991467</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -23157,6 +24369,12 @@
       <c r="AJ202" s="3" t="n">
         <v>-0.0007153075822603429</v>
       </c>
+      <c r="AK202" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="AL202" s="2" t="n">
+        <v>0.001431639226914883</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -23269,6 +24487,12 @@
       <c r="AJ203" s="3" t="n">
         <v>-0.005389514943655191</v>
       </c>
+      <c r="AK203" s="1" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="AL203" s="3" t="n">
+        <v>-0.001477832512315211</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -23381,6 +24605,12 @@
       <c r="AJ204" s="3" t="n">
         <v>-0.0003861003861003704</v>
       </c>
+      <c r="AK204" s="1" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="AL204" s="3" t="n">
+        <v>-0.002317497103128661</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -23493,6 +24723,12 @@
       <c r="AJ205" s="3" t="n">
         <v>-0.001616628175519581</v>
       </c>
+      <c r="AK205" s="1" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="AL205" s="3" t="n">
+        <v>-0.0002313208420079678</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -23605,6 +24841,12 @@
       <c r="AJ206" s="2" t="n">
         <v>0.004816112084063155</v>
       </c>
+      <c r="AK206" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="AL206" s="2" t="n">
+        <v>0.0008714596949890712</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -23717,6 +24959,12 @@
       <c r="AJ207" s="3" t="n">
         <v>-0.0007173601147776455</v>
       </c>
+      <c r="AK207" s="1" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="AL207" s="3" t="n">
+        <v>-0.001196458482890618</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -23829,6 +25077,12 @@
       <c r="AJ208" s="2" t="n">
         <v>0.001763429191535609</v>
       </c>
+      <c r="AK208" s="1" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="AL208" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -23941,6 +25195,12 @@
       <c r="AJ209" s="3" t="n">
         <v>-0.001187648456057041</v>
       </c>
+      <c r="AK209" s="1" t="n">
+        <v>0.04218</v>
+      </c>
+      <c r="AL209" s="2" t="n">
+        <v>0.003091557669441263</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -24053,6 +25313,12 @@
       <c r="AJ210" s="3" t="n">
         <v>-0.001080497028633052</v>
       </c>
+      <c r="AK210" s="1" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AL210" s="3" t="n">
+        <v>-0.00216333153055712</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -24165,6 +25431,12 @@
       <c r="AJ211" s="2" t="n">
         <v>0.00294985250737454</v>
       </c>
+      <c r="AK211" s="1" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AL211" s="3" t="n">
+        <v>-0.005462184873949561</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -24277,6 +25549,12 @@
       <c r="AJ212" s="3" t="n">
         <v>-0.001424501424501408</v>
       </c>
+      <c r="AK212" s="1" t="n">
+        <v>0.002109</v>
+      </c>
+      <c r="AL212" s="2" t="n">
+        <v>0.002853067047075779</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -24389,6 +25667,12 @@
       <c r="AJ213" s="3" t="n">
         <v>-0.002152852529601724</v>
       </c>
+      <c r="AK213" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="AL213" s="3" t="n">
+        <v>-0.001078748651564187</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -24501,6 +25785,12 @@
       <c r="AJ214" s="3" t="n">
         <v>-0.003661726242371285</v>
       </c>
+      <c r="AK214" s="1" t="n">
+        <v>0.005703</v>
+      </c>
+      <c r="AL214" s="3" t="n">
+        <v>-0.001925096254812844</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -24613,6 +25903,12 @@
       <c r="AJ215" s="2" t="n">
         <v>0.0005489478499542955</v>
       </c>
+      <c r="AK215" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="AL215" s="2" t="n">
+        <v>0.0009144111192392362</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -24725,6 +26021,12 @@
       <c r="AJ216" s="2" t="n">
         <v>0.001587301587301633</v>
       </c>
+      <c r="AK216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AL216" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -24837,6 +26139,12 @@
       <c r="AJ217" s="3" t="n">
         <v>-0.001078748651564216</v>
       </c>
+      <c r="AK217" s="1" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="AL217" s="3" t="n">
+        <v>-0.004319654427645762</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -24949,6 +26257,12 @@
       <c r="AJ218" s="3" t="n">
         <v>-0.002649006622516424</v>
       </c>
+      <c r="AK218" s="1" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AL218" s="3" t="n">
+        <v>-0.004989052797817746</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -25061,6 +26375,12 @@
       <c r="AJ219" s="3" t="n">
         <v>-0.000305903946160946</v>
       </c>
+      <c r="AK219" s="1" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="AL219" s="3" t="n">
+        <v>-0.001223990208078365</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -25173,6 +26493,12 @@
       <c r="AJ220" s="3" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="AK220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="AL220" s="2" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -25285,6 +26611,12 @@
       <c r="AJ221" s="3" t="n">
         <v>-0.002326783867631846</v>
       </c>
+      <c r="AK221" s="1" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AL221" s="3" t="n">
+        <v>-0.00207307592640572</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -25397,6 +26729,12 @@
       <c r="AJ222" s="2" t="n">
         <v>0.00107089312486602</v>
       </c>
+      <c r="AK222" s="1" t="n">
+        <v>0.04671</v>
+      </c>
+      <c r="AL222" s="3" t="n">
+        <v>-0.000641848523748295</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -25509,6 +26847,12 @@
       <c r="AJ223" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK223" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="AL223" s="3" t="n">
+        <v>-0.001879699248120224</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -25621,6 +26965,12 @@
       <c r="AJ224" s="2" t="n">
         <v>0.004555808656036394</v>
       </c>
+      <c r="AK224" s="1" t="n">
+        <v>3.973</v>
+      </c>
+      <c r="AL224" s="2" t="n">
+        <v>0.001007810531620056</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -25733,6 +27083,12 @@
       <c r="AJ225" s="3" t="n">
         <v>-0.001623200952277873</v>
       </c>
+      <c r="AK225" s="1" t="n">
+        <v>0.0009219</v>
+      </c>
+      <c r="AL225" s="3" t="n">
+        <v>-0.0007587253414263633</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -25845,6 +27201,12 @@
       <c r="AJ226" s="3" t="n">
         <v>-0.002602626286525634</v>
       </c>
+      <c r="AK226" s="1" t="n">
+        <v>0.008413</v>
+      </c>
+      <c r="AL226" s="3" t="n">
+        <v>-0.00213497805716984</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -25957,6 +27319,12 @@
       <c r="AJ227" s="2" t="n">
         <v>0.001458789204959824</v>
       </c>
+      <c r="AK227" s="1" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="AL227" s="3" t="n">
+        <v>-0.002913328477785752</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -26069,6 +27437,12 @@
       <c r="AJ228" s="2" t="n">
         <v>0.006715165081141498</v>
       </c>
+      <c r="AK228" s="1" t="n">
+        <v>0.03609</v>
+      </c>
+      <c r="AL228" s="2" t="n">
+        <v>0.003057254030016648</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -26181,6 +27555,12 @@
       <c r="AJ229" s="2" t="n">
         <v>0.001155401502022039</v>
       </c>
+      <c r="AK229" s="1" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="AL229" s="2" t="n">
+        <v>0.000769378726678176</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -26293,6 +27673,12 @@
       <c r="AJ230" s="3" t="n">
         <v>-0.001749271137026218</v>
       </c>
+      <c r="AK230" s="1" t="n">
+        <v>0.001709</v>
+      </c>
+      <c r="AL230" s="3" t="n">
+        <v>-0.00175233644859811</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -26405,6 +27791,12 @@
       <c r="AJ231" s="2" t="n">
         <v>0.002058036633051985</v>
       </c>
+      <c r="AK231" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="AL231" s="3" t="n">
+        <v>-0.002053809817210843</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -26517,6 +27909,12 @@
       <c r="AJ232" s="2" t="n">
         <v>0.000459558823529393</v>
       </c>
+      <c r="AK232" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="AL232" s="2" t="n">
+        <v>0.002756086357372419</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -26629,6 +28027,12 @@
       <c r="AJ233" s="3" t="n">
         <v>-0.001702417432754368</v>
       </c>
+      <c r="AK233" s="1" t="n">
+        <v>0.0005858</v>
+      </c>
+      <c r="AL233" s="3" t="n">
+        <v>-0.001023192360163736</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -26741,6 +28145,12 @@
       <c r="AJ234" s="3" t="n">
         <v>-0.007043245527539097</v>
       </c>
+      <c r="AK234" s="1" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="AL234" s="3" t="n">
+        <v>-0.0001418640941977692</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -26853,6 +28263,12 @@
       <c r="AJ235" s="3" t="n">
         <v>-0.02189265536723172</v>
       </c>
+      <c r="AK235" s="1" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="AL235" s="3" t="n">
+        <v>-0.01083032490974723</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -26965,6 +28381,12 @@
       <c r="AJ236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK236" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AL236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -27077,6 +28499,12 @@
       <c r="AJ237" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="AK237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="AL237" s="3" t="n">
+        <v>-0.002392344497607558</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -27189,6 +28617,12 @@
       <c r="AJ238" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK238" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="AL238" s="3" t="n">
+        <v>-0.007843137254901914</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -27301,6 +28735,12 @@
       <c r="AJ239" s="3" t="n">
         <v>-0.007973421926910204</v>
       </c>
+      <c r="AK239" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="AL239" s="2" t="n">
+        <v>0.001339584728734038</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -27413,6 +28853,12 @@
       <c r="AJ240" s="2" t="n">
         <v>0.0002551020408163327</v>
       </c>
+      <c r="AK240" s="1" t="n">
+        <v>0.0003921</v>
+      </c>
+      <c r="AL240" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -27525,6 +28971,12 @@
       <c r="AJ241" s="2" t="n">
         <v>0.0007374631268435766</v>
       </c>
+      <c r="AK241" s="1" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AL241" s="3" t="n">
+        <v>-0.0007369196757552616</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -27637,6 +29089,12 @@
       <c r="AJ242" s="2" t="n">
         <v>0.001433038040646157</v>
       </c>
+      <c r="AK242" s="1" t="n">
+        <v>0.07722999999999999</v>
+      </c>
+      <c r="AL242" s="2" t="n">
+        <v>0.004683231429686473</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -27749,6 +29207,12 @@
       <c r="AJ243" s="3" t="n">
         <v>-0.007021063189568594</v>
       </c>
+      <c r="AK243" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="AL243" s="3" t="n">
+        <v>-0.00454545454545471</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -27861,6 +29325,12 @@
       <c r="AJ244" s="2" t="n">
         <v>0.007571345369831076</v>
       </c>
+      <c r="AK244" s="1" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="AL244" s="3" t="n">
+        <v>-0.008670520231213721</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -27973,6 +29443,12 @@
       <c r="AJ245" s="2" t="n">
         <v>0.003496748024337447</v>
       </c>
+      <c r="AK245" s="1" t="n">
+        <v>1.4306</v>
+      </c>
+      <c r="AL245" s="3" t="n">
+        <v>-0.002996724510418824</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -28085,6 +29561,12 @@
       <c r="AJ246" s="3" t="n">
         <v>-0.001120448179271857</v>
       </c>
+      <c r="AK246" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AL246" s="2" t="n">
+        <v>0.001682557487380945</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -28197,6 +29679,12 @@
       <c r="AJ247" s="2" t="n">
         <v>0.0006023189278722577</v>
       </c>
+      <c r="AK247" s="1" t="n">
+        <v>0.006628</v>
+      </c>
+      <c r="AL247" s="3" t="n">
+        <v>-0.002558314522197089</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -28309,6 +29797,12 @@
       <c r="AJ248" s="2" t="n">
         <v>0.005653883972468155</v>
       </c>
+      <c r="AK248" s="1" t="n">
+        <v>0.004096</v>
+      </c>
+      <c r="AL248" s="2" t="n">
+        <v>0.001222195062331898</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -28421,6 +29915,12 @@
       <c r="AJ249" s="2" t="n">
         <v>0.0009025270758123002</v>
       </c>
+      <c r="AK249" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AL249" s="2" t="n">
+        <v>0.0009017132551848771</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -28533,6 +30033,12 @@
       <c r="AJ250" s="2" t="n">
         <v>0.01013611352447156</v>
       </c>
+      <c r="AK250" s="1" t="n">
+        <v>0.03479</v>
+      </c>
+      <c r="AL250" s="3" t="n">
+        <v>-0.002580275229357792</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -28645,6 +30151,12 @@
       <c r="AJ251" s="2" t="n">
         <v>0.001649387370405293</v>
       </c>
+      <c r="AK251" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="AL251" s="2" t="n">
+        <v>0.002117148906139727</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -28757,6 +30269,12 @@
       <c r="AJ252" s="3" t="n">
         <v>-0.01261988894497735</v>
       </c>
+      <c r="AK252" s="1" t="n">
+        <v>0.005855</v>
+      </c>
+      <c r="AL252" s="3" t="n">
+        <v>-0.002215405589638717</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -28869,6 +30387,12 @@
       <c r="AJ253" s="3" t="n">
         <v>-0.002972651605231952</v>
       </c>
+      <c r="AK253" s="1" t="n">
+        <v>0.01676</v>
+      </c>
+      <c r="AL253" s="3" t="n">
+        <v>-0.0005963029218842929</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -28981,6 +30505,12 @@
       <c r="AJ254" s="2" t="n">
         <v>0.0007745933384974186</v>
       </c>
+      <c r="AK254" s="1" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="AL254" s="3" t="n">
+        <v>-0.0007739938080496651</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -29093,6 +30623,12 @@
       <c r="AJ255" s="2" t="n">
         <v>0.001850138760406955</v>
       </c>
+      <c r="AK255" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="AL255" s="2" t="n">
+        <v>0.007848568790397047</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -29205,6 +30741,12 @@
       <c r="AJ256" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK256" s="1" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="AL256" s="3" t="n">
+        <v>-0.0009451795841211083</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -29317,6 +30859,12 @@
       <c r="AJ257" s="2" t="n">
         <v>0.003947887879984322</v>
       </c>
+      <c r="AK257" s="1" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="AL257" s="3" t="n">
+        <v>-0.0003932363350373414</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -29429,6 +30977,12 @@
       <c r="AJ258" s="2" t="n">
         <v>0.0003301201637395648</v>
       </c>
+      <c r="AK258" s="1" t="n">
+        <v>0.15178</v>
+      </c>
+      <c r="AL258" s="2" t="n">
+        <v>0.001782060590060012</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -29541,6 +31095,12 @@
       <c r="AJ259" s="2" t="n">
         <v>0.001768867924528298</v>
       </c>
+      <c r="AK259" s="1" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="AL259" s="3" t="n">
+        <v>-0.0007847753580537252</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -29653,6 +31213,12 @@
       <c r="AJ260" s="2" t="n">
         <v>0.001069137562366273</v>
       </c>
+      <c r="AK260" s="1" t="n">
+        <v>0.08479</v>
+      </c>
+      <c r="AL260" s="2" t="n">
+        <v>0.006170641984098809</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -29765,6 +31331,12 @@
       <c r="AJ261" s="3" t="n">
         <v>-0.007796471070988974</v>
       </c>
+      <c r="AK261" s="1" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="AL261" s="3" t="n">
+        <v>-0.01902398676592222</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -29877,6 +31449,12 @@
       <c r="AJ262" s="2" t="n">
         <v>0.004143646408839706</v>
       </c>
+      <c r="AK262" s="1" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="AL262" s="3" t="n">
+        <v>-0.007565337001375446</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -29989,6 +31567,12 @@
       <c r="AJ263" s="2" t="n">
         <v>0.001437908496732013</v>
       </c>
+      <c r="AK263" s="1" t="n">
+        <v>0.07667</v>
+      </c>
+      <c r="AL263" s="2" t="n">
+        <v>0.0007831875734238937</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -30101,6 +31685,12 @@
       <c r="AJ264" s="2" t="n">
         <v>0.0043545081967214</v>
       </c>
+      <c r="AK264" s="1" t="n">
+        <v>0.03948</v>
+      </c>
+      <c r="AL264" s="2" t="n">
+        <v>0.006885998469778103</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -30213,6 +31803,12 @@
       <c r="AJ265" s="3" t="n">
         <v>-0.002597402597402604</v>
       </c>
+      <c r="AK265" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="AL265" s="3" t="n">
+        <v>-0.0006510416666666402</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -30325,6 +31921,12 @@
       <c r="AJ266" s="2" t="n">
         <v>0.000334560053529653</v>
       </c>
+      <c r="AK266" s="1" t="n">
+        <v>0.005967</v>
+      </c>
+      <c r="AL266" s="3" t="n">
+        <v>-0.002173913043478259</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -30437,6 +32039,12 @@
       <c r="AJ267" s="3" t="n">
         <v>-0.0008064516129030997</v>
       </c>
+      <c r="AK267" s="1" t="n">
+        <v>0.03723</v>
+      </c>
+      <c r="AL267" s="2" t="n">
+        <v>0.001614205004035447</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -30549,6 +32157,12 @@
       <c r="AJ268" s="2" t="n">
         <v>0.0003269042170643868</v>
       </c>
+      <c r="AK268" s="1" t="n">
+        <v>0.03052</v>
+      </c>
+      <c r="AL268" s="3" t="n">
+        <v>-0.002614379084967327</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -30661,6 +32275,12 @@
       <c r="AJ269" s="2" t="n">
         <v>0.001723756906077355</v>
       </c>
+      <c r="AK269" s="1" t="n">
+        <v>0.22636</v>
+      </c>
+      <c r="AL269" s="3" t="n">
+        <v>-0.001235439463466301</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -30773,6 +32393,12 @@
       <c r="AJ270" s="2" t="n">
         <v>0.002145922746781118</v>
       </c>
+      <c r="AK270" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="AL270" s="3" t="n">
+        <v>-0.00749464668094219</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -30885,6 +32511,12 @@
       <c r="AJ271" s="3" t="n">
         <v>-0.0007719027402548142</v>
       </c>
+      <c r="AK271" s="1" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AL271" s="3" t="n">
+        <v>-0.001544998068752416</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -30997,6 +32629,12 @@
       <c r="AJ272" s="2" t="n">
         <v>0.002686727565824828</v>
       </c>
+      <c r="AK272" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AL272" s="3" t="n">
+        <v>-0.00321543408360123</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -31109,6 +32747,12 @@
       <c r="AJ273" s="3" t="n">
         <v>-0.003205128205128186</v>
       </c>
+      <c r="AK273" s="1" t="n">
+        <v>0.03117</v>
+      </c>
+      <c r="AL273" s="2" t="n">
+        <v>0.00225080385852092</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -31221,6 +32865,12 @@
       <c r="AJ274" s="2" t="n">
         <v>0.001044386422976531</v>
       </c>
+      <c r="AK274" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AL274" s="2" t="n">
+        <v>0.00156494522691703</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -31333,6 +32983,12 @@
       <c r="AJ275" s="3" t="n">
         <v>-0.002171395483497356</v>
       </c>
+      <c r="AK275" s="1" t="n">
+        <v>0.06891</v>
+      </c>
+      <c r="AL275" s="3" t="n">
+        <v>-0.0002901494269549706</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -31445,6 +33101,12 @@
       <c r="AJ276" s="3" t="n">
         <v>-0.002486016159104933</v>
       </c>
+      <c r="AK276" s="1" t="n">
+        <v>0.08021</v>
+      </c>
+      <c r="AL276" s="3" t="n">
+        <v>-0.0004984423676012258</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -31557,6 +33219,12 @@
       <c r="AJ277" s="3" t="n">
         <v>-0.0005206977349648092</v>
       </c>
+      <c r="AK277" s="1" t="n">
+        <v>0.00386</v>
+      </c>
+      <c r="AL277" s="2" t="n">
+        <v>0.005470174524615834</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -31669,6 +33337,12 @@
       <c r="AJ278" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK278" s="1" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="AL278" s="3" t="n">
+        <v>-0.001287830006439151</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -31781,6 +33455,12 @@
       <c r="AJ279" s="3" t="n">
         <v>-0.0009057971014492385</v>
       </c>
+      <c r="AK279" s="1" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="AL279" s="3" t="n">
+        <v>-0.001813236627379799</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -31893,6 +33573,12 @@
       <c r="AJ280" s="3" t="n">
         <v>-0.001243162605668857</v>
       </c>
+      <c r="AK280" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AL280" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -32005,6 +33691,12 @@
       <c r="AJ281" s="2" t="n">
         <v>0.001071428571428486</v>
       </c>
+      <c r="AK281" s="1" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="AL281" s="3" t="n">
+        <v>-0.003091925318111504</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -32117,6 +33809,12 @@
       <c r="AJ282" s="2" t="n">
         <v>0.003703703703703681</v>
       </c>
+      <c r="AK282" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AL282" s="3" t="n">
+        <v>-0.003690036900368981</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -32229,6 +33927,12 @@
       <c r="AJ283" s="3" t="n">
         <v>-0.002096161404428056</v>
       </c>
+      <c r="AK283" s="1" t="n">
+        <v>0.07603</v>
+      </c>
+      <c r="AL283" s="3" t="n">
+        <v>-0.001837993960877002</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -32341,6 +34045,12 @@
       <c r="AJ284" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK284" s="1" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="AL284" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -32453,6 +34163,12 @@
       <c r="AJ285" s="3" t="n">
         <v>-0.0004918839153960489</v>
       </c>
+      <c r="AK285" s="1" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="AL285" s="3" t="n">
+        <v>-0.002460629921259845</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -32565,6 +34281,12 @@
       <c r="AJ286" s="3" t="n">
         <v>-0.008363089644803626</v>
       </c>
+      <c r="AK286" s="1" t="n">
+        <v>0.10608</v>
+      </c>
+      <c r="AL286" s="2" t="n">
+        <v>0.005211788117123045</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -32677,6 +34399,12 @@
       <c r="AJ287" s="3" t="n">
         <v>-0.002305475504322872</v>
       </c>
+      <c r="AK287" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="AL287" s="3" t="n">
+        <v>-0.002310803004043811</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -32789,6 +34517,12 @@
       <c r="AJ288" s="2" t="n">
         <v>0.00859220092531394</v>
       </c>
+      <c r="AK288" s="1" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="AL288" s="3" t="n">
+        <v>-0.0006553079947575094</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -32901,6 +34635,12 @@
       <c r="AJ289" s="2" t="n">
         <v>0.1196792103639729</v>
       </c>
+      <c r="AK289" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="AL289" s="3" t="n">
+        <v>-0.1002754820936638</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -33013,6 +34753,12 @@
       <c r="AJ290" s="3" t="n">
         <v>-0.0004415011037529068</v>
       </c>
+      <c r="AK290" s="1" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="AL290" s="3" t="n">
+        <v>-0.0008833922261483127</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -33125,6 +34871,12 @@
       <c r="AJ291" s="2" t="n">
         <v>0.001133016088828462</v>
       </c>
+      <c r="AK291" s="1" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="AL291" s="2" t="n">
+        <v>0.0006790402897237821</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -33237,6 +34989,12 @@
       <c r="AJ292" s="2" t="n">
         <v>0.003470213996529789</v>
       </c>
+      <c r="AK292" s="1" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="AL292" s="2" t="n">
+        <v>0.0005763688760806281</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -33349,6 +35107,12 @@
       <c r="AJ293" s="2" t="n">
         <v>0.01140609636184852</v>
       </c>
+      <c r="AK293" s="1" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="AL293" s="3" t="n">
+        <v>-0.005249854170717469</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -33461,6 +35225,12 @@
       <c r="AJ294" s="2" t="n">
         <v>0.001110053916904545</v>
       </c>
+      <c r="AK294" s="1" t="n">
+        <v>0.06326</v>
+      </c>
+      <c r="AL294" s="2" t="n">
+        <v>0.002059242832250772</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -33573,6 +35343,12 @@
       <c r="AJ295" s="2" t="n">
         <v>0.003140096618357565</v>
       </c>
+      <c r="AK295" s="1" t="n">
+        <v>0.0004142</v>
+      </c>
+      <c r="AL295" s="3" t="n">
+        <v>-0.002648687695641769</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -33685,6 +35461,12 @@
       <c r="AJ296" s="3" t="n">
         <v>-0.001918158567775009</v>
       </c>
+      <c r="AK296" s="1" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="AL296" s="3" t="n">
+        <v>-0.002722613709160708</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -33797,6 +35579,12 @@
       <c r="AJ297" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK297" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AL297" s="3" t="n">
+        <v>-0.004085801838610802</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -33909,6 +35697,12 @@
       <c r="AJ298" s="3" t="n">
         <v>-0.002089864158829591</v>
       </c>
+      <c r="AK298" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AL298" s="2" t="n">
+        <v>0.00209424083769625</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -34021,6 +35815,12 @@
       <c r="AJ299" s="2" t="n">
         <v>0.00177657017452193</v>
       </c>
+      <c r="AK299" s="1" t="n">
+        <v>0.09588000000000001</v>
+      </c>
+      <c r="AL299" s="2" t="n">
+        <v>0.0002086375964949523</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -34133,6 +35933,12 @@
       <c r="AJ300" s="3" t="n">
         <v>-0.00268096514745316</v>
       </c>
+      <c r="AK300" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AL300" s="3" t="n">
+        <v>-0.004301075268817216</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -34245,6 +36051,12 @@
       <c r="AJ301" s="2" t="n">
         <v>0.002220577350111067</v>
       </c>
+      <c r="AK301" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AL301" s="3" t="n">
+        <v>-0.002954209748892179</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -34357,6 +36169,12 @@
       <c r="AJ302" s="3" t="n">
         <v>-0.001582994120307567</v>
       </c>
+      <c r="AK302" s="1" t="n">
+        <v>0.004423</v>
+      </c>
+      <c r="AL302" s="2" t="n">
+        <v>0.001812004530011369</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -34469,6 +36287,12 @@
       <c r="AJ303" s="3" t="n">
         <v>-0.007592190889370999</v>
       </c>
+      <c r="AK303" s="1" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="AL303" s="2" t="n">
+        <v>0.005464480874316907</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -34581,6 +36405,12 @@
       <c r="AJ304" s="3" t="n">
         <v>-0.001483679525222483</v>
       </c>
+      <c r="AK304" s="1" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="AL304" s="2" t="n">
+        <v>0.0006368074718743607</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -34693,6 +36523,12 @@
       <c r="AJ305" s="2" t="n">
         <v>0.001494489071548603</v>
       </c>
+      <c r="AK305" s="1" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="AL305" s="3" t="n">
+        <v>-0.0001865323633649715</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -34805,6 +36641,12 @@
       <c r="AJ306" s="3" t="n">
         <v>-0.001196581196581207</v>
       </c>
+      <c r="AK306" s="1" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="AL306" s="3" t="n">
+        <v>-0.002053739517371248</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -34917,6 +36759,12 @@
       <c r="AJ307" s="2" t="n">
         <v>0.0005720823798626372</v>
       </c>
+      <c r="AK307" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="AL307" s="3" t="n">
+        <v>-0.0005717552887363578</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -35029,6 +36877,12 @@
       <c r="AJ308" s="2" t="n">
         <v>0.007464192051644045</v>
       </c>
+      <c r="AK308" s="1" t="n">
+        <v>0.04982</v>
+      </c>
+      <c r="AL308" s="3" t="n">
+        <v>-0.002402883460152085</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -35141,6 +36995,12 @@
       <c r="AJ309" s="3" t="n">
         <v>-0.001093493712411033</v>
       </c>
+      <c r="AK309" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="AL309" s="2" t="n">
+        <v>0.0003648969166210144</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -35253,6 +37113,12 @@
       <c r="AJ310" s="3" t="n">
         <v>-0.004065040650406515</v>
       </c>
+      <c r="AK310" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AL310" s="2" t="n">
+        <v>0.004081632653061235</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -35365,6 +37231,12 @@
       <c r="AJ311" s="2" t="n">
         <v>0.002264364562694502</v>
       </c>
+      <c r="AK311" s="1" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="AL311" s="2" t="n">
+        <v>0.001412030499858838</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -35477,6 +37349,12 @@
       <c r="AJ312" s="2" t="n">
         <v>0.003811659192825034</v>
       </c>
+      <c r="AK312" s="1" t="n">
+        <v>0.008956</v>
+      </c>
+      <c r="AL312" s="2" t="n">
+        <v>0.0002233638597275257</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -35589,6 +37467,12 @@
       <c r="AJ313" s="2" t="n">
         <v>0.002957607624055174</v>
       </c>
+      <c r="AK313" s="1" t="n">
+        <v>0.012176</v>
+      </c>
+      <c r="AL313" s="3" t="n">
+        <v>-0.002621231979030208</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -35701,6 +37585,12 @@
       <c r="AJ314" s="2" t="n">
         <v>0.0117647058823529</v>
       </c>
+      <c r="AK314" s="1" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="AL314" s="2" t="n">
+        <v>0.008305647840531512</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -35813,6 +37703,12 @@
       <c r="AJ315" s="3" t="n">
         <v>-0.001402524544179588</v>
       </c>
+      <c r="AK315" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AL315" s="3" t="n">
+        <v>-0.001404494382022415</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -35925,6 +37821,12 @@
       <c r="AJ316" s="3" t="n">
         <v>-0.002670736360167793</v>
       </c>
+      <c r="AK316" s="1" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="AL316" s="3" t="n">
+        <v>-0.000382555470543399</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -36037,6 +37939,12 @@
       <c r="AJ317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AL317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -36149,6 +38057,12 @@
       <c r="AJ318" s="2" t="n">
         <v>0.001075491990414942</v>
       </c>
+      <c r="AK318" s="1" t="n">
+        <v>0.053126</v>
+      </c>
+      <c r="AL318" s="2" t="n">
+        <v>0.001319360675512678</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -36261,6 +38175,12 @@
       <c r="AJ319" s="3" t="n">
         <v>-0.0005208333333333122</v>
       </c>
+      <c r="AK319" s="1" t="n">
+        <v>0.03837</v>
+      </c>
+      <c r="AL319" s="3" t="n">
+        <v>-0.0002605523710264753</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -36373,6 +38293,12 @@
       <c r="AJ320" s="2" t="n">
         <v>0.001616220981486883</v>
       </c>
+      <c r="AK320" s="1" t="n">
+        <v>0.006816</v>
+      </c>
+      <c r="AL320" s="3" t="n">
+        <v>-0.0001466920932961908</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -36485,6 +38411,12 @@
       <c r="AJ321" s="3" t="n">
         <v>-0.0002203613926840753</v>
       </c>
+      <c r="AK321" s="1" t="n">
+        <v>4.523</v>
+      </c>
+      <c r="AL321" s="3" t="n">
+        <v>-0.003085739475424341</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -36597,6 +38529,12 @@
       <c r="AJ322" s="2" t="n">
         <v>0.002070393374741203</v>
       </c>
+      <c r="AK322" s="1" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="AL322" s="3" t="n">
+        <v>-0.001549586776859448</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -36709,6 +38647,12 @@
       <c r="AJ323" s="2" t="n">
         <v>0.001955853590388394</v>
       </c>
+      <c r="AK323" s="1" t="n">
+        <v>0.007137</v>
+      </c>
+      <c r="AL323" s="3" t="n">
+        <v>-0.0048800892359175</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -36821,6 +38765,12 @@
       <c r="AJ324" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK324" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AL324" s="3" t="n">
+        <v>-0.0005452562704470879</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -36933,6 +38883,12 @@
       <c r="AJ325" s="3" t="n">
         <v>-0.00505780346820807</v>
       </c>
+      <c r="AK325" s="1" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="AL325" s="2" t="n">
+        <v>0.0002420721374969474</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -37045,6 +39001,12 @@
       <c r="AJ326" s="3" t="n">
         <v>-0.0001384657989476783</v>
       </c>
+      <c r="AK326" s="1" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AL326" s="3" t="n">
+        <v>-0.0029081844619859</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -37157,6 +39119,12 @@
       <c r="AJ327" s="2" t="n">
         <v>0.005684754521963772</v>
       </c>
+      <c r="AK327" s="1" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="AL327" s="2" t="n">
+        <v>0.00719424460431661</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -37269,6 +39237,12 @@
       <c r="AJ328" s="2" t="n">
         <v>0.0004287245444801242</v>
       </c>
+      <c r="AK328" s="1" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="AL328" s="2" t="n">
+        <v>0.001285622455538867</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -37381,6 +39355,12 @@
       <c r="AJ329" s="2" t="n">
         <v>0.001485884101040187</v>
       </c>
+      <c r="AK329" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="AL329" s="3" t="n">
+        <v>-0.002967359050445111</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -37493,6 +39473,12 @@
       <c r="AJ330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK330" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AL330" s="3" t="n">
+        <v>-0.0008833922261483126</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -37605,6 +39591,12 @@
       <c r="AJ331" s="3" t="n">
         <v>-0.00182512029201923</v>
       </c>
+      <c r="AK331" s="1" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="AL331" s="3" t="n">
+        <v>-0.001994680851063795</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -37717,6 +39709,12 @@
       <c r="AJ332" s="3" t="n">
         <v>-0.001801978900465222</v>
       </c>
+      <c r="AK332" s="1" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AL332" s="3" t="n">
+        <v>-0.001477007910197939</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -37829,6 +39827,12 @@
       <c r="AJ333" s="2" t="n">
         <v>0.0005661712668081864</v>
       </c>
+      <c r="AK333" s="1" t="n">
+        <v>0.07062</v>
+      </c>
+      <c r="AL333" s="3" t="n">
+        <v>-0.0009902390720045355</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -37941,6 +39945,12 @@
       <c r="AJ334" s="2" t="n">
         <v>0.002538240598490358</v>
       </c>
+      <c r="AK334" s="1" t="n">
+        <v>0.15024</v>
+      </c>
+      <c r="AL334" s="2" t="n">
+        <v>0.0009994003597842043</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -38053,6 +40063,12 @@
       <c r="AJ335" s="3" t="n">
         <v>-0.001916932907348209</v>
       </c>
+      <c r="AK335" s="1" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="AL335" s="2" t="n">
+        <v>0.0006402048655569077</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -38165,6 +40181,12 @@
       <c r="AJ336" s="3" t="n">
         <v>-0.001146788990825721</v>
       </c>
+      <c r="AK336" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="AL336" s="3" t="n">
+        <v>-0.002870264064293918</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -38277,6 +40299,12 @@
       <c r="AJ337" s="3" t="n">
         <v>-0.02521008403361345</v>
       </c>
+      <c r="AK337" s="1" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="AL337" s="2" t="n">
+        <v>0.003042596348884257</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -38389,6 +40417,12 @@
       <c r="AJ338" s="2" t="n">
         <v>0.0003779289493575709</v>
       </c>
+      <c r="AK338" s="1" t="n">
+        <v>0.005283</v>
+      </c>
+      <c r="AL338" s="3" t="n">
+        <v>-0.002077823951643318</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -38501,6 +40535,12 @@
       <c r="AJ339" s="3" t="n">
         <v>-0.001549786904300596</v>
       </c>
+      <c r="AK339" s="1" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="AL339" s="3" t="n">
+        <v>-0.001358168412883209</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -38613,6 +40653,12 @@
       <c r="AJ340" s="2" t="n">
         <v>0.0008660315768437745</v>
       </c>
+      <c r="AK340" s="1" t="n">
+        <v>0.15015</v>
+      </c>
+      <c r="AL340" s="3" t="n">
+        <v>-0.0005990415335463707</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -38725,6 +40771,12 @@
       <c r="AJ341" s="2" t="n">
         <v>0.0002616431187859471</v>
       </c>
+      <c r="AK341" s="1" t="n">
+        <v>7.639</v>
+      </c>
+      <c r="AL341" s="3" t="n">
+        <v>-0.0009155113784985186</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -38837,6 +40889,12 @@
       <c r="AJ342" s="2" t="n">
         <v>0.001217285453438866</v>
       </c>
+      <c r="AK342" s="1" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AL342" s="3" t="n">
+        <v>-0.001519756838905776</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -38949,6 +41007,12 @@
       <c r="AJ343" s="3" t="n">
         <v>-0.003473945409429311</v>
       </c>
+      <c r="AK343" s="1" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="AL343" s="3" t="n">
+        <v>-0.0009960159362549395</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -39061,6 +41125,12 @@
       <c r="AJ344" s="3" t="n">
         <v>-0.002749770852428865</v>
       </c>
+      <c r="AK344" s="1" t="n">
+        <v>2.179</v>
+      </c>
+      <c r="AL344" s="2" t="n">
+        <v>0.001378676470588083</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -39173,6 +41243,12 @@
       <c r="AJ345" s="2" t="n">
         <v>0.0007874015748030629</v>
       </c>
+      <c r="AK345" s="1" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="AL345" s="2" t="n">
+        <v>0.002360346184107092</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -39285,6 +41361,12 @@
       <c r="AJ346" s="3" t="n">
         <v>-0.001351351351351363</v>
       </c>
+      <c r="AK346" s="1" t="n">
+        <v>0.005173</v>
+      </c>
+      <c r="AL346" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -39397,6 +41479,12 @@
       <c r="AJ347" s="3" t="n">
         <v>-0.0005285412262155622</v>
       </c>
+      <c r="AK347" s="1" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="AL347" s="3" t="n">
+        <v>-0.0008813678829543703</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -39509,6 +41597,12 @@
       <c r="AJ348" s="2" t="n">
         <v>0.0007886435331231604</v>
       </c>
+      <c r="AK348" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="AL348" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -39621,6 +41715,12 @@
       <c r="AJ349" s="3" t="n">
         <v>-0.0003856834310398025</v>
       </c>
+      <c r="AK349" s="1" t="n">
+        <v>5185.2</v>
+      </c>
+      <c r="AL349" s="2" t="n">
+        <v>0.0003086657921134837</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -39733,6 +41833,12 @@
       <c r="AJ350" s="3" t="n">
         <v>-0.0003603603603603457</v>
       </c>
+      <c r="AK350" s="1" t="n">
+        <v>0.02767</v>
+      </c>
+      <c r="AL350" s="3" t="n">
+        <v>-0.002523431867339604</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -39845,6 +41951,12 @@
       <c r="AJ351" s="3" t="n">
         <v>-0.01007919366450693</v>
       </c>
+      <c r="AK351" s="1" t="n">
+        <v>0.001376</v>
+      </c>
+      <c r="AL351" s="2" t="n">
+        <v>0.0007272727272728238</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -39957,6 +42069,12 @@
       <c r="AJ352" s="2" t="n">
         <v>0.001250781738586566</v>
       </c>
+      <c r="AK352" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="AL352" s="3" t="n">
+        <v>-0.003123048094940752</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -40069,6 +42187,12 @@
       <c r="AJ353" s="3" t="n">
         <v>-0.002538473742662227</v>
       </c>
+      <c r="AK353" s="1" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="AL353" s="3" t="n">
+        <v>-0.001113408620963842</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -40181,6 +42305,12 @@
       <c r="AJ354" s="3" t="n">
         <v>-0.008541168431841483</v>
       </c>
+      <c r="AK354" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AL354" s="3" t="n">
+        <v>-0.004824259131633399</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -40293,6 +42423,12 @@
       <c r="AJ355" s="3" t="n">
         <v>-0.0009585430146179081</v>
       </c>
+      <c r="AK355" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="AL355" s="3" t="n">
+        <v>-0.000479731350443732</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -40405,6 +42541,12 @@
       <c r="AJ356" s="3" t="n">
         <v>-0.0008851907586085054</v>
       </c>
+      <c r="AK356" s="1" t="n">
+        <v>0.11303</v>
+      </c>
+      <c r="AL356" s="2" t="n">
+        <v>0.001417560024807366</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -40517,6 +42659,12 @@
       <c r="AJ357" s="3" t="n">
         <v>-0.07084704659622389</v>
       </c>
+      <c r="AK357" s="1" t="n">
+        <v>0.005242</v>
+      </c>
+      <c r="AL357" s="3" t="n">
+        <v>-0.02274422073079786</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -40629,6 +42777,12 @@
       <c r="AJ358" s="3" t="n">
         <v>-0.001073537305421394</v>
       </c>
+      <c r="AK358" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AL358" s="3" t="n">
+        <v>-0.0005373455131649059</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -40741,6 +42895,12 @@
       <c r="AJ359" s="3" t="n">
         <v>-0.00178997613365152</v>
       </c>
+      <c r="AK359" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="AL359" s="2" t="n">
+        <v>0.004781829049611447</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -40853,6 +43013,12 @@
       <c r="AJ360" s="3" t="n">
         <v>-0.004953998584571713</v>
       </c>
+      <c r="AK360" s="1" t="n">
+        <v>0.08438</v>
+      </c>
+      <c r="AL360" s="2" t="n">
+        <v>0.0002370791844475136</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -40965,6 +43131,12 @@
       <c r="AJ361" s="3" t="n">
         <v>-0.01423027166882275</v>
       </c>
+      <c r="AK361" s="1" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="AL361" s="3" t="n">
+        <v>-0.00131233595800531</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -41077,6 +43249,12 @@
       <c r="AJ362" s="2" t="n">
         <v>0.009863785814936547</v>
       </c>
+      <c r="AK362" s="1" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="AL362" s="3" t="n">
+        <v>-0.001395348837209278</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -41189,6 +43367,12 @@
       <c r="AJ363" s="3" t="n">
         <v>-0.0002679528403001966</v>
       </c>
+      <c r="AK363" s="1" t="n">
+        <v>3.711</v>
+      </c>
+      <c r="AL363" s="3" t="n">
+        <v>-0.005360493165371219</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -41301,6 +43485,12 @@
       <c r="AJ364" s="2" t="n">
         <v>0.003610108303249107</v>
       </c>
+      <c r="AK364" s="1" t="n">
+        <v>0.01113</v>
+      </c>
+      <c r="AL364" s="2" t="n">
+        <v>0.0008992805755395317</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -41413,6 +43603,12 @@
       <c r="AJ365" s="2" t="n">
         <v>0.002354645897482307</v>
       </c>
+      <c r="AK365" s="1" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="AL365" s="3" t="n">
+        <v>-0.002710516805204144</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -41525,6 +43721,12 @@
       <c r="AJ366" s="2" t="n">
         <v>0.0008833922261483739</v>
       </c>
+      <c r="AK366" s="1" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="AL366" s="2" t="n">
+        <v>0.01059135039717567</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -41637,6 +43839,12 @@
       <c r="AJ367" s="3" t="n">
         <v>-0.01111934766493702</v>
       </c>
+      <c r="AK367" s="1" t="n">
+        <v>0.001338</v>
+      </c>
+      <c r="AL367" s="2" t="n">
+        <v>0.002998500749625261</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -41749,6 +43957,12 @@
       <c r="AJ368" s="2" t="n">
         <v>0.0003456619426200795</v>
       </c>
+      <c r="AK368" s="1" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AL368" s="2" t="n">
+        <v>0.002418797512094105</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -41861,6 +44075,12 @@
       <c r="AJ369" s="2" t="n">
         <v>0.004282655246252688</v>
       </c>
+      <c r="AK369" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="AL369" s="3" t="n">
+        <v>-0.001599147121535116</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -41973,6 +44193,12 @@
       <c r="AJ370" s="3" t="n">
         <v>-0.00394218134034167</v>
       </c>
+      <c r="AK370" s="1" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="AL370" s="3" t="n">
+        <v>-0.0003551857113863126</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -42085,6 +44311,12 @@
       <c r="AJ371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AL371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -42197,6 +44429,12 @@
       <c r="AJ372" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK372" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="AL372" s="3" t="n">
+        <v>-0.00189933523266862</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -42309,6 +44547,12 @@
       <c r="AJ373" s="3" t="n">
         <v>-0.00516717325227953</v>
       </c>
+      <c r="AK373" s="1" t="n">
+        <v>0.06566</v>
+      </c>
+      <c r="AL373" s="2" t="n">
+        <v>0.003055300947143169</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -42421,6 +44665,12 @@
       <c r="AJ374" s="2" t="n">
         <v>0.0007862665443585283</v>
       </c>
+      <c r="AK374" s="1" t="n">
+        <v>0.007625</v>
+      </c>
+      <c r="AL374" s="3" t="n">
+        <v>-0.00157129762995939</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -42533,6 +44783,12 @@
       <c r="AJ375" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK375" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="AL375" s="3" t="n">
+        <v>-0.0006242197253434254</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -42645,6 +44901,12 @@
       <c r="AJ376" s="2" t="n">
         <v>0.004109186968007081</v>
       </c>
+      <c r="AK376" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="AL376" s="3" t="n">
+        <v>-0.001169248757673223</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -42757,6 +45019,12 @@
       <c r="AJ377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK377" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AL377" s="3" t="n">
+        <v>-0.005988023952095772</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -42869,6 +45137,12 @@
       <c r="AJ378" s="2" t="n">
         <v>0.008904719501335654</v>
       </c>
+      <c r="AK378" s="1" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="AL378" s="3" t="n">
+        <v>-0.007060900264783778</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -42981,6 +45255,12 @@
       <c r="AJ379" s="3" t="n">
         <v>-0.001385681293302484</v>
       </c>
+      <c r="AK379" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="AL379" s="3" t="n">
+        <v>-0.005087881591119287</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -43093,6 +45373,12 @@
       <c r="AJ380" s="3" t="n">
         <v>-0.0005305039787798192</v>
       </c>
+      <c r="AK380" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AL380" s="3" t="n">
+        <v>-0.002123142250530699</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -43205,6 +45491,12 @@
       <c r="AJ381" s="2" t="n">
         <v>0.001672240802675633</v>
       </c>
+      <c r="AK381" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="AL381" s="2" t="n">
+        <v>0.0008347245409015264</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -43317,6 +45609,12 @@
       <c r="AJ382" s="2" t="n">
         <v>0.004108182129407689</v>
       </c>
+      <c r="AK382" s="1" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="AL382" s="2" t="n">
+        <v>0.004091374019775045</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -43429,6 +45727,12 @@
       <c r="AJ383" s="2" t="n">
         <v>0.002746833511368806</v>
       </c>
+      <c r="AK383" s="1" t="n">
+        <v>0.006563</v>
+      </c>
+      <c r="AL383" s="3" t="n">
+        <v>-0.001217470704611068</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -43541,6 +45845,12 @@
       <c r="AJ384" s="2" t="n">
         <v>0.002383222116301308</v>
       </c>
+      <c r="AK384" s="1" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="AL384" s="3" t="n">
+        <v>-0.0004755111745125817</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -43653,6 +45963,12 @@
       <c r="AJ385" s="3" t="n">
         <v>-0.001181102362204724</v>
       </c>
+      <c r="AK385" s="1" t="n">
+        <v>2531</v>
+      </c>
+      <c r="AL385" s="3" t="n">
+        <v>-0.002364998029168309</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -43765,6 +46081,12 @@
       <c r="AJ386" s="2" t="n">
         <v>0.0009995002498750911</v>
       </c>
+      <c r="AK386" s="1" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="AL386" s="3" t="n">
+        <v>-0.00299550673989025</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -43877,6 +46199,12 @@
       <c r="AJ387" s="3" t="n">
         <v>-0.001530131826741893</v>
       </c>
+      <c r="AK387" s="1" t="n">
+        <v>0.08486</v>
+      </c>
+      <c r="AL387" s="2" t="n">
+        <v>0.0003536484734174496</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -43989,6 +46317,12 @@
       <c r="AJ388" s="2" t="n">
         <v>0.02249203821656056</v>
       </c>
+      <c r="AK388" s="1" t="n">
+        <v>0.005402</v>
+      </c>
+      <c r="AL388" s="2" t="n">
+        <v>0.05158652910258898</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -44101,6 +46435,12 @@
       <c r="AJ389" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK389" s="1" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="AL389" s="3" t="n">
+        <v>-0.005664488017429265</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -44213,6 +46553,12 @@
       <c r="AJ390" s="2" t="n">
         <v>0.006718039913060578</v>
       </c>
+      <c r="AK390" s="1" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="AL390" s="2" t="n">
+        <v>0.002158979391560551</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -44325,6 +46671,12 @@
       <c r="AJ391" s="3" t="n">
         <v>-0.00197856553998356</v>
       </c>
+      <c r="AK391" s="1" t="n">
+        <v>0.0006051</v>
+      </c>
+      <c r="AL391" s="3" t="n">
+        <v>-0.0003304146704113743</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -44437,6 +46789,12 @@
       <c r="AJ392" s="3" t="n">
         <v>-0.0005134348793428418</v>
       </c>
+      <c r="AK392" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="AL392" s="3" t="n">
+        <v>-0.0001712328767123812</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -44549,6 +46907,12 @@
       <c r="AJ393" s="2" t="n">
         <v>0.000370782350760063</v>
       </c>
+      <c r="AK393" s="1" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="AL393" s="2" t="n">
+        <v>0.001482579688658308</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -44661,6 +47025,12 @@
       <c r="AJ394" s="2" t="n">
         <v>0.009010361916203658</v>
       </c>
+      <c r="AK394" s="1" t="n">
+        <v>0.006929</v>
+      </c>
+      <c r="AL394" s="2" t="n">
+        <v>0.03125465098973063</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -44773,6 +47143,12 @@
       <c r="AJ395" s="3" t="n">
         <v>-0.001737619461337896</v>
       </c>
+      <c r="AK395" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="AL395" s="3" t="n">
+        <v>-0.0008703220191471093</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -44885,6 +47261,12 @@
       <c r="AJ396" s="2" t="n">
         <v>0.00287081339712918</v>
       </c>
+      <c r="AK396" s="1" t="n">
+        <v>0.03124</v>
+      </c>
+      <c r="AL396" s="3" t="n">
+        <v>-0.006361323155216357</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -44997,6 +47379,12 @@
       <c r="AJ397" s="2" t="n">
         <v>0.003313452617627571</v>
       </c>
+      <c r="AK397" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="AL397" s="3" t="n">
+        <v>-0.0006605019815060551</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -45109,6 +47497,12 @@
       <c r="AJ398" s="2" t="n">
         <v>0.009060706735125231</v>
       </c>
+      <c r="AK398" s="1" t="n">
+        <v>0.003401</v>
+      </c>
+      <c r="AL398" s="2" t="n">
+        <v>0.01795869500149661</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -45221,6 +47615,12 @@
       <c r="AJ399" s="2" t="n">
         <v>0.009174311926605505</v>
       </c>
+      <c r="AK399" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="AL399" s="3" t="n">
+        <v>-0.007486631016042846</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -45333,6 +47733,12 @@
       <c r="AJ400" s="3" t="n">
         <v>-0.004285714285714359</v>
       </c>
+      <c r="AK400" s="1" t="n">
+        <v>0.006965</v>
+      </c>
+      <c r="AL400" s="3" t="n">
+        <v>-0.0007173601147775891</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -45445,6 +47851,12 @@
       <c r="AJ401" s="2" t="n">
         <v>0.007160246312473231</v>
       </c>
+      <c r="AK401" s="1" t="n">
+        <v>0.007146</v>
+      </c>
+      <c r="AL401" s="2" t="n">
+        <v>0.01606711218541154</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -45557,6 +47969,12 @@
       <c r="AJ402" s="3" t="n">
         <v>-0.004242575492887577</v>
       </c>
+      <c r="AK402" s="1" t="n">
+        <v>0.007998</v>
+      </c>
+      <c r="AL402" s="2" t="n">
+        <v>0.002255639097744443</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -45669,6 +48087,12 @@
       <c r="AJ403" s="2" t="n">
         <v>0.001217038539553844</v>
       </c>
+      <c r="AK403" s="1" t="n">
+        <v>0.04863</v>
+      </c>
+      <c r="AL403" s="3" t="n">
+        <v>-0.01478930307941656</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -45781,6 +48205,12 @@
       <c r="AJ404" s="2" t="n">
         <v>0.00673309991920262</v>
       </c>
+      <c r="AK404" s="1" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="AL404" s="2" t="n">
+        <v>0.003745318352059959</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -45893,6 +48323,12 @@
       <c r="AJ405" s="3" t="n">
         <v>-0.0009306654257793944</v>
       </c>
+      <c r="AK405" s="1" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="AL405" s="3" t="n">
+        <v>-0.001397298556124768</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -46005,6 +48441,12 @@
       <c r="AJ406" s="2" t="n">
         <v>0.001252086811352232</v>
       </c>
+      <c r="AK406" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AL406" s="2" t="n">
+        <v>0.0004168403501458482</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -46117,6 +48559,12 @@
       <c r="AJ407" s="3" t="n">
         <v>-0.00101378751013779</v>
       </c>
+      <c r="AK407" s="1" t="n">
+        <v>0.0004932</v>
+      </c>
+      <c r="AL407" s="2" t="n">
+        <v>0.001014816318246312</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -46229,6 +48677,12 @@
       <c r="AJ408" s="2" t="n">
         <v>0.007305194805194789</v>
       </c>
+      <c r="AK408" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="AL408" s="3" t="n">
+        <v>-0.004834810636583343</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -46341,6 +48795,12 @@
       <c r="AJ409" s="3" t="n">
         <v>-0.003152585119798238</v>
       </c>
+      <c r="AK409" s="1" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AL409" s="3" t="n">
+        <v>-0.002530044275774723</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -46453,6 +48913,12 @@
       <c r="AJ410" s="2" t="n">
         <v>0.0007153075822604255</v>
       </c>
+      <c r="AK410" s="1" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="AL410" s="2" t="n">
+        <v>0.000476530855372866</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -46565,6 +49031,12 @@
       <c r="AJ411" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK411" s="1" t="n">
+        <v>0.02976</v>
+      </c>
+      <c r="AL411" s="3" t="n">
+        <v>-0.001342281879194576</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -46677,6 +49149,12 @@
       <c r="AJ412" s="2" t="n">
         <v>0.001968503937007946</v>
       </c>
+      <c r="AK412" s="1" t="n">
+        <v>0.004577</v>
+      </c>
+      <c r="AL412" s="3" t="n">
+        <v>-0.000873171796550898</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -46789,6 +49267,12 @@
       <c r="AJ413" s="2" t="n">
         <v>0.003946329913180746</v>
       </c>
+      <c r="AK413" s="1" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="AL413" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -46901,6 +49385,12 @@
       <c r="AJ414" s="2" t="n">
         <v>0.001557632398753895</v>
       </c>
+      <c r="AK414" s="1" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AL414" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -47013,6 +49503,12 @@
       <c r="AJ415" s="3" t="n">
         <v>-0.002528901734103928</v>
       </c>
+      <c r="AK415" s="1" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="AL415" s="3" t="n">
+        <v>-0.002897500905469036</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -47125,6 +49621,12 @@
       <c r="AJ416" s="3" t="n">
         <v>-0.0006134969325153125</v>
       </c>
+      <c r="AK416" s="1" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="AL416" s="2" t="n">
+        <v>0.0009208103130755754</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -47237,6 +49739,12 @@
       <c r="AJ417" s="3" t="n">
         <v>-0.0007520681875157244</v>
       </c>
+      <c r="AK417" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="AL417" s="2" t="n">
+        <v>0.0005017561465127744</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -47349,6 +49857,12 @@
       <c r="AJ418" s="3" t="n">
         <v>-0.0001307360439272601</v>
       </c>
+      <c r="AK418" s="1" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="AL418" s="3" t="n">
+        <v>-0.001046025104602649</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -47461,6 +49975,12 @@
       <c r="AJ419" s="2" t="n">
         <v>0.001508295625942754</v>
       </c>
+      <c r="AK419" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="AL419" s="3" t="n">
+        <v>-0.004518072289156573</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -47573,6 +50093,12 @@
       <c r="AJ420" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK420" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="AL420" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -47685,6 +50211,12 @@
       <c r="AJ421" s="3" t="n">
         <v>-0.002919099249374504</v>
       </c>
+      <c r="AK421" s="1" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="AL421" s="2" t="n">
+        <v>0.0004182350480969844</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -47797,6 +50329,12 @@
       <c r="AJ422" s="2" t="n">
         <v>0.0113207547169812</v>
       </c>
+      <c r="AK422" s="1" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="AL422" s="2" t="n">
+        <v>0.003731343283582067</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -47909,6 +50447,12 @@
       <c r="AJ423" s="2" t="n">
         <v>0.001972386587771168</v>
       </c>
+      <c r="AK423" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="AL423" s="3" t="n">
+        <v>-0.0006561679790027345</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -48021,6 +50565,12 @@
       <c r="AJ424" s="3" t="n">
         <v>-0.001916626736943027</v>
       </c>
+      <c r="AK424" s="1" t="n">
+        <v>0.0002076</v>
+      </c>
+      <c r="AL424" s="3" t="n">
+        <v>-0.003360537686029716</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -48133,6 +50683,12 @@
       <c r="AJ425" s="2" t="n">
         <v>0.001603849238171613</v>
       </c>
+      <c r="AK425" s="1" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AL425" s="3" t="n">
+        <v>-0.001601281024819857</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -48245,6 +50801,12 @@
       <c r="AJ426" s="3" t="n">
         <v>-0.0007057163020466562</v>
       </c>
+      <c r="AK426" s="1" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AL426" s="3" t="n">
+        <v>-0.001412429378531075</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -48357,6 +50919,12 @@
       <c r="AJ427" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK427" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AL427" s="3" t="n">
+        <v>-0.0005122950819671922</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -48469,6 +51037,12 @@
       <c r="AJ428" s="2" t="n">
         <v>0.002268945696566289</v>
       </c>
+      <c r="AK428" s="1" t="n">
+        <v>0.06637999999999999</v>
+      </c>
+      <c r="AL428" s="2" t="n">
+        <v>0.001811047389073274</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -48581,6 +51155,12 @@
       <c r="AJ429" s="3" t="n">
         <v>-0.001510574018126722</v>
       </c>
+      <c r="AK429" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="AL429" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -48693,6 +51273,12 @@
       <c r="AJ430" s="3" t="n">
         <v>-0.001806847953744775</v>
       </c>
+      <c r="AK430" s="1" t="n">
+        <v>0.011059</v>
+      </c>
+      <c r="AL430" s="2" t="n">
+        <v>0.0009050592813828937</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -48805,6 +51391,12 @@
       <c r="AJ431" s="3" t="n">
         <v>-0.00209361447584868</v>
       </c>
+      <c r="AK431" s="1" t="n">
+        <v>0.006667</v>
+      </c>
+      <c r="AL431" s="3" t="n">
+        <v>-0.0008991458114790842</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -48917,6 +51509,12 @@
       <c r="AJ432" s="2" t="n">
         <v>0.001131221719457041</v>
       </c>
+      <c r="AK432" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="AL432" s="3" t="n">
+        <v>-0.00169491525423739</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -49029,6 +51627,12 @@
       <c r="AJ433" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK433" s="1" t="n">
+        <v>0.001372</v>
+      </c>
+      <c r="AL433" s="2" t="n">
+        <v>0.00365764447695685</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -49141,6 +51745,12 @@
       <c r="AJ434" s="3" t="n">
         <v>-0.007281553398058167</v>
       </c>
+      <c r="AK434" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="AL434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -49253,6 +51863,12 @@
       <c r="AJ435" s="3" t="n">
         <v>-0.001259346713892117</v>
       </c>
+      <c r="AK435" s="1" t="n">
+        <v>0.12707</v>
+      </c>
+      <c r="AL435" s="2" t="n">
+        <v>0.001418551501300226</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -49365,6 +51981,12 @@
       <c r="AJ436" s="3" t="n">
         <v>-0.004213483146067377</v>
       </c>
+      <c r="AK436" s="1" t="n">
+        <v>0.07774</v>
+      </c>
+      <c r="AL436" s="3" t="n">
+        <v>-0.003205539171688681</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -49477,6 +52099,12 @@
       <c r="AJ437" s="3" t="n">
         <v>-0.003174099349309636</v>
       </c>
+      <c r="AK437" s="1" t="n">
+        <v>0.6351</v>
+      </c>
+      <c r="AL437" s="2" t="n">
+        <v>0.01114472217799714</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -49589,6 +52217,12 @@
       <c r="AJ438" s="3" t="n">
         <v>-0.0002267573696145819</v>
       </c>
+      <c r="AK438" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="AL438" s="3" t="n">
+        <v>-0.0009072352007257513</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -49701,6 +52335,12 @@
       <c r="AJ439" s="2" t="n">
         <v>0.0002849002849003722</v>
       </c>
+      <c r="AK439" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="AL439" s="2" t="n">
+        <v>0.001566505269154073</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -49813,6 +52453,12 @@
       <c r="AJ440" s="3" t="n">
         <v>-0.001319261213720349</v>
       </c>
+      <c r="AK440" s="1" t="n">
+        <v>0.001513</v>
+      </c>
+      <c r="AL440" s="3" t="n">
+        <v>-0.000660501981505889</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -49925,6 +52571,12 @@
       <c r="AJ441" s="3" t="n">
         <v>-0.0003152585119797741</v>
       </c>
+      <c r="AK441" s="1" t="n">
+        <v>0.009519</v>
+      </c>
+      <c r="AL441" s="2" t="n">
+        <v>0.0006307158625038433</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -50037,6 +52689,12 @@
       <c r="AJ442" s="2" t="n">
         <v>0.001885014137606034</v>
       </c>
+      <c r="AK442" s="1" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="AL442" s="2" t="n">
+        <v>0.002822201317027388</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -50149,6 +52807,12 @@
       <c r="AJ443" s="2" t="n">
         <v>0.0004562043795621835</v>
       </c>
+      <c r="AK443" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="AL443" s="3" t="n">
+        <v>-0.001367989056087654</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -50261,6 +52925,12 @@
       <c r="AJ444" s="2" t="n">
         <v>0.004458431681090971</v>
       </c>
+      <c r="AK444" s="1" t="n">
+        <v>0.0003835</v>
+      </c>
+      <c r="AL444" s="2" t="n">
+        <v>0.001305483028720658</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -50373,6 +53043,12 @@
       <c r="AJ445" s="3" t="n">
         <v>-0.001117006422786885</v>
       </c>
+      <c r="AK445" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="AL445" s="3" t="n">
+        <v>-0.0002795638803467448</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -50485,6 +53161,12 @@
       <c r="AJ446" s="3" t="n">
         <v>-0.00376411543287324</v>
       </c>
+      <c r="AK446" s="1" t="n">
+        <v>0.08778</v>
+      </c>
+      <c r="AL446" s="2" t="n">
+        <v>0.005037783375314815</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -50597,6 +53279,12 @@
       <c r="AJ447" s="3" t="n">
         <v>-0.002139364303178384</v>
       </c>
+      <c r="AK447" s="1" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="AL447" s="3" t="n">
+        <v>-0.003062787136294098</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -50709,6 +53397,12 @@
       <c r="AJ448" s="2" t="n">
         <v>0.002337905236907906</v>
       </c>
+      <c r="AK448" s="1" t="n">
+        <v>0.06423</v>
+      </c>
+      <c r="AL448" s="3" t="n">
+        <v>-0.001243974498522945</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -50821,6 +53515,12 @@
       <c r="AJ449" s="2" t="n">
         <v>0.000610997963340168</v>
       </c>
+      <c r="AK449" s="1" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="AL449" s="2" t="n">
+        <v>0.005495623855078323</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -50933,6 +53633,12 @@
       <c r="AJ450" s="2" t="n">
         <v>0.002127659574467998</v>
       </c>
+      <c r="AK450" s="1" t="n">
+        <v>0.03776</v>
+      </c>
+      <c r="AL450" s="2" t="n">
+        <v>0.002123142250530883</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -51045,6 +53751,12 @@
       <c r="AJ451" s="2" t="n">
         <v>0.001814882032667803</v>
       </c>
+      <c r="AK451" s="1" t="n">
+        <v>0.00551</v>
+      </c>
+      <c r="AL451" s="3" t="n">
+        <v>-0.001811594202898477</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -51157,6 +53869,12 @@
       <c r="AJ452" s="3" t="n">
         <v>-0.002295552367288418</v>
       </c>
+      <c r="AK452" s="1" t="n">
+        <v>0.10453</v>
+      </c>
+      <c r="AL452" s="2" t="n">
+        <v>0.002109097881315291</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -51269,6 +53987,12 @@
       <c r="AJ453" s="3" t="n">
         <v>-0.004294478527607187</v>
       </c>
+      <c r="AK453" s="1" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="AL453" s="3" t="n">
+        <v>-0.004313000616142983</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -51381,6 +54105,12 @@
       <c r="AJ454" s="2" t="n">
         <v>0.003134796238244478</v>
       </c>
+      <c r="AK454" s="1" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="AL454" s="2" t="n">
+        <v>0.007986111111111157</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -51493,6 +54223,12 @@
       <c r="AJ455" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK455" s="1" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="AL455" s="3" t="n">
+        <v>-0.001118568232662193</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -51605,6 +54341,12 @@
       <c r="AJ456" s="3" t="n">
         <v>-0.002363268062120229</v>
       </c>
+      <c r="AK456" s="1" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="AL456" s="2" t="n">
+        <v>0.001353637901861253</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -51717,6 +54459,12 @@
       <c r="AJ457" s="2" t="n">
         <v>0.001014198782961419</v>
       </c>
+      <c r="AK457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="AL457" s="3" t="n">
+        <v>-0.001013171225937142</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -51829,6 +54577,12 @@
       <c r="AJ458" s="2" t="n">
         <v>0.002229654403567467</v>
       </c>
+      <c r="AK458" s="1" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="AL458" s="3" t="n">
+        <v>-0.002065787382806374</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -51941,6 +54695,12 @@
       <c r="AJ459" s="3" t="n">
         <v>-0.001394700139470078</v>
       </c>
+      <c r="AK459" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="AL459" s="3" t="n">
+        <v>-0.002793296089385482</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -52053,6 +54813,12 @@
       <c r="AJ460" s="2" t="n">
         <v>0.001438668918496198</v>
       </c>
+      <c r="AK460" s="1" t="n">
+        <v>0.016001</v>
+      </c>
+      <c r="AL460" s="3" t="n">
+        <v>-0.0005621486570892313</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -52165,6 +54931,12 @@
       <c r="AJ461" s="3" t="n">
         <v>-0.001796407185628669</v>
       </c>
+      <c r="AK461" s="1" t="n">
+        <v>0.01663</v>
+      </c>
+      <c r="AL461" s="3" t="n">
+        <v>-0.002399520095980914</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -52277,6 +55049,12 @@
       <c r="AJ462" s="3" t="n">
         <v>-0.002398081534772241</v>
       </c>
+      <c r="AK462" s="1" t="n">
+        <v>0.0002079</v>
+      </c>
+      <c r="AL462" s="3" t="n">
+        <v>-0.0004807692307691122</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -52389,6 +55167,12 @@
       <c r="AJ463" s="3" t="n">
         <v>-0.002010050251256339</v>
       </c>
+      <c r="AK463" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="AL463" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -52501,6 +55285,12 @@
       <c r="AJ464" s="2" t="n">
         <v>0.02554327106366757</v>
       </c>
+      <c r="AK464" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="AL464" s="3" t="n">
+        <v>-0.01115241635687739</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -52613,6 +55403,12 @@
       <c r="AJ465" s="3" t="n">
         <v>-0.008609271523178802</v>
       </c>
+      <c r="AK465" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="AL465" s="2" t="n">
+        <v>0.009352037408149598</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -52725,6 +55521,12 @@
       <c r="AJ466" s="3" t="n">
         <v>-0.0009107468123860564</v>
       </c>
+      <c r="AK466" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="AL466" s="2" t="n">
+        <v>0.0005469462169552471</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -52837,6 +55639,12 @@
       <c r="AJ467" s="2" t="n">
         <v>0.00291290416545304</v>
       </c>
+      <c r="AK467" s="1" t="n">
+        <v>0.03459</v>
+      </c>
+      <c r="AL467" s="2" t="n">
+        <v>0.004647110078419995</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -52949,6 +55757,12 @@
       <c r="AJ468" s="3" t="n">
         <v>-0.0003663003663004235</v>
       </c>
+      <c r="AK468" s="1" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="AL468" s="3" t="n">
+        <v>-0.004763649688530561</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -53061,6 +55875,12 @@
       <c r="AJ469" s="2" t="n">
         <v>0.00507749866381612</v>
       </c>
+      <c r="AK469" s="1" t="n">
+        <v>0.0007515</v>
+      </c>
+      <c r="AL469" s="3" t="n">
+        <v>-0.0009306035628821628</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -53173,6 +55993,12 @@
       <c r="AJ470" s="2" t="n">
         <v>0.00224466891133558</v>
       </c>
+      <c r="AK470" s="1" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AL470" s="3" t="n">
+        <v>-0.008958566629339313</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -53285,6 +56111,12 @@
       <c r="AJ471" s="3" t="n">
         <v>-0.001009081735620544</v>
       </c>
+      <c r="AK471" s="1" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="AL471" s="2" t="n">
+        <v>0.001010101010100969</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -53397,6 +56229,12 @@
       <c r="AJ472" s="2" t="n">
         <v>0.005507307773776665</v>
       </c>
+      <c r="AK472" s="1" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AL472" s="3" t="n">
+        <v>-0.001474615546661062</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -53509,6 +56347,12 @@
       <c r="AJ473" s="3" t="n">
         <v>-0.001824151769427218</v>
       </c>
+      <c r="AK473" s="1" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="AL473" s="2" t="n">
+        <v>0.0003654970760233516</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -53621,6 +56465,12 @@
       <c r="AJ474" s="2" t="n">
         <v>0.0006836827711940589</v>
       </c>
+      <c r="AK474" s="1" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="AL474" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -53733,6 +56583,12 @@
       <c r="AJ475" s="3" t="n">
         <v>-0.0004728691334671706</v>
       </c>
+      <c r="AK475" s="1" t="n">
+        <v>0.008456999999999999</v>
+      </c>
+      <c r="AL475" s="2" t="n">
+        <v>0.0002365464222351899</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -53845,6 +56701,12 @@
       <c r="AJ476" s="3" t="n">
         <v>-0.001588659415862216</v>
       </c>
+      <c r="AK476" s="1" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="AL476" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -53957,6 +56819,12 @@
       <c r="AJ477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK477" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="AL477" s="3" t="n">
+        <v>-0.0007352941176471819</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -54069,6 +56937,12 @@
       <c r="AJ478" s="2" t="n">
         <v>0.00652282990466631</v>
       </c>
+      <c r="AK478" s="1" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="AL478" s="3" t="n">
+        <v>-0.005732801595214418</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -54181,6 +57055,12 @@
       <c r="AJ479" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK479" s="1" t="n">
+        <v>0.008418999999999999</v>
+      </c>
+      <c r="AL479" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -54293,6 +57173,12 @@
       <c r="AJ480" s="3" t="n">
         <v>-0.01929437706725467</v>
       </c>
+      <c r="AK480" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AL480" s="2" t="n">
+        <v>0.0005621135469364583</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -54405,6 +57291,12 @@
       <c r="AJ481" s="3" t="n">
         <v>-0.0002576987501609618</v>
       </c>
+      <c r="AK481" s="1" t="n">
+        <v>0.07754999999999999</v>
+      </c>
+      <c r="AL481" s="3" t="n">
+        <v>-0.0005155303518496229</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -54517,6 +57409,12 @@
       <c r="AJ482" s="2" t="n">
         <v>0.0001992825827021946</v>
       </c>
+      <c r="AK482" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="AL482" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -54629,6 +57527,12 @@
       <c r="AJ483" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AL483" s="2" t="n">
+        <v>0.002066115702479434</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -54741,6 +57645,12 @@
       <c r="AJ484" s="2" t="n">
         <v>0.000734322220590518</v>
       </c>
+      <c r="AK484" s="1" t="n">
+        <v>0.06804</v>
+      </c>
+      <c r="AL484" s="3" t="n">
+        <v>-0.001467566774288272</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -54853,6 +57763,12 @@
       <c r="AJ485" s="2" t="n">
         <v>0.002886323268205989</v>
       </c>
+      <c r="AK485" s="1" t="n">
+        <v>0.0004525</v>
+      </c>
+      <c r="AL485" s="2" t="n">
+        <v>0.001771087004649146</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -54965,6 +57881,12 @@
       <c r="AJ486" s="3" t="n">
         <v>-0.005959031657355609</v>
       </c>
+      <c r="AK486" s="1" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="AL486" s="2" t="n">
+        <v>0.00537030098663669</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -55077,6 +57999,12 @@
       <c r="AJ487" s="3" t="n">
         <v>-0.002289639381797267</v>
       </c>
+      <c r="AK487" s="1" t="n">
+        <v>0.0001739</v>
+      </c>
+      <c r="AL487" s="3" t="n">
+        <v>-0.002294893861158977</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -55189,6 +58117,12 @@
       <c r="AJ488" s="3" t="n">
         <v>-0.001007162041181657</v>
       </c>
+      <c r="AK488" s="1" t="n">
+        <v>0.08967</v>
+      </c>
+      <c r="AL488" s="2" t="n">
+        <v>0.004480788618796881</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -55301,6 +58235,12 @@
       <c r="AJ489" s="2" t="n">
         <v>0.01166423661737149</v>
       </c>
+      <c r="AK489" s="1" t="n">
+        <v>0.04831</v>
+      </c>
+      <c r="AL489" s="3" t="n">
+        <v>-0.005353098620547731</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -55413,6 +58353,12 @@
       <c r="AJ490" s="3" t="n">
         <v>-0.00596318382162305</v>
       </c>
+      <c r="AK490" s="1" t="n">
+        <v>0.03798</v>
+      </c>
+      <c r="AL490" s="3" t="n">
+        <v>-0.009389671361502327</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -55525,6 +58471,12 @@
       <c r="AJ491" s="3" t="n">
         <v>-0.09473684210526324</v>
       </c>
+      <c r="AK491" s="1" t="n">
+        <v>0.08376</v>
+      </c>
+      <c r="AL491" s="3" t="n">
+        <v>-0.02604651162790688</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -55637,6 +58589,12 @@
       <c r="AJ492" s="3" t="n">
         <v>-0.003007280785058495</v>
       </c>
+      <c r="AK492" s="1" t="n">
+        <v>0.06351</v>
+      </c>
+      <c r="AL492" s="2" t="n">
+        <v>0.008255278615653162</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -55749,6 +58707,12 @@
       <c r="AJ493" s="2" t="n">
         <v>0.001904761904761827</v>
       </c>
+      <c r="AK493" s="1" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="AL493" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -55861,6 +58825,12 @@
       <c r="AJ494" s="3" t="n">
         <v>-0.001454016721192335</v>
       </c>
+      <c r="AK494" s="1" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AL494" s="3" t="n">
+        <v>-0.0003640334910811394</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -55973,6 +58943,12 @@
       <c r="AJ495" s="2" t="n">
         <v>0.0003132832080201461</v>
       </c>
+      <c r="AK495" s="1" t="n">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="AL495" s="3" t="n">
+        <v>-0.0003131850923896982</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -56085,6 +59061,12 @@
       <c r="AJ496" s="2" t="n">
         <v>0.0003411804844762504</v>
       </c>
+      <c r="AK496" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AL496" s="3" t="n">
+        <v>-0.00136425648021832</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -56197,6 +59179,12 @@
       <c r="AJ497" s="2" t="n">
         <v>0.002757583354224091</v>
       </c>
+      <c r="AK497" s="1" t="n">
+        <v>0.07983999999999999</v>
+      </c>
+      <c r="AL497" s="3" t="n">
+        <v>-0.002000000000000092</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -56309,6 +59297,12 @@
       <c r="AJ498" s="2" t="n">
         <v>0.001945525291828714</v>
       </c>
+      <c r="AK498" s="1" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="AL498" s="3" t="n">
+        <v>-0.003883495145631045</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -56421,6 +59415,12 @@
       <c r="AJ499" s="2" t="n">
         <v>0.0009510223490251633</v>
       </c>
+      <c r="AK499" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AL499" s="3" t="n">
+        <v>-0.003800475059382433</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -56533,6 +59533,12 @@
       <c r="AJ500" s="2" t="n">
         <v>0.003736920777279456</v>
       </c>
+      <c r="AK500" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="AL500" s="2" t="n">
+        <v>0.00670141474311242</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -56645,6 +59651,12 @@
       <c r="AJ501" s="2" t="n">
         <v>0.002004008016032122</v>
       </c>
+      <c r="AK501" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AL501" s="3" t="n">
+        <v>-0.002000000000000057</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -56757,6 +59769,12 @@
       <c r="AJ502" s="3" t="n">
         <v>-0.0003011141222523736</v>
       </c>
+      <c r="AK502" s="1" t="n">
+        <v>0.003324</v>
+      </c>
+      <c r="AL502" s="2" t="n">
+        <v>0.001204819277108463</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -56869,6 +59887,12 @@
       <c r="AJ503" s="3" t="n">
         <v>-0.007650273224043783</v>
       </c>
+      <c r="AK503" s="1" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="AL503" s="2" t="n">
+        <v>0.002202643171806269</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -56981,6 +60005,12 @@
       <c r="AJ504" s="2" t="n">
         <v>0.003768844221105461</v>
       </c>
+      <c r="AK504" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="AL504" s="3" t="n">
+        <v>-0.008135168961201474</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -57093,6 +60123,12 @@
       <c r="AJ505" s="2" t="n">
         <v>0.0007575757575756741</v>
       </c>
+      <c r="AK505" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="AL505" s="3" t="n">
+        <v>-0.001514004542013669</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -57205,6 +60241,12 @@
       <c r="AJ506" s="3" t="n">
         <v>-0.00117302052785919</v>
       </c>
+      <c r="AK506" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="AL506" s="3" t="n">
+        <v>-0.0005871990604814793</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -57317,6 +60359,12 @@
       <c r="AJ507" s="2" t="n">
         <v>0.0006954102920722642</v>
       </c>
+      <c r="AK507" s="1" t="n">
+        <v>0.002873</v>
+      </c>
+      <c r="AL507" s="3" t="n">
+        <v>-0.001737317581653856</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -57429,6 +60477,12 @@
       <c r="AJ508" s="2" t="n">
         <v>0.002270663033605764</v>
       </c>
+      <c r="AK508" s="1" t="n">
+        <v>2.199</v>
+      </c>
+      <c r="AL508" s="3" t="n">
+        <v>-0.003624830086089718</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -57541,6 +60595,12 @@
       <c r="AJ509" s="2" t="n">
         <v>0.001633986928104572</v>
       </c>
+      <c r="AK509" s="1" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="AL509" s="2" t="n">
+        <v>0.0005437737901033577</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -57653,6 +60713,12 @@
       <c r="AJ510" s="3" t="n">
         <v>-0.02386554621848736</v>
       </c>
+      <c r="AK510" s="1" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="AL510" s="2" t="n">
+        <v>0.004476584022038624</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -57765,6 +60831,12 @@
       <c r="AJ511" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK511" s="1" t="n">
+        <v>0.04041</v>
+      </c>
+      <c r="AL511" s="2" t="n">
+        <v>0.001486988847583755</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -57877,6 +60949,12 @@
       <c r="AJ512" s="2" t="n">
         <v>0.01086956521739131</v>
       </c>
+      <c r="AK512" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AL512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -57989,6 +61067,12 @@
       <c r="AJ513" s="2" t="n">
         <v>0.003074866310160488</v>
       </c>
+      <c r="AK513" s="1" t="n">
+        <v>0.014965</v>
+      </c>
+      <c r="AL513" s="3" t="n">
+        <v>-0.002732240437158544</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -58101,6 +61185,12 @@
       <c r="AJ514" s="3" t="n">
         <v>-0.0005727376861398439</v>
       </c>
+      <c r="AK514" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="AL514" s="2" t="n">
+        <v>0.0005730659025788926</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -58213,6 +61303,12 @@
       <c r="AJ515" s="3" t="n">
         <v>-0.0009302325581395615</v>
       </c>
+      <c r="AK515" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="AL515" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -58325,6 +61421,12 @@
       <c r="AJ516" s="3" t="n">
         <v>-0.003731343283582099</v>
       </c>
+      <c r="AK516" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AL516" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -58437,6 +61539,12 @@
       <c r="AJ517" s="3" t="n">
         <v>-0.0001297690111601522</v>
       </c>
+      <c r="AK517" s="1" t="n">
+        <v>0.007698</v>
+      </c>
+      <c r="AL517" s="3" t="n">
+        <v>-0.000908500973393908</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -58549,6 +61657,12 @@
       <c r="AJ518" s="3" t="n">
         <v>-0.00569981000633311</v>
       </c>
+      <c r="AK518" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AL518" s="3" t="n">
+        <v>-0.006369426751592319</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -58661,6 +61775,12 @@
       <c r="AJ519" s="3" t="n">
         <v>-0.0009539709038873513</v>
       </c>
+      <c r="AK519" s="1" t="n">
+        <v>0.004199</v>
+      </c>
+      <c r="AL519" s="2" t="n">
+        <v>0.002387204583432703</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -58773,6 +61893,12 @@
       <c r="AJ520" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK520" s="1" t="n">
+        <v>0.001162</v>
+      </c>
+      <c r="AL520" s="3" t="n">
+        <v>-0.0008598452278589131</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -58885,6 +62011,12 @@
       <c r="AJ521" s="3" t="n">
         <v>-0.004477611940298584</v>
       </c>
+      <c r="AK521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="AL521" s="3" t="n">
+        <v>-0.0007496251874062664</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -58997,6 +62129,12 @@
       <c r="AJ522" s="3" t="n">
         <v>-0.00334594122781491</v>
       </c>
+      <c r="AK522" s="1" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="AL522" s="2" t="n">
+        <v>0.002043497299664219</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -59109,6 +62247,12 @@
       <c r="AJ523" s="3" t="n">
         <v>-0.0008534850640114437</v>
       </c>
+      <c r="AK523" s="1" t="n">
+        <v>0.07056</v>
+      </c>
+      <c r="AL523" s="2" t="n">
+        <v>0.004555808656036458</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -59221,6 +62365,12 @@
       <c r="AJ524" s="2" t="n">
         <v>0.01019541206457097</v>
       </c>
+      <c r="AK524" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="AL524" s="3" t="n">
+        <v>-0.003364171572750219</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -59333,6 +62483,12 @@
       <c r="AJ525" s="2" t="n">
         <v>0.004242424242424279</v>
       </c>
+      <c r="AK525" s="1" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="AL525" s="3" t="n">
+        <v>-0.001810500905250588</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -59445,6 +62601,12 @@
       <c r="AJ526" s="2" t="n">
         <v>0.0004482629809488569</v>
       </c>
+      <c r="AK526" s="1" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="AL526" s="3" t="n">
+        <v>-0.001568217459487626</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -59557,6 +62719,12 @@
       <c r="AJ527" s="3" t="n">
         <v>-0.002788104089219378</v>
       </c>
+      <c r="AK527" s="1" t="n">
+        <v>0.04289</v>
+      </c>
+      <c r="AL527" s="3" t="n">
+        <v>-0.0006989748369059238</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -59669,6 +62837,12 @@
       <c r="AJ528" s="2" t="n">
         <v>0.0007251631617115065</v>
       </c>
+      <c r="AK528" s="1" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="AL528" s="3" t="n">
+        <v>-0.001086956521739212</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -59781,6 +62955,12 @@
       <c r="AJ529" s="3" t="n">
         <v>-0.002893757751136829</v>
       </c>
+      <c r="AK529" s="1" t="n">
+        <v>0.0007234</v>
+      </c>
+      <c r="AL529" s="3" t="n">
+        <v>-0.0002763957987838652</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -59893,6 +63073,12 @@
       <c r="AJ530" s="3" t="n">
         <v>-0.003335715987610227</v>
       </c>
+      <c r="AK530" s="1" t="n">
+        <v>0.004193</v>
+      </c>
+      <c r="AL530" s="2" t="n">
+        <v>0.002390628735357302</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -60005,6 +63191,12 @@
       <c r="AJ531" s="2" t="n">
         <v>0.003799392097264357</v>
       </c>
+      <c r="AK531" s="1" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="AL531" s="2" t="n">
+        <v>0.0007570022710068978</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -60117,6 +63309,12 @@
       <c r="AJ532" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AK532" s="1" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="AL532" s="2" t="n">
+        <v>0.00677966101694923</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -60229,6 +63427,12 @@
       <c r="AJ533" s="2" t="n">
         <v>0.001121914734480134</v>
       </c>
+      <c r="AK533" s="1" t="n">
+        <v>0.05348</v>
+      </c>
+      <c r="AL533" s="3" t="n">
+        <v>-0.001120657452372013</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -60341,6 +63545,12 @@
       <c r="AJ534" s="2" t="n">
         <v>0.001329787234042591</v>
       </c>
+      <c r="AK534" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AL534" s="3" t="n">
+        <v>-0.001992031872510109</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -60453,6 +63663,12 @@
       <c r="AJ535" s="2" t="n">
         <v>0.008149010477299054</v>
       </c>
+      <c r="AK535" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="AL535" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -60565,6 +63781,12 @@
       <c r="AJ536" s="2" t="n">
         <v>0.001403931006819106</v>
       </c>
+      <c r="AK536" s="1" t="n">
+        <v>0.004996</v>
+      </c>
+      <c r="AL536" s="2" t="n">
+        <v>0.0006008411776486142</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -60677,6 +63899,12 @@
       <c r="AJ537" s="2" t="n">
         <v>0.004091374019774902</v>
       </c>
+      <c r="AK537" s="1" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AL537" s="3" t="n">
+        <v>-0.002037351443123903</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -60789,6 +64017,12 @@
       <c r="AJ538" s="2" t="n">
         <v>0.0007518796992482201</v>
       </c>
+      <c r="AK538" s="1" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AL538" s="3" t="n">
+        <v>-0.0007513148009016774</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -60901,6 +64135,12 @@
       <c r="AJ539" s="2" t="n">
         <v>0.005964214711729655</v>
       </c>
+      <c r="AK539" s="1" t="n">
+        <v>0.02529</v>
+      </c>
+      <c r="AL539" s="3" t="n">
+        <v>-0.0003952569169960313</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -61013,6 +64253,12 @@
       <c r="AJ540" s="3" t="n">
         <v>-0.0007001575354454467</v>
       </c>
+      <c r="AK540" s="1" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="AL540" s="2" t="n">
+        <v>0.0001751620248729396</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -61125,6 +64371,12 @@
       <c r="AJ541" s="3" t="n">
         <v>-0.008547008547008643</v>
       </c>
+      <c r="AK541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="AL541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -61237,6 +64489,12 @@
       <c r="AJ542" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="AK542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AL542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -61349,6 +64607,12 @@
       <c r="AJ543" s="3" t="n">
         <v>-0.0008132285172133273</v>
       </c>
+      <c r="AK543" s="1" t="n">
+        <v>0.003689</v>
+      </c>
+      <c r="AL543" s="2" t="n">
+        <v>0.0008138903960933164</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR543"/>
+  <dimension ref="A1:AT543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,8 @@
     <col width="18" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,6 +695,16 @@
           <t>change_05:15</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>price_05:30</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>change_05:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -829,6 +841,12 @@
       <c r="AR2" s="3" t="n">
         <v>-0.001246626670727647</v>
       </c>
+      <c r="AS2" s="1" t="n">
+        <v>70507.39999999999</v>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>6.950108152184929e-05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -965,6 +983,12 @@
       <c r="AR3" s="3" t="n">
         <v>-0.001209195691393913</v>
       </c>
+      <c r="AS3" s="1" t="n">
+        <v>2064.51</v>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>-0.000232446646230521</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1101,6 +1125,12 @@
       <c r="AR4" s="3" t="n">
         <v>-0.000802292263610237</v>
       </c>
+      <c r="AS4" s="1" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>-0.0004588208304657748</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1237,6 +1267,12 @@
       <c r="AR5" s="3" t="n">
         <v>-0.01261739192773669</v>
       </c>
+      <c r="AS5" s="1" t="n">
+        <v>0.013809</v>
+      </c>
+      <c r="AT5" s="2" t="n">
+        <v>0.002613809627532097</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1373,6 +1409,12 @@
       <c r="AR6" s="2" t="n">
         <v>0.0007477833564790153</v>
       </c>
+      <c r="AS6" s="1" t="n">
+        <v>0.09347</v>
+      </c>
+      <c r="AT6" s="3" t="n">
+        <v>-0.002241673783091395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1509,6 +1551,12 @@
       <c r="AR7" s="3" t="n">
         <v>-0.0008628748112461997</v>
       </c>
+      <c r="AS7" s="1" t="n">
+        <v>1.3882</v>
+      </c>
+      <c r="AT7" s="3" t="n">
+        <v>-0.0009355883411297999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1645,6 +1693,12 @@
       <c r="AR8" s="3" t="n">
         <v>-0.002208846429952106</v>
       </c>
+      <c r="AS8" s="1" t="n">
+        <v>36.094</v>
+      </c>
+      <c r="AT8" s="3" t="n">
+        <v>-0.001217554928330205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1781,6 +1835,12 @@
       <c r="AR9" s="3" t="n">
         <v>-0.001041379521578094</v>
       </c>
+      <c r="AS9" s="1" t="n">
+        <v>652.41</v>
+      </c>
+      <c r="AT9" s="2" t="n">
+        <v>0.0001686340640809653</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1917,6 +1977,12 @@
       <c r="AR10" s="2" t="n">
         <v>0.002077066322876373</v>
       </c>
+      <c r="AS10" s="1" t="n">
+        <v>14.005</v>
+      </c>
+      <c r="AT10" s="2" t="n">
+        <v>0.001000643270674085</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2053,6 +2119,12 @@
       <c r="AR11" s="3" t="n">
         <v>-0.0002344775839430283</v>
       </c>
+      <c r="AS11" s="1" t="n">
+        <v>212.93</v>
+      </c>
+      <c r="AT11" s="3" t="n">
+        <v>-0.001219569398189366</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2189,6 +2261,12 @@
       <c r="AR12" s="3" t="n">
         <v>-0.0009245176105692655</v>
       </c>
+      <c r="AS12" s="1" t="n">
+        <v>0.0033435</v>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>-0.001940298507462685</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2325,6 +2403,12 @@
       <c r="AR13" s="3" t="n">
         <v>-0.02694097477345082</v>
       </c>
+      <c r="AS13" s="1" t="n">
+        <v>0.04033</v>
+      </c>
+      <c r="AT13" s="2" t="n">
+        <v>0.01510193808205377</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2461,6 +2545,12 @@
       <c r="AR14" s="2" t="n">
         <v>0.002278769464489093</v>
       </c>
+      <c r="AS14" s="1" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="AT14" s="2" t="n">
+        <v>0.00151572565365669</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2597,6 +2687,12 @@
       <c r="AR15" s="2" t="n">
         <v>0.0009125012673628835</v>
       </c>
+      <c r="AS15" s="1" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>-0.001823338735818388</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2733,6 +2829,12 @@
       <c r="AR16" s="2" t="n">
         <v>0.002661934338953049</v>
       </c>
+      <c r="AS16" s="1" t="n">
+        <v>0.05658</v>
+      </c>
+      <c r="AT16" s="2" t="n">
+        <v>0.001415929203539765</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2869,6 +2971,12 @@
       <c r="AR17" s="3" t="n">
         <v>-0.001136363636363637</v>
       </c>
+      <c r="AS17" s="1" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="AT17" s="2" t="n">
+        <v>0.009101251422070543</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3005,6 +3113,12 @@
       <c r="AR18" s="3" t="n">
         <v>-0.0007572889057174478</v>
       </c>
+      <c r="AS18" s="1" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>-0.001515725653656731</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3141,6 +3255,12 @@
       <c r="AR19" s="2" t="n">
         <v>0.002138435565559884</v>
       </c>
+      <c r="AS19" s="1" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AT19" s="2" t="n">
+        <v>0.005503144654088099</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3277,6 +3397,12 @@
       <c r="AR20" s="3" t="n">
         <v>-0.002588259654208547</v>
       </c>
+      <c r="AS20" s="1" t="n">
+        <v>9.618</v>
+      </c>
+      <c r="AT20" s="3" t="n">
+        <v>-0.00166078472078057</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3413,6 +3539,12 @@
       <c r="AR21" s="2" t="n">
         <v>0.003445176752546423</v>
       </c>
+      <c r="AS21" s="1" t="n">
+        <v>202.42</v>
+      </c>
+      <c r="AT21" s="2" t="n">
+        <v>0.007215007215007159</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3549,6 +3681,12 @@
       <c r="AR22" s="3" t="n">
         <v>-0.003556258026276753</v>
       </c>
+      <c r="AS22" s="1" t="n">
+        <v>0.020094</v>
+      </c>
+      <c r="AT22" s="3" t="n">
+        <v>-0.003965500148706265</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3685,6 +3823,12 @@
       <c r="AR23" s="2" t="n">
         <v>0.0005912754029433222</v>
       </c>
+      <c r="AS23" s="1" t="n">
+        <v>457.31</v>
+      </c>
+      <c r="AT23" s="2" t="n">
+        <v>0.0008754459302706819</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3821,6 +3965,12 @@
       <c r="AR24" s="2" t="n">
         <v>0.0001565519907229223</v>
       </c>
+      <c r="AS24" s="1" t="n">
+        <v>5174.33</v>
+      </c>
+      <c r="AT24" s="3" t="n">
+        <v>-9.275702876056761e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3957,6 +4107,12 @@
       <c r="AR25" s="3" t="n">
         <v>-0.001214262059829919</v>
       </c>
+      <c r="AS25" s="1" t="n">
+        <v>9.042</v>
+      </c>
+      <c r="AT25" s="3" t="n">
+        <v>-0.0006631299734748262</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4093,6 +4249,12 @@
       <c r="AR26" s="3" t="n">
         <v>-0.001941419768717886</v>
       </c>
+      <c r="AS26" s="1" t="n">
+        <v>0.11628</v>
+      </c>
+      <c r="AT26" s="3" t="n">
+        <v>-0.01657645466847094</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4229,6 +4391,12 @@
       <c r="AR27" s="3" t="n">
         <v>-0.001694915254237219</v>
       </c>
+      <c r="AS27" s="1" t="n">
+        <v>0.01172</v>
+      </c>
+      <c r="AT27" s="3" t="n">
+        <v>-0.005093378607809934</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4365,6 +4533,12 @@
       <c r="AR28" s="2" t="n">
         <v>0.0007739938080494503</v>
       </c>
+      <c r="AS28" s="1" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="AT28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4501,6 +4675,12 @@
       <c r="AR29" s="2" t="n">
         <v>0.02555307837420679</v>
       </c>
+      <c r="AS29" s="1" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="AT29" s="2" t="n">
+        <v>0.01688963210702348</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4637,6 +4817,12 @@
       <c r="AR30" s="3" t="n">
         <v>-0.001305483028720628</v>
       </c>
+      <c r="AS30" s="1" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="AT30" s="3" t="n">
+        <v>-0.001960784313725564</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4773,6 +4959,12 @@
       <c r="AR31" s="2" t="n">
         <v>0.001975308641975357</v>
       </c>
+      <c r="AS31" s="1" t="n">
+        <v>0.002027</v>
+      </c>
+      <c r="AT31" s="3" t="n">
+        <v>-0.0009857072449481674</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4909,6 +5101,12 @@
       <c r="AR32" s="3" t="n">
         <v>-0.001503759398496179</v>
       </c>
+      <c r="AS32" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AT32" s="2" t="n">
+        <v>0.007781124497991912</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5045,6 +5243,12 @@
       <c r="AR33" s="2" t="n">
         <v>0.004060913705583731</v>
       </c>
+      <c r="AS33" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AT33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5181,6 +5385,12 @@
       <c r="AR34" s="3" t="n">
         <v>-0.0009478672985782262</v>
       </c>
+      <c r="AS34" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AT34" s="3" t="n">
+        <v>-0.001897533206831042</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5317,6 +5527,12 @@
       <c r="AR35" s="2" t="n">
         <v>0.005512679162072734</v>
       </c>
+      <c r="AS35" s="1" t="n">
+        <v>0.009169999999999999</v>
+      </c>
+      <c r="AT35" s="2" t="n">
+        <v>0.005482456140350844</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5453,6 +5669,12 @@
       <c r="AR36" s="3" t="n">
         <v>-0.0008386916410400404</v>
       </c>
+      <c r="AS36" s="1" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AT36" s="3" t="n">
+        <v>-0.001678791270285365</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5589,6 +5811,12 @@
       <c r="AR37" s="3" t="n">
         <v>-0.001729804532087804</v>
       </c>
+      <c r="AS37" s="1" t="n">
+        <v>0.005759</v>
+      </c>
+      <c r="AT37" s="3" t="n">
+        <v>-0.002079362328885784</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5725,6 +5953,12 @@
       <c r="AR38" s="3" t="n">
         <v>-0.003795866722901694</v>
       </c>
+      <c r="AS38" s="1" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="AT38" s="2" t="n">
+        <v>0.0005003463936572204</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5861,6 +6095,12 @@
       <c r="AR39" s="3" t="n">
         <v>-0.001392757660167143</v>
       </c>
+      <c r="AS39" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="AT39" s="3" t="n">
+        <v>-0.004383343295477147</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5997,6 +6237,12 @@
       <c r="AR40" s="2" t="n">
         <v>0.003676224851279961</v>
       </c>
+      <c r="AS40" s="1" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="AT40" s="3" t="n">
+        <v>-0.001864677677144211</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6133,6 +6379,12 @@
       <c r="AR41" s="3" t="n">
         <v>-0.004181600955794541</v>
       </c>
+      <c r="AS41" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="AT41" s="3" t="n">
+        <v>-0.003599280143971143</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6269,6 +6521,12 @@
       <c r="AR42" s="3" t="n">
         <v>-0.001885098743267576</v>
       </c>
+      <c r="AS42" s="1" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AT42" s="2" t="n">
+        <v>8.993614533685688e-05</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6405,6 +6663,12 @@
       <c r="AR43" s="2" t="n">
         <v>0.06455512572533849</v>
       </c>
+      <c r="AS43" s="1" t="n">
+        <v>0.8483000000000001</v>
+      </c>
+      <c r="AT43" s="3" t="n">
+        <v>-0.03667953667953668</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6541,6 +6805,12 @@
       <c r="AR44" s="3" t="n">
         <v>-0.0003640334910811071</v>
       </c>
+      <c r="AS44" s="1" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="AT44" s="2" t="n">
+        <v>0.001092498179169613</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6677,6 +6947,12 @@
       <c r="AR45" s="3" t="n">
         <v>-0.01080736251571401</v>
       </c>
+      <c r="AS45" s="1" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="AT45" s="3" t="n">
+        <v>-0.003433167049183396</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6813,6 +7089,12 @@
       <c r="AR46" s="2" t="n">
         <v>0.001427347987439339</v>
       </c>
+      <c r="AS46" s="1" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="AT46" s="3" t="n">
+        <v>-0.002565564424173352</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6949,6 +7231,12 @@
       <c r="AR47" s="3" t="n">
         <v>-0.0005109862033725661</v>
       </c>
+      <c r="AS47" s="1" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="AT47" s="3" t="n">
+        <v>-0.002556237218813851</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7085,6 +7373,12 @@
       <c r="AR48" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS48" s="1" t="n">
+        <v>0.16016</v>
+      </c>
+      <c r="AT48" s="2" t="n">
+        <v>0.0004372540445998297</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7221,6 +7515,12 @@
       <c r="AR49" s="3" t="n">
         <v>-0.0001673360107095559</v>
       </c>
+      <c r="AS49" s="1" t="n">
+        <v>0.06017</v>
+      </c>
+      <c r="AT49" s="2" t="n">
+        <v>0.007029288702928933</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7357,6 +7657,12 @@
       <c r="AR50" s="2" t="n">
         <v>0.002583979328165449</v>
       </c>
+      <c r="AS50" s="1" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="AT50" s="2" t="n">
+        <v>0.007731958762886641</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7493,6 +7799,12 @@
       <c r="AR51" s="3" t="n">
         <v>-0.1315313764310924</v>
       </c>
+      <c r="AS51" s="1" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="AT51" s="2" t="n">
+        <v>0.0655664585191794</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7629,6 +7941,12 @@
       <c r="AR52" s="2" t="n">
         <v>0.007424907188660073</v>
       </c>
+      <c r="AS52" s="1" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AT52" s="3" t="n">
+        <v>-0.002010050251256246</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7765,6 +8083,12 @@
       <c r="AR53" s="3" t="n">
         <v>-0.006866416978776639</v>
       </c>
+      <c r="AS53" s="1" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="AT53" s="2" t="n">
+        <v>0.003771213073538763</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7901,6 +8225,12 @@
       <c r="AR54" s="3" t="n">
         <v>-0.0006522933260092282</v>
       </c>
+      <c r="AS54" s="1" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AT54" s="3" t="n">
+        <v>-0.00034353636332402</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8037,6 +8367,12 @@
       <c r="AR55" s="2" t="n">
         <v>0.0001398601398601584</v>
       </c>
+      <c r="AS55" s="1" t="n">
+        <v>0.007141</v>
+      </c>
+      <c r="AT55" s="3" t="n">
+        <v>-0.001398405817368265</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8173,6 +8509,12 @@
       <c r="AR56" s="2" t="n">
         <v>0.003814147018030478</v>
       </c>
+      <c r="AS56" s="1" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="AT56" s="2" t="n">
+        <v>0.007944732297063939</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8309,6 +8651,12 @@
       <c r="AR57" s="3" t="n">
         <v>-0.004519505233111386</v>
       </c>
+      <c r="AS57" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AT57" s="2" t="n">
+        <v>0.002150537634408597</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8445,6 +8793,12 @@
       <c r="AR58" s="2" t="n">
         <v>0.007899534130038514</v>
       </c>
+      <c r="AS58" s="1" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="AT58" s="3" t="n">
+        <v>-0.004220257234726726</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8581,6 +8935,12 @@
       <c r="AR59" s="3" t="n">
         <v>-0.005211726384364825</v>
       </c>
+      <c r="AS59" s="1" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="AT59" s="3" t="n">
+        <v>-0.0006548788474131565</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8717,6 +9077,12 @@
       <c r="AR60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AT60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8853,6 +9219,12 @@
       <c r="AR61" s="2" t="n">
         <v>0.001289490651192816</v>
       </c>
+      <c r="AS61" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="AT61" s="3" t="n">
+        <v>-0.001287830006439187</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8989,6 +9361,12 @@
       <c r="AR62" s="3" t="n">
         <v>-0.00701754385964913</v>
       </c>
+      <c r="AS62" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="AT62" s="3" t="n">
+        <v>-0.002650176678445134</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9125,6 +9503,12 @@
       <c r="AR63" s="2" t="n">
         <v>0.00113992590481622</v>
       </c>
+      <c r="AS63" s="1" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="AT63" s="3" t="n">
+        <v>-0.001992598918303383</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9261,6 +9645,12 @@
       <c r="AR64" s="3" t="n">
         <v>-0.003077975376196955</v>
       </c>
+      <c r="AS64" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT64" s="2" t="n">
+        <v>0.001715265866209226</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9397,6 +9787,12 @@
       <c r="AR65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS65" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="AT65" s="3" t="n">
+        <v>-0.0008467400508043686</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9533,6 +9929,12 @@
       <c r="AR66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS66" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="AT66" s="3" t="n">
+        <v>-0.0009930486593843382</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9669,6 +10071,12 @@
       <c r="AR67" s="2" t="n">
         <v>0.003574865942527153</v>
       </c>
+      <c r="AS67" s="1" t="n">
+        <v>0.007283</v>
+      </c>
+      <c r="AT67" s="3" t="n">
+        <v>-0.002192081107000894</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9805,6 +10213,12 @@
       <c r="AR68" s="2" t="n">
         <v>0.00109469074986314</v>
       </c>
+      <c r="AS68" s="1" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="AT68" s="2" t="n">
+        <v>0.008747949699289237</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9941,6 +10355,12 @@
       <c r="AR69" s="2" t="n">
         <v>0.004398020890599178</v>
       </c>
+      <c r="AS69" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="AT69" s="2" t="n">
+        <v>0.002006933041415782</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10077,6 +10497,12 @@
       <c r="AR70" s="3" t="n">
         <v>-0.004291845493562235</v>
       </c>
+      <c r="AS70" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AT70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10213,6 +10639,12 @@
       <c r="AR71" s="2" t="n">
         <v>0.00809368004132938</v>
       </c>
+      <c r="AS71" s="1" t="n">
+        <v>5.923</v>
+      </c>
+      <c r="AT71" s="2" t="n">
+        <v>0.01178681243594123</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10349,6 +10781,12 @@
       <c r="AR72" s="3" t="n">
         <v>-0.02540937323546014</v>
       </c>
+      <c r="AS72" s="1" t="n">
+        <v>0.001727</v>
+      </c>
+      <c r="AT72" s="2" t="n">
+        <v>0.0005793742757821065</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10485,6 +10923,12 @@
       <c r="AR73" s="2" t="n">
         <v>0.001487462813429618</v>
       </c>
+      <c r="AS73" s="1" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="AT73" s="3" t="n">
+        <v>-0.0005304476978569329</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10621,6 +11065,12 @@
       <c r="AR74" s="2" t="n">
         <v>0.001659751037344446</v>
       </c>
+      <c r="AS74" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="AT74" s="3" t="n">
+        <v>-0.0008285004142502308</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10757,6 +11207,12 @@
       <c r="AR75" s="3" t="n">
         <v>-0.007303386628316767</v>
       </c>
+      <c r="AS75" s="1" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="AT75" s="2" t="n">
+        <v>0.0006817407112826731</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10893,6 +11349,12 @@
       <c r="AR76" s="2" t="n">
         <v>0.004641350210970539</v>
       </c>
+      <c r="AS76" s="1" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="AT76" s="2" t="n">
+        <v>0.002267954640907119</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11029,6 +11491,12 @@
       <c r="AR77" s="2" t="n">
         <v>0.003341820496499075</v>
       </c>
+      <c r="AS77" s="1" t="n">
+        <v>0.06294</v>
+      </c>
+      <c r="AT77" s="3" t="n">
+        <v>-0.001744647105471832</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11165,6 +11633,12 @@
       <c r="AR78" s="3" t="n">
         <v>-0.001791170582657145</v>
       </c>
+      <c r="AS78" s="1" t="n">
+        <v>0.09462</v>
+      </c>
+      <c r="AT78" s="3" t="n">
+        <v>-0.0012666244458519</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11301,6 +11775,12 @@
       <c r="AR79" s="3" t="n">
         <v>-0.002449779519843216</v>
       </c>
+      <c r="AS79" s="1" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AT79" s="3" t="n">
+        <v>-0.007858546168958695</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11437,6 +11917,12 @@
       <c r="AR80" s="2" t="n">
         <v>0.0003340013360052435</v>
       </c>
+      <c r="AS80" s="1" t="n">
+        <v>0.005985</v>
+      </c>
+      <c r="AT80" s="3" t="n">
+        <v>-0.0008347245409014686</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11573,6 +12059,12 @@
       <c r="AR81" s="2" t="n">
         <v>0.002949852507374579</v>
       </c>
+      <c r="AS81" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AT81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11709,6 +12201,12 @@
       <c r="AR82" s="2" t="n">
         <v>0.001972386587771123</v>
       </c>
+      <c r="AS82" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="AT82" s="3" t="n">
+        <v>-0.0009842519685038286</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11845,6 +12343,12 @@
       <c r="AR83" s="3" t="n">
         <v>-0.005352798053528044</v>
       </c>
+      <c r="AS83" s="1" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="AT83" s="2" t="n">
+        <v>0.006196999347684253</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11981,6 +12485,12 @@
       <c r="AR84" s="2" t="n">
         <v>0.001891891891891883</v>
       </c>
+      <c r="AS84" s="1" t="n">
+        <v>1.1172</v>
+      </c>
+      <c r="AT84" s="2" t="n">
+        <v>0.004585918532505963</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12117,6 +12627,12 @@
       <c r="AR85" s="2" t="n">
         <v>0.003861003861003838</v>
       </c>
+      <c r="AS85" s="1" t="n">
+        <v>0.01286</v>
+      </c>
+      <c r="AT85" s="3" t="n">
+        <v>-0.01076923076923073</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12253,6 +12769,12 @@
       <c r="AR86" s="3" t="n">
         <v>-0.003571428571428426</v>
       </c>
+      <c r="AS86" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AT86" s="3" t="n">
+        <v>-0.002389486260454112</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12389,6 +12911,12 @@
       <c r="AR87" s="3" t="n">
         <v>-0.002163721601154067</v>
       </c>
+      <c r="AS87" s="1" t="n">
+        <v>8.298</v>
+      </c>
+      <c r="AT87" s="3" t="n">
+        <v>-0.000361402240693906</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12525,6 +13053,12 @@
       <c r="AR88" s="3" t="n">
         <v>-0.001029239766081966</v>
       </c>
+      <c r="AS88" s="1" t="n">
+        <v>2.1279</v>
+      </c>
+      <c r="AT88" s="3" t="n">
+        <v>-0.003465555191308047</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12661,6 +13195,12 @@
       <c r="AR89" s="3" t="n">
         <v>-0.01626127357201424</v>
       </c>
+      <c r="AS89" s="1" t="n">
+        <v>0.00724</v>
+      </c>
+      <c r="AT89" s="2" t="n">
+        <v>0.005695235449368001</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12797,6 +13337,12 @@
       <c r="AR90" s="3" t="n">
         <v>-0.002624671916010559</v>
       </c>
+      <c r="AS90" s="1" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AT90" s="2" t="n">
+        <v>0.0006578947368422081</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12933,6 +13479,12 @@
       <c r="AR91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS91" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="AT91" s="3" t="n">
+        <v>-0.004424778761061935</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13069,6 +13621,12 @@
       <c r="AR92" s="3" t="n">
         <v>-0.007478427612655828</v>
       </c>
+      <c r="AS92" s="1" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="AT92" s="2" t="n">
+        <v>0.003284389489953566</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13205,6 +13763,12 @@
       <c r="AR93" s="3" t="n">
         <v>-0.001275031875796921</v>
       </c>
+      <c r="AS93" s="1" t="n">
+        <v>1.3331</v>
+      </c>
+      <c r="AT93" s="2" t="n">
+        <v>0.001126464403724885</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13341,6 +13905,12 @@
       <c r="AR94" s="2" t="n">
         <v>0.009235599036285309</v>
       </c>
+      <c r="AS94" s="1" t="n">
+        <v>0.056332</v>
+      </c>
+      <c r="AT94" s="2" t="n">
+        <v>0.01877238036676669</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13477,6 +14047,12 @@
       <c r="AR95" s="3" t="n">
         <v>-0.004166666666666671</v>
       </c>
+      <c r="AS95" s="1" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="AT95" s="2" t="n">
+        <v>0.0004184100418410743</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13613,6 +14189,12 @@
       <c r="AR96" s="2" t="n">
         <v>0.000555041628122048</v>
       </c>
+      <c r="AS96" s="1" t="n">
+        <v>1.0798</v>
+      </c>
+      <c r="AT96" s="3" t="n">
+        <v>-0.001664201183431769</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13749,6 +14331,12 @@
       <c r="AR97" s="2" t="n">
         <v>0.001558846453624363</v>
       </c>
+      <c r="AS97" s="1" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="AT97" s="3" t="n">
+        <v>-0.0003891050583657159</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13885,6 +14473,12 @@
       <c r="AR98" s="2" t="n">
         <v>0.003754906980713398</v>
       </c>
+      <c r="AS98" s="1" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="AT98" s="2" t="n">
+        <v>0.00238054752593108</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14021,6 +14615,12 @@
       <c r="AR99" s="3" t="n">
         <v>-0.00780894617134195</v>
       </c>
+      <c r="AS99" s="1" t="n">
+        <v>0.13068</v>
+      </c>
+      <c r="AT99" s="3" t="n">
+        <v>-0.001451822419194588</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14157,6 +14757,12 @@
       <c r="AR100" s="3" t="n">
         <v>-0.002251527822450969</v>
       </c>
+      <c r="AS100" s="1" t="n">
+        <v>0.03104</v>
+      </c>
+      <c r="AT100" s="2" t="n">
+        <v>0.000644745325596475</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14293,6 +14899,12 @@
       <c r="AR101" s="2" t="n">
         <v>0.006679389312976999</v>
       </c>
+      <c r="AS101" s="1" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="AT101" s="3" t="n">
+        <v>-0.0009478672985780947</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -14429,6 +15041,12 @@
       <c r="AR102" s="2" t="n">
         <v>0.0009074410163339013</v>
       </c>
+      <c r="AS102" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AT102" s="3" t="n">
+        <v>-0.0004533091568449498</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -14565,6 +15183,12 @@
       <c r="AR103" s="3" t="n">
         <v>-0.001543209876543147</v>
       </c>
+      <c r="AS103" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="AT103" s="3" t="n">
+        <v>-0.005151983513652725</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14701,6 +15325,12 @@
       <c r="AR104" s="3" t="n">
         <v>-0.0006666666666665932</v>
       </c>
+      <c r="AS104" s="1" t="n">
+        <v>2.998</v>
+      </c>
+      <c r="AT104" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14837,6 +15467,12 @@
       <c r="AR105" s="2" t="n">
         <v>0.0009273570324575312</v>
       </c>
+      <c r="AS105" s="1" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="AT105" s="2" t="n">
+        <v>0.0003088326127238422</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14973,6 +15609,12 @@
       <c r="AR106" s="3" t="n">
         <v>-0.001806140878988529</v>
       </c>
+      <c r="AS106" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="AT106" s="2" t="n">
+        <v>0.003618817852834677</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15109,6 +15751,12 @@
       <c r="AR107" s="3" t="n">
         <v>-0.01144114411441152</v>
       </c>
+      <c r="AS107" s="1" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="AT107" s="3" t="n">
+        <v>-0.006677053193857117</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15245,6 +15893,12 @@
       <c r="AR108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS108" s="1" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AT108" s="3" t="n">
+        <v>-0.0002977963073257564</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -15381,6 +16035,12 @@
       <c r="AR109" s="3" t="n">
         <v>-0.008384819064430648</v>
       </c>
+      <c r="AS109" s="1" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="AT109" s="3" t="n">
+        <v>-0.003560302625723288</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -15517,6 +16177,12 @@
       <c r="AR110" s="3" t="n">
         <v>-0.008086253369272258</v>
       </c>
+      <c r="AS110" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="AT110" s="2" t="n">
+        <v>0.008831521739130429</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -15653,6 +16319,12 @@
       <c r="AR111" s="2" t="n">
         <v>0.0005461496450027919</v>
       </c>
+      <c r="AS111" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="AT111" s="3" t="n">
+        <v>-0.0016375545851529</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -15789,6 +16461,12 @@
       <c r="AR112" s="2" t="n">
         <v>0.004688721021099234</v>
       </c>
+      <c r="AS112" s="1" t="n">
+        <v>0.03852</v>
+      </c>
+      <c r="AT112" s="3" t="n">
+        <v>-0.00129634430904852</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -15925,6 +16603,12 @@
       <c r="AR113" s="3" t="n">
         <v>-0.002133206921071425</v>
       </c>
+      <c r="AS113" s="1" t="n">
+        <v>4.206</v>
+      </c>
+      <c r="AT113" s="3" t="n">
+        <v>-0.0009501187648455011</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -16061,6 +16745,12 @@
       <c r="AR114" s="2" t="n">
         <v>0.01719043781896315</v>
       </c>
+      <c r="AS114" s="1" t="n">
+        <v>0.007545</v>
+      </c>
+      <c r="AT114" s="3" t="n">
+        <v>-0.003828888302086134</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -16197,6 +16887,12 @@
       <c r="AR115" s="2" t="n">
         <v>0.001593943016537232</v>
       </c>
+      <c r="AS115" s="1" t="n">
+        <v>0.10114</v>
+      </c>
+      <c r="AT115" s="2" t="n">
+        <v>0.005967774020290326</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -16333,6 +17029,12 @@
       <c r="AR116" s="2" t="n">
         <v>0.0002413127413128152</v>
       </c>
+      <c r="AS116" s="1" t="n">
+        <v>0.08282</v>
+      </c>
+      <c r="AT116" s="3" t="n">
+        <v>-0.0009650180940892248</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -16469,6 +17171,12 @@
       <c r="AR117" s="3" t="n">
         <v>-0.001331114808652284</v>
       </c>
+      <c r="AS117" s="1" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AT117" s="3" t="n">
+        <v>-0.000666444518493762</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -16605,6 +17313,12 @@
       <c r="AR118" s="3" t="n">
         <v>-0.001772264067345962</v>
       </c>
+      <c r="AS118" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="AT118" s="2" t="n">
+        <v>0.001331557922769586</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -16741,6 +17455,12 @@
       <c r="AR119" s="3" t="n">
         <v>-0.002636783124588078</v>
       </c>
+      <c r="AS119" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="AT119" s="3" t="n">
+        <v>-0.001321877065432769</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -16877,6 +17597,12 @@
       <c r="AR120" s="2" t="n">
         <v>0.001376462491397093</v>
       </c>
+      <c r="AS120" s="1" t="n">
+        <v>0.004424</v>
+      </c>
+      <c r="AT120" s="2" t="n">
+        <v>0.01351660939289806</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -17013,6 +17739,12 @@
       <c r="AR121" s="3" t="n">
         <v>-0.002781641168289242</v>
       </c>
+      <c r="AS121" s="1" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="AT121" s="3" t="n">
+        <v>-0.008368200836820194</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -17149,6 +17881,12 @@
       <c r="AR122" s="2" t="n">
         <v>0.002580645161290325</v>
       </c>
+      <c r="AS122" s="1" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AT122" s="3" t="n">
+        <v>-0.002574002574002576</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -17285,6 +18023,12 @@
       <c r="AR123" s="3" t="n">
         <v>-0.001156069364161722</v>
       </c>
+      <c r="AS123" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="AT123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -17421,6 +18165,12 @@
       <c r="AR124" s="2" t="n">
         <v>0.002452984464431767</v>
       </c>
+      <c r="AS124" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="AT124" s="2" t="n">
+        <v>0.008156606851549706</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -17557,6 +18307,12 @@
       <c r="AR125" s="3" t="n">
         <v>-0.0001020929045430947</v>
       </c>
+      <c r="AS125" s="1" t="n">
+        <v>0.09787</v>
+      </c>
+      <c r="AT125" s="3" t="n">
+        <v>-0.0007147232999795857</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -17693,6 +18449,12 @@
       <c r="AR126" s="2" t="n">
         <v>0.00699893955461302</v>
       </c>
+      <c r="AS126" s="1" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="AT126" s="3" t="n">
+        <v>-0.002737994945240063</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -17829,6 +18591,12 @@
       <c r="AR127" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS127" s="1" t="n">
+        <v>3.23e-05</v>
+      </c>
+      <c r="AT127" s="2" t="n">
+        <v>0.006230529595015516</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -17965,6 +18733,12 @@
       <c r="AR128" s="2" t="n">
         <v>0.0005281690140846444</v>
       </c>
+      <c r="AS128" s="1" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="AT128" s="2" t="n">
+        <v>0.001055780397677167</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18101,6 +18875,12 @@
       <c r="AR129" s="2" t="n">
         <v>0.0004623208506703998</v>
       </c>
+      <c r="AS129" s="1" t="n">
+        <v>0.06496</v>
+      </c>
+      <c r="AT129" s="2" t="n">
+        <v>0.0006161429451632528</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -18237,6 +19017,12 @@
       <c r="AR130" s="3" t="n">
         <v>-0.006589785831960443</v>
       </c>
+      <c r="AS130" s="1" t="n">
+        <v>0.000603</v>
+      </c>
+      <c r="AT130" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -18373,6 +19159,12 @@
       <c r="AR131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AT131" s="2" t="n">
+        <v>0.01149425287356323</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18509,6 +19301,12 @@
       <c r="AR132" s="3" t="n">
         <v>-0.00332115576220525</v>
       </c>
+      <c r="AS132" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AT132" s="3" t="n">
+        <v>-0.000333222259246881</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -18645,6 +19443,12 @@
       <c r="AR133" s="2" t="n">
         <v>0.004134672179562942</v>
       </c>
+      <c r="AS133" s="1" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="AT133" s="3" t="n">
+        <v>-0.00117647058823545</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -18781,6 +19585,12 @@
       <c r="AR134" s="3" t="n">
         <v>-0.002377954958735536</v>
       </c>
+      <c r="AS134" s="1" t="n">
+        <v>0.14234</v>
+      </c>
+      <c r="AT134" s="3" t="n">
+        <v>-0.002103196859225987</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -18917,6 +19727,12 @@
       <c r="AR135" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS135" s="1" t="n">
+        <v>0.02944</v>
+      </c>
+      <c r="AT135" s="3" t="n">
+        <v>-0.001695489996608951</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19053,6 +19869,12 @@
       <c r="AR136" s="3" t="n">
         <v>-0.001417936901807839</v>
       </c>
+      <c r="AS136" s="1" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AT136" s="2" t="n">
+        <v>0.002484913028043902</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -19189,6 +20011,12 @@
       <c r="AR137" s="2" t="n">
         <v>0.0004602991944764209</v>
       </c>
+      <c r="AS137" s="1" t="n">
+        <v>0.0004345</v>
+      </c>
+      <c r="AT137" s="3" t="n">
+        <v>-0.000460087416609167</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -19325,6 +20153,12 @@
       <c r="AR138" s="2" t="n">
         <v>0.00420109228399391</v>
       </c>
+      <c r="AS138" s="1" t="n">
+        <v>0.028604</v>
+      </c>
+      <c r="AT138" s="3" t="n">
+        <v>-0.002789011295495754</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -19461,6 +20295,12 @@
       <c r="AR139" s="3" t="n">
         <v>-0.001248699271592185</v>
       </c>
+      <c r="AS139" s="1" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="AT139" s="3" t="n">
+        <v>-0.001562825588664278</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -19597,6 +20437,12 @@
       <c r="AR140" s="2" t="n">
         <v>0.001391594767603675</v>
       </c>
+      <c r="AS140" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AT140" s="2" t="n">
+        <v>0.001389660922734854</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -19733,6 +20579,12 @@
       <c r="AR141" s="2" t="n">
         <v>0.0007487832272556789</v>
       </c>
+      <c r="AS141" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="AT141" s="3" t="n">
+        <v>-0.004863449307893813</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -19869,6 +20721,12 @@
       <c r="AR142" s="3" t="n">
         <v>-0.001382083176278414</v>
       </c>
+      <c r="AS142" s="1" t="n">
+        <v>0.07945000000000001</v>
+      </c>
+      <c r="AT142" s="3" t="n">
+        <v>-0.0003774534474080067</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -20005,6 +20863,12 @@
       <c r="AR143" s="2" t="n">
         <v>0.005761409850881118</v>
       </c>
+      <c r="AS143" s="1" t="n">
+        <v>0.08916</v>
+      </c>
+      <c r="AT143" s="2" t="n">
+        <v>0.001460181961136753</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -20141,6 +21005,12 @@
       <c r="AR144" s="3" t="n">
         <v>-0.004322766570605344</v>
       </c>
+      <c r="AS144" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="AT144" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -20277,6 +21147,12 @@
       <c r="AR145" s="3" t="n">
         <v>-0.001301744337412109</v>
       </c>
+      <c r="AS145" s="1" t="n">
+        <v>0.11559</v>
+      </c>
+      <c r="AT145" s="2" t="n">
+        <v>0.00443169968717411</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -20413,6 +21289,12 @@
       <c r="AR146" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS146" s="1" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AT146" s="2" t="n">
+        <v>0.002945990180032772</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -20549,6 +21431,12 @@
       <c r="AR147" s="3" t="n">
         <v>-0.008130081300813016</v>
       </c>
+      <c r="AS147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AT147" s="2" t="n">
+        <v>0.008196721311475417</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -20685,6 +21573,12 @@
       <c r="AR148" s="3" t="n">
         <v>-0.0004587389775217396</v>
       </c>
+      <c r="AS148" s="1" t="n">
+        <v>1.9486</v>
+      </c>
+      <c r="AT148" s="3" t="n">
+        <v>-0.006323304436511966</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -20821,6 +21715,12 @@
       <c r="AR149" s="3" t="n">
         <v>-0.0008069722401549618</v>
       </c>
+      <c r="AS149" s="1" t="n">
+        <v>0.06198</v>
+      </c>
+      <c r="AT149" s="2" t="n">
+        <v>0.001130673558391223</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -20957,6 +21857,12 @@
       <c r="AR150" s="3" t="n">
         <v>-0.0153846153846155</v>
       </c>
+      <c r="AS150" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AT150" s="2" t="n">
+        <v>0.001802884615384584</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -21093,6 +21999,12 @@
       <c r="AR151" s="2" t="n">
         <v>0.001045244139166655</v>
       </c>
+      <c r="AS151" s="1" t="n">
+        <v>6.706e-05</v>
+      </c>
+      <c r="AT151" s="2" t="n">
+        <v>0.0002983293556086396</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -21229,6 +22141,12 @@
       <c r="AR152" s="2" t="n">
         <v>0.002728512960436569</v>
       </c>
+      <c r="AS152" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AT152" s="3" t="n">
+        <v>-0.0006802721088435097</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -21365,6 +22283,12 @@
       <c r="AR153" s="3" t="n">
         <v>-0.001890359168242053</v>
       </c>
+      <c r="AS153" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="AT153" s="3" t="n">
+        <v>-0.00284090909090914</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -21501,6 +22425,12 @@
       <c r="AR154" s="2" t="n">
         <v>0.002024633035262225</v>
       </c>
+      <c r="AS154" s="1" t="n">
+        <v>0.0005939</v>
+      </c>
+      <c r="AT154" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -21637,6 +22567,12 @@
       <c r="AR155" s="3" t="n">
         <v>-0.0004980079681274698</v>
       </c>
+      <c r="AS155" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="AT155" s="2" t="n">
+        <v>0.0004982561036372493</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -21773,6 +22709,12 @@
       <c r="AR156" s="2" t="n">
         <v>0.004244031830238739</v>
       </c>
+      <c r="AS156" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="AT156" s="2" t="n">
+        <v>0.001584786053882845</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -21909,6 +22851,12 @@
       <c r="AR157" s="2" t="n">
         <v>0.003958380456910236</v>
       </c>
+      <c r="AS157" s="1" t="n">
+        <v>0.08953</v>
+      </c>
+      <c r="AT157" s="2" t="n">
+        <v>0.008561450940633061</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -22045,6 +22993,12 @@
       <c r="AR158" s="2" t="n">
         <v>0.004655048937693853</v>
       </c>
+      <c r="AS158" s="1" t="n">
+        <v>0.008408000000000001</v>
+      </c>
+      <c r="AT158" s="3" t="n">
+        <v>-0.001069264583580681</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -22181,6 +23135,12 @@
       <c r="AR159" s="2" t="n">
         <v>0.005557761016276217</v>
       </c>
+      <c r="AS159" s="1" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="AT159" s="2" t="n">
+        <v>0.00315831030398737</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -22317,6 +23277,12 @@
       <c r="AR160" s="3" t="n">
         <v>-0.0003107037439802532</v>
       </c>
+      <c r="AS160" s="1" t="n">
+        <v>1.2864</v>
+      </c>
+      <c r="AT160" s="3" t="n">
+        <v>-0.0004662004662004149</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -22453,6 +23419,12 @@
       <c r="AR161" s="3" t="n">
         <v>-0.00343324970289185</v>
       </c>
+      <c r="AS161" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="AT161" s="3" t="n">
+        <v>-0.003577580495561165</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -22589,6 +23561,12 @@
       <c r="AR162" s="3" t="n">
         <v>-0.004004004004004101</v>
       </c>
+      <c r="AS162" s="1" t="n">
+        <v>0.004059</v>
+      </c>
+      <c r="AT162" s="2" t="n">
+        <v>0.0198492462311558</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -22725,6 +23703,12 @@
       <c r="AR163" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS163" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="AT163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -22861,6 +23845,12 @@
       <c r="AR164" s="2" t="n">
         <v>7.224389539083151e-05</v>
       </c>
+      <c r="AS164" s="1" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="AT164" s="3" t="n">
+        <v>-0.0002167160297624713</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -22997,6 +23987,12 @@
       <c r="AR165" s="2" t="n">
         <v>0.006141985767536398</v>
       </c>
+      <c r="AS165" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="AT165" s="3" t="n">
+        <v>-0.006441291626320901</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23133,6 +24129,12 @@
       <c r="AR166" s="2" t="n">
         <v>0.004060324825985947</v>
       </c>
+      <c r="AS166" s="1" t="n">
+        <v>0.005207</v>
+      </c>
+      <c r="AT166" s="2" t="n">
+        <v>0.002695936838051247</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -23269,6 +24271,12 @@
       <c r="AR167" s="2" t="n">
         <v>0.001796676149124047</v>
       </c>
+      <c r="AS167" s="1" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="AT167" s="3" t="n">
+        <v>-0.001195635928859614</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -23405,6 +24413,12 @@
       <c r="AR168" s="3" t="n">
         <v>-0.004188481675392645</v>
       </c>
+      <c r="AS168" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AT168" s="3" t="n">
+        <v>-0.001051524710830735</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -23541,6 +24555,12 @@
       <c r="AR169" s="2" t="n">
         <v>0.00181582360570689</v>
       </c>
+      <c r="AS169" s="1" t="n">
+        <v>0.03861</v>
+      </c>
+      <c r="AT169" s="3" t="n">
+        <v>-0.0002589331952357085</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -23677,6 +24697,12 @@
       <c r="AR170" s="3" t="n">
         <v>-0.001402524544179588</v>
       </c>
+      <c r="AS170" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="AT170" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -23813,6 +24839,12 @@
       <c r="AR171" s="3" t="n">
         <v>-0.0008800234672923643</v>
       </c>
+      <c r="AS171" s="1" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AT171" s="3" t="n">
+        <v>-0.00117439812096304</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -23949,6 +24981,12 @@
       <c r="AR172" s="2" t="n">
         <v>0.001839249586168804</v>
       </c>
+      <c r="AS172" s="1" t="n">
+        <v>5.434</v>
+      </c>
+      <c r="AT172" s="3" t="n">
+        <v>-0.002386634844868717</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -24085,6 +25123,12 @@
       <c r="AR173" s="2" t="n">
         <v>0.0002193463478833749</v>
       </c>
+      <c r="AS173" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AT173" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -24221,6 +25265,12 @@
       <c r="AR174" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS174" s="1" t="n">
+        <v>0.03934</v>
+      </c>
+      <c r="AT174" s="2" t="n">
+        <v>0.002548419979612714</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -24357,6 +25407,12 @@
       <c r="AR175" s="2" t="n">
         <v>0.0001795654516071346</v>
       </c>
+      <c r="AS175" s="1" t="n">
+        <v>0.005587</v>
+      </c>
+      <c r="AT175" s="2" t="n">
+        <v>0.00305206463195685</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -24493,6 +25549,12 @@
       <c r="AR176" s="2" t="n">
         <v>0.001324503311258224</v>
       </c>
+      <c r="AS176" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="AT176" s="3" t="n">
+        <v>-0.001322751322751269</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -24629,6 +25691,12 @@
       <c r="AR177" s="3" t="n">
         <v>-0.003359462486002242</v>
       </c>
+      <c r="AS177" s="1" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AT177" s="3" t="n">
+        <v>-0.002808988764045009</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -24765,6 +25833,12 @@
       <c r="AR178" s="2" t="n">
         <v>0.0005084207181443213</v>
       </c>
+      <c r="AS178" s="1" t="n">
+        <v>15.748</v>
+      </c>
+      <c r="AT178" s="2" t="n">
+        <v>0.0003176014736707746</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -24901,6 +25975,12 @@
       <c r="AR179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS179" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AT179" s="2" t="n">
+        <v>0.003174603174603177</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -25037,6 +26117,12 @@
       <c r="AR180" s="3" t="n">
         <v>-0.006857025892948561</v>
       </c>
+      <c r="AS180" s="1" t="n">
+        <v>0.09704</v>
+      </c>
+      <c r="AT180" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -25173,6 +26259,12 @@
       <c r="AR181" s="3" t="n">
         <v>-0.002655337227827936</v>
       </c>
+      <c r="AS181" s="1" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="AT181" s="3" t="n">
+        <v>-0.0005324813631522311</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -25309,6 +26401,12 @@
       <c r="AR182" s="2" t="n">
         <v>0.000336530371866164</v>
       </c>
+      <c r="AS182" s="1" t="n">
+        <v>0.05945</v>
+      </c>
+      <c r="AT182" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -25445,6 +26543,12 @@
       <c r="AR183" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS183" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AT183" s="3" t="n">
+        <v>-0.002493765586034955</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -25581,6 +26685,12 @@
       <c r="AR184" s="2" t="n">
         <v>0.0009341429238674758</v>
       </c>
+      <c r="AS184" s="1" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="AT184" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -25717,6 +26827,12 @@
       <c r="AR185" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS185" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AT185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -25853,6 +26969,12 @@
       <c r="AR186" s="3" t="n">
         <v>-0.002753015207131644</v>
       </c>
+      <c r="AS186" s="1" t="n">
+        <v>0.007586</v>
+      </c>
+      <c r="AT186" s="3" t="n">
+        <v>-0.00276061522282111</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -25989,6 +27111,12 @@
       <c r="AR187" s="2" t="n">
         <v>0.004078605858361104</v>
       </c>
+      <c r="AS187" s="1" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="AT187" s="2" t="n">
+        <v>0.004800590841949865</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -26125,6 +27253,12 @@
       <c r="AR188" s="2" t="n">
         <v>0.001630656339176594</v>
       </c>
+      <c r="AS188" s="1" t="n">
+        <v>0.04919</v>
+      </c>
+      <c r="AT188" s="2" t="n">
+        <v>0.001017501017500905</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -26261,6 +27395,12 @@
       <c r="AR189" s="2" t="n">
         <v>0.002742946708464083</v>
       </c>
+      <c r="AS189" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AT189" s="2" t="n">
+        <v>0.0003907776475185189</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -26397,6 +27537,12 @@
       <c r="AR190" s="2" t="n">
         <v>0.0001752848378615057</v>
       </c>
+      <c r="AS190" s="1" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="AT190" s="2" t="n">
+        <v>0.0003505082369435295</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -26533,6 +27679,12 @@
       <c r="AR191" s="3" t="n">
         <v>-0.001161632923995963</v>
       </c>
+      <c r="AS191" s="1" t="n">
+        <v>6.026</v>
+      </c>
+      <c r="AT191" s="2" t="n">
+        <v>0.001162983884366119</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -26669,6 +27821,12 @@
       <c r="AR192" s="2" t="n">
         <v>0.005455067470571383</v>
       </c>
+      <c r="AS192" s="1" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AT192" s="3" t="n">
+        <v>-0.003712164477441529</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -26805,6 +27963,12 @@
       <c r="AR193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS193" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="AT193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -26941,6 +28105,12 @@
       <c r="AR194" s="2" t="n">
         <v>0.001748251748251677</v>
       </c>
+      <c r="AS194" s="1" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="AT194" s="3" t="n">
+        <v>-0.001163467132053472</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -27077,6 +28247,12 @@
       <c r="AR195" s="2" t="n">
         <v>0.004645221228661128</v>
       </c>
+      <c r="AS195" s="1" t="n">
+        <v>0.0008659</v>
+      </c>
+      <c r="AT195" s="2" t="n">
+        <v>0.0009247485839786279</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -27213,6 +28389,12 @@
       <c r="AR196" s="2" t="n">
         <v>0.001966568338249802</v>
       </c>
+      <c r="AS196" s="1" t="n">
+        <v>0.001016</v>
+      </c>
+      <c r="AT196" s="3" t="n">
+        <v>-0.002944062806673174</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -27349,6 +28531,12 @@
       <c r="AR197" s="2" t="n">
         <v>0.001241464928615628</v>
       </c>
+      <c r="AS197" s="1" t="n">
+        <v>0.000161</v>
+      </c>
+      <c r="AT197" s="3" t="n">
+        <v>-0.001859888406695476</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -27485,6 +28673,12 @@
       <c r="AR198" s="2" t="n">
         <v>0.001842893342547802</v>
       </c>
+      <c r="AS198" s="1" t="n">
+        <v>4.351</v>
+      </c>
+      <c r="AT198" s="2" t="n">
+        <v>0.0004598758335248976</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -27621,6 +28815,12 @@
       <c r="AR199" s="2" t="n">
         <v>0.0006071645415907041</v>
       </c>
+      <c r="AS199" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="AT199" s="2" t="n">
+        <v>0.003033980582524274</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -27757,6 +28957,12 @@
       <c r="AR200" s="3" t="n">
         <v>-0.01344463971880495</v>
       </c>
+      <c r="AS200" s="1" t="n">
+        <v>0.022545</v>
+      </c>
+      <c r="AT200" s="2" t="n">
+        <v>0.004052730025830623</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -27893,6 +29099,12 @@
       <c r="AR201" s="2" t="n">
         <v>0.001681749018979754</v>
       </c>
+      <c r="AS201" s="1" t="n">
+        <v>0.12523</v>
+      </c>
+      <c r="AT201" s="2" t="n">
+        <v>0.001199232491205718</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -28029,6 +29241,12 @@
       <c r="AR202" s="2" t="n">
         <v>0.001426533523537869</v>
       </c>
+      <c r="AS202" s="1" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="AT202" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -28165,6 +29383,12 @@
       <c r="AR203" s="3" t="n">
         <v>-0.0009920634920634517</v>
       </c>
+      <c r="AS203" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AT203" s="2" t="n">
+        <v>0.002979145978152808</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -28301,6 +29525,12 @@
       <c r="AR204" s="3" t="n">
         <v>-0.000772797527047882</v>
       </c>
+      <c r="AS204" s="1" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="AT204" s="2" t="n">
+        <v>0.0003866976024748489</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -28437,6 +29667,12 @@
       <c r="AR205" s="3" t="n">
         <v>-0.004364805881001637</v>
       </c>
+      <c r="AS205" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AT205" s="3" t="n">
+        <v>-0.0009229349330872438</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -28573,6 +29809,12 @@
       <c r="AR206" s="2" t="n">
         <v>0.006063230835859733</v>
       </c>
+      <c r="AS206" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="AT206" s="2" t="n">
+        <v>0.005165733964700756</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -28709,6 +29951,12 @@
       <c r="AR207" s="3" t="n">
         <v>-0.0004784688995214784</v>
       </c>
+      <c r="AS207" s="1" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="AT207" s="2" t="n">
+        <v>0.0009573958831978094</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -28845,6 +30093,12 @@
       <c r="AR208" s="2" t="n">
         <v>0.002435723951285516</v>
       </c>
+      <c r="AS208" s="1" t="n">
+        <v>0.07396</v>
+      </c>
+      <c r="AT208" s="3" t="n">
+        <v>-0.001619870410367105</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -28981,6 +30235,12 @@
       <c r="AR209" s="2" t="n">
         <v>0.001899786274044093</v>
       </c>
+      <c r="AS209" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AT209" s="3" t="n">
+        <v>-0.003792367859682399</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -29117,6 +30377,12 @@
       <c r="AR210" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS210" s="1" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="AT210" s="2" t="n">
+        <v>0.001626898047722314</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -29253,6 +30519,12 @@
       <c r="AR211" s="3" t="n">
         <v>-0.0008445945945946187</v>
       </c>
+      <c r="AS211" s="1" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="AT211" s="3" t="n">
+        <v>-0.0008453085376162542</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -29389,6 +30661,12 @@
       <c r="AR212" s="3" t="n">
         <v>-0.001415094339622625</v>
       </c>
+      <c r="AS212" s="1" t="n">
+        <v>0.002122</v>
+      </c>
+      <c r="AT212" s="2" t="n">
+        <v>0.002361832782239126</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -29525,6 +30803,12 @@
       <c r="AR213" s="2" t="n">
         <v>0.002157497303128373</v>
       </c>
+      <c r="AS213" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="AT213" s="3" t="n">
+        <v>-0.003229278794402586</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -29661,6 +30945,12 @@
       <c r="AR214" s="2" t="n">
         <v>0.001571777855396343</v>
       </c>
+      <c r="AS214" s="1" t="n">
+        <v>0.005732</v>
+      </c>
+      <c r="AT214" s="3" t="n">
+        <v>-0.0005231037489101187</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -29797,6 +31087,12 @@
       <c r="AR215" s="2" t="n">
         <v>0.001276906238599063</v>
       </c>
+      <c r="AS215" s="1" t="n">
+        <v>0.05498</v>
+      </c>
+      <c r="AT215" s="2" t="n">
+        <v>0.001639642922208049</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -29933,6 +31229,12 @@
       <c r="AR216" s="3" t="n">
         <v>-0.003169572107765542</v>
       </c>
+      <c r="AS216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AT216" s="2" t="n">
+        <v>0.003179650238473859</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -30069,6 +31371,12 @@
       <c r="AR217" s="3" t="n">
         <v>-0.003236245954692649</v>
       </c>
+      <c r="AS217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="AT217" s="2" t="n">
+        <v>0.004329004329004303</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -30205,6 +31513,12 @@
       <c r="AR218" s="3" t="n">
         <v>-0.003015075376884448</v>
       </c>
+      <c r="AS218" s="1" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AT218" s="3" t="n">
+        <v>-0.00219614055299539</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -30341,6 +31655,12 @@
       <c r="AR219" s="3" t="n">
         <v>-0.001223615784643652</v>
       </c>
+      <c r="AS219" s="1" t="n">
+        <v>0.003283</v>
+      </c>
+      <c r="AT219" s="2" t="n">
+        <v>0.005513016845329184</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -30477,6 +31797,12 @@
       <c r="AR220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="AT220" s="3" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -30613,6 +31939,12 @@
       <c r="AR221" s="3" t="n">
         <v>-0.003622250970245648</v>
       </c>
+      <c r="AS221" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="AT221" s="3" t="n">
+        <v>-0.001038691249026365</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -30749,6 +32081,12 @@
       <c r="AR222" s="3" t="n">
         <v>-0.0002138579982892015</v>
       </c>
+      <c r="AS222" s="1" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="AT222" s="2" t="n">
+        <v>0.0008556149732619972</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -30885,6 +32223,12 @@
       <c r="AR223" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS223" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="AT223" s="2" t="n">
+        <v>0.000942507068803043</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -31021,6 +32365,12 @@
       <c r="AR224" s="2" t="n">
         <v>0.007279116465863432</v>
       </c>
+      <c r="AS224" s="1" t="n">
+        <v>4.022</v>
+      </c>
+      <c r="AT224" s="2" t="n">
+        <v>0.002242711188637015</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -31157,6 +32507,12 @@
       <c r="AR225" s="3" t="n">
         <v>-0.0009720272167620344</v>
       </c>
+      <c r="AS225" s="1" t="n">
+        <v>0.000926</v>
+      </c>
+      <c r="AT225" s="2" t="n">
+        <v>0.00108108108108099</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -31293,6 +32649,12 @@
       <c r="AR226" s="3" t="n">
         <v>-0.0002374169040833964</v>
       </c>
+      <c r="AS226" s="1" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="AT226" s="2" t="n">
+        <v>0.002137259558299563</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -31429,6 +32791,12 @@
       <c r="AR227" s="3" t="n">
         <v>-0.0009739469198929951</v>
       </c>
+      <c r="AS227" s="1" t="n">
+        <v>0.04098</v>
+      </c>
+      <c r="AT227" s="3" t="n">
+        <v>-0.001218620521569449</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -31565,6 +32933,12 @@
       <c r="AR228" s="2" t="n">
         <v>0.01021253105161475</v>
       </c>
+      <c r="AS228" s="1" t="n">
+        <v>0.03657</v>
+      </c>
+      <c r="AT228" s="3" t="n">
+        <v>-0.0008196721311476023</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -31701,6 +33075,12 @@
       <c r="AR229" s="3" t="n">
         <v>-0.002685593708037622</v>
       </c>
+      <c r="AS229" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AT229" s="2" t="n">
+        <v>0.0001923446816694773</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -31837,6 +33217,12 @@
       <c r="AR230" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS230" s="1" t="n">
+        <v>0.001708</v>
+      </c>
+      <c r="AT230" s="3" t="n">
+        <v>-0.006976744186046429</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -31973,6 +33359,12 @@
       <c r="AR231" s="2" t="n">
         <v>0.006748466257668792</v>
       </c>
+      <c r="AS231" s="1" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="AT231" s="2" t="n">
+        <v>0.006093845216331398</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -32109,6 +33501,12 @@
       <c r="AR232" s="2" t="n">
         <v>0.003205128205128234</v>
       </c>
+      <c r="AS232" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="AT232" s="2" t="n">
+        <v>0.00228206298493845</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -32245,6 +33643,12 @@
       <c r="AR233" s="3" t="n">
         <v>-0.0005120327700972062</v>
       </c>
+      <c r="AS233" s="1" t="n">
+        <v>0.0005845</v>
+      </c>
+      <c r="AT233" s="3" t="n">
+        <v>-0.001878415300546586</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -32381,6 +33785,12 @@
       <c r="AR234" s="2" t="n">
         <v>0.01089048490822896</v>
       </c>
+      <c r="AS234" s="1" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="AT234" s="2" t="n">
+        <v>0.007244021360575705</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -32517,6 +33927,12 @@
       <c r="AR235" s="3" t="n">
         <v>-0.009475218658892122</v>
       </c>
+      <c r="AS235" s="1" t="n">
+        <v>0.01319</v>
+      </c>
+      <c r="AT235" s="3" t="n">
+        <v>-0.02943340691685058</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -32653,6 +34069,12 @@
       <c r="AR236" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="AS236" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AT236" s="3" t="n">
+        <v>-0.004784688995215282</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -32789,6 +34211,12 @@
       <c r="AR237" s="2" t="n">
         <v>0.002403846153846265</v>
       </c>
+      <c r="AS237" s="1" t="n">
+        <v>0.00415</v>
+      </c>
+      <c r="AT237" s="3" t="n">
+        <v>-0.004796163069544377</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -32925,6 +34353,12 @@
       <c r="AR238" s="3" t="n">
         <v>-0.003968253968253945</v>
       </c>
+      <c r="AS238" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AT238" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -33061,6 +34495,12 @@
       <c r="AR239" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS239" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="AT239" s="2" t="n">
+        <v>0.001997336884154379</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -33197,6 +34637,12 @@
       <c r="AR240" s="2" t="n">
         <v>0.002547770700637005</v>
       </c>
+      <c r="AS240" s="1" t="n">
+        <v>0.0003936</v>
+      </c>
+      <c r="AT240" s="2" t="n">
+        <v>0.0002541296060991167</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -33333,6 +34779,12 @@
       <c r="AR241" s="2" t="n">
         <v>0.002572583608967212</v>
       </c>
+      <c r="AS241" s="1" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AT241" s="2" t="n">
+        <v>0.002565982404692206</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -33469,6 +34921,12 @@
       <c r="AR242" s="2" t="n">
         <v>0.002077112813189582</v>
       </c>
+      <c r="AS242" s="1" t="n">
+        <v>0.07706</v>
+      </c>
+      <c r="AT242" s="3" t="n">
+        <v>-0.001684155978753611</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -33605,6 +35063,12 @@
       <c r="AR243" s="3" t="n">
         <v>-0.003051881993896288</v>
       </c>
+      <c r="AS243" s="1" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="AT243" s="3" t="n">
+        <v>-0.006122448979591764</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -33741,6 +35205,12 @@
       <c r="AR244" s="3" t="n">
         <v>-0.002550724637681136</v>
       </c>
+      <c r="AS244" s="1" t="n">
+        <v>0.08702</v>
+      </c>
+      <c r="AT244" s="2" t="n">
+        <v>0.01150761362315477</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -33877,6 +35347,12 @@
       <c r="AR245" s="2" t="n">
         <v>0.000771875657848487</v>
       </c>
+      <c r="AS245" s="1" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="AT245" s="3" t="n">
+        <v>-0.003575936053849308</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -34013,6 +35489,12 @@
       <c r="AR246" s="3" t="n">
         <v>-0.001664816870144409</v>
       </c>
+      <c r="AS246" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="AT246" s="3" t="n">
+        <v>-0.005002779321845459</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -34149,6 +35631,12 @@
       <c r="AR247" s="3" t="n">
         <v>-0.0003015226895824311</v>
       </c>
+      <c r="AS247" s="1" t="n">
+        <v>0.006645</v>
+      </c>
+      <c r="AT247" s="2" t="n">
+        <v>0.00211129543055348</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -34285,6 +35773,12 @@
       <c r="AR248" s="2" t="n">
         <v>0.006986268369067576</v>
       </c>
+      <c r="AS248" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="AT248" s="2" t="n">
+        <v>0.0007177033492823919</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -34421,6 +35915,12 @@
       <c r="AR249" s="2" t="n">
         <v>0.007181328545780926</v>
       </c>
+      <c r="AS249" s="1" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="AT249" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -34557,6 +36057,12 @@
       <c r="AR250" s="3" t="n">
         <v>-0.003174603174603146</v>
       </c>
+      <c r="AS250" s="1" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="AT250" s="2" t="n">
+        <v>0.005790387955993017</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -34693,6 +36199,12 @@
       <c r="AR251" s="2" t="n">
         <v>0.001881467544684777</v>
       </c>
+      <c r="AS251" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="AT251" s="2" t="n">
+        <v>0.004694835680751145</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -34829,6 +36341,12 @@
       <c r="AR252" s="3" t="n">
         <v>-0.005287395531297932</v>
       </c>
+      <c r="AS252" s="1" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="AT252" s="3" t="n">
+        <v>-0.0003429355281207588</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -34965,6 +36483,12 @@
       <c r="AR253" s="2" t="n">
         <v>0.003562945368170876</v>
       </c>
+      <c r="AS253" s="1" t="n">
+        <v>0.01683</v>
+      </c>
+      <c r="AT253" s="3" t="n">
+        <v>-0.004142011834319359</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -35101,6 +36625,12 @@
       <c r="AR254" s="3" t="n">
         <v>-0.00077160493827152</v>
       </c>
+      <c r="AS254" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="AT254" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -35237,6 +36767,12 @@
       <c r="AR255" s="3" t="n">
         <v>-0.008329477093937974</v>
       </c>
+      <c r="AS255" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="AT255" s="2" t="n">
+        <v>0.0009332711152589447</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -35373,6 +36909,12 @@
       <c r="AR256" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS256" s="1" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="AT256" s="3" t="n">
+        <v>-0.0009425070688029776</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -35509,6 +37051,12 @@
       <c r="AR257" s="2" t="n">
         <v>0.003540519276160496</v>
       </c>
+      <c r="AS257" s="1" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="AT257" s="2" t="n">
+        <v>0.001960015680125361</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -35645,6 +37193,12 @@
       <c r="AR258" s="2" t="n">
         <v>0.002569677801937151</v>
       </c>
+      <c r="AS258" s="1" t="n">
+        <v>0.15211</v>
+      </c>
+      <c r="AT258" s="3" t="n">
+        <v>-0.000328601472134559</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -35781,6 +37335,12 @@
       <c r="AR259" s="2" t="n">
         <v>0.0009790483649892586</v>
       </c>
+      <c r="AS259" s="1" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="AT259" s="2" t="n">
+        <v>0.0001956181533646921</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -35917,6 +37477,12 @@
       <c r="AR260" s="3" t="n">
         <v>-0.01102855816113295</v>
       </c>
+      <c r="AS260" s="1" t="n">
+        <v>0.08533</v>
+      </c>
+      <c r="AT260" s="2" t="n">
+        <v>0.001643385373870187</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -36053,6 +37619,12 @@
       <c r="AR261" s="2" t="n">
         <v>0.01013513513513507</v>
       </c>
+      <c r="AS261" s="1" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="AT261" s="3" t="n">
+        <v>-0.007525083612040117</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -36189,6 +37761,12 @@
       <c r="AR262" s="3" t="n">
         <v>-0.003474635163307856</v>
       </c>
+      <c r="AS262" s="1" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="AT262" s="3" t="n">
+        <v>-0.0006973500697349302</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -36325,6 +37903,12 @@
       <c r="AR263" s="2" t="n">
         <v>0.002074688796680593</v>
       </c>
+      <c r="AS263" s="1" t="n">
+        <v>0.07743999999999999</v>
+      </c>
+      <c r="AT263" s="2" t="n">
+        <v>0.002070393374741116</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -36461,6 +38045,12 @@
       <c r="AR264" s="2" t="n">
         <v>0.005858380030565311</v>
       </c>
+      <c r="AS264" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="AT264" s="3" t="n">
+        <v>-0.005824259306153308</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -36597,6 +38187,12 @@
       <c r="AR265" s="2" t="n">
         <v>0.0006497725795972273</v>
       </c>
+      <c r="AS265" s="1" t="n">
+        <v>0.01539</v>
+      </c>
+      <c r="AT265" s="3" t="n">
+        <v>-0.0006493506493507355</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -36733,6 +38329,12 @@
       <c r="AR266" s="2" t="n">
         <v>0.002846140967687871</v>
       </c>
+      <c r="AS266" s="1" t="n">
+        <v>0.005986</v>
+      </c>
+      <c r="AT266" s="3" t="n">
+        <v>-0.0006677796327211458</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -36869,6 +38471,12 @@
       <c r="AR267" s="2" t="n">
         <v>0.002684563758389339</v>
       </c>
+      <c r="AS267" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AT267" s="2" t="n">
+        <v>0.0005354752342703931</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -37005,6 +38613,12 @@
       <c r="AR268" s="3" t="n">
         <v>-0.0009819967266776512</v>
       </c>
+      <c r="AS268" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="AT268" s="2" t="n">
+        <v>0.0009829619921363777</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -37141,6 +38755,12 @@
       <c r="AR269" s="3" t="n">
         <v>-0.00021927901061308</v>
       </c>
+      <c r="AS269" s="1" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="AT269" s="2" t="n">
+        <v>0.002061674781769523</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -37277,6 +38897,12 @@
       <c r="AR270" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS270" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="AT270" s="3" t="n">
+        <v>-0.004305705059203449</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -37413,6 +39039,12 @@
       <c r="AR271" s="2" t="n">
         <v>0.0007739938080494503</v>
       </c>
+      <c r="AS271" s="1" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="AT271" s="3" t="n">
+        <v>-0.0007733952049496441</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -37549,6 +39181,12 @@
       <c r="AR272" s="2" t="n">
         <v>0.0005379236148466325</v>
       </c>
+      <c r="AS272" s="1" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="AT272" s="2" t="n">
+        <v>0.0005376344086020913</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -37685,6 +39323,12 @@
       <c r="AR273" s="2" t="n">
         <v>0.009223918575063567</v>
       </c>
+      <c r="AS273" s="1" t="n">
+        <v>0.03172</v>
+      </c>
+      <c r="AT273" s="3" t="n">
+        <v>-0.0003151591553735601</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -37821,6 +39465,12 @@
       <c r="AR274" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS274" s="1" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AT274" s="3" t="n">
+        <v>-0.003668763102725399</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -37957,6 +39607,12 @@
       <c r="AR275" s="2" t="n">
         <v>0.002309135517390583</v>
       </c>
+      <c r="AS275" s="1" t="n">
+        <v>0.06948</v>
+      </c>
+      <c r="AT275" s="2" t="n">
+        <v>0.0004319654427646112</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -38093,6 +39749,12 @@
       <c r="AR276" s="2" t="n">
         <v>0.001245174947079927</v>
       </c>
+      <c r="AS276" s="1" t="n">
+        <v>0.08039</v>
+      </c>
+      <c r="AT276" s="3" t="n">
+        <v>-0.0002487252829249129</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -38229,6 +39891,12 @@
       <c r="AR277" s="3" t="n">
         <v>-0.001806917914300369</v>
       </c>
+      <c r="AS277" s="1" t="n">
+        <v>0.003867</v>
+      </c>
+      <c r="AT277" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -38365,6 +40033,12 @@
       <c r="AR278" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS278" s="1" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="AT278" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -38501,6 +40175,12 @@
       <c r="AR279" s="2" t="n">
         <v>0.001811594202898634</v>
       </c>
+      <c r="AS279" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AT279" s="3" t="n">
+        <v>-0.0009041591320071964</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -38637,6 +40317,12 @@
       <c r="AR280" s="2" t="n">
         <v>0.0002495009980040684</v>
       </c>
+      <c r="AS280" s="1" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="AT280" s="2" t="n">
+        <v>0.0009977550511349057</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -38773,6 +40459,12 @@
       <c r="AR281" s="2" t="n">
         <v>0.0005942476824339731</v>
       </c>
+      <c r="AS281" s="1" t="n">
+        <v>0.08416999999999999</v>
+      </c>
+      <c r="AT281" s="3" t="n">
+        <v>-0.0002375579047393529</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -38909,6 +40601,12 @@
       <c r="AR282" s="2" t="n">
         <v>0.007380073800738091</v>
       </c>
+      <c r="AS282" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AT282" s="3" t="n">
+        <v>-0.003663003663003768</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -39045,6 +40743,12 @@
       <c r="AR283" s="2" t="n">
         <v>0.0007878151260502969</v>
       </c>
+      <c r="AS283" s="1" t="n">
+        <v>0.07648000000000001</v>
+      </c>
+      <c r="AT283" s="2" t="n">
+        <v>0.003411178168459856</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -39181,6 +40885,12 @@
       <c r="AR284" s="3" t="n">
         <v>-0.001239925604463762</v>
       </c>
+      <c r="AS284" s="1" t="n">
+        <v>0.001612</v>
+      </c>
+      <c r="AT284" s="2" t="n">
+        <v>0.000620732464307831</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -39317,6 +41027,12 @@
       <c r="AR285" s="3" t="n">
         <v>-0.0009861932938856298</v>
       </c>
+      <c r="AS285" s="1" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AT285" s="2" t="n">
+        <v>0.001974333662389</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -39453,6 +41169,12 @@
       <c r="AR286" s="2" t="n">
         <v>0.00431438754455063</v>
       </c>
+      <c r="AS286" s="1" t="n">
+        <v>0.10749</v>
+      </c>
+      <c r="AT286" s="2" t="n">
+        <v>0.00382891296227127</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -39589,6 +41311,12 @@
       <c r="AR287" s="2" t="n">
         <v>0.0005780346820809014</v>
       </c>
+      <c r="AS287" s="1" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="AT287" s="2" t="n">
+        <v>0.002888503755054964</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -39725,6 +41453,12 @@
       <c r="AR288" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS288" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AT288" s="3" t="n">
+        <v>-0.001302931596091265</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -39861,6 +41595,12 @@
       <c r="AR289" s="2" t="n">
         <v>0.01340996168582365</v>
       </c>
+      <c r="AS289" s="1" t="n">
+        <v>0.01584</v>
+      </c>
+      <c r="AT289" s="3" t="n">
+        <v>-0.001890359168241889</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -39997,6 +41737,12 @@
       <c r="AR290" s="3" t="n">
         <v>-0.0004418912947414449</v>
       </c>
+      <c r="AS290" s="1" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AT290" s="2" t="n">
+        <v>0.001326259946949652</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -40133,6 +41879,12 @@
       <c r="AR291" s="2" t="n">
         <v>0.0009011038522188689</v>
       </c>
+      <c r="AS291" s="1" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="AT291" s="2" t="n">
+        <v>0.0009002925950934311</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -40269,6 +42021,12 @@
       <c r="AR292" s="2" t="n">
         <v>0.00113830392714855</v>
       </c>
+      <c r="AS292" s="1" t="n">
+        <v>1.766</v>
+      </c>
+      <c r="AT292" s="2" t="n">
+        <v>0.003979533826037589</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -40405,6 +42163,12 @@
       <c r="AR293" s="3" t="n">
         <v>-0.00118273211117677</v>
       </c>
+      <c r="AS293" s="1" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="AT293" s="2" t="n">
+        <v>0.00513124136569969</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -40541,6 +42305,12 @@
       <c r="AR294" s="3" t="n">
         <v>-0.002211690363349151</v>
       </c>
+      <c r="AS294" s="1" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="AT294" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -40677,6 +42447,12 @@
       <c r="AR295" s="2" t="n">
         <v>0.002408477842003781</v>
       </c>
+      <c r="AS295" s="1" t="n">
+        <v>0.0004146</v>
+      </c>
+      <c r="AT295" s="3" t="n">
+        <v>-0.003844305622296936</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -40813,6 +42589,12 @@
       <c r="AR296" s="3" t="n">
         <v>-0.0003207698476343725</v>
       </c>
+      <c r="AS296" s="1" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="AT296" s="2" t="n">
+        <v>0.001283491095780496</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -40949,6 +42731,12 @@
       <c r="AR297" s="3" t="n">
         <v>-0.002059732234809534</v>
       </c>
+      <c r="AS297" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="AT297" s="2" t="n">
+        <v>0.002063983488132154</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -41085,6 +42873,12 @@
       <c r="AR298" s="3" t="n">
         <v>-0.002083333333333393</v>
       </c>
+      <c r="AS298" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="AT298" s="2" t="n">
+        <v>0.00104384133611694</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -41221,6 +43015,12 @@
       <c r="AR299" s="3" t="n">
         <v>-0.0001045587620242171</v>
       </c>
+      <c r="AS299" s="1" t="n">
+        <v>0.09556000000000001</v>
+      </c>
+      <c r="AT299" s="3" t="n">
+        <v>-0.000731987869915305</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -41357,6 +43157,12 @@
       <c r="AR300" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS300" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AT300" s="2" t="n">
+        <v>0.001622498647917727</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -41493,6 +43299,12 @@
       <c r="AR301" s="2" t="n">
         <v>0.0007390983000738797</v>
       </c>
+      <c r="AS301" s="1" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AT301" s="3" t="n">
+        <v>-0.0007385524372230127</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -41629,6 +43441,12 @@
       <c r="AR302" s="3" t="n">
         <v>-0.001570563159075625</v>
       </c>
+      <c r="AS302" s="1" t="n">
+        <v>0.004461</v>
+      </c>
+      <c r="AT302" s="2" t="n">
+        <v>0.002471910112359489</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -41765,6 +43583,12 @@
       <c r="AR303" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS303" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="AT303" s="3" t="n">
+        <v>-0.001090512540894176</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -41901,6 +43725,12 @@
       <c r="AR304" s="3" t="n">
         <v>-0.001270648030495601</v>
       </c>
+      <c r="AS304" s="1" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="AT304" s="3" t="n">
+        <v>-0.000212044105173947</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -42037,6 +43867,12 @@
       <c r="AR305" s="2" t="n">
         <v>0.0005571030640667652</v>
       </c>
+      <c r="AS305" s="1" t="n">
+        <v>0.05362</v>
+      </c>
+      <c r="AT305" s="3" t="n">
+        <v>-0.004825538233110549</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -42173,6 +44009,12 @@
       <c r="AR306" s="2" t="n">
         <v>0.001538198598530162</v>
       </c>
+      <c r="AS306" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="AT306" s="2" t="n">
+        <v>0.0003412969283276311</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -42309,6 +44151,12 @@
       <c r="AR307" s="3" t="n">
         <v>-0.0005714285714285085</v>
       </c>
+      <c r="AS307" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="AT307" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -42445,6 +44293,12 @@
       <c r="AR308" s="3" t="n">
         <v>-0.001206030150753859</v>
       </c>
+      <c r="AS308" s="1" t="n">
+        <v>0.04952</v>
+      </c>
+      <c r="AT308" s="3" t="n">
+        <v>-0.003421211511370428</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -42581,6 +44435,12 @@
       <c r="AR309" s="2" t="n">
         <v>0.002553812477198024</v>
       </c>
+      <c r="AS309" s="1" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="AT309" s="2" t="n">
+        <v>0.002911208151382907</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -42717,6 +44577,12 @@
       <c r="AR310" s="3" t="n">
         <v>-0.004065040650406515</v>
       </c>
+      <c r="AS310" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AT310" s="2" t="n">
+        <v>0.004081632653061235</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -42853,6 +44719,12 @@
       <c r="AR311" s="2" t="n">
         <v>0.0004181767493727662</v>
       </c>
+      <c r="AS311" s="1" t="n">
+        <v>0.07192</v>
+      </c>
+      <c r="AT311" s="2" t="n">
+        <v>0.002090009753378812</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -42989,6 +44861,12 @@
       <c r="AR312" s="3" t="n">
         <v>-0.005522421029379247</v>
       </c>
+      <c r="AS312" s="1" t="n">
+        <v>0.009002</v>
+      </c>
+      <c r="AT312" s="3" t="n">
+        <v>-0.0002221235006664</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -43125,6 +45003,12 @@
       <c r="AR313" s="2" t="n">
         <v>0.001312120715105822</v>
       </c>
+      <c r="AS313" s="1" t="n">
+        <v>0.012188</v>
+      </c>
+      <c r="AT313" s="3" t="n">
+        <v>-0.001801801801801899</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -43261,6 +45145,12 @@
       <c r="AR314" s="2" t="n">
         <v>0.01101591187270499</v>
       </c>
+      <c r="AS314" s="1" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="AT314" s="2" t="n">
+        <v>0.004439063761097618</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -43397,6 +45287,12 @@
       <c r="AR315" s="3" t="n">
         <v>-0.001406469760900083</v>
       </c>
+      <c r="AS315" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="AT315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -43533,6 +45429,12 @@
       <c r="AR316" s="3" t="n">
         <v>-0.002295332823259544</v>
       </c>
+      <c r="AS316" s="1" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AT316" s="2" t="n">
+        <v>0.003834355828220863</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -43669,6 +45571,12 @@
       <c r="AR317" s="2" t="n">
         <v>0.01785714285714284</v>
       </c>
+      <c r="AS317" s="1" t="n">
+        <v>1.15e-05</v>
+      </c>
+      <c r="AT317" s="2" t="n">
+        <v>0.008771929824561469</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -43805,6 +45713,12 @@
       <c r="AR318" s="2" t="n">
         <v>0.002055827989438041</v>
       </c>
+      <c r="AS318" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="AT318" s="2" t="n">
+        <v>0.0005834854787403548</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -43941,6 +45855,12 @@
       <c r="AR319" s="3" t="n">
         <v>-0.002868318122555384</v>
       </c>
+      <c r="AS319" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="AT319" s="2" t="n">
+        <v>0.001569037656903702</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -44077,6 +45997,12 @@
       <c r="AR320" s="3" t="n">
         <v>-0.0005850519233582756</v>
       </c>
+      <c r="AS320" s="1" t="n">
+        <v>0.006844</v>
+      </c>
+      <c r="AT320" s="2" t="n">
+        <v>0.001609834626079408</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -44213,6 +46139,12 @@
       <c r="AR321" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS321" s="1" t="n">
+        <v>4.532</v>
+      </c>
+      <c r="AT321" s="2" t="n">
+        <v>0.0006623978803268081</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -44349,6 +46281,12 @@
       <c r="AR322" s="2" t="n">
         <v>0.0005157297576069571</v>
       </c>
+      <c r="AS322" s="1" t="n">
+        <v>1.941</v>
+      </c>
+      <c r="AT322" s="2" t="n">
+        <v>0.0005154639175258309</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -44485,6 +46423,12 @@
       <c r="AR323" s="2" t="n">
         <v>0.0007008690776563869</v>
       </c>
+      <c r="AS323" s="1" t="n">
+        <v>0.007128</v>
+      </c>
+      <c r="AT323" s="3" t="n">
+        <v>-0.001540832049306708</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -44621,6 +46565,12 @@
       <c r="AR324" s="3" t="n">
         <v>-0.0005455537370430766</v>
       </c>
+      <c r="AS324" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="AT324" s="2" t="n">
+        <v>0.001637554585152961</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -44757,6 +46707,12 @@
       <c r="AR325" s="2" t="n">
         <v>0.00169944161204184</v>
       </c>
+      <c r="AS325" s="1" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="AT325" s="2" t="n">
+        <v>0.005332040717401792</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -44893,6 +46849,12 @@
       <c r="AR326" s="3" t="n">
         <v>-0.0008332176086654532</v>
       </c>
+      <c r="AS326" s="1" t="n">
+        <v>0.007204</v>
+      </c>
+      <c r="AT326" s="2" t="n">
+        <v>0.001250868658790872</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -45029,6 +46991,12 @@
       <c r="AR327" s="2" t="n">
         <v>0.006069802731411263</v>
       </c>
+      <c r="AS327" s="1" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="AT327" s="3" t="n">
+        <v>-0.01106083459024625</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -45165,6 +47133,12 @@
       <c r="AR328" s="2" t="n">
         <v>0.001911233807602489</v>
       </c>
+      <c r="AS328" s="1" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="AT328" s="2" t="n">
+        <v>0.001483679525222506</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -45301,6 +47275,12 @@
       <c r="AR329" s="3" t="n">
         <v>-0.0007429420505200291</v>
       </c>
+      <c r="AS329" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="AT329" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -45437,6 +47417,12 @@
       <c r="AR330" s="2" t="n">
         <v>0.0008818342151675737</v>
       </c>
+      <c r="AS330" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="AT330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -45573,6 +47559,12 @@
       <c r="AR331" s="2" t="n">
         <v>0.001330450690171334</v>
       </c>
+      <c r="AS331" s="1" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="AT331" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -45709,6 +47701,12 @@
       <c r="AR332" s="2" t="n">
         <v>0.005603801409143192</v>
       </c>
+      <c r="AS332" s="1" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AT332" s="3" t="n">
+        <v>-0.0002281170566382536</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -45845,6 +47843,12 @@
       <c r="AR333" s="3" t="n">
         <v>-0.0004252906152537886</v>
       </c>
+      <c r="AS333" s="1" t="n">
+        <v>0.07042</v>
+      </c>
+      <c r="AT333" s="3" t="n">
+        <v>-0.00127641469295145</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -45981,6 +47985,12 @@
       <c r="AR334" s="3" t="n">
         <v>-0.0004671338004672305</v>
       </c>
+      <c r="AS334" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AT334" s="2" t="n">
+        <v>0.003471758579249517</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -46117,6 +48127,12 @@
       <c r="AR335" s="2" t="n">
         <v>0.0006402048655569077</v>
       </c>
+      <c r="AS335" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="AT335" s="2" t="n">
+        <v>0.0006397952655151423</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -46253,6 +48269,12 @@
       <c r="AR336" s="2" t="n">
         <v>0.001148105625717599</v>
       </c>
+      <c r="AS336" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="AT336" s="2" t="n">
+        <v>0.002866972477064223</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -46389,6 +48411,12 @@
       <c r="AR337" s="3" t="n">
         <v>-0.0007594936708861329</v>
       </c>
+      <c r="AS337" s="1" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="AT337" s="2" t="n">
+        <v>0.0007600709399544528</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -46525,6 +48553,12 @@
       <c r="AR338" s="2" t="n">
         <v>0.001696832579185582</v>
       </c>
+      <c r="AS338" s="1" t="n">
+        <v>0.005315</v>
+      </c>
+      <c r="AT338" s="2" t="n">
+        <v>0.0003764351590439047</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -46661,6 +48695,12 @@
       <c r="AR339" s="3" t="n">
         <v>-0.00058309037900879</v>
       </c>
+      <c r="AS339" s="1" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="AT339" s="3" t="n">
+        <v>-0.0007779074290159154</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -46797,6 +48837,12 @@
       <c r="AR340" s="2" t="n">
         <v>0.0006660893891959567</v>
       </c>
+      <c r="AS340" s="1" t="n">
+        <v>0.15013</v>
+      </c>
+      <c r="AT340" s="3" t="n">
+        <v>-0.0006656460094521</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -46933,6 +48979,12 @@
       <c r="AR341" s="2" t="n">
         <v>0.0003920031360251031</v>
       </c>
+      <c r="AS341" s="1" t="n">
+        <v>7.656</v>
+      </c>
+      <c r="AT341" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -47069,6 +49121,12 @@
       <c r="AR342" s="3" t="n">
         <v>-0.0009137983551628601</v>
       </c>
+      <c r="AS342" s="1" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AT342" s="3" t="n">
+        <v>-0.0003048780487804542</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -47205,6 +49263,12 @@
       <c r="AR343" s="2" t="n">
         <v>0.0009990009990009582</v>
       </c>
+      <c r="AS343" s="1" t="n">
+        <v>0.02004</v>
+      </c>
+      <c r="AT343" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -47341,6 +49405,12 @@
       <c r="AR344" s="3" t="n">
         <v>-0.001375515818431964</v>
       </c>
+      <c r="AS344" s="1" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="AT344" s="3" t="n">
+        <v>-0.001377410468319612</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -47477,6 +49547,12 @@
       <c r="AR345" s="2" t="n">
         <v>0.005577689243027983</v>
       </c>
+      <c r="AS345" s="1" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="AT345" s="3" t="n">
+        <v>-0.004754358161648182</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -47613,6 +49689,12 @@
       <c r="AR346" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS346" s="1" t="n">
+        <v>0.005161</v>
+      </c>
+      <c r="AT346" s="3" t="n">
+        <v>-0.001161215405457699</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -47749,6 +49831,12 @@
       <c r="AR347" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS347" s="1" t="n">
+        <v>0.05733</v>
+      </c>
+      <c r="AT347" s="2" t="n">
+        <v>0.008265916285613756</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -47885,6 +49973,12 @@
       <c r="AR348" s="2" t="n">
         <v>0.003921568627450984</v>
       </c>
+      <c r="AS348" s="1" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="AT348" s="2" t="n">
+        <v>0.002343749999999959</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -48021,6 +50115,12 @@
       <c r="AR349" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS349" s="1" t="n">
+        <v>5193.1</v>
+      </c>
+      <c r="AT349" s="3" t="n">
+        <v>-1.925595008847229e-05</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -48157,6 +50257,12 @@
       <c r="AR350" s="2" t="n">
         <v>0.001080302484695671</v>
       </c>
+      <c r="AS350" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="AT350" s="2" t="n">
+        <v>0.003597122302158377</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -48293,6 +50399,12 @@
       <c r="AR351" s="3" t="n">
         <v>-0.004373177842565546</v>
       </c>
+      <c r="AS351" s="1" t="n">
+        <v>0.001367</v>
+      </c>
+      <c r="AT351" s="2" t="n">
+        <v>0.0007320644216690453</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -48429,6 +50541,12 @@
       <c r="AR352" s="2" t="n">
         <v>0.00627352572145542</v>
       </c>
+      <c r="AS352" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="AT352" s="3" t="n">
+        <v>-0.00436408977556092</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -48565,6 +50683,12 @@
       <c r="AR353" s="3" t="n">
         <v>-0.0009563277016257934</v>
       </c>
+      <c r="AS353" s="1" t="n">
+        <v>6.276</v>
+      </c>
+      <c r="AT353" s="2" t="n">
+        <v>0.001276324186343332</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -48701,6 +50825,12 @@
       <c r="AR354" s="2" t="n">
         <v>0.002769124264451447</v>
       </c>
+      <c r="AS354" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AT354" s="3" t="n">
+        <v>-0.0024162927166035</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -48837,6 +50967,12 @@
       <c r="AR355" s="2" t="n">
         <v>0.0009567089213106522</v>
       </c>
+      <c r="AS355" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="AT355" s="2" t="n">
+        <v>0.004778972520907976</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -48973,6 +51109,12 @@
       <c r="AR356" s="2" t="n">
         <v>0.000805946091161394</v>
       </c>
+      <c r="AS356" s="1" t="n">
+        <v>0.11153</v>
+      </c>
+      <c r="AT356" s="3" t="n">
+        <v>-0.002057981388689997</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -49109,6 +51251,12 @@
       <c r="AR357" s="3" t="n">
         <v>-0.005313092979127181</v>
       </c>
+      <c r="AS357" s="1" t="n">
+        <v>0.005189</v>
+      </c>
+      <c r="AT357" s="3" t="n">
+        <v>-0.01011064479206412</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -49245,6 +51393,12 @@
       <c r="AR358" s="3" t="n">
         <v>-0.003234501347708838</v>
       </c>
+      <c r="AS358" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="AT358" s="3" t="n">
+        <v>-0.01135749053542465</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -49381,6 +51535,12 @@
       <c r="AR359" s="2" t="n">
         <v>0.003590664272890422</v>
       </c>
+      <c r="AS359" s="1" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="AT359" s="2" t="n">
+        <v>0.01610017889087662</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -49517,6 +51677,12 @@
       <c r="AR360" s="3" t="n">
         <v>-0.003202087286527589</v>
       </c>
+      <c r="AS360" s="1" t="n">
+        <v>0.08387</v>
+      </c>
+      <c r="AT360" s="3" t="n">
+        <v>-0.002141582391433666</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -49653,6 +51819,12 @@
       <c r="AR361" s="2" t="n">
         <v>0.002628120893561111</v>
       </c>
+      <c r="AS361" s="1" t="n">
+        <v>0.00773</v>
+      </c>
+      <c r="AT361" s="2" t="n">
+        <v>0.01310615989515076</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -49789,6 +51961,12 @@
       <c r="AR362" s="2" t="n">
         <v>0.009042429863204171</v>
       </c>
+      <c r="AS362" s="1" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="AT362" s="3" t="n">
+        <v>-0.005744485294117653</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -49925,6 +52103,12 @@
       <c r="AR363" s="3" t="n">
         <v>-0.00270782561603039</v>
       </c>
+      <c r="AS363" s="1" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="AT363" s="2" t="n">
+        <v>0.0005430355688298192</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -50061,6 +52245,12 @@
       <c r="AR364" s="2" t="n">
         <v>0.006311992786294015</v>
       </c>
+      <c r="AS364" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="AT364" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -50197,6 +52387,12 @@
       <c r="AR365" s="2" t="n">
         <v>0.001268805510241084</v>
       </c>
+      <c r="AS365" s="1" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="AT365" s="2" t="n">
+        <v>0.001086169442433101</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -50333,6 +52529,12 @@
       <c r="AR366" s="3" t="n">
         <v>-0.009700176366842945</v>
       </c>
+      <c r="AS366" s="1" t="n">
+        <v>0.02266</v>
+      </c>
+      <c r="AT366" s="2" t="n">
+        <v>0.008904719501335654</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -50469,6 +52671,12 @@
       <c r="AR367" s="3" t="n">
         <v>-0.0007496251874062338</v>
       </c>
+      <c r="AS367" s="1" t="n">
+        <v>0.001318</v>
+      </c>
+      <c r="AT367" s="3" t="n">
+        <v>-0.01125281320330086</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -50605,6 +52813,12 @@
       <c r="AR368" s="3" t="n">
         <v>-0.004142216085605918</v>
       </c>
+      <c r="AS368" s="1" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AT368" s="3" t="n">
+        <v>-0.001733102253032931</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -50741,6 +52955,12 @@
       <c r="AR369" s="3" t="n">
         <v>-0.007434944237918281</v>
       </c>
+      <c r="AS369" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="AT369" s="3" t="n">
+        <v>-0.01551631888710533</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -50877,6 +53097,12 @@
       <c r="AR370" s="3" t="n">
         <v>-0.00585987261146503</v>
       </c>
+      <c r="AS370" s="1" t="n">
+        <v>0.19142</v>
+      </c>
+      <c r="AT370" s="3" t="n">
+        <v>-0.01886212198872367</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -51013,6 +53239,12 @@
       <c r="AR371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS371" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AT371" s="2" t="n">
+        <v>0.01315789473684212</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -51149,6 +53381,12 @@
       <c r="AR372" s="3" t="n">
         <v>-0.002854424357754469</v>
       </c>
+      <c r="AS372" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AT372" s="2" t="n">
+        <v>0.004770992366412218</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -51285,6 +53523,12 @@
       <c r="AR373" s="3" t="n">
         <v>-0.002745576571079921</v>
       </c>
+      <c r="AS373" s="1" t="n">
+        <v>0.06591</v>
+      </c>
+      <c r="AT373" s="2" t="n">
+        <v>0.008106454573264038</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -51421,6 +53665,12 @@
       <c r="AR374" s="3" t="n">
         <v>-0.0005236287472181782</v>
       </c>
+      <c r="AS374" s="1" t="n">
+        <v>0.007643</v>
+      </c>
+      <c r="AT374" s="2" t="n">
+        <v>0.001047806155861078</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -51557,6 +53807,12 @@
       <c r="AR375" s="2" t="n">
         <v>0.002487562189054797</v>
       </c>
+      <c r="AS375" s="1" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="AT375" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -51693,6 +53949,12 @@
       <c r="AR376" s="2" t="n">
         <v>0.002332361516035042</v>
       </c>
+      <c r="AS376" s="1" t="n">
+        <v>0.003431</v>
+      </c>
+      <c r="AT376" s="3" t="n">
+        <v>-0.002036067481093677</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -51829,6 +54091,12 @@
       <c r="AR377" s="2" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="AS377" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AT377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -51965,6 +54233,12 @@
       <c r="AR378" s="3" t="n">
         <v>-0.003568242640499564</v>
       </c>
+      <c r="AS378" s="1" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="AT378" s="2" t="n">
+        <v>0.0008952551477172182</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -52101,6 +54375,12 @@
       <c r="AR379" s="2" t="n">
         <v>0.002784222737819073</v>
       </c>
+      <c r="AS379" s="1" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="AT379" s="2" t="n">
+        <v>0.002313743637204903</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -52237,6 +54517,12 @@
       <c r="AR380" s="2" t="n">
         <v>0.001594896331738372</v>
       </c>
+      <c r="AS380" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="AT380" s="2" t="n">
+        <v>0.0005307855626326748</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -52373,6 +54659,12 @@
       <c r="AR381" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS381" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="AT381" s="2" t="n">
+        <v>0.00166112956810636</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -52509,6 +54801,12 @@
       <c r="AR382" s="3" t="n">
         <v>-0.004774897680763907</v>
       </c>
+      <c r="AS382" s="1" t="n">
+        <v>0.02915</v>
+      </c>
+      <c r="AT382" s="3" t="n">
+        <v>-0.001028101439342092</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -52645,6 +54943,12 @@
       <c r="AR383" s="3" t="n">
         <v>-0.001823154056517754</v>
       </c>
+      <c r="AS383" s="1" t="n">
+        <v>0.006573</v>
+      </c>
+      <c r="AT383" s="2" t="n">
+        <v>0.0004566210045661386</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -52781,6 +55085,12 @@
       <c r="AR384" s="2" t="n">
         <v>0.002378686964795336</v>
       </c>
+      <c r="AS384" s="1" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="AT384" s="2" t="n">
+        <v>0.003322259136212654</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -52917,6 +55227,12 @@
       <c r="AR385" s="3" t="n">
         <v>-0.002366863905325444</v>
       </c>
+      <c r="AS385" s="1" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AT385" s="2" t="n">
+        <v>0.00276789244760775</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -53053,6 +55369,12 @@
       <c r="AR386" s="2" t="n">
         <v>0.000501253132832025</v>
       </c>
+      <c r="AS386" s="1" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="AT386" s="3" t="n">
+        <v>-0.0005010020040079608</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -53189,6 +55511,12 @@
       <c r="AR387" s="3" t="n">
         <v>-0.001651722510618231</v>
       </c>
+      <c r="AS387" s="1" t="n">
+        <v>0.08469</v>
+      </c>
+      <c r="AT387" s="2" t="n">
+        <v>0.0008272276057669655</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -53325,6 +55653,12 @@
       <c r="AR388" s="3" t="n">
         <v>-0.004276827371695241</v>
       </c>
+      <c r="AS388" s="1" t="n">
+        <v>0.005141</v>
+      </c>
+      <c r="AT388" s="2" t="n">
+        <v>0.003709488481062069</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -53461,6 +55795,12 @@
       <c r="AR389" s="3" t="n">
         <v>-0.005622837370242285</v>
       </c>
+      <c r="AS389" s="1" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="AT389" s="3" t="n">
+        <v>-0.001739886907350951</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -53597,6 +55937,12 @@
       <c r="AR390" s="2" t="n">
         <v>0.000391619345995649</v>
       </c>
+      <c r="AS390" s="1" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="AT390" s="2" t="n">
+        <v>0.007046388725777914</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -53733,6 +56079,12 @@
       <c r="AR391" s="2" t="n">
         <v>0.001316872427983571</v>
       </c>
+      <c r="AS391" s="1" t="n">
+        <v>0.0006092</v>
+      </c>
+      <c r="AT391" s="2" t="n">
+        <v>0.001479533125102692</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -53869,6 +56221,12 @@
       <c r="AR392" s="2" t="n">
         <v>0.001023716089404497</v>
       </c>
+      <c r="AS392" s="1" t="n">
+        <v>0.05877</v>
+      </c>
+      <c r="AT392" s="2" t="n">
+        <v>0.001704448610874431</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -54005,6 +56363,12 @@
       <c r="AR393" s="3" t="n">
         <v>-0.001476559616094337</v>
       </c>
+      <c r="AS393" s="1" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AT393" s="2" t="n">
+        <v>0.001478743068391704</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -54141,6 +56505,12 @@
       <c r="AR394" s="3" t="n">
         <v>-0.00117078881896668</v>
       </c>
+      <c r="AS394" s="1" t="n">
+        <v>0.006798</v>
+      </c>
+      <c r="AT394" s="3" t="n">
+        <v>-0.003956043956043973</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -54277,6 +56647,12 @@
       <c r="AR395" s="2" t="n">
         <v>0.001739130434782538</v>
       </c>
+      <c r="AS395" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="AT395" s="3" t="n">
+        <v>-0.002604166666666621</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -54413,6 +56789,12 @@
       <c r="AR396" s="2" t="n">
         <v>0.0009668063164680067</v>
       </c>
+      <c r="AS396" s="1" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="AT396" s="3" t="n">
+        <v>-0.001609787508048984</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -54549,6 +56931,12 @@
       <c r="AR397" s="2" t="n">
         <v>0.001320132013201358</v>
       </c>
+      <c r="AS397" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="AT397" s="2" t="n">
+        <v>0.001318391562294039</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -54685,6 +57073,12 @@
       <c r="AR398" s="3" t="n">
         <v>-0.0009107468123861458</v>
       </c>
+      <c r="AS398" s="1" t="n">
+        <v>0.003286</v>
+      </c>
+      <c r="AT398" s="3" t="n">
+        <v>-0.001519295047098216</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -54821,6 +57215,12 @@
       <c r="AR399" s="3" t="n">
         <v>-0.008125677139761691</v>
       </c>
+      <c r="AS399" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="AT399" s="2" t="n">
+        <v>0.008192244675041007</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -54957,6 +57357,12 @@
       <c r="AR400" s="3" t="n">
         <v>-0.004595060310166558</v>
       </c>
+      <c r="AS400" s="1" t="n">
+        <v>0.00692</v>
+      </c>
+      <c r="AT400" s="3" t="n">
+        <v>-0.001731102135025946</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -55093,6 +57499,12 @@
       <c r="AR401" s="2" t="n">
         <v>0.006677084813183715</v>
       </c>
+      <c r="AS401" s="1" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="AT401" s="3" t="n">
+        <v>-0.00508044030482648</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -55229,6 +57641,12 @@
       <c r="AR402" s="3" t="n">
         <v>-0.004116766467065873</v>
       </c>
+      <c r="AS402" s="1" t="n">
+        <v>0.007984</v>
+      </c>
+      <c r="AT402" s="2" t="n">
+        <v>0.0001252661906550501</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -55365,6 +57783,12 @@
       <c r="AR403" s="2" t="n">
         <v>0.001442109600329638</v>
       </c>
+      <c r="AS403" s="1" t="n">
+        <v>0.04836</v>
+      </c>
+      <c r="AT403" s="3" t="n">
+        <v>-0.005142974696564498</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -55501,6 +57925,12 @@
       <c r="AR404" s="3" t="n">
         <v>-0.002811997857525467</v>
       </c>
+      <c r="AS404" s="1" t="n">
+        <v>0.14951</v>
+      </c>
+      <c r="AT404" s="2" t="n">
+        <v>0.003827044447428595</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -55637,6 +58067,12 @@
       <c r="AR405" s="3" t="n">
         <v>-0.001657981999052596</v>
       </c>
+      <c r="AS405" s="1" t="n">
+        <v>0.04225</v>
+      </c>
+      <c r="AT405" s="2" t="n">
+        <v>0.002372479240806711</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -55773,6 +58209,12 @@
       <c r="AR406" s="3" t="n">
         <v>-0.0004163197335553247</v>
       </c>
+      <c r="AS406" s="1" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="AT406" s="3" t="n">
+        <v>-0.001457725947521937</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -55909,6 +58351,12 @@
       <c r="AR407" s="2" t="n">
         <v>0.0006058158319869812</v>
       </c>
+      <c r="AS407" s="1" t="n">
+        <v>0.0004959</v>
+      </c>
+      <c r="AT407" s="2" t="n">
+        <v>0.000807265388496488</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -56045,6 +58493,12 @@
       <c r="AR408" s="3" t="n">
         <v>-0.0008149959250203417</v>
       </c>
+      <c r="AS408" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="AT408" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -56181,6 +58635,12 @@
       <c r="AR409" s="2" t="n">
         <v>0.001900538485904482</v>
       </c>
+      <c r="AS409" s="1" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AT409" s="3" t="n">
+        <v>-0.002213088839709244</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -56317,6 +58777,12 @@
       <c r="AR410" s="2" t="n">
         <v>0.006152389966871824</v>
       </c>
+      <c r="AS410" s="1" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AT410" s="2" t="n">
+        <v>0.002351834430855972</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -56453,6 +58919,12 @@
       <c r="AR411" s="3" t="n">
         <v>-0.001340033500837583</v>
       </c>
+      <c r="AS411" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="AT411" s="2" t="n">
+        <v>0.003354579000335438</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -56589,6 +59061,12 @@
       <c r="AR412" s="2" t="n">
         <v>0.0008726003490400661</v>
       </c>
+      <c r="AS412" s="1" t="n">
+        <v>0.004587</v>
+      </c>
+      <c r="AT412" s="3" t="n">
+        <v>-0.0002179598953792791</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -56725,6 +59203,12 @@
       <c r="AR413" s="2" t="n">
         <v>0.002752654345261417</v>
       </c>
+      <c r="AS413" s="1" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AT413" s="2" t="n">
+        <v>0.001960784313725492</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -56861,6 +59345,12 @@
       <c r="AR414" s="2" t="n">
         <v>0.002323780015491955</v>
       </c>
+      <c r="AS414" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AT414" s="2" t="n">
+        <v>0.001545595054095828</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -56997,6 +59487,12 @@
       <c r="AR415" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS415" s="1" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="AT415" s="2" t="n">
+        <v>0.001101321585902962</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -57133,6 +59629,12 @@
       <c r="AR416" s="3" t="n">
         <v>-0.005484460694698342</v>
       </c>
+      <c r="AS416" s="1" t="n">
+        <v>0.03258</v>
+      </c>
+      <c r="AT416" s="3" t="n">
+        <v>-0.001838235294117785</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -57269,6 +59771,12 @@
       <c r="AR417" s="3" t="n">
         <v>-0.001252505010019902</v>
       </c>
+      <c r="AS417" s="1" t="n">
+        <v>0.03989</v>
+      </c>
+      <c r="AT417" s="2" t="n">
+        <v>0.0005016302984700072</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -57405,6 +59913,12 @@
       <c r="AR418" s="2" t="n">
         <v>0.0001310100877768898</v>
       </c>
+      <c r="AS418" s="1" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="AT418" s="2" t="n">
+        <v>0.001702908042965565</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -57541,6 +60055,12 @@
       <c r="AR419" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS419" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="AT419" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -57677,6 +60197,12 @@
       <c r="AR420" s="2" t="n">
         <v>0.003405221339387158</v>
       </c>
+      <c r="AS420" s="1" t="n">
+        <v>0.0886</v>
+      </c>
+      <c r="AT420" s="2" t="n">
+        <v>0.002262443438913935</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -57813,6 +60339,12 @@
       <c r="AR421" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS421" s="1" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="AT421" s="3" t="n">
+        <v>-0.001257334450963934</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -57949,6 +60481,12 @@
       <c r="AR422" s="3" t="n">
         <v>-0.02499999999999997</v>
       </c>
+      <c r="AS422" s="1" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="AT422" s="2" t="n">
+        <v>0.0183150183150182</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -58085,6 +60623,12 @@
       <c r="AR423" s="2" t="n">
         <v>0.002616088947024092</v>
       </c>
+      <c r="AS423" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="AT423" s="3" t="n">
+        <v>-0.00391389432485316</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -58221,6 +60765,12 @@
       <c r="AR424" s="3" t="n">
         <v>-0.004329004329004434</v>
       </c>
+      <c r="AS424" s="1" t="n">
+        <v>0.0002072</v>
+      </c>
+      <c r="AT424" s="2" t="n">
+        <v>0.0009661835748792506</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -58357,6 +60907,12 @@
       <c r="AR425" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS425" s="1" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="AT425" s="2" t="n">
+        <v>0.0008012820512821409</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -58493,6 +61049,12 @@
       <c r="AR426" s="3" t="n">
         <v>-0.002120141342756264</v>
       </c>
+      <c r="AS426" s="1" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="AT426" s="2" t="n">
+        <v>0.002832861189801702</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -58629,6 +61191,12 @@
       <c r="AR427" s="3" t="n">
         <v>-0.0005130836326320981</v>
       </c>
+      <c r="AS427" s="1" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="AT427" s="2" t="n">
+        <v>0.0005133470225872481</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -58765,6 +61333,12 @@
       <c r="AR428" s="2" t="n">
         <v>0.0004509243950095952</v>
       </c>
+      <c r="AS428" s="1" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="AT428" s="2" t="n">
+        <v>0.003455528846153966</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -58901,6 +61475,12 @@
       <c r="AR429" s="2" t="n">
         <v>0.003018867924528179</v>
       </c>
+      <c r="AS429" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AT429" s="2" t="n">
+        <v>0.0007524454477051675</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -59037,6 +61617,12 @@
       <c r="AR430" s="3" t="n">
         <v>-0.0009995456610630495</v>
       </c>
+      <c r="AS430" s="1" t="n">
+        <v>0.010983</v>
+      </c>
+      <c r="AT430" s="3" t="n">
+        <v>-0.001000545752228542</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -59173,6 +61759,12 @@
       <c r="AR431" s="3" t="n">
         <v>-0.002247527719508579</v>
       </c>
+      <c r="AS431" s="1" t="n">
+        <v>0.006675</v>
+      </c>
+      <c r="AT431" s="2" t="n">
+        <v>0.002402763177654361</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -59309,6 +61901,12 @@
       <c r="AR432" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS432" s="1" t="n">
+        <v>0.001777</v>
+      </c>
+      <c r="AT432" s="2" t="n">
+        <v>0.002256063169768686</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -59445,6 +62043,12 @@
       <c r="AR433" s="2" t="n">
         <v>0.004325883201153517</v>
       </c>
+      <c r="AS433" s="1" t="n">
+        <v>0.001391</v>
+      </c>
+      <c r="AT433" s="3" t="n">
+        <v>-0.001435750179468652</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -59581,6 +62185,12 @@
       <c r="AR434" s="2" t="n">
         <v>0.004901960784313712</v>
       </c>
+      <c r="AS434" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="AT434" s="3" t="n">
+        <v>-0.00243902439024383</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -59717,6 +62327,12 @@
       <c r="AR435" s="3" t="n">
         <v>-0.001728880157170907</v>
       </c>
+      <c r="AS435" s="1" t="n">
+        <v>0.12703</v>
+      </c>
+      <c r="AT435" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -59853,6 +62469,12 @@
       <c r="AR436" s="2" t="n">
         <v>0.002439337527282009</v>
       </c>
+      <c r="AS436" s="1" t="n">
+        <v>0.07809000000000001</v>
+      </c>
+      <c r="AT436" s="2" t="n">
+        <v>0.0001280737704919314</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -59989,6 +62611,12 @@
       <c r="AR437" s="2" t="n">
         <v>0.0009436929852153726</v>
       </c>
+      <c r="AS437" s="1" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="AT437" s="2" t="n">
+        <v>0.003456945317410402</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -60125,6 +62753,12 @@
       <c r="AR438" s="3" t="n">
         <v>-0.007819905213270235</v>
       </c>
+      <c r="AS438" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AT438" s="2" t="n">
+        <v>0.001671841413900182</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -60261,6 +62895,12 @@
       <c r="AR439" s="3" t="n">
         <v>-0.001136686558681397</v>
       </c>
+      <c r="AS439" s="1" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="AT439" s="3" t="n">
+        <v>-0.00056899004267423</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -60397,6 +63037,12 @@
       <c r="AR440" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS440" s="1" t="n">
+        <v>0.001519</v>
+      </c>
+      <c r="AT440" s="2" t="n">
+        <v>0.001318391562294034</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -60533,6 +63179,12 @@
       <c r="AR441" s="2" t="n">
         <v>0.0009414225941421121</v>
       </c>
+      <c r="AS441" s="1" t="n">
+        <v>0.009561</v>
+      </c>
+      <c r="AT441" s="3" t="n">
+        <v>-0.0008360330233043502</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -60669,6 +63321,12 @@
       <c r="AR442" s="2" t="n">
         <v>0.01027077497665744</v>
       </c>
+      <c r="AS442" s="1" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="AT442" s="2" t="n">
+        <v>0.00277264325323465</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -60805,6 +63463,12 @@
       <c r="AR443" s="3" t="n">
         <v>-0.0004572473708275991</v>
       </c>
+      <c r="AS443" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="AT443" s="2" t="n">
+        <v>0.0004574565416285266</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -60941,6 +63605,12 @@
       <c r="AR444" s="3" t="n">
         <v>-0.0101509630400834</v>
       </c>
+      <c r="AS444" s="1" t="n">
+        <v>0.0003808</v>
+      </c>
+      <c r="AT444" s="2" t="n">
+        <v>0.001314751511964271</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -61077,6 +63747,12 @@
       <c r="AR445" s="2" t="n">
         <v>0.002235261246158054</v>
       </c>
+      <c r="AS445" s="1" t="n">
+        <v>0.03587</v>
+      </c>
+      <c r="AT445" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -61213,6 +63889,12 @@
       <c r="AR446" s="2" t="n">
         <v>0.0009141812364300849</v>
       </c>
+      <c r="AS446" s="1" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="AT446" s="2" t="n">
+        <v>0.008105948167599067</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -61349,6 +64031,12 @@
       <c r="AR447" s="3" t="n">
         <v>-0.00122624156958921</v>
       </c>
+      <c r="AS447" s="1" t="n">
+        <v>3.264</v>
+      </c>
+      <c r="AT447" s="2" t="n">
+        <v>0.001841620626150946</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -61485,6 +64173,12 @@
       <c r="AR448" s="3" t="n">
         <v>-0.0006237330422581046</v>
       </c>
+      <c r="AS448" s="1" t="n">
+        <v>0.06413000000000001</v>
+      </c>
+      <c r="AT448" s="2" t="n">
+        <v>0.0006241223279764745</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -61621,6 +64315,12 @@
       <c r="AR449" s="2" t="n">
         <v>0.00121629839854042</v>
       </c>
+      <c r="AS449" s="1" t="n">
+        <v>0.4942</v>
+      </c>
+      <c r="AT449" s="2" t="n">
+        <v>0.0006074104069649057</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -61757,6 +64457,12 @@
       <c r="AR450" s="2" t="n">
         <v>0.0005292405398255127</v>
       </c>
+      <c r="AS450" s="1" t="n">
+        <v>0.03786</v>
+      </c>
+      <c r="AT450" s="2" t="n">
+        <v>0.001322401481089513</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -61893,6 +64599,12 @@
       <c r="AR451" s="3" t="n">
         <v>-0.001811594202898477</v>
       </c>
+      <c r="AS451" s="1" t="n">
+        <v>0.00551</v>
+      </c>
+      <c r="AT451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -62029,6 +64741,12 @@
       <c r="AR452" s="2" t="n">
         <v>0.001527446300716061</v>
       </c>
+      <c r="AS452" s="1" t="n">
+        <v>0.10565</v>
+      </c>
+      <c r="AT452" s="2" t="n">
+        <v>0.007053665046230013</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -62165,6 +64883,12 @@
       <c r="AR453" s="3" t="n">
         <v>-0.0006188118811880936</v>
       </c>
+      <c r="AS453" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="AT453" s="3" t="n">
+        <v>-0.00495356037151704</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -62301,6 +65025,12 @@
       <c r="AR454" s="3" t="n">
         <v>-0.004468889652801616</v>
       </c>
+      <c r="AS454" s="1" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AT454" s="3" t="n">
+        <v>-0.007251381215469582</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -62437,6 +65167,12 @@
       <c r="AR455" s="3" t="n">
         <v>-0.001117318435754191</v>
       </c>
+      <c r="AS455" s="1" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AT455" s="2" t="n">
+        <v>0.002237136465324387</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -62573,6 +65309,12 @@
       <c r="AR456" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS456" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="AT456" s="3" t="n">
+        <v>-0.001353637901861253</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -62709,6 +65451,12 @@
       <c r="AR457" s="2" t="n">
         <v>0.002028397565922838</v>
       </c>
+      <c r="AS457" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="AT457" s="2" t="n">
+        <v>0.001012145748987813</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -62845,6 +65593,12 @@
       <c r="AR458" s="3" t="n">
         <v>-0.0004752851711026972</v>
       </c>
+      <c r="AS458" s="1" t="n">
+        <v>0.06318</v>
+      </c>
+      <c r="AT458" s="2" t="n">
+        <v>0.00142653352353791</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -62981,6 +65735,12 @@
       <c r="AR459" s="3" t="n">
         <v>-0.001395673412421557</v>
       </c>
+      <c r="AS459" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="AT459" s="2" t="n">
+        <v>0.001397624039133537</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -63117,6 +65877,12 @@
       <c r="AR460" s="2" t="n">
         <v>0.001498969458497265</v>
       </c>
+      <c r="AS460" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="AT460" s="2" t="n">
+        <v>0.0003118178983472442</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -63253,6 +66019,12 @@
       <c r="AR461" s="3" t="n">
         <v>-0.00479041916167666</v>
       </c>
+      <c r="AS461" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AT461" s="3" t="n">
+        <v>-0.001203369434416317</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -63389,6 +66161,12 @@
       <c r="AR462" s="3" t="n">
         <v>-0.001438159156279997</v>
       </c>
+      <c r="AS462" s="1" t="n">
+        <v>0.0002094</v>
+      </c>
+      <c r="AT462" s="2" t="n">
+        <v>0.005280844935189629</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -63525,6 +66303,12 @@
       <c r="AR463" s="2" t="n">
         <v>0.004065040650406479</v>
       </c>
+      <c r="AS463" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="AT463" s="3" t="n">
+        <v>-0.001012145748987883</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -63661,6 +66445,12 @@
       <c r="AR464" s="2" t="n">
         <v>0.004163512490537565</v>
       </c>
+      <c r="AS464" s="1" t="n">
+        <v>0.02643</v>
+      </c>
+      <c r="AT464" s="3" t="n">
+        <v>-0.003769317753486726</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -63797,6 +66587,12 @@
       <c r="AR465" s="3" t="n">
         <v>-0.006613756613756573</v>
       </c>
+      <c r="AS465" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="AT465" s="2" t="n">
+        <v>0.004660452729693667</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -63933,6 +66729,12 @@
       <c r="AR466" s="2" t="n">
         <v>0.0003649635036496202</v>
       </c>
+      <c r="AS466" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="AT466" s="3" t="n">
+        <v>-0.0009120758847136343</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -64069,6 +66871,12 @@
       <c r="AR467" s="3" t="n">
         <v>-0.0005798782255726061</v>
       </c>
+      <c r="AS467" s="1" t="n">
+        <v>0.03454</v>
+      </c>
+      <c r="AT467" s="2" t="n">
+        <v>0.002030751378009882</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -64205,6 +67013,12 @@
       <c r="AR468" s="2" t="n">
         <v>0.002209944751381299</v>
       </c>
+      <c r="AS468" s="1" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="AT468" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -64341,6 +67155,12 @@
       <c r="AR469" s="2" t="n">
         <v>0.001868410516481951</v>
       </c>
+      <c r="AS469" s="1" t="n">
+        <v>0.0007498</v>
+      </c>
+      <c r="AT469" s="3" t="n">
+        <v>-0.001198881044358556</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -64477,6 +67297,12 @@
       <c r="AR470" s="3" t="n">
         <v>-0.001135073779795688</v>
       </c>
+      <c r="AS470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AT470" s="2" t="n">
+        <v>0.001136363636363637</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -64613,6 +67439,12 @@
       <c r="AR471" s="2" t="n">
         <v>0.00605449041372344</v>
       </c>
+      <c r="AS471" s="1" t="n">
+        <v>0.009979999999999999</v>
+      </c>
+      <c r="AT471" s="2" t="n">
+        <v>0.001003009027081203</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -64749,6 +67581,12 @@
       <c r="AR472" s="3" t="n">
         <v>-0.004206983592763963</v>
       </c>
+      <c r="AS472" s="1" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="AT472" s="2" t="n">
+        <v>0.0002112378538234698</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -64885,6 +67723,12 @@
       <c r="AR473" s="2" t="n">
         <v>0.000728862973761055</v>
       </c>
+      <c r="AS473" s="1" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="AT473" s="2" t="n">
+        <v>0.003641660597232341</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -65021,6 +67865,12 @@
       <c r="AR474" s="3" t="n">
         <v>-0.0004549590536851498</v>
       </c>
+      <c r="AS474" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="AT474" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -65157,6 +68007,12 @@
       <c r="AR475" s="2" t="n">
         <v>0.001063955550301493</v>
       </c>
+      <c r="AS475" s="1" t="n">
+        <v>0.008463</v>
+      </c>
+      <c r="AT475" s="3" t="n">
+        <v>-0.0005904581955597303</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -65293,6 +68149,12 @@
       <c r="AR476" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS476" s="1" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="AT476" s="3" t="n">
+        <v>-0.003433055419323058</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -65429,6 +68291,12 @@
       <c r="AR477" s="2" t="n">
         <v>0.005878030859661978</v>
       </c>
+      <c r="AS477" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="AT477" s="2" t="n">
+        <v>0.0007304601899197717</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -65565,6 +68433,12 @@
       <c r="AR478" s="3" t="n">
         <v>-0.004975124378109457</v>
       </c>
+      <c r="AS478" s="1" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AT478" s="3" t="n">
+        <v>-0.005750000000000061</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -65701,6 +68575,12 @@
       <c r="AR479" s="3" t="n">
         <v>-0.0002388059701492854</v>
       </c>
+      <c r="AS479" s="1" t="n">
+        <v>0.008390999999999999</v>
+      </c>
+      <c r="AT479" s="2" t="n">
+        <v>0.00214976710856311</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -65837,6 +68717,12 @@
       <c r="AR480" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS480" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="AT480" s="2" t="n">
+        <v>0.008810572687224693</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -65973,6 +68859,12 @@
       <c r="AR481" s="3" t="n">
         <v>-0.002189875048306112</v>
       </c>
+      <c r="AS481" s="1" t="n">
+        <v>0.07732</v>
+      </c>
+      <c r="AT481" s="3" t="n">
+        <v>-0.00180738445649369</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -66109,6 +69001,12 @@
       <c r="AR482" s="2" t="n">
         <v>0.001589825119236957</v>
       </c>
+      <c r="AS482" s="1" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="AT482" s="2" t="n">
+        <v>0.001388888888888901</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -66245,6 +69143,12 @@
       <c r="AR483" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS483" s="1" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="AT483" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -66381,6 +69285,12 @@
       <c r="AR484" s="2" t="n">
         <v>0.0004404639553663522</v>
       </c>
+      <c r="AS484" s="1" t="n">
+        <v>0.06818</v>
+      </c>
+      <c r="AT484" s="2" t="n">
+        <v>0.000587026709715268</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -66517,6 +69427,12 @@
       <c r="AR485" s="3" t="n">
         <v>-0.004205400619743231</v>
       </c>
+      <c r="AS485" s="1" t="n">
+        <v>0.0004467</v>
+      </c>
+      <c r="AT485" s="3" t="n">
+        <v>-0.007112691709268659</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -66653,6 +69569,12 @@
       <c r="AR486" s="3" t="n">
         <v>-0.00808256652574001</v>
       </c>
+      <c r="AS486" s="1" t="n">
+        <v>0.07965</v>
+      </c>
+      <c r="AT486" s="3" t="n">
+        <v>-0.001504324934185723</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -66789,6 +69711,12 @@
       <c r="AR487" s="2" t="n">
         <v>0.003452243958573156</v>
       </c>
+      <c r="AS487" s="1" t="n">
+        <v>0.0001742</v>
+      </c>
+      <c r="AT487" s="3" t="n">
+        <v>-0.001146788990825716</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -66925,6 +69853,12 @@
       <c r="AR488" s="2" t="n">
         <v>0.002685765443151344</v>
       </c>
+      <c r="AS488" s="1" t="n">
+        <v>0.08962000000000001</v>
+      </c>
+      <c r="AT488" s="2" t="n">
+        <v>0.0002232142857143541</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -67061,6 +69995,12 @@
       <c r="AR489" s="3" t="n">
         <v>-0.001454394348639115</v>
       </c>
+      <c r="AS489" s="1" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="AT489" s="2" t="n">
+        <v>0.0006242197253433676</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -67197,6 +70137,12 @@
       <c r="AR490" s="2" t="n">
         <v>0.003215434083601341</v>
       </c>
+      <c r="AS490" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AT490" s="3" t="n">
+        <v>-0.001869658119658136</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -67333,6 +70279,12 @@
       <c r="AR491" s="3" t="n">
         <v>-0.001708984375000015</v>
       </c>
+      <c r="AS491" s="1" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="AT491" s="3" t="n">
+        <v>-0.00293470286133534</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -67469,6 +70421,12 @@
       <c r="AR492" s="2" t="n">
         <v>0.004732607666824337</v>
       </c>
+      <c r="AS492" s="1" t="n">
+        <v>0.06368</v>
+      </c>
+      <c r="AT492" s="3" t="n">
+        <v>-0.0001570105197047594</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -67605,6 +70563,12 @@
       <c r="AR493" s="2" t="n">
         <v>0.003795066413662249</v>
       </c>
+      <c r="AS493" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="AT493" s="3" t="n">
+        <v>-0.001890359168242053</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -67741,6 +70705,12 @@
       <c r="AR494" s="2" t="n">
         <v>0.002179440610243332</v>
       </c>
+      <c r="AS494" s="1" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="AT494" s="2" t="n">
+        <v>0.0007249003262052682</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -67877,6 +70847,12 @@
       <c r="AR495" s="3" t="n">
         <v>-0.001726031696218406</v>
       </c>
+      <c r="AS495" s="1" t="n">
+        <v>0.06364</v>
+      </c>
+      <c r="AT495" s="2" t="n">
+        <v>0.0003143665513990274</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -68013,6 +70989,12 @@
       <c r="AR496" s="3" t="n">
         <v>-0.002047781569965834</v>
       </c>
+      <c r="AS496" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AT496" s="3" t="n">
+        <v>-0.0003419972640218501</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -68149,6 +71131,12 @@
       <c r="AR497" s="3" t="n">
         <v>-0.0003769791404875879</v>
       </c>
+      <c r="AS497" s="1" t="n">
+        <v>0.07928</v>
+      </c>
+      <c r="AT497" s="3" t="n">
+        <v>-0.003394091766184695</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -68285,6 +71273,12 @@
       <c r="AR498" s="3" t="n">
         <v>-0.002918287937743274</v>
       </c>
+      <c r="AS498" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="AT498" s="2" t="n">
+        <v>0.002926829268292767</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -68421,6 +71415,12 @@
       <c r="AR499" s="2" t="n">
         <v>0.005026328386787981</v>
       </c>
+      <c r="AS499" s="1" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="AT499" s="3" t="n">
+        <v>-0.0002381519409382263</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -68557,6 +71557,12 @@
       <c r="AR500" s="2" t="n">
         <v>0.001731387583477631</v>
       </c>
+      <c r="AS500" s="1" t="n">
+        <v>0.04092</v>
+      </c>
+      <c r="AT500" s="2" t="n">
+        <v>0.01037037037037029</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -68693,6 +71699,12 @@
       <c r="AR501" s="3" t="n">
         <v>-0.002002002002002059</v>
       </c>
+      <c r="AS501" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="AT501" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -68829,6 +71841,12 @@
       <c r="AR502" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS502" s="1" t="n">
+        <v>0.003325</v>
+      </c>
+      <c r="AT502" s="2" t="n">
+        <v>0.0003008423586040009</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -68965,6 +71983,12 @@
       <c r="AR503" s="2" t="n">
         <v>0.001100110011001055</v>
       </c>
+      <c r="AS503" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="AT503" s="3" t="n">
+        <v>-0.002197802197802299</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -69101,6 +72125,12 @@
       <c r="AR504" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS504" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="AT504" s="2" t="n">
+        <v>0.00126023944549468</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -69237,6 +72267,12 @@
       <c r="AR505" s="2" t="n">
         <v>0.0007575757575756741</v>
       </c>
+      <c r="AS505" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AT505" s="2" t="n">
+        <v>0.001514004542013669</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -69373,6 +72409,12 @@
       <c r="AR506" s="3" t="n">
         <v>-0.001174398120962959</v>
       </c>
+      <c r="AS506" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="AT506" s="2" t="n">
+        <v>0.0005878894767783417</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -69509,6 +72551,12 @@
       <c r="AR507" s="2" t="n">
         <v>0.004168113928447328</v>
       </c>
+      <c r="AS507" s="1" t="n">
+        <v>0.002888</v>
+      </c>
+      <c r="AT507" s="3" t="n">
+        <v>-0.00103770321687996</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -69645,6 +72693,12 @@
       <c r="AR508" s="2" t="n">
         <v>0.001809136137494348</v>
       </c>
+      <c r="AS508" s="1" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="AT508" s="2" t="n">
+        <v>0.0009029345372461508</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -69781,6 +72835,12 @@
       <c r="AR509" s="2" t="n">
         <v>0.00253807106598987</v>
       </c>
+      <c r="AS509" s="1" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="AT509" s="3" t="n">
+        <v>-0.0003616636528028786</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -69917,6 +72977,12 @@
       <c r="AR510" s="2" t="n">
         <v>0.002053388090349111</v>
       </c>
+      <c r="AS510" s="1" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="AT510" s="3" t="n">
+        <v>-0.003415300546448067</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -70053,6 +73119,12 @@
       <c r="AR511" s="2" t="n">
         <v>0.001234263144902529</v>
       </c>
+      <c r="AS511" s="1" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="AT511" s="3" t="n">
+        <v>-0.0004930966469427808</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -70189,6 +73261,12 @@
       <c r="AR512" s="3" t="n">
         <v>-0.01063829787234044</v>
       </c>
+      <c r="AS512" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AT512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -70325,6 +73403,12 @@
       <c r="AR513" s="3" t="n">
         <v>-0.003208127255714439</v>
       </c>
+      <c r="AS513" s="1" t="n">
+        <v>0.014836</v>
+      </c>
+      <c r="AT513" s="3" t="n">
+        <v>-0.005229985248759551</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -70461,6 +73545,12 @@
       <c r="AR514" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS514" s="1" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="AT514" s="2" t="n">
+        <v>0.002862049227246711</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -70597,6 +73687,12 @@
       <c r="AR515" s="3" t="n">
         <v>-0.00277264325323483</v>
       </c>
+      <c r="AS515" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="AT515" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -70733,6 +73829,12 @@
       <c r="AR516" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS516" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="AT516" s="2" t="n">
+        <v>0.003745318352059935</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -70869,6 +73971,12 @@
       <c r="AR517" s="3" t="n">
         <v>-0.0003899649031587675</v>
       </c>
+      <c r="AS517" s="1" t="n">
+        <v>0.007679</v>
+      </c>
+      <c r="AT517" s="3" t="n">
+        <v>-0.001430429128738586</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -71005,6 +74113,12 @@
       <c r="AR518" s="2" t="n">
         <v>0.00833867864015405</v>
       </c>
+      <c r="AS518" s="1" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="AT518" s="3" t="n">
+        <v>-0.005089058524173041</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -71141,6 +74255,12 @@
       <c r="AR519" s="3" t="n">
         <v>-0.002863278453829601</v>
       </c>
+      <c r="AS519" s="1" t="n">
+        <v>0.004178</v>
+      </c>
+      <c r="AT519" s="3" t="n">
+        <v>-0.0002392916965781605</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -71277,6 +74397,12 @@
       <c r="AR520" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS520" s="1" t="n">
+        <v>0.001162</v>
+      </c>
+      <c r="AT520" s="2" t="n">
+        <v>0.001724137931034525</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -71413,6 +74539,12 @@
       <c r="AR521" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS521" s="1" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="AT521" s="2" t="n">
+        <v>0.003728560775540619</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -71549,6 +74681,12 @@
       <c r="AR522" s="3" t="n">
         <v>-0.001888711317739311</v>
       </c>
+      <c r="AS522" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AT522" s="2" t="n">
+        <v>0.004366812227074078</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -71685,6 +74823,12 @@
       <c r="AR523" s="2" t="n">
         <v>0.0008534850640114437</v>
       </c>
+      <c r="AS523" s="1" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="AT523" s="2" t="n">
+        <v>0.0005685048322910512</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -71821,6 +74965,12 @@
       <c r="AR524" s="2" t="n">
         <v>0.009298393913778444</v>
       </c>
+      <c r="AS524" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="AT524" s="2" t="n">
+        <v>0.01842546063651604</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -71957,6 +75107,12 @@
       <c r="AR525" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS525" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="AT525" s="3" t="n">
+        <v>-0.002422774076317495</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -72093,6 +75249,12 @@
       <c r="AR526" s="3" t="n">
         <v>-0.003219767877199653</v>
       </c>
+      <c r="AS526" s="1" t="n">
+        <v>0.13329</v>
+      </c>
+      <c r="AT526" s="2" t="n">
+        <v>0.001277043269230795</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -72229,6 +75391,12 @@
       <c r="AR527" s="3" t="n">
         <v>-0.0006981615080289096</v>
       </c>
+      <c r="AS527" s="1" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="AT527" s="3" t="n">
+        <v>-0.0004657661853749228</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -72365,6 +75533,12 @@
       <c r="AR528" s="3" t="n">
         <v>-0.0007251631617113052</v>
       </c>
+      <c r="AS528" s="1" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="AT528" s="2" t="n">
+        <v>0.001088534107401912</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -72501,6 +75675,12 @@
       <c r="AR529" s="3" t="n">
         <v>-0.00289017341040462</v>
       </c>
+      <c r="AS529" s="1" t="n">
+        <v>0.000724</v>
+      </c>
+      <c r="AT529" s="3" t="n">
+        <v>-0.0006901311249136756</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -72637,6 +75817,12 @@
       <c r="AR530" s="3" t="n">
         <v>-0.0007142857142856026</v>
       </c>
+      <c r="AS530" s="1" t="n">
+        <v>0.004197</v>
+      </c>
+      <c r="AT530" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -72773,6 +75959,12 @@
       <c r="AR531" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS531" s="1" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="AT531" s="2" t="n">
+        <v>0.0007564296520422767</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -72909,6 +76101,12 @@
       <c r="AR532" s="2" t="n">
         <v>0.005037783375314889</v>
       </c>
+      <c r="AS532" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="AT532" s="3" t="n">
+        <v>-0.008354218880534678</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -73045,6 +76243,12 @@
       <c r="AR533" s="3" t="n">
         <v>-0.003739715781600576</v>
       </c>
+      <c r="AS533" s="1" t="n">
+        <v>0.05332</v>
+      </c>
+      <c r="AT533" s="2" t="n">
+        <v>0.0007507507507507202</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -73181,6 +76385,12 @@
       <c r="AR534" s="3" t="n">
         <v>-0.0006648936170213879</v>
       </c>
+      <c r="AS534" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="AT534" s="2" t="n">
+        <v>0.001330671989354662</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -73317,6 +76527,12 @@
       <c r="AR535" s="2" t="n">
         <v>0.03718535469107559</v>
       </c>
+      <c r="AS535" s="1" t="n">
+        <v>0.01718</v>
+      </c>
+      <c r="AT535" s="3" t="n">
+        <v>-0.05239933811362379</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -73453,6 +76669,12 @@
       <c r="AR536" s="3" t="n">
         <v>-0.000601081947505416</v>
       </c>
+      <c r="AS536" s="1" t="n">
+        <v>0.004984</v>
+      </c>
+      <c r="AT536" s="3" t="n">
+        <v>-0.0008019246190859123</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -73589,6 +76811,12 @@
       <c r="AR537" s="2" t="n">
         <v>0.001024940211820864</v>
       </c>
+      <c r="AS537" s="1" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AT537" s="3" t="n">
+        <v>-0.0003412969283276075</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -73725,6 +76953,12 @@
       <c r="AR538" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AT538" s="3" t="n">
+        <v>-0.001504890895410022</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -73861,6 +77095,12 @@
       <c r="AR539" s="2" t="n">
         <v>0.000792707094728603</v>
       </c>
+      <c r="AS539" s="1" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="AT539" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -73997,6 +77237,12 @@
       <c r="AR540" s="3" t="n">
         <v>-0.002449265220433891</v>
       </c>
+      <c r="AS540" s="1" t="n">
+        <v>0.05677</v>
+      </c>
+      <c r="AT540" s="3" t="n">
+        <v>-0.004384426517011579</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -74133,6 +77379,12 @@
       <c r="AR541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS541" s="1" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="AT541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -74269,6 +77521,12 @@
       <c r="AR542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AS542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AT542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -74405,6 +77663,12 @@
       <c r="AR543" s="3" t="n">
         <v>-0.001637554585152937</v>
       </c>
+      <c r="AS543" s="1" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="AT543" s="2" t="n">
+        <v>0.003280481137233541</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV543"/>
+  <dimension ref="A1:AX543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,8 @@
     <col width="18" customWidth="1" min="46" max="46"/>
     <col width="13" customWidth="1" min="47" max="47"/>
     <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,6 +719,16 @@
           <t>change_05:45</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>price_06:00</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>change_06:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -865,6 +877,12 @@
       <c r="AV2" s="2" t="n">
         <v>0.0009389085400966657</v>
       </c>
+      <c r="AW2" s="1" t="n">
+        <v>70702.3</v>
+      </c>
+      <c r="AX2" s="2" t="n">
+        <v>0.001823628098892462</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1013,6 +1031,12 @@
       <c r="AV3" s="2" t="n">
         <v>0.001089846985483238</v>
       </c>
+      <c r="AW3" s="1" t="n">
+        <v>2071.66</v>
+      </c>
+      <c r="AX3" s="2" t="n">
+        <v>0.002370860670808239</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1161,6 +1185,12 @@
       <c r="AV4" s="2" t="n">
         <v>0.002868946522836814</v>
       </c>
+      <c r="AW4" s="1" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AX4" s="2" t="n">
+        <v>0.0009154365488041915</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1309,6 +1339,12 @@
       <c r="AV5" s="2" t="n">
         <v>0.01223839524947503</v>
       </c>
+      <c r="AW5" s="1" t="n">
+        <v>0.013843</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>-0.009658034053512765</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1457,6 +1493,12 @@
       <c r="AV6" s="2" t="n">
         <v>0.001818765379266112</v>
       </c>
+      <c r="AW6" s="1" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+      <c r="AX6" s="2" t="n">
+        <v>0.0002135839384877429</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1605,6 +1647,12 @@
       <c r="AV7" s="2" t="n">
         <v>0.001152571675550946</v>
       </c>
+      <c r="AW7" s="1" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="AX7" s="2" t="n">
+        <v>0.001295150381349852</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1753,6 +1801,12 @@
       <c r="AV8" s="2" t="n">
         <v>0.00152379896935778</v>
       </c>
+      <c r="AW8" s="1" t="n">
+        <v>36.316</v>
+      </c>
+      <c r="AX8" s="2" t="n">
+        <v>0.004619768181692484</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1901,6 +1955,12 @@
       <c r="AV9" s="2" t="n">
         <v>0.001348845051424711</v>
       </c>
+      <c r="AW9" s="1" t="n">
+        <v>654.38</v>
+      </c>
+      <c r="AX9" s="2" t="n">
+        <v>0.001668478011296717</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2049,6 +2109,12 @@
       <c r="AV10" s="3" t="n">
         <v>-0.002427704391288875</v>
       </c>
+      <c r="AW10" s="1" t="n">
+        <v>14.124</v>
+      </c>
+      <c r="AX10" s="2" t="n">
+        <v>0.01095125617350229</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2197,6 +2263,12 @@
       <c r="AV11" s="2" t="n">
         <v>0.002958718827783757</v>
       </c>
+      <c r="AW11" s="1" t="n">
+        <v>213.87</v>
+      </c>
+      <c r="AX11" s="2" t="n">
+        <v>0.001451582693388286</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2345,6 +2417,12 @@
       <c r="AV12" s="2" t="n">
         <v>0.003260056826678596</v>
       </c>
+      <c r="AW12" s="1" t="n">
+        <v>0.0033541</v>
+      </c>
+      <c r="AX12" s="3" t="n">
+        <v>-8.94347722394327e-05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2493,6 +2571,12 @@
       <c r="AV13" s="2" t="n">
         <v>0.00471113315150019</v>
       </c>
+      <c r="AW13" s="1" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AX13" s="2" t="n">
+        <v>0.005923000987166761</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2641,6 +2725,12 @@
       <c r="AV14" s="2" t="n">
         <v>0.0003783579265986886</v>
       </c>
+      <c r="AW14" s="1" t="n">
+        <v>2.653</v>
+      </c>
+      <c r="AX14" s="2" t="n">
+        <v>0.003403933434190581</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2789,6 +2879,12 @@
       <c r="AV15" s="2" t="n">
         <v>0.002029632636492796</v>
       </c>
+      <c r="AW15" s="1" t="n">
+        <v>0.9907</v>
+      </c>
+      <c r="AX15" s="2" t="n">
+        <v>0.00334211059347779</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2937,6 +3033,12 @@
       <c r="AV16" s="2" t="n">
         <v>0.002651113467656492</v>
       </c>
+      <c r="AW16" s="1" t="n">
+        <v>0.05756</v>
+      </c>
+      <c r="AX16" s="2" t="n">
+        <v>0.01463070685704208</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3085,6 +3187,12 @@
       <c r="AV17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW17" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AX17" s="3" t="n">
+        <v>-0.004509582863585123</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3233,6 +3341,12 @@
       <c r="AV18" s="2" t="n">
         <v>0.001518026565464939</v>
       </c>
+      <c r="AW18" s="1" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="AX18" s="2" t="n">
+        <v>0.003410382720727383</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3381,6 +3495,12 @@
       <c r="AV19" s="2" t="n">
         <v>0.01242600245727692</v>
       </c>
+      <c r="AW19" s="1" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AX19" s="3" t="n">
+        <v>-0.002978735140800467</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3529,6 +3649,12 @@
       <c r="AV20" s="2" t="n">
         <v>0.000831773757537858</v>
       </c>
+      <c r="AW20" s="1" t="n">
+        <v>9.638999999999999</v>
+      </c>
+      <c r="AX20" s="2" t="n">
+        <v>0.001350509038022013</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3677,6 +3803,12 @@
       <c r="AV21" s="2" t="n">
         <v>0.0008398379606759012</v>
       </c>
+      <c r="AW21" s="1" t="n">
+        <v>205.44</v>
+      </c>
+      <c r="AX21" s="2" t="n">
+        <v>0.0140678217088701</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3825,6 +3957,12 @@
       <c r="AV22" s="3" t="n">
         <v>-0.0006469592913307019</v>
       </c>
+      <c r="AW22" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AX22" s="3" t="n">
+        <v>-0.004033663662168278</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3973,6 +4111,12 @@
       <c r="AV23" s="2" t="n">
         <v>0.002995779668058876</v>
       </c>
+      <c r="AW23" s="1" t="n">
+        <v>458.81</v>
+      </c>
+      <c r="AX23" s="2" t="n">
+        <v>0.0002834219935466893</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4121,6 +4265,12 @@
       <c r="AV24" s="3" t="n">
         <v>-0.0002724990481859206</v>
       </c>
+      <c r="AW24" s="1" t="n">
+        <v>5172.67</v>
+      </c>
+      <c r="AX24" s="3" t="n">
+        <v>-4.832860357399689e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4269,6 +4419,12 @@
       <c r="AV25" s="2" t="n">
         <v>0.001437735014377339</v>
       </c>
+      <c r="AW25" s="1" t="n">
+        <v>9.066000000000001</v>
+      </c>
+      <c r="AX25" s="2" t="n">
+        <v>0.001214798453892988</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4417,6 +4573,12 @@
       <c r="AV26" s="3" t="n">
         <v>-0.009373925008599878</v>
       </c>
+      <c r="AW26" s="1" t="n">
+        <v>0.11578</v>
+      </c>
+      <c r="AX26" s="2" t="n">
+        <v>0.005121972393436872</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4565,6 +4727,12 @@
       <c r="AV27" s="2" t="n">
         <v>0.007679180887371997</v>
       </c>
+      <c r="AW27" s="1" t="n">
+        <v>0.01174</v>
+      </c>
+      <c r="AX27" s="3" t="n">
+        <v>-0.005927180355630727</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4713,6 +4881,12 @@
       <c r="AV28" s="2" t="n">
         <v>0.00309358081979892</v>
       </c>
+      <c r="AW28" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="AX28" s="2" t="n">
+        <v>0.003084040092521206</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4861,6 +5035,12 @@
       <c r="AV29" s="3" t="n">
         <v>-0.007564545305048545</v>
       </c>
+      <c r="AW29" s="1" t="n">
+        <v>0.06033</v>
+      </c>
+      <c r="AX29" s="3" t="n">
+        <v>-0.0003314001657000694</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5009,6 +5189,12 @@
       <c r="AV30" s="2" t="n">
         <v>0.001309757694826458</v>
       </c>
+      <c r="AW30" s="1" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="AX30" s="2" t="n">
+        <v>0.001962066710268224</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5157,6 +5343,12 @@
       <c r="AV31" s="2" t="n">
         <v>0.005426739023186839</v>
       </c>
+      <c r="AW31" s="1" t="n">
+        <v>0.002047</v>
+      </c>
+      <c r="AX31" s="2" t="n">
+        <v>0.004416094210009974</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5305,6 +5497,12 @@
       <c r="AV32" s="2" t="n">
         <v>0.002241594022415935</v>
       </c>
+      <c r="AW32" s="1" t="n">
+        <v>0.04033</v>
+      </c>
+      <c r="AX32" s="2" t="n">
+        <v>0.002236580516898604</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5453,6 +5651,12 @@
       <c r="AV33" s="2" t="n">
         <v>0.007077856420626818</v>
       </c>
+      <c r="AW33" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="AX33" s="2" t="n">
+        <v>0.003012048192771171</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5601,6 +5805,12 @@
       <c r="AV34" s="2" t="n">
         <v>0.0009505703422053504</v>
       </c>
+      <c r="AW34" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AX34" s="2" t="n">
+        <v>0.003798670465337109</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5749,6 +5959,12 @@
       <c r="AV35" s="3" t="n">
         <v>-0.01199563794983631</v>
       </c>
+      <c r="AW35" s="1" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="AX35" s="3" t="n">
+        <v>-0.007726269315673357</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5897,6 +6113,12 @@
       <c r="AV36" s="2" t="n">
         <v>0.0008408071748877997</v>
       </c>
+      <c r="AW36" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AX36" s="2" t="n">
+        <v>0.004200504060487263</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6045,6 +6267,12 @@
       <c r="AV37" s="2" t="n">
         <v>0.0003472825143252992</v>
       </c>
+      <c r="AW37" s="1" t="n">
+        <v>0.005765</v>
+      </c>
+      <c r="AX37" s="2" t="n">
+        <v>0.000694323902100422</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6193,6 +6421,12 @@
       <c r="AV38" s="2" t="n">
         <v>0.00126947489901903</v>
       </c>
+      <c r="AW38" s="1" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="AX38" s="2" t="n">
+        <v>0.001421546027355085</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6341,6 +6575,12 @@
       <c r="AV39" s="2" t="n">
         <v>0.006003602161296811</v>
       </c>
+      <c r="AW39" s="1" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="AX39" s="2" t="n">
+        <v>0.002188183807439805</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6489,6 +6729,12 @@
       <c r="AV40" s="3" t="n">
         <v>-0.004536962903656351</v>
       </c>
+      <c r="AW40" s="1" t="n">
+        <v>0.15003</v>
+      </c>
+      <c r="AX40" s="2" t="n">
+        <v>0.00556300268096513</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6637,6 +6883,12 @@
       <c r="AV41" s="2" t="n">
         <v>0.003010234798314271</v>
       </c>
+      <c r="AW41" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AX41" s="2" t="n">
+        <v>0.00240096038415373</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6785,6 +7037,12 @@
       <c r="AV42" s="2" t="n">
         <v>0.0008992805755395172</v>
       </c>
+      <c r="AW42" s="1" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="AX42" s="2" t="n">
+        <v>0.001707097933513007</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6933,6 +7191,12 @@
       <c r="AV43" s="3" t="n">
         <v>-0.01367440763880709</v>
       </c>
+      <c r="AW43" s="1" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="AX43" s="3" t="n">
+        <v>-0.0001195171507111139</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7081,6 +7345,12 @@
       <c r="AV44" s="2" t="n">
         <v>0.0003637686431430179</v>
       </c>
+      <c r="AW44" s="1" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AX44" s="2" t="n">
+        <v>0.001818181818181844</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7229,6 +7499,12 @@
       <c r="AV45" s="3" t="n">
         <v>-0.006090597639893378</v>
       </c>
+      <c r="AW45" s="1" t="n">
+        <v>0.51896</v>
+      </c>
+      <c r="AX45" s="3" t="n">
+        <v>-0.006204519341248604</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7377,6 +7653,12 @@
       <c r="AV46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW46" s="1" t="n">
+        <v>0.7014</v>
+      </c>
+      <c r="AX46" s="2" t="n">
+        <v>0.002286367533581089</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7525,6 +7807,12 @@
       <c r="AV47" s="2" t="n">
         <v>0.001281394156842617</v>
       </c>
+      <c r="AW47" s="1" t="n">
+        <v>3.921</v>
+      </c>
+      <c r="AX47" s="2" t="n">
+        <v>0.00358331200409516</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7673,6 +7961,12 @@
       <c r="AV48" s="2" t="n">
         <v>0.0006243756243757289</v>
       </c>
+      <c r="AW48" s="1" t="n">
+        <v>0.16051</v>
+      </c>
+      <c r="AX48" s="2" t="n">
+        <v>0.001559965056782729</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7821,6 +8115,12 @@
       <c r="AV49" s="2" t="n">
         <v>0.007312614259597739</v>
       </c>
+      <c r="AW49" s="1" t="n">
+        <v>0.06074</v>
+      </c>
+      <c r="AX49" s="2" t="n">
+        <v>0.00214486058406212</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7969,6 +8269,12 @@
       <c r="AV50" s="2" t="n">
         <v>0.002557544757033144</v>
       </c>
+      <c r="AW50" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="AX50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8117,6 +8423,12 @@
       <c r="AV51" s="2" t="n">
         <v>0.07222919864192358</v>
       </c>
+      <c r="AW51" s="1" t="n">
+        <v>0.22655</v>
+      </c>
+      <c r="AX51" s="3" t="n">
+        <v>-0.01730719181053177</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8265,6 +8577,12 @@
       <c r="AV52" s="3" t="n">
         <v>-0.002349781805975087</v>
       </c>
+      <c r="AW52" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AX52" s="2" t="n">
+        <v>0.0006729475100941385</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8413,6 +8731,12 @@
       <c r="AV53" s="2" t="n">
         <v>0.004383218534752526</v>
       </c>
+      <c r="AW53" s="1" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="AX53" s="2" t="n">
+        <v>0.004364089775561136</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8561,6 +8885,12 @@
       <c r="AV54" s="3" t="n">
         <v>-0.0001374617684457885</v>
       </c>
+      <c r="AW54" s="1" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AX54" s="3" t="n">
+        <v>-0.001237326001031007</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8709,6 +9039,12 @@
       <c r="AV55" s="2" t="n">
         <v>0.003640946646127991</v>
       </c>
+      <c r="AW55" s="1" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AX55" s="2" t="n">
+        <v>0.004604437002930103</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8857,6 +9193,12 @@
       <c r="AV56" s="3" t="n">
         <v>-0.0006854009595614343</v>
       </c>
+      <c r="AW56" s="1" t="n">
+        <v>0.02904</v>
+      </c>
+      <c r="AX56" s="3" t="n">
+        <v>-0.004115226337448511</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9005,6 +9347,12 @@
       <c r="AV57" s="2" t="n">
         <v>0.0002384358607535303</v>
       </c>
+      <c r="AW57" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="AX57" s="2" t="n">
+        <v>0.006674612634088094</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9153,6 +9501,12 @@
       <c r="AV58" s="3" t="n">
         <v>-0.01977800201816337</v>
       </c>
+      <c r="AW58" s="1" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="AX58" s="2" t="n">
+        <v>0.01502985381922986</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9301,6 +9655,12 @@
       <c r="AV59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW59" s="1" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="AX59" s="2" t="n">
+        <v>0.007863695937090439</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9449,6 +9809,12 @@
       <c r="AV60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AX60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9597,6 +9963,12 @@
       <c r="AV61" s="2" t="n">
         <v>0.00322372662798195</v>
       </c>
+      <c r="AW61" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="AX61" s="2" t="n">
+        <v>0.001285347043701836</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9745,6 +10117,12 @@
       <c r="AV62" s="2" t="n">
         <v>0.004428697962798843</v>
       </c>
+      <c r="AW62" s="1" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="AX62" s="2" t="n">
+        <v>0.003527336860670197</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9893,6 +10271,12 @@
       <c r="AV63" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW63" s="1" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="AX63" s="2" t="n">
+        <v>0.002852253280091274</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10041,6 +10425,12 @@
       <c r="AV64" s="3" t="n">
         <v>-0.0006849315068492396</v>
       </c>
+      <c r="AW64" s="1" t="n">
+        <v>2.918</v>
+      </c>
+      <c r="AX64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10189,6 +10579,12 @@
       <c r="AV65" s="2" t="n">
         <v>0.001271186440678061</v>
       </c>
+      <c r="AW65" s="1" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="AX65" s="3" t="n">
+        <v>-0.0004231908590775735</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10337,6 +10733,12 @@
       <c r="AV66" s="2" t="n">
         <v>0.002982107355864897</v>
       </c>
+      <c r="AW66" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AX66" s="2" t="n">
+        <v>0.0009910802775025061</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10485,6 +10887,12 @@
       <c r="AV67" s="3" t="n">
         <v>-0.0010984484415763</v>
       </c>
+      <c r="AW67" s="1" t="n">
+        <v>0.007305</v>
+      </c>
+      <c r="AX67" s="2" t="n">
+        <v>0.004123711340206136</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10633,6 +11041,12 @@
       <c r="AV68" s="2" t="n">
         <v>0.002168021680216756</v>
       </c>
+      <c r="AW68" s="1" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AX68" s="3" t="n">
+        <v>-0.004326663061114024</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10781,6 +11195,12 @@
       <c r="AV69" s="2" t="n">
         <v>0.004552075746540427</v>
       </c>
+      <c r="AW69" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="AX69" s="2" t="n">
+        <v>0.0054377379010332</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10929,6 +11349,12 @@
       <c r="AV70" s="2" t="n">
         <v>0.00431034482758621</v>
       </c>
+      <c r="AW70" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AX70" s="2" t="n">
+        <v>0.004291845493562235</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11077,6 +11503,12 @@
       <c r="AV71" s="3" t="n">
         <v>-0.0006753334458889833</v>
       </c>
+      <c r="AW71" s="1" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="AX71" s="3" t="n">
+        <v>-0.004054738976178412</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11225,6 +11657,12 @@
       <c r="AV72" s="2" t="n">
         <v>0.005790387955993067</v>
       </c>
+      <c r="AW72" s="1" t="n">
+        <v>0.001707</v>
+      </c>
+      <c r="AX72" s="3" t="n">
+        <v>-0.01727115716753027</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11373,6 +11811,12 @@
       <c r="AV73" s="2" t="n">
         <v>0.003290521176095947</v>
       </c>
+      <c r="AW73" s="1" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="AX73" s="2" t="n">
+        <v>0.0009521794329242614</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11521,6 +11965,12 @@
       <c r="AV74" s="2" t="n">
         <v>0.001658374792703198</v>
       </c>
+      <c r="AW74" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AX74" s="2" t="n">
+        <v>0.00165562913907278</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11669,6 +12119,12 @@
       <c r="AV75" s="2" t="n">
         <v>0.001674804133076053</v>
       </c>
+      <c r="AW75" s="1" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="AX75" s="2" t="n">
+        <v>0.0007368152577436192</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11817,6 +12273,12 @@
       <c r="AV76" s="2" t="n">
         <v>0.007877975192759054</v>
       </c>
+      <c r="AW76" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="AX76" s="2" t="n">
+        <v>0.001995676035256862</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11965,6 +12427,12 @@
       <c r="AV77" s="2" t="n">
         <v>0.002383222116301197</v>
       </c>
+      <c r="AW77" s="1" t="n">
+        <v>0.06315</v>
+      </c>
+      <c r="AX77" s="2" t="n">
+        <v>0.0009510223490252735</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12113,6 +12581,12 @@
       <c r="AV78" s="2" t="n">
         <v>0.004967237370534752</v>
       </c>
+      <c r="AW78" s="1" t="n">
+        <v>0.09537</v>
+      </c>
+      <c r="AX78" s="2" t="n">
+        <v>0.002944578820065228</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12261,6 +12735,12 @@
       <c r="AV79" s="2" t="n">
         <v>0.01386138613861385</v>
       </c>
+      <c r="AW79" s="1" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AX79" s="2" t="n">
+        <v>0.01098632812500001</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12409,6 +12889,12 @@
       <c r="AV80" s="2" t="n">
         <v>0.002840434419381875</v>
       </c>
+      <c r="AW80" s="1" t="n">
+        <v>0.006013</v>
+      </c>
+      <c r="AX80" s="2" t="n">
+        <v>0.001832722425858001</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12557,6 +13043,12 @@
       <c r="AV81" s="2" t="n">
         <v>0.0009803921568627733</v>
       </c>
+      <c r="AW81" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="AX81" s="2" t="n">
+        <v>0.001958863858961858</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12705,6 +13197,12 @@
       <c r="AV82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW82" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AX82" s="2" t="n">
+        <v>0.004926108374384104</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12853,6 +13351,12 @@
       <c r="AV83" s="2" t="n">
         <v>0.008914100486223694</v>
       </c>
+      <c r="AW83" s="1" t="n">
+        <v>0.06254999999999999</v>
+      </c>
+      <c r="AX83" s="2" t="n">
+        <v>0.00481927710843365</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13001,6 +13505,12 @@
       <c r="AV84" s="3" t="n">
         <v>-0.000358037952022875</v>
       </c>
+      <c r="AW84" s="1" t="n">
+        <v>1.1176</v>
+      </c>
+      <c r="AX84" s="2" t="n">
+        <v>0.0007163323782234168</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13149,6 +13659,12 @@
       <c r="AV85" s="2" t="n">
         <v>0.004665629860031049</v>
       </c>
+      <c r="AW85" s="1" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="AX85" s="2" t="n">
+        <v>0.003869969040247789</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13297,6 +13813,12 @@
       <c r="AV86" s="2" t="n">
         <v>0.004191616766467103</v>
       </c>
+      <c r="AW86" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="AX86" s="2" t="n">
+        <v>0.001788908765652879</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13445,6 +13967,12 @@
       <c r="AV87" s="2" t="n">
         <v>0.002410219329958975</v>
       </c>
+      <c r="AW87" s="1" t="n">
+        <v>8.337999999999999</v>
+      </c>
+      <c r="AX87" s="2" t="n">
+        <v>0.002404424140418319</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13593,6 +14121,12 @@
       <c r="AV88" s="3" t="n">
         <v>-4.699468959996567e-05</v>
       </c>
+      <c r="AW88" s="1" t="n">
+        <v>2.1221</v>
+      </c>
+      <c r="AX88" s="3" t="n">
+        <v>-0.002678823197668972</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13741,6 +14275,12 @@
       <c r="AV89" s="2" t="n">
         <v>0.008701657458563493</v>
       </c>
+      <c r="AW89" s="1" t="n">
+        <v>0.007404</v>
+      </c>
+      <c r="AX89" s="2" t="n">
+        <v>0.01382993290428597</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13889,6 +14429,12 @@
       <c r="AV90" s="3" t="n">
         <v>-0.0006574621959238371</v>
       </c>
+      <c r="AW90" s="1" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="AX90" s="2" t="n">
+        <v>0.001973684210526391</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14037,6 +14583,12 @@
       <c r="AV91" s="2" t="n">
         <v>0.004444444444444432</v>
       </c>
+      <c r="AW91" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="AX91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14185,6 +14737,12 @@
       <c r="AV92" s="3" t="n">
         <v>-0.0001925669170035841</v>
       </c>
+      <c r="AW92" s="1" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="AX92" s="3" t="n">
+        <v>-0.004237288135593181</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14333,6 +14891,12 @@
       <c r="AV93" s="2" t="n">
         <v>0.001200210036756467</v>
       </c>
+      <c r="AW93" s="1" t="n">
+        <v>1.3383</v>
+      </c>
+      <c r="AX93" s="2" t="n">
+        <v>0.002697235333782908</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14481,6 +15045,12 @@
       <c r="AV94" s="3" t="n">
         <v>-0.01865724632535687</v>
       </c>
+      <c r="AW94" s="1" t="n">
+        <v>0.05568</v>
+      </c>
+      <c r="AX94" s="2" t="n">
+        <v>0.00721766972377496</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14629,6 +15199,12 @@
       <c r="AV95" s="2" t="n">
         <v>0.002509410288582139</v>
       </c>
+      <c r="AW95" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AX95" s="2" t="n">
+        <v>0.00125156445556944</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14777,6 +15353,12 @@
       <c r="AV96" s="2" t="n">
         <v>0.002963511761437182</v>
       </c>
+      <c r="AW96" s="1" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="AX96" s="2" t="n">
+        <v>0.000554016620498554</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14925,6 +15507,12 @@
       <c r="AV97" s="2" t="n">
         <v>0.001167769560140004</v>
       </c>
+      <c r="AW97" s="1" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AX97" s="2" t="n">
+        <v>0.002332814930015511</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -15073,6 +15661,12 @@
       <c r="AV98" s="2" t="n">
         <v>0.0001696352841390823</v>
       </c>
+      <c r="AW98" s="1" t="n">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="AX98" s="3" t="n">
+        <v>-0.0006784260515604935</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -15221,6 +15815,12 @@
       <c r="AV99" s="2" t="n">
         <v>0.003979185797367772</v>
       </c>
+      <c r="AW99" s="1" t="n">
+        <v>0.13065</v>
+      </c>
+      <c r="AX99" s="3" t="n">
+        <v>-0.00419207317073188</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -15369,6 +15969,12 @@
       <c r="AV100" s="2" t="n">
         <v>0.0003221649484535951</v>
       </c>
+      <c r="AW100" s="1" t="n">
+        <v>0.03109</v>
+      </c>
+      <c r="AX100" s="2" t="n">
+        <v>0.001288244766505584</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -15517,6 +16123,12 @@
       <c r="AV101" s="2" t="n">
         <v>0.002846299810246576</v>
       </c>
+      <c r="AW101" s="1" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="AX101" s="2" t="n">
+        <v>0.001892147587511828</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15665,6 +16277,12 @@
       <c r="AV102" s="2" t="n">
         <v>0.006802721088435411</v>
       </c>
+      <c r="AW102" s="1" t="n">
+        <v>0.02219</v>
+      </c>
+      <c r="AX102" s="3" t="n">
+        <v>-0.0004504504504504321</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -15813,6 +16431,12 @@
       <c r="AV103" s="2" t="n">
         <v>0.002589331952356186</v>
       </c>
+      <c r="AW103" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="AX103" s="3" t="n">
+        <v>-0.007231404958677571</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -15961,6 +16585,12 @@
       <c r="AV104" s="2" t="n">
         <v>0.003002001334222781</v>
       </c>
+      <c r="AW104" s="1" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="AX104" s="2" t="n">
+        <v>0.0003325573661456235</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -16109,6 +16739,12 @@
       <c r="AV105" s="2" t="n">
         <v>0.004013584439641944</v>
       </c>
+      <c r="AW105" s="1" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="AX105" s="2" t="n">
+        <v>0.002767527675276639</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -16257,6 +16893,12 @@
       <c r="AV106" s="2" t="n">
         <v>0.005408653846153918</v>
       </c>
+      <c r="AW106" s="1" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="AX106" s="2" t="n">
+        <v>0.0005977286312013687</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -16405,6 +17047,12 @@
       <c r="AV107" s="3" t="n">
         <v>-0.001568451714093611</v>
       </c>
+      <c r="AW107" s="1" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="AX107" s="2" t="n">
+        <v>0.001795332136445294</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -16553,6 +17201,12 @@
       <c r="AV108" s="2" t="n">
         <v>0.003276735180220405</v>
       </c>
+      <c r="AW108" s="1" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AX108" s="2" t="n">
+        <v>0.001781472684085479</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16701,6 +17355,12 @@
       <c r="AV109" s="3" t="n">
         <v>-0.00267976775346132</v>
       </c>
+      <c r="AW109" s="1" t="n">
+        <v>0.2231</v>
+      </c>
+      <c r="AX109" s="3" t="n">
+        <v>-0.0008956560680698868</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16849,6 +17509,12 @@
       <c r="AV110" s="3" t="n">
         <v>-0.00673400673400681</v>
       </c>
+      <c r="AW110" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="AX110" s="2" t="n">
+        <v>0.004067796610169561</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -16997,6 +17663,12 @@
       <c r="AV111" s="2" t="n">
         <v>0.002186987424822309</v>
       </c>
+      <c r="AW111" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="AX111" s="2" t="n">
+        <v>0.001636661211129358</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -17145,6 +17817,12 @@
       <c r="AV112" s="3" t="n">
         <v>-0.00103842159916922</v>
       </c>
+      <c r="AW112" s="1" t="n">
+        <v>0.03858</v>
+      </c>
+      <c r="AX112" s="2" t="n">
+        <v>0.002598752598752673</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -17293,6 +17971,12 @@
       <c r="AV113" s="3" t="n">
         <v>-0.0009510223490253085</v>
       </c>
+      <c r="AW113" s="1" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AX113" s="2" t="n">
+        <v>0.004283674440742454</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -17441,6 +18125,12 @@
       <c r="AV114" s="3" t="n">
         <v>-0.002915838303512187</v>
       </c>
+      <c r="AW114" s="1" t="n">
+        <v>0.007529</v>
+      </c>
+      <c r="AX114" s="2" t="n">
+        <v>0.0007975541672205143</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -17589,6 +18279,12 @@
       <c r="AV115" s="3" t="n">
         <v>-0.0002966185485464541</v>
       </c>
+      <c r="AW115" s="1" t="n">
+        <v>0.10086</v>
+      </c>
+      <c r="AX115" s="3" t="n">
+        <v>-0.002472554643457622</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -17737,6 +18433,12 @@
       <c r="AV116" s="2" t="n">
         <v>0.001931900507123804</v>
       </c>
+      <c r="AW116" s="1" t="n">
+        <v>0.08314000000000001</v>
+      </c>
+      <c r="AX116" s="2" t="n">
+        <v>0.00192817546396731</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -17885,6 +18587,12 @@
       <c r="AV117" s="2" t="n">
         <v>0.0006668889629875891</v>
       </c>
+      <c r="AW117" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="AX117" s="2" t="n">
+        <v>0.000666444518493947</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -18033,6 +18741,12 @@
       <c r="AV118" s="3" t="n">
         <v>-0.0008865248226949993</v>
       </c>
+      <c r="AW118" s="1" t="n">
+        <v>0.02247</v>
+      </c>
+      <c r="AX118" s="3" t="n">
+        <v>-0.003105590062111828</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18181,6 +18895,12 @@
       <c r="AV119" s="2" t="n">
         <v>0.004632693580410181</v>
       </c>
+      <c r="AW119" s="1" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="AX119" s="2" t="n">
+        <v>0.001976284584980385</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18329,6 +19049,12 @@
       <c r="AV120" s="3" t="n">
         <v>-0.008363471971066842</v>
       </c>
+      <c r="AW120" s="1" t="n">
+        <v>0.004392</v>
+      </c>
+      <c r="AX120" s="2" t="n">
+        <v>0.001139731023478413</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -18477,6 +19203,12 @@
       <c r="AV121" s="2" t="n">
         <v>0.0002344116268167944</v>
       </c>
+      <c r="AW121" s="1" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="AX121" s="3" t="n">
+        <v>-0.001406140145301254</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -18625,6 +19357,12 @@
       <c r="AV122" s="2" t="n">
         <v>0.003870967741935487</v>
       </c>
+      <c r="AW122" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="AX122" s="2" t="n">
+        <v>0.001285347043701801</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18773,6 +19511,12 @@
       <c r="AV123" s="2" t="n">
         <v>0.003472222222222161</v>
       </c>
+      <c r="AW123" s="1" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="AX123" s="2" t="n">
+        <v>0.001153402537485615</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -18921,6 +19665,12 @@
       <c r="AV124" s="2" t="n">
         <v>0.004045307443365671</v>
       </c>
+      <c r="AW124" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="AX124" s="2" t="n">
+        <v>0.008058017727639092</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -19069,6 +19819,12 @@
       <c r="AV125" s="2" t="n">
         <v>0.00255440890977828</v>
       </c>
+      <c r="AW125" s="1" t="n">
+        <v>0.09841999999999999</v>
+      </c>
+      <c r="AX125" s="2" t="n">
+        <v>0.003057480635955919</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -19217,6 +19973,12 @@
       <c r="AV126" s="2" t="n">
         <v>0.002111932418162533</v>
       </c>
+      <c r="AW126" s="1" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AX126" s="3" t="n">
+        <v>-0.001896733403582715</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -19365,6 +20127,12 @@
       <c r="AV127" s="2" t="n">
         <v>0.01238390092879266</v>
       </c>
+      <c r="AW127" s="1" t="n">
+        <v>3.28e-05</v>
+      </c>
+      <c r="AX127" s="2" t="n">
+        <v>0.003058103975535035</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -19513,6 +20281,12 @@
       <c r="AV128" s="3" t="n">
         <v>-0.000351555633678991</v>
       </c>
+      <c r="AW128" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AX128" s="2" t="n">
+        <v>0.002285915245296233</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -19661,6 +20435,12 @@
       <c r="AV129" s="2" t="n">
         <v>0.0003078817733988954</v>
       </c>
+      <c r="AW129" s="1" t="n">
+        <v>0.06493</v>
+      </c>
+      <c r="AX129" s="3" t="n">
+        <v>-0.0007694675284702139</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -19809,6 +20589,12 @@
       <c r="AV130" s="3" t="n">
         <v>-0.001326699834162553</v>
       </c>
+      <c r="AW130" s="1" t="n">
+        <v>0.0006015</v>
+      </c>
+      <c r="AX130" s="3" t="n">
+        <v>-0.001162404516771775</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -19957,6 +20743,12 @@
       <c r="AV131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AX131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -20105,6 +20897,12 @@
       <c r="AV132" s="2" t="n">
         <v>0.01233333333333346</v>
       </c>
+      <c r="AW132" s="1" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AX132" s="3" t="n">
+        <v>-0.001646361540994404</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -20253,6 +21051,12 @@
       <c r="AV133" s="2" t="n">
         <v>0.007950530035335673</v>
       </c>
+      <c r="AW133" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="AX133" s="2" t="n">
+        <v>0.005258545135845941</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -20401,6 +21205,12 @@
       <c r="AV134" s="3" t="n">
         <v>-0.000210762961922174</v>
       </c>
+      <c r="AW134" s="1" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="AX134" s="2" t="n">
+        <v>0.001545920876958738</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -20549,6 +21359,12 @@
       <c r="AV135" s="2" t="n">
         <v>0.003057065217391298</v>
       </c>
+      <c r="AW135" s="1" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="AX135" s="2" t="n">
+        <v>0.001693193362681949</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -20697,6 +21513,12 @@
       <c r="AV136" s="3" t="n">
         <v>-0.0007082152974504099</v>
       </c>
+      <c r="AW136" s="1" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AX136" s="2" t="n">
+        <v>0.002834868887314027</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -20845,6 +21667,12 @@
       <c r="AV137" s="2" t="n">
         <v>0.006444188722669768</v>
       </c>
+      <c r="AW137" s="1" t="n">
+        <v>0.0004384</v>
+      </c>
+      <c r="AX137" s="2" t="n">
+        <v>0.002515435627715464</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -20993,6 +21821,12 @@
       <c r="AV138" s="3" t="n">
         <v>-0.006747308068801643</v>
       </c>
+      <c r="AW138" s="1" t="n">
+        <v>0.028432</v>
+      </c>
+      <c r="AX138" s="2" t="n">
+        <v>0.0007391503290978911</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21141,6 +21975,12 @@
       <c r="AV139" s="3" t="n">
         <v>-0.002608786392570179</v>
       </c>
+      <c r="AW139" s="1" t="n">
+        <v>0.09561</v>
+      </c>
+      <c r="AX139" s="2" t="n">
+        <v>0.0003138731952291509</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21289,6 +22129,12 @@
       <c r="AV140" s="2" t="n">
         <v>0.0002775464890368831</v>
       </c>
+      <c r="AW140" s="1" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AX140" s="2" t="n">
+        <v>0.0002774694783573501</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21437,6 +22283,12 @@
       <c r="AV141" s="2" t="n">
         <v>0.01090225563909782</v>
       </c>
+      <c r="AW141" s="1" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AX141" s="2" t="n">
+        <v>0.006322052807735218</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21585,6 +22437,12 @@
       <c r="AV142" s="2" t="n">
         <v>0.003146633102580067</v>
       </c>
+      <c r="AW142" s="1" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="AX142" s="2" t="n">
+        <v>0.003011292346298672</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -21733,6 +22591,12 @@
       <c r="AV143" s="2" t="n">
         <v>0.006280843427545884</v>
       </c>
+      <c r="AW143" s="1" t="n">
+        <v>0.08971999999999999</v>
+      </c>
+      <c r="AX143" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -21881,6 +22745,12 @@
       <c r="AV144" s="3" t="n">
         <v>-0.002894356005788594</v>
       </c>
+      <c r="AW144" s="1" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="AX144" s="2" t="n">
+        <v>0.005805515239477435</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22029,6 +22899,12 @@
       <c r="AV145" s="3" t="n">
         <v>-0.008305216714248659</v>
       </c>
+      <c r="AW145" s="1" t="n">
+        <v>0.11447</v>
+      </c>
+      <c r="AX145" s="3" t="n">
+        <v>-0.001395795167059177</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -22177,6 +23053,12 @@
       <c r="AV146" s="2" t="n">
         <v>0.002937336814621449</v>
       </c>
+      <c r="AW146" s="1" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AX146" s="2" t="n">
+        <v>0.003579563944028604</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -22325,6 +23207,12 @@
       <c r="AV147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AX147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -22473,6 +23361,12 @@
       <c r="AV148" s="2" t="n">
         <v>0.0006671456430256885</v>
       </c>
+      <c r="AW148" s="1" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="AX148" s="2" t="n">
+        <v>0.00107697830657982</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -22621,6 +23515,12 @@
       <c r="AV149" s="2" t="n">
         <v>0.0006453694740238524</v>
       </c>
+      <c r="AW149" s="1" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="AX149" s="2" t="n">
+        <v>0.001451144792002577</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -22769,6 +23669,12 @@
       <c r="AV150" s="3" t="n">
         <v>-0.000599880023995135</v>
       </c>
+      <c r="AW150" s="1" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="AX150" s="2" t="n">
+        <v>0.01380552220888353</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -22917,6 +23823,12 @@
       <c r="AV151" s="2" t="n">
         <v>0.003280644199224695</v>
       </c>
+      <c r="AW151" s="1" t="n">
+        <v>6.736000000000001e-05</v>
+      </c>
+      <c r="AX151" s="2" t="n">
+        <v>0.001189060642092735</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -23065,6 +23977,12 @@
       <c r="AV152" s="2" t="n">
         <v>0.002042205582028626</v>
       </c>
+      <c r="AW152" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="AX152" s="2" t="n">
+        <v>0.0006793478260869289</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -23213,6 +24131,12 @@
       <c r="AV153" s="2" t="n">
         <v>0.002374169040835775</v>
       </c>
+      <c r="AW153" s="1" t="n">
+        <v>0.02119</v>
+      </c>
+      <c r="AX153" s="2" t="n">
+        <v>0.003789673140691625</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -23361,6 +24285,12 @@
       <c r="AV154" s="2" t="n">
         <v>0.0008418925745076047</v>
       </c>
+      <c r="AW154" s="1" t="n">
+        <v>0.0005947</v>
+      </c>
+      <c r="AX154" s="2" t="n">
+        <v>0.0005047106325705806</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -23509,6 +24439,12 @@
       <c r="AV155" s="2" t="n">
         <v>0.003984063745019931</v>
       </c>
+      <c r="AW155" s="1" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="AX155" s="2" t="n">
+        <v>0.001736111111111126</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -23657,6 +24593,12 @@
       <c r="AV156" s="2" t="n">
         <v>0.003164556962025187</v>
       </c>
+      <c r="AW156" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="AX156" s="3" t="n">
+        <v>-0.003154574132491985</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -23805,6 +24747,12 @@
       <c r="AV157" s="2" t="n">
         <v>0.003350832123310563</v>
       </c>
+      <c r="AW157" s="1" t="n">
+        <v>0.09071</v>
+      </c>
+      <c r="AX157" s="2" t="n">
+        <v>0.009796281865746475</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -23953,6 +24901,12 @@
       <c r="AV158" s="2" t="n">
         <v>0.02152711703139853</v>
       </c>
+      <c r="AW158" s="1" t="n">
+        <v>0.008507000000000001</v>
+      </c>
+      <c r="AX158" s="3" t="n">
+        <v>-0.009547095121667102</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -24101,6 +25055,12 @@
       <c r="AV159" s="3" t="n">
         <v>-0.001967729240456471</v>
       </c>
+      <c r="AW159" s="1" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="AX159" s="2" t="n">
+        <v>0.002365930599369</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -24249,6 +25209,12 @@
       <c r="AV160" s="2" t="n">
         <v>0.002643034825870701</v>
       </c>
+      <c r="AW160" s="1" t="n">
+        <v>1.2932</v>
+      </c>
+      <c r="AX160" s="2" t="n">
+        <v>0.002636067607380871</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -24397,6 +25363,12 @@
       <c r="AV161" s="2" t="n">
         <v>0.0006648936170212495</v>
       </c>
+      <c r="AW161" s="1" t="n">
+        <v>0.007521</v>
+      </c>
+      <c r="AX161" s="3" t="n">
+        <v>-0.0005315614617939753</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -24545,6 +25517,12 @@
       <c r="AV162" s="2" t="n">
         <v>0.004927322000492745</v>
       </c>
+      <c r="AW162" s="1" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="AX162" s="3" t="n">
+        <v>-0.007109585682765477</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -24693,6 +25671,12 @@
       <c r="AV163" s="2" t="n">
         <v>0.002070393374741116</v>
       </c>
+      <c r="AW163" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="AX163" s="2" t="n">
+        <v>0.001033057851239699</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -24841,6 +25825,12 @@
       <c r="AV164" s="3" t="n">
         <v>-0.0005057803468207536</v>
       </c>
+      <c r="AW164" s="1" t="n">
+        <v>1.3866</v>
+      </c>
+      <c r="AX164" s="2" t="n">
+        <v>0.002385599653003745</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -24989,6 +25979,12 @@
       <c r="AV165" s="2" t="n">
         <v>0.0007203389830508328</v>
       </c>
+      <c r="AW165" s="1" t="n">
+        <v>0.023633</v>
+      </c>
+      <c r="AX165" s="2" t="n">
+        <v>0.0006774780878181871</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -25137,6 +26133,12 @@
       <c r="AV166" s="2" t="n">
         <v>0.0001920491645861596</v>
       </c>
+      <c r="AW166" s="1" t="n">
+        <v>0.005231</v>
+      </c>
+      <c r="AX166" s="2" t="n">
+        <v>0.00441628264208918</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -25285,6 +26287,12 @@
       <c r="AV167" s="2" t="n">
         <v>0.001795600778093597</v>
       </c>
+      <c r="AW167" s="1" t="n">
+        <v>0.06698</v>
+      </c>
+      <c r="AX167" s="2" t="n">
+        <v>0.0004480955937266953</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -25433,6 +26441,12 @@
       <c r="AV168" s="2" t="n">
         <v>0.001052631578947399</v>
       </c>
+      <c r="AW168" s="1" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="AX168" s="2" t="n">
+        <v>0.001051524710830735</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -25581,6 +26595,12 @@
       <c r="AV169" s="2" t="n">
         <v>0.003108003108003161</v>
       </c>
+      <c r="AW169" s="1" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AX169" s="2" t="n">
+        <v>0.002323780015491862</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -25729,6 +26749,12 @@
       <c r="AV170" s="2" t="n">
         <v>0.0004213483146067975</v>
       </c>
+      <c r="AW170" s="1" t="n">
+        <v>0.007137</v>
+      </c>
+      <c r="AX170" s="2" t="n">
+        <v>0.001965463989891917</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -25877,6 +26903,12 @@
       <c r="AV171" s="2" t="n">
         <v>0.0008818342151676146</v>
       </c>
+      <c r="AW171" s="1" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AX171" s="2" t="n">
+        <v>0.002643171806167272</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -26025,6 +27057,12 @@
       <c r="AV172" s="2" t="n">
         <v>0.001656238498343661</v>
       </c>
+      <c r="AW172" s="1" t="n">
+        <v>5.461</v>
+      </c>
+      <c r="AX172" s="2" t="n">
+        <v>0.003306999816277913</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -26173,6 +27211,12 @@
       <c r="AV173" s="2" t="n">
         <v>0.002850877192982416</v>
       </c>
+      <c r="AW173" s="1" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="AX173" s="2" t="n">
+        <v>0.002186748305270126</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -26321,6 +27365,12 @@
       <c r="AV174" s="2" t="n">
         <v>0.00152516522623278</v>
       </c>
+      <c r="AW174" s="1" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="AX174" s="3" t="n">
+        <v>-0.0007614213197968353</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -26469,6 +27519,12 @@
       <c r="AV175" s="3" t="n">
         <v>-0.005369608018614577</v>
       </c>
+      <c r="AW175" s="1" t="n">
+        <v>0.00555</v>
+      </c>
+      <c r="AX175" s="3" t="n">
+        <v>-0.001259672485153871</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -26617,6 +27673,12 @@
       <c r="AV176" s="2" t="n">
         <v>0.002649006622516563</v>
       </c>
+      <c r="AW176" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="AX176" s="2" t="n">
+        <v>0.001321003963011835</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -26765,6 +27827,12 @@
       <c r="AV177" s="3" t="n">
         <v>-0.0005633802816900789</v>
       </c>
+      <c r="AW177" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="AX177" s="2" t="n">
+        <v>0.0050732807215332</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -26913,6 +27981,12 @@
       <c r="AV178" s="2" t="n">
         <v>0.00406400812801626</v>
       </c>
+      <c r="AW178" s="1" t="n">
+        <v>15.832</v>
+      </c>
+      <c r="AX178" s="2" t="n">
+        <v>0.001264862130027912</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -27061,6 +28135,12 @@
       <c r="AV179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW179" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AX179" s="2" t="n">
+        <v>0.003164556962025319</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -27209,6 +28289,12 @@
       <c r="AV180" s="3" t="n">
         <v>-0.002473206924979432</v>
       </c>
+      <c r="AW180" s="1" t="n">
+        <v>0.09675</v>
+      </c>
+      <c r="AX180" s="3" t="n">
+        <v>-0.0005165289256197778</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -27357,6 +28443,12 @@
       <c r="AV181" s="2" t="n">
         <v>0.0005327650506126211</v>
       </c>
+      <c r="AW181" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="AX181" s="2" t="n">
+        <v>0.001597444089456841</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -27505,6 +28597,12 @@
       <c r="AV182" s="2" t="n">
         <v>0.001682085786375037</v>
       </c>
+      <c r="AW182" s="1" t="n">
+        <v>0.05965</v>
+      </c>
+      <c r="AX182" s="2" t="n">
+        <v>0.001679261125105002</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -27653,6 +28751,12 @@
       <c r="AV183" s="3" t="n">
         <v>-0.0008333333333332993</v>
       </c>
+      <c r="AW183" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="AX183" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -27801,6 +28905,12 @@
       <c r="AV184" s="2" t="n">
         <v>0.006532897806812775</v>
       </c>
+      <c r="AW184" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="AX184" s="2" t="n">
+        <v>0.003708854891052397</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -27949,6 +29059,12 @@
       <c r="AV185" s="3" t="n">
         <v>-0.002739726027397263</v>
       </c>
+      <c r="AW185" s="1" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AX185" s="2" t="n">
+        <v>0.005494505494505499</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -28097,6 +29213,12 @@
       <c r="AV186" s="2" t="n">
         <v>0.001054574215660453</v>
       </c>
+      <c r="AW186" s="1" t="n">
+        <v>0.007616</v>
+      </c>
+      <c r="AX186" s="2" t="n">
+        <v>0.002897023966289217</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -28245,6 +29367,12 @@
       <c r="AV187" s="2" t="n">
         <v>0.006615214994487204</v>
       </c>
+      <c r="AW187" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AX187" s="3" t="n">
+        <v>-0.003285870755750115</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -28393,6 +29521,12 @@
       <c r="AV188" s="2" t="n">
         <v>0.001423053466151669</v>
       </c>
+      <c r="AW188" s="1" t="n">
+        <v>0.04934</v>
+      </c>
+      <c r="AX188" s="2" t="n">
+        <v>0.001624035728786108</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -28541,6 +29675,12 @@
       <c r="AV189" s="2" t="n">
         <v>0.001953125000000002</v>
       </c>
+      <c r="AW189" s="1" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AX189" s="2" t="n">
+        <v>0.002339181286549666</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -28689,6 +29829,12 @@
       <c r="AV190" s="3" t="n">
         <v>-0.0003503854239663244</v>
       </c>
+      <c r="AW190" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="AX190" s="2" t="n">
+        <v>0.00297932001402039</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -28837,6 +29983,12 @@
       <c r="AV191" s="2" t="n">
         <v>0.001493528045137793</v>
       </c>
+      <c r="AW191" s="1" t="n">
+        <v>6.048</v>
+      </c>
+      <c r="AX191" s="2" t="n">
+        <v>0.002154101077050522</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -28985,6 +30137,12 @@
       <c r="AV192" s="3" t="n">
         <v>-0.001146460303812013</v>
       </c>
+      <c r="AW192" s="1" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AX192" s="2" t="n">
+        <v>0.001721664275466413</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -29133,6 +30291,12 @@
       <c r="AV193" s="2" t="n">
         <v>0.004716981132075388</v>
       </c>
+      <c r="AW193" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="AX193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -29281,6 +30445,12 @@
       <c r="AV194" s="2" t="n">
         <v>0.004659289458357613</v>
       </c>
+      <c r="AW194" s="1" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="AX194" s="2" t="n">
+        <v>0.001739130434782538</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -29429,6 +30599,12 @@
       <c r="AV195" s="2" t="n">
         <v>0.004042037186742154</v>
       </c>
+      <c r="AW195" s="1" t="n">
+        <v>0.0008688</v>
+      </c>
+      <c r="AX195" s="3" t="n">
+        <v>-0.0006901311249137504</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -29577,6 +30753,12 @@
       <c r="AV196" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW196" s="1" t="n">
+        <v>0.001014</v>
+      </c>
+      <c r="AX196" s="3" t="n">
+        <v>-0.001968503937007922</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -29725,6 +30907,12 @@
       <c r="AV197" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW197" s="1" t="n">
+        <v>0.0001617</v>
+      </c>
+      <c r="AX197" s="2" t="n">
+        <v>0.004347826086956458</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -29873,6 +31061,12 @@
       <c r="AV198" s="2" t="n">
         <v>0.006205470006894998</v>
       </c>
+      <c r="AW198" s="1" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="AX198" s="2" t="n">
+        <v>0.00114207400639559</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -30021,6 +31215,12 @@
       <c r="AV199" s="2" t="n">
         <v>0.004839685420447642</v>
       </c>
+      <c r="AW199" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="AX199" s="2" t="n">
+        <v>0.004214328717640013</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -30169,6 +31369,12 @@
       <c r="AV200" s="2" t="n">
         <v>0.001641162120204139</v>
       </c>
+      <c r="AW200" s="1" t="n">
+        <v>0.022555</v>
+      </c>
+      <c r="AX200" s="3" t="n">
+        <v>-0.001195642547161576</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -30317,6 +31523,12 @@
       <c r="AV201" s="2" t="n">
         <v>0.002715004391918703</v>
       </c>
+      <c r="AW201" s="1" t="n">
+        <v>0.12456</v>
+      </c>
+      <c r="AX201" s="3" t="n">
+        <v>-0.008043322449629554</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -30465,6 +31677,12 @@
       <c r="AV202" s="2" t="n">
         <v>0.006410256410256396</v>
       </c>
+      <c r="AW202" s="1" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="AX202" s="3" t="n">
+        <v>-0.000707714083510233</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -30613,6 +31831,12 @@
       <c r="AV203" s="2" t="n">
         <v>0.001485148514851596</v>
       </c>
+      <c r="AW203" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="AX203" s="2" t="n">
+        <v>0.001730103806228217</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -30761,6 +31985,12 @@
       <c r="AV204" s="2" t="n">
         <v>0.001546192500966307</v>
       </c>
+      <c r="AW204" s="1" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="AX204" s="2" t="n">
+        <v>0.002315708220764223</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -30909,6 +32139,12 @@
       <c r="AV205" s="2" t="n">
         <v>0.0002309468822170646</v>
       </c>
+      <c r="AW205" s="1" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="AX205" s="2" t="n">
+        <v>0.003694296929115656</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -31057,6 +32293,12 @@
       <c r="AV206" s="2" t="n">
         <v>0.00171306209850115</v>
       </c>
+      <c r="AW206" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="AX206" s="2" t="n">
+        <v>0.002992731936725123</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -31205,6 +32447,12 @@
       <c r="AV207" s="2" t="n">
         <v>0.001195600191296005</v>
       </c>
+      <c r="AW207" s="1" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="AX207" s="2" t="n">
+        <v>0.001194172438500094</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -31353,6 +32601,12 @@
       <c r="AV208" s="2" t="n">
         <v>0.002974580854515927</v>
       </c>
+      <c r="AW208" s="1" t="n">
+        <v>0.07414</v>
+      </c>
+      <c r="AX208" s="3" t="n">
+        <v>-0.0005392289026691611</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -31501,6 +32755,12 @@
       <c r="AV209" s="2" t="n">
         <v>0.002141327623126334</v>
       </c>
+      <c r="AW209" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="AX209" s="2" t="n">
+        <v>0.002136752136752132</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -31649,6 +32909,12 @@
       <c r="AV210" s="2" t="n">
         <v>0.002165674066052971</v>
       </c>
+      <c r="AW210" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="AX210" s="2" t="n">
+        <v>0.001620745542949878</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -31797,6 +33063,12 @@
       <c r="AV211" s="2" t="n">
         <v>0.00676818950930622</v>
       </c>
+      <c r="AW211" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="AX211" s="3" t="n">
+        <v>-0.002100840336134456</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -31945,6 +33217,12 @@
       <c r="AV212" s="2" t="n">
         <v>0.003770028275211951</v>
       </c>
+      <c r="AW212" s="1" t="n">
+        <v>0.002123</v>
+      </c>
+      <c r="AX212" s="3" t="n">
+        <v>-0.00328638497652585</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -32093,6 +33371,12 @@
       <c r="AV213" s="2" t="n">
         <v>0.003239740820734344</v>
       </c>
+      <c r="AW213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AX213" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -32241,6 +33525,12 @@
       <c r="AV214" s="2" t="n">
         <v>0.003140265177948323</v>
       </c>
+      <c r="AW214" s="1" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="AX214" s="2" t="n">
+        <v>0.003478260869565227</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -32389,6 +33679,12 @@
       <c r="AV215" s="2" t="n">
         <v>0.001455074572571785</v>
       </c>
+      <c r="AW215" s="1" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="AX215" s="2" t="n">
+        <v>0.003632401017072263</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -32537,6 +33833,12 @@
       <c r="AV216" s="2" t="n">
         <v>0.003169572107765323</v>
       </c>
+      <c r="AW216" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="AX216" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -32685,6 +33987,12 @@
       <c r="AV217" s="2" t="n">
         <v>0.001077586206896583</v>
       </c>
+      <c r="AW217" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AX217" s="2" t="n">
+        <v>0.001076426264800892</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -32833,6 +34141,12 @@
       <c r="AV218" s="3" t="n">
         <v>-0.0007577124300919646</v>
       </c>
+      <c r="AW218" s="1" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="AX218" s="3" t="n">
+        <v>-0.001769336318336268</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -32981,6 +34295,12 @@
       <c r="AV219" s="2" t="n">
         <v>0.001522997258605005</v>
       </c>
+      <c r="AW219" s="1" t="n">
+        <v>0.003296</v>
+      </c>
+      <c r="AX219" s="2" t="n">
+        <v>0.002433090024330827</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -33129,6 +34449,12 @@
       <c r="AV220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="AX220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -33277,6 +34603,12 @@
       <c r="AV221" s="2" t="n">
         <v>0.00155965687548751</v>
       </c>
+      <c r="AW221" s="1" t="n">
+        <v>0.03883</v>
+      </c>
+      <c r="AX221" s="2" t="n">
+        <v>0.00778614066960814</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -33425,6 +34757,12 @@
       <c r="AV222" s="2" t="n">
         <v>0.002350929685830284</v>
       </c>
+      <c r="AW222" s="1" t="n">
+        <v>0.04695</v>
+      </c>
+      <c r="AX222" s="2" t="n">
+        <v>0.001066098081023485</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -33573,6 +34911,12 @@
       <c r="AV223" s="2" t="n">
         <v>0.0009416195856874093</v>
       </c>
+      <c r="AW223" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="AX223" s="2" t="n">
+        <v>0.003762935089369686</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -33721,6 +35065,12 @@
       <c r="AV224" s="2" t="n">
         <v>0.01044256588761805</v>
       </c>
+      <c r="AW224" s="1" t="n">
+        <v>4.063</v>
+      </c>
+      <c r="AX224" s="3" t="n">
+        <v>-0.0002460629921260664</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -33869,6 +35219,12 @@
       <c r="AV225" s="2" t="n">
         <v>0.002267818574514036</v>
       </c>
+      <c r="AW225" s="1" t="n">
+        <v>0.0009300000000000001</v>
+      </c>
+      <c r="AX225" s="2" t="n">
+        <v>0.002047193190389075</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -34017,6 +35373,12 @@
       <c r="AV226" s="2" t="n">
         <v>0.00580568720379152</v>
       </c>
+      <c r="AW226" s="1" t="n">
+        <v>0.008463999999999999</v>
+      </c>
+      <c r="AX226" s="3" t="n">
+        <v>-0.002944987631052034</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -34165,6 +35527,12 @@
       <c r="AV227" s="2" t="n">
         <v>0.003416300634455693</v>
       </c>
+      <c r="AW227" s="1" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="AX227" s="2" t="n">
+        <v>0.002431906614786062</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -34313,6 +35681,12 @@
       <c r="AV228" s="2" t="n">
         <v>0.0008203445447088392</v>
       </c>
+      <c r="AW228" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="AX228" s="2" t="n">
+        <v>0.003551912568305961</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -34461,6 +35835,12 @@
       <c r="AV229" s="2" t="n">
         <v>0.006538461538461539</v>
       </c>
+      <c r="AW229" s="1" t="n">
+        <v>0.05216</v>
+      </c>
+      <c r="AX229" s="3" t="n">
+        <v>-0.003439052350019099</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -34609,6 +35989,12 @@
       <c r="AV230" s="2" t="n">
         <v>0.001170960187353531</v>
       </c>
+      <c r="AW230" s="1" t="n">
+        <v>0.001716</v>
+      </c>
+      <c r="AX230" s="2" t="n">
+        <v>0.003508771929824647</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -34757,6 +36143,12 @@
       <c r="AV231" s="2" t="n">
         <v>0.0004037956793862141</v>
       </c>
+      <c r="AW231" s="1" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="AX231" s="2" t="n">
+        <v>0.008879919273461209</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -34905,6 +36297,12 @@
       <c r="AV232" s="3" t="n">
         <v>-0.002732240437158517</v>
       </c>
+      <c r="AW232" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="AX232" s="2" t="n">
+        <v>0.0009132420091323829</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -35053,6 +36451,12 @@
       <c r="AV233" s="3" t="n">
         <v>-0.0001710863986312202</v>
       </c>
+      <c r="AW233" s="1" t="n">
+        <v>0.0005865</v>
+      </c>
+      <c r="AX233" s="2" t="n">
+        <v>0.003593429158110878</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -35201,6 +36605,12 @@
       <c r="AV234" s="2" t="n">
         <v>0.01249366096537743</v>
       </c>
+      <c r="AW234" s="1" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="AX234" s="3" t="n">
+        <v>-0.006283580730352518</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -35349,6 +36759,12 @@
       <c r="AV235" s="3" t="n">
         <v>-0.0007581501137224862</v>
       </c>
+      <c r="AW235" s="1" t="n">
+        <v>0.01329</v>
+      </c>
+      <c r="AX235" s="2" t="n">
+        <v>0.008345978755690363</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -35497,6 +36913,12 @@
       <c r="AV236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW236" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AX236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -35645,6 +37067,12 @@
       <c r="AV237" s="2" t="n">
         <v>0.002409638554216769</v>
       </c>
+      <c r="AW237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="AX237" s="2" t="n">
+        <v>0.002403846153846265</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -35793,6 +37221,12 @@
       <c r="AV238" s="3" t="n">
         <v>-0.003984063745019896</v>
       </c>
+      <c r="AW238" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AX238" s="2" t="n">
+        <v>0.003999999999999976</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -35941,6 +37375,12 @@
       <c r="AV239" s="2" t="n">
         <v>0.00332225913621272</v>
       </c>
+      <c r="AW239" s="1" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="AX239" s="2" t="n">
+        <v>0.003311258278145675</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -36089,6 +37529,12 @@
       <c r="AV240" s="2" t="n">
         <v>0.005589430894308941</v>
       </c>
+      <c r="AW240" s="1" t="n">
+        <v>0.0003957</v>
+      </c>
+      <c r="AX240" s="3" t="n">
+        <v>-0.0002526528549772674</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -36237,6 +37683,12 @@
       <c r="AV241" s="2" t="n">
         <v>0.002925045703839003</v>
       </c>
+      <c r="AW241" s="1" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="AX241" s="2" t="n">
+        <v>0.004010207801676959</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -36385,6 +37837,12 @@
       <c r="AV242" s="2" t="n">
         <v>0.002595380223202593</v>
       </c>
+      <c r="AW242" s="1" t="n">
+        <v>0.07763</v>
+      </c>
+      <c r="AX242" s="2" t="n">
+        <v>0.004789024074553575</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -36533,6 +37991,12 @@
       <c r="AV243" s="2" t="n">
         <v>0.005646817248459906</v>
       </c>
+      <c r="AW243" s="1" t="n">
+        <v>0.01965</v>
+      </c>
+      <c r="AX243" s="2" t="n">
+        <v>0.00306278713629408</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -36681,6 +38145,12 @@
       <c r="AV244" s="3" t="n">
         <v>-0.001034245001149239</v>
       </c>
+      <c r="AW244" s="1" t="n">
+        <v>0.08697000000000001</v>
+      </c>
+      <c r="AX244" s="2" t="n">
+        <v>0.0004601403428046963</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -36829,6 +38299,12 @@
       <c r="AV245" s="3" t="n">
         <v>-0.000633312222925989</v>
       </c>
+      <c r="AW245" s="1" t="n">
+        <v>1.4174</v>
+      </c>
+      <c r="AX245" s="3" t="n">
+        <v>-0.001971553302351721</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -36977,6 +38453,12 @@
       <c r="AV246" s="3" t="n">
         <v>-0.0005586592178770723</v>
       </c>
+      <c r="AW246" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="AX246" s="2" t="n">
+        <v>0.001676914477361586</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -37125,6 +38607,12 @@
       <c r="AV247" s="3" t="n">
         <v>-0.0001504890895410283</v>
       </c>
+      <c r="AW247" s="1" t="n">
+        <v>0.006664</v>
+      </c>
+      <c r="AX247" s="2" t="n">
+        <v>0.003010234798314276</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -37273,6 +38761,12 @@
       <c r="AV248" s="3" t="n">
         <v>-0.006454697585465004</v>
       </c>
+      <c r="AW248" s="1" t="n">
+        <v>0.004187</v>
+      </c>
+      <c r="AX248" s="2" t="n">
+        <v>0.007459095283926799</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -37421,6 +38915,12 @@
       <c r="AV249" s="3" t="n">
         <v>-0.000891265597147852</v>
       </c>
+      <c r="AW249" s="1" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="AX249" s="2" t="n">
+        <v>0.004460303300624446</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -37569,6 +39069,12 @@
       <c r="AV250" s="3" t="n">
         <v>-0.001151410477835301</v>
       </c>
+      <c r="AW250" s="1" t="n">
+        <v>0.03475</v>
+      </c>
+      <c r="AX250" s="2" t="n">
+        <v>0.00144092219020177</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -37717,6 +39223,12 @@
       <c r="AV251" s="3" t="n">
         <v>-0.001168224299065292</v>
       </c>
+      <c r="AW251" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AX251" s="2" t="n">
+        <v>0.0009356725146198448</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -37865,6 +39377,12 @@
       <c r="AV252" s="3" t="n">
         <v>-0.0008576329331045963</v>
       </c>
+      <c r="AW252" s="1" t="n">
+        <v>0.005799</v>
+      </c>
+      <c r="AX252" s="3" t="n">
+        <v>-0.004463519313304717</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -38013,6 +39531,12 @@
       <c r="AV253" s="3" t="n">
         <v>-0.001782531194296034</v>
       </c>
+      <c r="AW253" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="AX253" s="2" t="n">
+        <v>0.003571428571428632</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -38161,6 +39685,12 @@
       <c r="AV254" s="2" t="n">
         <v>0.001544401544401589</v>
       </c>
+      <c r="AW254" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="AX254" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -38309,6 +39839,12 @@
       <c r="AV255" s="2" t="n">
         <v>0.0004662004662004472</v>
       </c>
+      <c r="AW255" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="AX255" s="3" t="n">
+        <v>-0.005591798695246905</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -38457,6 +39993,12 @@
       <c r="AV256" s="2" t="n">
         <v>0.003301886792452859</v>
       </c>
+      <c r="AW256" s="1" t="n">
+        <v>0.02128</v>
+      </c>
+      <c r="AX256" s="2" t="n">
+        <v>0.0004701457451809869</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -38605,6 +40147,12 @@
       <c r="AV257" s="3" t="n">
         <v>-0.0007824726134584971</v>
       </c>
+      <c r="AW257" s="1" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="AX257" s="2" t="n">
+        <v>0.002740798747063454</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -38753,6 +40301,12 @@
       <c r="AV258" s="2" t="n">
         <v>0.01255670238643084</v>
       </c>
+      <c r="AW258" s="1" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="AX258" s="2" t="n">
+        <v>0.006622516556291527</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -38901,6 +40455,12 @@
       <c r="AV259" s="2" t="n">
         <v>0.0037160179933502</v>
       </c>
+      <c r="AW259" s="1" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="AX259" s="2" t="n">
+        <v>0.001169134840218326</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -39049,6 +40609,12 @@
       <c r="AV260" s="3" t="n">
         <v>-0.001992265322864215</v>
       </c>
+      <c r="AW260" s="1" t="n">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="AX260" s="2" t="n">
+        <v>0.006106153123532252</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -39197,6 +40763,12 @@
       <c r="AV261" s="2" t="n">
         <v>0.003791069924178652</v>
       </c>
+      <c r="AW261" s="1" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="AX261" s="2" t="n">
+        <v>0.004196391103650864</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -39345,6 +40917,12 @@
       <c r="AV262" s="2" t="n">
         <v>0.004187020237264406</v>
       </c>
+      <c r="AW262" s="1" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="AX262" s="3" t="n">
+        <v>-0.000694927032661494</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -39493,6 +41071,12 @@
       <c r="AV263" s="2" t="n">
         <v>0.001033057851239807</v>
       </c>
+      <c r="AW263" s="1" t="n">
+        <v>0.07761999999999999</v>
+      </c>
+      <c r="AX263" s="2" t="n">
+        <v>0.001289989680082417</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -39641,6 +41225,12 @@
       <c r="AV264" s="2" t="n">
         <v>0.007641365257259162</v>
       </c>
+      <c r="AW264" s="1" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="AX264" s="3" t="n">
+        <v>-0.00404448938321538</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -39789,6 +41379,12 @@
       <c r="AV265" s="3" t="n">
         <v>-0.0006497725795971145</v>
       </c>
+      <c r="AW265" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="AX265" s="3" t="n">
+        <v>-0.001300390117035058</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -39937,6 +41533,12 @@
       <c r="AV266" s="2" t="n">
         <v>0.006014032743067085</v>
       </c>
+      <c r="AW266" s="1" t="n">
+        <v>0.006049</v>
+      </c>
+      <c r="AX266" s="2" t="n">
+        <v>0.004483560278977104</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -40085,6 +41687,12 @@
       <c r="AV267" s="2" t="n">
         <v>0.002140754616002054</v>
       </c>
+      <c r="AW267" s="1" t="n">
+        <v>0.03752</v>
+      </c>
+      <c r="AX267" s="2" t="n">
+        <v>0.001869158878504689</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -40233,6 +41841,12 @@
       <c r="AV268" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW268" s="1" t="n">
+        <v>0.03056</v>
+      </c>
+      <c r="AX268" s="2" t="n">
+        <v>0.0003273322422258459</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -40381,6 +41995,12 @@
       <c r="AV269" s="2" t="n">
         <v>0.00599719838907364</v>
       </c>
+      <c r="AW269" s="1" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="AX269" s="2" t="n">
+        <v>0.003350593968930946</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -40529,6 +42149,12 @@
       <c r="AV270" s="3" t="n">
         <v>-0.002162162162162164</v>
       </c>
+      <c r="AW270" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="AX270" s="2" t="n">
+        <v>0.003250270855904661</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -40677,6 +42303,12 @@
       <c r="AV271" s="3" t="n">
         <v>-0.0003869969040247252</v>
       </c>
+      <c r="AW271" s="1" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AX271" s="2" t="n">
+        <v>0.0007742934572202012</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -40825,6 +42457,12 @@
       <c r="AV272" s="2" t="n">
         <v>0.001612036539495016</v>
       </c>
+      <c r="AW272" s="1" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="AX272" s="2" t="n">
+        <v>0.002145922746781028</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -40973,6 +42611,12 @@
       <c r="AV273" s="2" t="n">
         <v>0.002837326607818405</v>
       </c>
+      <c r="AW273" s="1" t="n">
+        <v>0.03183</v>
+      </c>
+      <c r="AX273" s="2" t="n">
+        <v>0.0006287331027978367</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -41121,6 +42765,12 @@
       <c r="AV274" s="2" t="n">
         <v>0.0005260389268806773</v>
       </c>
+      <c r="AW274" s="1" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="AX274" s="3" t="n">
+        <v>-0.002103049421661469</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -41269,6 +42919,12 @@
       <c r="AV275" s="2" t="n">
         <v>0.005325273459988419</v>
       </c>
+      <c r="AW275" s="1" t="n">
+        <v>0.06999</v>
+      </c>
+      <c r="AX275" s="2" t="n">
+        <v>0.002004294917680762</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -41417,6 +43073,12 @@
       <c r="AV276" s="2" t="n">
         <v>0.002239084463241692</v>
       </c>
+      <c r="AW276" s="1" t="n">
+        <v>0.08074000000000001</v>
+      </c>
+      <c r="AX276" s="2" t="n">
+        <v>0.002109966488767575</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -41565,6 +43227,12 @@
       <c r="AV277" s="2" t="n">
         <v>0.004913369537108849</v>
       </c>
+      <c r="AW277" s="1" t="n">
+        <v>0.003909</v>
+      </c>
+      <c r="AX277" s="2" t="n">
+        <v>0.00591868244981987</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -41713,6 +43381,12 @@
       <c r="AV278" s="2" t="n">
         <v>0.002570694087403601</v>
       </c>
+      <c r="AW278" s="1" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="AX278" s="3" t="n">
+        <v>-0.0006410256410257127</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -41861,6 +43535,12 @@
       <c r="AV279" s="2" t="n">
         <v>0.0009049773755655739</v>
       </c>
+      <c r="AW279" s="1" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="AX279" s="2" t="n">
+        <v>0.0009041591320071964</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -42009,6 +43689,12 @@
       <c r="AV280" s="2" t="n">
         <v>0.005232992773486217</v>
       </c>
+      <c r="AW280" s="1" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AX280" s="3" t="n">
+        <v>-0.001487357461576538</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -42157,6 +43843,12 @@
       <c r="AV281" s="2" t="n">
         <v>0.00475228703813724</v>
       </c>
+      <c r="AW281" s="1" t="n">
+        <v>0.08483</v>
+      </c>
+      <c r="AX281" s="2" t="n">
+        <v>0.003074376256355638</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -42305,6 +43997,12 @@
       <c r="AV282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW282" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AX282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -42453,6 +44151,12 @@
       <c r="AV283" s="2" t="n">
         <v>0.002615062761506169</v>
       </c>
+      <c r="AW283" s="1" t="n">
+        <v>0.07677</v>
+      </c>
+      <c r="AX283" s="2" t="n">
+        <v>0.001173708920187881</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -42601,6 +44305,12 @@
       <c r="AV284" s="3" t="n">
         <v>-0.003101736972704723</v>
       </c>
+      <c r="AW284" s="1" t="n">
+        <v>0.001614</v>
+      </c>
+      <c r="AX284" s="2" t="n">
+        <v>0.004355942750466747</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -42749,6 +44459,12 @@
       <c r="AV285" s="2" t="n">
         <v>0.00295566502463049</v>
       </c>
+      <c r="AW285" s="1" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="AX285" s="2" t="n">
+        <v>0.0009823182711198709</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -42897,6 +44613,12 @@
       <c r="AV286" s="2" t="n">
         <v>0.002604893478463136</v>
       </c>
+      <c r="AW286" s="1" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="AX286" s="2" t="n">
+        <v>0.0001855804027094019</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -43045,6 +44767,12 @@
       <c r="AV287" s="3" t="n">
         <v>-0.0005760368663594235</v>
       </c>
+      <c r="AW287" s="1" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="AX287" s="2" t="n">
+        <v>0.001729106628242004</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -43193,6 +44921,12 @@
       <c r="AV288" s="2" t="n">
         <v>0.005218525766470986</v>
       </c>
+      <c r="AW288" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="AX288" s="2" t="n">
+        <v>0.001946787800129819</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -43341,6 +45075,12 @@
       <c r="AV289" s="2" t="n">
         <v>0.01073232323232323</v>
       </c>
+      <c r="AW289" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="AX289" s="3" t="n">
+        <v>-0.001249219237976214</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -43489,6 +45229,12 @@
       <c r="AV290" s="2" t="n">
         <v>0.00220750551876375</v>
       </c>
+      <c r="AW290" s="1" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="AX290" s="2" t="n">
+        <v>0.00220264317180612</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -43637,6 +45383,12 @@
       <c r="AV291" s="2" t="n">
         <v>0.001574094895435201</v>
       </c>
+      <c r="AW291" s="1" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="AX291" s="2" t="n">
+        <v>0.0006735518634934148</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -43785,6 +45537,12 @@
       <c r="AV292" s="2" t="n">
         <v>0.003397508493771237</v>
       </c>
+      <c r="AW292" s="1" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="AX292" s="3" t="n">
+        <v>-0.005643340857787816</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -43933,6 +45691,12 @@
       <c r="AV293" s="2" t="n">
         <v>0.001374435499705354</v>
       </c>
+      <c r="AW293" s="1" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="AX293" s="3" t="n">
+        <v>-0.00411764705882343</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -44081,6 +45845,12 @@
       <c r="AV294" s="3" t="n">
         <v>-0.0006333122229258767</v>
       </c>
+      <c r="AW294" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="AX294" s="2" t="n">
+        <v>0.002851711026615964</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -44229,6 +45999,12 @@
       <c r="AV295" s="3" t="n">
         <v>-0.001688374336710123</v>
       </c>
+      <c r="AW295" s="1" t="n">
+        <v>0.0004152</v>
+      </c>
+      <c r="AX295" s="2" t="n">
+        <v>0.003140855279052988</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -44377,6 +46153,12 @@
       <c r="AV296" s="2" t="n">
         <v>0.0008011536612723004</v>
       </c>
+      <c r="AW296" s="1" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="AX296" s="2" t="n">
+        <v>0.000800512327889804</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -44525,6 +46307,12 @@
       <c r="AV297" s="3" t="n">
         <v>-0.001029866117404767</v>
       </c>
+      <c r="AW297" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="AX297" s="2" t="n">
+        <v>0.002061855670103009</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -44673,6 +46461,12 @@
       <c r="AV298" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW298" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="AX298" s="2" t="n">
+        <v>0.003128258602711102</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -44821,6 +46615,12 @@
       <c r="AV299" s="2" t="n">
         <v>0.0007325240686479763</v>
       </c>
+      <c r="AW299" s="1" t="n">
+        <v>0.09601</v>
+      </c>
+      <c r="AX299" s="2" t="n">
+        <v>0.00397364843668296</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -44969,6 +46769,12 @@
       <c r="AV300" s="2" t="n">
         <v>0.001619870410367292</v>
       </c>
+      <c r="AW300" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="AX300" s="2" t="n">
+        <v>0.0005390835579514605</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -45117,6 +46923,12 @@
       <c r="AV301" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW301" s="1" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AX301" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -45265,6 +47077,12 @@
       <c r="AV302" s="2" t="n">
         <v>0.01210490921318095</v>
       </c>
+      <c r="AW302" s="1" t="n">
+        <v>0.004473</v>
+      </c>
+      <c r="AX302" s="3" t="n">
+        <v>-0.009302325581395239</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -45413,6 +47231,12 @@
       <c r="AV303" s="2" t="n">
         <v>0.003275109170305733</v>
       </c>
+      <c r="AW303" s="1" t="n">
+        <v>0.009209999999999999</v>
+      </c>
+      <c r="AX303" s="2" t="n">
+        <v>0.002176278563656059</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -45561,6 +47385,12 @@
       <c r="AV304" s="2" t="n">
         <v>0.002969247083775235</v>
       </c>
+      <c r="AW304" s="1" t="n">
+        <v>4.727</v>
+      </c>
+      <c r="AX304" s="3" t="n">
+        <v>-0.000422922393740702</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -45709,6 +47539,12 @@
       <c r="AV305" s="2" t="n">
         <v>0.006527415143603061</v>
       </c>
+      <c r="AW305" s="1" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="AX305" s="2" t="n">
+        <v>0.007967389290346487</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -45857,6 +47693,12 @@
       <c r="AV306" s="3" t="n">
         <v>-0.0001705902422380779</v>
       </c>
+      <c r="AW306" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="AX306" s="2" t="n">
+        <v>0.001023716089404497</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -46005,6 +47847,12 @@
       <c r="AV307" s="2" t="n">
         <v>0.003430531732418465</v>
       </c>
+      <c r="AW307" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="AX307" s="2" t="n">
+        <v>0.0005698005698006653</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -46153,6 +48001,12 @@
       <c r="AV308" s="3" t="n">
         <v>-0.002423263327948345</v>
       </c>
+      <c r="AW308" s="1" t="n">
+        <v>0.04933</v>
+      </c>
+      <c r="AX308" s="3" t="n">
+        <v>-0.001417004048583008</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -46301,6 +48155,12 @@
       <c r="AV309" s="3" t="n">
         <v>-0.005261248185776512</v>
       </c>
+      <c r="AW309" s="1" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="AX309" s="2" t="n">
+        <v>0.002918110523436159</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -46449,6 +48309,12 @@
       <c r="AV310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW310" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AX310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -46597,6 +48463,12 @@
       <c r="AV311" s="3" t="n">
         <v>-0.002085650723025548</v>
       </c>
+      <c r="AW311" s="1" t="n">
+        <v>0.07198</v>
+      </c>
+      <c r="AX311" s="2" t="n">
+        <v>0.002926013654730415</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -46745,6 +48617,12 @@
       <c r="AV312" s="2" t="n">
         <v>0.004665629860031145</v>
       </c>
+      <c r="AW312" s="1" t="n">
+        <v>0.009058999999999999</v>
+      </c>
+      <c r="AX312" s="2" t="n">
+        <v>0.00165855816010608</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -46893,6 +48771,12 @@
       <c r="AV313" s="2" t="n">
         <v>0.002625533311453953</v>
       </c>
+      <c r="AW313" s="1" t="n">
+        <v>0.012208</v>
+      </c>
+      <c r="AX313" s="3" t="n">
+        <v>-0.0009819967266775662</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -47041,6 +48925,12 @@
       <c r="AV314" s="2" t="n">
         <v>0.01245480112494983</v>
       </c>
+      <c r="AW314" s="1" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="AX314" s="2" t="n">
+        <v>0.01428571428571425</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -47189,6 +49079,12 @@
       <c r="AV315" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW315" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AX315" s="2" t="n">
+        <v>0.001408450704225295</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -47337,6 +49233,12 @@
       <c r="AV316" s="2" t="n">
         <v>0.00267379679144398</v>
       </c>
+      <c r="AW316" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AX316" s="2" t="n">
+        <v>0.002285714285714246</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -47485,6 +49387,12 @@
       <c r="AV317" s="3" t="n">
         <v>-0.008695652173913108</v>
       </c>
+      <c r="AW317" s="1" t="n">
+        <v>1.15e-05</v>
+      </c>
+      <c r="AX317" s="2" t="n">
+        <v>0.008771929824561469</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -47633,6 +49541,12 @@
       <c r="AV318" s="3" t="n">
         <v>-0.0002257336343114771</v>
       </c>
+      <c r="AW318" s="1" t="n">
+        <v>0.053488</v>
+      </c>
+      <c r="AX318" s="2" t="n">
+        <v>0.006397230375555054</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -47781,6 +49695,12 @@
       <c r="AV319" s="2" t="n">
         <v>0.0005221932114882294</v>
       </c>
+      <c r="AW319" s="1" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="AX319" s="2" t="n">
+        <v>0.0002609603340293074</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -47929,6 +49849,12 @@
       <c r="AV320" s="2" t="n">
         <v>0.0005844535359438433</v>
       </c>
+      <c r="AW320" s="1" t="n">
+        <v>0.006861</v>
+      </c>
+      <c r="AX320" s="2" t="n">
+        <v>0.001898364485981307</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -48077,6 +50003,12 @@
       <c r="AV321" s="2" t="n">
         <v>0.003089143865842947</v>
       </c>
+      <c r="AW321" s="1" t="n">
+        <v>4.568</v>
+      </c>
+      <c r="AX321" s="2" t="n">
+        <v>0.004839419269687495</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -48225,6 +50157,12 @@
       <c r="AV322" s="2" t="n">
         <v>0.001030396702730552</v>
       </c>
+      <c r="AW322" s="1" t="n">
+        <v>1.949</v>
+      </c>
+      <c r="AX322" s="2" t="n">
+        <v>0.003088008234688628</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -48373,6 +50311,12 @@
       <c r="AV323" s="2" t="n">
         <v>0.0007014590347923396</v>
       </c>
+      <c r="AW323" s="1" t="n">
+        <v>0.007149</v>
+      </c>
+      <c r="AX323" s="2" t="n">
+        <v>0.002243095471751071</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -48521,6 +50465,12 @@
       <c r="AV324" s="2" t="n">
         <v>0.0005449591280653729</v>
       </c>
+      <c r="AW324" s="1" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="AX324" s="2" t="n">
+        <v>0.001633986928104508</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -48669,6 +50619,12 @@
       <c r="AV325" s="2" t="n">
         <v>0.004098360655737655</v>
       </c>
+      <c r="AW325" s="1" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="AX325" s="3" t="n">
+        <v>-0.0009603841536613588</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -48817,6 +50773,12 @@
       <c r="AV326" s="2" t="n">
         <v>0.001249305941143734</v>
       </c>
+      <c r="AW326" s="1" t="n">
+        <v>0.00723</v>
+      </c>
+      <c r="AX326" s="2" t="n">
+        <v>0.002356855677249483</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -48965,6 +50927,12 @@
       <c r="AV327" s="2" t="n">
         <v>0.006609049313675625</v>
       </c>
+      <c r="AW327" s="1" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="AX327" s="2" t="n">
+        <v>0.0005050505050504494</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -49113,6 +51081,12 @@
       <c r="AV328" s="2" t="n">
         <v>0.004021164021164049</v>
       </c>
+      <c r="AW328" s="1" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AX328" s="3" t="n">
+        <v>-0.005059021922428359</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -49261,6 +51235,12 @@
       <c r="AV329" s="3" t="n">
         <v>-0.002973977695167294</v>
       </c>
+      <c r="AW329" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="AX329" s="2" t="n">
+        <v>0.0007457121551080979</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -49409,6 +51389,12 @@
       <c r="AV330" s="2" t="n">
         <v>0.002643171806167354</v>
       </c>
+      <c r="AW330" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AX330" s="2" t="n">
+        <v>0.001757469244288275</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -49557,6 +51543,12 @@
       <c r="AV331" s="2" t="n">
         <v>0.001494768310911828</v>
       </c>
+      <c r="AW331" s="1" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="AX331" s="2" t="n">
+        <v>0.002487562189054821</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -49705,6 +51697,12 @@
       <c r="AV332" s="2" t="n">
         <v>0.001434205808533511</v>
       </c>
+      <c r="AW332" s="1" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AX332" s="2" t="n">
+        <v>0.002115678807408079</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -49853,6 +51851,12 @@
       <c r="AV333" s="2" t="n">
         <v>0.003266117580233002</v>
       </c>
+      <c r="AW333" s="1" t="n">
+        <v>0.07069</v>
+      </c>
+      <c r="AX333" s="2" t="n">
+        <v>0.0005661712668081864</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -50001,6 +52005,12 @@
       <c r="AV334" s="3" t="n">
         <v>-0.001463739188290073</v>
       </c>
+      <c r="AW334" s="1" t="n">
+        <v>0.15004</v>
+      </c>
+      <c r="AX334" s="3" t="n">
+        <v>-0.0002665245202557602</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -50149,6 +52159,12 @@
       <c r="AV335" s="3" t="n">
         <v>-0.00191815856777508</v>
       </c>
+      <c r="AW335" s="1" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="AX335" s="2" t="n">
+        <v>0.001281229980781587</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -50297,6 +52313,12 @@
       <c r="AV336" s="3" t="n">
         <v>-0.002858776443682107</v>
       </c>
+      <c r="AW336" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="AX336" s="3" t="n">
+        <v>-0.002293577981651442</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -50445,6 +52467,12 @@
       <c r="AV337" s="2" t="n">
         <v>0.003797468354430313</v>
       </c>
+      <c r="AW337" s="1" t="n">
+        <v>0.03968</v>
+      </c>
+      <c r="AX337" s="2" t="n">
+        <v>0.000756620428751633</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -50593,6 +52621,12 @@
       <c r="AV338" s="2" t="n">
         <v>0.001693320790216267</v>
       </c>
+      <c r="AW338" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="AX338" s="2" t="n">
+        <v>0.001126972201352353</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -50741,6 +52775,12 @@
       <c r="AV339" s="2" t="n">
         <v>0.001946282600233475</v>
       </c>
+      <c r="AW339" s="1" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="AX339" s="2" t="n">
+        <v>0.004079254079254115</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -50889,6 +52929,12 @@
       <c r="AV340" s="2" t="n">
         <v>0.0008659162059547807</v>
       </c>
+      <c r="AW340" s="1" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="AX340" s="2" t="n">
+        <v>0.003527219486223896</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -51037,6 +53083,12 @@
       <c r="AV341" s="2" t="n">
         <v>0.0009143155694880566</v>
       </c>
+      <c r="AW341" s="1" t="n">
+        <v>7.671</v>
+      </c>
+      <c r="AX341" s="2" t="n">
+        <v>0.00104397755448258</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -51185,6 +53237,12 @@
       <c r="AV342" s="2" t="n">
         <v>0.0006099420555046598</v>
       </c>
+      <c r="AW342" s="1" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AX342" s="3" t="n">
+        <v>-0.003047851264858278</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -51333,6 +53391,12 @@
       <c r="AV343" s="2" t="n">
         <v>0.003992015968063883</v>
       </c>
+      <c r="AW343" s="1" t="n">
+        <v>0.02014</v>
+      </c>
+      <c r="AX343" s="2" t="n">
+        <v>0.0009940357852884023</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -51481,6 +53545,12 @@
       <c r="AV344" s="3" t="n">
         <v>-0.001839080459770117</v>
       </c>
+      <c r="AW344" s="1" t="n">
+        <v>2.177</v>
+      </c>
+      <c r="AX344" s="2" t="n">
+        <v>0.002763703362505863</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -51629,6 +53699,12 @@
       <c r="AV345" s="2" t="n">
         <v>0.0007961783439489569</v>
       </c>
+      <c r="AW345" s="1" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="AX345" s="2" t="n">
+        <v>0.003182179793158317</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -51777,6 +53853,12 @@
       <c r="AV346" s="2" t="n">
         <v>0.002518891687657429</v>
       </c>
+      <c r="AW346" s="1" t="n">
+        <v>0.005181</v>
+      </c>
+      <c r="AX346" s="2" t="n">
+        <v>0.001352918438345586</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -51925,6 +54007,12 @@
       <c r="AV347" s="2" t="n">
         <v>0.002267573696145093</v>
       </c>
+      <c r="AW347" s="1" t="n">
+        <v>0.05757</v>
+      </c>
+      <c r="AX347" s="2" t="n">
+        <v>0.001914375217542742</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -52073,6 +54161,12 @@
       <c r="AV348" s="2" t="n">
         <v>0.001558846453624363</v>
       </c>
+      <c r="AW348" s="1" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AX348" s="2" t="n">
+        <v>0.00155642023346308</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -52221,6 +54315,12 @@
       <c r="AV349" s="3" t="n">
         <v>-0.0003851264177466253</v>
       </c>
+      <c r="AW349" s="1" t="n">
+        <v>5192.2</v>
+      </c>
+      <c r="AX349" s="2" t="n">
+        <v>0.0002119011384869207</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -52369,6 +54469,12 @@
       <c r="AV350" s="3" t="n">
         <v>-0.001792114695340553</v>
       </c>
+      <c r="AW350" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="AX350" s="2" t="n">
+        <v>0.001795332136445294</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -52517,6 +54623,12 @@
       <c r="AV351" s="2" t="n">
         <v>0.004389173372348314</v>
       </c>
+      <c r="AW351" s="1" t="n">
+        <v>0.001382</v>
+      </c>
+      <c r="AX351" s="2" t="n">
+        <v>0.00655498907501813</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -52665,6 +54777,12 @@
       <c r="AV352" s="3" t="n">
         <v>-0.01001878522229182</v>
       </c>
+      <c r="AW352" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AX352" s="2" t="n">
+        <v>0.001265022137887361</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -52813,6 +54931,12 @@
       <c r="AV353" s="2" t="n">
         <v>0.003983428935627845</v>
       </c>
+      <c r="AW353" s="1" t="n">
+        <v>6.312</v>
+      </c>
+      <c r="AX353" s="2" t="n">
+        <v>0.001745754642120317</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -52961,6 +55085,12 @@
       <c r="AV354" s="2" t="n">
         <v>0.0006920415224914654</v>
       </c>
+      <c r="AW354" s="1" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AX354" s="2" t="n">
+        <v>0.001383125864453705</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -53109,6 +55239,12 @@
       <c r="AV355" s="2" t="n">
         <v>0.001189060642092781</v>
       </c>
+      <c r="AW355" s="1" t="n">
+        <v>0.04216</v>
+      </c>
+      <c r="AX355" s="2" t="n">
+        <v>0.001425178147268515</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -53257,6 +55393,12 @@
       <c r="AV356" s="3" t="n">
         <v>-0.001613915538420152</v>
       </c>
+      <c r="AW356" s="1" t="n">
+        <v>0.11155</v>
+      </c>
+      <c r="AX356" s="2" t="n">
+        <v>0.001796138302649231</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -53405,6 +55547,12 @@
       <c r="AV357" s="2" t="n">
         <v>0.005781460782424291</v>
       </c>
+      <c r="AW357" s="1" t="n">
+        <v>0.005231</v>
+      </c>
+      <c r="AX357" s="2" t="n">
+        <v>0.002299291051925795</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -53553,6 +55701,12 @@
       <c r="AV358" s="3" t="n">
         <v>-0.006017505470459463</v>
       </c>
+      <c r="AW358" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="AX358" s="2" t="n">
+        <v>0.00660429279031374</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -53701,6 +55855,12 @@
       <c r="AV359" s="3" t="n">
         <v>-0.0134976525821596</v>
       </c>
+      <c r="AW359" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AX359" s="3" t="n">
+        <v>-0.01249256395002969</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -53849,6 +56009,12 @@
       <c r="AV360" s="3" t="n">
         <v>-0.0004769285799451338</v>
       </c>
+      <c r="AW360" s="1" t="n">
+        <v>0.08401</v>
+      </c>
+      <c r="AX360" s="2" t="n">
+        <v>0.002147202672074432</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -53997,6 +56163,12 @@
       <c r="AV361" s="2" t="n">
         <v>0.002587322121604146</v>
       </c>
+      <c r="AW361" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="AX361" s="3" t="n">
+        <v>-0.005161290322580659</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -54145,6 +56317,12 @@
       <c r="AV362" s="2" t="n">
         <v>0.004853247053385825</v>
       </c>
+      <c r="AW362" s="1" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="AX362" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -54293,6 +56471,12 @@
       <c r="AV363" s="2" t="n">
         <v>0.001899592944369096</v>
       </c>
+      <c r="AW363" s="1" t="n">
+        <v>3.683</v>
+      </c>
+      <c r="AX363" s="3" t="n">
+        <v>-0.002437703141928586</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -54441,6 +56625,12 @@
       <c r="AV364" s="2" t="n">
         <v>0.0008960573476702144</v>
       </c>
+      <c r="AW364" s="1" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="AX364" s="2" t="n">
+        <v>0.002685765443151344</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -54589,6 +56779,12 @@
       <c r="AV365" s="2" t="n">
         <v>0.001808318264014393</v>
       </c>
+      <c r="AW365" s="1" t="n">
+        <v>0.05553</v>
+      </c>
+      <c r="AX365" s="2" t="n">
+        <v>0.002346570397112006</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -54737,6 +56933,12 @@
       <c r="AV366" s="3" t="n">
         <v>-0.007943512797881712</v>
       </c>
+      <c r="AW366" s="1" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="AX366" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -54885,6 +57087,12 @@
       <c r="AV367" s="2" t="n">
         <v>0.004552352048558533</v>
       </c>
+      <c r="AW367" s="1" t="n">
+        <v>0.001326</v>
+      </c>
+      <c r="AX367" s="2" t="n">
+        <v>0.001510574018126761</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -55033,6 +57241,12 @@
       <c r="AV368" s="3" t="n">
         <v>-0.000694444444444368</v>
       </c>
+      <c r="AW368" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AX368" s="2" t="n">
+        <v>0.005211952744961784</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -55181,6 +57395,12 @@
       <c r="AV369" s="2" t="n">
         <v>0.005434782608695619</v>
       </c>
+      <c r="AW369" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="AX369" s="3" t="n">
+        <v>-0.005405405405405373</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -55329,6 +57549,12 @@
       <c r="AV370" s="2" t="n">
         <v>0.004597220771079259</v>
       </c>
+      <c r="AW370" s="1" t="n">
+        <v>0.19372</v>
+      </c>
+      <c r="AX370" s="2" t="n">
+        <v>0.007384295371814897</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -55477,6 +57703,12 @@
       <c r="AV371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AX371" s="3" t="n">
+        <v>-0.012987012987013</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -55625,6 +57857,12 @@
       <c r="AV372" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW372" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AX372" s="3" t="n">
+        <v>-0.0009496676163343102</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -55773,6 +58011,12 @@
       <c r="AV373" s="3" t="n">
         <v>-0.001062054316492196</v>
       </c>
+      <c r="AW373" s="1" t="n">
+        <v>0.06587999999999999</v>
+      </c>
+      <c r="AX373" s="2" t="n">
+        <v>0.0006075334143377639</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -55921,6 +58165,12 @@
       <c r="AV374" s="3" t="n">
         <v>-0.0001308386759125037</v>
       </c>
+      <c r="AW374" s="1" t="n">
+        <v>0.007641</v>
+      </c>
+      <c r="AX374" s="3" t="n">
+        <v>-0.0001308557969118206</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -56069,6 +58319,12 @@
       <c r="AV375" s="2" t="n">
         <v>0.001861042183622796</v>
       </c>
+      <c r="AW375" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="AX375" s="2" t="n">
+        <v>0.001238390092879292</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -56217,6 +58473,12 @@
       <c r="AV376" s="2" t="n">
         <v>0.001165840862722267</v>
       </c>
+      <c r="AW376" s="1" t="n">
+        <v>0.003447</v>
+      </c>
+      <c r="AX376" s="2" t="n">
+        <v>0.003493449781659347</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -56365,6 +58627,12 @@
       <c r="AV377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW377" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AX377" s="2" t="n">
+        <v>0.006024096385542133</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -56513,6 +58781,12 @@
       <c r="AV378" s="3" t="n">
         <v>-0.002683363148479473</v>
       </c>
+      <c r="AW378" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="AX378" s="3" t="n">
+        <v>-0.0008968609865470487</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -56661,6 +58935,12 @@
       <c r="AV379" s="2" t="n">
         <v>0.005078485687904084</v>
       </c>
+      <c r="AW379" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="AX379" s="3" t="n">
+        <v>-0.002756086357372578</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -56809,6 +59089,12 @@
       <c r="AV380" s="2" t="n">
         <v>0.001061007957559823</v>
       </c>
+      <c r="AW380" s="1" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="AX380" s="2" t="n">
+        <v>0.000529941706412273</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -56957,6 +59243,12 @@
       <c r="AV381" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW381" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="AX381" s="2" t="n">
+        <v>0.001658374792703198</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -57105,6 +59397,12 @@
       <c r="AV382" s="2" t="n">
         <v>0.001372212692967473</v>
       </c>
+      <c r="AW382" s="1" t="n">
+        <v>0.02924</v>
+      </c>
+      <c r="AX382" s="2" t="n">
+        <v>0.00171291538198006</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -57253,6 +59551,12 @@
       <c r="AV383" s="3" t="n">
         <v>-0.001369237790962948</v>
       </c>
+      <c r="AW383" s="1" t="n">
+        <v>0.006561</v>
+      </c>
+      <c r="AX383" s="3" t="n">
+        <v>-0.0004570383912249235</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -57401,6 +59705,12 @@
       <c r="AV384" s="3" t="n">
         <v>-0.001892147587511749</v>
       </c>
+      <c r="AW384" s="1" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="AX384" s="3" t="n">
+        <v>-0.003791469194312806</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -57549,6 +59859,12 @@
       <c r="AV385" s="3" t="n">
         <v>-0.0003943217665615142</v>
       </c>
+      <c r="AW385" s="1" t="n">
+        <v>2543</v>
+      </c>
+      <c r="AX385" s="2" t="n">
+        <v>0.003155818540433925</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -57697,6 +60013,12 @@
       <c r="AV386" s="2" t="n">
         <v>0.005012531328320806</v>
       </c>
+      <c r="AW386" s="1" t="n">
+        <v>0.2003</v>
+      </c>
+      <c r="AX386" s="3" t="n">
+        <v>-0.0009975062344139936</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -57845,6 +60167,12 @@
       <c r="AV387" s="2" t="n">
         <v>0.002125398512221037</v>
       </c>
+      <c r="AW387" s="1" t="n">
+        <v>0.08482000000000001</v>
+      </c>
+      <c r="AX387" s="3" t="n">
+        <v>-0.0005891363261458052</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -57993,6 +60321,12 @@
       <c r="AV388" s="3" t="n">
         <v>-0.004473837774751913</v>
       </c>
+      <c r="AW388" s="1" t="n">
+        <v>0.005138</v>
+      </c>
+      <c r="AX388" s="2" t="n">
+        <v>0.00390777647518563</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -58141,6 +60475,12 @@
       <c r="AV389" s="3" t="n">
         <v>-0.008714596949891166</v>
       </c>
+      <c r="AW389" s="1" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="AX389" s="3" t="n">
+        <v>-0.0008791208791208433</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -58289,6 +60629,12 @@
       <c r="AV390" s="2" t="n">
         <v>0.008357628765792191</v>
       </c>
+      <c r="AW390" s="1" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="AX390" s="3" t="n">
+        <v>-0.002505782575173629</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -58437,6 +60783,12 @@
       <c r="AV391" s="2" t="n">
         <v>0.001805646749835983</v>
       </c>
+      <c r="AW391" s="1" t="n">
+        <v>0.0006121</v>
+      </c>
+      <c r="AX391" s="2" t="n">
+        <v>0.002949369162706759</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -58585,6 +60937,12 @@
       <c r="AV392" s="3" t="n">
         <v>-0.001701548409052286</v>
       </c>
+      <c r="AW392" s="1" t="n">
+        <v>0.05879</v>
+      </c>
+      <c r="AX392" s="2" t="n">
+        <v>0.002045338333049293</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -58733,6 +61091,12 @@
       <c r="AV393" s="2" t="n">
         <v>0.001845699520118127</v>
       </c>
+      <c r="AW393" s="1" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="AX393" s="2" t="n">
+        <v>0.001105379513633097</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -58881,6 +61245,12 @@
       <c r="AV394" s="2" t="n">
         <v>0.008237716975580999</v>
       </c>
+      <c r="AW394" s="1" t="n">
+        <v>0.006883</v>
+      </c>
+      <c r="AX394" s="2" t="n">
+        <v>0.004231105923548349</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -59029,6 +61399,12 @@
       <c r="AV395" s="2" t="n">
         <v>0.002610966057441207</v>
       </c>
+      <c r="AW395" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="AX395" s="2" t="n">
+        <v>0.001736111111111161</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -59177,6 +61553,12 @@
       <c r="AV396" s="2" t="n">
         <v>0.002257336343115144</v>
       </c>
+      <c r="AW396" s="1" t="n">
+        <v>0.03113</v>
+      </c>
+      <c r="AX396" s="2" t="n">
+        <v>0.001608751608751655</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -59325,6 +61707,12 @@
       <c r="AV397" s="2" t="n">
         <v>0.001974983541803783</v>
       </c>
+      <c r="AW397" s="1" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="AX397" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -59473,6 +61861,12 @@
       <c r="AV398" s="3" t="n">
         <v>-0.0006086427267193645</v>
       </c>
+      <c r="AW398" s="1" t="n">
+        <v>0.003291</v>
+      </c>
+      <c r="AX398" s="2" t="n">
+        <v>0.002131546894031687</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -59621,6 +62015,12 @@
       <c r="AV399" s="2" t="n">
         <v>0.002708559046587105</v>
       </c>
+      <c r="AW399" s="1" t="n">
+        <v>0.01866</v>
+      </c>
+      <c r="AX399" s="2" t="n">
+        <v>0.008103727714748829</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -59769,6 +62169,12 @@
       <c r="AV400" s="2" t="n">
         <v>0.001445086705202379</v>
       </c>
+      <c r="AW400" s="1" t="n">
+        <v>0.006918</v>
+      </c>
+      <c r="AX400" s="3" t="n">
+        <v>-0.001731601731601836</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -59917,6 +62323,12 @@
       <c r="AV401" s="2" t="n">
         <v>0.0004255319148936735</v>
       </c>
+      <c r="AW401" s="1" t="n">
+        <v>0.007078</v>
+      </c>
+      <c r="AX401" s="2" t="n">
+        <v>0.003544590954203863</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -60065,6 +62477,12 @@
       <c r="AV402" s="3" t="n">
         <v>-0.0002505010020040413</v>
       </c>
+      <c r="AW402" s="1" t="n">
+        <v>0.008071</v>
+      </c>
+      <c r="AX402" s="2" t="n">
+        <v>0.01115008769731904</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -60213,6 +62631,12 @@
       <c r="AV403" s="2" t="n">
         <v>0.004755996691480584</v>
       </c>
+      <c r="AW403" s="1" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="AX403" s="3" t="n">
+        <v>-0.002675447622967651</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -60361,6 +62785,12 @@
       <c r="AV404" s="2" t="n">
         <v>0.003277372750986492</v>
       </c>
+      <c r="AW404" s="1" t="n">
+        <v>0.14985</v>
+      </c>
+      <c r="AX404" s="3" t="n">
+        <v>-0.0009999999999998899</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -60509,6 +62939,12 @@
       <c r="AV405" s="2" t="n">
         <v>0.007573964497041275</v>
       </c>
+      <c r="AW405" s="1" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="AX405" s="2" t="n">
+        <v>0.008456659619450461</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -60657,6 +63093,12 @@
       <c r="AV406" s="2" t="n">
         <v>0.002711157455683052</v>
       </c>
+      <c r="AW406" s="1" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="AX406" s="2" t="n">
+        <v>0.0002079866888518906</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -60805,6 +63247,12 @@
       <c r="AV407" s="3" t="n">
         <v>-0.002218189151038461</v>
       </c>
+      <c r="AW407" s="1" t="n">
+        <v>0.0004957</v>
+      </c>
+      <c r="AX407" s="2" t="n">
+        <v>0.001818916734033888</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -60953,6 +63401,12 @@
       <c r="AV408" s="3" t="n">
         <v>-0.001631321370310026</v>
       </c>
+      <c r="AW408" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AX408" s="2" t="n">
+        <v>0.00490196078431381</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -61101,6 +63555,12 @@
       <c r="AV409" s="2" t="n">
         <v>0.00316856780735108</v>
       </c>
+      <c r="AW409" s="1" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AX409" s="2" t="n">
+        <v>0.0006317119393557596</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -61249,6 +63709,12 @@
       <c r="AV410" s="3" t="n">
         <v>-0.01689347724073201</v>
       </c>
+      <c r="AW410" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="AX410" s="2" t="n">
+        <v>0.003579952267303039</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -61397,6 +63863,12 @@
       <c r="AV411" s="3" t="n">
         <v>-0.0006686726847208019</v>
       </c>
+      <c r="AW411" s="1" t="n">
+        <v>0.02987</v>
+      </c>
+      <c r="AX411" s="3" t="n">
+        <v>-0.0006691201070591899</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -61545,6 +64017,12 @@
       <c r="AV412" s="2" t="n">
         <v>0.001308044473512084</v>
       </c>
+      <c r="AW412" s="1" t="n">
+        <v>0.004603</v>
+      </c>
+      <c r="AX412" s="2" t="n">
+        <v>0.002177226213803714</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -61693,6 +64171,12 @@
       <c r="AV413" s="2" t="n">
         <v>0.002348336594911896</v>
       </c>
+      <c r="AW413" s="1" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="AX413" s="2" t="n">
+        <v>0.0007809449433814057</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -61841,6 +64325,12 @@
       <c r="AV414" s="3" t="n">
         <v>-0.002314814814814902</v>
       </c>
+      <c r="AW414" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AX414" s="2" t="n">
+        <v>0.0007733952049498159</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -61989,6 +64479,12 @@
       <c r="AV415" s="2" t="n">
         <v>0.0003667033370004892</v>
       </c>
+      <c r="AW415" s="1" t="n">
+        <v>2.736</v>
+      </c>
+      <c r="AX415" s="2" t="n">
+        <v>0.002932551319648096</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -62137,6 +64633,12 @@
       <c r="AV416" s="2" t="n">
         <v>0.008901166359730065</v>
       </c>
+      <c r="AW416" s="1" t="n">
+        <v>0.03266</v>
+      </c>
+      <c r="AX416" s="3" t="n">
+        <v>-0.006388804380894488</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -62285,6 +64787,12 @@
       <c r="AV417" s="2" t="n">
         <v>0.001253446979192816</v>
       </c>
+      <c r="AW417" s="1" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="AX417" s="2" t="n">
+        <v>0.0007511266900349351</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -62433,6 +64941,12 @@
       <c r="AV418" s="3" t="n">
         <v>-0.0006538511834705701</v>
       </c>
+      <c r="AW418" s="1" t="n">
+        <v>0.07655000000000001</v>
+      </c>
+      <c r="AX418" s="2" t="n">
+        <v>0.001701125359853508</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -62581,6 +65095,12 @@
       <c r="AV419" s="2" t="n">
         <v>0.001508295625942754</v>
       </c>
+      <c r="AW419" s="1" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="AX419" s="2" t="n">
+        <v>0.001506024096385481</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -62729,6 +65249,12 @@
       <c r="AV420" s="2" t="n">
         <v>0.004514672686230221</v>
       </c>
+      <c r="AW420" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="AX420" s="2" t="n">
+        <v>0.00112359550561801</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -62877,6 +65403,12 @@
       <c r="AV421" s="2" t="n">
         <v>0.004196391103650864</v>
       </c>
+      <c r="AW421" s="1" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="AX421" s="2" t="n">
+        <v>0.001671541997492619</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -63025,6 +65557,12 @@
       <c r="AV422" s="2" t="n">
         <v>0.007194244604316629</v>
       </c>
+      <c r="AW422" s="1" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="AX422" s="2" t="n">
+        <v>0.00357142857142855</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -63173,6 +65711,12 @@
       <c r="AV423" s="2" t="n">
         <v>0.0006548788474131564</v>
       </c>
+      <c r="AW423" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="AX423" s="2" t="n">
+        <v>0.001308900523560247</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -63321,6 +65865,12 @@
       <c r="AV424" s="2" t="n">
         <v>0.002413127413127472</v>
       </c>
+      <c r="AW424" s="1" t="n">
+        <v>0.0002083</v>
+      </c>
+      <c r="AX424" s="2" t="n">
+        <v>0.002888781896966719</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -63469,6 +66019,12 @@
       <c r="AV425" s="2" t="n">
         <v>0.002401921537229697</v>
       </c>
+      <c r="AW425" s="1" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="AX425" s="2" t="n">
+        <v>0.0007987220447283465</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -63617,6 +66173,12 @@
       <c r="AV426" s="2" t="n">
         <v>0.001412429378531075</v>
       </c>
+      <c r="AW426" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="AX426" s="2" t="n">
+        <v>0.002820874471086039</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -63765,6 +66327,12 @@
       <c r="AV427" s="2" t="n">
         <v>0.0005130836326320981</v>
       </c>
+      <c r="AW427" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AX427" s="2" t="n">
+        <v>0.0005128205128204919</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -63913,6 +66481,12 @@
       <c r="AV428" s="2" t="n">
         <v>0.0004491690372810637</v>
       </c>
+      <c r="AW428" s="1" t="n">
+        <v>0.06704</v>
+      </c>
+      <c r="AX428" s="2" t="n">
+        <v>0.003292427416941005</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -64061,6 +66635,12 @@
       <c r="AV429" s="2" t="n">
         <v>0.0007518796992480374</v>
       </c>
+      <c r="AW429" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AX429" s="3" t="n">
+        <v>-0.0007513148009014951</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -64209,6 +66789,12 @@
       <c r="AV430" s="2" t="n">
         <v>0.003550942365473991</v>
       </c>
+      <c r="AW430" s="1" t="n">
+        <v>0.011043</v>
+      </c>
+      <c r="AX430" s="2" t="n">
+        <v>0.001905280348394138</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -64357,6 +66943,12 @@
       <c r="AV431" s="3" t="n">
         <v>-0.004194756554307153</v>
       </c>
+      <c r="AW431" s="1" t="n">
+        <v>0.006645</v>
+      </c>
+      <c r="AX431" s="3" t="n">
+        <v>-0.0003008876184745397</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -64505,6 +67097,12 @@
       <c r="AV432" s="2" t="n">
         <v>0.001125492402926308</v>
       </c>
+      <c r="AW432" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="AX432" s="2" t="n">
+        <v>0.0005621135469364339</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -64653,6 +67251,12 @@
       <c r="AV433" s="2" t="n">
         <v>0.005032350826743239</v>
       </c>
+      <c r="AW433" s="1" t="n">
+        <v>0.001402</v>
+      </c>
+      <c r="AX433" s="2" t="n">
+        <v>0.002861230329041558</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -64801,6 +67405,12 @@
       <c r="AV434" s="2" t="n">
         <v>0.002444987775061051</v>
       </c>
+      <c r="AW434" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="AX434" s="3" t="n">
+        <v>-0.00243902439024383</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -64949,6 +67559,12 @@
       <c r="AV435" s="2" t="n">
         <v>0.00141698811304405</v>
       </c>
+      <c r="AW435" s="1" t="n">
+        <v>0.12768</v>
+      </c>
+      <c r="AX435" s="2" t="n">
+        <v>0.003694678091345006</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -65097,6 +67713,12 @@
       <c r="AV436" s="2" t="n">
         <v>0.002433090024330845</v>
       </c>
+      <c r="AW436" s="1" t="n">
+        <v>0.07863000000000001</v>
+      </c>
+      <c r="AX436" s="2" t="n">
+        <v>0.004471129279509493</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -65245,6 +67867,12 @@
       <c r="AV437" s="2" t="n">
         <v>0.003914813654870119</v>
       </c>
+      <c r="AW437" s="1" t="n">
+        <v>0.6435999999999999</v>
+      </c>
+      <c r="AX437" s="2" t="n">
+        <v>0.00389954765247223</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -65393,6 +68021,12 @@
       <c r="AV438" s="2" t="n">
         <v>0.04363376251788282</v>
       </c>
+      <c r="AW438" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AX438" s="2" t="n">
+        <v>0.005254740689970164</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -65541,6 +68175,12 @@
       <c r="AV439" s="3" t="n">
         <v>-0.001280956447480882</v>
       </c>
+      <c r="AW439" s="1" t="n">
+        <v>0.07058</v>
+      </c>
+      <c r="AX439" s="2" t="n">
+        <v>0.005842952828844344</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -65689,6 +68329,12 @@
       <c r="AV440" s="2" t="n">
         <v>0.0006583278472680268</v>
       </c>
+      <c r="AW440" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AX440" s="2" t="n">
+        <v>0.001973684210526292</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -65837,6 +68483,12 @@
       <c r="AV441" s="2" t="n">
         <v>0.0002091831398389568</v>
       </c>
+      <c r="AW441" s="1" t="n">
+        <v>0.009558000000000001</v>
+      </c>
+      <c r="AX441" s="3" t="n">
+        <v>-0.0005228484785109063</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -65985,6 +68637,12 @@
       <c r="AV442" s="3" t="n">
         <v>-0.0009216589861750137</v>
       </c>
+      <c r="AW442" s="1" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="AX442" s="2" t="n">
+        <v>0.006457564575645659</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -66133,6 +68791,12 @@
       <c r="AV443" s="3" t="n">
         <v>-0.0009144947416551982</v>
       </c>
+      <c r="AW443" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="AX443" s="2" t="n">
+        <v>0.001372997711670425</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -66281,6 +68945,12 @@
       <c r="AV444" s="3" t="n">
         <v>-0.002363445378151176</v>
       </c>
+      <c r="AW444" s="1" t="n">
+        <v>0.0003822</v>
+      </c>
+      <c r="AX444" s="2" t="n">
+        <v>0.006054224795998951</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -66429,6 +69099,12 @@
       <c r="AV445" s="3" t="n">
         <v>-0.0002787844995817152</v>
       </c>
+      <c r="AW445" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="AX445" s="3" t="n">
+        <v>-0.003067484662576852</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -66577,6 +69253,12 @@
       <c r="AV446" s="2" t="n">
         <v>0.003850509626273987</v>
       </c>
+      <c r="AW446" s="1" t="n">
+        <v>0.08835</v>
+      </c>
+      <c r="AX446" s="3" t="n">
+        <v>-0.003271660649819479</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -66725,6 +69407,12 @@
       <c r="AV447" s="2" t="n">
         <v>0.002144607843137291</v>
       </c>
+      <c r="AW447" s="1" t="n">
+        <v>3.277</v>
+      </c>
+      <c r="AX447" s="2" t="n">
+        <v>0.001834301436869528</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -66873,6 +69561,12 @@
       <c r="AV448" s="3" t="n">
         <v>-0.001247466084515993</v>
       </c>
+      <c r="AW448" s="1" t="n">
+        <v>0.06411</v>
+      </c>
+      <c r="AX448" s="2" t="n">
+        <v>0.0009367681498829742</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -67021,6 +69715,12 @@
       <c r="AV449" s="2" t="n">
         <v>0.001214083367057962</v>
       </c>
+      <c r="AW449" s="1" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="AX449" s="2" t="n">
+        <v>0.0002021018593370836</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -67169,6 +69869,12 @@
       <c r="AV450" s="2" t="n">
         <v>0.0005282620179608872</v>
       </c>
+      <c r="AW450" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="AX450" s="3" t="n">
+        <v>-0.008711721224920723</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -67317,6 +70023,12 @@
       <c r="AV451" s="2" t="n">
         <v>0.003629764065335763</v>
       </c>
+      <c r="AW451" s="1" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="AX451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -67465,6 +70177,12 @@
       <c r="AV452" s="2" t="n">
         <v>0.02006625650733564</v>
       </c>
+      <c r="AW452" s="1" t="n">
+        <v>0.10659</v>
+      </c>
+      <c r="AX452" s="3" t="n">
+        <v>-0.01094924375985896</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -67613,6 +70331,12 @@
       <c r="AV453" s="2" t="n">
         <v>0.002489110143123732</v>
       </c>
+      <c r="AW453" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="AX453" s="3" t="n">
+        <v>-0.00310366232153929</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -67761,6 +70485,12 @@
       <c r="AV454" s="3" t="n">
         <v>-0.006956521739130441</v>
       </c>
+      <c r="AW454" s="1" t="n">
+        <v>2.864</v>
+      </c>
+      <c r="AX454" s="2" t="n">
+        <v>0.003152364273204868</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -67909,6 +70639,12 @@
       <c r="AV455" s="2" t="n">
         <v>0.002232142857142859</v>
       </c>
+      <c r="AW455" s="1" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX455" s="2" t="n">
+        <v>0.001113585746102451</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -68057,6 +70793,12 @@
       <c r="AV456" s="3" t="n">
         <v>-0.001694340901389323</v>
       </c>
+      <c r="AW456" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="AX456" s="2" t="n">
+        <v>0.002036659877800334</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -68205,6 +70947,12 @@
       <c r="AV457" s="2" t="n">
         <v>0.002022244691607778</v>
       </c>
+      <c r="AW457" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="AX457" s="2" t="n">
+        <v>0.001009081735620544</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -68353,6 +71101,12 @@
       <c r="AV458" s="2" t="n">
         <v>0.01060462171573289</v>
       </c>
+      <c r="AW458" s="1" t="n">
+        <v>0.06399000000000001</v>
+      </c>
+      <c r="AX458" s="2" t="n">
+        <v>0.002192638997650763</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -68501,6 +71255,12 @@
       <c r="AV459" s="2" t="n">
         <v>0.001395673412421436</v>
       </c>
+      <c r="AW459" s="1" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="AX459" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -68649,6 +71409,12 @@
       <c r="AV460" s="3" t="n">
         <v>-0.001122194513715535</v>
       </c>
+      <c r="AW460" s="1" t="n">
+        <v>0.016038</v>
+      </c>
+      <c r="AX460" s="2" t="n">
+        <v>0.000998626888028876</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -68797,6 +71563,12 @@
       <c r="AV461" s="2" t="n">
         <v>0.001807228915662577</v>
       </c>
+      <c r="AW461" s="1" t="n">
+        <v>0.01663</v>
+      </c>
+      <c r="AX461" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -68945,6 +71717,12 @@
       <c r="AV462" s="2" t="n">
         <v>0.002387774594078377</v>
       </c>
+      <c r="AW462" s="1" t="n">
+        <v>0.0002097</v>
+      </c>
+      <c r="AX462" s="3" t="n">
+        <v>-0.000952834683182491</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -69093,6 +71871,12 @@
       <c r="AV463" s="3" t="n">
         <v>-0.001013171225937213</v>
       </c>
+      <c r="AW463" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AX463" s="2" t="n">
+        <v>0.004056795131845958</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -69241,6 +72025,12 @@
       <c r="AV464" s="3" t="n">
         <v>-0.003026863412788506</v>
       </c>
+      <c r="AW464" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="AX464" s="2" t="n">
+        <v>0.001897533206831174</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -69389,6 +72179,12 @@
       <c r="AV465" s="3" t="n">
         <v>-0.003313452617627548</v>
       </c>
+      <c r="AW465" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="AX465" s="2" t="n">
+        <v>0.004654255319148978</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -69537,6 +72333,12 @@
       <c r="AV466" s="3" t="n">
         <v>-0.0001825817053130568</v>
       </c>
+      <c r="AW466" s="1" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="AX466" s="2" t="n">
+        <v>0.001278305332359271</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -69685,6 +72487,12 @@
       <c r="AV467" s="3" t="n">
         <v>-0.002026635784597586</v>
       </c>
+      <c r="AW467" s="1" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="AX467" s="2" t="n">
+        <v>0.002320858717725464</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -69833,6 +72641,12 @@
       <c r="AV468" s="3" t="n">
         <v>-0.005145167217934603</v>
       </c>
+      <c r="AW468" s="1" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AX468" s="2" t="n">
+        <v>0.001108237901736281</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -69981,6 +72795,12 @@
       <c r="AV469" s="3" t="n">
         <v>-0.001867164577220638</v>
       </c>
+      <c r="AW469" s="1" t="n">
+        <v>0.0007481</v>
+      </c>
+      <c r="AX469" s="3" t="n">
+        <v>-0.0004008551576696326</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -70129,6 +72949,12 @@
       <c r="AV470" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW470" s="1" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="AX470" s="2" t="n">
+        <v>0.003405221339387063</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -70277,6 +73103,12 @@
       <c r="AV471" s="3" t="n">
         <v>-0.002004008016031982</v>
       </c>
+      <c r="AW471" s="1" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AX471" s="2" t="n">
+        <v>0.003012048192771136</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -70425,6 +73257,12 @@
       <c r="AV472" s="3" t="n">
         <v>-0.0002111932418163265</v>
       </c>
+      <c r="AW472" s="1" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="AX472" s="2" t="n">
+        <v>0.002112378538234112</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -70573,6 +73411,12 @@
       <c r="AV473" s="2" t="n">
         <v>0.005805515239477468</v>
       </c>
+      <c r="AW473" s="1" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="AX473" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -70721,6 +73565,12 @@
       <c r="AV474" s="2" t="n">
         <v>0.0002275830678198239</v>
       </c>
+      <c r="AW474" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="AX474" s="2" t="n">
+        <v>0.004095563139931731</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -70869,6 +73719,12 @@
       <c r="AV475" s="2" t="n">
         <v>0.001654259718775862</v>
       </c>
+      <c r="AW475" s="1" t="n">
+        <v>0.008496</v>
+      </c>
+      <c r="AX475" s="2" t="n">
+        <v>0.002241358971334189</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -71017,6 +73873,12 @@
       <c r="AV476" s="2" t="n">
         <v>0.0009842519685038969</v>
       </c>
+      <c r="AW476" s="1" t="n">
+        <v>0.08135000000000001</v>
+      </c>
+      <c r="AX476" s="3" t="n">
+        <v>-0.000122910521140562</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -71165,6 +74027,12 @@
       <c r="AV477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW477" s="1" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="AX477" s="2" t="n">
+        <v>0.0007299270072991896</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -71313,6 +74181,12 @@
       <c r="AV478" s="2" t="n">
         <v>0.007794820216243378</v>
       </c>
+      <c r="AW478" s="1" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="AX478" s="3" t="n">
+        <v>-0.005489021956087774</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -71461,6 +74335,12 @@
       <c r="AV479" s="2" t="n">
         <v>0.002860207365034138</v>
       </c>
+      <c r="AW479" s="1" t="n">
+        <v>0.008390999999999999</v>
+      </c>
+      <c r="AX479" s="3" t="n">
+        <v>-0.002852049910873612</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -71609,6 +74489,12 @@
       <c r="AV480" s="2" t="n">
         <v>0.006004366812227019</v>
       </c>
+      <c r="AW480" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="AX480" s="3" t="n">
+        <v>-0.008681497558328647</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -71757,6 +74643,12 @@
       <c r="AV481" s="2" t="n">
         <v>0.0006466632177961005</v>
       </c>
+      <c r="AW481" s="1" t="n">
+        <v>0.07772999999999999</v>
+      </c>
+      <c r="AX481" s="2" t="n">
+        <v>0.004652966265994562</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -71905,6 +74797,12 @@
       <c r="AV482" s="2" t="n">
         <v>0.0003962750148602969</v>
       </c>
+      <c r="AW482" s="1" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="AX482" s="2" t="n">
+        <v>0.004951475539710838</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -72053,6 +74951,12 @@
       <c r="AV483" s="3" t="n">
         <v>-0.00205549845837625</v>
       </c>
+      <c r="AW483" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="AX483" s="2" t="n">
+        <v>0.001029866117404695</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -72201,6 +75105,12 @@
       <c r="AV484" s="2" t="n">
         <v>0.008213552361396172</v>
       </c>
+      <c r="AW484" s="1" t="n">
+        <v>0.06862</v>
+      </c>
+      <c r="AX484" s="3" t="n">
+        <v>-0.001745708466685992</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -72349,6 +75259,12 @@
       <c r="AV485" s="2" t="n">
         <v>0.002014775016789719</v>
       </c>
+      <c r="AW485" s="1" t="n">
+        <v>0.0004479</v>
+      </c>
+      <c r="AX485" s="2" t="n">
+        <v>0.0006702412868632871</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -72497,6 +75413,12 @@
       <c r="AV486" s="2" t="n">
         <v>0.00539861895794099</v>
       </c>
+      <c r="AW486" s="1" t="n">
+        <v>0.07997</v>
+      </c>
+      <c r="AX486" s="3" t="n">
+        <v>-0.001373626373626361</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -72645,6 +75567,12 @@
       <c r="AV487" s="2" t="n">
         <v>0.001148105625717594</v>
       </c>
+      <c r="AW487" s="1" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="AX487" s="2" t="n">
+        <v>0.003440366972476992</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -72793,6 +75721,12 @@
       <c r="AV488" s="3" t="n">
         <v>-0.002454809194376387</v>
       </c>
+      <c r="AW488" s="1" t="n">
+        <v>0.08941</v>
+      </c>
+      <c r="AX488" s="2" t="n">
+        <v>0.0001118568232663311</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -72941,6 +75875,12 @@
       <c r="AV489" s="3" t="n">
         <v>-0.001871490954460383</v>
       </c>
+      <c r="AW489" s="1" t="n">
+        <v>0.04799</v>
+      </c>
+      <c r="AX489" s="3" t="n">
+        <v>-0.0002083333333333971</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -73089,6 +76029,12 @@
       <c r="AV490" s="2" t="n">
         <v>0.0005351886540005134</v>
       </c>
+      <c r="AW490" s="1" t="n">
+        <v>0.03739</v>
+      </c>
+      <c r="AX490" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -73237,6 +76183,12 @@
       <c r="AV491" s="3" t="n">
         <v>-0.005764042187883225</v>
       </c>
+      <c r="AW491" s="1" t="n">
+        <v>0.08105</v>
+      </c>
+      <c r="AX491" s="3" t="n">
+        <v>-0.0002467003823856682</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -73385,6 +76337,12 @@
       <c r="AV492" s="3" t="n">
         <v>-0.0003140703517588901</v>
       </c>
+      <c r="AW492" s="1" t="n">
+        <v>0.06368</v>
+      </c>
+      <c r="AX492" s="2" t="n">
+        <v>0.0003141690229344349</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -73533,6 +76491,12 @@
       <c r="AV493" s="2" t="n">
         <v>0.001893939393939481</v>
       </c>
+      <c r="AW493" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AX493" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -73681,6 +76645,12 @@
       <c r="AV494" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW494" s="1" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AX494" s="2" t="n">
+        <v>0.001086562839550768</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -73829,6 +76799,12 @@
       <c r="AV495" s="2" t="n">
         <v>0.001885606536769251</v>
       </c>
+      <c r="AW495" s="1" t="n">
+        <v>0.06372999999999999</v>
+      </c>
+      <c r="AX495" s="3" t="n">
+        <v>-0.0004705144291091946</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -73977,6 +76953,12 @@
       <c r="AV496" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW496" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AX496" s="2" t="n">
+        <v>0.0006842285323297228</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -74125,6 +77107,12 @@
       <c r="AV497" s="2" t="n">
         <v>0.006180625630675964</v>
       </c>
+      <c r="AW497" s="1" t="n">
+        <v>0.07983</v>
+      </c>
+      <c r="AX497" s="2" t="n">
+        <v>0.0007521624670929484</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -74273,6 +77261,12 @@
       <c r="AV498" s="3" t="n">
         <v>-0.0009727626459144248</v>
       </c>
+      <c r="AW498" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="AX498" s="2" t="n">
+        <v>0.000973709834469356</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -74421,6 +77415,12 @@
       <c r="AV499" s="2" t="n">
         <v>0.001905669366364858</v>
       </c>
+      <c r="AW499" s="1" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AX499" s="2" t="n">
+        <v>0.003090822634331864</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -74569,6 +77569,12 @@
       <c r="AV500" s="3" t="n">
         <v>-0.004887585532746794</v>
       </c>
+      <c r="AW500" s="1" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="AX500" s="3" t="n">
+        <v>-0.0002455795677798655</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -74717,6 +77723,12 @@
       <c r="AV501" s="3" t="n">
         <v>-0.001003009027081273</v>
       </c>
+      <c r="AW501" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AX501" s="2" t="n">
+        <v>0.002008032128514114</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -74865,6 +77877,12 @@
       <c r="AV502" s="2" t="n">
         <v>0.001804511278195598</v>
       </c>
+      <c r="AW502" s="1" t="n">
+        <v>0.003332</v>
+      </c>
+      <c r="AX502" s="2" t="n">
+        <v>0.0003002101471028817</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -75013,6 +78031,12 @@
       <c r="AV503" s="3" t="n">
         <v>-0.006607929515418424</v>
       </c>
+      <c r="AW503" s="1" t="n">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="AX503" s="2" t="n">
+        <v>0.007760532150776121</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -75161,6 +78185,12 @@
       <c r="AV504" s="2" t="n">
         <v>0.006293266205160308</v>
       </c>
+      <c r="AW504" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="AX504" s="3" t="n">
+        <v>-0.003752345215759784</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -75309,6 +78339,12 @@
       <c r="AV505" s="3" t="n">
         <v>-0.0007558578987149583</v>
       </c>
+      <c r="AW505" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="AX505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -75457,6 +78493,12 @@
       <c r="AV506" s="2" t="n">
         <v>0.002937720329024557</v>
       </c>
+      <c r="AW506" s="1" t="n">
+        <v>0.01709</v>
+      </c>
+      <c r="AX506" s="2" t="n">
+        <v>0.001171646162858972</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -75605,6 +78647,12 @@
       <c r="AV507" s="2" t="n">
         <v>0.001385041551246571</v>
       </c>
+      <c r="AW507" s="1" t="n">
+        <v>0.002902</v>
+      </c>
+      <c r="AX507" s="2" t="n">
+        <v>0.003457814661134172</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -75753,6 +78801,12 @@
       <c r="AV508" s="2" t="n">
         <v>0.001804239963915202</v>
       </c>
+      <c r="AW508" s="1" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX508" s="3" t="n">
+        <v>-0.0004502476361998603</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -75901,6 +78955,12 @@
       <c r="AV509" s="3" t="n">
         <v>-0.003437047756874144</v>
       </c>
+      <c r="AW509" s="1" t="n">
+        <v>0.05536</v>
+      </c>
+      <c r="AX509" s="2" t="n">
+        <v>0.00490107097476855</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -76049,6 +79109,12 @@
       <c r="AV510" s="3" t="n">
         <v>-0.001713502398903407</v>
       </c>
+      <c r="AW510" s="1" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AX510" s="3" t="n">
+        <v>-0.001029866117404695</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -76197,6 +79263,12 @@
       <c r="AV511" s="2" t="n">
         <v>0.0004933399111987959</v>
       </c>
+      <c r="AW511" s="1" t="n">
+        <v>0.04052</v>
+      </c>
+      <c r="AX511" s="3" t="n">
+        <v>-0.0009861932938855615</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -76345,6 +79417,12 @@
       <c r="AV512" s="2" t="n">
         <v>0.01075268817204302</v>
       </c>
+      <c r="AW512" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AX512" s="3" t="n">
+        <v>-0.01063829787234044</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -76493,6 +79571,12 @@
       <c r="AV513" s="2" t="n">
         <v>0.01314370450256127</v>
       </c>
+      <c r="AW513" s="1" t="n">
+        <v>0.015028</v>
+      </c>
+      <c r="AX513" s="3" t="n">
+        <v>-0.000199587519127106</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -76641,6 +79725,12 @@
       <c r="AV514" s="3" t="n">
         <v>-0.001141552511415558</v>
       </c>
+      <c r="AW514" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="AX514" s="2" t="n">
+        <v>0.00285714285714286</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -76789,6 +79879,12 @@
       <c r="AV515" s="2" t="n">
         <v>0.001853568118628413</v>
       </c>
+      <c r="AW515" s="1" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="AX515" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -76937,6 +80033,12 @@
       <c r="AV516" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW516" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="AX516" s="2" t="n">
+        <v>0.003731343283582099</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -77085,6 +80187,12 @@
       <c r="AV517" s="3" t="n">
         <v>-0.000130225289751287</v>
       </c>
+      <c r="AW517" s="1" t="n">
+        <v>0.007706</v>
+      </c>
+      <c r="AX517" s="2" t="n">
+        <v>0.003646783016410556</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -77233,6 +80341,12 @@
       <c r="AV518" s="3" t="n">
         <v>-0.004475703324808223</v>
       </c>
+      <c r="AW518" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="AX518" s="3" t="n">
+        <v>-0.001926782273603116</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -77381,6 +80495,12 @@
       <c r="AV519" s="3" t="n">
         <v>-0.001914791766395451</v>
       </c>
+      <c r="AW519" s="1" t="n">
+        <v>0.004194</v>
+      </c>
+      <c r="AX519" s="2" t="n">
+        <v>0.005755395683453169</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -77529,6 +80649,12 @@
       <c r="AV520" s="3" t="n">
         <v>-0.0008605851979347097</v>
       </c>
+      <c r="AW520" s="1" t="n">
+        <v>0.001164</v>
+      </c>
+      <c r="AX520" s="2" t="n">
+        <v>0.002583979328165531</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -77677,6 +80803,12 @@
       <c r="AV521" s="3" t="n">
         <v>-0.001485884101040058</v>
       </c>
+      <c r="AW521" s="1" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="AX521" s="3" t="n">
+        <v>-0.003720238095238072</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -77825,6 +80957,12 @@
       <c r="AV522" s="3" t="n">
         <v>-0.003478260869565156</v>
       </c>
+      <c r="AW522" s="1" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="AX522" s="2" t="n">
+        <v>0.002181500872600432</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -77973,6 +81111,12 @@
       <c r="AV523" s="2" t="n">
         <v>0.001420454545454389</v>
       </c>
+      <c r="AW523" s="1" t="n">
+        <v>0.07084</v>
+      </c>
+      <c r="AX523" s="2" t="n">
+        <v>0.004822695035461093</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -78121,6 +81265,12 @@
       <c r="AV524" s="3" t="n">
         <v>-0.01891447368421061</v>
       </c>
+      <c r="AW524" s="1" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="AX524" s="2" t="n">
+        <v>0.002514668901927956</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -78269,6 +81419,12 @@
       <c r="AV525" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW525" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="AX525" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -78417,6 +81573,12 @@
       <c r="AV526" s="2" t="n">
         <v>0.000150048765849051</v>
       </c>
+      <c r="AW526" s="1" t="n">
+        <v>0.13273</v>
+      </c>
+      <c r="AX526" s="3" t="n">
+        <v>-0.004350761383242254</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -78565,6 +81727,12 @@
       <c r="AV527" s="2" t="n">
         <v>0.002795899347623533</v>
       </c>
+      <c r="AW527" s="1" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AX527" s="2" t="n">
+        <v>0.0006970260223047237</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -78713,6 +81881,12 @@
       <c r="AV528" s="2" t="n">
         <v>0.001087350489307802</v>
       </c>
+      <c r="AW528" s="1" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="AX528" s="2" t="n">
+        <v>0.002172338884866001</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -78861,6 +82035,12 @@
       <c r="AV529" s="2" t="n">
         <v>0.0005524861878453172</v>
       </c>
+      <c r="AW529" s="1" t="n">
+        <v>0.0007270999999999999</v>
+      </c>
+      <c r="AX529" s="2" t="n">
+        <v>0.003727222528989375</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -79009,6 +82189,12 @@
       <c r="AV530" s="2" t="n">
         <v>0.0007147962830592162</v>
       </c>
+      <c r="AW530" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AX530" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -79157,6 +82343,12 @@
       <c r="AV531" s="2" t="n">
         <v>0.003023431594860169</v>
       </c>
+      <c r="AW531" s="1" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="AX531" s="2" t="n">
+        <v>0.001507159005275058</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -79305,6 +82497,12 @@
       <c r="AV532" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW532" s="1" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="AX532" s="2" t="n">
+        <v>0.0008424599831508245</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -79453,6 +82651,12 @@
       <c r="AV533" s="2" t="n">
         <v>0.003000750187546895</v>
       </c>
+      <c r="AW533" s="1" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="AX533" s="2" t="n">
+        <v>0.001308900523560221</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -79601,6 +82805,12 @@
       <c r="AV534" s="3" t="n">
         <v>-0.0006644518272424518</v>
       </c>
+      <c r="AW534" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="AX534" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -79749,6 +82959,12 @@
       <c r="AV535" s="3" t="n">
         <v>-0.002910360884749792</v>
       </c>
+      <c r="AW535" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="AX535" s="3" t="n">
+        <v>-0.006421482778750671</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -79897,6 +83113,12 @@
       <c r="AV536" s="2" t="n">
         <v>0.002207062600321146</v>
       </c>
+      <c r="AW536" s="1" t="n">
+        <v>0.005004</v>
+      </c>
+      <c r="AX536" s="2" t="n">
+        <v>0.001801801801801694</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -80045,6 +83267,12 @@
       <c r="AV537" s="3" t="n">
         <v>-0.000341413451689959</v>
       </c>
+      <c r="AW537" s="1" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AX537" s="2" t="n">
+        <v>0.004781420765027364</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -80193,6 +83421,12 @@
       <c r="AV538" s="3" t="n">
         <v>-0.003014318010550121</v>
       </c>
+      <c r="AW538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="AX538" s="2" t="n">
+        <v>0.003023431594860174</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -80341,6 +83575,12 @@
       <c r="AV539" s="3" t="n">
         <v>-0.0007920792079208972</v>
       </c>
+      <c r="AW539" s="1" t="n">
+        <v>0.02515</v>
+      </c>
+      <c r="AX539" s="3" t="n">
+        <v>-0.003170828378914</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -80489,6 +83729,12 @@
       <c r="AV540" s="2" t="n">
         <v>0.003346838118724603</v>
       </c>
+      <c r="AW540" s="1" t="n">
+        <v>0.05706</v>
+      </c>
+      <c r="AX540" s="2" t="n">
+        <v>0.00175561797752814</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -80637,6 +83883,12 @@
       <c r="AV541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW541" s="1" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="AX541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -80785,6 +84037,12 @@
       <c r="AV542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AW542" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="AX542" s="2" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -80933,6 +84191,12 @@
       <c r="AV543" s="2" t="n">
         <v>0.01008174386920973</v>
       </c>
+      <c r="AW543" s="1" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="AX543" s="2" t="n">
+        <v>0.001079039654707337</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
